--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>225225</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>8.69499969482422</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>8.28999996185303</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>8.52499961853027</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>8.42000007629395</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>595183</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>8.43000030517578</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>7.73999977111816</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>8.40999984741211</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>8.04500007629395</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>268498</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>8.42500019073486</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>8.0649995803833</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>8.06999969482422</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>8.32999992370605</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>508631</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>8.39999961853027</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>8.36499977111816</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>90776</v>
+        <v>106575</v>
       </c>
       <c r="C2715" t="n">
-        <v>9.22000026702881</v>
+        <v>9.21500015258789</v>
       </c>
       <c r="D2715" t="n">
-        <v>8.99499988555908</v>
+        <v>9.01500034332275</v>
       </c>
       <c r="E2715" t="n">
+        <v>9.10499954223633</v>
+      </c>
+      <c r="F2715" t="n">
         <v>9.08500003814697</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>9.04500007629395</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>503117</v>
+        <v>90776</v>
       </c>
       <c r="C2716" t="n">
-        <v>9.25</v>
+        <v>9.22000026702881</v>
       </c>
       <c r="D2716" t="n">
-        <v>8.67000007629395</v>
+        <v>8.99499988555908</v>
       </c>
       <c r="E2716" t="n">
-        <v>9.25</v>
+        <v>9.08500003814697</v>
       </c>
       <c r="F2716" t="n">
-        <v>8.73999977111816</v>
+        <v>9.04500007629395</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>196053</v>
+        <v>503117</v>
       </c>
       <c r="C2717" t="n">
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
       <c r="D2717" t="n">
-        <v>8.53999996185303</v>
+        <v>8.67000007629395</v>
       </c>
       <c r="E2717" t="n">
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
       <c r="F2717" t="n">
-        <v>8.5649995803833</v>
+        <v>8.73999977111816</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>202506</v>
+        <v>196053</v>
       </c>
       <c r="C2718" t="n">
-        <v>8.8100004196167</v>
+        <v>8.75</v>
       </c>
       <c r="D2718" t="n">
-        <v>8.57999992370605</v>
+        <v>8.53999996185303</v>
       </c>
       <c r="E2718" t="n">
-        <v>8.60000038146973</v>
+        <v>8.75</v>
       </c>
       <c r="F2718" t="n">
-        <v>8.57999992370605</v>
+        <v>8.5649995803833</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>225225</v>
+        <v>202506</v>
       </c>
       <c r="C2719" t="n">
-        <v>8.69499969482422</v>
+        <v>8.8100004196167</v>
       </c>
       <c r="D2719" t="n">
-        <v>8.28999996185303</v>
+        <v>8.57999992370605</v>
       </c>
       <c r="E2719" t="n">
-        <v>8.52499961853027</v>
+        <v>8.60000038146973</v>
       </c>
       <c r="F2719" t="n">
-        <v>8.42000007629395</v>
+        <v>8.57999992370605</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>595183</v>
+        <v>225225</v>
       </c>
       <c r="C2720" t="n">
-        <v>8.43000030517578</v>
+        <v>8.69499969482422</v>
       </c>
       <c r="D2720" t="n">
-        <v>7.73999977111816</v>
+        <v>8.28999996185303</v>
       </c>
       <c r="E2720" t="n">
-        <v>8.40999984741211</v>
+        <v>8.52499961853027</v>
       </c>
       <c r="F2720" t="n">
-        <v>8.04500007629395</v>
+        <v>8.42000007629395</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>268498</v>
+        <v>595183</v>
       </c>
       <c r="C2721" t="n">
-        <v>8.42500019073486</v>
+        <v>8.43000030517578</v>
       </c>
       <c r="D2721" t="n">
-        <v>8.0649995803833</v>
+        <v>7.73999977111816</v>
       </c>
       <c r="E2721" t="n">
-        <v>8.06999969482422</v>
+        <v>8.40999984741211</v>
       </c>
       <c r="F2721" t="n">
-        <v>8.32999992370605</v>
+        <v>8.04500007629395</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>508631</v>
+        <v>268498</v>
       </c>
       <c r="C2722" t="n">
-        <v>8.39999961853027</v>
+        <v>8.42500019073486</v>
       </c>
       <c r="D2722" t="n">
+        <v>8.0649995803833</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>8.06999969482422</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>8.32999992370605</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>845196</v>
+      </c>
+      <c r="C2723" t="n">
         <v>8</v>
       </c>
-      <c r="E2722" t="n">
-        <v>8.36499977111816</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>8</v>
-      </c>
-      <c r="G2722" t="s">
+      <c r="D2723" t="n">
+        <v>7.51999998092651</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>7.99499988555908</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>7.60500001907349</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -421,7 +421,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G2" t="n">
-        <v>18.2763519287109</v>
+        <v>18.2763500213623</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G3" t="n">
-        <v>18.01096534729</v>
+        <v>18.0109634399414</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>17.9401931762695</v>
+        <v>17.9401950836182</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>17.6836528778076</v>
+        <v>17.6836547851562</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G7" t="n">
-        <v>18.249813079834</v>
+        <v>18.2498111724854</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G8" t="n">
-        <v>19.4086742401123</v>
+        <v>19.4086723327637</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G9" t="n">
-        <v>19.1344356536865</v>
+        <v>19.1344375610352</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G11" t="n">
-        <v>18.462121963501</v>
+        <v>18.4621238708496</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G13" t="n">
-        <v>18.0994243621826</v>
+        <v>18.0994262695312</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G14" t="n">
-        <v>17.6394214630127</v>
+        <v>17.6394233703613</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G15" t="n">
-        <v>17.5686550140381</v>
+        <v>17.5686511993408</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G16" t="n">
-        <v>18.1878890991211</v>
+        <v>18.1878871917725</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G17" t="n">
-        <v>18.0994243621826</v>
+        <v>18.0994262695312</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>18.2232761383057</v>
+        <v>18.223274230957</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>17.7632713317871</v>
+        <v>17.7632694244385</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>17.9578838348389</v>
+        <v>17.9578857421875</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G25" t="n">
-        <v>18.2586555480957</v>
+        <v>18.2586574554443</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G31" t="n">
-        <v>17.0201854705811</v>
+        <v>17.0201835632324</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G33" t="n">
-        <v>17.6305751800537</v>
+        <v>17.6305732727051</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>20.8099994659424</v>
       </c>
       <c r="G35" t="n">
-        <v>18.4090423583984</v>
+        <v>18.4090442657471</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>18.9752044677734</v>
+        <v>18.9752063751221</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>20.5</v>
       </c>
       <c r="G38" t="n">
-        <v>18.1348114013672</v>
+        <v>18.1348133087158</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G39" t="n">
-        <v>17.3121109008789</v>
+        <v>17.3121089935303</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G40" t="n">
-        <v>17.7632713317871</v>
+        <v>17.7632694244385</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G41" t="n">
-        <v>17.9048099517822</v>
+        <v>17.9048080444336</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G42" t="n">
-        <v>18.3471221923828</v>
+        <v>18.3471183776855</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G44" t="n">
-        <v>19.001745223999</v>
+        <v>19.0017433166504</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>21.3099994659424</v>
       </c>
       <c r="G45" t="n">
-        <v>18.8513565063477</v>
+        <v>18.8513584136963</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>19.9482917785645</v>
+        <v>19.9482936859131</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>19.7271385192871</v>
+        <v>19.7271347045898</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G50" t="n">
-        <v>19.3379039764404</v>
+        <v>19.3379020690918</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G51" t="n">
-        <v>19.6475200653076</v>
+        <v>19.647518157959</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G53" t="n">
-        <v>19.1167430877686</v>
+        <v>19.1167469024658</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G54" t="n">
-        <v>19.3379039764404</v>
+        <v>19.3379020690918</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G55" t="n">
-        <v>19.4440574645996</v>
+        <v>19.444055557251</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>20.0367565155029</v>
+        <v>20.0367546081543</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>22.8099994659424</v>
       </c>
       <c r="G57" t="n">
-        <v>20.1782932281494</v>
+        <v>20.178295135498</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>22.0100002288818</v>
       </c>
       <c r="G59" t="n">
-        <v>19.4705963134766</v>
+        <v>19.4705944061279</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G60" t="n">
-        <v>18.9663581848145</v>
+        <v>18.9663619995117</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G61" t="n">
-        <v>19.4794387817383</v>
+        <v>19.4794425964355</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G63" t="n">
-        <v>19.8686771392822</v>
+        <v>19.8686752319336</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G68" t="n">
-        <v>18.5151977539062</v>
+        <v>18.5152015686035</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>18.9309749603271</v>
+        <v>18.9309730529785</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G70" t="n">
-        <v>18.8955898284912</v>
+        <v>18.8955879211426</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G71" t="n">
-        <v>18.5240478515625</v>
+        <v>18.5240459442139</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>21.25</v>
       </c>
       <c r="G74" t="n">
-        <v>18.7982788085938</v>
+        <v>18.7982807159424</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G75" t="n">
-        <v>18.8778953552246</v>
+        <v>18.8778972625732</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G77" t="n">
-        <v>18.8071250915527</v>
+        <v>18.8071269989014</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G78" t="n">
-        <v>18.3205814361572</v>
+        <v>18.3205833435059</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G80" t="n">
-        <v>17.8251953125</v>
+        <v>17.8251914978027</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G82" t="n">
-        <v>18.0640392303467</v>
+        <v>18.0640411376953</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>18.3117370605469</v>
+        <v>18.3117389678955</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G84" t="n">
-        <v>17.8782691955566</v>
+        <v>17.878267288208</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>18.0021171569824</v>
+        <v>18.0021190643311</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G86" t="n">
-        <v>17.7190380096436</v>
+        <v>17.7190399169922</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G87" t="n">
-        <v>17.9048099517822</v>
+        <v>17.9048080444336</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G89" t="n">
-        <v>17.1440277099609</v>
+        <v>17.1440296173096</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G91" t="n">
-        <v>17.9844264984131</v>
+        <v>17.9844245910645</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>17.6394214630127</v>
+        <v>17.6394233703613</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>21.25</v>
       </c>
       <c r="G95" t="n">
-        <v>18.7982788085938</v>
+        <v>18.7982807159424</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>18.0640392303467</v>
+        <v>18.0640411376953</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>20.2700004577637</v>
       </c>
       <c r="G97" t="n">
-        <v>17.9313507080078</v>
+        <v>17.9313488006592</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G99" t="n">
-        <v>17.6482696533203</v>
+        <v>17.648265838623</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G102" t="n">
-        <v>17.7025985717773</v>
+        <v>17.7025966644287</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G104" t="n">
-        <v>17.530553817749</v>
+        <v>17.5305519104004</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G107" t="n">
-        <v>17.3041763305664</v>
+        <v>17.304178237915</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>19.25</v>
       </c>
       <c r="G110" t="n">
-        <v>17.4309463500977</v>
+        <v>17.430944442749</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>17.747875213623</v>
+        <v>17.7478733062744</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G113" t="n">
-        <v>17.6844902038574</v>
+        <v>17.6844882965088</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G115" t="n">
-        <v>16.7155990600586</v>
+        <v>16.71559715271</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G116" t="n">
-        <v>16.5435523986816</v>
+        <v>16.5435543060303</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G117" t="n">
-        <v>17.0415821075439</v>
+        <v>17.0415802001953</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G120" t="n">
-        <v>17.9380264282227</v>
+        <v>17.9380283355713</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G126" t="n">
-        <v>16.6793766021729</v>
+        <v>16.6793785095215</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>18.25</v>
       </c>
       <c r="G128" t="n">
-        <v>16.5254421234131</v>
+        <v>16.5254440307617</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G130" t="n">
-        <v>16.8061504364014</v>
+        <v>16.8061485290527</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>17.75</v>
       </c>
       <c r="G132" t="n">
-        <v>16.0726928710938</v>
+        <v>16.0726909637451</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G133" t="n">
-        <v>15.8734817504883</v>
+        <v>15.8734798431396</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G134" t="n">
-        <v>16.3624534606934</v>
+        <v>16.3624515533447</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G137" t="n">
-        <v>17.0959091186523</v>
+        <v>17.095911026001</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G138" t="n">
-        <v>17.1321334838867</v>
+        <v>17.1321315765381</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G144" t="n">
-        <v>17.9018096923828</v>
+        <v>17.9018077850342</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G145" t="n">
-        <v>18.1372394561768</v>
+        <v>18.1372413635254</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>17.9289703369141</v>
+        <v>17.9289722442627</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G150" t="n">
-        <v>19.2147903442383</v>
+        <v>19.2147884368896</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>20.5699996948242</v>
       </c>
       <c r="G151" t="n">
-        <v>18.6262130737305</v>
+        <v>18.6262111663818</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G152" t="n">
-        <v>18.4994430541992</v>
+        <v>18.4994411468506</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G157" t="n">
-        <v>18.4994430541992</v>
+        <v>18.4994411468506</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G158" t="n">
-        <v>18.8073139190674</v>
+        <v>18.8073120117188</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G165" t="n">
-        <v>18.7529811859131</v>
+        <v>18.7529830932617</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G168" t="n">
-        <v>18.6081027984619</v>
+        <v>18.6081008911133</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6533794403076</v>
+        <v>18.653377532959</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G171" t="n">
-        <v>18.5175533294678</v>
+        <v>18.5175514221191</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>18.6081027984619</v>
+        <v>18.6081008911133</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G181" t="n">
-        <v>19.3143939971924</v>
+        <v>19.314395904541</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G182" t="n">
-        <v>18.8888072967529</v>
+        <v>18.8888092041016</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G184" t="n">
-        <v>19.1332950592041</v>
+        <v>19.1332931518555</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>19.160457611084</v>
+        <v>19.1604595184326</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G187" t="n">
-        <v>19.9391918182373</v>
+        <v>19.9391937255859</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>20.4643840789795</v>
+        <v>20.4643859863281</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>20.8446979522705</v>
+        <v>20.8446960449219</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G197" t="n">
-        <v>20.7994232177734</v>
+        <v>20.7994213104248</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G198" t="n">
-        <v>20.4009990692139</v>
+        <v>20.4010009765625</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G199" t="n">
-        <v>20.1021842956543</v>
+        <v>20.1021823883057</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>20.3647785186768</v>
+        <v>20.3647804260254</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>20.4191074371338</v>
+        <v>20.4191093444824</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>20.0116329193115</v>
+        <v>20.0116310119629</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G206" t="n">
-        <v>20.2651710510254</v>
+        <v>20.2651748657227</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>20.3285579681396</v>
+        <v>20.3285598754883</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G209" t="n">
-        <v>20.03879737854</v>
+        <v>20.0387954711914</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>22.25</v>
       </c>
       <c r="G210" t="n">
-        <v>20.1474590301514</v>
+        <v>20.1474571228027</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G211" t="n">
-        <v>20.2289524078369</v>
+        <v>20.2289543151855</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G214" t="n">
-        <v>20.1836814880371</v>
+        <v>20.1836795806885</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G215" t="n">
-        <v>20.03879737854</v>
+        <v>20.0387954711914</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>21.5900001525879</v>
       </c>
       <c r="G216" t="n">
-        <v>19.549825668335</v>
+        <v>19.5498275756836</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G217" t="n">
-        <v>19.4140014648438</v>
+        <v>19.4140033721924</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G219" t="n">
-        <v>19.7218704223633</v>
+        <v>19.7218723297119</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G220" t="n">
-        <v>19.7943134307861</v>
+        <v>19.7943115234375</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G221" t="n">
-        <v>19.5226593017578</v>
+        <v>19.5226612091064</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G224" t="n">
-        <v>19.7490367889404</v>
+        <v>19.7490348815918</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G226" t="n">
-        <v>18.0919647216797</v>
+        <v>18.0919628143311</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G227" t="n">
-        <v>18.3002300262451</v>
+        <v>18.3002281188965</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G231" t="n">
-        <v>17.7388153076172</v>
+        <v>17.7388172149658</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G232" t="n">
-        <v>17.8565349578857</v>
+        <v>17.8565330505371</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>17.8203125</v>
+        <v>17.8203105926514</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>17.6392116546631</v>
+        <v>17.6392097473145</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G237" t="n">
-        <v>18.8073139190674</v>
+        <v>18.8073120117188</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>19.2872295379639</v>
+        <v>19.2872276306152</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G242" t="n">
-        <v>19.3958911895752</v>
+        <v>19.3958892822266</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>19.3777809143066</v>
+        <v>19.377779006958</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G244" t="n">
-        <v>19.1151866912842</v>
+        <v>19.1151847839355</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G245" t="n">
-        <v>19.5860443115234</v>
+        <v>19.5860462188721</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>21.2700004577637</v>
       </c>
       <c r="G246" t="n">
-        <v>19.2600650787354</v>
+        <v>19.2600631713867</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G248" t="n">
-        <v>20.2651710510254</v>
+        <v>20.2651748657227</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G250" t="n">
-        <v>20.2651710510254</v>
+        <v>20.2651748657227</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G251" t="n">
-        <v>20.3466682434082</v>
+        <v>20.3466701507568</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>20.2380065917969</v>
+        <v>20.2380084991455</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G253" t="n">
-        <v>20.1293468475342</v>
+        <v>20.1293487548828</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G254" t="n">
-        <v>20.1836814880371</v>
+        <v>20.1836795806885</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>20.2289524078369</v>
+        <v>20.2289543151855</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G258" t="n">
-        <v>20.8084774017334</v>
+        <v>20.8084754943848</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G260" t="n">
-        <v>21.4785480499268</v>
+        <v>21.4785461425781</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G264" t="n">
-        <v>22.2572822570801</v>
+        <v>22.2572803497314</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>24.6299991607666</v>
       </c>
       <c r="G266" t="n">
-        <v>22.3025569915771</v>
+        <v>22.3025550842285</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>22.2753925323486</v>
+        <v>22.275390625</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G271" t="n">
-        <v>23.0722351074219</v>
+        <v>23.0722332000732</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>25.5699996948242</v>
       </c>
       <c r="G273" t="n">
-        <v>23.1537303924561</v>
+        <v>23.1537284851074</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G276" t="n">
-        <v>22.3568878173828</v>
+        <v>22.3568859100342</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>26.2299995422363</v>
       </c>
       <c r="G281" t="n">
-        <v>23.7513637542725</v>
+        <v>23.7513618469238</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>26.6399993896484</v>
       </c>
       <c r="G282" t="n">
-        <v>24.1226196289062</v>
+        <v>24.1226215362549</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G283" t="n">
-        <v>23.6427040100098</v>
+        <v>23.6427021026611</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G284" t="n">
-        <v>23.6879768371582</v>
+        <v>23.6879749298096</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G287" t="n">
-        <v>23.7423076629639</v>
+        <v>23.7423057556152</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>23.6879768371582</v>
+        <v>23.6879749298096</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>26.1700000762939</v>
       </c>
       <c r="G292" t="n">
-        <v>23.6970329284668</v>
+        <v>23.6970348358154</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>26.5200004577637</v>
       </c>
       <c r="G294" t="n">
-        <v>24.0139598846436</v>
+        <v>24.0139579772949</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>23.9777374267578</v>
+        <v>23.9777355194092</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G299" t="n">
-        <v>24.430492401123</v>
+        <v>24.4304904937744</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>24.7655258178711</v>
+        <v>24.7655277252197</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G304" t="n">
-        <v>25.4265441894531</v>
+        <v>25.4265460968018</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>28.2900009155273</v>
       </c>
       <c r="G305" t="n">
-        <v>25.6167011260986</v>
+        <v>25.6167030334473</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>28.3299999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>25.6529216766357</v>
+        <v>25.6529235839844</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>25.5352077484131</v>
+        <v>25.5352058410645</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G310" t="n">
-        <v>24.955680847168</v>
+        <v>24.9556827545166</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>27.5</v>
       </c>
       <c r="G311" t="n">
-        <v>24.9013538360596</v>
+        <v>24.9013557434082</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>27.3899993896484</v>
       </c>
       <c r="G313" t="n">
-        <v>24.8017482757568</v>
+        <v>24.8017501831055</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>27.1900005340576</v>
       </c>
       <c r="G314" t="n">
-        <v>24.6206474304199</v>
+        <v>24.6206455230713</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>28.0200004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>25.3722171783447</v>
+        <v>25.3722152709961</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>25.6257514953613</v>
+        <v>25.62575340271</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G318" t="n">
-        <v>25.2273349761963</v>
+        <v>25.2273368835449</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>25.173002243042</v>
+        <v>25.1730041503906</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>25.399377822876</v>
+        <v>25.3993759155273</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G322" t="n">
-        <v>25.4265441894531</v>
+        <v>25.4265460968018</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>27.75</v>
       </c>
       <c r="G325" t="n">
-        <v>25.1277294158936</v>
+        <v>25.1277275085449</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>28.4300003051758</v>
       </c>
       <c r="G326" t="n">
-        <v>25.7434711456299</v>
+        <v>25.7434692382812</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>28.1700000762939</v>
       </c>
       <c r="G329" t="n">
-        <v>25.5080413818359</v>
+        <v>25.5080394744873</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>25.2635555267334</v>
+        <v>25.2635536193848</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G332" t="n">
-        <v>24.7836360931396</v>
+        <v>24.7836380004883</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>24.7655258178711</v>
+        <v>24.7655277252197</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G343" t="n">
-        <v>26.676139831543</v>
+        <v>26.6761379241943</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>26.6670837402344</v>
+        <v>26.667085647583</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G347" t="n">
-        <v>26.9115695953369</v>
+        <v>26.9115657806396</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>28.5300006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>25.8340225219727</v>
+        <v>25.8340244293213</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>25.2299995422363</v>
       </c>
       <c r="G359" t="n">
-        <v>23.2202472686768</v>
+        <v>23.2202453613281</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>22.9625492095947</v>
+        <v>22.9625511169434</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>22.8705158233643</v>
+        <v>22.8705177307129</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G363" t="n">
-        <v>22.8613147735596</v>
+        <v>22.8613128662109</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>22.2262763977051</v>
+        <v>22.2262783050537</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>22.3643264770508</v>
+        <v>22.3643283843994</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G375" t="n">
-        <v>22.8797206878662</v>
+        <v>22.8797225952148</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G380" t="n">
-        <v>23.0269737243652</v>
+        <v>23.0269756317139</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G381" t="n">
-        <v>22.6036167144775</v>
+        <v>22.6036186218262</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>23</v>
       </c>
       <c r="G389" t="n">
-        <v>21.1678848266602</v>
+        <v>21.1678829193115</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>23</v>
       </c>
       <c r="G390" t="n">
-        <v>21.1678848266602</v>
+        <v>21.1678829193115</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G391" t="n">
-        <v>21.2046985626221</v>
+        <v>21.2046966552734</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G394" t="n">
-        <v>21.5084075927734</v>
+        <v>21.5084095001221</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G396" t="n">
-        <v>21.8857517242432</v>
+        <v>21.8857498168945</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G398" t="n">
-        <v>22.6220245361328</v>
+        <v>22.6220226287842</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G402" t="n">
-        <v>22.5299911499023</v>
+        <v>22.5299892425537</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G407" t="n">
-        <v>21.4255790710449</v>
+        <v>21.4255809783936</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G412" t="n">
-        <v>22.3551273345947</v>
+        <v>22.3551254272461</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G415" t="n">
-        <v>22.6220245361328</v>
+        <v>22.6220226287842</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>24.2700004577637</v>
       </c>
       <c r="G417" t="n">
-        <v>22.3367176055908</v>
+        <v>22.3367195129395</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>24.0300006866455</v>
       </c>
       <c r="G418" t="n">
-        <v>22.1158351898193</v>
+        <v>22.115837097168</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>21.7661056518555</v>
+        <v>21.7661037445068</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>23.9699993133545</v>
       </c>
       <c r="G420" t="n">
-        <v>22.0606155395508</v>
+        <v>22.0606136322021</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>21.9961929321289</v>
+        <v>21.9961910247803</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G426" t="n">
-        <v>22.0053958892822</v>
+        <v>22.0053939819336</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G428" t="n">
-        <v>22.3551273345947</v>
+        <v>22.3551254272461</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G429" t="n">
-        <v>22.0053958892822</v>
+        <v>22.0053939819336</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G433" t="n">
-        <v>21.7753086090088</v>
+        <v>21.7753105163574</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G435" t="n">
-        <v>21.9961929321289</v>
+        <v>21.9961910247803</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>21.9041576385498</v>
+        <v>21.9041557312012</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G439" t="n">
-        <v>21.0574398040771</v>
+        <v>21.0574378967285</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>20.7997455596924</v>
+        <v>20.799747467041</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>22.9300003051758</v>
       </c>
       <c r="G442" t="n">
-        <v>21.1034622192383</v>
+        <v>21.1034603118896</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G446" t="n">
-        <v>22.0974292755127</v>
+        <v>22.0974311828613</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G452" t="n">
-        <v>20.9746112823486</v>
+        <v>20.9746131896973</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>20.7997455596924</v>
+        <v>20.799747467041</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G455" t="n">
-        <v>21.1402721405029</v>
+        <v>21.1402702331543</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>22.5</v>
       </c>
       <c r="G457" t="n">
-        <v>20.7077102661133</v>
+        <v>20.7077121734619</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>19.9714374542236</v>
+        <v>19.9714393615723</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>22.5</v>
       </c>
       <c r="G477" t="n">
-        <v>20.7077102661133</v>
+        <v>20.7077121734619</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>21.9099998474121</v>
       </c>
       <c r="G479" t="n">
-        <v>20.1647090911865</v>
+        <v>20.1647071838379</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>19.6953353881836</v>
+        <v>19.695333480835</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>20.4316101074219</v>
+        <v>20.4316082000732</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G489" t="n">
-        <v>20.5696582794189</v>
+        <v>20.5696601867676</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>20.661693572998</v>
+        <v>20.6616954803467</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>22.5</v>
       </c>
       <c r="G493" t="n">
-        <v>20.7077102661133</v>
+        <v>20.7077121734619</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G502" t="n">
-        <v>20.7721347808838</v>
+        <v>20.7721366882324</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G504" t="n">
-        <v>19.7965717315674</v>
+        <v>19.796573638916</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G505" t="n">
-        <v>19.8609943389893</v>
+        <v>19.8609962463379</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>20.2291355133057</v>
+        <v>20.229133605957</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>20.523645401001</v>
+        <v>20.5236434936523</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>20.4316101074219</v>
+        <v>20.4316082000732</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G524" t="n">
-        <v>20.1739120483398</v>
+        <v>20.1739139556885</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>21.2599182128906</v>
+        <v>21.259916305542</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>21.2599182128906</v>
+        <v>21.259916305542</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G544" t="n">
-        <v>20.5604553222656</v>
+        <v>20.5604572296143</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>23.4699993133545</v>
       </c>
       <c r="G554" t="n">
-        <v>21.6004428863525</v>
+        <v>21.6004447937012</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G555" t="n">
-        <v>20.6248798370361</v>
+        <v>20.6248817443848</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>22.0300006866455</v>
       </c>
       <c r="G556" t="n">
-        <v>20.2751522064209</v>
+        <v>20.2751502990723</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>19.9714374542236</v>
+        <v>19.9714393615723</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>19.649320602417</v>
+        <v>19.6493186950684</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G561" t="n">
-        <v>19.9990482330322</v>
+        <v>19.9990501403809</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G563" t="n">
-        <v>19.8609943389893</v>
+        <v>19.8609962463379</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G566" t="n">
-        <v>20.5696582794189</v>
+        <v>20.5696601867676</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G568" t="n">
-        <v>20.523645401001</v>
+        <v>20.5236434936523</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G569" t="n">
-        <v>20.3763885498047</v>
+        <v>20.3763866424561</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>20.6156749725342</v>
+        <v>20.6156768798828</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G582" t="n">
-        <v>20.9746112823486</v>
+        <v>20.9746131896973</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G583" t="n">
-        <v>21.2046985626221</v>
+        <v>21.2046966552734</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>21.2783260345459</v>
+        <v>21.2783241271973</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G586" t="n">
-        <v>21.7753086090088</v>
+        <v>21.7753105163574</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>21.536018371582</v>
+        <v>21.5360202789307</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>21.536018371582</v>
+        <v>21.5360202789307</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G589" t="n">
-        <v>21.7937183380127</v>
+        <v>21.7937164306641</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G592" t="n">
-        <v>22.4195518493652</v>
+        <v>22.4195499420166</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G595" t="n">
-        <v>22.8797206878662</v>
+        <v>22.8797225952148</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>22.9165325164795</v>
+        <v>22.9165344238281</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G601" t="n">
-        <v>22.6864490509033</v>
+        <v>22.6864471435547</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>22.7324676513672</v>
+        <v>22.7324657440186</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G603" t="n">
-        <v>22.8337020874023</v>
+        <v>22.8337001800537</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G604" t="n">
-        <v>22.7692794799805</v>
+        <v>22.7692775726318</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>22.9165325164795</v>
+        <v>22.9165344238281</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>7.46000003814697</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>505357</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>7.67500019073486</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>7.21000003814697</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>7.36999988555908</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>7.61999988555908</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>7.61999988555908</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -447,7 +447,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G3" t="n">
-        <v>18.0109634399414</v>
+        <v>18.01096534729</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G9" t="n">
-        <v>19.1344375610352</v>
+        <v>19.1344356536865</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G10" t="n">
-        <v>18.8425102233887</v>
+        <v>18.84250831604</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G11" t="n">
-        <v>18.4621238708496</v>
+        <v>18.462121963501</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G13" t="n">
-        <v>18.0994262695312</v>
+        <v>18.0994243621826</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G14" t="n">
-        <v>17.6394233703613</v>
+        <v>17.6394214630127</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G16" t="n">
-        <v>18.1878871917725</v>
+        <v>18.1878890991211</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G17" t="n">
-        <v>18.0994262695312</v>
+        <v>18.0994243621826</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G18" t="n">
-        <v>18.4798145294189</v>
+        <v>18.4798126220703</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>17.7632694244385</v>
+        <v>17.7632675170898</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G22" t="n">
-        <v>18.6744346618652</v>
+        <v>18.6744327545166</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>17.9578857421875</v>
+        <v>17.9578838348389</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>17.1617221832275</v>
+        <v>17.1617240905762</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G30" t="n">
-        <v>16.6486415863037</v>
+        <v>16.6486396789551</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G31" t="n">
-        <v>17.0201835632324</v>
+        <v>17.0201854705811</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G32" t="n">
-        <v>17.48903465271</v>
+        <v>17.4890365600586</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G33" t="n">
-        <v>17.6305732727051</v>
+        <v>17.6305751800537</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G34" t="n">
-        <v>18.4798145294189</v>
+        <v>18.4798126220703</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>20.8099994659424</v>
       </c>
       <c r="G35" t="n">
-        <v>18.4090442657471</v>
+        <v>18.4090461730957</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>18.9752063751221</v>
+        <v>18.9752044677734</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>20.5</v>
       </c>
       <c r="G38" t="n">
-        <v>18.1348133087158</v>
+        <v>18.1348114013672</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G39" t="n">
-        <v>17.3121089935303</v>
+        <v>17.3121109008789</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G40" t="n">
-        <v>17.7632694244385</v>
+        <v>17.7632675170898</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G42" t="n">
-        <v>18.3471183776855</v>
+        <v>18.3471221923828</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>21.5</v>
       </c>
       <c r="G43" t="n">
-        <v>19.0194358825684</v>
+        <v>19.019437789917</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>21.3099994659424</v>
       </c>
       <c r="G45" t="n">
-        <v>18.8513584136963</v>
+        <v>18.8513603210449</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G46" t="n">
-        <v>19.3113613128662</v>
+        <v>19.3113651275635</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G47" t="n">
-        <v>19.992525100708</v>
+        <v>19.9925231933594</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>19.9482936859131</v>
+        <v>19.9482917785645</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>19.7271347045898</v>
+        <v>19.7271366119385</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G51" t="n">
-        <v>19.647518157959</v>
+        <v>19.6475200653076</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G52" t="n">
-        <v>19.983678817749</v>
+        <v>19.9836769104004</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>22.8099994659424</v>
       </c>
       <c r="G57" t="n">
-        <v>20.178295135498</v>
+        <v>20.1782932281494</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G58" t="n">
-        <v>19.4971351623535</v>
+        <v>19.4971332550049</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>22.0100002288818</v>
       </c>
       <c r="G59" t="n">
-        <v>19.4705944061279</v>
+        <v>19.4705963134766</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G60" t="n">
-        <v>18.9663619995117</v>
+        <v>18.9663581848145</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G61" t="n">
-        <v>19.4794425964355</v>
+        <v>19.4794406890869</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G64" t="n">
-        <v>19.4971351623535</v>
+        <v>19.4971332550049</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G65" t="n">
-        <v>19.417516708374</v>
+        <v>19.4175205230713</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G66" t="n">
-        <v>18.8690509796143</v>
+        <v>18.8690490722656</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G67" t="n">
-        <v>18.833667755127</v>
+        <v>18.8336658477783</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G70" t="n">
-        <v>18.8955879211426</v>
+        <v>18.8955898284912</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G71" t="n">
-        <v>18.5240459442139</v>
+        <v>18.5240478515625</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G72" t="n">
-        <v>19.3113613128662</v>
+        <v>19.3113651275635</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>18.9486656188965</v>
+        <v>18.9486675262451</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G75" t="n">
-        <v>18.8778972625732</v>
+        <v>18.8778953552246</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G78" t="n">
-        <v>18.3205833435059</v>
+        <v>18.3205814361572</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>18.3117389678955</v>
+        <v>18.3117370605469</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G84" t="n">
-        <v>17.878267288208</v>
+        <v>17.8782691955566</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G86" t="n">
-        <v>17.7190399169922</v>
+        <v>17.7190361022949</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G88" t="n">
-        <v>17.444803237915</v>
+        <v>17.4448013305664</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G90" t="n">
-        <v>17.5509586334229</v>
+        <v>17.5509567260742</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G91" t="n">
-        <v>17.9844245910645</v>
+        <v>17.9844264984131</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>17.6394233703613</v>
+        <v>17.6394214630127</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G94" t="n">
-        <v>18.833667755127</v>
+        <v>18.8336658477783</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>20.2700004577637</v>
       </c>
       <c r="G97" t="n">
-        <v>17.9313488006592</v>
+        <v>17.9313468933105</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>17.7367305755615</v>
+        <v>17.7367286682129</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G99" t="n">
-        <v>17.648265838623</v>
+        <v>17.6482677459717</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G100" t="n">
-        <v>17.593936920166</v>
+        <v>17.5939388275146</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G102" t="n">
-        <v>17.7025966644287</v>
+        <v>17.7025985717773</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G103" t="n">
-        <v>17.6482677459717</v>
+        <v>17.648265838623</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G105" t="n">
-        <v>17.593936920166</v>
+        <v>17.5939388275146</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G106" t="n">
-        <v>17.4128341674805</v>
+        <v>17.4128360748291</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G107" t="n">
-        <v>17.304178237915</v>
+        <v>17.3041763305664</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>17.4762191772461</v>
+        <v>17.4762210845947</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G109" t="n">
-        <v>17.4762191772461</v>
+        <v>17.4762210845947</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G113" t="n">
-        <v>17.6844882965088</v>
+        <v>17.6844863891602</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G115" t="n">
-        <v>16.71559715271</v>
+        <v>16.7155990600586</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G116" t="n">
-        <v>16.5435543060303</v>
+        <v>16.5435562133789</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>17.8384246826172</v>
+        <v>17.8384265899658</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G120" t="n">
-        <v>17.9380283355713</v>
+        <v>17.9380302429199</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G121" t="n">
-        <v>17.7297630310059</v>
+        <v>17.7297611236572</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G122" t="n">
-        <v>17.8655891418457</v>
+        <v>17.8655853271484</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G123" t="n">
-        <v>18.1825160980225</v>
+        <v>18.1825122833252</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>16.3896179199219</v>
+        <v>16.3896160125732</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G126" t="n">
-        <v>16.6793785095215</v>
+        <v>16.6793804168701</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G127" t="n">
-        <v>16.262845993042</v>
+        <v>16.2628479003906</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>16.6069393157959</v>
+        <v>16.6069374084473</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>17.75</v>
       </c>
       <c r="G132" t="n">
-        <v>16.0726909637451</v>
+        <v>16.0726890563965</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G133" t="n">
-        <v>15.8734798431396</v>
+        <v>15.8734817504883</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G134" t="n">
-        <v>16.3624515533447</v>
+        <v>16.3624534606934</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G135" t="n">
-        <v>16.4439468383789</v>
+        <v>16.4439487457275</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G136" t="n">
-        <v>16.6974868774414</v>
+        <v>16.69748878479</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G137" t="n">
-        <v>17.095911026001</v>
+        <v>17.0959072113037</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G139" t="n">
-        <v>17.0868549346924</v>
+        <v>17.086856842041</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G143" t="n">
-        <v>17.8655891418457</v>
+        <v>17.8655853271484</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G145" t="n">
-        <v>18.1372413635254</v>
+        <v>18.1372394561768</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G149" t="n">
-        <v>19.0699081420898</v>
+        <v>19.0699100494385</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G153" t="n">
-        <v>18.2187347412109</v>
+        <v>18.2187385559082</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G159" t="n">
-        <v>18.94313621521</v>
+        <v>18.9431381225586</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G160" t="n">
-        <v>19.04274559021</v>
+        <v>19.0427417755127</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>18.4722747802734</v>
+        <v>18.4722766876221</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G164" t="n">
-        <v>18.6171550750732</v>
+        <v>18.6171569824219</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G165" t="n">
-        <v>18.7529830932617</v>
+        <v>18.7529811859131</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>18.9703025817871</v>
+        <v>18.9703044891357</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G167" t="n">
-        <v>18.6805400848389</v>
+        <v>18.6805419921875</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G168" t="n">
-        <v>18.6081008911133</v>
+        <v>18.6080989837646</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G169" t="n">
-        <v>18.653377532959</v>
+        <v>18.6533794403076</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G171" t="n">
-        <v>18.5175514221191</v>
+        <v>18.5175533294678</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>18.6081008911133</v>
+        <v>18.6080989837646</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G173" t="n">
-        <v>18.8706970214844</v>
+        <v>18.870698928833</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>18.6986484527588</v>
+        <v>18.6986522674561</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>19.1061267852783</v>
+        <v>19.106128692627</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>22</v>
       </c>
       <c r="G177" t="n">
-        <v>19.9210815429688</v>
+        <v>19.9210834503174</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>19.5588798522949</v>
+        <v>19.5588817596436</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>21.4899997711182</v>
       </c>
       <c r="G180" t="n">
-        <v>19.4592742919922</v>
+        <v>19.4592723846436</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G181" t="n">
-        <v>19.314395904541</v>
+        <v>19.3143939971924</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G183" t="n">
-        <v>18.6805400848389</v>
+        <v>18.6805419921875</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G184" t="n">
-        <v>19.1332931518555</v>
+        <v>19.1332950592041</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>19.1604595184326</v>
+        <v>19.160457611084</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G188" t="n">
-        <v>20.4553298950195</v>
+        <v>20.4553279876709</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G190" t="n">
-        <v>20.4553298950195</v>
+        <v>20.4553279876709</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G191" t="n">
-        <v>20.3104476928711</v>
+        <v>20.3104496002197</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>20.3919429779053</v>
+        <v>20.3919448852539</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>20.8446960449219</v>
+        <v>20.8446979522705</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G197" t="n">
-        <v>20.7994213104248</v>
+        <v>20.7994194030762</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G198" t="n">
-        <v>20.4010009765625</v>
+        <v>20.4009990692139</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>22.6700000762939</v>
       </c>
       <c r="G200" t="n">
-        <v>20.5277690887451</v>
+        <v>20.5277709960938</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G203" t="n">
-        <v>20.7541446685791</v>
+        <v>20.7541427612305</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>20.0116310119629</v>
+        <v>20.0116348266602</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G206" t="n">
-        <v>20.2651748657227</v>
+        <v>20.2651710510254</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>22.25</v>
       </c>
       <c r="G210" t="n">
-        <v>20.1474571228027</v>
+        <v>20.1474590301514</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G212" t="n">
-        <v>20.5006046295166</v>
+        <v>20.500602722168</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G217" t="n">
-        <v>19.4140033721924</v>
+        <v>19.4139976501465</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>19.5045509338379</v>
+        <v>19.5045528411865</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G220" t="n">
-        <v>19.7943115234375</v>
+        <v>19.7943134307861</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G221" t="n">
-        <v>19.5226612091064</v>
+        <v>19.5226593017578</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>19.830530166626</v>
+        <v>19.8305320739746</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>21.9899997711182</v>
       </c>
       <c r="G223" t="n">
-        <v>19.9120254516602</v>
+        <v>19.9120273590088</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G224" t="n">
-        <v>19.7490348815918</v>
+        <v>19.7490367889404</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.4722747802734</v>
+        <v>18.4722766876221</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G226" t="n">
-        <v>18.0919628143311</v>
+        <v>18.0919647216797</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>18.2458992004395</v>
+        <v>18.2459011077881</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G231" t="n">
-        <v>17.7388172149658</v>
+        <v>17.7388191223145</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G232" t="n">
-        <v>17.8565330505371</v>
+        <v>17.8565349578857</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>17.8203105926514</v>
+        <v>17.8203144073486</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>17.6392097473145</v>
+        <v>17.6392135620117</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G235" t="n">
-        <v>18.3455066680908</v>
+        <v>18.3455047607422</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>20.3099994659424</v>
       </c>
       <c r="G236" t="n">
-        <v>18.3907794952393</v>
+        <v>18.3907814025879</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G239" t="n">
-        <v>18.8706970214844</v>
+        <v>18.870698928833</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>19.2872276306152</v>
+        <v>19.2872314453125</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G242" t="n">
-        <v>19.3958892822266</v>
+        <v>19.3958911895752</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G244" t="n">
-        <v>19.1151847839355</v>
+        <v>19.1151866912842</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G245" t="n">
-        <v>19.5860462188721</v>
+        <v>19.5860443115234</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>21.2700004577637</v>
       </c>
       <c r="G246" t="n">
-        <v>19.2600631713867</v>
+        <v>19.2600612640381</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G248" t="n">
-        <v>20.2651748657227</v>
+        <v>20.2651710510254</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>22.5</v>
       </c>
       <c r="G249" t="n">
-        <v>20.3738346099854</v>
+        <v>20.373836517334</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G250" t="n">
-        <v>20.2651748657227</v>
+        <v>20.2651710510254</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G251" t="n">
-        <v>20.3466701507568</v>
+        <v>20.3466682434082</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>20.2380084991455</v>
+        <v>20.2380065917969</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G253" t="n">
-        <v>20.1293487548828</v>
+        <v>20.1293468475342</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G257" t="n">
-        <v>20.3104476928711</v>
+        <v>20.3104496002197</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G258" t="n">
-        <v>20.8084754943848</v>
+        <v>20.8084735870361</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G263" t="n">
-        <v>22.0580711364746</v>
+        <v>22.0580730438232</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G264" t="n">
-        <v>22.2572803497314</v>
+        <v>22.2572822570801</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G265" t="n">
-        <v>22.2935028076172</v>
+        <v>22.2935009002686</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>24.6299991607666</v>
       </c>
       <c r="G266" t="n">
-        <v>22.3025550842285</v>
+        <v>22.3025569915771</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>22.275390625</v>
+        <v>22.2753944396973</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G270" t="n">
-        <v>22.818696975708</v>
+        <v>22.8186950683594</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>25.5699996948242</v>
       </c>
       <c r="G273" t="n">
-        <v>23.1537284851074</v>
+        <v>23.1537303924561</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>22.5923175811768</v>
+        <v>22.5923194885254</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G276" t="n">
-        <v>22.3568859100342</v>
+        <v>22.3568878173828</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>22.9092445373535</v>
+        <v>22.9092426300049</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G278" t="n">
-        <v>22.1757850646973</v>
+        <v>22.1757869720459</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G280" t="n">
-        <v>23.6064796447754</v>
+        <v>23.606481552124</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>26.2299995422363</v>
       </c>
       <c r="G281" t="n">
-        <v>23.7513618469238</v>
+        <v>23.7513637542725</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>26.6399993896484</v>
       </c>
       <c r="G282" t="n">
-        <v>24.1226215362549</v>
+        <v>24.1226196289062</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>23.561206817627</v>
+        <v>23.5612087249756</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G286" t="n">
-        <v>23.561206817627</v>
+        <v>23.5612087249756</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>23.7241973876953</v>
+        <v>23.7241992950439</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>26.3099994659424</v>
       </c>
       <c r="G291" t="n">
-        <v>23.8238010406494</v>
+        <v>23.8238048553467</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>26.1700000762939</v>
       </c>
       <c r="G292" t="n">
-        <v>23.6970348358154</v>
+        <v>23.6970310211182</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G293" t="n">
-        <v>23.7241973876953</v>
+        <v>23.7241992950439</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G295" t="n">
-        <v>24.2856101989746</v>
+        <v>24.285608291626</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>24.068286895752</v>
+        <v>24.0682888031006</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>23.9777355194092</v>
+        <v>23.9777412414551</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G299" t="n">
-        <v>24.4304904937744</v>
+        <v>24.430492401123</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G300" t="n">
-        <v>24.6115951538086</v>
+        <v>24.61159324646</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>24.7655277252197</v>
+        <v>24.7655258178711</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>27.8199996948242</v>
       </c>
       <c r="G302" t="n">
-        <v>25.1911144256592</v>
+        <v>25.1911125183105</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G304" t="n">
-        <v>25.4265460968018</v>
+        <v>25.4265422821045</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>28.3299999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>25.6529235839844</v>
+        <v>25.6529216766357</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>25.7615833282471</v>
+        <v>25.7615814208984</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>27.5</v>
       </c>
       <c r="G311" t="n">
-        <v>24.9013557434082</v>
+        <v>24.9013538360596</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>27.3899993896484</v>
       </c>
       <c r="G313" t="n">
-        <v>24.8017501831055</v>
+        <v>24.8017482757568</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>27.1900005340576</v>
       </c>
       <c r="G314" t="n">
-        <v>24.6206455230713</v>
+        <v>24.6206474304199</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G318" t="n">
-        <v>25.2273368835449</v>
+        <v>25.227331161499</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>25.1730041503906</v>
+        <v>25.173002243042</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>25.3993759155273</v>
+        <v>25.3993797302246</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G322" t="n">
-        <v>25.4265460968018</v>
+        <v>25.4265422821045</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>28.4099998474121</v>
       </c>
       <c r="G323" t="n">
-        <v>25.7253589630127</v>
+        <v>25.7253608703613</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>27.9300003051758</v>
       </c>
       <c r="G324" t="n">
-        <v>25.2907218933105</v>
+        <v>25.2907199859619</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>27.75</v>
       </c>
       <c r="G325" t="n">
-        <v>25.1277275085449</v>
+        <v>25.1277256011963</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>28.4300003051758</v>
       </c>
       <c r="G326" t="n">
-        <v>25.7434692382812</v>
+        <v>25.7434711456299</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>28.2099990844727</v>
       </c>
       <c r="G327" t="n">
-        <v>25.5442600250244</v>
+        <v>25.5442581176758</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G328" t="n">
-        <v>25.4808750152588</v>
+        <v>25.4808731079102</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>28.1700000762939</v>
       </c>
       <c r="G329" t="n">
-        <v>25.5080394744873</v>
+        <v>25.5080413818359</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>25.2635536193848</v>
+        <v>25.2635555267334</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>25.0824546813965</v>
+        <v>25.0824527740479</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>24.7655277252197</v>
+        <v>24.7655258178711</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>24.2674999237061</v>
+        <v>24.2674980163574</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>27.8199996948242</v>
       </c>
       <c r="G336" t="n">
-        <v>25.1911144256592</v>
+        <v>25.1911125183105</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>26.1237850189209</v>
+        <v>26.1237831115723</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>29.4099998474121</v>
       </c>
       <c r="G340" t="n">
-        <v>26.6308650970459</v>
+        <v>26.6308631896973</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>29.25</v>
       </c>
       <c r="G341" t="n">
-        <v>26.4859848022461</v>
+        <v>26.4859828948975</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G343" t="n">
-        <v>26.6761379241943</v>
+        <v>26.676139831543</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>26.8934631347656</v>
+        <v>26.893461227417</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>29</v>
       </c>
       <c r="G345" t="n">
-        <v>26.2596073150635</v>
+        <v>26.2596054077148</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>26.667085647583</v>
+        <v>26.6670837402344</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G347" t="n">
-        <v>26.9115657806396</v>
+        <v>26.9115715026855</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>29.4099998474121</v>
       </c>
       <c r="G348" t="n">
-        <v>26.6308650970459</v>
+        <v>26.6308631896973</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>29.3700008392334</v>
       </c>
       <c r="G350" t="n">
-        <v>26.5946464538574</v>
+        <v>26.5946483612061</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>29</v>
       </c>
       <c r="G351" t="n">
-        <v>26.2596073150635</v>
+        <v>26.2596054077148</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>27.9699993133545</v>
       </c>
       <c r="G353" t="n">
-        <v>25.326940536499</v>
+        <v>25.3269386291504</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>28.5300006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>25.8340244293213</v>
+        <v>25.8340225219727</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>25.2299995422363</v>
       </c>
       <c r="G359" t="n">
-        <v>23.2202453613281</v>
+        <v>23.2202472686768</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>25.1299991607666</v>
       </c>
       <c r="G360" t="n">
-        <v>23.1282138824463</v>
+        <v>23.1282119750977</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>22.9625511169434</v>
+        <v>22.962553024292</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G363" t="n">
-        <v>22.8613128662109</v>
+        <v>22.8613166809082</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>24.25</v>
       </c>
       <c r="G369" t="n">
-        <v>22.3183097839355</v>
+        <v>22.3183116912842</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>22.2262783050537</v>
+        <v>22.2262763977051</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G371" t="n">
-        <v>22.3827323913574</v>
+        <v>22.3827362060547</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G373" t="n">
-        <v>22.7416687011719</v>
+        <v>22.7416667938232</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G375" t="n">
-        <v>22.8797225952148</v>
+        <v>22.8797206878662</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>23.2846698760986</v>
+        <v>23.2846717834473</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G378" t="n">
-        <v>23.4319248199463</v>
+        <v>23.4319229125977</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G379" t="n">
-        <v>22.8060932159424</v>
+        <v>22.8060913085938</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G380" t="n">
-        <v>23.0269756317139</v>
+        <v>23.0269737243652</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G381" t="n">
-        <v>22.6036186218262</v>
+        <v>22.6036167144775</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>23.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>21.5452251434326</v>
+        <v>21.545223236084</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>21.4900016784668</v>
+        <v>21.4900035858154</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>21.7200889587402</v>
+        <v>21.7200870513916</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G386" t="n">
-        <v>21.5544281005859</v>
+        <v>21.5544300079346</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>23.5</v>
       </c>
       <c r="G388" t="n">
-        <v>21.6280555725098</v>
+        <v>21.6280536651611</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>23.2700004577637</v>
       </c>
       <c r="G393" t="n">
-        <v>21.4163761138916</v>
+        <v>21.416374206543</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G394" t="n">
-        <v>21.5084095001221</v>
+        <v>21.5084114074707</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G395" t="n">
-        <v>21.9133586883545</v>
+        <v>21.9133605957031</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G396" t="n">
-        <v>21.8857498168945</v>
+        <v>21.8857517242432</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>23.8700008392334</v>
       </c>
       <c r="G397" t="n">
-        <v>21.9685821533203</v>
+        <v>21.9685802459717</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G398" t="n">
-        <v>22.6220226287842</v>
+        <v>22.6220245361328</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G402" t="n">
-        <v>22.5299892425537</v>
+        <v>22.5299911499023</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G403" t="n">
-        <v>22.6312294006348</v>
+        <v>22.6312274932861</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G404" t="n">
-        <v>22.6404323577881</v>
+        <v>22.6404342651367</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G405" t="n">
-        <v>22.5575981140137</v>
+        <v>22.5576000213623</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G407" t="n">
-        <v>21.4255809783936</v>
+        <v>21.4255790710449</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>23.5300006866455</v>
       </c>
       <c r="G408" t="n">
-        <v>21.6556663513184</v>
+        <v>21.6556644439697</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>24.25</v>
       </c>
       <c r="G413" t="n">
-        <v>22.3183097839355</v>
+        <v>22.3183116912842</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G414" t="n">
-        <v>22.0514125823975</v>
+        <v>22.0514106750488</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G415" t="n">
-        <v>22.6220226287842</v>
+        <v>22.6220245361328</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>24.2700004577637</v>
       </c>
       <c r="G417" t="n">
-        <v>22.3367195129395</v>
+        <v>22.3367176055908</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>24.0300006866455</v>
       </c>
       <c r="G418" t="n">
-        <v>22.115837097168</v>
+        <v>22.1158351898193</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>21.7661037445068</v>
+        <v>21.7661056518555</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>23.9699993133545</v>
       </c>
       <c r="G420" t="n">
-        <v>22.0606136322021</v>
+        <v>22.0606174468994</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G422" t="n">
-        <v>21.9133586883545</v>
+        <v>21.9133605957031</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G425" t="n">
-        <v>21.7016830444336</v>
+        <v>21.701681137085</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G430" t="n">
-        <v>21.9133586883545</v>
+        <v>21.9133605957031</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>23.7700004577637</v>
       </c>
       <c r="G431" t="n">
-        <v>21.8765487670898</v>
+        <v>21.8765468597412</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G439" t="n">
-        <v>21.0574378967285</v>
+        <v>21.0574398040771</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G440" t="n">
-        <v>20.9470024108887</v>
+        <v>20.94700050354</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>22.9300003051758</v>
       </c>
       <c r="G442" t="n">
-        <v>21.1034603118896</v>
+        <v>21.103458404541</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>21.0758495330811</v>
+        <v>21.0758476257324</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G444" t="n">
-        <v>21.3243427276611</v>
+        <v>21.3243408203125</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G446" t="n">
-        <v>22.0974311828613</v>
+        <v>22.0974292755127</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G447" t="n">
-        <v>22.0514125823975</v>
+        <v>22.0514106750488</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>22.3827323913574</v>
+        <v>22.3827362060547</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>23.5100002288818</v>
       </c>
       <c r="G450" t="n">
-        <v>21.6372585296631</v>
+        <v>21.6372566223145</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G452" t="n">
-        <v>20.9746131896973</v>
+        <v>20.9746112823486</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>20.9838123321533</v>
+        <v>20.983814239502</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G455" t="n">
-        <v>21.1402702331543</v>
+        <v>21.1402721405029</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G456" t="n">
-        <v>21.0666446685791</v>
+        <v>21.0666427612305</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G458" t="n">
-        <v>21.0942573547363</v>
+        <v>21.0942554473877</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G462" t="n">
-        <v>20.6340827941895</v>
+        <v>20.6340847015381</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G463" t="n">
-        <v>20.4500179290771</v>
+        <v>20.4500141143799</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G465" t="n">
-        <v>20.3947944641113</v>
+        <v>20.3947925567627</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G466" t="n">
-        <v>20.0082511901855</v>
+        <v>20.0082492828369</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>19.9714393615723</v>
+        <v>19.9714374542236</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>20.0634708404541</v>
+        <v>20.0634727478027</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G469" t="n">
-        <v>20.4868297576904</v>
+        <v>20.4868278503418</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G473" t="n">
-        <v>21.0666446685791</v>
+        <v>21.0666427612305</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G476" t="n">
-        <v>20.9470024108887</v>
+        <v>20.94700050354</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>21.9099998474121</v>
       </c>
       <c r="G479" t="n">
-        <v>20.1647071838379</v>
+        <v>20.1647090911865</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G480" t="n">
-        <v>20.0910816192627</v>
+        <v>20.0910835266113</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>19.695333480835</v>
+        <v>19.6953353881836</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G485" t="n">
-        <v>20.1831150054932</v>
+        <v>20.1831169128418</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G486" t="n">
-        <v>20.0450668334961</v>
+        <v>20.0450649261475</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>20.4316082000732</v>
+        <v>20.4316101074219</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>20.6616954803467</v>
+        <v>20.661693572998</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G491" t="n">
-        <v>20.9838123321533</v>
+        <v>20.983814239502</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>23.0300006866455</v>
       </c>
       <c r="G496" t="n">
-        <v>21.1954936981201</v>
+        <v>21.1954917907715</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>23.3099994659424</v>
       </c>
       <c r="G498" t="n">
-        <v>21.4531879425049</v>
+        <v>21.4531898498535</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>23.2700004577637</v>
       </c>
       <c r="G499" t="n">
-        <v>21.4163761138916</v>
+        <v>21.416374206543</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G501" t="n">
-        <v>20.6708965301514</v>
+        <v>20.6708984375</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G502" t="n">
-        <v>20.7721366882324</v>
+        <v>20.7721347808838</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>19.4652481079102</v>
+        <v>19.4652462005615</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G504" t="n">
-        <v>19.796573638916</v>
+        <v>19.7965698242188</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G507" t="n">
-        <v>20.2199306488037</v>
+        <v>20.2199268341064</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>20.229133605957</v>
+        <v>20.2291316986084</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G512" t="n">
-        <v>20.2199306488037</v>
+        <v>20.2199268341064</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>20.5236434936523</v>
+        <v>20.5236415863037</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G514" t="n">
-        <v>20.6524925231934</v>
+        <v>20.6524906158447</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>22.7199993133545</v>
       </c>
       <c r="G515" t="n">
-        <v>20.9101867675781</v>
+        <v>20.9101886749268</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G516" t="n">
-        <v>20.6524925231934</v>
+        <v>20.6524906158447</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G520" t="n">
-        <v>20.4868297576904</v>
+        <v>20.4868278503418</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>20.4316082000732</v>
+        <v>20.4316101074219</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G522" t="n">
-        <v>20.4500179290771</v>
+        <v>20.4500141143799</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G525" t="n">
-        <v>20.9470024108887</v>
+        <v>20.94700050354</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G531" t="n">
-        <v>21.5176105499268</v>
+        <v>21.5176124572754</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G533" t="n">
-        <v>20.8549671173096</v>
+        <v>20.8549652099609</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G534" t="n">
-        <v>21.3243427276611</v>
+        <v>21.3243408203125</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>22.7299995422363</v>
       </c>
       <c r="G535" t="n">
-        <v>20.9193916320801</v>
+        <v>20.9193897247314</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G536" t="n">
-        <v>20.5052375793457</v>
+        <v>20.5052356719971</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G538" t="n">
-        <v>20.6340827941895</v>
+        <v>20.6340847015381</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G539" t="n">
-        <v>20.0266590118408</v>
+        <v>20.0266571044922</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G541" t="n">
-        <v>20.0082511901855</v>
+        <v>20.0082492828369</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G546" t="n">
-        <v>20.6340827941895</v>
+        <v>20.6340847015381</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G547" t="n">
-        <v>20.4500179290771</v>
+        <v>20.4500141143799</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G548" t="n">
-        <v>20.9838123321533</v>
+        <v>20.983814239502</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>23.0300006866455</v>
       </c>
       <c r="G549" t="n">
-        <v>21.1954936981201</v>
+        <v>21.1954917907715</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G552" t="n">
-        <v>20.8365592956543</v>
+        <v>20.8365573883057</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G555" t="n">
-        <v>20.6248817443848</v>
+        <v>20.6248798370361</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>22.0300006866455</v>
       </c>
       <c r="G556" t="n">
-        <v>20.2751502990723</v>
+        <v>20.2751522064209</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G557" t="n">
-        <v>20.0910816192627</v>
+        <v>20.0910835266113</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>20.1094875335693</v>
+        <v>20.109489440918</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>19.9714393615723</v>
+        <v>19.9714374542236</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G561" t="n">
-        <v>19.9990501403809</v>
+        <v>19.9990463256836</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>20.1094875335693</v>
+        <v>20.109489440918</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>22.6800003051758</v>
       </c>
       <c r="G567" t="n">
-        <v>20.8733749389648</v>
+        <v>20.8733730316162</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G568" t="n">
-        <v>20.5236434936523</v>
+        <v>20.5236415863037</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G570" t="n">
-        <v>20.6524925231934</v>
+        <v>20.6524906158447</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>22.3099994659424</v>
       </c>
       <c r="G571" t="n">
-        <v>20.5328464508057</v>
+        <v>20.5328483581543</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G574" t="n">
-        <v>20.6340827941895</v>
+        <v>20.6340847015381</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G575" t="n">
-        <v>20.6432876586914</v>
+        <v>20.64328956604</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>20.6156768798828</v>
+        <v>20.6156749725342</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G580" t="n">
-        <v>20.3947944641113</v>
+        <v>20.3947925567627</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G582" t="n">
-        <v>20.9746131896973</v>
+        <v>20.9746112823486</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G585" t="n">
-        <v>21.3151378631592</v>
+        <v>21.3151359558105</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>21.5360202789307</v>
+        <v>21.536018371582</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>21.5360202789307</v>
+        <v>21.536018371582</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G592" t="n">
-        <v>22.4195499420166</v>
+        <v>22.4195518493652</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G593" t="n">
-        <v>22.2078685760498</v>
+        <v>22.2078704833984</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G595" t="n">
-        <v>22.8797225952148</v>
+        <v>22.8797206878662</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G596" t="n">
-        <v>22.7416687011719</v>
+        <v>22.7416667938232</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>22.6404323577881</v>
+        <v>22.6404342651367</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G599" t="n">
-        <v>22.6312294006348</v>
+        <v>22.6312274932861</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>22.9165344238281</v>
+        <v>22.9165325164795</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G601" t="n">
-        <v>22.6864471435547</v>
+        <v>22.6864490509033</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>22.7324657440186</v>
+        <v>22.7324676513672</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G603" t="n">
-        <v>22.8337001800537</v>
+        <v>22.8337020874023</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G605" t="n">
-        <v>22.9073314666748</v>
+        <v>22.9073295593262</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G606" t="n">
-        <v>23.2754669189453</v>
+        <v>23.2754688262939</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>22.9165344238281</v>
+        <v>22.9165325164795</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G608" t="n">
-        <v>22.9913024902344</v>
+        <v>22.991304397583</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G609" t="n">
-        <v>23.3090686798096</v>
+        <v>23.3090705871582</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>23.4118747711182</v>
+        <v>23.4118728637695</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G611" t="n">
-        <v>22.9071865081787</v>
+        <v>22.9071884155273</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G612" t="n">
-        <v>22.9819583892822</v>
+        <v>22.9819564819336</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G614" t="n">
-        <v>22.3557720184326</v>
+        <v>22.355770111084</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>22.6174602508545</v>
+        <v>22.6174621582031</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G616" t="n">
-        <v>23.0754203796387</v>
+        <v>23.07541847229</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>24.8199996948242</v>
       </c>
       <c r="G618" t="n">
-        <v>23.1969165802002</v>
+        <v>23.1969184875488</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G620" t="n">
-        <v>23.4586067199707</v>
+        <v>23.4586048126221</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G621" t="n">
-        <v>22.6548442840576</v>
+        <v>22.6548461914062</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>24.3299999237061</v>
       </c>
       <c r="G622" t="n">
-        <v>22.7389602661133</v>
+        <v>22.7389583587646</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G623" t="n">
-        <v>23.1595306396484</v>
+        <v>23.1595325469971</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G626" t="n">
-        <v>23.3838386535645</v>
+        <v>23.3838367462158</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>21.3899993896484</v>
       </c>
       <c r="G633" t="n">
-        <v>19.9912185668945</v>
+        <v>19.9912166595459</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G634" t="n">
-        <v>19.7388782501221</v>
+        <v>19.7388744354248</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G635" t="n">
-        <v>19.56130027771</v>
+        <v>19.5612983703613</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G636" t="n">
-        <v>19.3089542388916</v>
+        <v>19.3089561462402</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>19.5332622528076</v>
+        <v>19.533260345459</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G638" t="n">
-        <v>19.4958763122559</v>
+        <v>19.4958782196045</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G640" t="n">
-        <v>19.0285739898682</v>
+        <v>19.0285758972168</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>19.3449993133545</v>
       </c>
       <c r="G645" t="n">
-        <v>18.079948425293</v>
+        <v>18.0799503326416</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G647" t="n">
-        <v>18.6033306121826</v>
+        <v>18.603328704834</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G648" t="n">
-        <v>18.6360416412354</v>
+        <v>18.6360397338867</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G649" t="n">
-        <v>18.7949237823486</v>
+        <v>18.794921875</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>20.0900001525879</v>
       </c>
       <c r="G650" t="n">
-        <v>18.7762317657471</v>
+        <v>18.7762298583984</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>19.875</v>
       </c>
       <c r="G653" t="n">
-        <v>18.5752925872803</v>
+        <v>18.5752906799316</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G654" t="n">
-        <v>18.3930416107178</v>
+        <v>18.3930435180664</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>19.8250007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>18.5285606384277</v>
+        <v>18.5285625457764</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>19.6749992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>18.388370513916</v>
+        <v>18.3883686065674</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G660" t="n">
-        <v>18.2435054779053</v>
+        <v>18.2435073852539</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>19.0149993896484</v>
       </c>
       <c r="G662" t="n">
-        <v>17.7715263366699</v>
+        <v>17.7715282440186</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>20.0699996948242</v>
       </c>
       <c r="G666" t="n">
-        <v>18.7575378417969</v>
+        <v>18.7575397491455</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>19.5550003051758</v>
       </c>
       <c r="G671" t="n">
-        <v>18.276216506958</v>
+        <v>18.2762184143066</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G672" t="n">
-        <v>18.2528514862061</v>
+        <v>18.2528533935547</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>19.6650009155273</v>
       </c>
       <c r="G674" t="n">
-        <v>18.3790245056152</v>
+        <v>18.3790225982666</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G677" t="n">
-        <v>19.4024181365967</v>
+        <v>19.402416229248</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G679" t="n">
-        <v>19.4304523468018</v>
+        <v>19.4304542541504</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>20.5100002288818</v>
       </c>
       <c r="G682" t="n">
-        <v>19.1687660217285</v>
+        <v>19.1687641143799</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>19.1126899719238</v>
+        <v>19.1126880645752</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G685" t="n">
-        <v>18.7388439178467</v>
+        <v>18.7388458251953</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G688" t="n">
-        <v>18.8416519165039</v>
+        <v>18.8416538238525</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G689" t="n">
-        <v>19.6080303192139</v>
+        <v>19.6080284118652</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G691" t="n">
-        <v>19.5239143371582</v>
+        <v>19.5239162445068</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G692" t="n">
-        <v>19.4211101531982</v>
+        <v>19.4211082458496</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>19.8136425018311</v>
+        <v>19.8136444091797</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G694" t="n">
-        <v>20.0753326416016</v>
+        <v>20.0753307342529</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G695" t="n">
-        <v>19.748218536377</v>
+        <v>19.7482204437256</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G697" t="n">
-        <v>19.6080303192139</v>
+        <v>19.6080284118652</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>19.7669124603271</v>
+        <v>19.7669105529785</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G700" t="n">
-        <v>19.5706443786621</v>
+        <v>19.5706462860107</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G701" t="n">
-        <v>19.2809162139893</v>
+        <v>19.2809181213379</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G705" t="n">
-        <v>18.8042697906494</v>
+        <v>18.804271697998</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>18.1780834197998</v>
+        <v>18.1780853271484</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>18.6453857421875</v>
+        <v>18.6453876495361</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>19.2049999237061</v>
       </c>
       <c r="G714" t="n">
-        <v>17.9491062164307</v>
+        <v>17.949104309082</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G717" t="n">
-        <v>19.5706443786621</v>
+        <v>19.5706462860107</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>20.5300006866455</v>
       </c>
       <c r="G718" t="n">
-        <v>19.1874561309814</v>
+        <v>19.1874580383301</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>20.9699993133545</v>
       </c>
       <c r="G720" t="n">
-        <v>19.5986843109131</v>
+        <v>19.5986824035645</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G722" t="n">
-        <v>19.6454162597656</v>
+        <v>19.645414352417</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G723" t="n">
-        <v>19.4771842956543</v>
+        <v>19.4771862030029</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>20.0005626678467</v>
+        <v>20.0005645751953</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>21</v>
       </c>
       <c r="G729" t="n">
-        <v>19.6267223358154</v>
+        <v>19.6267204284668</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G733" t="n">
-        <v>19.701488494873</v>
+        <v>19.7014904022217</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>21</v>
       </c>
       <c r="G734" t="n">
-        <v>19.6267223358154</v>
+        <v>19.6267204284668</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G738" t="n">
-        <v>18.6033306121826</v>
+        <v>18.603328704834</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>19.5332622528076</v>
+        <v>19.533260345459</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G747" t="n">
-        <v>19.701488494873</v>
+        <v>19.7014904022217</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>19.5332622528076</v>
+        <v>19.533260345459</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G749" t="n">
-        <v>19.4304523468018</v>
+        <v>19.4304542541504</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>19.206148147583</v>
+        <v>19.2061462402344</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G753" t="n">
-        <v>18.3930416107178</v>
+        <v>18.3930435180664</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G754" t="n">
-        <v>17.0472087860107</v>
+        <v>17.0472106933594</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>17.7450008392334</v>
       </c>
       <c r="G757" t="n">
-        <v>16.5845813751221</v>
+        <v>16.5845794677734</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G760" t="n">
-        <v>16.7200984954834</v>
+        <v>16.7200965881348</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>16.495792388916</v>
+        <v>16.4957904815674</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G762" t="n">
-        <v>16.7528095245361</v>
+        <v>16.7528076171875</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>17.1650009155273</v>
       </c>
       <c r="G765" t="n">
-        <v>16.0425109863281</v>
+        <v>16.0425071716309</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>16.495792388916</v>
+        <v>16.4957904815674</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>16.5425205230713</v>
+        <v>16.5425243377686</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G770" t="n">
-        <v>16.6640205383301</v>
+        <v>16.6640224456787</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>16.495792388916</v>
+        <v>16.4957904815674</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G774" t="n">
-        <v>16.6827125549316</v>
+        <v>16.6827144622803</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G775" t="n">
-        <v>16.5985984802246</v>
+        <v>16.5986003875732</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G787" t="n">
-        <v>16.495792388916</v>
+        <v>16.4957904815674</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G788" t="n">
-        <v>16.523832321167</v>
+        <v>16.5238285064697</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G792" t="n">
-        <v>16.5799083709717</v>
+        <v>16.579906463623</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>17.1967449188232</v>
+        <v>17.1967468261719</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>18.8050003051758</v>
       </c>
       <c r="G797" t="n">
-        <v>17.5752620697021</v>
+        <v>17.5752601623535</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G799" t="n">
-        <v>17.4163780212402</v>
+        <v>17.4163799285889</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>18.4349994659424</v>
       </c>
       <c r="G802" t="n">
-        <v>17.229455947876</v>
+        <v>17.2294578552246</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G804" t="n">
-        <v>17.4397449493408</v>
+        <v>17.4397430419922</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G806" t="n">
-        <v>17.729471206665</v>
+        <v>17.7294731140137</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G807" t="n">
-        <v>17.6547031402588</v>
+        <v>17.6547050476074</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G809" t="n">
-        <v>17.4163780212402</v>
+        <v>17.4163799285889</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>18.0249996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>16.8462677001953</v>
+        <v>16.8462696075439</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G812" t="n">
-        <v>17.1687088012695</v>
+        <v>17.1687107086182</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>18</v>
       </c>
       <c r="G813" t="n">
-        <v>16.822904586792</v>
+        <v>16.8229064941406</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>19.1650009155273</v>
       </c>
       <c r="G815" t="n">
-        <v>17.9117202758789</v>
+        <v>17.9117221832275</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G817" t="n">
-        <v>17.6593780517578</v>
+        <v>17.6593761444092</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G818" t="n">
-        <v>17.7948951721191</v>
+        <v>17.7948970794678</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>18.6149997711182</v>
       </c>
       <c r="G822" t="n">
-        <v>17.3976860046387</v>
+        <v>17.3976898193359</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G823" t="n">
-        <v>17.6266651153564</v>
+        <v>17.6266670227051</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G826" t="n">
-        <v>17.869665145874</v>
+        <v>17.8696632385254</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G829" t="n">
-        <v>18.056583404541</v>
+        <v>18.0565814971924</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G832" t="n">
-        <v>18.0191993713379</v>
+        <v>18.0192012786865</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G834" t="n">
-        <v>17.9070491790771</v>
+        <v>17.9070472717285</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>19.5550003051758</v>
       </c>
       <c r="G838" t="n">
-        <v>18.276216506958</v>
+        <v>18.2762184143066</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G840" t="n">
-        <v>18.439769744873</v>
+        <v>18.4397716522217</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>19.8250007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>18.5285606384277</v>
+        <v>18.5285625457764</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>19.8449993133545</v>
       </c>
       <c r="G842" t="n">
-        <v>18.5472507476807</v>
+        <v>18.5472526550293</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G844" t="n">
-        <v>18.3930416107178</v>
+        <v>18.3930435180664</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G845" t="n">
-        <v>18.3089275360107</v>
+        <v>18.3089294433594</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>19.6550006866455</v>
       </c>
       <c r="G847" t="n">
-        <v>18.3696784973145</v>
+        <v>18.3696765899658</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>18.0612602233887</v>
+        <v>18.06125831604</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G853" t="n">
-        <v>18.0939712524414</v>
+        <v>18.0939674377441</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G854" t="n">
-        <v>17.6266651153564</v>
+        <v>17.6266670227051</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>19.3449993133545</v>
       </c>
       <c r="G855" t="n">
-        <v>18.079948425293</v>
+        <v>18.0799503326416</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>20.0472965240479</v>
+        <v>20.0472946166992</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>19.9071025848389</v>
+        <v>19.9071044921875</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G860" t="n">
-        <v>19.9735889434814</v>
+        <v>19.9735870361328</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G862" t="n">
-        <v>19.204273223877</v>
+        <v>19.2042751312256</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G863" t="n">
-        <v>19.4892082214355</v>
+        <v>19.4892063140869</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>20.1299991607666</v>
       </c>
       <c r="G864" t="n">
-        <v>19.1187953948975</v>
+        <v>19.1187973022461</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>19.9549999237061</v>
       </c>
       <c r="G866" t="n">
-        <v>18.9525890350342</v>
+        <v>18.9525871276855</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G868" t="n">
-        <v>17.7131443023682</v>
+        <v>17.7131423950195</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>18.6650009155273</v>
       </c>
       <c r="G869" t="n">
-        <v>17.7273902893066</v>
+        <v>17.7273921966553</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G873" t="n">
-        <v>19.1757831573486</v>
+        <v>19.1757850646973</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>20.2299995422363</v>
       </c>
       <c r="G876" t="n">
-        <v>19.2137718200684</v>
+        <v>19.213773727417</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>19.9850006103516</v>
       </c>
       <c r="G877" t="n">
-        <v>18.9810829162598</v>
+        <v>18.9810791015625</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G878" t="n">
-        <v>18.905101776123</v>
+        <v>18.9050998687744</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G879" t="n">
-        <v>19.0333194732666</v>
+        <v>19.033317565918</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G880" t="n">
-        <v>19.6601638793945</v>
+        <v>19.6601657867432</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G882" t="n">
-        <v>19.9355945587158</v>
+        <v>19.9355964660645</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G883" t="n">
-        <v>20.0210762023926</v>
+        <v>20.0210742950439</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G885" t="n">
-        <v>19.7171478271484</v>
+        <v>19.7171497344971</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G887" t="n">
-        <v>19.7456455230713</v>
+        <v>19.745641708374</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>20.4674625396729</v>
+        <v>20.4674663543701</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G893" t="n">
-        <v>20.2870121002197</v>
+        <v>20.2870101928711</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>21.0900001525879</v>
       </c>
       <c r="G902" t="n">
-        <v>20.0305728912354</v>
+        <v>20.030574798584</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G903" t="n">
-        <v>19.8691120147705</v>
+        <v>19.8691139221191</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G904" t="n">
-        <v>19.9735889434814</v>
+        <v>19.9735870361328</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G905" t="n">
-        <v>19.8691120147705</v>
+        <v>19.8691139221191</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G906" t="n">
-        <v>19.9355945587158</v>
+        <v>19.9355964660645</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G908" t="n">
-        <v>20.0020790100098</v>
+        <v>20.0020809173584</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G914" t="n">
-        <v>17.2952461242676</v>
+        <v>17.2952442169189</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G915" t="n">
-        <v>17.2762508392334</v>
+        <v>17.2762489318848</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G916" t="n">
-        <v>17.2667541503906</v>
+        <v>17.266752243042</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G917" t="n">
-        <v>17.3854751586914</v>
+        <v>17.3854732513428</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>17.9150009155273</v>
       </c>
       <c r="G920" t="n">
-        <v>17.015064239502</v>
+        <v>17.0150680541992</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G926" t="n">
-        <v>16.9153385162354</v>
+        <v>16.915340423584</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G928" t="n">
-        <v>16.7348861694336</v>
+        <v>16.734884262085</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>17.7350006103516</v>
       </c>
       <c r="G931" t="n">
-        <v>16.844108581543</v>
+        <v>16.8441066741943</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G932" t="n">
-        <v>16.497444152832</v>
+        <v>16.4974422454834</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G933" t="n">
-        <v>16.6683979034424</v>
+        <v>16.668399810791</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G935" t="n">
-        <v>16.9248352050781</v>
+        <v>16.9248371124268</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G936" t="n">
-        <v>17.4329605102539</v>
+        <v>17.4329624176025</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>18.0450000762939</v>
       </c>
       <c r="G939" t="n">
-        <v>17.1385364532471</v>
+        <v>17.1385345458984</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>17.2857494354248</v>
+        <v>17.2857475280762</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>17.7350006103516</v>
       </c>
       <c r="G944" t="n">
-        <v>16.844108581543</v>
+        <v>16.8441066741943</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>17.0450000762939</v>
       </c>
       <c r="G949" t="n">
-        <v>16.1887683868408</v>
+        <v>16.1887664794922</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>16.9549999237061</v>
       </c>
       <c r="G953" t="n">
-        <v>16.1032886505127</v>
+        <v>16.1032905578613</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>15.4811906814575</v>
+        <v>15.4811916351318</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G956" t="n">
-        <v>15.538179397583</v>
+        <v>15.5381784439087</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>15.4811906814575</v>
+        <v>15.4811916351318</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>16.4150009155273</v>
       </c>
       <c r="G962" t="n">
-        <v>15.5904169082642</v>
+        <v>15.5904159545898</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G964" t="n">
-        <v>15.6806421279907</v>
+        <v>15.680643081665</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G965" t="n">
-        <v>15.4052104949951</v>
+        <v>15.4052095413208</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>16.1350002288818</v>
       </c>
       <c r="G966" t="n">
-        <v>15.324481010437</v>
+        <v>15.3244800567627</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>16.0650005340576</v>
       </c>
       <c r="G968" t="n">
-        <v>15.2579965591431</v>
+        <v>15.2579975128174</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G971" t="n">
-        <v>15.0348014831543</v>
+        <v>15.0348024368286</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G973" t="n">
-        <v>15.9608249664307</v>
+        <v>15.9608240127563</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>15.7661228179932</v>
+        <v>15.7661218643188</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G975" t="n">
-        <v>15.8800916671753</v>
+        <v>15.8800926208496</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>16.75</v>
       </c>
       <c r="G976" t="n">
-        <v>15.9085855484009</v>
+        <v>15.9085874557495</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G980" t="n">
-        <v>16.4024658203125</v>
+        <v>16.4024639129639</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G985" t="n">
-        <v>17.2762508392334</v>
+        <v>17.2762489318848</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G988" t="n">
-        <v>16.4404544830322</v>
+        <v>16.4404563903809</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G992" t="n">
-        <v>16.4024658203125</v>
+        <v>16.4024639129639</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>18.0949993133545</v>
       </c>
       <c r="G997" t="n">
-        <v>17.1860237121582</v>
+        <v>17.1860218048096</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G998" t="n">
-        <v>16.6873950958252</v>
+        <v>16.6873970031738</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1000" t="n">
-        <v>16.7348861694336</v>
+        <v>16.734884262085</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1005" t="n">
-        <v>17.2477588653564</v>
+        <v>17.2477569580078</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>18.2549991607666</v>
       </c>
       <c r="G1006" t="n">
-        <v>17.3379859924316</v>
+        <v>17.337984085083</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G1007" t="n">
-        <v>17.409215927124</v>
+        <v>17.4092178344727</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1009" t="n">
-        <v>17.5421829223633</v>
+        <v>17.5421848297119</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>18.4050006866455</v>
       </c>
       <c r="G1010" t="n">
-        <v>17.4804496765137</v>
+        <v>17.4804515838623</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>17.8556060791016</v>
+        <v>17.8556079864502</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>18.75</v>
       </c>
       <c r="G1015" t="n">
-        <v>17.8081188201904</v>
+        <v>17.8081207275391</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>18.6049995422363</v>
       </c>
       <c r="G1017" t="n">
-        <v>17.6704044342041</v>
+        <v>17.6704025268555</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>18.5550003051758</v>
       </c>
       <c r="G1018" t="n">
-        <v>17.622917175293</v>
+        <v>17.6229152679443</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>18.6149997711182</v>
       </c>
       <c r="G1019" t="n">
-        <v>17.6799011230469</v>
+        <v>17.6799030303955</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1020" t="n">
-        <v>17.9885749816895</v>
+        <v>17.9885768890381</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1022" t="n">
-        <v>18.0930500030518</v>
+        <v>18.0930480957031</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.9030952453613</v>
+        <v>17.90309715271</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>18.7950000762939</v>
       </c>
       <c r="G1024" t="n">
-        <v>17.8508605957031</v>
+        <v>17.8508586883545</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>18.2549991607666</v>
       </c>
       <c r="G1026" t="n">
-        <v>17.3379859924316</v>
+        <v>17.337984085083</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.2287635803223</v>
+        <v>17.228759765625</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>18</v>
       </c>
       <c r="G1029" t="n">
-        <v>17.0957946777344</v>
+        <v>17.095796585083</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1032" t="n">
-        <v>16.5924167633057</v>
+        <v>16.5924186706543</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>15.8610982894897</v>
+        <v>15.8611001968384</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G1034" t="n">
-        <v>16.2694988250732</v>
+        <v>16.2694969177246</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1035" t="n">
-        <v>16.2979927062988</v>
+        <v>16.2979907989502</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1037" t="n">
-        <v>15.8468523025513</v>
+        <v>15.8468494415283</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1038" t="n">
-        <v>15.8800916671753</v>
+        <v>15.8800926208496</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>16.6149997711182</v>
       </c>
       <c r="G1042" t="n">
-        <v>15.7803678512573</v>
+        <v>15.7803688049316</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>15.7186336517334</v>
+        <v>15.7186317443848</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1045" t="n">
-        <v>15.9845695495605</v>
+        <v>15.9845685958862</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.747127532959</v>
+        <v>15.7471265792847</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1048" t="n">
-        <v>15.8610982894897</v>
+        <v>15.8611001968384</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>16.7250003814697</v>
       </c>
       <c r="G1050" t="n">
-        <v>15.8848428726196</v>
+        <v>15.8848438262939</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>14.3249998092651</v>
       </c>
       <c r="G1056" t="n">
-        <v>13.6054029464722</v>
+        <v>13.6054039001465</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G1057" t="n">
-        <v>13.5721616744995</v>
+        <v>13.5721607208252</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1060" t="n">
-        <v>12.9738082885742</v>
+        <v>12.9738092422485</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>9.5620002746582</v>
       </c>
       <c r="G1066" t="n">
-        <v>9.08166694641113</v>
+        <v>9.08166599273682</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>10.164999961853</v>
       </c>
       <c r="G1067" t="n">
-        <v>9.65437602996826</v>
+        <v>9.65437412261963</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1074" t="n">
-        <v>13.0877799987793</v>
+        <v>13.0877809524536</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>13.6549997329712</v>
       </c>
       <c r="G1076" t="n">
-        <v>12.9690599441528</v>
+        <v>12.9690589904785</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1080" t="n">
-        <v>11.2072439193726</v>
+        <v>11.2072429656982</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1082" t="n">
-        <v>11.1882476806641</v>
+        <v>11.1882467269897</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1083" t="n">
-        <v>11.568154335022</v>
+        <v>11.5681552886963</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1085" t="n">
-        <v>11.6251411437988</v>
+        <v>11.6251401901245</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1088" t="n">
-        <v>11.4541826248169</v>
+        <v>11.4541835784912</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>11.5396614074707</v>
+        <v>11.5396604537964</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>10.399941444397</v>
+        <v>10.3999423980713</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>11</v>
       </c>
       <c r="G1094" t="n">
-        <v>10.4474296569824</v>
+        <v>10.4474306106567</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1097" t="n">
-        <v>10.7323598861694</v>
+        <v>10.7323608398438</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1099" t="n">
-        <v>10.722861289978</v>
+        <v>10.7228622436523</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1100" t="n">
-        <v>10.3049659729004</v>
+        <v>10.3049650192261</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G1103" t="n">
-        <v>10.3429565429688</v>
+        <v>10.3429574966431</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1104" t="n">
-        <v>10.4094400405884</v>
+        <v>10.4094390869141</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1110" t="n">
-        <v>10.4094400405884</v>
+        <v>10.4094390869141</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1111" t="n">
-        <v>10.399941444397</v>
+        <v>10.3999423980713</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G1114" t="n">
-        <v>9.64962673187256</v>
+        <v>9.64962577819824</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1115" t="n">
-        <v>9.78259372711182</v>
+        <v>9.78259468078613</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>13</v>
       </c>
       <c r="G1118" t="n">
-        <v>12.346962928772</v>
+        <v>12.3469638824463</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>13.1542654037476</v>
+        <v>13.1542644500732</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G1128" t="n">
-        <v>11.8815784454346</v>
+        <v>11.8815774917603</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1133" t="n">
-        <v>12.3089723587036</v>
+        <v>12.3089714050293</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1135" t="n">
-        <v>12.5749063491821</v>
+        <v>12.5749073028564</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>13.25</v>
       </c>
       <c r="G1136" t="n">
-        <v>12.5844039916992</v>
+        <v>12.5844049453735</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1140" t="n">
-        <v>11.7296142578125</v>
+        <v>11.7296152114868</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G1142" t="n">
-        <v>11.5206661224365</v>
+        <v>11.5206670761108</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1143" t="n">
-        <v>11.7581081390381</v>
+        <v>11.7581071853638</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1144" t="n">
-        <v>11.4541826248169</v>
+        <v>11.4541835784912</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1145" t="n">
-        <v>11.5871486663818</v>
+        <v>11.5871496200562</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1147" t="n">
-        <v>11.3402099609375</v>
+        <v>11.3402109146118</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.9887971878052</v>
+        <v>10.9887962341309</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1151" t="n">
-        <v>10.9887971878052</v>
+        <v>10.9887962341309</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1152" t="n">
-        <v>11.1882476806641</v>
+        <v>11.1882467269897</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.2452344894409</v>
+        <v>11.2452335357666</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G1159" t="n">
-        <v>11.0267877578735</v>
+        <v>11.0267868041992</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1161" t="n">
-        <v>10.8368339538574</v>
+        <v>10.8368349075317</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G1162" t="n">
-        <v>11.0552806854248</v>
+        <v>11.0552816390991</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1163" t="n">
-        <v>11.2167415618896</v>
+        <v>11.2167406082153</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1167" t="n">
-        <v>10.8368339538574</v>
+        <v>10.8368349075317</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G1170" t="n">
-        <v>10.3619518280029</v>
+        <v>10.3619508743286</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1172" t="n">
-        <v>11.6251411437988</v>
+        <v>11.6251401901245</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1173" t="n">
-        <v>11.644136428833</v>
+        <v>11.6441354751587</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1174" t="n">
-        <v>11.3307123184204</v>
+        <v>11.3307132720947</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G1178" t="n">
-        <v>10.760853767395</v>
+        <v>10.7608528137207</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>10.7798490524292</v>
+        <v>10.7798480987549</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1181" t="n">
-        <v>10.6753740310669</v>
+        <v>10.6753749847412</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1183" t="n">
-        <v>11.6251411437988</v>
+        <v>11.6251401901245</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1184" t="n">
-        <v>11.6251411437988</v>
+        <v>11.6251401901245</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1185" t="n">
-        <v>11.4636793136597</v>
+        <v>11.463680267334</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1188" t="n">
-        <v>11.7960977554321</v>
+        <v>11.7960996627808</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G1191" t="n">
-        <v>11.4256896972656</v>
+        <v>11.4256887435913</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1193" t="n">
-        <v>11.4541826248169</v>
+        <v>11.4541835784912</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G1195" t="n">
-        <v>11.4256896972656</v>
+        <v>11.4256887435913</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>11.5871486663818</v>
+        <v>11.5871496200562</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1201" t="n">
-        <v>11.568154335022</v>
+        <v>11.5681552886963</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1203" t="n">
-        <v>11.4636793136597</v>
+        <v>11.463680267334</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>12.0145444869995</v>
+        <v>12.0145454406738</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1209" t="n">
-        <v>11.9860506057739</v>
+        <v>11.9860515594482</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.1285171508789</v>
+        <v>12.1285181045532</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1212" t="n">
-        <v>12.2804803848267</v>
+        <v>12.2804794311523</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>13.25</v>
       </c>
       <c r="G1215" t="n">
-        <v>12.5844039916992</v>
+        <v>12.5844049453735</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G1217" t="n">
-        <v>12.5464143753052</v>
+        <v>12.5464134216309</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>12.2044982910156</v>
+        <v>12.2044973373413</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>12.0145444869995</v>
+        <v>12.0145454406738</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1222" t="n">
-        <v>12.8978281021118</v>
+        <v>12.8978271484375</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1223" t="n">
-        <v>12.1949996948242</v>
+        <v>12.1950006484985</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1224" t="n">
-        <v>11.8910760879517</v>
+        <v>11.8910751342773</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G1225" t="n">
-        <v>11.6726293563843</v>
+        <v>11.67262840271</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G1231" t="n">
-        <v>11.0552806854248</v>
+        <v>11.0552816390991</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1232" t="n">
-        <v>11.0647773742676</v>
+        <v>11.0647783279419</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1234" t="n">
-        <v>11.3592052459717</v>
+        <v>11.359206199646</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G1236" t="n">
-        <v>12.7933530807495</v>
+        <v>12.7933540344238</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1238" t="n">
-        <v>12.8978281021118</v>
+        <v>12.8978271484375</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1239" t="n">
-        <v>13.7811107635498</v>
+        <v>13.7811098098755</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1240" t="n">
-        <v>13.7146253585815</v>
+        <v>13.7146263122559</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1241" t="n">
-        <v>13.9235744476318</v>
+        <v>13.9235754013062</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G1242" t="n">
-        <v>13.9330730438232</v>
+        <v>13.9330739974976</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1244" t="n">
-        <v>14.3414726257324</v>
+        <v>14.3414716720581</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1246" t="n">
-        <v>14.6264009475708</v>
+        <v>14.6264019012451</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1247" t="n">
-        <v>14.6264009475708</v>
+        <v>14.6264019012451</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1249" t="n">
-        <v>14.1515188217163</v>
+        <v>14.1515197753906</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>15</v>
       </c>
       <c r="G1250" t="n">
-        <v>14.2464952468872</v>
+        <v>14.2464962005615</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G1252" t="n">
-        <v>14.4649419784546</v>
+        <v>14.4649410247803</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1253" t="n">
-        <v>14.9113321304321</v>
+        <v>14.9113311767578</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>15</v>
       </c>
       <c r="G1256" t="n">
-        <v>14.2464952468872</v>
+        <v>14.2464962005615</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1257" t="n">
-        <v>14.4934349060059</v>
+        <v>14.4934358596802</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G1259" t="n">
-        <v>14.5979089736938</v>
+        <v>14.5979099273682</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1262" t="n">
-        <v>14.8828401565552</v>
+        <v>14.8828392028809</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1265" t="n">
-        <v>14.3794622421265</v>
+        <v>14.3794641494751</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G1269" t="n">
-        <v>15.110782623291</v>
+        <v>15.1107835769653</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1273" t="n">
-        <v>14.7118806838989</v>
+        <v>14.7118816375732</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1275" t="n">
-        <v>14.5884103775024</v>
+        <v>14.5884113311768</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1276" t="n">
-        <v>14.5789136886597</v>
+        <v>14.578914642334</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1279" t="n">
-        <v>14.5314264297485</v>
+        <v>14.5314254760742</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1280" t="n">
-        <v>13.9615650177002</v>
+        <v>13.9615659713745</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1282" t="n">
-        <v>14.3794622421265</v>
+        <v>14.3794641494751</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G1283" t="n">
-        <v>14.4459466934204</v>
+        <v>14.4459457397461</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1285" t="n">
-        <v>15.2912397384644</v>
+        <v>15.29123878479</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1286" t="n">
-        <v>14.683388710022</v>
+        <v>14.6833877563477</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>15.0537967681885</v>
+        <v>15.0537977218628</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1292" t="n">
-        <v>15.0442991256714</v>
+        <v>15.0443000793457</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1295" t="n">
-        <v>14.6359004974365</v>
+        <v>14.6358995437622</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1296" t="n">
-        <v>14.6264009475708</v>
+        <v>14.6264019012451</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1298" t="n">
-        <v>14.5789136886597</v>
+        <v>14.578914642334</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>15.7700004577637</v>
       </c>
       <c r="G1303" t="n">
-        <v>14.9778156280518</v>
+        <v>14.9778165817261</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1305" t="n">
-        <v>14.7783651351929</v>
+        <v>14.7783641815186</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G1306" t="n">
-        <v>14.825852394104</v>
+        <v>14.8258533477783</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G1315" t="n">
-        <v>14.8448476791382</v>
+        <v>14.8448486328125</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1316" t="n">
-        <v>14.9873123168945</v>
+        <v>14.9873132705688</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1321" t="n">
-        <v>15.8231077194214</v>
+        <v>15.8231086730957</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1323" t="n">
-        <v>15.8800916671753</v>
+        <v>15.8800926208496</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>15.7376298904419</v>
+        <v>15.7376270294189</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1327" t="n">
-        <v>15.7091369628906</v>
+        <v>15.7091360092163</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1330" t="n">
-        <v>15.3672199249268</v>
+        <v>15.3672208786011</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1331" t="n">
-        <v>15.3387269973755</v>
+        <v>15.3387260437012</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1332" t="n">
-        <v>15.6996374130249</v>
+        <v>15.6996402740479</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1333" t="n">
-        <v>15.538179397583</v>
+        <v>15.5381784439087</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G1335" t="n">
-        <v>15.9608249664307</v>
+        <v>15.9608240127563</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>16.4449996948242</v>
       </c>
       <c r="G1336" t="n">
-        <v>15.6189079284668</v>
+        <v>15.6189069747925</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>16.2450008392334</v>
       </c>
       <c r="G1337" t="n">
-        <v>15.4289560317993</v>
+        <v>15.428955078125</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>16.4650001525879</v>
       </c>
       <c r="G1338" t="n">
-        <v>15.6379041671753</v>
+        <v>15.637903213501</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1339" t="n">
-        <v>15.8468523025513</v>
+        <v>15.8468494415283</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>17.625</v>
       </c>
       <c r="G1342" t="n">
-        <v>16.7396335601807</v>
+        <v>16.739631652832</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>17.7649993896484</v>
       </c>
       <c r="G1344" t="n">
-        <v>16.8726005554199</v>
+        <v>16.8725986480713</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1345" t="n">
-        <v>16.4784469604492</v>
+        <v>16.4784488677979</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>17.9349994659424</v>
       </c>
       <c r="G1346" t="n">
-        <v>17.0340576171875</v>
+        <v>17.0340595245361</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G1349" t="n">
-        <v>17.3854751586914</v>
+        <v>17.3854732513428</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>18.2049999237061</v>
       </c>
       <c r="G1351" t="n">
-        <v>17.2904968261719</v>
+        <v>17.2904987335205</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>17.9850006103516</v>
       </c>
       <c r="G1352" t="n">
-        <v>17.0815467834473</v>
+        <v>17.0815486907959</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1353" t="n">
-        <v>16.9248352050781</v>
+        <v>16.9248371124268</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1354" t="n">
-        <v>17.0245609283447</v>
+        <v>17.0245628356934</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1356" t="n">
-        <v>17.5421829223633</v>
+        <v>17.5421848297119</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>18.3850002288818</v>
       </c>
       <c r="G1358" t="n">
-        <v>17.4614543914795</v>
+        <v>17.4614562988281</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1360" t="n">
-        <v>17.4187145233154</v>
+        <v>17.4187164306641</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>19.1949996948242</v>
       </c>
       <c r="G1365" t="n">
-        <v>18.2307643890381</v>
+        <v>18.2307662963867</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>18.9050006866455</v>
       </c>
       <c r="G1369" t="n">
-        <v>17.9553337097168</v>
+        <v>17.9553356170654</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>18.9950008392334</v>
       </c>
       <c r="G1372" t="n">
-        <v>18.0408134460449</v>
+        <v>18.0408115386963</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1373" t="n">
-        <v>18.3304901123047</v>
+        <v>18.3304920196533</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1374" t="n">
-        <v>18.3304901123047</v>
+        <v>18.3304920196533</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G1380" t="n">
-        <v>18.5299434661865</v>
+        <v>18.5299415588379</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>19.2649993896484</v>
       </c>
       <c r="G1383" t="n">
-        <v>18.2972469329834</v>
+        <v>18.297248840332</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1385" t="n">
-        <v>18.1690292358398</v>
+        <v>18.1690311431885</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1386" t="n">
-        <v>18.1690292358398</v>
+        <v>18.1690311431885</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1387" t="n">
-        <v>18.1690292358398</v>
+        <v>18.1690311431885</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1389" t="n">
-        <v>18.4444637298584</v>
+        <v>18.444465637207</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>19.3050003051758</v>
       </c>
       <c r="G1393" t="n">
-        <v>18.3352394104004</v>
+        <v>18.335241317749</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>18.0450000762939</v>
       </c>
       <c r="G1396" t="n">
-        <v>17.1385364532471</v>
+        <v>17.1385345458984</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1398" t="n">
-        <v>17.2287635803223</v>
+        <v>17.228759765625</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>18.0650005340576</v>
       </c>
       <c r="G1401" t="n">
-        <v>17.1575317382812</v>
+        <v>17.1575298309326</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G1405" t="n">
-        <v>16.7253875732422</v>
+        <v>16.7253856658936</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1406" t="n">
-        <v>16.877347946167</v>
+        <v>16.8773498535156</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>16.4449996948242</v>
       </c>
       <c r="G1409" t="n">
-        <v>15.6189079284668</v>
+        <v>15.6189069747925</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>16.8250007629395</v>
       </c>
       <c r="G1410" t="n">
-        <v>15.9798202514648</v>
+        <v>15.9798192977905</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G1413" t="n">
-        <v>16.2505035400391</v>
+        <v>16.2505054473877</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>17.0249996185303</v>
       </c>
       <c r="G1415" t="n">
-        <v>16.169771194458</v>
+        <v>16.1697731018066</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G1417" t="n">
-        <v>16.0368041992188</v>
+        <v>16.0368061065674</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>17.0249996185303</v>
       </c>
       <c r="G1420" t="n">
-        <v>16.169771194458</v>
+        <v>16.1697731018066</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>18.3150005340576</v>
       </c>
       <c r="G1425" t="n">
-        <v>17.3949718475342</v>
+        <v>17.3949699401855</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G1426" t="n">
-        <v>18.4919528961182</v>
+        <v>18.4919509887695</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>17.0008182525635</v>
+        <v>17.0008163452148</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G1431" t="n">
-        <v>16.5164375305176</v>
+        <v>16.5164356231689</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>16.5650005340576</v>
       </c>
       <c r="G1432" t="n">
-        <v>15.7328805923462</v>
+        <v>15.7328796386719</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>16.5750007629395</v>
       </c>
       <c r="G1433" t="n">
-        <v>15.7423782348633</v>
+        <v>15.7423791885376</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>17</v>
       </c>
       <c r="G1434" t="n">
-        <v>16.1460266113281</v>
+        <v>16.1460285186768</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>16.8150005340576</v>
       </c>
       <c r="G1437" t="n">
-        <v>15.9703216552734</v>
+        <v>15.9703226089478</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G1442" t="n">
-        <v>16.6873950958252</v>
+        <v>16.6873970031738</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>17.9349994659424</v>
       </c>
       <c r="G1445" t="n">
-        <v>17.0340576171875</v>
+        <v>17.0340595245361</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>18.8150005340576</v>
       </c>
       <c r="G1447" t="n">
-        <v>17.8698558807373</v>
+        <v>17.8698539733887</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>18.75</v>
       </c>
       <c r="G1449" t="n">
-        <v>17.8081188201904</v>
+        <v>17.8081207275391</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>17.6049995422363</v>
       </c>
       <c r="G1454" t="n">
-        <v>16.7206382751465</v>
+        <v>16.7206363677979</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1458" t="n">
-        <v>17.0245609283447</v>
+        <v>17.0245628356934</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1459" t="n">
-        <v>16.9438304901123</v>
+        <v>16.9438323974609</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1460" t="n">
-        <v>16.8298606872559</v>
+        <v>16.8298587799072</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>17.9850006103516</v>
       </c>
       <c r="G1463" t="n">
-        <v>17.0815467834473</v>
+        <v>17.0815486907959</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1465" t="n">
-        <v>17.0245609283447</v>
+        <v>17.0245628356934</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>17.9449996948242</v>
       </c>
       <c r="G1467" t="n">
-        <v>17.0435562133789</v>
+        <v>17.0435581207275</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>17.5949993133545</v>
       </c>
       <c r="G1469" t="n">
-        <v>16.7111396789551</v>
+        <v>16.7111377716064</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>17.0008182525635</v>
+        <v>17.0008163452148</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1473" t="n">
-        <v>17.2287635803223</v>
+        <v>17.228759765625</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1474" t="n">
-        <v>16.9438304901123</v>
+        <v>16.9438323974609</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>18</v>
       </c>
       <c r="G1476" t="n">
-        <v>17.0957946777344</v>
+        <v>17.095796585083</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G1477" t="n">
-        <v>17.4329605102539</v>
+        <v>17.4329624176025</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1480" t="n">
-        <v>17.2857494354248</v>
+        <v>17.2857475280762</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G1482" t="n">
-        <v>17.3427333831787</v>
+        <v>17.3427352905273</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>18.6550006866455</v>
       </c>
       <c r="G1484" t="n">
-        <v>17.7178936004639</v>
+        <v>17.7178916931152</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G1488" t="n">
-        <v>18.7008991241455</v>
+        <v>18.7009010314941</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.7911262512207</v>
+        <v>18.7911281585693</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>19.9750003814697</v>
       </c>
       <c r="G1490" t="n">
-        <v>18.9715843200684</v>
+        <v>18.9715824127197</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1491" t="n">
-        <v>18.1690292358398</v>
+        <v>18.1690311431885</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1492" t="n">
-        <v>17.9458351135254</v>
+        <v>17.945837020874</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G1493" t="n">
-        <v>18.4302177429199</v>
+        <v>18.4302158355713</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>19.5349998474121</v>
       </c>
       <c r="G1494" t="n">
-        <v>18.5536861419678</v>
+        <v>18.5536880493164</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1496" t="n">
-        <v>19.0903053283691</v>
+        <v>19.0903034210205</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>18.9240951538086</v>
+        <v>18.92409324646</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1499" t="n">
-        <v>19.1662845611572</v>
+        <v>19.1662864685059</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1500" t="n">
-        <v>19.1662845611572</v>
+        <v>19.1662864685059</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1505" t="n">
-        <v>19.1377906799316</v>
+        <v>19.1377925872803</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G1508" t="n">
-        <v>19.8691120147705</v>
+        <v>19.8691139221191</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G1509" t="n">
-        <v>19.7456455230713</v>
+        <v>19.745641708374</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1510" t="n">
-        <v>20.4579677581787</v>
+        <v>20.4579696655273</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1512" t="n">
-        <v>21.0373268127441</v>
+        <v>21.0373249053955</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1513" t="n">
-        <v>21.4457225799561</v>
+        <v>21.4457244873047</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1515" t="n">
-        <v>20.7523975372314</v>
+        <v>20.7523956298828</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G1516" t="n">
-        <v>20.6384239196777</v>
+        <v>20.6384220123291</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G1518" t="n">
-        <v>20.0970554351807</v>
+        <v>20.0970573425293</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G1519" t="n">
-        <v>20.7903861999512</v>
+        <v>20.7903842926025</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G1520" t="n">
-        <v>20.7144031524658</v>
+        <v>20.7144050598145</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1522" t="n">
-        <v>21.0373268127441</v>
+        <v>21.0373249053955</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G1524" t="n">
-        <v>21.094310760498</v>
+        <v>21.0943088531494</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1525" t="n">
-        <v>21.4172306060791</v>
+        <v>21.4172325134277</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G1526" t="n">
-        <v>21.3982353210449</v>
+        <v>21.3982391357422</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G1531" t="n">
-        <v>21.6261806488037</v>
+        <v>21.6261825561523</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G1532" t="n">
-        <v>19.7171478271484</v>
+        <v>19.7171497344971</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1542" t="n">
-        <v>17.4946975708008</v>
+        <v>17.4946956634521</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1543" t="n">
-        <v>17.5421829223633</v>
+        <v>17.5421848297119</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1544" t="n">
-        <v>18.0930500030518</v>
+        <v>18.0930480957031</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>19.5750007629395</v>
       </c>
       <c r="G1548" t="n">
-        <v>18.5916786193848</v>
+        <v>18.5916767120361</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>19.0550003051758</v>
       </c>
       <c r="G1550" t="n">
-        <v>18.0977993011475</v>
+        <v>18.0977973937988</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1551" t="n">
-        <v>17.9458351135254</v>
+        <v>17.945837020874</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>18.9950008392334</v>
       </c>
       <c r="G1552" t="n">
-        <v>18.0408134460449</v>
+        <v>18.0408115386963</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G1553" t="n">
-        <v>18.0503101348877</v>
+        <v>18.0503082275391</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G1559" t="n">
-        <v>18.6819038391113</v>
+        <v>18.68190574646</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>19.7649993896484</v>
       </c>
       <c r="G1560" t="n">
-        <v>18.7721309661865</v>
+        <v>18.7721328735352</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>19.7950000762939</v>
       </c>
       <c r="G1561" t="n">
-        <v>18.8006248474121</v>
+        <v>18.8006267547607</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1562" t="n">
-        <v>18.5964260101318</v>
+        <v>18.5964241027832</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G1565" t="n">
-        <v>17.9220905303955</v>
+        <v>17.9220924377441</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>19.4249992370605</v>
       </c>
       <c r="G1567" t="n">
-        <v>18.4492130279541</v>
+        <v>18.4492111206055</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G1570" t="n">
-        <v>17.12428855896</v>
+        <v>17.1242904663086</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G1579" t="n">
-        <v>15.5856657028198</v>
+        <v>15.5856676101685</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1581" t="n">
-        <v>15.8610982894897</v>
+        <v>15.8611001968384</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1582" t="n">
-        <v>15.8136100769043</v>
+        <v>15.81360912323</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1585" t="n">
-        <v>15.253246307373</v>
+        <v>15.2532482147217</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1586" t="n">
-        <v>15.5191831588745</v>
+        <v>15.5191822052002</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>16.6650009155273</v>
       </c>
       <c r="G1587" t="n">
-        <v>15.8278589248657</v>
+        <v>15.8278579711914</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>17.6550006866455</v>
       </c>
       <c r="G1588" t="n">
-        <v>16.7681255340576</v>
+        <v>16.7681274414062</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1592" t="n">
-        <v>15.9750709533691</v>
+        <v>15.9750699996948</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1595" t="n">
-        <v>14.5884103775024</v>
+        <v>14.5884113311768</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1597" t="n">
-        <v>15.0442991256714</v>
+        <v>15.0443000793457</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1598" t="n">
-        <v>15.3387269973755</v>
+        <v>15.3387260437012</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1599" t="n">
-        <v>15.4811906814575</v>
+        <v>15.4811916351318</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1600" t="n">
-        <v>15.633152961731</v>
+        <v>15.6331548690796</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1602" t="n">
-        <v>15.6996374130249</v>
+        <v>15.6996402740479</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1603" t="n">
-        <v>15.8895902633667</v>
+        <v>15.889591217041</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>16.3299999237061</v>
       </c>
       <c r="G1604" t="n">
-        <v>15.5096855163574</v>
+        <v>15.5096845626831</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G1611" t="n">
-        <v>15.0348014831543</v>
+        <v>15.0348024368286</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1614" t="n">
-        <v>14.3224763870239</v>
+        <v>14.3224773406982</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1616" t="n">
-        <v>12.8123483657837</v>
+        <v>12.812349319458</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1618" t="n">
-        <v>14.1990079879761</v>
+        <v>14.1990070343018</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G1620" t="n">
-        <v>15.0158071517944</v>
+        <v>15.0158061981201</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1622" t="n">
-        <v>15.3672199249268</v>
+        <v>15.3672208786011</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1623" t="n">
-        <v>14.9113321304321</v>
+        <v>14.9113311767578</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G1625" t="n">
-        <v>14.8327655792236</v>
+        <v>14.8327665328979</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1627" t="n">
-        <v>14.6870603561401</v>
+        <v>14.6870594024658</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1628" t="n">
-        <v>15.0756072998047</v>
+        <v>15.075608253479</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1632" t="n">
-        <v>15.8915557861328</v>
+        <v>15.8915548324585</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1633" t="n">
-        <v>15.9886903762817</v>
+        <v>15.9886913299561</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1635" t="n">
-        <v>15.9692640304565</v>
+        <v>15.9692649841309</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1640" t="n">
-        <v>13.7545480728149</v>
+        <v>13.7545490264893</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1643" t="n">
-        <v>13.3660020828247</v>
+        <v>13.366003036499</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1644" t="n">
-        <v>13.7254076004028</v>
+        <v>13.7254085540771</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>13.9391088485718</v>
+        <v>13.9391078948975</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1667" t="n">
-        <v>15.6972808837891</v>
+        <v>15.6972818374634</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1669" t="n">
-        <v>16.2315311431885</v>
+        <v>16.2315330505371</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1672" t="n">
-        <v>15.872127532959</v>
+        <v>15.8721265792847</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1676" t="n">
-        <v>16.4646606445312</v>
+        <v>16.4646625518799</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1685" t="n">
-        <v>17.0960502624512</v>
+        <v>17.0960483551025</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1686" t="n">
-        <v>16.9503440856934</v>
+        <v>16.950345993042</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1693" t="n">
-        <v>16.0664024353027</v>
+        <v>16.0664005279541</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>16.1100006103516</v>
       </c>
       <c r="G1695" t="n">
-        <v>15.6487140655518</v>
+        <v>15.6487131118774</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1696" t="n">
-        <v>15.6001434326172</v>
+        <v>15.6001443862915</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1704" t="n">
-        <v>15.1727437973022</v>
+        <v>15.1727428436279</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>14.75</v>
       </c>
       <c r="G1709" t="n">
-        <v>14.327654838562</v>
+        <v>14.3276538848877</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1715" t="n">
-        <v>13.540846824646</v>
+        <v>13.5408477783203</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1716" t="n">
-        <v>13.9391088485718</v>
+        <v>13.9391078948975</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1744" t="n">
-        <v>14.8230514526367</v>
+        <v>14.823052406311</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1749" t="n">
-        <v>16.2315311431885</v>
+        <v>16.2315330505371</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1752" t="n">
-        <v>15.9304094314575</v>
+        <v>15.9304103851318</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1754" t="n">
-        <v>15.9789781570435</v>
+        <v>15.9789791107178</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G1759" t="n">
-        <v>15.7652769088745</v>
+        <v>15.7652759552002</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1761" t="n">
-        <v>16.5229415893555</v>
+        <v>16.5229434967041</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1764" t="n">
-        <v>16.8434944152832</v>
+        <v>16.8434925079346</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1777" t="n">
-        <v>15.9789781570435</v>
+        <v>15.9789791107178</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1780" t="n">
-        <v>15.9789781570435</v>
+        <v>15.9789791107178</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1781" t="n">
-        <v>16.1635360717773</v>
+        <v>16.163537979126</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1798" t="n">
-        <v>17.7954330444336</v>
+        <v>17.795431137085</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1799" t="n">
-        <v>17.9119987487793</v>
+        <v>17.9119968414307</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G1800" t="n">
-        <v>18.0382747650146</v>
+        <v>18.038272857666</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G1829" t="n">
-        <v>18.0382747650146</v>
+        <v>18.038272857666</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1833" t="n">
-        <v>16.5229415893555</v>
+        <v>16.5229434967041</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1835" t="n">
-        <v>16.3189563751221</v>
+        <v>16.3189544677734</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1836" t="n">
-        <v>16.581226348877</v>
+        <v>16.5812244415283</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1845" t="n">
-        <v>16.076114654541</v>
+        <v>16.0761127471924</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1851" t="n">
-        <v>16.0664024353027</v>
+        <v>16.0664005279541</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1860" t="n">
-        <v>15.8818416595459</v>
+        <v>15.8818407058716</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1861" t="n">
-        <v>15.7361364364624</v>
+        <v>15.7361373901367</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1867" t="n">
-        <v>15.6778535842896</v>
+        <v>15.6778526306152</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1872" t="n">
-        <v>15.0756072998047</v>
+        <v>15.075608253479</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1873" t="n">
-        <v>15.085319519043</v>
+        <v>15.0853204727173</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1879" t="n">
-        <v>14.7064876556396</v>
+        <v>14.706488609314</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -71230,7 +71230,7 @@
         <v>46287.2916666667</v>
       </c>
       <c r="B2726" t="n">
-        <v>505357</v>
+        <v>504557</v>
       </c>
       <c r="C2726" t="n">
         <v>7.67500019073486</v>
@@ -71248,6 +71248,32 @@
         <v>7.61999988555908</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>246410</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>7.74499988555908</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>7.53000020980835</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>7.67000007629395</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -421,7 +421,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G2" t="n">
-        <v>18.2763500213623</v>
+        <v>18.2763519287109</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G4" t="n">
-        <v>17.4978828430176</v>
+        <v>17.4978809356689</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>17.9401950836182</v>
+        <v>17.9401931762695</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>17.6836547851562</v>
+        <v>17.6836528778076</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G7" t="n">
-        <v>18.2498111724854</v>
+        <v>18.249813079834</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G9" t="n">
-        <v>19.1344356536865</v>
+        <v>19.1344375610352</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G11" t="n">
-        <v>18.462121963501</v>
+        <v>18.4621238708496</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G12" t="n">
-        <v>18.2851982116699</v>
+        <v>18.2851963043213</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G13" t="n">
-        <v>18.0994243621826</v>
+        <v>18.0994281768799</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G14" t="n">
-        <v>17.6394214630127</v>
+        <v>17.6394233703613</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G15" t="n">
-        <v>17.5686511993408</v>
+        <v>17.5686531066895</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G16" t="n">
-        <v>18.1878890991211</v>
+        <v>18.1878910064697</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G17" t="n">
-        <v>18.0994243621826</v>
+        <v>18.0994281768799</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G18" t="n">
-        <v>18.4798126220703</v>
+        <v>18.4798145294189</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>17.7632675170898</v>
+        <v>17.7632694244385</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>17.9578838348389</v>
+        <v>17.9578857421875</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G24" t="n">
-        <v>18.2055816650391</v>
+        <v>18.2055797576904</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G27" t="n">
-        <v>17.3563423156738</v>
+        <v>17.3563404083252</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G28" t="n">
-        <v>16.9051837921143</v>
+        <v>16.9051856994629</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>17.1617240905762</v>
+        <v>17.1617221832275</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G30" t="n">
-        <v>16.6486396789551</v>
+        <v>16.6486415863037</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G31" t="n">
-        <v>17.0201854705811</v>
+        <v>17.0201816558838</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G33" t="n">
-        <v>17.6305751800537</v>
+        <v>17.6305770874023</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G34" t="n">
-        <v>18.4798126220703</v>
+        <v>18.4798145294189</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>20.8099994659424</v>
       </c>
       <c r="G35" t="n">
-        <v>18.4090461730957</v>
+        <v>18.4090423583984</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>20.5</v>
       </c>
       <c r="G38" t="n">
-        <v>18.1348114013672</v>
+        <v>18.1348133087158</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G40" t="n">
-        <v>17.7632675170898</v>
+        <v>17.7632694244385</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G42" t="n">
-        <v>18.3471221923828</v>
+        <v>18.3471183776855</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>21.5</v>
       </c>
       <c r="G43" t="n">
-        <v>19.019437789917</v>
+        <v>19.0194358825684</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G44" t="n">
-        <v>19.0017433166504</v>
+        <v>19.001745223999</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>21.3099994659424</v>
       </c>
       <c r="G45" t="n">
-        <v>18.8513603210449</v>
+        <v>18.8513584136963</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G46" t="n">
-        <v>19.3113651275635</v>
+        <v>19.3113613128662</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G47" t="n">
-        <v>19.9925231933594</v>
+        <v>19.992525100708</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>19.9482917785645</v>
+        <v>19.9482936859131</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>19.7271366119385</v>
+        <v>19.7271347045898</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G50" t="n">
-        <v>19.3379020690918</v>
+        <v>19.3378982543945</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G52" t="n">
-        <v>19.9836769104004</v>
+        <v>19.983678817749</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G53" t="n">
-        <v>19.1167469024658</v>
+        <v>19.1167449951172</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G54" t="n">
-        <v>19.3379020690918</v>
+        <v>19.3378982543945</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>22.8099994659424</v>
       </c>
       <c r="G57" t="n">
-        <v>20.1782932281494</v>
+        <v>20.178295135498</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G58" t="n">
-        <v>19.4971332550049</v>
+        <v>19.4971351623535</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>22.0100002288818</v>
       </c>
       <c r="G59" t="n">
-        <v>19.4705963134766</v>
+        <v>19.4705944061279</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G60" t="n">
-        <v>18.9663581848145</v>
+        <v>18.9663600921631</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G61" t="n">
-        <v>19.4794406890869</v>
+        <v>19.4794387817383</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G62" t="n">
-        <v>19.9129066467285</v>
+        <v>19.9129104614258</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G64" t="n">
-        <v>19.4971332550049</v>
+        <v>19.4971351623535</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G65" t="n">
-        <v>19.4175205230713</v>
+        <v>19.417516708374</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G67" t="n">
-        <v>18.8336658477783</v>
+        <v>18.833667755127</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G70" t="n">
-        <v>18.8955898284912</v>
+        <v>18.8955879211426</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G72" t="n">
-        <v>19.3113651275635</v>
+        <v>19.3113613128662</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>18.9486675262451</v>
+        <v>18.9486656188965</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G78" t="n">
-        <v>18.3205814361572</v>
+        <v>18.3205833435059</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G82" t="n">
-        <v>18.0640411376953</v>
+        <v>18.0640392303467</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>18.0021190643311</v>
+        <v>18.0021171569824</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G86" t="n">
-        <v>17.7190361022949</v>
+        <v>17.7190399169922</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G90" t="n">
-        <v>17.5509567260742</v>
+        <v>17.5509605407715</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G91" t="n">
-        <v>17.9844264984131</v>
+        <v>17.9844245910645</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>17.6394214630127</v>
+        <v>17.6394233703613</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G93" t="n">
-        <v>17.4182662963867</v>
+        <v>17.4182643890381</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G94" t="n">
-        <v>18.8336658477783</v>
+        <v>18.833667755127</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>18.0640411376953</v>
+        <v>18.0640392303467</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>20.2700004577637</v>
       </c>
       <c r="G97" t="n">
-        <v>17.9313468933105</v>
+        <v>17.9313488006592</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>17.7367286682129</v>
+        <v>17.7367324829102</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G101" t="n">
-        <v>17.8112602233887</v>
+        <v>17.81125831604</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G102" t="n">
-        <v>17.7025985717773</v>
+        <v>17.7025966644287</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G103" t="n">
-        <v>17.648265838623</v>
+        <v>17.6482696533203</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G104" t="n">
-        <v>17.5305519104004</v>
+        <v>17.5305500030518</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G106" t="n">
-        <v>17.4128360748291</v>
+        <v>17.4128341674805</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G107" t="n">
-        <v>17.3041763305664</v>
+        <v>17.304178237915</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>19.25</v>
       </c>
       <c r="G110" t="n">
-        <v>17.430944442749</v>
+        <v>17.4309463500977</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G111" t="n">
-        <v>17.4852771759033</v>
+        <v>17.4852752685547</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G113" t="n">
-        <v>17.6844863891602</v>
+        <v>17.6844902038574</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G115" t="n">
-        <v>16.7155990600586</v>
+        <v>16.71559715271</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G116" t="n">
-        <v>16.5435562133789</v>
+        <v>16.5435543060303</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G117" t="n">
-        <v>17.0415802001953</v>
+        <v>17.0415782928467</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>17.8384265899658</v>
+        <v>17.8384227752686</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G121" t="n">
-        <v>17.7297611236572</v>
+        <v>17.7297649383545</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G122" t="n">
-        <v>17.8655853271484</v>
+        <v>17.8655910491943</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G123" t="n">
-        <v>18.1825122833252</v>
+        <v>18.1825141906738</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>16.3896160125732</v>
+        <v>16.3896179199219</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G126" t="n">
-        <v>16.6793804168701</v>
+        <v>16.6793785095215</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G127" t="n">
-        <v>16.2628479003906</v>
+        <v>16.262845993042</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>16.6069374084473</v>
+        <v>16.6069393157959</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>17.75</v>
       </c>
       <c r="G132" t="n">
-        <v>16.0726890563965</v>
+        <v>16.0726928710938</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G133" t="n">
-        <v>15.8734817504883</v>
+        <v>15.8734798431396</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G134" t="n">
-        <v>16.3624534606934</v>
+        <v>16.3624515533447</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G135" t="n">
-        <v>16.4439487457275</v>
+        <v>16.4439468383789</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G137" t="n">
-        <v>17.0959072113037</v>
+        <v>17.095911026001</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G138" t="n">
-        <v>17.1321315765381</v>
+        <v>17.1321296691895</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>17.3403968811035</v>
+        <v>17.3403949737549</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G143" t="n">
-        <v>17.8655853271484</v>
+        <v>17.8655910491943</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>17.9289722442627</v>
+        <v>17.9289741516113</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>18.6352672576904</v>
+        <v>18.6352653503418</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G149" t="n">
-        <v>19.0699100494385</v>
+        <v>19.0699081420898</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G150" t="n">
-        <v>19.2147884368896</v>
+        <v>19.214786529541</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>20.5699996948242</v>
       </c>
       <c r="G151" t="n">
-        <v>18.6262111663818</v>
+        <v>18.6262092590332</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G153" t="n">
-        <v>18.2187385559082</v>
+        <v>18.2187366485596</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G155" t="n">
-        <v>18.5809364318848</v>
+        <v>18.5809383392334</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G158" t="n">
-        <v>18.8073120117188</v>
+        <v>18.8073139190674</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G159" t="n">
-        <v>18.9431381225586</v>
+        <v>18.94313621521</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G160" t="n">
-        <v>19.0427417755127</v>
+        <v>19.0427436828613</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>18.4722766876221</v>
+        <v>18.4722747802734</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G168" t="n">
-        <v>18.6080989837646</v>
+        <v>18.6081008911133</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6533794403076</v>
+        <v>18.6533756256104</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G171" t="n">
-        <v>18.5175533294678</v>
+        <v>18.5175514221191</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>18.6080989837646</v>
+        <v>18.6081008911133</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>18.6986522674561</v>
+        <v>18.6986484527588</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>22</v>
       </c>
       <c r="G177" t="n">
-        <v>19.9210834503174</v>
+        <v>19.9210815429688</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>19.5588817596436</v>
+        <v>19.5588798522949</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>21.4899997711182</v>
       </c>
       <c r="G180" t="n">
-        <v>19.4592723846436</v>
+        <v>19.4592761993408</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G181" t="n">
-        <v>19.3143939971924</v>
+        <v>19.314395904541</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G184" t="n">
-        <v>19.1332950592041</v>
+        <v>19.1332931518555</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>19.160457611084</v>
+        <v>19.1604614257812</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G187" t="n">
-        <v>19.9391937255859</v>
+        <v>19.9391918182373</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G188" t="n">
-        <v>20.4553279876709</v>
+        <v>20.4553298950195</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G190" t="n">
-        <v>20.4553279876709</v>
+        <v>20.4553298950195</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>20.3919448852539</v>
+        <v>20.3919467926025</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>20.8446979522705</v>
+        <v>20.8446941375732</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G198" t="n">
-        <v>20.4009990692139</v>
+        <v>20.4010009765625</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>22.6700000762939</v>
       </c>
       <c r="G200" t="n">
-        <v>20.5277709960938</v>
+        <v>20.5277690887451</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>20.3647804260254</v>
+        <v>20.3647785186768</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G203" t="n">
-        <v>20.7541427612305</v>
+        <v>20.7541446685791</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>20.0116348266602</v>
+        <v>20.0116329193115</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G206" t="n">
-        <v>20.2651710510254</v>
+        <v>20.265172958374</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>20.3285598754883</v>
+        <v>20.3285579681396</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G209" t="n">
-        <v>20.0387954711914</v>
+        <v>20.03879737854</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>22.25</v>
       </c>
       <c r="G210" t="n">
-        <v>20.1474590301514</v>
+        <v>20.1474571228027</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G211" t="n">
-        <v>20.2289543151855</v>
+        <v>20.2289562225342</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G212" t="n">
-        <v>20.500602722168</v>
+        <v>20.5006046295166</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G213" t="n">
-        <v>20.5639896392822</v>
+        <v>20.5639877319336</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G215" t="n">
-        <v>20.0387954711914</v>
+        <v>20.03879737854</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G217" t="n">
-        <v>19.4139976501465</v>
+        <v>19.4140033721924</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>19.5045528411865</v>
+        <v>19.5045490264893</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G220" t="n">
-        <v>19.7943134307861</v>
+        <v>19.7943096160889</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G221" t="n">
-        <v>19.5226593017578</v>
+        <v>19.5226612091064</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>21.9899997711182</v>
       </c>
       <c r="G223" t="n">
-        <v>19.9120273590088</v>
+        <v>19.9120254516602</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G224" t="n">
-        <v>19.7490367889404</v>
+        <v>19.7490348815918</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.4722766876221</v>
+        <v>18.4722747802734</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G226" t="n">
-        <v>18.0919647216797</v>
+        <v>18.0919628143311</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>18.2459011077881</v>
+        <v>18.2458992004395</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G231" t="n">
-        <v>17.7388191223145</v>
+        <v>17.7388172149658</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G232" t="n">
-        <v>17.8565349578857</v>
+        <v>17.8565330505371</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>17.8203144073486</v>
+        <v>17.8203105926514</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>17.6392135620117</v>
+        <v>17.6392097473145</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>20.3099994659424</v>
       </c>
       <c r="G236" t="n">
-        <v>18.3907814025879</v>
+        <v>18.3907794952393</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G237" t="n">
-        <v>18.8073120117188</v>
+        <v>18.8073139190674</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>19.151403427124</v>
+        <v>19.1514053344727</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>19.2872314453125</v>
+        <v>19.2872257232666</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G242" t="n">
-        <v>19.3958911895752</v>
+        <v>19.3958892822266</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>19.377779006958</v>
+        <v>19.3777809143066</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G244" t="n">
-        <v>19.1151866912842</v>
+        <v>19.1151828765869</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G245" t="n">
-        <v>19.5860443115234</v>
+        <v>19.5860462188721</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>21.2700004577637</v>
       </c>
       <c r="G246" t="n">
-        <v>19.2600612640381</v>
+        <v>19.2600631713867</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G248" t="n">
-        <v>20.2651710510254</v>
+        <v>20.265172958374</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G250" t="n">
-        <v>20.2651710510254</v>
+        <v>20.265172958374</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>20.2380065917969</v>
+        <v>20.2380084991455</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G253" t="n">
-        <v>20.1293468475342</v>
+        <v>20.1293487548828</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>20.2289543151855</v>
+        <v>20.2289562225342</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>20.1565132141113</v>
+        <v>20.15651512146</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G258" t="n">
-        <v>20.8084735870361</v>
+        <v>20.8084754943848</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G263" t="n">
-        <v>22.0580730438232</v>
+        <v>22.058069229126</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G265" t="n">
-        <v>22.2935009002686</v>
+        <v>22.2935028076172</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>24.6299991607666</v>
       </c>
       <c r="G266" t="n">
-        <v>22.3025569915771</v>
+        <v>22.3025550842285</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>22.2753944396973</v>
+        <v>22.275390625</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G269" t="n">
-        <v>22.2391700744629</v>
+        <v>22.2391719818115</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G270" t="n">
-        <v>22.8186950683594</v>
+        <v>22.818696975708</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G272" t="n">
-        <v>22.891134262085</v>
+        <v>22.8911361694336</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>22.5923194885254</v>
+        <v>22.5923175811768</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G276" t="n">
-        <v>22.3568878173828</v>
+        <v>22.3568859100342</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>22.9092426300049</v>
+        <v>22.9092445373535</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G278" t="n">
-        <v>22.1757869720459</v>
+        <v>22.1757850646973</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G279" t="n">
-        <v>22.1395664215088</v>
+        <v>22.1395645141602</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>26.2299995422363</v>
       </c>
       <c r="G281" t="n">
-        <v>23.7513637542725</v>
+        <v>23.7513618469238</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>26.6399993896484</v>
       </c>
       <c r="G282" t="n">
-        <v>24.1226196289062</v>
+        <v>24.1226215362549</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G283" t="n">
-        <v>23.6427021026611</v>
+        <v>23.6427040100098</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G284" t="n">
-        <v>23.6879749298096</v>
+        <v>23.6879768371582</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>23.7241992950439</v>
+        <v>23.7241973876953</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>23.6879749298096</v>
+        <v>23.6879768371582</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>26.3099994659424</v>
       </c>
       <c r="G291" t="n">
-        <v>23.8238048553467</v>
+        <v>23.823802947998</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>26.1700000762939</v>
       </c>
       <c r="G292" t="n">
-        <v>23.6970310211182</v>
+        <v>23.6970329284668</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G293" t="n">
-        <v>23.7241992950439</v>
+        <v>23.7241973876953</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G295" t="n">
-        <v>24.285608291626</v>
+        <v>24.2856101989746</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>23.9777412414551</v>
+        <v>23.9777355194092</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G299" t="n">
-        <v>24.430492401123</v>
+        <v>24.4304885864258</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>24.7655258178711</v>
+        <v>24.7655277252197</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>27.8199996948242</v>
       </c>
       <c r="G302" t="n">
-        <v>25.1911125183105</v>
+        <v>25.1911144256592</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G304" t="n">
-        <v>25.4265422821045</v>
+        <v>25.4265460968018</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>28.2900009155273</v>
       </c>
       <c r="G305" t="n">
-        <v>25.6167030334473</v>
+        <v>25.6167011260986</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>28.3299999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>25.6529216766357</v>
+        <v>25.6529235839844</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>25.7615814208984</v>
+        <v>25.7615833282471</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G310" t="n">
-        <v>24.9556827545166</v>
+        <v>24.955680847168</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>27.5</v>
       </c>
       <c r="G311" t="n">
-        <v>24.9013538360596</v>
+        <v>24.9013557434082</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>25.62575340271</v>
+        <v>25.6257553100586</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G318" t="n">
-        <v>25.227331161499</v>
+        <v>25.2273368835449</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>27.7900009155273</v>
       </c>
       <c r="G320" t="n">
-        <v>25.1639499664307</v>
+        <v>25.163948059082</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>25.3993797302246</v>
+        <v>25.399377822876</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G322" t="n">
-        <v>25.4265422821045</v>
+        <v>25.4265460968018</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>28.4099998474121</v>
       </c>
       <c r="G323" t="n">
-        <v>25.7253608703613</v>
+        <v>25.7253589630127</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>27.75</v>
       </c>
       <c r="G325" t="n">
-        <v>25.1277256011963</v>
+        <v>25.1277275085449</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G328" t="n">
-        <v>25.4808731079102</v>
+        <v>25.4808750152588</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>25.2635555267334</v>
+        <v>25.2635536193848</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>25.0824527740479</v>
+        <v>25.0824546813965</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>24.7655258178711</v>
+        <v>24.7655277252197</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>24.2674980163574</v>
+        <v>24.2675018310547</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>27.8199996948242</v>
       </c>
       <c r="G336" t="n">
-        <v>25.1911125183105</v>
+        <v>25.1911144256592</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>28.1900005340576</v>
       </c>
       <c r="G337" t="n">
-        <v>25.5261497497559</v>
+        <v>25.5261478424072</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>28.9200000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>26.1871700286865</v>
+        <v>26.1871681213379</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>29.4099998474121</v>
       </c>
       <c r="G340" t="n">
-        <v>26.6308631896973</v>
+        <v>26.6308670043945</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>29.25</v>
       </c>
       <c r="G341" t="n">
-        <v>26.4859828948975</v>
+        <v>26.4859867095947</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>29.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>26.3229942321777</v>
+        <v>26.3229923248291</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G343" t="n">
-        <v>26.676139831543</v>
+        <v>26.6761379241943</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>29</v>
       </c>
       <c r="G345" t="n">
-        <v>26.2596054077148</v>
+        <v>26.2596073150635</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>26.6670837402344</v>
+        <v>26.667085647583</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G347" t="n">
-        <v>26.9115715026855</v>
+        <v>26.9115695953369</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>29.4099998474121</v>
       </c>
       <c r="G348" t="n">
-        <v>26.6308631896973</v>
+        <v>26.6308670043945</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>29.3700008392334</v>
       </c>
       <c r="G350" t="n">
-        <v>26.5946483612061</v>
+        <v>26.5946445465088</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>29</v>
       </c>
       <c r="G351" t="n">
-        <v>26.2596054077148</v>
+        <v>26.2596073150635</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G352" t="n">
-        <v>25.3088302612305</v>
+        <v>25.3088283538818</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>28.5300006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>25.8340225219727</v>
+        <v>25.8340244293213</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G355" t="n">
-        <v>25.8984451293945</v>
+        <v>25.8984432220459</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>25.6599998474121</v>
       </c>
       <c r="G358" t="n">
-        <v>23.6159954071045</v>
+        <v>23.6159934997559</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>22.962553024292</v>
+        <v>22.9625511169434</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>22.8705177307129</v>
+        <v>22.8705196380615</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G363" t="n">
-        <v>22.8613166809082</v>
+        <v>22.8613109588623</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>25.25</v>
       </c>
       <c r="G365" t="n">
-        <v>23.2386531829834</v>
+        <v>23.238655090332</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>24.8700008392334</v>
       </c>
       <c r="G367" t="n">
-        <v>22.8889255523682</v>
+        <v>22.8889236450195</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G371" t="n">
-        <v>22.3827362060547</v>
+        <v>22.3827342987061</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>22.3643283843994</v>
+        <v>22.3643264770508</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G373" t="n">
-        <v>22.7416667938232</v>
+        <v>22.7416687011719</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G375" t="n">
-        <v>22.8797206878662</v>
+        <v>22.8797225952148</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>23.2846717834473</v>
+        <v>23.2846698760986</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G378" t="n">
-        <v>23.4319229125977</v>
+        <v>23.4319267272949</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G379" t="n">
-        <v>22.8060913085938</v>
+        <v>22.806095123291</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G380" t="n">
-        <v>23.0269737243652</v>
+        <v>23.0269756317139</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G381" t="n">
-        <v>22.6036167144775</v>
+        <v>22.6036205291748</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>23.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>21.545223236084</v>
+        <v>21.5452251434326</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>21.7200870513916</v>
+        <v>21.7200889587402</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G386" t="n">
-        <v>21.5544300079346</v>
+        <v>21.5544281005859</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>21.6740703582764</v>
+        <v>21.674072265625</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>23.5</v>
       </c>
       <c r="G388" t="n">
-        <v>21.6280536651611</v>
+        <v>21.6280555725098</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>23</v>
       </c>
       <c r="G389" t="n">
-        <v>21.1678829193115</v>
+        <v>21.1678810119629</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>23</v>
       </c>
       <c r="G390" t="n">
-        <v>21.1678829193115</v>
+        <v>21.1678810119629</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G391" t="n">
-        <v>21.2046966552734</v>
+        <v>21.2046985626221</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>23.2700004577637</v>
       </c>
       <c r="G393" t="n">
-        <v>21.416374206543</v>
+        <v>21.4163761138916</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G395" t="n">
-        <v>21.9133605957031</v>
+        <v>21.9133586883545</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G396" t="n">
-        <v>21.8857517242432</v>
+        <v>21.8857498168945</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>24.3099994659424</v>
       </c>
       <c r="G399" t="n">
-        <v>22.3735313415527</v>
+        <v>22.3735332489014</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G402" t="n">
-        <v>22.5299911499023</v>
+        <v>22.5299892425537</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G403" t="n">
-        <v>22.6312274932861</v>
+        <v>22.6312294006348</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G404" t="n">
-        <v>22.6404342651367</v>
+        <v>22.6404323577881</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G405" t="n">
-        <v>22.5576000213623</v>
+        <v>22.5575981140137</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G407" t="n">
-        <v>21.4255790710449</v>
+        <v>21.4255809783936</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>23.5300006866455</v>
       </c>
       <c r="G408" t="n">
-        <v>21.6556644439697</v>
+        <v>21.6556663513184</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>24.1900005340576</v>
       </c>
       <c r="G410" t="n">
-        <v>22.2630920410156</v>
+        <v>22.263090133667</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G414" t="n">
-        <v>22.0514106750488</v>
+        <v>22.0514125823975</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>24.2700004577637</v>
       </c>
       <c r="G417" t="n">
-        <v>22.3367176055908</v>
+        <v>22.3367195129395</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>24.0300006866455</v>
       </c>
       <c r="G418" t="n">
-        <v>22.1158351898193</v>
+        <v>22.115837097168</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>21.7661056518555</v>
+        <v>21.7661037445068</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>23.9699993133545</v>
       </c>
       <c r="G420" t="n">
-        <v>22.0606174468994</v>
+        <v>22.0606136322021</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G422" t="n">
-        <v>21.9133605957031</v>
+        <v>21.9133586883545</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G426" t="n">
-        <v>22.0053939819336</v>
+        <v>22.0053958892822</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G429" t="n">
-        <v>22.0053939819336</v>
+        <v>22.0053958892822</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G430" t="n">
-        <v>21.9133605957031</v>
+        <v>21.9133586883545</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>21.9041557312012</v>
+        <v>21.9041576385498</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G437" t="n">
-        <v>21.6832733154297</v>
+        <v>21.6832752227783</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G438" t="n">
-        <v>20.8273544311523</v>
+        <v>20.827356338501</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G440" t="n">
-        <v>20.94700050354</v>
+        <v>20.9470024108887</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>20.799747467041</v>
+        <v>20.7997455596924</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>22.9300003051758</v>
       </c>
       <c r="G442" t="n">
-        <v>21.103458404541</v>
+        <v>21.1034603118896</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>21.0758476257324</v>
+        <v>21.0758495330811</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>21.9501762390137</v>
+        <v>21.950174331665</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G446" t="n">
-        <v>22.0974292755127</v>
+        <v>22.0974311828613</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G447" t="n">
-        <v>22.0514106750488</v>
+        <v>22.0514125823975</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>23.75</v>
       </c>
       <c r="G448" t="n">
-        <v>21.8581390380859</v>
+        <v>21.8581371307373</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>22.3827362060547</v>
+        <v>22.3827342987061</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>23.5100002288818</v>
       </c>
       <c r="G450" t="n">
-        <v>21.6372566223145</v>
+        <v>21.6372585296631</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G452" t="n">
-        <v>20.9746112823486</v>
+        <v>20.9746150970459</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>20.799747467041</v>
+        <v>20.7997455596924</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G456" t="n">
-        <v>21.0666427612305</v>
+        <v>21.0666446685791</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G459" t="n">
-        <v>21.1586799621582</v>
+        <v>21.1586780548096</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G462" t="n">
-        <v>20.6340847015381</v>
+        <v>20.6340827941895</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G463" t="n">
-        <v>20.4500141143799</v>
+        <v>20.4500160217285</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G465" t="n">
-        <v>20.3947925567627</v>
+        <v>20.3947944641113</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G466" t="n">
-        <v>20.0082492828369</v>
+        <v>20.0082511901855</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>19.9714374542236</v>
+        <v>19.9714393615723</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>20.0634727478027</v>
+        <v>20.0634708404541</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G469" t="n">
-        <v>20.4868278503418</v>
+        <v>20.4868297576904</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G473" t="n">
-        <v>21.0666427612305</v>
+        <v>21.0666446685791</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G476" t="n">
-        <v>20.94700050354</v>
+        <v>20.9470024108887</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>22</v>
       </c>
       <c r="G478" t="n">
-        <v>20.2475414276123</v>
+        <v>20.2475395202637</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>21.9099998474121</v>
       </c>
       <c r="G479" t="n">
-        <v>20.1647090911865</v>
+        <v>20.1647071838379</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G480" t="n">
-        <v>20.0910835266113</v>
+        <v>20.0910816192627</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>19.6953353881836</v>
+        <v>19.6953315734863</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G485" t="n">
-        <v>20.1831169128418</v>
+        <v>20.1831150054932</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>20.4316101074219</v>
+        <v>20.4316082000732</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G494" t="n">
-        <v>21.0482387542725</v>
+        <v>21.0482406616211</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>23.0300006866455</v>
       </c>
       <c r="G496" t="n">
-        <v>21.1954917907715</v>
+        <v>21.1954936981201</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>23.2700004577637</v>
       </c>
       <c r="G499" t="n">
-        <v>21.416374206543</v>
+        <v>21.4163761138916</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G501" t="n">
-        <v>20.6708984375</v>
+        <v>20.6708965301514</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G502" t="n">
-        <v>20.7721347808838</v>
+        <v>20.7721366882324</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>19.4652462005615</v>
+        <v>19.4652481079102</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G504" t="n">
-        <v>19.7965698242188</v>
+        <v>19.796573638916</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G507" t="n">
-        <v>20.2199268341064</v>
+        <v>20.2199287414551</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G512" t="n">
-        <v>20.2199268341064</v>
+        <v>20.2199287414551</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G514" t="n">
-        <v>20.6524906158447</v>
+        <v>20.6524925231934</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>22.7199993133545</v>
       </c>
       <c r="G515" t="n">
-        <v>20.9101886749268</v>
+        <v>20.9101867675781</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G516" t="n">
-        <v>20.6524906158447</v>
+        <v>20.6524925231934</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>22.2399997711182</v>
       </c>
       <c r="G518" t="n">
-        <v>20.4684238433838</v>
+        <v>20.4684219360352</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G520" t="n">
-        <v>20.4868278503418</v>
+        <v>20.4868297576904</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>20.4316101074219</v>
+        <v>20.4316082000732</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G522" t="n">
-        <v>20.4500141143799</v>
+        <v>20.4500160217285</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>22</v>
       </c>
       <c r="G523" t="n">
-        <v>20.2475414276123</v>
+        <v>20.2475395202637</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G525" t="n">
-        <v>20.94700050354</v>
+        <v>20.9470024108887</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G533" t="n">
-        <v>20.8549652099609</v>
+        <v>20.8549690246582</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>22.7299995422363</v>
       </c>
       <c r="G535" t="n">
-        <v>20.9193897247314</v>
+        <v>20.9193916320801</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G536" t="n">
-        <v>20.5052356719971</v>
+        <v>20.5052375793457</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>22.1100006103516</v>
       </c>
       <c r="G537" t="n">
-        <v>20.3487777709961</v>
+        <v>20.3487796783447</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G538" t="n">
-        <v>20.6340847015381</v>
+        <v>20.6340827941895</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G539" t="n">
-        <v>20.0266571044922</v>
+        <v>20.0266590118408</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>21.4300003051758</v>
       </c>
       <c r="G540" t="n">
-        <v>19.7229442596436</v>
+        <v>19.7229461669922</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G541" t="n">
-        <v>20.0082492828369</v>
+        <v>20.0082511901855</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G542" t="n">
-        <v>19.9162158966064</v>
+        <v>19.9162178039551</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>22</v>
       </c>
       <c r="G543" t="n">
-        <v>20.2475414276123</v>
+        <v>20.2475395202637</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G546" t="n">
-        <v>20.6340847015381</v>
+        <v>20.6340827941895</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G547" t="n">
-        <v>20.4500141143799</v>
+        <v>20.4500160217285</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>23.0300006866455</v>
       </c>
       <c r="G549" t="n">
-        <v>21.1954917907715</v>
+        <v>21.1954936981201</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G552" t="n">
-        <v>20.8365573883057</v>
+        <v>20.8365592956543</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G555" t="n">
-        <v>20.6248798370361</v>
+        <v>20.6248817443848</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G557" t="n">
-        <v>20.0910835266113</v>
+        <v>20.0910816192627</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>20.109489440918</v>
+        <v>20.1094875335693</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>19.9714374542236</v>
+        <v>19.9714393615723</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G561" t="n">
-        <v>19.9990463256836</v>
+        <v>19.9990482330322</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>20.109489440918</v>
+        <v>20.1094875335693</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>22.6800003051758</v>
       </c>
       <c r="G567" t="n">
-        <v>20.8733730316162</v>
+        <v>20.8733749389648</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G569" t="n">
-        <v>20.3763866424561</v>
+        <v>20.3763885498047</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G570" t="n">
-        <v>20.6524906158447</v>
+        <v>20.6524925231934</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>22.3099994659424</v>
       </c>
       <c r="G571" t="n">
-        <v>20.5328483581543</v>
+        <v>20.532844543457</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G574" t="n">
-        <v>20.6340847015381</v>
+        <v>20.6340827941895</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G575" t="n">
-        <v>20.64328956604</v>
+        <v>20.6432876586914</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>20.6156749725342</v>
+        <v>20.6156768798828</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G580" t="n">
-        <v>20.3947925567627</v>
+        <v>20.3947944641113</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G582" t="n">
-        <v>20.9746112823486</v>
+        <v>20.9746150970459</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G583" t="n">
-        <v>21.2046966552734</v>
+        <v>21.2046985626221</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>21.2783241271973</v>
+        <v>21.2783260345459</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>21.536018371582</v>
+        <v>21.5360221862793</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>21.536018371582</v>
+        <v>21.5360221862793</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G589" t="n">
-        <v>21.7937164306641</v>
+        <v>21.7937145233154</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G592" t="n">
-        <v>22.4195518493652</v>
+        <v>22.419548034668</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G593" t="n">
-        <v>22.2078704833984</v>
+        <v>22.2078685760498</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G595" t="n">
-        <v>22.8797206878662</v>
+        <v>22.8797225952148</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G596" t="n">
-        <v>22.7416667938232</v>
+        <v>22.7416687011719</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>22.6404342651367</v>
+        <v>22.6404323577881</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>24.5699996948242</v>
       </c>
       <c r="G598" t="n">
-        <v>22.6128196716309</v>
+        <v>22.6128215789795</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G599" t="n">
-        <v>22.6312274932861</v>
+        <v>22.6312294006348</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G601" t="n">
-        <v>22.6864490509033</v>
+        <v>22.6864471435547</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>22.7324676513672</v>
+        <v>22.7324657440186</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G603" t="n">
-        <v>22.8337020874023</v>
+        <v>22.8337001800537</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G604" t="n">
-        <v>22.7692775726318</v>
+        <v>22.7692794799805</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G605" t="n">
-        <v>22.9073295593262</v>
+        <v>22.9073314666748</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G609" t="n">
-        <v>23.3090705871582</v>
+        <v>23.3090686798096</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>23.4118728637695</v>
+        <v>23.4118747711182</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G614" t="n">
-        <v>22.355770111084</v>
+        <v>22.3557720184326</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>24.9899997711182</v>
       </c>
       <c r="G617" t="n">
-        <v>23.3557987213135</v>
+        <v>23.3557968139648</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>24.8199996948242</v>
       </c>
       <c r="G618" t="n">
-        <v>23.1969184875488</v>
+        <v>23.1969165802002</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G621" t="n">
-        <v>22.6548461914062</v>
+        <v>22.6548442840576</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>24.3299999237061</v>
       </c>
       <c r="G622" t="n">
-        <v>22.7389583587646</v>
+        <v>22.7389602661133</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G626" t="n">
-        <v>23.3838367462158</v>
+        <v>23.3838386535645</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G629" t="n">
-        <v>22.9258804321289</v>
+        <v>22.9258823394775</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G630" t="n">
-        <v>20.9912452697754</v>
+        <v>20.991247177124</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>21.3899993896484</v>
       </c>
       <c r="G633" t="n">
-        <v>19.9912166595459</v>
+        <v>19.9912185668945</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G634" t="n">
-        <v>19.7388744354248</v>
+        <v>19.7388782501221</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G636" t="n">
-        <v>19.3089561462402</v>
+        <v>19.3089542388916</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G638" t="n">
-        <v>19.4958782196045</v>
+        <v>19.4958763122559</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G641" t="n">
-        <v>18.6266937255859</v>
+        <v>18.6266956329346</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G642" t="n">
-        <v>18.3836975097656</v>
+        <v>18.383695602417</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>19.3449993133545</v>
       </c>
       <c r="G645" t="n">
-        <v>18.0799503326416</v>
+        <v>18.079948425293</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G646" t="n">
-        <v>18.3836975097656</v>
+        <v>18.383695602417</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G649" t="n">
-        <v>18.794921875</v>
+        <v>18.7949237823486</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>20.0900001525879</v>
       </c>
       <c r="G650" t="n">
-        <v>18.7762298583984</v>
+        <v>18.7762317657471</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>19.875</v>
       </c>
       <c r="G653" t="n">
-        <v>18.5752906799316</v>
+        <v>18.5752925872803</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>19.8250007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>18.5285625457764</v>
+        <v>18.5285587310791</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>19.7250003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>18.4351005554199</v>
+        <v>18.4350986480713</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>19.6749992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>18.3883686065674</v>
+        <v>18.388370513916</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G659" t="n">
-        <v>18.4911766052246</v>
+        <v>18.491174697876</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G660" t="n">
-        <v>18.2435073852539</v>
+        <v>18.2435054779053</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>17.8042392730713</v>
+        <v>17.8042373657227</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>19.375</v>
       </c>
       <c r="G663" t="n">
-        <v>18.1079883575439</v>
+        <v>18.1079864501953</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>20.0699996948242</v>
       </c>
       <c r="G666" t="n">
-        <v>18.7575397491455</v>
+        <v>18.7575378417969</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G670" t="n">
-        <v>18.4911766052246</v>
+        <v>18.491174697876</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>19.5550003051758</v>
       </c>
       <c r="G671" t="n">
-        <v>18.2762184143066</v>
+        <v>18.276216506958</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G672" t="n">
-        <v>18.2528533935547</v>
+        <v>18.2528514862061</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>19.6650009155273</v>
       </c>
       <c r="G674" t="n">
-        <v>18.3790225982666</v>
+        <v>18.3790245056152</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G677" t="n">
-        <v>19.402416229248</v>
+        <v>19.4024181365967</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G679" t="n">
-        <v>19.4304542541504</v>
+        <v>19.4304523468018</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G680" t="n">
-        <v>19.3650321960449</v>
+        <v>19.3650302886963</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>20.5100002288818</v>
       </c>
       <c r="G682" t="n">
-        <v>19.1687641143799</v>
+        <v>19.1687679290771</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>19.1126880645752</v>
+        <v>19.1126899719238</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G685" t="n">
-        <v>18.7388458251953</v>
+        <v>18.7388439178467</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G687" t="n">
-        <v>19.0566120147705</v>
+        <v>19.0566101074219</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G689" t="n">
-        <v>19.6080284118652</v>
+        <v>19.6080303192139</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G691" t="n">
-        <v>19.5239162445068</v>
+        <v>19.5239143371582</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G692" t="n">
-        <v>19.4211082458496</v>
+        <v>19.4211101531982</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>19.8136444091797</v>
+        <v>19.8136425018311</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G695" t="n">
-        <v>19.7482204437256</v>
+        <v>19.748218536377</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G697" t="n">
-        <v>19.6080284118652</v>
+        <v>19.6080303192139</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>19.7669105529785</v>
+        <v>19.7669124603271</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>21.1700000762939</v>
       </c>
       <c r="G699" t="n">
-        <v>19.7856063842773</v>
+        <v>19.7856044769287</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G701" t="n">
-        <v>19.2809181213379</v>
+        <v>19.2809162139893</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G704" t="n">
-        <v>19.0566120147705</v>
+        <v>19.0566101074219</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G705" t="n">
-        <v>18.804271697998</v>
+        <v>18.8042697906494</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>18.1780853271484</v>
+        <v>18.1780834197998</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>18.6453876495361</v>
+        <v>18.6453857421875</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>19.1049995422363</v>
       </c>
       <c r="G709" t="n">
-        <v>17.8556442260742</v>
+        <v>17.8556423187256</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G716" t="n">
-        <v>18.2154674530029</v>
+        <v>18.2154655456543</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>20.5300006866455</v>
       </c>
       <c r="G718" t="n">
-        <v>19.1874580383301</v>
+        <v>19.1874561309814</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G722" t="n">
-        <v>19.645414352417</v>
+        <v>19.6454162597656</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>20.9099998474121</v>
       </c>
       <c r="G724" t="n">
-        <v>19.5426063537598</v>
+        <v>19.5426082611084</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>20.0005645751953</v>
+        <v>20.0005626678467</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G733" t="n">
-        <v>19.7014904022217</v>
+        <v>19.701488494873</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G742" t="n">
-        <v>19.3650321960449</v>
+        <v>19.3650302886963</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G747" t="n">
-        <v>19.7014904022217</v>
+        <v>19.701488494873</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G749" t="n">
-        <v>19.4304542541504</v>
+        <v>19.4304523468018</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>19.2061462402344</v>
+        <v>19.206148147583</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G754" t="n">
-        <v>17.0472106933594</v>
+        <v>17.0472087860107</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>17.7450008392334</v>
       </c>
       <c r="G757" t="n">
-        <v>16.5845794677734</v>
+        <v>16.5845813751221</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>16.4957904815674</v>
+        <v>16.495792388916</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G762" t="n">
-        <v>16.7528076171875</v>
+        <v>16.7528095245361</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>17.1650009155273</v>
       </c>
       <c r="G765" t="n">
-        <v>16.0425071716309</v>
+        <v>16.0425109863281</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>16.4957904815674</v>
+        <v>16.495792388916</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>16.5425243377686</v>
+        <v>16.5425224304199</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G769" t="n">
-        <v>16.8415966033936</v>
+        <v>16.8415985107422</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G770" t="n">
-        <v>16.6640224456787</v>
+        <v>16.6640205383301</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>16.4957904815674</v>
+        <v>16.495792388916</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G774" t="n">
-        <v>16.6827144622803</v>
+        <v>16.6827125549316</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G775" t="n">
-        <v>16.5986003875732</v>
+        <v>16.5985984802246</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G779" t="n">
-        <v>16.1593341827393</v>
+        <v>16.1593360900879</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>16.2154121398926</v>
+        <v>16.2154102325439</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G787" t="n">
-        <v>16.4957904815674</v>
+        <v>16.495792388916</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G788" t="n">
-        <v>16.5238285064697</v>
+        <v>16.5238304138184</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G792" t="n">
-        <v>16.579906463623</v>
+        <v>16.5799083709717</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G794" t="n">
-        <v>17.7855491638184</v>
+        <v>17.785551071167</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>17.1967468261719</v>
+        <v>17.1967449188232</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>18.8050003051758</v>
       </c>
       <c r="G797" t="n">
-        <v>17.5752601623535</v>
+        <v>17.5752620697021</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G799" t="n">
-        <v>17.4163799285889</v>
+        <v>17.4163780212402</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G801" t="n">
-        <v>17.1313247680664</v>
+        <v>17.1313228607178</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>18.7150001525879</v>
       </c>
       <c r="G803" t="n">
-        <v>17.4911479949951</v>
+        <v>17.4911499023438</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G804" t="n">
-        <v>17.4397430419922</v>
+        <v>17.4397449493408</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>18.6749992370605</v>
       </c>
       <c r="G805" t="n">
-        <v>17.453763961792</v>
+        <v>17.4537620544434</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G806" t="n">
-        <v>17.7294731140137</v>
+        <v>17.729471206665</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G807" t="n">
-        <v>17.6547050476074</v>
+        <v>17.6547031402588</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>17.3369369506836</v>
+        <v>17.3369388580322</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G809" t="n">
-        <v>17.4163799285889</v>
+        <v>17.4163780212402</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G812" t="n">
-        <v>17.1687107086182</v>
+        <v>17.1687088012695</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>18</v>
       </c>
       <c r="G813" t="n">
-        <v>16.8229064941406</v>
+        <v>16.822904586792</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>19.1650009155273</v>
       </c>
       <c r="G815" t="n">
-        <v>17.9117221832275</v>
+        <v>17.9117202758789</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G817" t="n">
-        <v>17.6593761444092</v>
+        <v>17.6593780517578</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G818" t="n">
-        <v>17.7948970794678</v>
+        <v>17.7948951721191</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G821" t="n">
-        <v>17.3275928497314</v>
+        <v>17.3275909423828</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>18.6149997711182</v>
       </c>
       <c r="G822" t="n">
-        <v>17.3976898193359</v>
+        <v>17.3976879119873</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G823" t="n">
-        <v>17.6266670227051</v>
+        <v>17.6266651153564</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>19.5949993133545</v>
       </c>
       <c r="G827" t="n">
-        <v>18.3135986328125</v>
+        <v>18.3136005401611</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G828" t="n">
-        <v>18.2154674530029</v>
+        <v>18.2154655456543</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G829" t="n">
-        <v>18.0565814971924</v>
+        <v>18.056583404541</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>19.5949993133545</v>
       </c>
       <c r="G830" t="n">
-        <v>18.3135986328125</v>
+        <v>18.3136005401611</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>20</v>
       </c>
       <c r="G835" t="n">
-        <v>18.6921157836914</v>
+        <v>18.69211769104</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>19.5550003051758</v>
       </c>
       <c r="G838" t="n">
-        <v>18.2762184143066</v>
+        <v>18.276216506958</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>19.8549995422363</v>
       </c>
       <c r="G839" t="n">
-        <v>18.5565986633301</v>
+        <v>18.5565967559814</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G840" t="n">
-        <v>18.4397716522217</v>
+        <v>18.439769744873</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>19.8250007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>18.5285625457764</v>
+        <v>18.5285587310791</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G845" t="n">
-        <v>18.3089294433594</v>
+        <v>18.3089275360107</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>19.6550006866455</v>
       </c>
       <c r="G847" t="n">
-        <v>18.3696765899658</v>
+        <v>18.3696784973145</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G853" t="n">
-        <v>18.0939674377441</v>
+        <v>18.0939693450928</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G854" t="n">
-        <v>17.6266670227051</v>
+        <v>17.6266651153564</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>19.3449993133545</v>
       </c>
       <c r="G855" t="n">
-        <v>18.0799503326416</v>
+        <v>18.079948425293</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>20.0472946166992</v>
+        <v>20.0472965240479</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>19.9071044921875</v>
+        <v>19.9071025848389</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>20.1299991607666</v>
       </c>
       <c r="G864" t="n">
-        <v>19.1187973022461</v>
+        <v>19.1187953948975</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>19.9549999237061</v>
       </c>
       <c r="G866" t="n">
-        <v>18.9525871276855</v>
+        <v>18.9525890350342</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G868" t="n">
-        <v>17.7131423950195</v>
+        <v>17.7131443023682</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>18.6650009155273</v>
       </c>
       <c r="G869" t="n">
-        <v>17.7273921966553</v>
+        <v>17.7273902893066</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>18.7749996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>17.8318614959717</v>
+        <v>17.8318634033203</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G872" t="n">
-        <v>18.6534099578857</v>
+        <v>18.6534118652344</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>20.2299995422363</v>
       </c>
       <c r="G876" t="n">
-        <v>19.213773727417</v>
+        <v>19.2137718200684</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>19.9850006103516</v>
       </c>
       <c r="G877" t="n">
-        <v>18.9810791015625</v>
+        <v>18.9810810089111</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G878" t="n">
-        <v>18.9050998687744</v>
+        <v>18.905101776123</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G879" t="n">
-        <v>19.033317565918</v>
+        <v>19.0333194732666</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G880" t="n">
-        <v>19.6601657867432</v>
+        <v>19.6601638793945</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G887" t="n">
-        <v>19.745641708374</v>
+        <v>19.7456436157227</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>20.4674663543701</v>
+        <v>20.4674644470215</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>21.5699996948242</v>
       </c>
       <c r="G892" t="n">
-        <v>20.4864616394043</v>
+        <v>20.4864597320557</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>21.0900001525879</v>
       </c>
       <c r="G902" t="n">
-        <v>20.030574798584</v>
+        <v>20.0305728912354</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G907" t="n">
-        <v>19.9640884399414</v>
+        <v>19.96409034729</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G908" t="n">
-        <v>20.0020809173584</v>
+        <v>20.0020790100098</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G915" t="n">
-        <v>17.2762489318848</v>
+        <v>17.2762508392334</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G916" t="n">
-        <v>17.266752243042</v>
+        <v>17.2667541503906</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>17.9150009155273</v>
       </c>
       <c r="G920" t="n">
-        <v>17.0150680541992</v>
+        <v>17.0150661468506</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>17.4750003814697</v>
       </c>
       <c r="G921" t="n">
-        <v>16.59716796875</v>
+        <v>16.5971660614014</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G922" t="n">
-        <v>16.2837448120117</v>
+        <v>16.2837467193604</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G926" t="n">
-        <v>16.915340423584</v>
+        <v>16.9153385162354</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G928" t="n">
-        <v>16.734884262085</v>
+        <v>16.7348861694336</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G929" t="n">
-        <v>16.948579788208</v>
+        <v>16.9485816955566</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>17.6350002288818</v>
       </c>
       <c r="G930" t="n">
-        <v>16.7491302490234</v>
+        <v>16.7491321563721</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G933" t="n">
-        <v>16.668399810791</v>
+        <v>16.6683979034424</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G936" t="n">
-        <v>17.4329624176025</v>
+        <v>17.4329605102539</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>17.2857475280762</v>
+        <v>17.2857494354248</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G951" t="n">
-        <v>16.3454780578613</v>
+        <v>16.34547996521</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>16.9549999237061</v>
       </c>
       <c r="G953" t="n">
-        <v>16.1032905578613</v>
+        <v>16.1032886505127</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>16.8649997711182</v>
       </c>
       <c r="G954" t="n">
-        <v>16.0178089141846</v>
+        <v>16.0178108215332</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>15.4811916351318</v>
+        <v>15.4811906814575</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G956" t="n">
-        <v>15.5381784439087</v>
+        <v>15.538179397583</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>16.3850002288818</v>
       </c>
       <c r="G957" t="n">
-        <v>15.5619220733643</v>
+        <v>15.5619230270386</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>15.4811916351318</v>
+        <v>15.4811906814575</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>16.1350002288818</v>
       </c>
       <c r="G966" t="n">
-        <v>15.3244800567627</v>
+        <v>15.324481010437</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>16.0650005340576</v>
       </c>
       <c r="G968" t="n">
-        <v>15.2579975128174</v>
+        <v>15.2579965591431</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G971" t="n">
-        <v>15.0348024368286</v>
+        <v>15.0348014831543</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G972" t="n">
-        <v>15.319730758667</v>
+        <v>15.3197317123413</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G973" t="n">
-        <v>15.9608240127563</v>
+        <v>15.960823059082</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G975" t="n">
-        <v>15.8800926208496</v>
+        <v>15.8800916671753</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>16.9950008392334</v>
       </c>
       <c r="G978" t="n">
-        <v>16.1412811279297</v>
+        <v>16.1412792205811</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G980" t="n">
-        <v>16.4024639129639</v>
+        <v>16.4024658203125</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>17.4549999237061</v>
       </c>
       <c r="G981" t="n">
-        <v>16.5781726837158</v>
+        <v>16.5781707763672</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G985" t="n">
-        <v>17.2762489318848</v>
+        <v>17.2762508392334</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G992" t="n">
-        <v>16.4024639129639</v>
+        <v>16.4024658203125</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G998" t="n">
-        <v>16.6873970031738</v>
+        <v>16.6873950958252</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1000" t="n">
-        <v>16.734884262085</v>
+        <v>16.7348861694336</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>18.2549991607666</v>
       </c>
       <c r="G1006" t="n">
-        <v>17.337984085083</v>
+        <v>17.3379859924316</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G1007" t="n">
-        <v>17.4092178344727</v>
+        <v>17.409215927124</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1009" t="n">
-        <v>17.5421848297119</v>
+        <v>17.5421829223633</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>18.4050006866455</v>
       </c>
       <c r="G1010" t="n">
-        <v>17.4804515838623</v>
+        <v>17.4804496765137</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>19.0750007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>18.1167964935303</v>
+        <v>18.1167945861816</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1020" t="n">
-        <v>17.9885768890381</v>
+        <v>17.9885749816895</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>18.2549991607666</v>
       </c>
       <c r="G1026" t="n">
-        <v>17.337984085083</v>
+        <v>17.3379859924316</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.228759765625</v>
+        <v>17.2287616729736</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>18</v>
       </c>
       <c r="G1029" t="n">
-        <v>17.095796585083</v>
+        <v>17.0957946777344</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1035" t="n">
-        <v>16.2979907989502</v>
+        <v>16.2979927062988</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1037" t="n">
-        <v>15.8468494415283</v>
+        <v>15.8468503952026</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1038" t="n">
-        <v>15.8800926208496</v>
+        <v>15.8800916671753</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>15.7186317443848</v>
+        <v>15.7186326980591</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>16.1550006866455</v>
       </c>
       <c r="G1044" t="n">
-        <v>15.3434762954712</v>
+        <v>15.3434772491455</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1045" t="n">
-        <v>15.9845685958862</v>
+        <v>15.9845676422119</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.7471265792847</v>
+        <v>15.747127532959</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1047" t="n">
-        <v>15.6046619415283</v>
+        <v>15.604660987854</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1049" t="n">
-        <v>15.7043867111206</v>
+        <v>15.7043857574463</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>16.7250003814697</v>
       </c>
       <c r="G1050" t="n">
-        <v>15.8848438262939</v>
+        <v>15.8848428726196</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>16.3649997711182</v>
       </c>
       <c r="G1051" t="n">
-        <v>15.5429258346558</v>
+        <v>15.5429267883301</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G1057" t="n">
-        <v>13.5721607208252</v>
+        <v>13.5721616744995</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>11.3549995422363</v>
       </c>
       <c r="G1065" t="n">
-        <v>10.7845973968506</v>
+        <v>10.7845964431763</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>10.164999961853</v>
       </c>
       <c r="G1067" t="n">
-        <v>9.65437412261963</v>
+        <v>9.65437507629395</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1074" t="n">
-        <v>13.0877809524536</v>
+        <v>13.0877799987793</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>13.6549997329712</v>
       </c>
       <c r="G1076" t="n">
-        <v>12.9690589904785</v>
+        <v>12.9690599441528</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1080" t="n">
-        <v>11.2072429656982</v>
+        <v>11.2072439193726</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1082" t="n">
-        <v>11.1882467269897</v>
+        <v>11.1882476806641</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1083" t="n">
-        <v>11.5681552886963</v>
+        <v>11.568154335022</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1085" t="n">
-        <v>11.6251401901245</v>
+        <v>11.6251411437988</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1100" t="n">
-        <v>10.3049650192261</v>
+        <v>10.3049659729004</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G1103" t="n">
-        <v>10.3429574966431</v>
+        <v>10.3429565429688</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G1114" t="n">
-        <v>9.64962577819824</v>
+        <v>9.64962673187256</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1115" t="n">
-        <v>9.78259468078613</v>
+        <v>9.78259372711182</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>13</v>
       </c>
       <c r="G1118" t="n">
-        <v>12.3469638824463</v>
+        <v>12.346962928772</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1130" t="n">
-        <v>12.062032699585</v>
+        <v>12.0620336532593</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1131" t="n">
-        <v>12.1190185546875</v>
+        <v>12.1190195083618</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1133" t="n">
-        <v>12.3089714050293</v>
+        <v>12.3089723587036</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1138" t="n">
-        <v>11.8055963516235</v>
+        <v>11.8055953979492</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G1142" t="n">
-        <v>11.5206670761108</v>
+        <v>11.5206661224365</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1145" t="n">
-        <v>11.5871496200562</v>
+        <v>11.5871486663818</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1147" t="n">
-        <v>11.3402109146118</v>
+        <v>11.3402099609375</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.9887962341309</v>
+        <v>10.9887971878052</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G1150" t="n">
-        <v>11.1787509918213</v>
+        <v>11.1787519454956</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1151" t="n">
-        <v>10.9887962341309</v>
+        <v>10.9887971878052</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1152" t="n">
-        <v>11.1882467269897</v>
+        <v>11.1882476806641</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G1162" t="n">
-        <v>11.0552816390991</v>
+        <v>11.0552806854248</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1163" t="n">
-        <v>11.2167406082153</v>
+        <v>11.2167415618896</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1172" t="n">
-        <v>11.6251401901245</v>
+        <v>11.6251411437988</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1173" t="n">
-        <v>11.6441354751587</v>
+        <v>11.644136428833</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1177" t="n">
-        <v>10.9603042602539</v>
+        <v>10.9603052139282</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>10.7798480987549</v>
+        <v>10.7798490524292</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1181" t="n">
-        <v>10.6753749847412</v>
+        <v>10.6753740310669</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1183" t="n">
-        <v>11.6251401901245</v>
+        <v>11.6251411437988</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1184" t="n">
-        <v>11.6251401901245</v>
+        <v>11.6251411437988</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1188" t="n">
-        <v>11.7960996627808</v>
+        <v>11.7960987091064</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G1191" t="n">
-        <v>11.4256887435913</v>
+        <v>11.4256896972656</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G1195" t="n">
-        <v>11.4256887435913</v>
+        <v>11.4256896972656</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>11.5871496200562</v>
+        <v>11.5871486663818</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1201" t="n">
-        <v>11.5681552886963</v>
+        <v>11.568154335022</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>12.75</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.1095209121704</v>
+        <v>12.1095218658447</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>12.0145454406738</v>
+        <v>12.0145444869995</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.1285181045532</v>
+        <v>12.1285171508789</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1212" t="n">
-        <v>12.2804794311523</v>
+        <v>12.2804803848267</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>12.0145454406738</v>
+        <v>12.0145444869995</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1222" t="n">
-        <v>12.8978271484375</v>
+        <v>12.8978281021118</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1224" t="n">
-        <v>11.8910751342773</v>
+        <v>11.8910760879517</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G1225" t="n">
-        <v>11.67262840271</v>
+        <v>11.6726293563843</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G1231" t="n">
-        <v>11.0552816390991</v>
+        <v>11.0552806854248</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1234" t="n">
-        <v>11.359206199646</v>
+        <v>11.3592052459717</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G1236" t="n">
-        <v>12.7933540344238</v>
+        <v>12.7933530807495</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1238" t="n">
-        <v>12.8978271484375</v>
+        <v>12.8978281021118</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1239" t="n">
-        <v>13.7811098098755</v>
+        <v>13.7811107635498</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1240" t="n">
-        <v>13.7146263122559</v>
+        <v>13.7146253585815</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G1242" t="n">
-        <v>13.9330739974976</v>
+        <v>13.9330730438232</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1244" t="n">
-        <v>14.3414716720581</v>
+        <v>14.3414726257324</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1246" t="n">
-        <v>14.6264019012451</v>
+        <v>14.6264009475708</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1247" t="n">
-        <v>14.6264019012451</v>
+        <v>14.6264009475708</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G1248" t="n">
-        <v>14.3129787445068</v>
+        <v>14.3129796981812</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1249" t="n">
-        <v>14.1515197753906</v>
+        <v>14.1515188217163</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G1252" t="n">
-        <v>14.4649410247803</v>
+        <v>14.4649419784546</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1253" t="n">
-        <v>14.9113311767578</v>
+        <v>14.9113321304321</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G1259" t="n">
-        <v>14.5979099273682</v>
+        <v>14.5979089736938</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1262" t="n">
-        <v>14.8828392028809</v>
+        <v>14.8828401565552</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1263" t="n">
-        <v>14.8543462753296</v>
+        <v>14.8543472290039</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1265" t="n">
-        <v>14.3794641494751</v>
+        <v>14.3794631958008</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1276" t="n">
-        <v>14.578914642334</v>
+        <v>14.5789136886597</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1277" t="n">
-        <v>14.4079561233521</v>
+        <v>14.4079551696777</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1280" t="n">
-        <v>13.9615659713745</v>
+        <v>13.9615650177002</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1282" t="n">
-        <v>14.3794641494751</v>
+        <v>14.3794631958008</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G1283" t="n">
-        <v>14.4459457397461</v>
+        <v>14.4459466934204</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G1284" t="n">
-        <v>15.319730758667</v>
+        <v>15.3197317123413</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1286" t="n">
-        <v>14.6833877563477</v>
+        <v>14.683388710022</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1288" t="n">
-        <v>15.8041124343872</v>
+        <v>15.8041114807129</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1290" t="n">
-        <v>15.2627458572388</v>
+        <v>15.2627449035645</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1292" t="n">
-        <v>15.0443000793457</v>
+        <v>15.0442991256714</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1295" t="n">
-        <v>14.6358995437622</v>
+        <v>14.6359004974365</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1296" t="n">
-        <v>14.6264019012451</v>
+        <v>14.6264009475708</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1297" t="n">
-        <v>14.4364490509033</v>
+        <v>14.4364500045776</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1298" t="n">
-        <v>14.578914642334</v>
+        <v>14.5789136886597</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1305" t="n">
-        <v>14.7783641815186</v>
+        <v>14.7783651351929</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G1306" t="n">
-        <v>14.8258533477783</v>
+        <v>14.825852394104</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1310" t="n">
-        <v>15.1202802658081</v>
+        <v>15.1202812194824</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1312" t="n">
-        <v>15.2627458572388</v>
+        <v>15.2627449035645</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1314" t="n">
-        <v>15.1012849807739</v>
+        <v>15.1012859344482</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G1315" t="n">
-        <v>14.8448486328125</v>
+        <v>14.8448476791382</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1320" t="n">
-        <v>16.0320568084717</v>
+        <v>16.032054901123</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1321" t="n">
-        <v>15.8231086730957</v>
+        <v>15.8231077194214</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1323" t="n">
-        <v>15.8800926208496</v>
+        <v>15.8800916671753</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>15.7376270294189</v>
+        <v>15.7376289367676</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1327" t="n">
-        <v>15.7091360092163</v>
+        <v>15.7091369628906</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1332" t="n">
-        <v>15.6996402740479</v>
+        <v>15.6996393203735</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1333" t="n">
-        <v>15.5381784439087</v>
+        <v>15.538179397583</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G1335" t="n">
-        <v>15.9608240127563</v>
+        <v>15.960823059082</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1339" t="n">
-        <v>15.8468494415283</v>
+        <v>15.8468503952026</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G1340" t="n">
-        <v>16.2837448120117</v>
+        <v>16.2837467193604</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1345" t="n">
-        <v>16.4784488677979</v>
+        <v>16.4784469604492</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>17.9349994659424</v>
       </c>
       <c r="G1346" t="n">
-        <v>17.0340595245361</v>
+        <v>17.0340576171875</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G1348" t="n">
-        <v>17.4567050933838</v>
+        <v>17.4567031860352</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>17.9850006103516</v>
       </c>
       <c r="G1352" t="n">
-        <v>17.0815486907959</v>
+        <v>17.0815467834473</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1354" t="n">
-        <v>17.0245628356934</v>
+        <v>17.0245609283447</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1356" t="n">
-        <v>17.5421848297119</v>
+        <v>17.5421829223633</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>18.3850002288818</v>
       </c>
       <c r="G1358" t="n">
-        <v>17.4614562988281</v>
+        <v>17.4614543914795</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1363" t="n">
-        <v>18.1975231170654</v>
+        <v>18.1975250244141</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G1364" t="n">
-        <v>18.1500358581543</v>
+        <v>18.1500377655029</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>18.9050006866455</v>
       </c>
       <c r="G1369" t="n">
-        <v>17.9553356170654</v>
+        <v>17.9553337097168</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>18.9950008392334</v>
       </c>
       <c r="G1372" t="n">
-        <v>18.0408115386963</v>
+        <v>18.0408134460449</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1373" t="n">
-        <v>18.3304920196533</v>
+        <v>18.3304901123047</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1374" t="n">
-        <v>18.3304920196533</v>
+        <v>18.3304901123047</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G1378" t="n">
-        <v>18.3542366027832</v>
+        <v>18.3542346954346</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G1382" t="n">
-        <v>18.3542366027832</v>
+        <v>18.3542346954346</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>19.3050003051758</v>
       </c>
       <c r="G1393" t="n">
-        <v>18.335241317749</v>
+        <v>18.3352394104004</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G1394" t="n">
-        <v>17.8461112976074</v>
+        <v>17.8461093902588</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1398" t="n">
-        <v>17.228759765625</v>
+        <v>17.2287616729736</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>18.0650005340576</v>
       </c>
       <c r="G1401" t="n">
-        <v>17.1575298309326</v>
+        <v>17.1575317382812</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G1405" t="n">
-        <v>16.7253856658936</v>
+        <v>16.7253875732422</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>16.8250007629395</v>
       </c>
       <c r="G1410" t="n">
-        <v>15.9798192977905</v>
+        <v>15.9798202514648</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G1413" t="n">
-        <v>16.2505054473877</v>
+        <v>16.2505035400391</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>16.9150009155273</v>
       </c>
       <c r="G1422" t="n">
-        <v>16.0652980804443</v>
+        <v>16.065299987793</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>18.3150005340576</v>
       </c>
       <c r="G1425" t="n">
-        <v>17.3949699401855</v>
+        <v>17.3949718475342</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G1426" t="n">
-        <v>18.4919509887695</v>
+        <v>18.4919528961182</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>16.5650005340576</v>
       </c>
       <c r="G1432" t="n">
-        <v>15.7328796386719</v>
+        <v>15.7328805923462</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1436" t="n">
-        <v>15.8041124343872</v>
+        <v>15.8041114807129</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>16.8150005340576</v>
       </c>
       <c r="G1437" t="n">
-        <v>15.9703226089478</v>
+        <v>15.9703235626221</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G1442" t="n">
-        <v>16.6873970031738</v>
+        <v>16.6873950958252</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>17.9349994659424</v>
       </c>
       <c r="G1445" t="n">
-        <v>17.0340595245361</v>
+        <v>17.0340576171875</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>17.6049995422363</v>
       </c>
       <c r="G1454" t="n">
-        <v>16.7206363677979</v>
+        <v>16.7206382751465</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1456" t="n">
-        <v>16.9628295898438</v>
+        <v>16.9628276824951</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1458" t="n">
-        <v>17.0245628356934</v>
+        <v>17.0245609283447</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1460" t="n">
-        <v>16.8298587799072</v>
+        <v>16.8298606872559</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>17.9850006103516</v>
       </c>
       <c r="G1463" t="n">
-        <v>17.0815486907959</v>
+        <v>17.0815467834473</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1465" t="n">
-        <v>17.0245628356934</v>
+        <v>17.0245609283447</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>17.5949993133545</v>
       </c>
       <c r="G1469" t="n">
-        <v>16.7111377716064</v>
+        <v>16.7111396789551</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1473" t="n">
-        <v>17.228759765625</v>
+        <v>17.2287616729736</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>18</v>
       </c>
       <c r="G1476" t="n">
-        <v>17.095796585083</v>
+        <v>17.0957946777344</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G1477" t="n">
-        <v>17.4329624176025</v>
+        <v>17.4329605102539</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1480" t="n">
-        <v>17.2857475280762</v>
+        <v>17.2857494354248</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G1482" t="n">
-        <v>17.3427352905273</v>
+        <v>17.3427333831787</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.7911281585693</v>
+        <v>18.7911262512207</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>19.9750003814697</v>
       </c>
       <c r="G1490" t="n">
-        <v>18.9715824127197</v>
+        <v>18.9715843200684</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1492" t="n">
-        <v>17.945837020874</v>
+        <v>17.9458351135254</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G1493" t="n">
-        <v>18.4302158355713</v>
+        <v>18.4302177429199</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>19.5349998474121</v>
       </c>
       <c r="G1494" t="n">
-        <v>18.5536880493164</v>
+        <v>18.5536861419678</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>19.7549991607666</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.7626323699951</v>
+        <v>18.7626342773438</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1496" t="n">
-        <v>19.0903034210205</v>
+        <v>19.0903053283691</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>18.92409324646</v>
+        <v>18.9240951538086</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1499" t="n">
-        <v>19.1662864685059</v>
+        <v>19.1662845611572</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1500" t="n">
-        <v>19.1662864685059</v>
+        <v>19.1662845611572</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G1509" t="n">
-        <v>19.745641708374</v>
+        <v>19.7456436157227</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1512" t="n">
-        <v>21.0373249053955</v>
+        <v>21.0373268127441</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G1517" t="n">
-        <v>20.1635398864746</v>
+        <v>20.1635417938232</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G1518" t="n">
-        <v>20.0970573425293</v>
+        <v>20.0970554351807</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G1519" t="n">
-        <v>20.7903842926025</v>
+        <v>20.7903861999512</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1522" t="n">
-        <v>21.0373249053955</v>
+        <v>21.0373268127441</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G1523" t="n">
-        <v>21.0183296203613</v>
+        <v>21.0183277130127</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G1524" t="n">
-        <v>21.0943088531494</v>
+        <v>21.094310760498</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1525" t="n">
-        <v>21.4172325134277</v>
+        <v>21.4172306060791</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G1526" t="n">
-        <v>21.3982391357422</v>
+        <v>21.3982372283936</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G1528" t="n">
-        <v>21.5691947937012</v>
+        <v>21.5691928863525</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G1541" t="n">
-        <v>18.0550594329834</v>
+        <v>18.055061340332</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1543" t="n">
-        <v>17.5421848297119</v>
+        <v>17.5421829223633</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1549" t="n">
-        <v>18.5394401550293</v>
+        <v>18.5394420623779</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>19.0550003051758</v>
       </c>
       <c r="G1550" t="n">
-        <v>18.0977973937988</v>
+        <v>18.0977993011475</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1551" t="n">
-        <v>17.945837020874</v>
+        <v>17.9458351135254</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>18.9950008392334</v>
       </c>
       <c r="G1552" t="n">
-        <v>18.0408115386963</v>
+        <v>18.0408134460449</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G1553" t="n">
-        <v>18.0503082275391</v>
+        <v>18.0503101348877</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>19.25</v>
       </c>
       <c r="G1555" t="n">
-        <v>18.2830028533936</v>
+        <v>18.2830009460449</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G1559" t="n">
-        <v>18.68190574646</v>
+        <v>18.6819038391113</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>19.7649993896484</v>
       </c>
       <c r="G1560" t="n">
-        <v>18.7721328735352</v>
+        <v>18.7721309661865</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>19.7950000762939</v>
       </c>
       <c r="G1561" t="n">
-        <v>18.8006267547607</v>
+        <v>18.8006248474121</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1562" t="n">
-        <v>18.5964241027832</v>
+        <v>18.5964260101318</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G1563" t="n">
-        <v>18.7768821716309</v>
+        <v>18.7768802642822</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>19.6450004577637</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.6581611633301</v>
+        <v>18.6581592559814</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>18.5650005340576</v>
       </c>
       <c r="G1568" t="n">
-        <v>17.6324138641357</v>
+        <v>17.6324157714844</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G1570" t="n">
-        <v>17.1242904663086</v>
+        <v>17.12428855896</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>15.2749996185303</v>
       </c>
       <c r="G1573" t="n">
-        <v>14.5076818466187</v>
+        <v>14.5076808929443</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>16.7549991607666</v>
       </c>
       <c r="G1574" t="n">
-        <v>15.9133348464966</v>
+        <v>15.9133329391479</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>16.1650009155273</v>
       </c>
       <c r="G1576" t="n">
-        <v>15.3529739379883</v>
+        <v>15.3529748916626</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G1579" t="n">
-        <v>15.5856676101685</v>
+        <v>15.5856666564941</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1580" t="n">
-        <v>15.7043867111206</v>
+        <v>15.7043857574463</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1585" t="n">
-        <v>15.2532482147217</v>
+        <v>15.2532472610474</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1586" t="n">
-        <v>15.5191822052002</v>
+        <v>15.5191831588745</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1592" t="n">
-        <v>15.9750699996948</v>
+        <v>15.9750709533691</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1593" t="n">
-        <v>15.2627458572388</v>
+        <v>15.2627449035645</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1597" t="n">
-        <v>15.0443000793457</v>
+        <v>15.0442991256714</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1599" t="n">
-        <v>15.4811916351318</v>
+        <v>15.4811906814575</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1600" t="n">
-        <v>15.6331548690796</v>
+        <v>15.6331539154053</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1602" t="n">
-        <v>15.6996402740479</v>
+        <v>15.6996393203735</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1603" t="n">
-        <v>15.889591217041</v>
+        <v>15.8895902633667</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1608" t="n">
-        <v>15.1392765045166</v>
+        <v>15.1392755508423</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G1611" t="n">
-        <v>15.0348024368286</v>
+        <v>15.0348014831543</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1616" t="n">
-        <v>12.812349319458</v>
+        <v>12.8123483657837</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1618" t="n">
-        <v>14.1990070343018</v>
+        <v>14.1990079879761</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1623" t="n">
-        <v>14.9113311767578</v>
+        <v>14.9113321304321</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G1625" t="n">
-        <v>14.8327665328979</v>
+        <v>14.8327655792236</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1627" t="n">
-        <v>14.6870594024658</v>
+        <v>14.6870603561401</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1628" t="n">
-        <v>15.075608253479</v>
+        <v>15.0756072998047</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1632" t="n">
-        <v>15.8915548324585</v>
+        <v>15.8915557861328</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1633" t="n">
-        <v>15.9886913299561</v>
+        <v>15.9886903762817</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1635" t="n">
-        <v>15.9692649841309</v>
+        <v>15.9692640304565</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1640" t="n">
-        <v>13.7545490264893</v>
+        <v>13.7545480728149</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1643" t="n">
-        <v>13.366003036499</v>
+        <v>13.3660020828247</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1644" t="n">
-        <v>13.7254085540771</v>
+        <v>13.7254076004028</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>13.9391078948975</v>
+        <v>13.9391088485718</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1667" t="n">
-        <v>15.6972818374634</v>
+        <v>15.6972808837891</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1669" t="n">
-        <v>16.2315330505371</v>
+        <v>16.2315311431885</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1672" t="n">
-        <v>15.8721265792847</v>
+        <v>15.872127532959</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1676" t="n">
-        <v>16.4646625518799</v>
+        <v>16.4646606445312</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1685" t="n">
-        <v>17.0960483551025</v>
+        <v>17.0960502624512</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1686" t="n">
-        <v>16.950345993042</v>
+        <v>16.9503440856934</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1693" t="n">
-        <v>16.0664005279541</v>
+        <v>16.0664024353027</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>16.1100006103516</v>
       </c>
       <c r="G1695" t="n">
-        <v>15.6487131118774</v>
+        <v>15.6487140655518</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1696" t="n">
-        <v>15.6001443862915</v>
+        <v>15.6001434326172</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1704" t="n">
-        <v>15.1727428436279</v>
+        <v>15.1727437973022</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>14.75</v>
       </c>
       <c r="G1709" t="n">
-        <v>14.3276538848877</v>
+        <v>14.327654838562</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1715" t="n">
-        <v>13.5408477783203</v>
+        <v>13.540846824646</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1716" t="n">
-        <v>13.9391078948975</v>
+        <v>13.9391088485718</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1744" t="n">
-        <v>14.823052406311</v>
+        <v>14.8230514526367</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1749" t="n">
-        <v>16.2315330505371</v>
+        <v>16.2315311431885</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1752" t="n">
-        <v>15.9304103851318</v>
+        <v>15.9304094314575</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1754" t="n">
-        <v>15.9789791107178</v>
+        <v>15.9789781570435</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G1759" t="n">
-        <v>15.7652759552002</v>
+        <v>15.7652769088745</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1761" t="n">
-        <v>16.5229434967041</v>
+        <v>16.5229415893555</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1764" t="n">
-        <v>16.8434925079346</v>
+        <v>16.8434944152832</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1777" t="n">
-        <v>15.9789791107178</v>
+        <v>15.9789781570435</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1780" t="n">
-        <v>15.9789791107178</v>
+        <v>15.9789781570435</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1781" t="n">
-        <v>16.163537979126</v>
+        <v>16.1635360717773</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1798" t="n">
-        <v>17.795431137085</v>
+        <v>17.7954330444336</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1799" t="n">
-        <v>17.9119968414307</v>
+        <v>17.9119987487793</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G1800" t="n">
-        <v>18.038272857666</v>
+        <v>18.0382747650146</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G1829" t="n">
-        <v>18.038272857666</v>
+        <v>18.0382747650146</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1833" t="n">
-        <v>16.5229434967041</v>
+        <v>16.5229415893555</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1835" t="n">
-        <v>16.3189544677734</v>
+        <v>16.3189563751221</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1836" t="n">
-        <v>16.5812244415283</v>
+        <v>16.581226348877</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1845" t="n">
-        <v>16.0761127471924</v>
+        <v>16.076114654541</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1851" t="n">
-        <v>16.0664005279541</v>
+        <v>16.0664024353027</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1860" t="n">
-        <v>15.8818407058716</v>
+        <v>15.8818416595459</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1861" t="n">
-        <v>15.7361373901367</v>
+        <v>15.7361364364624</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1867" t="n">
-        <v>15.6778526306152</v>
+        <v>15.6778535842896</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1872" t="n">
-        <v>15.075608253479</v>
+        <v>15.0756072998047</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1873" t="n">
-        <v>15.0853204727173</v>
+        <v>15.085319519043</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1879" t="n">
-        <v>14.706488609314</v>
+        <v>14.7064876556396</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>7.69999980926514</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>318725</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>7.80999994277954</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>7.6100001335144</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>7.76000022888184</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>7.61999988555908</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>7.61999988555908</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -421,7 +421,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G2" t="n">
-        <v>18.2763519287109</v>
+        <v>18.2763500213623</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G3" t="n">
-        <v>18.01096534729</v>
+        <v>18.0109634399414</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G4" t="n">
-        <v>17.4978809356689</v>
+        <v>17.4978828430176</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>17.9401931762695</v>
+        <v>17.9401950836182</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G8" t="n">
-        <v>19.4086723327637</v>
+        <v>19.4086742401123</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G10" t="n">
-        <v>18.84250831604</v>
+        <v>18.8425121307373</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G13" t="n">
-        <v>18.0994281768799</v>
+        <v>18.0994262695312</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G14" t="n">
-        <v>17.6394233703613</v>
+        <v>17.6394195556641</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G15" t="n">
-        <v>17.5686531066895</v>
+        <v>17.5686550140381</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G16" t="n">
-        <v>18.1878910064697</v>
+        <v>18.1878890991211</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G17" t="n">
-        <v>18.0994281768799</v>
+        <v>18.0994262695312</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G18" t="n">
-        <v>18.4798145294189</v>
+        <v>18.4798164367676</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>17.7632694244385</v>
+        <v>17.7632675170898</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>17.9578857421875</v>
+        <v>17.9578838348389</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G24" t="n">
-        <v>18.2055797576904</v>
+        <v>18.2055816650391</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G25" t="n">
-        <v>18.2586574554443</v>
+        <v>18.2586555480957</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G26" t="n">
-        <v>18.0817356109619</v>
+        <v>18.0817337036133</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G27" t="n">
-        <v>17.3563404083252</v>
+        <v>17.3563423156738</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G28" t="n">
-        <v>16.9051856994629</v>
+        <v>16.9051818847656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>17.1617221832275</v>
+        <v>17.1617240905762</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G31" t="n">
-        <v>17.0201816558838</v>
+        <v>17.0201835632324</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G32" t="n">
-        <v>17.4890365600586</v>
+        <v>17.48903465271</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G34" t="n">
-        <v>18.4798145294189</v>
+        <v>18.4798164367676</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>20.8099994659424</v>
       </c>
       <c r="G35" t="n">
-        <v>18.4090423583984</v>
+        <v>18.4090461730957</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>18.9752044677734</v>
+        <v>18.9752063751221</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G40" t="n">
-        <v>17.7632694244385</v>
+        <v>17.7632675170898</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G41" t="n">
-        <v>17.9048080444336</v>
+        <v>17.9048099517822</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G42" t="n">
-        <v>18.3471183776855</v>
+        <v>18.3471202850342</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G44" t="n">
-        <v>19.001745223999</v>
+        <v>19.0017433166504</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G46" t="n">
-        <v>19.3113613128662</v>
+        <v>19.3113632202148</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G47" t="n">
-        <v>19.992525100708</v>
+        <v>19.9925231933594</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G50" t="n">
-        <v>19.3378982543945</v>
+        <v>19.3379020690918</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G54" t="n">
-        <v>19.3378982543945</v>
+        <v>19.3379020690918</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>20.0367546081543</v>
+        <v>20.0367527008057</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>22.0100002288818</v>
       </c>
       <c r="G59" t="n">
-        <v>19.4705944061279</v>
+        <v>19.4705963134766</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G60" t="n">
-        <v>18.9663600921631</v>
+        <v>18.9663581848145</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G61" t="n">
-        <v>19.4794387817383</v>
+        <v>19.4794425964355</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G62" t="n">
-        <v>19.9129104614258</v>
+        <v>19.9129066467285</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G65" t="n">
-        <v>19.417516708374</v>
+        <v>19.4175186157227</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G67" t="n">
-        <v>18.833667755127</v>
+        <v>18.8336658477783</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G68" t="n">
-        <v>18.5152015686035</v>
+        <v>18.5151996612549</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G70" t="n">
-        <v>18.8955879211426</v>
+        <v>18.8955898284912</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G72" t="n">
-        <v>19.3113613128662</v>
+        <v>19.3113632202148</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G77" t="n">
-        <v>18.8071269989014</v>
+        <v>18.8071250915527</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G78" t="n">
-        <v>18.3205833435059</v>
+        <v>18.3205795288086</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>18.3648147583008</v>
+        <v>18.3648109436035</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G81" t="n">
-        <v>18.0817356109619</v>
+        <v>18.0817337036133</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>18.3117370605469</v>
+        <v>18.3117351531982</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G87" t="n">
-        <v>17.9048080444336</v>
+        <v>17.9048099517822</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G88" t="n">
-        <v>17.4448013305664</v>
+        <v>17.444803237915</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G89" t="n">
-        <v>17.1440296173096</v>
+        <v>17.1440277099609</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G90" t="n">
-        <v>17.5509605407715</v>
+        <v>17.5509586334229</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G91" t="n">
-        <v>17.9844245910645</v>
+        <v>17.9844264984131</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>17.6394233703613</v>
+        <v>17.6394195556641</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G94" t="n">
-        <v>18.833667755127</v>
+        <v>18.8336658477783</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>20.2700004577637</v>
       </c>
       <c r="G97" t="n">
-        <v>17.9313488006592</v>
+        <v>17.9313507080078</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>17.7367324829102</v>
+        <v>17.7367305755615</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G100" t="n">
-        <v>17.5939388275146</v>
+        <v>17.593936920166</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G102" t="n">
-        <v>17.7025966644287</v>
+        <v>17.7025985717773</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G105" t="n">
-        <v>17.5939388275146</v>
+        <v>17.593936920166</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G106" t="n">
-        <v>17.4128341674805</v>
+        <v>17.4128379821777</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G107" t="n">
-        <v>17.304178237915</v>
+        <v>17.3041763305664</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>19.25</v>
       </c>
       <c r="G110" t="n">
-        <v>17.4309463500977</v>
+        <v>17.4309482574463</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G113" t="n">
-        <v>17.6844902038574</v>
+        <v>17.6844882965088</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G114" t="n">
-        <v>17.1502418518066</v>
+        <v>17.150239944458</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G115" t="n">
-        <v>16.71559715271</v>
+        <v>16.7155990600586</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G121" t="n">
-        <v>17.7297649383545</v>
+        <v>17.7297611236572</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G122" t="n">
-        <v>17.8655910491943</v>
+        <v>17.8655891418457</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>16.6069393157959</v>
+        <v>16.6069374084473</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>17.75</v>
       </c>
       <c r="G132" t="n">
-        <v>16.0726928710938</v>
+        <v>16.0726909637451</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G133" t="n">
-        <v>15.8734798431396</v>
+        <v>15.8734817504883</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G134" t="n">
-        <v>16.3624515533447</v>
+        <v>16.3624496459961</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G137" t="n">
-        <v>17.095911026001</v>
+        <v>17.0959091186523</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G138" t="n">
-        <v>17.1321296691895</v>
+        <v>17.1321334838867</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G139" t="n">
-        <v>17.086856842041</v>
+        <v>17.0868549346924</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G140" t="n">
-        <v>17.1502418518066</v>
+        <v>17.150239944458</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>17.0325260162354</v>
+        <v>17.0325241088867</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G143" t="n">
-        <v>17.8655910491943</v>
+        <v>17.8655891418457</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G145" t="n">
-        <v>18.1372394561768</v>
+        <v>18.1372413635254</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G147" t="n">
-        <v>18.7710914611816</v>
+        <v>18.771089553833</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>18.6352653503418</v>
+        <v>18.6352672576904</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G150" t="n">
-        <v>19.214786529541</v>
+        <v>19.2147903442383</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>20.5699996948242</v>
       </c>
       <c r="G151" t="n">
-        <v>18.6262092590332</v>
+        <v>18.6262130737305</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G153" t="n">
-        <v>18.2187366485596</v>
+        <v>18.2187347412109</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G165" t="n">
-        <v>18.7529811859131</v>
+        <v>18.7529792785645</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>18.9703044891357</v>
+        <v>18.9703025817871</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6533756256104</v>
+        <v>18.653377532959</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G171" t="n">
-        <v>18.5175514221191</v>
+        <v>18.5175533294678</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>18.6986484527588</v>
+        <v>18.6986503601074</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>22</v>
       </c>
       <c r="G177" t="n">
-        <v>19.9210815429688</v>
+        <v>19.9210796356201</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>19.5588798522949</v>
+        <v>19.5588817596436</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G184" t="n">
-        <v>19.1332931518555</v>
+        <v>19.1332950592041</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G185" t="n">
-        <v>18.7710914611816</v>
+        <v>18.771089553833</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>19.1604614257812</v>
+        <v>19.1604595184326</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>20.3557224273682</v>
+        <v>20.3557243347168</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>20.3919467926025</v>
+        <v>20.3919448852539</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>20.4643859863281</v>
+        <v>20.4643840789795</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G194" t="n">
-        <v>20.3557224273682</v>
+        <v>20.3557243347168</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>20.6907615661621</v>
+        <v>20.6907577514648</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>20.8446941375732</v>
+        <v>20.8446960449219</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G197" t="n">
-        <v>20.7994194030762</v>
+        <v>20.7994213104248</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G198" t="n">
-        <v>20.4010009765625</v>
+        <v>20.4009990692139</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>20.3647785186768</v>
+        <v>20.3647804260254</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>20.0116329193115</v>
+        <v>20.0116310119629</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>20.3285579681396</v>
+        <v>20.3285598754883</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G208" t="n">
-        <v>20.3557224273682</v>
+        <v>20.3557243347168</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G209" t="n">
-        <v>20.03879737854</v>
+        <v>20.0387992858887</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>22.25</v>
       </c>
       <c r="G210" t="n">
-        <v>20.1474571228027</v>
+        <v>20.1474590301514</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G211" t="n">
-        <v>20.2289562225342</v>
+        <v>20.2289524078369</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G213" t="n">
-        <v>20.5639877319336</v>
+        <v>20.5639896392822</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G214" t="n">
-        <v>20.1836795806885</v>
+        <v>20.1836776733398</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G215" t="n">
-        <v>20.03879737854</v>
+        <v>20.0387992858887</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>21.5900001525879</v>
       </c>
       <c r="G216" t="n">
-        <v>19.5498275756836</v>
+        <v>19.549825668335</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G217" t="n">
-        <v>19.4140033721924</v>
+        <v>19.4140014648438</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>19.5045490264893</v>
+        <v>19.5045509338379</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G220" t="n">
-        <v>19.7943096160889</v>
+        <v>19.7943134307861</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G226" t="n">
-        <v>18.0919628143311</v>
+        <v>18.0919666290283</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G227" t="n">
-        <v>18.3002281188965</v>
+        <v>18.3002300262451</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G228" t="n">
-        <v>18.3273944854736</v>
+        <v>18.3273963928223</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G230" t="n">
-        <v>18.0104694366455</v>
+        <v>18.0104675292969</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G231" t="n">
-        <v>17.7388172149658</v>
+        <v>17.7388191223145</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>17.8203105926514</v>
+        <v>17.8203125</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>17.6392097473145</v>
+        <v>17.6392116546631</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G235" t="n">
-        <v>18.3455047607422</v>
+        <v>18.3455066680908</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>19.2872257232666</v>
+        <v>19.2872276306152</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G242" t="n">
-        <v>19.3958892822266</v>
+        <v>19.3958911895752</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>19.3777809143066</v>
+        <v>19.377779006958</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G244" t="n">
-        <v>19.1151828765869</v>
+        <v>19.1151847839355</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>21.2700004577637</v>
       </c>
       <c r="G246" t="n">
-        <v>19.2600631713867</v>
+        <v>19.2600650787354</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>22.5</v>
       </c>
       <c r="G249" t="n">
-        <v>20.373836517334</v>
+        <v>20.3738346099854</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>20.2380084991455</v>
+        <v>20.2380104064941</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G254" t="n">
-        <v>20.1836795806885</v>
+        <v>20.1836776733398</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>20.2289562225342</v>
+        <v>20.2289524078369</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>20.15651512146</v>
+        <v>20.1565132141113</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G259" t="n">
-        <v>20.6183204650879</v>
+        <v>20.6183223724365</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G260" t="n">
-        <v>21.4785461425781</v>
+        <v>21.4785480499268</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G265" t="n">
-        <v>22.2935028076172</v>
+        <v>22.2935009002686</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>22.3206672668457</v>
+        <v>22.3206653594971</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G270" t="n">
-        <v>22.818696975708</v>
+        <v>22.8186950683594</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G272" t="n">
-        <v>22.8911361694336</v>
+        <v>22.891134262085</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>22.5923175811768</v>
+        <v>22.5923156738281</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G276" t="n">
-        <v>22.3568859100342</v>
+        <v>22.3568878173828</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G278" t="n">
-        <v>22.1757850646973</v>
+        <v>22.1757869720459</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G279" t="n">
-        <v>22.1395645141602</v>
+        <v>22.1395664215088</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G280" t="n">
-        <v>23.606481552124</v>
+        <v>23.6064834594727</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>26.2299995422363</v>
       </c>
       <c r="G281" t="n">
-        <v>23.7513618469238</v>
+        <v>23.7513599395752</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>26.6399993896484</v>
       </c>
       <c r="G282" t="n">
-        <v>24.1226215362549</v>
+        <v>24.1226196289062</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>23.5612087249756</v>
+        <v>23.561206817627</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G286" t="n">
-        <v>23.5612087249756</v>
+        <v>23.561206817627</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G287" t="n">
-        <v>23.7423057556152</v>
+        <v>23.7423076629639</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>23.7241973876953</v>
+        <v>23.7241992950439</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>23.6336479187012</v>
+        <v>23.6336498260498</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G293" t="n">
-        <v>23.7241973876953</v>
+        <v>23.7241992950439</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>24.0682888031006</v>
+        <v>24.0682907104492</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>23.9777355194092</v>
+        <v>23.9777374267578</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>26.8299999237061</v>
       </c>
       <c r="G298" t="n">
-        <v>24.2946643829346</v>
+        <v>24.2946624755859</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>27.8199996948242</v>
       </c>
       <c r="G302" t="n">
-        <v>25.1911144256592</v>
+        <v>25.1911125183105</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>28.0400009155273</v>
       </c>
       <c r="G303" t="n">
-        <v>25.3903255462646</v>
+        <v>25.3903274536133</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>25.6710319519043</v>
+        <v>25.6710338592529</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>28.3299999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>25.6529235839844</v>
+        <v>25.6529216766357</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>27.5</v>
       </c>
       <c r="G311" t="n">
-        <v>24.9013557434082</v>
+        <v>24.9013538360596</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>25.0643444061279</v>
+        <v>25.0643463134766</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>27.3899993896484</v>
       </c>
       <c r="G313" t="n">
-        <v>24.8017482757568</v>
+        <v>24.8017501831055</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>25.6257553100586</v>
+        <v>25.62575340271</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G318" t="n">
-        <v>25.2273368835449</v>
+        <v>25.2273349761963</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>27.7900009155273</v>
       </c>
       <c r="G320" t="n">
-        <v>25.163948059082</v>
+        <v>25.1639499664307</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>28.4099998474121</v>
       </c>
       <c r="G323" t="n">
-        <v>25.7253589630127</v>
+        <v>25.7253608703613</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>27.75</v>
       </c>
       <c r="G325" t="n">
-        <v>25.1277275085449</v>
+        <v>25.1277294158936</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>28.2099990844727</v>
       </c>
       <c r="G327" t="n">
-        <v>25.5442581176758</v>
+        <v>25.5442600250244</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>25.2635536193848</v>
+        <v>25.2635555267334</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>25.0824546813965</v>
+        <v>25.0824565887451</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>24.2675018310547</v>
+        <v>24.2674999237061</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>27.8199996948242</v>
       </c>
       <c r="G336" t="n">
-        <v>25.1911144256592</v>
+        <v>25.1911125183105</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>28.1900005340576</v>
       </c>
       <c r="G337" t="n">
-        <v>25.5261478424072</v>
+        <v>25.5261516571045</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>28.9200000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>26.1871681213379</v>
+        <v>26.1871662139893</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>29.4099998474121</v>
       </c>
       <c r="G340" t="n">
-        <v>26.6308670043945</v>
+        <v>26.6308650970459</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>29.25</v>
       </c>
       <c r="G341" t="n">
-        <v>26.4859867095947</v>
+        <v>26.4859848022461</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>29.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>26.3229923248291</v>
+        <v>26.3229961395264</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>26.893461227417</v>
+        <v>26.8934631347656</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>29</v>
       </c>
       <c r="G345" t="n">
-        <v>26.2596073150635</v>
+        <v>26.2596092224121</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>26.667085647583</v>
+        <v>26.6670837402344</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>29.4099998474121</v>
       </c>
       <c r="G348" t="n">
-        <v>26.6308670043945</v>
+        <v>26.6308650970459</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>29.3700008392334</v>
       </c>
       <c r="G350" t="n">
-        <v>26.5946445465088</v>
+        <v>26.5946464538574</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>29</v>
       </c>
       <c r="G351" t="n">
-        <v>26.2596073150635</v>
+        <v>26.2596092224121</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G352" t="n">
-        <v>25.3088283538818</v>
+        <v>25.3088302612305</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>27.9699993133545</v>
       </c>
       <c r="G353" t="n">
-        <v>25.3269386291504</v>
+        <v>25.326940536499</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>28.5300006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>25.8340244293213</v>
+        <v>25.8340225219727</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>25.2299995422363</v>
       </c>
       <c r="G359" t="n">
-        <v>23.2202472686768</v>
+        <v>23.2202453613281</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>22.8705196380615</v>
+        <v>22.8705177307129</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G363" t="n">
-        <v>22.8613109588623</v>
+        <v>22.8613128662109</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G364" t="n">
-        <v>23.266263961792</v>
+        <v>23.2662658691406</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>25.25</v>
       </c>
       <c r="G365" t="n">
-        <v>23.238655090332</v>
+        <v>23.2386531829834</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>22.3643264770508</v>
+        <v>22.3643283843994</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G373" t="n">
-        <v>22.7416687011719</v>
+        <v>22.7416667938232</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>23.2846698760986</v>
+        <v>23.2846717834473</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G378" t="n">
-        <v>23.4319267272949</v>
+        <v>23.4319248199463</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G380" t="n">
-        <v>23.0269756317139</v>
+        <v>23.0269775390625</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G381" t="n">
-        <v>22.6036205291748</v>
+        <v>22.6036167144775</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>23.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>21.5452251434326</v>
+        <v>21.545223236084</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>21.4900035858154</v>
+        <v>21.4900016784668</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>21.674072265625</v>
+        <v>21.6740703582764</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>23</v>
       </c>
       <c r="G389" t="n">
-        <v>21.1678810119629</v>
+        <v>21.1678829193115</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>23</v>
       </c>
       <c r="G390" t="n">
-        <v>21.1678810119629</v>
+        <v>21.1678829193115</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G394" t="n">
-        <v>21.5084114074707</v>
+        <v>21.5084095001221</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G395" t="n">
-        <v>21.9133586883545</v>
+        <v>21.9133605957031</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>24.3099994659424</v>
       </c>
       <c r="G399" t="n">
-        <v>22.3735332489014</v>
+        <v>22.3735313415527</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G400" t="n">
-        <v>22.2170734405518</v>
+        <v>22.2170715332031</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G402" t="n">
-        <v>22.5299892425537</v>
+        <v>22.5299911499023</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G405" t="n">
-        <v>22.5575981140137</v>
+        <v>22.5576019287109</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G411" t="n">
-        <v>22.539192199707</v>
+        <v>22.5391941070557</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G412" t="n">
-        <v>22.3551254272461</v>
+        <v>22.3551273345947</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>23.9699993133545</v>
       </c>
       <c r="G420" t="n">
-        <v>22.0606136322021</v>
+        <v>22.0606155395508</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G421" t="n">
-        <v>21.7569007873535</v>
+        <v>21.7568988800049</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G422" t="n">
-        <v>21.9133586883545</v>
+        <v>21.9133605957031</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G426" t="n">
-        <v>22.0053958892822</v>
+        <v>22.0053939819336</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G427" t="n">
-        <v>22.2170734405518</v>
+        <v>22.2170715332031</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G428" t="n">
-        <v>22.3551254272461</v>
+        <v>22.3551273345947</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G429" t="n">
-        <v>22.0053958892822</v>
+        <v>22.0053939819336</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G430" t="n">
-        <v>21.9133586883545</v>
+        <v>21.9133605957031</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G432" t="n">
-        <v>22.1250400543213</v>
+        <v>22.1250419616699</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G433" t="n">
-        <v>21.7753105163574</v>
+        <v>21.7753086090088</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>23.9300003051758</v>
       </c>
       <c r="G434" t="n">
-        <v>22.0238037109375</v>
+        <v>22.0238018035889</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G437" t="n">
-        <v>21.6832752227783</v>
+        <v>21.6832733154297</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G440" t="n">
-        <v>20.9470024108887</v>
+        <v>20.94700050354</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G444" t="n">
-        <v>21.3243408203125</v>
+        <v>21.3243427276611</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>21.950174331665</v>
+        <v>21.9501762390137</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G446" t="n">
-        <v>22.0974311828613</v>
+        <v>22.0974292755127</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>23.75</v>
       </c>
       <c r="G448" t="n">
-        <v>21.8581371307373</v>
+        <v>21.8581390380859</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G451" t="n">
-        <v>21.2967300415039</v>
+        <v>21.2967319488525</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G452" t="n">
-        <v>20.9746150970459</v>
+        <v>20.9746112823486</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838123321533</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G458" t="n">
-        <v>21.0942554473877</v>
+        <v>21.0942573547363</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G465" t="n">
-        <v>20.3947944641113</v>
+        <v>20.39479637146</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G466" t="n">
-        <v>20.0082511901855</v>
+        <v>20.0082492828369</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G474" t="n">
-        <v>21.2415103912354</v>
+        <v>21.2415084838867</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G475" t="n">
-        <v>20.9285945892334</v>
+        <v>20.9285926818848</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G476" t="n">
-        <v>20.9470024108887</v>
+        <v>20.94700050354</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>21.9099998474121</v>
       </c>
       <c r="G479" t="n">
-        <v>20.1647071838379</v>
+        <v>20.1647090911865</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G480" t="n">
-        <v>20.0910816192627</v>
+        <v>20.0910835266113</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G481" t="n">
-        <v>19.2719783782959</v>
+        <v>19.2719764709473</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>19.6953315734863</v>
+        <v>19.695333480835</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G483" t="n">
-        <v>19.8057765960693</v>
+        <v>19.8057746887207</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G484" t="n">
-        <v>19.7321491241455</v>
+        <v>19.7321472167969</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G485" t="n">
-        <v>20.1831150054932</v>
+        <v>20.1831169128418</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>20.2935581207275</v>
+        <v>20.2935562133789</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G489" t="n">
-        <v>20.5696601867676</v>
+        <v>20.5696620941162</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>20.661693572998</v>
+        <v>20.6616954803467</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G491" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838123321533</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G494" t="n">
-        <v>21.0482406616211</v>
+        <v>21.0482387542725</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>23.3099994659424</v>
       </c>
       <c r="G498" t="n">
-        <v>21.4531898498535</v>
+        <v>21.4531879425049</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G502" t="n">
-        <v>20.7721366882324</v>
+        <v>20.7721347808838</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>19.4652481079102</v>
+        <v>19.4652500152588</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G504" t="n">
-        <v>19.796573638916</v>
+        <v>19.7965717315674</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G508" t="n">
-        <v>20.2935581207275</v>
+        <v>20.2935562133789</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>20.2291316986084</v>
+        <v>20.229133605957</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>20.2935581207275</v>
+        <v>20.2935562133789</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G525" t="n">
-        <v>20.9470024108887</v>
+        <v>20.94700050354</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G526" t="n">
-        <v>21.7569007873535</v>
+        <v>21.7568988800049</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G527" t="n">
-        <v>21.2967300415039</v>
+        <v>21.2967319488525</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G533" t="n">
-        <v>20.8549690246582</v>
+        <v>20.8549671173096</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G534" t="n">
-        <v>21.3243408203125</v>
+        <v>21.3243427276611</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G539" t="n">
-        <v>20.0266590118408</v>
+        <v>20.0266571044922</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G541" t="n">
-        <v>20.0082511901855</v>
+        <v>20.0082492828369</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G542" t="n">
-        <v>19.9162178039551</v>
+        <v>19.9162158966064</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G544" t="n">
-        <v>20.5604572296143</v>
+        <v>20.5604553222656</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G548" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838123321533</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G550" t="n">
-        <v>20.9285945892334</v>
+        <v>20.9285926818848</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>22.75</v>
       </c>
       <c r="G551" t="n">
-        <v>20.9377975463867</v>
+        <v>20.9377956390381</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G553" t="n">
-        <v>21.2967300415039</v>
+        <v>21.2967319488525</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G557" t="n">
-        <v>20.0910816192627</v>
+        <v>20.0910835266113</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>20.1094875335693</v>
+        <v>20.109489440918</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G561" t="n">
-        <v>19.9990482330322</v>
+        <v>19.9990463256836</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>20.1094875335693</v>
+        <v>20.109489440918</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G566" t="n">
-        <v>20.5696601867676</v>
+        <v>20.5696620941162</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G580" t="n">
-        <v>20.3947944641113</v>
+        <v>20.39479637146</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G582" t="n">
-        <v>20.9746150970459</v>
+        <v>20.9746112823486</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>21.2783260345459</v>
+        <v>21.2783241271973</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G585" t="n">
-        <v>21.3151359558105</v>
+        <v>21.3151378631592</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G586" t="n">
-        <v>21.7753105163574</v>
+        <v>21.7753086090088</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>21.5360221862793</v>
+        <v>21.536018371582</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>21.5360221862793</v>
+        <v>21.536018371582</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G589" t="n">
-        <v>21.7937145233154</v>
+        <v>21.7937164306641</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>24.5</v>
       </c>
       <c r="G591" t="n">
-        <v>22.548397064209</v>
+        <v>22.5483989715576</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G592" t="n">
-        <v>22.419548034668</v>
+        <v>22.4195499420166</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>24.5200004577637</v>
       </c>
       <c r="G594" t="n">
-        <v>22.5668029785156</v>
+        <v>22.5668048858643</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G596" t="n">
-        <v>22.7416687011719</v>
+        <v>22.7416667938232</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>24.5699996948242</v>
       </c>
       <c r="G598" t="n">
-        <v>22.6128215789795</v>
+        <v>22.6128196716309</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>22.7324657440186</v>
+        <v>22.7324638366699</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G603" t="n">
-        <v>22.8337001800537</v>
+        <v>22.8337020874023</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G604" t="n">
-        <v>22.7692794799805</v>
+        <v>22.7692813873291</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G605" t="n">
-        <v>22.9073314666748</v>
+        <v>22.9073295593262</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G606" t="n">
-        <v>23.2754688262939</v>
+        <v>23.2754707336426</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G611" t="n">
-        <v>22.9071884155273</v>
+        <v>22.907190322876</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G613" t="n">
-        <v>22.7296123504639</v>
+        <v>22.7296142578125</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G614" t="n">
-        <v>22.3557720184326</v>
+        <v>22.355770111084</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>22.6174621582031</v>
+        <v>22.6174602508545</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G620" t="n">
-        <v>23.4586048126221</v>
+        <v>23.4586067199707</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>24.3299999237061</v>
       </c>
       <c r="G622" t="n">
-        <v>22.7389602661133</v>
+        <v>22.7389583587646</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>23.5053367614746</v>
+        <v>23.505334854126</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G630" t="n">
-        <v>20.991247177124</v>
+        <v>20.9912452697754</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G631" t="n">
-        <v>20.3370227813721</v>
+        <v>20.3370208740234</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G632" t="n">
-        <v>20.3370227813721</v>
+        <v>20.3370208740234</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G634" t="n">
-        <v>19.7388782501221</v>
+        <v>19.7388763427734</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G636" t="n">
-        <v>19.3089542388916</v>
+        <v>19.3089561462402</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>19.346342086792</v>
+        <v>19.3463401794434</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G640" t="n">
-        <v>19.0285758972168</v>
+        <v>19.0285739898682</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G641" t="n">
-        <v>18.6266956329346</v>
+        <v>18.6266937255859</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G648" t="n">
-        <v>18.6360397338867</v>
+        <v>18.6360378265381</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G651" t="n">
-        <v>18.7201557159424</v>
+        <v>18.720157623291</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>19.875</v>
       </c>
       <c r="G653" t="n">
-        <v>18.5752925872803</v>
+        <v>18.5752906799316</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>19.7250003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>18.4350986480713</v>
+        <v>18.4351005554199</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>17.8042373657227</v>
+        <v>17.8042392730713</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>19.375</v>
       </c>
       <c r="G663" t="n">
-        <v>18.1079864501953</v>
+        <v>18.1079883575439</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G665" t="n">
-        <v>18.6734237670898</v>
+        <v>18.6734256744385</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G668" t="n">
-        <v>18.6734237670898</v>
+        <v>18.6734256744385</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G669" t="n">
-        <v>18.7201557159424</v>
+        <v>18.720157623291</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G675" t="n">
-        <v>19.1407260894775</v>
+        <v>19.1407241821289</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G677" t="n">
-        <v>19.4024181365967</v>
+        <v>19.402416229248</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G679" t="n">
-        <v>19.4304523468018</v>
+        <v>19.430456161499</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G680" t="n">
-        <v>19.3650302886963</v>
+        <v>19.3650321960449</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>20.5</v>
       </c>
       <c r="G681" t="n">
-        <v>19.1594181060791</v>
+        <v>19.1594200134277</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>20.5100002288818</v>
       </c>
       <c r="G682" t="n">
-        <v>19.1687679290771</v>
+        <v>19.1687660217285</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G685" t="n">
-        <v>18.7388439178467</v>
+        <v>18.7388458251953</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>20.5</v>
       </c>
       <c r="G686" t="n">
-        <v>19.1594181060791</v>
+        <v>19.1594200134277</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G688" t="n">
-        <v>18.8416538238525</v>
+        <v>18.8416519165039</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>21.1700000762939</v>
       </c>
       <c r="G699" t="n">
-        <v>19.7856044769287</v>
+        <v>19.7856063842773</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G701" t="n">
-        <v>19.2809162139893</v>
+        <v>19.2809181213379</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G703" t="n">
-        <v>18.8977298736572</v>
+        <v>18.8977279663086</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>18.8790378570557</v>
+        <v>18.879035949707</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>19.1049995422363</v>
       </c>
       <c r="G709" t="n">
-        <v>17.8556423187256</v>
+        <v>17.8556442260742</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G711" t="n">
-        <v>17.1546897888184</v>
+        <v>17.1546878814697</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>19.2049999237061</v>
       </c>
       <c r="G714" t="n">
-        <v>17.949104309082</v>
+        <v>17.9491062164307</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G716" t="n">
-        <v>18.2154655456543</v>
+        <v>18.2154693603516</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>20.5300006866455</v>
       </c>
       <c r="G718" t="n">
-        <v>19.1874561309814</v>
+        <v>19.1874580383301</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G722" t="n">
-        <v>19.6454162597656</v>
+        <v>19.6454124450684</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G733" t="n">
-        <v>19.701488494873</v>
+        <v>19.7014904022217</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G742" t="n">
-        <v>19.3650302886963</v>
+        <v>19.3650321960449</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>19.346342086792</v>
+        <v>19.3463401794434</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G747" t="n">
-        <v>19.701488494873</v>
+        <v>19.7014904022217</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G749" t="n">
-        <v>19.4304523468018</v>
+        <v>19.430456161499</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>20.5</v>
       </c>
       <c r="G750" t="n">
-        <v>19.1594181060791</v>
+        <v>19.1594200134277</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G752" t="n">
-        <v>18.6734237670898</v>
+        <v>18.6734256744385</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G756" t="n">
-        <v>16.8135566711426</v>
+        <v>16.8135585784912</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>17.7450008392334</v>
       </c>
       <c r="G757" t="n">
-        <v>16.5845813751221</v>
+        <v>16.5845794677734</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>17.7049999237061</v>
       </c>
       <c r="G758" t="n">
-        <v>16.5471973419189</v>
+        <v>16.5471954345703</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G760" t="n">
-        <v>16.7200965881348</v>
+        <v>16.7200984954834</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>17.6550006866455</v>
       </c>
       <c r="G763" t="n">
-        <v>16.500467300415</v>
+        <v>16.5004653930664</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>17.1650009155273</v>
       </c>
       <c r="G765" t="n">
-        <v>16.0425109863281</v>
+        <v>16.0425090789795</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G776" t="n">
-        <v>16.8135566711426</v>
+        <v>16.8135585784912</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>17.5750007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>16.4256973266602</v>
+        <v>16.4256992340088</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>17.2549991607666</v>
       </c>
       <c r="G778" t="n">
-        <v>16.1266212463379</v>
+        <v>16.1266231536865</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G779" t="n">
-        <v>16.1593360900879</v>
+        <v>16.1593341827393</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>17.2549991607666</v>
       </c>
       <c r="G780" t="n">
-        <v>16.1266212463379</v>
+        <v>16.1266231536865</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>16.4490623474121</v>
+        <v>16.4490642547607</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>17.3250007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>16.192045211792</v>
+        <v>16.1920471191406</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>16.2154102325439</v>
+        <v>16.2154121398926</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G788" t="n">
-        <v>16.5238304138184</v>
+        <v>16.523832321167</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G791" t="n">
-        <v>16.299524307251</v>
+        <v>16.2995262145996</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G794" t="n">
-        <v>17.785551071167</v>
+        <v>17.7855491638184</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>17.1967449188232</v>
+        <v>17.1967468261719</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>18.4249992370605</v>
       </c>
       <c r="G796" t="n">
-        <v>17.2201118469238</v>
+        <v>17.2201099395752</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G800" t="n">
-        <v>17.1079597473145</v>
+        <v>17.1079616546631</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>18.7150001525879</v>
       </c>
       <c r="G803" t="n">
-        <v>17.4911499023438</v>
+        <v>17.4911479949951</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G807" t="n">
-        <v>17.6547031402588</v>
+        <v>17.6547012329102</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>17.3369388580322</v>
+        <v>17.3369369506836</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>18.3449993133545</v>
       </c>
       <c r="G810" t="n">
-        <v>17.1453418731689</v>
+        <v>17.1453437805176</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>18.0249996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>16.8462696075439</v>
+        <v>16.8462715148926</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>19.1650009155273</v>
       </c>
       <c r="G815" t="n">
-        <v>17.9117202758789</v>
+        <v>17.9117221832275</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>18.0378913879395</v>
+        <v>18.0378932952881</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G817" t="n">
-        <v>17.6593780517578</v>
+        <v>17.6593761444092</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G819" t="n">
-        <v>17.6360130310059</v>
+        <v>17.6360111236572</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G820" t="n">
-        <v>17.6360130310059</v>
+        <v>17.6360111236572</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>18.6149997711182</v>
       </c>
       <c r="G822" t="n">
-        <v>17.3976879119873</v>
+        <v>17.3976860046387</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G824" t="n">
-        <v>17.6360130310059</v>
+        <v>17.6360111236572</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>18.7250003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>17.5004940032959</v>
+        <v>17.5004959106445</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G828" t="n">
-        <v>18.2154655456543</v>
+        <v>18.2154693603516</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>19.2250003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>17.9677982330322</v>
+        <v>17.9677963256836</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>20</v>
       </c>
       <c r="G835" t="n">
-        <v>18.69211769104</v>
+        <v>18.6921157836914</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>19.8549995422363</v>
       </c>
       <c r="G839" t="n">
-        <v>18.5565967559814</v>
+        <v>18.5565986633301</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G840" t="n">
-        <v>18.439769744873</v>
+        <v>18.4397716522217</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G845" t="n">
-        <v>18.3089275360107</v>
+        <v>18.3089256286621</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>18.06125831604</v>
+        <v>18.0612602233887</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>21.25</v>
       </c>
       <c r="G856" t="n">
-        <v>19.8603744506836</v>
+        <v>19.860372543335</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>19.9071025848389</v>
+        <v>19.9071044921875</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G860" t="n">
-        <v>19.9735870361328</v>
+        <v>19.9735889434814</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G862" t="n">
-        <v>19.2042751312256</v>
+        <v>19.204273223877</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G863" t="n">
-        <v>19.4892063140869</v>
+        <v>19.4892082214355</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>18.7749996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>17.8318634033203</v>
+        <v>17.8318614959717</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G872" t="n">
-        <v>18.6534118652344</v>
+        <v>18.6534099578857</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G873" t="n">
-        <v>19.1757850646973</v>
+        <v>19.1757831573486</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>19.9850006103516</v>
       </c>
       <c r="G877" t="n">
-        <v>18.9810810089111</v>
+        <v>18.9810829162598</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G882" t="n">
-        <v>19.9355964660645</v>
+        <v>19.9355945587158</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G883" t="n">
-        <v>20.0210742950439</v>
+        <v>20.0210762023926</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G885" t="n">
-        <v>19.7171497344971</v>
+        <v>19.7171478271484</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G887" t="n">
-        <v>19.7456436157227</v>
+        <v>19.7456455230713</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>20.4674644470215</v>
+        <v>20.4674625396729</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>21.5699996948242</v>
       </c>
       <c r="G892" t="n">
-        <v>20.4864597320557</v>
+        <v>20.4864616394043</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G893" t="n">
-        <v>20.2870101928711</v>
+        <v>20.2870121002197</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G903" t="n">
-        <v>19.8691139221191</v>
+        <v>19.8691120147705</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G904" t="n">
-        <v>19.9735870361328</v>
+        <v>19.9735889434814</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G905" t="n">
-        <v>19.8691139221191</v>
+        <v>19.8691120147705</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G906" t="n">
-        <v>19.9355964660645</v>
+        <v>19.9355945587158</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G907" t="n">
-        <v>19.96409034729</v>
+        <v>19.9640884399414</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G914" t="n">
-        <v>17.2952442169189</v>
+        <v>17.2952461242676</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G917" t="n">
-        <v>17.3854732513428</v>
+        <v>17.3854751586914</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>17.9150009155273</v>
       </c>
       <c r="G920" t="n">
-        <v>17.0150661468506</v>
+        <v>17.015064239502</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>17.4750003814697</v>
       </c>
       <c r="G921" t="n">
-        <v>16.5971660614014</v>
+        <v>16.59716796875</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G922" t="n">
-        <v>16.2837467193604</v>
+        <v>16.2837448120117</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G929" t="n">
-        <v>16.9485816955566</v>
+        <v>16.948579788208</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>17.6350002288818</v>
       </c>
       <c r="G930" t="n">
-        <v>16.7491321563721</v>
+        <v>16.7491302490234</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>17.7350006103516</v>
       </c>
       <c r="G931" t="n">
-        <v>16.8441066741943</v>
+        <v>16.844108581543</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G932" t="n">
-        <v>16.4974422454834</v>
+        <v>16.497444152832</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G935" t="n">
-        <v>16.9248371124268</v>
+        <v>16.9248352050781</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>18.0450000762939</v>
       </c>
       <c r="G939" t="n">
-        <v>17.1385345458984</v>
+        <v>17.1385364532471</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>17.7350006103516</v>
       </c>
       <c r="G944" t="n">
-        <v>16.8441066741943</v>
+        <v>16.844108581543</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>17.0450000762939</v>
       </c>
       <c r="G949" t="n">
-        <v>16.1887664794922</v>
+        <v>16.1887683868408</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G951" t="n">
-        <v>16.34547996521</v>
+        <v>16.3454780578613</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>16.8649997711182</v>
       </c>
       <c r="G954" t="n">
-        <v>16.0178108215332</v>
+        <v>16.0178089141846</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>16.3850002288818</v>
       </c>
       <c r="G957" t="n">
-        <v>15.5619230270386</v>
+        <v>15.5619220733643</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>16.4150009155273</v>
       </c>
       <c r="G962" t="n">
-        <v>15.5904159545898</v>
+        <v>15.5904169082642</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G964" t="n">
-        <v>15.680643081665</v>
+        <v>15.6806421279907</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G965" t="n">
-        <v>15.4052095413208</v>
+        <v>15.4052104949951</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G972" t="n">
-        <v>15.3197317123413</v>
+        <v>15.319730758667</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G973" t="n">
-        <v>15.960823059082</v>
+        <v>15.9608249664307</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>15.7661218643188</v>
+        <v>15.7661228179932</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>16.75</v>
       </c>
       <c r="G976" t="n">
-        <v>15.9085874557495</v>
+        <v>15.9085855484009</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>16.9950008392334</v>
       </c>
       <c r="G978" t="n">
-        <v>16.1412792205811</v>
+        <v>16.1412811279297</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>17.4549999237061</v>
       </c>
       <c r="G981" t="n">
-        <v>16.5781707763672</v>
+        <v>16.5781726837158</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G988" t="n">
-        <v>16.4404563903809</v>
+        <v>16.4404544830322</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>18.0949993133545</v>
       </c>
       <c r="G997" t="n">
-        <v>17.1860218048096</v>
+        <v>17.1860237121582</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1005" t="n">
-        <v>17.2477569580078</v>
+        <v>17.2477588653564</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>19.0750007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>18.1167945861816</v>
+        <v>18.1167964935303</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>17.8556079864502</v>
+        <v>17.8556060791016</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>18.75</v>
       </c>
       <c r="G1015" t="n">
-        <v>17.8081207275391</v>
+        <v>17.8081188201904</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>18.6049995422363</v>
       </c>
       <c r="G1017" t="n">
-        <v>17.6704025268555</v>
+        <v>17.6704044342041</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>18.5550003051758</v>
       </c>
       <c r="G1018" t="n">
-        <v>17.6229152679443</v>
+        <v>17.622917175293</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>18.6149997711182</v>
       </c>
       <c r="G1019" t="n">
-        <v>17.6799030303955</v>
+        <v>17.6799011230469</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1022" t="n">
-        <v>18.0930480957031</v>
+        <v>18.0930500030518</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.90309715271</v>
+        <v>17.9030952453613</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>18.7950000762939</v>
       </c>
       <c r="G1024" t="n">
-        <v>17.8508586883545</v>
+        <v>17.8508605957031</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.2287616729736</v>
+        <v>17.2287635803223</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1032" t="n">
-        <v>16.5924186706543</v>
+        <v>16.5924167633057</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>15.8611001968384</v>
+        <v>15.8610982894897</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G1034" t="n">
-        <v>16.2694969177246</v>
+        <v>16.2694988250732</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1037" t="n">
-        <v>15.8468503952026</v>
+        <v>15.8468523025513</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>16.6149997711182</v>
       </c>
       <c r="G1042" t="n">
-        <v>15.7803688049316</v>
+        <v>15.7803678512573</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>15.7186326980591</v>
+        <v>15.7186336517334</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>16.1550006866455</v>
       </c>
       <c r="G1044" t="n">
-        <v>15.3434772491455</v>
+        <v>15.3434762954712</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1045" t="n">
-        <v>15.9845676422119</v>
+        <v>15.9845695495605</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1047" t="n">
-        <v>15.604660987854</v>
+        <v>15.6046619415283</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1048" t="n">
-        <v>15.8611001968384</v>
+        <v>15.8610982894897</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1049" t="n">
-        <v>15.7043857574463</v>
+        <v>15.7043867111206</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>16.3649997711182</v>
       </c>
       <c r="G1051" t="n">
-        <v>15.5429267883301</v>
+        <v>15.5429258346558</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>14.3249998092651</v>
       </c>
       <c r="G1056" t="n">
-        <v>13.6054039001465</v>
+        <v>13.6054029464722</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1060" t="n">
-        <v>12.9738092422485</v>
+        <v>12.9738082885742</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>11.3549995422363</v>
       </c>
       <c r="G1065" t="n">
-        <v>10.7845964431763</v>
+        <v>10.7845973968506</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>9.5620002746582</v>
       </c>
       <c r="G1066" t="n">
-        <v>9.08166599273682</v>
+        <v>9.08166694641113</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>10.164999961853</v>
       </c>
       <c r="G1067" t="n">
-        <v>9.65437507629395</v>
+        <v>9.65437602996826</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1088" t="n">
-        <v>11.4541835784912</v>
+        <v>11.4541826248169</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>11.5396604537964</v>
+        <v>11.5396614074707</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>10.3999423980713</v>
+        <v>10.399941444397</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>11</v>
       </c>
       <c r="G1094" t="n">
-        <v>10.4474306106567</v>
+        <v>10.4474296569824</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1097" t="n">
-        <v>10.7323608398438</v>
+        <v>10.7323598861694</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1099" t="n">
-        <v>10.7228622436523</v>
+        <v>10.722861289978</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1104" t="n">
-        <v>10.4094390869141</v>
+        <v>10.4094400405884</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1110" t="n">
-        <v>10.4094390869141</v>
+        <v>10.4094400405884</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1111" t="n">
-        <v>10.3999423980713</v>
+        <v>10.399941444397</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>13.1542644500732</v>
+        <v>13.1542654037476</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G1128" t="n">
-        <v>11.8815774917603</v>
+        <v>11.8815784454346</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1130" t="n">
-        <v>12.0620336532593</v>
+        <v>12.062032699585</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1131" t="n">
-        <v>12.1190195083618</v>
+        <v>12.1190185546875</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1135" t="n">
-        <v>12.5749073028564</v>
+        <v>12.5749063491821</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>13.25</v>
       </c>
       <c r="G1136" t="n">
-        <v>12.5844049453735</v>
+        <v>12.5844039916992</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1138" t="n">
-        <v>11.8055953979492</v>
+        <v>11.8055963516235</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1140" t="n">
-        <v>11.7296152114868</v>
+        <v>11.7296142578125</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1143" t="n">
-        <v>11.7581071853638</v>
+        <v>11.7581081390381</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1144" t="n">
-        <v>11.4541835784912</v>
+        <v>11.4541826248169</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G1150" t="n">
-        <v>11.1787519454956</v>
+        <v>11.1787509918213</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.2452335357666</v>
+        <v>11.2452344894409</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G1159" t="n">
-        <v>11.0267868041992</v>
+        <v>11.0267877578735</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1161" t="n">
-        <v>10.8368349075317</v>
+        <v>10.8368339538574</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1167" t="n">
-        <v>10.8368349075317</v>
+        <v>10.8368339538574</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G1170" t="n">
-        <v>10.3619508743286</v>
+        <v>10.3619518280029</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1174" t="n">
-        <v>11.3307132720947</v>
+        <v>11.3307123184204</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1177" t="n">
-        <v>10.9603052139282</v>
+        <v>10.9603042602539</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G1178" t="n">
-        <v>10.7608528137207</v>
+        <v>10.760853767395</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1185" t="n">
-        <v>11.463680267334</v>
+        <v>11.4636793136597</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1188" t="n">
-        <v>11.7960987091064</v>
+        <v>11.7960977554321</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1193" t="n">
-        <v>11.4541835784912</v>
+        <v>11.4541826248169</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1203" t="n">
-        <v>11.463680267334</v>
+        <v>11.4636793136597</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>12.75</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.1095218658447</v>
+        <v>12.1095209121704</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1209" t="n">
-        <v>11.9860515594482</v>
+        <v>11.9860506057739</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>13.25</v>
       </c>
       <c r="G1215" t="n">
-        <v>12.5844049453735</v>
+        <v>12.5844039916992</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G1217" t="n">
-        <v>12.5464134216309</v>
+        <v>12.5464143753052</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>12.2044973373413</v>
+        <v>12.2044982910156</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1223" t="n">
-        <v>12.1950006484985</v>
+        <v>12.1949996948242</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1232" t="n">
-        <v>11.0647783279419</v>
+        <v>11.0647773742676</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1241" t="n">
-        <v>13.9235754013062</v>
+        <v>13.9235744476318</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G1248" t="n">
-        <v>14.3129796981812</v>
+        <v>14.3129787445068</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>15</v>
       </c>
       <c r="G1250" t="n">
-        <v>14.2464962005615</v>
+        <v>14.2464952468872</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>15</v>
       </c>
       <c r="G1256" t="n">
-        <v>14.2464962005615</v>
+        <v>14.2464952468872</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1257" t="n">
-        <v>14.4934358596802</v>
+        <v>14.4934349060059</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1263" t="n">
-        <v>14.8543472290039</v>
+        <v>14.8543462753296</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1265" t="n">
-        <v>14.3794631958008</v>
+        <v>14.3794622421265</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G1269" t="n">
-        <v>15.1107835769653</v>
+        <v>15.110782623291</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1273" t="n">
-        <v>14.7118816375732</v>
+        <v>14.7118806838989</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1275" t="n">
-        <v>14.5884113311768</v>
+        <v>14.5884103775024</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1277" t="n">
-        <v>14.4079551696777</v>
+        <v>14.4079561233521</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1279" t="n">
-        <v>14.5314254760742</v>
+        <v>14.5314264297485</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1282" t="n">
-        <v>14.3794631958008</v>
+        <v>14.3794622421265</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G1284" t="n">
-        <v>15.3197317123413</v>
+        <v>15.319730758667</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1285" t="n">
-        <v>15.29123878479</v>
+        <v>15.2912397384644</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>15.0537977218628</v>
+        <v>15.0537967681885</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1288" t="n">
-        <v>15.8041114807129</v>
+        <v>15.8041124343872</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1290" t="n">
-        <v>15.2627449035645</v>
+        <v>15.2627458572388</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1297" t="n">
-        <v>14.4364500045776</v>
+        <v>14.4364490509033</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>15.7700004577637</v>
       </c>
       <c r="G1303" t="n">
-        <v>14.9778165817261</v>
+        <v>14.9778156280518</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1310" t="n">
-        <v>15.1202812194824</v>
+        <v>15.1202802658081</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1312" t="n">
-        <v>15.2627449035645</v>
+        <v>15.2627458572388</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1314" t="n">
-        <v>15.1012859344482</v>
+        <v>15.1012849807739</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1316" t="n">
-        <v>14.9873132705688</v>
+        <v>14.9873123168945</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1320" t="n">
-        <v>16.032054901123</v>
+        <v>16.0320568084717</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>15.7376289367676</v>
+        <v>15.7376298904419</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1330" t="n">
-        <v>15.3672208786011</v>
+        <v>15.3672199249268</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1331" t="n">
-        <v>15.3387260437012</v>
+        <v>15.3387269973755</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1332" t="n">
-        <v>15.6996393203735</v>
+        <v>15.6996374130249</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G1335" t="n">
-        <v>15.960823059082</v>
+        <v>15.9608249664307</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>16.4449996948242</v>
       </c>
       <c r="G1336" t="n">
-        <v>15.6189069747925</v>
+        <v>15.6189079284668</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>16.2450008392334</v>
       </c>
       <c r="G1337" t="n">
-        <v>15.428955078125</v>
+        <v>15.4289560317993</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>16.4650001525879</v>
       </c>
       <c r="G1338" t="n">
-        <v>15.637903213501</v>
+        <v>15.6379041671753</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1339" t="n">
-        <v>15.8468503952026</v>
+        <v>15.8468523025513</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G1340" t="n">
-        <v>16.2837467193604</v>
+        <v>16.2837448120117</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>17.625</v>
       </c>
       <c r="G1342" t="n">
-        <v>16.739631652832</v>
+        <v>16.7396335601807</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>17.7649993896484</v>
       </c>
       <c r="G1344" t="n">
-        <v>16.8725986480713</v>
+        <v>16.8726005554199</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G1348" t="n">
-        <v>17.4567031860352</v>
+        <v>17.4567050933838</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G1349" t="n">
-        <v>17.3854732513428</v>
+        <v>17.3854751586914</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>18.2049999237061</v>
       </c>
       <c r="G1351" t="n">
-        <v>17.2904987335205</v>
+        <v>17.2904968261719</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1353" t="n">
-        <v>16.9248371124268</v>
+        <v>16.9248352050781</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1360" t="n">
-        <v>17.4187164306641</v>
+        <v>17.4187145233154</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1363" t="n">
-        <v>18.1975250244141</v>
+        <v>18.1975231170654</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G1364" t="n">
-        <v>18.1500377655029</v>
+        <v>18.1500358581543</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>19.1949996948242</v>
       </c>
       <c r="G1365" t="n">
-        <v>18.2307662963867</v>
+        <v>18.2307643890381</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G1378" t="n">
-        <v>18.3542346954346</v>
+        <v>18.3542366027832</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G1380" t="n">
-        <v>18.5299415588379</v>
+        <v>18.5299434661865</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G1382" t="n">
-        <v>18.3542346954346</v>
+        <v>18.3542366027832</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>19.2649993896484</v>
       </c>
       <c r="G1383" t="n">
-        <v>18.297248840332</v>
+        <v>18.2972469329834</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1385" t="n">
-        <v>18.1690311431885</v>
+        <v>18.1690292358398</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1386" t="n">
-        <v>18.1690311431885</v>
+        <v>18.1690292358398</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1387" t="n">
-        <v>18.1690311431885</v>
+        <v>18.1690292358398</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1389" t="n">
-        <v>18.444465637207</v>
+        <v>18.4444637298584</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G1394" t="n">
-        <v>17.8461093902588</v>
+        <v>17.8461112976074</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>18.0450000762939</v>
       </c>
       <c r="G1396" t="n">
-        <v>17.1385345458984</v>
+        <v>17.1385364532471</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1398" t="n">
-        <v>17.2287616729736</v>
+        <v>17.2287635803223</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1406" t="n">
-        <v>16.8773498535156</v>
+        <v>16.877347946167</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>16.4449996948242</v>
       </c>
       <c r="G1409" t="n">
-        <v>15.6189069747925</v>
+        <v>15.6189079284668</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>17.0249996185303</v>
       </c>
       <c r="G1415" t="n">
-        <v>16.1697731018066</v>
+        <v>16.169771194458</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G1417" t="n">
-        <v>16.0368061065674</v>
+        <v>16.0368041992188</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>17.0249996185303</v>
       </c>
       <c r="G1420" t="n">
-        <v>16.1697731018066</v>
+        <v>16.169771194458</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>16.9150009155273</v>
       </c>
       <c r="G1422" t="n">
-        <v>16.065299987793</v>
+        <v>16.0652980804443</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>17.0008163452148</v>
+        <v>17.0008182525635</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G1431" t="n">
-        <v>16.5164356231689</v>
+        <v>16.5164375305176</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>16.5750007629395</v>
       </c>
       <c r="G1433" t="n">
-        <v>15.7423791885376</v>
+        <v>15.7423782348633</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>17</v>
       </c>
       <c r="G1434" t="n">
-        <v>16.1460285186768</v>
+        <v>16.1460266113281</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1436" t="n">
-        <v>15.8041114807129</v>
+        <v>15.8041124343872</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>16.8150005340576</v>
       </c>
       <c r="G1437" t="n">
-        <v>15.9703235626221</v>
+        <v>15.9703216552734</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>18.8150005340576</v>
       </c>
       <c r="G1447" t="n">
-        <v>17.8698539733887</v>
+        <v>17.8698558807373</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>18.75</v>
       </c>
       <c r="G1449" t="n">
-        <v>17.8081207275391</v>
+        <v>17.8081188201904</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1456" t="n">
-        <v>16.9628276824951</v>
+        <v>16.9628295898438</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1459" t="n">
-        <v>16.9438323974609</v>
+        <v>16.9438304901123</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>17.9449996948242</v>
       </c>
       <c r="G1467" t="n">
-        <v>17.0435581207275</v>
+        <v>17.0435562133789</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>17.0008163452148</v>
+        <v>17.0008182525635</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1473" t="n">
-        <v>17.2287616729736</v>
+        <v>17.2287635803223</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1474" t="n">
-        <v>16.9438323974609</v>
+        <v>16.9438304901123</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>18.6550006866455</v>
       </c>
       <c r="G1484" t="n">
-        <v>17.7178916931152</v>
+        <v>17.7178936004639</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G1488" t="n">
-        <v>18.7009010314941</v>
+        <v>18.7008991241455</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1491" t="n">
-        <v>18.1690311431885</v>
+        <v>18.1690292358398</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>19.7549991607666</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.7626342773438</v>
+        <v>18.7626323699951</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1505" t="n">
-        <v>19.1377925872803</v>
+        <v>19.1377906799316</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G1508" t="n">
-        <v>19.8691139221191</v>
+        <v>19.8691120147705</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G1509" t="n">
-        <v>19.7456436157227</v>
+        <v>19.7456455230713</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1510" t="n">
-        <v>20.4579696655273</v>
+        <v>20.4579677581787</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1513" t="n">
-        <v>21.4457244873047</v>
+        <v>21.4457225799561</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1515" t="n">
-        <v>20.7523956298828</v>
+        <v>20.7523975372314</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G1516" t="n">
-        <v>20.6384220123291</v>
+        <v>20.6384239196777</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G1517" t="n">
-        <v>20.1635417938232</v>
+        <v>20.1635398864746</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G1520" t="n">
-        <v>20.7144050598145</v>
+        <v>20.7144031524658</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G1523" t="n">
-        <v>21.0183277130127</v>
+        <v>21.0183296203613</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G1526" t="n">
-        <v>21.3982372283936</v>
+        <v>21.3982353210449</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G1528" t="n">
-        <v>21.5691928863525</v>
+        <v>21.5691947937012</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G1531" t="n">
-        <v>21.6261825561523</v>
+        <v>21.6261806488037</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G1532" t="n">
-        <v>19.7171497344971</v>
+        <v>19.7171478271484</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G1541" t="n">
-        <v>18.055061340332</v>
+        <v>18.0550594329834</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1542" t="n">
-        <v>17.4946956634521</v>
+        <v>17.4946975708008</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1544" t="n">
-        <v>18.0930480957031</v>
+        <v>18.0930500030518</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>19.5750007629395</v>
       </c>
       <c r="G1548" t="n">
-        <v>18.5916767120361</v>
+        <v>18.5916786193848</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1549" t="n">
-        <v>18.5394420623779</v>
+        <v>18.5394401550293</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>19.25</v>
       </c>
       <c r="G1555" t="n">
-        <v>18.2830009460449</v>
+        <v>18.2830028533936</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G1563" t="n">
-        <v>18.7768802642822</v>
+        <v>18.7768821716309</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G1565" t="n">
-        <v>17.9220924377441</v>
+        <v>17.9220905303955</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>19.6450004577637</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.6581592559814</v>
+        <v>18.6581611633301</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>19.4249992370605</v>
       </c>
       <c r="G1567" t="n">
-        <v>18.4492111206055</v>
+        <v>18.4492130279541</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>18.5650005340576</v>
       </c>
       <c r="G1568" t="n">
-        <v>17.6324157714844</v>
+        <v>17.6324138641357</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>15.2749996185303</v>
       </c>
       <c r="G1573" t="n">
-        <v>14.5076808929443</v>
+        <v>14.5076818466187</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>16.7549991607666</v>
       </c>
       <c r="G1574" t="n">
-        <v>15.9133329391479</v>
+        <v>15.9133348464966</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>16.1650009155273</v>
       </c>
       <c r="G1576" t="n">
-        <v>15.3529748916626</v>
+        <v>15.3529739379883</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G1579" t="n">
-        <v>15.5856666564941</v>
+        <v>15.5856657028198</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1580" t="n">
-        <v>15.7043857574463</v>
+        <v>15.7043867111206</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1581" t="n">
-        <v>15.8611001968384</v>
+        <v>15.8610982894897</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1582" t="n">
-        <v>15.81360912323</v>
+        <v>15.8136100769043</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1585" t="n">
-        <v>15.2532472610474</v>
+        <v>15.253246307373</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>16.6650009155273</v>
       </c>
       <c r="G1587" t="n">
-        <v>15.8278579711914</v>
+        <v>15.8278589248657</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>17.6550006866455</v>
       </c>
       <c r="G1588" t="n">
-        <v>16.7681274414062</v>
+        <v>16.7681255340576</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1593" t="n">
-        <v>15.2627449035645</v>
+        <v>15.2627458572388</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1595" t="n">
-        <v>14.5884113311768</v>
+        <v>14.5884103775024</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1598" t="n">
-        <v>15.3387260437012</v>
+        <v>15.3387269973755</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1600" t="n">
-        <v>15.6331539154053</v>
+        <v>15.633152961731</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1602" t="n">
-        <v>15.6996393203735</v>
+        <v>15.6996374130249</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>16.3299999237061</v>
       </c>
       <c r="G1604" t="n">
-        <v>15.5096845626831</v>
+        <v>15.5096855163574</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1608" t="n">
-        <v>15.1392755508423</v>
+        <v>15.1392765045166</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1614" t="n">
-        <v>14.3224773406982</v>
+        <v>14.3224763870239</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G1620" t="n">
-        <v>15.0158061981201</v>
+        <v>15.0158071517944</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1622" t="n">
-        <v>15.3672208786011</v>
+        <v>15.3672199249268</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>7.61999988555908</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>680932</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>7.71500015258789</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>7.25500011444092</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>7.65000009536743</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>7.40999984741211</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>7.40999984741211</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -447,7 +447,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G3" t="n">
-        <v>18.01096534729</v>
+        <v>18.0109634399414</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G4" t="n">
-        <v>17.4978828430176</v>
+        <v>17.4978809356689</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>17.9401950836182</v>
+        <v>17.9401912689209</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G8" t="n">
-        <v>19.4086723327637</v>
+        <v>19.408670425415</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G10" t="n">
-        <v>18.8425140380859</v>
+        <v>18.8425102233887</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G14" t="n">
-        <v>17.6394214630127</v>
+        <v>17.6394233703613</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G15" t="n">
-        <v>17.5686531066895</v>
+        <v>17.5686511993408</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G16" t="n">
-        <v>18.1878871917725</v>
+        <v>18.1878910064697</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G18" t="n">
-        <v>18.4798126220703</v>
+        <v>18.4798145294189</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>18.2232723236084</v>
+        <v>18.223274230957</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G21" t="n">
-        <v>18.3913536071777</v>
+        <v>18.3913516998291</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G22" t="n">
-        <v>18.6744327545166</v>
+        <v>18.6744346618652</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>17.9578819274902</v>
+        <v>17.9578838348389</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G27" t="n">
-        <v>17.3563442230225</v>
+        <v>17.3563423156738</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>17.1617240905762</v>
+        <v>17.1617221832275</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G30" t="n">
-        <v>16.6486415863037</v>
+        <v>16.6486434936523</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G31" t="n">
-        <v>17.0201854705811</v>
+        <v>17.0201835632324</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G32" t="n">
-        <v>17.4890384674072</v>
+        <v>17.48903465271</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G33" t="n">
-        <v>17.6305751800537</v>
+        <v>17.6305732727051</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G34" t="n">
-        <v>18.4798126220703</v>
+        <v>18.4798145294189</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>20.8099994659424</v>
       </c>
       <c r="G35" t="n">
-        <v>18.4090423583984</v>
+        <v>18.4090442657471</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G36" t="n">
-        <v>18.4532794952393</v>
+        <v>18.4532775878906</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>18.9752044677734</v>
+        <v>18.9752063751221</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>20.5</v>
       </c>
       <c r="G38" t="n">
-        <v>18.1348133087158</v>
+        <v>18.1348114013672</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G41" t="n">
-        <v>17.9048099517822</v>
+        <v>17.9048080444336</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G42" t="n">
-        <v>18.3471183776855</v>
+        <v>18.3471221923828</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G47" t="n">
-        <v>19.9925231933594</v>
+        <v>19.992525100708</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>19.9482936859131</v>
+        <v>19.9482917785645</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G50" t="n">
-        <v>19.3379020690918</v>
+        <v>19.3379039764404</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G52" t="n">
-        <v>19.983678817749</v>
+        <v>19.9836750030518</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G53" t="n">
-        <v>19.1167469024658</v>
+        <v>19.1167449951172</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G54" t="n">
-        <v>19.3379020690918</v>
+        <v>19.3379039764404</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G55" t="n">
-        <v>19.444055557251</v>
+        <v>19.4440536499023</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G62" t="n">
-        <v>19.9129085540771</v>
+        <v>19.9129066467285</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G65" t="n">
-        <v>19.4175186157227</v>
+        <v>19.417516708374</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G66" t="n">
-        <v>18.8690490722656</v>
+        <v>18.8690509796143</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G67" t="n">
-        <v>18.833667755127</v>
+        <v>18.8336658477783</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G68" t="n">
-        <v>18.5151996612549</v>
+        <v>18.5152015686035</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>18.9309730529785</v>
+        <v>18.9309749603271</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G71" t="n">
-        <v>18.5240478515625</v>
+        <v>18.5240440368652</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>18.9486656188965</v>
+        <v>18.9486694335938</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>21.25</v>
       </c>
       <c r="G74" t="n">
-        <v>18.7982788085938</v>
+        <v>18.7982807159424</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G75" t="n">
-        <v>18.8778972625732</v>
+        <v>18.8778953552246</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G76" t="n">
-        <v>19.2936706542969</v>
+        <v>19.2936687469482</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>18.3648128509521</v>
+        <v>18.3648166656494</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G82" t="n">
-        <v>18.0640430450439</v>
+        <v>18.0640411376953</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>18.0021171569824</v>
+        <v>18.0021190643311</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G87" t="n">
-        <v>17.9048099517822</v>
+        <v>17.9048080444336</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G88" t="n">
-        <v>17.4448013305664</v>
+        <v>17.4448051452637</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G89" t="n">
-        <v>17.1440296173096</v>
+        <v>17.1440277099609</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G91" t="n">
-        <v>17.9844264984131</v>
+        <v>17.9844284057617</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>17.6394214630127</v>
+        <v>17.6394233703613</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G93" t="n">
-        <v>17.4182682037354</v>
+        <v>17.4182662963867</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G94" t="n">
-        <v>18.833667755127</v>
+        <v>18.8336658477783</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>21.25</v>
       </c>
       <c r="G95" t="n">
-        <v>18.7982788085938</v>
+        <v>18.7982807159424</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>18.0640430450439</v>
+        <v>18.0640411376953</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>20.2700004577637</v>
       </c>
       <c r="G97" t="n">
-        <v>17.9313468933105</v>
+        <v>17.9313488006592</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>17.7367267608643</v>
+        <v>17.7367305755615</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G99" t="n">
-        <v>17.6482696533203</v>
+        <v>17.648265838623</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G100" t="n">
-        <v>17.593936920166</v>
+        <v>17.5939407348633</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G104" t="n">
-        <v>17.530553817749</v>
+        <v>17.5305519104004</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G105" t="n">
-        <v>17.593936920166</v>
+        <v>17.5939407348633</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G107" t="n">
-        <v>17.3041763305664</v>
+        <v>17.304178237915</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G111" t="n">
-        <v>17.4852771759033</v>
+        <v>17.4852752685547</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G113" t="n">
-        <v>17.6844882965088</v>
+        <v>17.6844863891602</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G114" t="n">
-        <v>17.1502418518066</v>
+        <v>17.150239944458</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G115" t="n">
-        <v>16.7155990600586</v>
+        <v>16.71559715271</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G117" t="n">
-        <v>17.0415802001953</v>
+        <v>17.0415821075439</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G118" t="n">
-        <v>17.0778007507324</v>
+        <v>17.0778026580811</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>17.8384227752686</v>
+        <v>17.8384246826172</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G120" t="n">
-        <v>17.9380302429199</v>
+        <v>17.9380283355713</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G121" t="n">
-        <v>17.7297611236572</v>
+        <v>17.7297649383545</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G122" t="n">
-        <v>17.8655891418457</v>
+        <v>17.8655872344971</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G124" t="n">
-        <v>16.8514232635498</v>
+        <v>16.8514251708984</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>16.3896160125732</v>
+        <v>16.3896179199219</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G126" t="n">
-        <v>16.6793804168701</v>
+        <v>16.6793785095215</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G127" t="n">
-        <v>16.2628440856934</v>
+        <v>16.2628479003906</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>16.6069393157959</v>
+        <v>16.6069374084473</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G131" t="n">
-        <v>16.8242568969727</v>
+        <v>16.8242607116699</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G133" t="n">
-        <v>15.873480796814</v>
+        <v>15.8734817504883</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G134" t="n">
-        <v>16.3624515533447</v>
+        <v>16.3624534606934</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G136" t="n">
-        <v>16.6974906921387</v>
+        <v>16.69748878479</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G137" t="n">
-        <v>17.095911026001</v>
+        <v>17.0959091186523</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G138" t="n">
-        <v>17.1321315765381</v>
+        <v>17.1321296691895</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G139" t="n">
-        <v>17.086856842041</v>
+        <v>17.0868549346924</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G140" t="n">
-        <v>17.1502418518066</v>
+        <v>17.150239944458</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>17.3403949737549</v>
+        <v>17.3403987884521</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G143" t="n">
-        <v>17.8655891418457</v>
+        <v>17.8655872344971</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G144" t="n">
-        <v>17.9018096923828</v>
+        <v>17.9018077850342</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G145" t="n">
-        <v>18.1372394561768</v>
+        <v>18.1372413635254</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>17.9289741516113</v>
+        <v>17.9289722442627</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>18.6352653503418</v>
+        <v>18.6352691650391</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G149" t="n">
-        <v>19.0699100494385</v>
+        <v>19.0699081420898</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>20.5699996948242</v>
       </c>
       <c r="G151" t="n">
-        <v>18.6262092590332</v>
+        <v>18.6262111663818</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G155" t="n">
-        <v>18.5809345245361</v>
+        <v>18.5809364318848</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G156" t="n">
-        <v>18.7620334625244</v>
+        <v>18.762035369873</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G159" t="n">
-        <v>18.9431381225586</v>
+        <v>18.94313621521</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G160" t="n">
-        <v>19.04274559021</v>
+        <v>19.0427436828613</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>18.4722747802734</v>
+        <v>18.4722766876221</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G164" t="n">
-        <v>18.6171550750732</v>
+        <v>18.6171588897705</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G165" t="n">
-        <v>18.7529792785645</v>
+        <v>18.7529811859131</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G167" t="n">
-        <v>18.6805419921875</v>
+        <v>18.6805400848389</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6533756256104</v>
+        <v>18.653377532959</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G173" t="n">
-        <v>18.8706970214844</v>
+        <v>18.870698928833</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>18.6986503601074</v>
+        <v>18.6986522674561</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G175" t="n">
-        <v>18.7620334625244</v>
+        <v>18.762035369873</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>19.1061305999756</v>
+        <v>19.106128692627</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>19.5588817596436</v>
+        <v>19.5588798522949</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G182" t="n">
-        <v>18.8888072967529</v>
+        <v>18.8888092041016</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G183" t="n">
-        <v>18.6805419921875</v>
+        <v>18.6805400848389</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>19.1604614257812</v>
+        <v>19.160457611084</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G187" t="n">
-        <v>19.9391899108887</v>
+        <v>19.9391918182373</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G188" t="n">
-        <v>20.4553279876709</v>
+        <v>20.4553260803223</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>20.3557224273682</v>
+        <v>20.3557205200195</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G190" t="n">
-        <v>20.4553279876709</v>
+        <v>20.4553260803223</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>20.3919429779053</v>
+        <v>20.3919448852539</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>20.4643840789795</v>
+        <v>20.4643859863281</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G194" t="n">
-        <v>20.3557224273682</v>
+        <v>20.3557205200195</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>20.6907596588135</v>
+        <v>20.6907634735107</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>20.8446960449219</v>
+        <v>20.8446941375732</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G197" t="n">
-        <v>20.7994194030762</v>
+        <v>20.7994213104248</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G198" t="n">
-        <v>20.4009990692139</v>
+        <v>20.4010009765625</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>22.6900005340576</v>
       </c>
       <c r="G202" t="n">
-        <v>20.5458793640137</v>
+        <v>20.545877456665</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G203" t="n">
-        <v>20.7541465759277</v>
+        <v>20.7541446685791</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G206" t="n">
-        <v>20.265172958374</v>
+        <v>20.2651748657227</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G208" t="n">
-        <v>20.3557224273682</v>
+        <v>20.3557205200195</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>22.25</v>
       </c>
       <c r="G210" t="n">
-        <v>20.1474590301514</v>
+        <v>20.1474571228027</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G211" t="n">
-        <v>20.2289524078369</v>
+        <v>20.2289543151855</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G214" t="n">
-        <v>20.1836814880371</v>
+        <v>20.1836795806885</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>19.5045490264893</v>
+        <v>19.5045509338379</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G219" t="n">
-        <v>19.7218704223633</v>
+        <v>19.7218723297119</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G220" t="n">
-        <v>19.7943115234375</v>
+        <v>19.7943134307861</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G221" t="n">
-        <v>19.5226612091064</v>
+        <v>19.5226593017578</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>19.830530166626</v>
+        <v>19.8305320739746</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>21.9899997711182</v>
       </c>
       <c r="G223" t="n">
-        <v>19.9120254516602</v>
+        <v>19.9120273590088</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.4722747802734</v>
+        <v>18.4722766876221</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G226" t="n">
-        <v>18.0919666290283</v>
+        <v>18.0919628143311</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G228" t="n">
-        <v>18.3273963928223</v>
+        <v>18.3273944854736</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>18.2458992004395</v>
+        <v>18.2459011077881</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G232" t="n">
-        <v>17.8565330505371</v>
+        <v>17.8565349578857</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>17.6392116546631</v>
+        <v>17.6392135620117</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G239" t="n">
-        <v>18.8706970214844</v>
+        <v>18.870698928833</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>19.1514053344727</v>
+        <v>19.151403427124</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>19.2872314453125</v>
+        <v>19.2872276306152</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G242" t="n">
-        <v>19.3958911895752</v>
+        <v>19.3958930969238</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G244" t="n">
-        <v>19.1151866912842</v>
+        <v>19.1151847839355</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G245" t="n">
-        <v>19.5860443115234</v>
+        <v>19.5860462188721</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G248" t="n">
-        <v>20.265172958374</v>
+        <v>20.2651748657227</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>22.5</v>
       </c>
       <c r="G249" t="n">
-        <v>20.3738327026367</v>
+        <v>20.373836517334</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G250" t="n">
-        <v>20.265172958374</v>
+        <v>20.2651748657227</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>20.2380104064941</v>
+        <v>20.2380084991455</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G254" t="n">
-        <v>20.1836814880371</v>
+        <v>20.1836795806885</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>20.2289524078369</v>
+        <v>20.2289543151855</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>20.1565132141113</v>
+        <v>20.1565113067627</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G259" t="n">
-        <v>20.6183204650879</v>
+        <v>20.6183185577393</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G261" t="n">
-        <v>21.5328807830811</v>
+        <v>21.5328788757324</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G264" t="n">
-        <v>22.2572803497314</v>
+        <v>22.2572822570801</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>24.6299991607666</v>
       </c>
       <c r="G266" t="n">
-        <v>22.3025531768799</v>
+        <v>22.3025550842285</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>22.3206653594971</v>
+        <v>22.3206672668457</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>22.2753925323486</v>
+        <v>22.275390625</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G269" t="n">
-        <v>22.2391719818115</v>
+        <v>22.2391700744629</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G272" t="n">
-        <v>22.8911361694336</v>
+        <v>22.891134262085</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>25.5100002288818</v>
       </c>
       <c r="G274" t="n">
-        <v>23.0993976593018</v>
+        <v>23.0993995666504</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>22.5923156738281</v>
+        <v>22.5923194885254</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>22.9092445373535</v>
+        <v>22.9092426300049</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G280" t="n">
-        <v>23.6064834594727</v>
+        <v>23.606481552124</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>26.2299995422363</v>
       </c>
       <c r="G281" t="n">
-        <v>23.7513637542725</v>
+        <v>23.7513618469238</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>26.6399993896484</v>
       </c>
       <c r="G282" t="n">
-        <v>24.1226177215576</v>
+        <v>24.1226196289062</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G283" t="n">
-        <v>23.6427021026611</v>
+        <v>23.6427040100098</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>23.561206817627</v>
+        <v>23.5612087249756</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G286" t="n">
-        <v>23.561206817627</v>
+        <v>23.5612087249756</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>23.7241973876953</v>
+        <v>23.7241992950439</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>23.6336479187012</v>
+        <v>23.6336460113525</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G293" t="n">
-        <v>23.7241973876953</v>
+        <v>23.7241992950439</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>26.5200004577637</v>
       </c>
       <c r="G294" t="n">
-        <v>24.0139579772949</v>
+        <v>24.0139598846436</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>23.9777374267578</v>
+        <v>23.9777393341064</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G299" t="n">
-        <v>24.4304904937744</v>
+        <v>24.4304885864258</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>27.8199996948242</v>
       </c>
       <c r="G302" t="n">
-        <v>25.1911125183105</v>
+        <v>25.1911144256592</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>28.0400009155273</v>
       </c>
       <c r="G303" t="n">
-        <v>25.3903255462646</v>
+        <v>25.3903274536133</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>25.6710319519043</v>
+        <v>25.6710300445557</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>28.3299999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>25.6529216766357</v>
+        <v>25.6529197692871</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>25.7615814208984</v>
+        <v>25.7615795135498</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G310" t="n">
-        <v>24.9556789398193</v>
+        <v>24.9556846618652</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>27.5</v>
       </c>
       <c r="G311" t="n">
-        <v>24.9013500213623</v>
+        <v>24.9013538360596</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>25.0643444061279</v>
+        <v>25.0643424987793</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>27.3899993896484</v>
       </c>
       <c r="G313" t="n">
-        <v>24.8017463684082</v>
+        <v>24.8017482757568</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>27.1900005340576</v>
       </c>
       <c r="G314" t="n">
-        <v>24.6206474304199</v>
+        <v>24.6206455230713</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>27.5400009155273</v>
       </c>
       <c r="G315" t="n">
-        <v>24.937572479248</v>
+        <v>24.9375743865967</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>28.0200004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>25.3722152709961</v>
+        <v>25.3722133636475</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>25.6257572174072</v>
+        <v>25.62575340271</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>25.1730041503906</v>
+        <v>25.173002243042</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>25.3993797302246</v>
+        <v>25.399377822876</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>28.4099998474121</v>
       </c>
       <c r="G323" t="n">
-        <v>25.7253608703613</v>
+        <v>25.7253570556641</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>27.9300003051758</v>
       </c>
       <c r="G324" t="n">
-        <v>25.2907218933105</v>
+        <v>25.2907199859619</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>28.1700000762939</v>
       </c>
       <c r="G329" t="n">
-        <v>25.5080432891846</v>
+        <v>25.5080394744873</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>25.2635536193848</v>
+        <v>25.2635517120361</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>25.0824546813965</v>
+        <v>25.0824527740479</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G332" t="n">
-        <v>24.7836380004883</v>
+        <v>24.7836360931396</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>26.9699993133545</v>
       </c>
       <c r="G333" t="n">
-        <v>24.4214344024658</v>
+        <v>24.4214363098145</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>24.2674999237061</v>
+        <v>24.2674980163574</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>27.8199996948242</v>
       </c>
       <c r="G336" t="n">
-        <v>25.1911125183105</v>
+        <v>25.1911144256592</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>28.1900005340576</v>
       </c>
       <c r="G337" t="n">
-        <v>25.5261516571045</v>
+        <v>25.5261478424072</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>28.9200000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>26.1871662139893</v>
+        <v>26.1871681213379</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>29.4099998474121</v>
       </c>
       <c r="G340" t="n">
-        <v>26.6308650970459</v>
+        <v>26.6308631896973</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>29.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>26.3229942321777</v>
+        <v>26.3229923248291</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G343" t="n">
-        <v>26.6761379241943</v>
+        <v>26.676139831543</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>26.8934593200684</v>
+        <v>26.893461227417</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>29</v>
       </c>
       <c r="G345" t="n">
-        <v>26.2596073150635</v>
+        <v>26.2596092224121</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>26.6670837402344</v>
+        <v>26.667085647583</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>29.4099998474121</v>
       </c>
       <c r="G348" t="n">
-        <v>26.6308650970459</v>
+        <v>26.6308631896973</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>29</v>
       </c>
       <c r="G351" t="n">
-        <v>26.2596073150635</v>
+        <v>26.2596092224121</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>27.9699993133545</v>
       </c>
       <c r="G353" t="n">
-        <v>25.326940536499</v>
+        <v>25.3269386291504</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>28.5300006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>25.834020614624</v>
+        <v>25.8340244293213</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G355" t="n">
-        <v>25.8984451293945</v>
+        <v>25.8984432220459</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>26.8500003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>24.7112045288086</v>
+        <v>24.71120262146</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>25.6599998474121</v>
       </c>
       <c r="G358" t="n">
-        <v>23.6159954071045</v>
+        <v>23.6159934997559</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>22.9625492095947</v>
+        <v>22.9625511169434</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>22.8705177307129</v>
+        <v>22.8705158233643</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G363" t="n">
-        <v>22.8613128662109</v>
+        <v>22.8613147735596</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G366" t="n">
-        <v>23.0453853607178</v>
+        <v>23.0453834533691</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>24</v>
       </c>
       <c r="G368" t="n">
-        <v>22.088228225708</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G373" t="n">
-        <v>22.7416667938232</v>
+        <v>22.7416706085205</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G374" t="n">
-        <v>22.9533462524414</v>
+        <v>22.95334815979</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>23.2846717834473</v>
+        <v>23.2846698760986</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>23.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>21.545223236084</v>
+        <v>21.5452213287354</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>21.4900035858154</v>
+        <v>21.4900016784668</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>21.7200870513916</v>
+        <v>21.7200889587402</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>21.6740703582764</v>
+        <v>21.674072265625</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>23.5</v>
       </c>
       <c r="G388" t="n">
-        <v>21.6280555725098</v>
+        <v>21.6280536651611</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G395" t="n">
-        <v>21.9133605957031</v>
+        <v>21.9133625030518</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G396" t="n">
-        <v>21.8857517242432</v>
+        <v>21.8857498168945</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>23.8700008392334</v>
       </c>
       <c r="G397" t="n">
-        <v>21.9685840606689</v>
+        <v>21.9685821533203</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G398" t="n">
-        <v>22.6220226287842</v>
+        <v>22.6220245361328</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G400" t="n">
-        <v>22.2170715332031</v>
+        <v>22.2170734405518</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G401" t="n">
-        <v>22.4103469848633</v>
+        <v>22.4103450775146</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G402" t="n">
-        <v>22.5299911499023</v>
+        <v>22.5299892425537</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>24</v>
       </c>
       <c r="G406" t="n">
-        <v>22.088228225708</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G407" t="n">
-        <v>21.4255790710449</v>
+        <v>21.4255771636963</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>24</v>
       </c>
       <c r="G409" t="n">
-        <v>22.088228225708</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>24.1900005340576</v>
       </c>
       <c r="G410" t="n">
-        <v>22.263090133667</v>
+        <v>22.2630920410156</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G411" t="n">
-        <v>22.5391941070557</v>
+        <v>22.539192199707</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G415" t="n">
-        <v>22.6220226287842</v>
+        <v>22.6220245361328</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G416" t="n">
-        <v>22.7876853942871</v>
+        <v>22.7876873016357</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>24.2700004577637</v>
       </c>
       <c r="G417" t="n">
-        <v>22.3367195129395</v>
+        <v>22.3367176055908</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>24.0300006866455</v>
       </c>
       <c r="G418" t="n">
-        <v>22.115837097168</v>
+        <v>22.1158351898193</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>23.9699993133545</v>
       </c>
       <c r="G420" t="n">
-        <v>22.0606155395508</v>
+        <v>22.0606136322021</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G421" t="n">
-        <v>21.7569007873535</v>
+        <v>21.7569026947021</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G422" t="n">
-        <v>21.9133605957031</v>
+        <v>21.9133625030518</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>24</v>
       </c>
       <c r="G423" t="n">
-        <v>22.088228225708</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G425" t="n">
-        <v>21.701681137085</v>
+        <v>21.7016830444336</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G426" t="n">
-        <v>22.0053958892822</v>
+        <v>22.0053939819336</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G427" t="n">
-        <v>22.2170715332031</v>
+        <v>22.2170734405518</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G429" t="n">
-        <v>22.0053958892822</v>
+        <v>22.0053939819336</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G430" t="n">
-        <v>21.9133605957031</v>
+        <v>21.9133625030518</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G432" t="n">
-        <v>22.1250419616699</v>
+        <v>22.1250400543213</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G433" t="n">
-        <v>21.7753086090088</v>
+        <v>21.7753067016602</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>23.9300003051758</v>
       </c>
       <c r="G434" t="n">
-        <v>22.0238018035889</v>
+        <v>22.0238037109375</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>20.7997455596924</v>
+        <v>20.799747467041</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>21.0758495330811</v>
+        <v>21.0758457183838</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G446" t="n">
-        <v>22.0974292755127</v>
+        <v>22.0974273681641</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>23.75</v>
       </c>
       <c r="G448" t="n">
-        <v>21.8581428527832</v>
+        <v>21.8581390380859</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G451" t="n">
-        <v>21.2967319488525</v>
+        <v>21.2967300415039</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>20.7997455596924</v>
+        <v>20.799747467041</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838161468506</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G458" t="n">
-        <v>21.0942554473877</v>
+        <v>21.0942573547363</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G461" t="n">
-        <v>21.0022201538086</v>
+        <v>21.0022220611572</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G463" t="n">
-        <v>20.4500141143799</v>
+        <v>20.4500160217285</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>20.3855895996094</v>
+        <v>20.385591506958</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G469" t="n">
-        <v>20.4868278503418</v>
+        <v>20.4868297576904</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G470" t="n">
-        <v>20.7445259094238</v>
+        <v>20.7445240020752</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G471" t="n">
-        <v>20.8917808532715</v>
+        <v>20.8917827606201</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G474" t="n">
-        <v>21.2415084838867</v>
+        <v>21.241512298584</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G475" t="n">
-        <v>20.9285945892334</v>
+        <v>20.9285926818848</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G481" t="n">
-        <v>19.2719783782959</v>
+        <v>19.2719764709473</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>19.6953353881836</v>
+        <v>19.695333480835</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G483" t="n">
-        <v>19.8057765960693</v>
+        <v>19.8057746887207</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G485" t="n">
-        <v>20.1831169128418</v>
+        <v>20.1831188201904</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>20.2935562133789</v>
+        <v>20.2935581207275</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>20.4316082000732</v>
+        <v>20.4316120147705</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G489" t="n">
-        <v>20.5696620941162</v>
+        <v>20.5696601867676</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G491" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838161468506</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G492" t="n">
-        <v>21.131067276001</v>
+        <v>21.1310691833496</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G495" t="n">
-        <v>21.0022201538086</v>
+        <v>21.0022220611572</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>23.3099994659424</v>
       </c>
       <c r="G498" t="n">
-        <v>21.4531898498535</v>
+        <v>21.4531879425049</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G502" t="n">
-        <v>20.7721347808838</v>
+        <v>20.7721366882324</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>19.4652500152588</v>
+        <v>19.4652481079102</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G504" t="n">
-        <v>19.7965717315674</v>
+        <v>19.7965698242188</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G508" t="n">
-        <v>20.2935562133789</v>
+        <v>20.2935581207275</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>20.2291316986084</v>
+        <v>20.2291355133057</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>20.2935562133789</v>
+        <v>20.2935581207275</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G511" t="n">
-        <v>20.3855895996094</v>
+        <v>20.385591506958</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>20.5236415863037</v>
+        <v>20.5236434936523</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G514" t="n">
-        <v>20.652494430542</v>
+        <v>20.6524906158447</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G516" t="n">
-        <v>20.652494430542</v>
+        <v>20.6524906158447</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>22.2399997711182</v>
       </c>
       <c r="G518" t="n">
-        <v>20.4684219360352</v>
+        <v>20.4684238433838</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G520" t="n">
-        <v>20.4868278503418</v>
+        <v>20.4868297576904</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>20.4316082000732</v>
+        <v>20.4316120147705</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G522" t="n">
-        <v>20.4500141143799</v>
+        <v>20.4500160217285</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G524" t="n">
-        <v>20.1739139556885</v>
+        <v>20.1739120483398</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G526" t="n">
-        <v>21.7569007873535</v>
+        <v>21.7569026947021</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G527" t="n">
-        <v>21.2967319488525</v>
+        <v>21.2967300415039</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G531" t="n">
-        <v>21.5176105499268</v>
+        <v>21.5176124572754</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G533" t="n">
-        <v>20.8549690246582</v>
+        <v>20.8549652099609</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>22.7299995422363</v>
       </c>
       <c r="G535" t="n">
-        <v>20.9193916320801</v>
+        <v>20.9193897247314</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G536" t="n">
-        <v>20.5052375793457</v>
+        <v>20.5052356719971</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>22.1100006103516</v>
       </c>
       <c r="G537" t="n">
-        <v>20.3487796783447</v>
+        <v>20.3487777709961</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G539" t="n">
-        <v>20.0266571044922</v>
+        <v>20.0266551971436</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>21.4300003051758</v>
       </c>
       <c r="G540" t="n">
-        <v>19.7229461669922</v>
+        <v>19.7229480743408</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G542" t="n">
-        <v>19.9162158966064</v>
+        <v>19.9162139892578</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G544" t="n">
-        <v>20.5604553222656</v>
+        <v>20.5604572296143</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G547" t="n">
-        <v>20.4500141143799</v>
+        <v>20.4500160217285</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G548" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838161468506</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G550" t="n">
-        <v>20.9285945892334</v>
+        <v>20.9285926818848</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G552" t="n">
-        <v>20.8365592956543</v>
+        <v>20.8365573883057</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G553" t="n">
-        <v>21.2967319488525</v>
+        <v>21.2967300415039</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>23.4699993133545</v>
       </c>
       <c r="G554" t="n">
-        <v>21.6004447937012</v>
+        <v>21.6004428863525</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G555" t="n">
-        <v>20.6248817443848</v>
+        <v>20.6248798370361</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>22.0300006866455</v>
       </c>
       <c r="G556" t="n">
-        <v>20.2751502990723</v>
+        <v>20.2751522064209</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>19.6493186950684</v>
+        <v>19.6493167877197</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>21.8700008392334</v>
       </c>
       <c r="G564" t="n">
-        <v>20.1278972625732</v>
+        <v>20.1278953552246</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G566" t="n">
-        <v>20.5696620941162</v>
+        <v>20.5696601867676</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>22.6800003051758</v>
       </c>
       <c r="G567" t="n">
-        <v>20.8733749389648</v>
+        <v>20.8733730316162</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G568" t="n">
-        <v>20.5236415863037</v>
+        <v>20.5236434936523</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G570" t="n">
-        <v>20.652494430542</v>
+        <v>20.6524906158447</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>22.3099994659424</v>
       </c>
       <c r="G571" t="n">
-        <v>20.5328464508057</v>
+        <v>20.5328483581543</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G572" t="n">
-        <v>20.3027591705322</v>
+        <v>20.3027610778809</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>20.3855895996094</v>
+        <v>20.385591506958</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G575" t="n">
-        <v>20.64328956604</v>
+        <v>20.6432876586914</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>20.6156787872314</v>
+        <v>20.6156749725342</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G577" t="n">
-        <v>20.7445259094238</v>
+        <v>20.7445240020752</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>20.3855895996094</v>
+        <v>20.385591506958</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G581" t="n">
-        <v>20.7261180877686</v>
+        <v>20.7261161804199</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>21.2783241271973</v>
+        <v>21.2783260345459</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G585" t="n">
-        <v>21.3151378631592</v>
+        <v>21.3151359558105</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G586" t="n">
-        <v>21.7753086090088</v>
+        <v>21.7753067016602</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>21.5360164642334</v>
+        <v>21.536018371582</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>21.5360164642334</v>
+        <v>21.536018371582</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G593" t="n">
-        <v>22.2078685760498</v>
+        <v>22.2078666687012</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G596" t="n">
-        <v>22.7416667938232</v>
+        <v>22.7416706085205</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>24.5699996948242</v>
       </c>
       <c r="G598" t="n">
-        <v>22.6128196716309</v>
+        <v>22.6128215789795</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>22.7324638366699</v>
+        <v>22.7324657440186</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G603" t="n">
-        <v>22.833703994751</v>
+        <v>22.8337059020996</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G605" t="n">
-        <v>22.9073295593262</v>
+        <v>22.9073276519775</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G606" t="n">
-        <v>23.2754707336426</v>
+        <v>23.2754688262939</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G609" t="n">
-        <v>23.3090667724609</v>
+        <v>23.3090705871582</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>23.4118766784668</v>
+        <v>23.4118747711182</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>22.6174602508545</v>
+        <v>22.6174621582031</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>24.9899997711182</v>
       </c>
       <c r="G617" t="n">
-        <v>23.3557987213135</v>
+        <v>23.3558006286621</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>24.8199996948242</v>
       </c>
       <c r="G618" t="n">
-        <v>23.1969146728516</v>
+        <v>23.1969184875488</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G620" t="n">
-        <v>23.4586067199707</v>
+        <v>23.4586048126221</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>23.505334854126</v>
+        <v>23.5053367614746</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G629" t="n">
-        <v>22.9258804321289</v>
+        <v>22.9258823394775</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G634" t="n">
-        <v>19.7388763427734</v>
+        <v>19.7388744354248</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G635" t="n">
-        <v>19.56130027771</v>
+        <v>19.5612983703613</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G636" t="n">
-        <v>19.3089561462402</v>
+        <v>19.3089542388916</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>19.3463401794434</v>
+        <v>19.346342086792</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G640" t="n">
-        <v>19.0285739898682</v>
+        <v>19.0285758972168</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>18.6220188140869</v>
+        <v>18.6220226287842</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G647" t="n">
-        <v>18.6033306121826</v>
+        <v>18.603328704834</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G648" t="n">
-        <v>18.6360416412354</v>
+        <v>18.6360397338867</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G649" t="n">
-        <v>18.7949237823486</v>
+        <v>18.794921875</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>20.0900001525879</v>
       </c>
       <c r="G650" t="n">
-        <v>18.7762317657471</v>
+        <v>18.7762298583984</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G652" t="n">
-        <v>18.6220188140869</v>
+        <v>18.6220226287842</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>19.8250007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>18.5285606384277</v>
+        <v>18.5285625457764</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G659" t="n">
-        <v>18.4911766052246</v>
+        <v>18.491174697876</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G660" t="n">
-        <v>18.2435054779053</v>
+        <v>18.2435073852539</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>17.8042411804199</v>
+        <v>17.8042392730713</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G665" t="n">
-        <v>18.6734256744385</v>
+        <v>18.6734237670898</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>20.0699996948242</v>
       </c>
       <c r="G666" t="n">
-        <v>18.7575378417969</v>
+        <v>18.7575397491455</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G668" t="n">
-        <v>18.6734256744385</v>
+        <v>18.6734237670898</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G670" t="n">
-        <v>18.4911766052246</v>
+        <v>18.491174697876</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>19.5550003051758</v>
       </c>
       <c r="G671" t="n">
-        <v>18.276216506958</v>
+        <v>18.2762184143066</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>19.4850006103516</v>
       </c>
       <c r="G673" t="n">
-        <v>18.2107925415039</v>
+        <v>18.2107944488525</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>19.6650009155273</v>
       </c>
       <c r="G674" t="n">
-        <v>18.3790245056152</v>
+        <v>18.3790225982666</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>19.4398002624512</v>
+        <v>19.4398021697998</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G677" t="n">
-        <v>19.4024143218994</v>
+        <v>19.402416229248</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G679" t="n">
-        <v>19.4304580688477</v>
+        <v>19.4304542541504</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G680" t="n">
-        <v>19.3650302886963</v>
+        <v>19.3650321960449</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>20.5</v>
       </c>
       <c r="G681" t="n">
-        <v>19.1594219207764</v>
+        <v>19.1594181060791</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>19.1126880645752</v>
+        <v>19.1126899719238</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>20.5</v>
       </c>
       <c r="G686" t="n">
-        <v>19.1594219207764</v>
+        <v>19.1594181060791</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G688" t="n">
-        <v>18.8416519165039</v>
+        <v>18.8416538238525</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G689" t="n">
-        <v>19.6080284118652</v>
+        <v>19.6080303192139</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G691" t="n">
-        <v>19.5239143371582</v>
+        <v>19.5239162445068</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G692" t="n">
-        <v>19.4211101531982</v>
+        <v>19.4211082458496</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>19.8136444091797</v>
+        <v>19.8136425018311</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G694" t="n">
-        <v>20.0753326416016</v>
+        <v>20.0753307342529</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G695" t="n">
-        <v>19.748218536377</v>
+        <v>19.7482204437256</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G697" t="n">
-        <v>19.6080284118652</v>
+        <v>19.6080303192139</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>21.1700000762939</v>
       </c>
       <c r="G699" t="n">
-        <v>19.7856044769287</v>
+        <v>19.7856063842773</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G703" t="n">
-        <v>18.8977279663086</v>
+        <v>18.8977298736572</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>18.879035949707</v>
+        <v>18.8790378570557</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>18.1780853271484</v>
+        <v>18.1780834197998</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>18.6453838348389</v>
+        <v>18.6453876495361</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G711" t="n">
-        <v>17.1546878814697</v>
+        <v>17.1546897888184</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G712" t="n">
-        <v>16.9817886352539</v>
+        <v>16.9817867279053</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G716" t="n">
-        <v>18.2154693603516</v>
+        <v>18.2154655456543</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>20.5300006866455</v>
       </c>
       <c r="G718" t="n">
-        <v>19.1874580383301</v>
+        <v>19.1874599456787</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G719" t="n">
-        <v>19.0098819732666</v>
+        <v>19.0098838806152</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>20.9699993133545</v>
       </c>
       <c r="G720" t="n">
-        <v>19.5986824035645</v>
+        <v>19.5986843109131</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G721" t="n">
-        <v>19.589334487915</v>
+        <v>19.5893363952637</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G722" t="n">
-        <v>19.6454124450684</v>
+        <v>19.645414352417</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>20.9099998474121</v>
       </c>
       <c r="G724" t="n">
-        <v>19.5426082611084</v>
+        <v>19.5426044464111</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>19.4398002624512</v>
+        <v>19.4398021697998</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>19.4865322113037</v>
+        <v>19.4865303039551</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G732" t="n">
-        <v>19.4398002624512</v>
+        <v>19.4398021697998</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G735" t="n">
-        <v>19.4865322113037</v>
+        <v>19.4865303039551</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G737" t="n">
-        <v>18.7481937408447</v>
+        <v>18.7481918334961</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G738" t="n">
-        <v>18.6033306121826</v>
+        <v>18.603328704834</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>18.7855777740479</v>
+        <v>18.7855796813965</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>18.7855777740479</v>
+        <v>18.7855796813965</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>19.0659561157227</v>
+        <v>19.0659580230713</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G742" t="n">
-        <v>19.3650302886963</v>
+        <v>19.3650321960449</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>19.4865322113037</v>
+        <v>19.4865303039551</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>19.3463401794434</v>
+        <v>19.346342086792</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G749" t="n">
-        <v>19.4304580688477</v>
+        <v>19.4304542541504</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>20.5</v>
       </c>
       <c r="G750" t="n">
-        <v>19.1594219207764</v>
+        <v>19.1594181060791</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>19.2061500549316</v>
+        <v>19.206148147583</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G752" t="n">
-        <v>18.6734256744385</v>
+        <v>18.6734237670898</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G754" t="n">
-        <v>17.0472087860107</v>
+        <v>17.0472106933594</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G755" t="n">
-        <v>16.7107524871826</v>
+        <v>16.710750579834</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G756" t="n">
-        <v>16.8135585784912</v>
+        <v>16.8135566711426</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>17.7450008392334</v>
       </c>
       <c r="G757" t="n">
-        <v>16.5845813751221</v>
+        <v>16.5845794677734</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>17.6949996948242</v>
       </c>
       <c r="G759" t="n">
-        <v>16.5378475189209</v>
+        <v>16.5378494262695</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>16.495792388916</v>
+        <v>16.4957904815674</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>17.6149997711182</v>
       </c>
       <c r="G764" t="n">
-        <v>16.4630794525146</v>
+        <v>16.4630813598633</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>17.1650009155273</v>
       </c>
       <c r="G765" t="n">
-        <v>16.0425090789795</v>
+        <v>16.0425071716309</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>16.495792388916</v>
+        <v>16.4957904815674</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G770" t="n">
-        <v>16.6640205383301</v>
+        <v>16.6640224456787</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>16.495792388916</v>
+        <v>16.4957904815674</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>17.75</v>
       </c>
       <c r="G773" t="n">
-        <v>16.5892543792725</v>
+        <v>16.5892524719238</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G774" t="n">
-        <v>16.6827125549316</v>
+        <v>16.6827144622803</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G775" t="n">
-        <v>16.5985984802246</v>
+        <v>16.5986003875732</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G776" t="n">
-        <v>16.8135585784912</v>
+        <v>16.8135566711426</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>17.2549991607666</v>
       </c>
       <c r="G778" t="n">
-        <v>16.1266231536865</v>
+        <v>16.1266212463379</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>17.2549991607666</v>
       </c>
       <c r="G780" t="n">
-        <v>16.1266231536865</v>
+        <v>16.1266212463379</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>16.4490623474121</v>
+        <v>16.4490642547607</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>17.6149997711182</v>
       </c>
       <c r="G784" t="n">
-        <v>16.4630794525146</v>
+        <v>16.4630813598633</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G787" t="n">
-        <v>16.495792388916</v>
+        <v>16.4957904815674</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>17.75</v>
       </c>
       <c r="G789" t="n">
-        <v>16.5892543792725</v>
+        <v>16.5892524719238</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G790" t="n">
-        <v>16.4023303985596</v>
+        <v>16.4023323059082</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G791" t="n">
-        <v>16.2995262145996</v>
+        <v>16.299524307251</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G792" t="n">
-        <v>16.5799083709717</v>
+        <v>16.579906463623</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>18.4249992370605</v>
       </c>
       <c r="G796" t="n">
-        <v>17.2201099395752</v>
+        <v>17.2201118469238</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>18.8050003051758</v>
       </c>
       <c r="G797" t="n">
-        <v>17.5752620697021</v>
+        <v>17.5752601623535</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G799" t="n">
-        <v>17.4163799285889</v>
+        <v>17.4163780212402</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G800" t="n">
-        <v>17.1079597473145</v>
+        <v>17.1079616546631</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>18.4349994659424</v>
       </c>
       <c r="G802" t="n">
-        <v>17.229455947876</v>
+        <v>17.2294578552246</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>18.6749992370605</v>
       </c>
       <c r="G805" t="n">
-        <v>17.4537620544434</v>
+        <v>17.453763961792</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G807" t="n">
-        <v>17.6547012329102</v>
+        <v>17.6547050476074</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G809" t="n">
-        <v>17.4163799285889</v>
+        <v>17.4163780212402</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>18.3449993133545</v>
       </c>
       <c r="G810" t="n">
-        <v>17.1453437805176</v>
+        <v>17.1453418731689</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G812" t="n">
-        <v>17.1687088012695</v>
+        <v>17.1687107086182</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>19.25</v>
       </c>
       <c r="G814" t="n">
-        <v>17.9911632537842</v>
+        <v>17.9911613464355</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>18.0378913879395</v>
+        <v>18.0378932952881</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G817" t="n">
-        <v>17.6593780517578</v>
+        <v>17.6593761444092</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G819" t="n">
-        <v>17.6360130310059</v>
+        <v>17.6360111236572</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G820" t="n">
-        <v>17.6360130310059</v>
+        <v>17.6360111236572</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G824" t="n">
-        <v>17.6360130310059</v>
+        <v>17.6360111236572</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>19.5949993133545</v>
       </c>
       <c r="G827" t="n">
-        <v>18.3136024475098</v>
+        <v>18.3135986328125</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G828" t="n">
-        <v>18.2154693603516</v>
+        <v>18.2154655456543</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G829" t="n">
-        <v>18.056583404541</v>
+        <v>18.0565814971924</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>19.5949993133545</v>
       </c>
       <c r="G830" t="n">
-        <v>18.3136024475098</v>
+        <v>18.3135986328125</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>19.5650005340576</v>
       </c>
       <c r="G831" t="n">
-        <v>18.2855606079102</v>
+        <v>18.2855625152588</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>19.2250003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>17.9677982330322</v>
+        <v>17.9677963256836</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>18.5051956176758</v>
+        <v>18.5051937103271</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>19.625</v>
       </c>
       <c r="G837" t="n">
-        <v>18.3416404724121</v>
+        <v>18.3416385650635</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>19.5550003051758</v>
       </c>
       <c r="G838" t="n">
-        <v>18.276216506958</v>
+        <v>18.2762184143066</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G840" t="n">
-        <v>18.4397735595703</v>
+        <v>18.4397716522217</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>19.8250007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>18.5285606384277</v>
+        <v>18.5285625457764</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>19.8449993133545</v>
       </c>
       <c r="G842" t="n">
-        <v>18.5472526550293</v>
+        <v>18.5472507476807</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>18.5051956176758</v>
+        <v>18.5051937103271</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G845" t="n">
-        <v>18.3089275360107</v>
+        <v>18.3089294433594</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G848" t="n">
-        <v>18.5893077850342</v>
+        <v>18.5893096923828</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>19.2849998474121</v>
       </c>
       <c r="G849" t="n">
-        <v>18.0238723754883</v>
+        <v>18.0238742828369</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G850" t="n">
-        <v>17.8603172302246</v>
+        <v>17.8603191375732</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>18.06125831604</v>
+        <v>18.0612564086914</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G852" t="n">
-        <v>17.5986270904541</v>
+        <v>17.5986289978027</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>21.25</v>
       </c>
       <c r="G856" t="n">
-        <v>19.860372543335</v>
+        <v>19.8603744506836</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>19.9071044921875</v>
+        <v>19.9071025848389</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G860" t="n">
-        <v>19.9735889434814</v>
+        <v>19.9735870361328</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>20.25</v>
       </c>
       <c r="G865" t="n">
-        <v>19.2327709197998</v>
+        <v>19.2327690124512</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>19.9549999237061</v>
       </c>
       <c r="G866" t="n">
-        <v>18.9525890350342</v>
+        <v>18.9525871276855</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>19.4150009155273</v>
       </c>
       <c r="G867" t="n">
-        <v>18.4397144317627</v>
+        <v>18.4397163391113</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>18.6650009155273</v>
       </c>
       <c r="G869" t="n">
-        <v>17.7273902893066</v>
+        <v>17.7273921966553</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>18.7749996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>17.8318634033203</v>
+        <v>17.8318614959717</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>19.3449993133545</v>
       </c>
       <c r="G871" t="n">
-        <v>18.3732318878174</v>
+        <v>18.3732299804688</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G873" t="n">
-        <v>19.1757831573486</v>
+        <v>19.1757850646973</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G875" t="n">
-        <v>19.2802581787109</v>
+        <v>19.2802562713623</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>20.2299995422363</v>
       </c>
       <c r="G876" t="n">
-        <v>19.2137718200684</v>
+        <v>19.213773727417</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>19.9850006103516</v>
       </c>
       <c r="G877" t="n">
-        <v>18.9810810089111</v>
+        <v>18.9810791015625</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G878" t="n">
-        <v>18.905101776123</v>
+        <v>18.9050998687744</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G879" t="n">
-        <v>19.0333194732666</v>
+        <v>19.033317565918</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G880" t="n">
-        <v>19.6601638793945</v>
+        <v>19.6601657867432</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G885" t="n">
-        <v>19.7171478271484</v>
+        <v>19.7171497344971</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G887" t="n">
-        <v>19.7456455230713</v>
+        <v>19.745641708374</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>20.1350479125977</v>
+        <v>20.135046005249</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G890" t="n">
-        <v>20.1920318603516</v>
+        <v>20.1920337677002</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>20.4674644470215</v>
+        <v>20.4674663543701</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>21.5699996948242</v>
       </c>
       <c r="G892" t="n">
-        <v>20.4864597320557</v>
+        <v>20.4864616394043</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G893" t="n">
-        <v>20.2870121002197</v>
+        <v>20.2870101928711</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G895" t="n">
-        <v>19.8406181335449</v>
+        <v>19.8406200408936</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>21.0100002288818</v>
       </c>
       <c r="G898" t="n">
-        <v>19.95458984375</v>
+        <v>19.9545917510986</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G900" t="n">
-        <v>19.9071006774902</v>
+        <v>19.9071025848389</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>21.0900001525879</v>
       </c>
       <c r="G902" t="n">
-        <v>20.0305728912354</v>
+        <v>20.030574798584</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G903" t="n">
-        <v>19.8691120147705</v>
+        <v>19.8691139221191</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G904" t="n">
-        <v>19.9735889434814</v>
+        <v>19.9735870361328</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G905" t="n">
-        <v>19.8691120147705</v>
+        <v>19.8691139221191</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G912" t="n">
-        <v>17.9315891265869</v>
+        <v>17.9315872192383</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>18.5049991607666</v>
       </c>
       <c r="G913" t="n">
-        <v>17.5754241943359</v>
+        <v>17.5754261016846</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G915" t="n">
-        <v>17.276252746582</v>
+        <v>17.2762489318848</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G916" t="n">
-        <v>17.2667541503906</v>
+        <v>17.266752243042</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>17.9150009155273</v>
       </c>
       <c r="G920" t="n">
-        <v>17.015064239502</v>
+        <v>17.0150680541992</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>17.4750003814697</v>
       </c>
       <c r="G921" t="n">
-        <v>16.5971698760986</v>
+        <v>16.59716796875</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G926" t="n">
-        <v>16.9153385162354</v>
+        <v>16.915340423584</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G928" t="n">
-        <v>16.7348861694336</v>
+        <v>16.734884262085</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G929" t="n">
-        <v>16.9485816955566</v>
+        <v>16.948579788208</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G932" t="n">
-        <v>16.497444152832</v>
+        <v>16.4974422454834</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G933" t="n">
-        <v>16.6683979034424</v>
+        <v>16.668399810791</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G934" t="n">
-        <v>16.630407333374</v>
+        <v>16.6304092407227</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G936" t="n">
-        <v>17.4329605102539</v>
+        <v>17.4329624176025</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G946" t="n">
-        <v>16.696891784668</v>
+        <v>16.6968936920166</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G947" t="n">
-        <v>16.7538776397705</v>
+        <v>16.7538795471191</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G956" t="n">
-        <v>15.538179397583</v>
+        <v>15.5381784439087</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>16.3850002288818</v>
       </c>
       <c r="G957" t="n">
-        <v>15.5619211196899</v>
+        <v>15.5619220733643</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>16.4150009155273</v>
       </c>
       <c r="G962" t="n">
-        <v>15.5904169082642</v>
+        <v>15.5904159545898</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G965" t="n">
-        <v>15.4052104949951</v>
+        <v>15.4052095413208</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>16.1350002288818</v>
       </c>
       <c r="G966" t="n">
-        <v>15.324481010437</v>
+        <v>15.3244800567627</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>16.0650005340576</v>
       </c>
       <c r="G968" t="n">
-        <v>15.2579965591431</v>
+        <v>15.2579975128174</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>15.7661228179932</v>
+        <v>15.7661218643188</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>16.75</v>
       </c>
       <c r="G976" t="n">
-        <v>15.9085865020752</v>
+        <v>15.9085874557495</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G985" t="n">
-        <v>17.276252746582</v>
+        <v>17.2762489318848</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G987" t="n">
-        <v>16.9723281860352</v>
+        <v>16.9723262786865</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G988" t="n">
-        <v>16.4404544830322</v>
+        <v>16.4404563903809</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>17.5</v>
       </c>
       <c r="G993" t="n">
-        <v>16.6209125518799</v>
+        <v>16.6209106445312</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>18.0949993133545</v>
       </c>
       <c r="G997" t="n">
-        <v>17.1860237121582</v>
+        <v>17.1860218048096</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G998" t="n">
-        <v>16.6873950958252</v>
+        <v>16.6873970031738</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G999" t="n">
-        <v>16.696891784668</v>
+        <v>16.6968936920166</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1000" t="n">
-        <v>16.7348861694336</v>
+        <v>16.734884262085</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1001" t="n">
-        <v>17.9695816040039</v>
+        <v>17.9695796966553</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>19.0699996948242</v>
       </c>
       <c r="G1002" t="n">
-        <v>18.1120433807373</v>
+        <v>18.1120452880859</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>18.2549991607666</v>
       </c>
       <c r="G1006" t="n">
-        <v>17.3379859924316</v>
+        <v>17.337984085083</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G1007" t="n">
-        <v>17.409215927124</v>
+        <v>17.4092178344727</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>19.0750007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>18.1167945861816</v>
+        <v>18.1167964935303</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>18.9549999237061</v>
       </c>
       <c r="G1016" t="n">
-        <v>18.0028209686279</v>
+        <v>18.0028228759766</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>18.6149997711182</v>
       </c>
       <c r="G1019" t="n">
-        <v>17.6799011230469</v>
+        <v>17.6799030303955</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1022" t="n">
-        <v>18.0930500030518</v>
+        <v>18.0930480957031</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.9030952453613</v>
+        <v>17.90309715271</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>18.2549991607666</v>
       </c>
       <c r="G1026" t="n">
-        <v>17.3379859924316</v>
+        <v>17.337984085083</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.2287616729736</v>
+        <v>17.228759765625</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>18</v>
       </c>
       <c r="G1029" t="n">
-        <v>17.0957946777344</v>
+        <v>17.095796585083</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1032" t="n">
-        <v>16.5924167633057</v>
+        <v>16.5924186706543</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>15.8610982894897</v>
+        <v>15.8611001968384</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G1034" t="n">
-        <v>16.2694988250732</v>
+        <v>16.2694969177246</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1037" t="n">
-        <v>15.8468523025513</v>
+        <v>15.8468494415283</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>17.1849994659424</v>
       </c>
       <c r="G1039" t="n">
-        <v>16.3217334747314</v>
+        <v>16.3217353820801</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>16.6149997711182</v>
       </c>
       <c r="G1042" t="n">
-        <v>15.780366897583</v>
+        <v>15.7803688049316</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>15.7186336517334</v>
+        <v>15.7186317443848</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1045" t="n">
-        <v>15.9845676422119</v>
+        <v>15.9845685958862</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1048" t="n">
-        <v>15.8610982894897</v>
+        <v>15.8611001968384</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1049" t="n">
-        <v>15.7043876647949</v>
+        <v>15.7043867111206</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>16.7250003814697</v>
       </c>
       <c r="G1050" t="n">
-        <v>15.8848447799683</v>
+        <v>15.8848438262939</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1053" t="n">
-        <v>13.8096027374268</v>
+        <v>13.8096036911011</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1054" t="n">
-        <v>13.8665885925293</v>
+        <v>13.8665895462036</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>14.3249998092651</v>
       </c>
       <c r="G1056" t="n">
-        <v>13.6054029464722</v>
+        <v>13.6054039001465</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G1057" t="n">
-        <v>13.5721616744995</v>
+        <v>13.5721607208252</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>13.7650003433228</v>
       </c>
       <c r="G1058" t="n">
-        <v>13.0735349655151</v>
+        <v>13.0735340118408</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G1059" t="n">
-        <v>13.0497903823853</v>
+        <v>13.0497894287109</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1060" t="n">
-        <v>12.9738082885742</v>
+        <v>12.9738092422485</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>11.875</v>
       </c>
       <c r="G1063" t="n">
-        <v>11.2784767150879</v>
+        <v>11.2784757614136</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1064" t="n">
-        <v>10.656379699707</v>
+        <v>10.6563787460327</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>11.3549995422363</v>
       </c>
       <c r="G1065" t="n">
-        <v>10.7845964431763</v>
+        <v>10.7845973968506</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>10.164999961853</v>
       </c>
       <c r="G1067" t="n">
-        <v>9.65437507629395</v>
+        <v>9.65437412261963</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1073" t="n">
-        <v>12.1665086746216</v>
+        <v>12.1665077209473</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1074" t="n">
-        <v>13.0877799987793</v>
+        <v>13.0877809524536</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>11.75</v>
       </c>
       <c r="G1081" t="n">
-        <v>11.1597557067871</v>
+        <v>11.1597547531128</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1082" t="n">
-        <v>11.1882476806641</v>
+        <v>11.1882467269897</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1085" t="n">
-        <v>11.6251411437988</v>
+        <v>11.6251401901245</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>11.5396614074707</v>
+        <v>11.5396604537964</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>10.399941444397</v>
+        <v>10.3999423980713</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1097" t="n">
-        <v>10.7323598861694</v>
+        <v>10.7323608398438</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G1098" t="n">
-        <v>10.9128160476685</v>
+        <v>10.9128150939941</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G1103" t="n">
-        <v>10.3429555892944</v>
+        <v>10.3429574966431</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1104" t="n">
-        <v>10.4094400405884</v>
+        <v>10.4094390869141</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1105" t="n">
-        <v>10.2574777603149</v>
+        <v>10.2574768066406</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1106" t="n">
-        <v>10.2574777603149</v>
+        <v>10.2574768066406</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1107" t="n">
-        <v>10.2574777603149</v>
+        <v>10.2574768066406</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1110" t="n">
-        <v>10.4094400405884</v>
+        <v>10.4094390869141</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1111" t="n">
-        <v>10.399941444397</v>
+        <v>10.3999423980713</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1113" t="n">
-        <v>9.89656543731689</v>
+        <v>9.89656639099121</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1115" t="n">
-        <v>9.78259372711182</v>
+        <v>9.78259468078613</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>13</v>
       </c>
       <c r="G1118" t="n">
-        <v>12.3469619750977</v>
+        <v>12.3469638824463</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1129" t="n">
-        <v>11.7771034240723</v>
+        <v>11.7771024703979</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1132" t="n">
-        <v>12.2899761199951</v>
+        <v>12.2899770736694</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1133" t="n">
-        <v>12.3089723587036</v>
+        <v>12.3089714050293</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1135" t="n">
-        <v>12.5749063491821</v>
+        <v>12.5749073028564</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>13.25</v>
       </c>
       <c r="G1136" t="n">
-        <v>12.5844039916992</v>
+        <v>12.5844049453735</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1139" t="n">
-        <v>11.5111694335938</v>
+        <v>11.5111684799194</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1140" t="n">
-        <v>11.7296142578125</v>
+        <v>11.7296152114868</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G1142" t="n">
-        <v>11.5206661224365</v>
+        <v>11.5206670761108</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1143" t="n">
-        <v>11.7581081390381</v>
+        <v>11.7581071853638</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1147" t="n">
-        <v>11.3402099609375</v>
+        <v>11.3402109146118</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>11.75</v>
       </c>
       <c r="G1148" t="n">
-        <v>11.1597557067871</v>
+        <v>11.1597547531128</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.9887971878052</v>
+        <v>10.9887962341309</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1151" t="n">
-        <v>10.9887971878052</v>
+        <v>10.9887962341309</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1152" t="n">
-        <v>11.1882476806641</v>
+        <v>11.1882467269897</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1153" t="n">
-        <v>11.2262372970581</v>
+        <v>11.2262382507324</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1154" t="n">
-        <v>11.2262372970581</v>
+        <v>11.2262382507324</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.2452344894409</v>
+        <v>11.2452335357666</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G1159" t="n">
-        <v>11.0267877578735</v>
+        <v>11.0267868041992</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1161" t="n">
-        <v>10.8368339538574</v>
+        <v>10.8368349075317</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G1162" t="n">
-        <v>11.0552806854248</v>
+        <v>11.0552816390991</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1163" t="n">
-        <v>11.2167415618896</v>
+        <v>11.2167406082153</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G1166" t="n">
-        <v>10.5708990097046</v>
+        <v>10.5708999633789</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1167" t="n">
-        <v>10.8368339538574</v>
+        <v>10.8368349075317</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>11.75</v>
       </c>
       <c r="G1171" t="n">
-        <v>11.1597557067871</v>
+        <v>11.1597547531128</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1172" t="n">
-        <v>11.6251411437988</v>
+        <v>11.6251401901245</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1173" t="n">
-        <v>11.644136428833</v>
+        <v>11.6441354751587</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1177" t="n">
-        <v>10.9603033065796</v>
+        <v>10.9603042602539</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G1178" t="n">
-        <v>10.760853767395</v>
+        <v>10.7608528137207</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1179" t="n">
-        <v>10.656379699707</v>
+        <v>10.6563787460327</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>10.7798490524292</v>
+        <v>10.7798480987549</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1181" t="n">
-        <v>10.6753740310669</v>
+        <v>10.6753749847412</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G1182" t="n">
-        <v>11.6156415939331</v>
+        <v>11.6156425476074</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1183" t="n">
-        <v>11.6251411437988</v>
+        <v>11.6251401901245</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1184" t="n">
-        <v>11.6251411437988</v>
+        <v>11.6251401901245</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1185" t="n">
-        <v>11.4636793136597</v>
+        <v>11.463680267334</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>12</v>
       </c>
       <c r="G1186" t="n">
-        <v>11.3971977233887</v>
+        <v>11.3971967697144</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1188" t="n">
-        <v>11.7960987091064</v>
+        <v>11.7960996627808</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G1191" t="n">
-        <v>11.4256896972656</v>
+        <v>11.4256887435913</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G1195" t="n">
-        <v>11.4256896972656</v>
+        <v>11.4256887435913</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1199" t="n">
-        <v>12.0810279846191</v>
+        <v>12.0810289382935</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1203" t="n">
-        <v>11.4636793136597</v>
+        <v>11.463680267334</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1204" t="n">
-        <v>11.6061449050903</v>
+        <v>11.6061458587646</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>12.0145444869995</v>
+        <v>12.0145454406738</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G1207" t="n">
-        <v>11.9385623931885</v>
+        <v>11.9385633468628</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1212" t="n">
-        <v>12.2804803848267</v>
+        <v>12.2804794311523</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>13.25</v>
       </c>
       <c r="G1215" t="n">
-        <v>12.5844039916992</v>
+        <v>12.5844049453735</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G1217" t="n">
-        <v>12.5464143753052</v>
+        <v>12.5464134216309</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>12.2044982910156</v>
+        <v>12.2044973373413</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>12.0145444869995</v>
+        <v>12.0145454406738</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1222" t="n">
-        <v>12.8978281021118</v>
+        <v>12.8978271484375</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1224" t="n">
-        <v>11.8910760879517</v>
+        <v>11.8910751342773</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G1229" t="n">
-        <v>10.5139131546021</v>
+        <v>10.5139141082764</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G1230" t="n">
-        <v>10.7988443374634</v>
+        <v>10.7988433837891</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G1231" t="n">
-        <v>11.0552806854248</v>
+        <v>11.0552816390991</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1234" t="n">
-        <v>11.3592052459717</v>
+        <v>11.359206199646</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G1236" t="n">
-        <v>12.7933530807495</v>
+        <v>12.7933540344238</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1238" t="n">
-        <v>12.8978281021118</v>
+        <v>12.8978271484375</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1239" t="n">
-        <v>13.7811107635498</v>
+        <v>13.7811098098755</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1240" t="n">
-        <v>13.7146253585815</v>
+        <v>13.7146263122559</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1241" t="n">
-        <v>13.9235744476318</v>
+        <v>13.9235754013062</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G1242" t="n">
-        <v>13.9330730438232</v>
+        <v>13.9330739974976</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1244" t="n">
-        <v>14.3414726257324</v>
+        <v>14.3414716720581</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>15</v>
       </c>
       <c r="G1250" t="n">
-        <v>14.2464952468872</v>
+        <v>14.2464962005615</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1251" t="n">
-        <v>14.4269504547119</v>
+        <v>14.4269514083862</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1253" t="n">
-        <v>14.9113321304321</v>
+        <v>14.9113311767578</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1254" t="n">
-        <v>14.4269504547119</v>
+        <v>14.4269514083862</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>15</v>
       </c>
       <c r="G1256" t="n">
-        <v>14.2464952468872</v>
+        <v>14.2464962005615</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1257" t="n">
-        <v>14.4934349060059</v>
+        <v>14.4934358596802</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G1259" t="n">
-        <v>14.5979089736938</v>
+        <v>14.5979099273682</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1262" t="n">
-        <v>14.8828401565552</v>
+        <v>14.8828392028809</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1265" t="n">
-        <v>14.3794631958008</v>
+        <v>14.3794641494751</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1266" t="n">
-        <v>14.5694169998169</v>
+        <v>14.5694160461426</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G1269" t="n">
-        <v>15.110782623291</v>
+        <v>15.1107835769653</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1272" t="n">
-        <v>14.7688684463501</v>
+        <v>14.7688674926758</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1273" t="n">
-        <v>14.7118806838989</v>
+        <v>14.7118816375732</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1274" t="n">
-        <v>14.5694169998169</v>
+        <v>14.5694160461426</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1276" t="n">
-        <v>14.5789136886597</v>
+        <v>14.578914642334</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1279" t="n">
-        <v>14.5314264297485</v>
+        <v>14.5314254760742</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1280" t="n">
-        <v>13.9615650177002</v>
+        <v>13.9615659713745</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1282" t="n">
-        <v>14.3794631958008</v>
+        <v>14.3794641494751</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G1283" t="n">
-        <v>14.4459466934204</v>
+        <v>14.4459457397461</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1286" t="n">
-        <v>14.683388710022</v>
+        <v>14.6833877563477</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1288" t="n">
-        <v>15.8041114807129</v>
+        <v>15.8041124343872</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>16.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>15.6711454391479</v>
+        <v>15.6711444854736</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1292" t="n">
-        <v>15.0442991256714</v>
+        <v>15.0443000793457</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1294" t="n">
-        <v>14.7688684463501</v>
+        <v>14.7688674926758</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1298" t="n">
-        <v>14.5789136886597</v>
+        <v>14.578914642334</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1302" t="n">
-        <v>15.0822896957397</v>
+        <v>15.0822906494141</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G1304" t="n">
-        <v>14.6928853988647</v>
+        <v>14.6928863525391</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1305" t="n">
-        <v>14.7783651351929</v>
+        <v>14.7783641815186</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1307" t="n">
-        <v>14.7688684463501</v>
+        <v>14.7688674926758</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1316" t="n">
-        <v>14.9873123168945</v>
+        <v>14.9873132705688</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1318" t="n">
-        <v>15.8705940246582</v>
+        <v>15.8705949783325</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1321" t="n">
-        <v>15.8231077194214</v>
+        <v>15.8231086730957</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1322" t="n">
-        <v>15.9370794296265</v>
+        <v>15.9370803833008</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>15.7376298904419</v>
+        <v>15.7376270294189</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1327" t="n">
-        <v>15.7091379165649</v>
+        <v>15.7091360092163</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1330" t="n">
-        <v>15.3672199249268</v>
+        <v>15.3672208786011</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1331" t="n">
-        <v>15.3387269973755</v>
+        <v>15.3387260437012</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1332" t="n">
-        <v>15.6996374130249</v>
+        <v>15.6996402740479</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1333" t="n">
-        <v>15.538179397583</v>
+        <v>15.5381784439087</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>16.5149993896484</v>
       </c>
       <c r="G1334" t="n">
-        <v>15.6853914260864</v>
+        <v>15.6853904724121</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>16.4449996948242</v>
       </c>
       <c r="G1336" t="n">
-        <v>15.6189079284668</v>
+        <v>15.6189069747925</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1339" t="n">
-        <v>15.8468523025513</v>
+        <v>15.8468494415283</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1341" t="n">
-        <v>16.696891784668</v>
+        <v>16.6968936920166</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1343" t="n">
-        <v>16.8678493499756</v>
+        <v>16.8678512573242</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>17.7649993896484</v>
       </c>
       <c r="G1344" t="n">
-        <v>16.8726005554199</v>
+        <v>16.8725986480713</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1345" t="n">
-        <v>16.4784469604492</v>
+        <v>16.4784488677979</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1347" t="n">
-        <v>17.5136947631836</v>
+        <v>17.513692855835</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G1348" t="n">
-        <v>17.4567070007324</v>
+        <v>17.4567050933838</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1350" t="n">
-        <v>17.0388107299805</v>
+        <v>17.0388088226318</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>18.2049999237061</v>
       </c>
       <c r="G1351" t="n">
-        <v>17.2904968261719</v>
+        <v>17.2904987335205</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>17.9850006103516</v>
       </c>
       <c r="G1352" t="n">
-        <v>17.0815467834473</v>
+        <v>17.0815486907959</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1354" t="n">
-        <v>17.0245609283447</v>
+        <v>17.0245628356934</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>18.3850002288818</v>
       </c>
       <c r="G1358" t="n">
-        <v>17.4614543914795</v>
+        <v>17.4614562988281</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1360" t="n">
-        <v>17.4187145233154</v>
+        <v>17.4187164306641</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>19.1949996948242</v>
       </c>
       <c r="G1365" t="n">
-        <v>18.2307643890381</v>
+        <v>18.2307662963867</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1366" t="n">
-        <v>17.9315891265869</v>
+        <v>17.9315872192383</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1373" t="n">
-        <v>18.3304901123047</v>
+        <v>18.3304920196533</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1374" t="n">
-        <v>18.3304901123047</v>
+        <v>18.3304920196533</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G1375" t="n">
-        <v>18.3209953308105</v>
+        <v>18.3209934234619</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G1379" t="n">
-        <v>18.3969764709473</v>
+        <v>18.3969745635986</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G1381" t="n">
-        <v>18.3969764709473</v>
+        <v>18.3969745635986</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G1384" t="n">
-        <v>18.3209953308105</v>
+        <v>18.3209934234619</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1389" t="n">
-        <v>18.4444618225098</v>
+        <v>18.444465637207</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1392" t="n">
-        <v>18.5584354400635</v>
+        <v>18.5584373474121</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>19.3050003051758</v>
       </c>
       <c r="G1393" t="n">
-        <v>18.3352394104004</v>
+        <v>18.335241317749</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1398" t="n">
-        <v>17.2287616729736</v>
+        <v>17.228759765625</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G1399" t="n">
-        <v>17.1812725067139</v>
+        <v>17.1812744140625</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G1402" t="n">
-        <v>16.6114139556885</v>
+        <v>16.6114120483398</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1404" t="n">
-        <v>16.696891784668</v>
+        <v>16.6968936920166</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G1405" t="n">
-        <v>16.7253875732422</v>
+        <v>16.7253856658936</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1406" t="n">
-        <v>16.877347946167</v>
+        <v>16.8773498535156</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>16.4449996948242</v>
       </c>
       <c r="G1409" t="n">
-        <v>15.6189079284668</v>
+        <v>15.6189069747925</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>16.8250007629395</v>
       </c>
       <c r="G1410" t="n">
-        <v>15.9798202514648</v>
+        <v>15.9798192977905</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>16.098539352417</v>
+        <v>16.0985412597656</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>16.8549995422363</v>
       </c>
       <c r="G1412" t="n">
-        <v>16.0083103179932</v>
+        <v>16.0083122253418</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G1413" t="n">
-        <v>16.2505035400391</v>
+        <v>16.2505054473877</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G1417" t="n">
-        <v>16.0368041992188</v>
+        <v>16.0368061065674</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>16.8449993133545</v>
       </c>
       <c r="G1418" t="n">
-        <v>15.9988145828247</v>
+        <v>15.9988136291504</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>16.9150009155273</v>
       </c>
       <c r="G1422" t="n">
-        <v>16.065299987793</v>
+        <v>16.0652980804443</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>18.0149993896484</v>
       </c>
       <c r="G1424" t="n">
-        <v>17.1100425720215</v>
+        <v>17.1100406646729</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>18.3150005340576</v>
       </c>
       <c r="G1425" t="n">
-        <v>17.3949718475342</v>
+        <v>17.3949699401855</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>17.0008182525635</v>
+        <v>17.0008163452148</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>16.5650005340576</v>
       </c>
       <c r="G1432" t="n">
-        <v>15.7328805923462</v>
+        <v>15.7328796386719</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>16.5750007629395</v>
       </c>
       <c r="G1433" t="n">
-        <v>15.7423782348633</v>
+        <v>15.7423791885376</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1436" t="n">
-        <v>15.8041114807129</v>
+        <v>15.8041124343872</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>16.8150005340576</v>
       </c>
       <c r="G1437" t="n">
-        <v>15.9703216552734</v>
+        <v>15.9703226089478</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>17.1849994659424</v>
       </c>
       <c r="G1438" t="n">
-        <v>16.3217334747314</v>
+        <v>16.3217353820801</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G1442" t="n">
-        <v>16.6873950958252</v>
+        <v>16.6873970031738</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>17.1849994659424</v>
       </c>
       <c r="G1443" t="n">
-        <v>16.3217334747314</v>
+        <v>16.3217353820801</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>18.8150005340576</v>
       </c>
       <c r="G1447" t="n">
-        <v>17.8698558807373</v>
+        <v>17.8698539733887</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1452" t="n">
-        <v>16.696891784668</v>
+        <v>16.6968936920166</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1458" t="n">
-        <v>17.0245609283447</v>
+        <v>17.0245628356934</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1459" t="n">
-        <v>16.9438304901123</v>
+        <v>16.9438323974609</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>17.9850006103516</v>
       </c>
       <c r="G1463" t="n">
-        <v>17.0815467834473</v>
+        <v>17.0815486907959</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>17.7250003814697</v>
       </c>
       <c r="G1464" t="n">
-        <v>16.8346118927002</v>
+        <v>16.8346099853516</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1465" t="n">
-        <v>17.0245609283447</v>
+        <v>17.0245628356934</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>17.9449996948242</v>
       </c>
       <c r="G1467" t="n">
-        <v>17.0435562133789</v>
+        <v>17.0435581207275</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>17.5949993133545</v>
       </c>
       <c r="G1469" t="n">
-        <v>16.7111396789551</v>
+        <v>16.7111377716064</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>17.0008182525635</v>
+        <v>17.0008163452148</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1473" t="n">
-        <v>17.2287616729736</v>
+        <v>17.228759765625</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1474" t="n">
-        <v>16.9438304901123</v>
+        <v>16.9438323974609</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1475" t="n">
-        <v>17.0388107299805</v>
+        <v>17.0388088226318</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>18</v>
       </c>
       <c r="G1476" t="n">
-        <v>17.0957946777344</v>
+        <v>17.095796585083</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G1477" t="n">
-        <v>17.4329605102539</v>
+        <v>17.4329624176025</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G1481" t="n">
-        <v>17.1812725067139</v>
+        <v>17.1812744140625</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G1482" t="n">
-        <v>17.3427333831787</v>
+        <v>17.3427352905273</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>18.6550006866455</v>
       </c>
       <c r="G1484" t="n">
-        <v>17.7178936004639</v>
+        <v>17.7178916931152</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G1493" t="n">
-        <v>18.4302177429199</v>
+        <v>18.4302158355713</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>19.5349998474121</v>
       </c>
       <c r="G1494" t="n">
-        <v>18.5536861419678</v>
+        <v>18.5536880493164</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>19.7549991607666</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.7626342773438</v>
+        <v>18.7626323699951</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1496" t="n">
-        <v>19.0903053283691</v>
+        <v>19.0903034210205</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1497" t="n">
-        <v>19.3752326965332</v>
+        <v>19.3752346038818</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1503" t="n">
-        <v>19.2802581787109</v>
+        <v>19.2802562713623</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1505" t="n">
-        <v>19.1377906799316</v>
+        <v>19.1377925872803</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G1506" t="n">
-        <v>19.6316719055176</v>
+        <v>19.6316699981689</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G1508" t="n">
-        <v>19.8691120147705</v>
+        <v>19.8691139221191</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G1509" t="n">
-        <v>19.7456455230713</v>
+        <v>19.745641708374</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1510" t="n">
-        <v>20.4579677581787</v>
+        <v>20.4579696655273</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G1519" t="n">
-        <v>20.7903861999512</v>
+        <v>20.7903842926025</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G1520" t="n">
-        <v>20.7144031524658</v>
+        <v>20.7144050598145</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G1521" t="n">
-        <v>21.0278263092041</v>
+        <v>21.0278282165527</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G1524" t="n">
-        <v>21.094310760498</v>
+        <v>21.0943088531494</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1525" t="n">
-        <v>21.4172306060791</v>
+        <v>21.4172325134277</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G1526" t="n">
-        <v>21.3982372283936</v>
+        <v>21.3982391357422</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G1528" t="n">
-        <v>21.5691928863525</v>
+        <v>21.5691947937012</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G1530" t="n">
-        <v>21.5976886749268</v>
+        <v>21.5976867675781</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G1531" t="n">
-        <v>21.6261806488037</v>
+        <v>21.6261825561523</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G1532" t="n">
-        <v>19.7171478271484</v>
+        <v>19.7171497344971</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1538" t="n">
-        <v>19.2802581787109</v>
+        <v>19.2802562713623</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1542" t="n">
-        <v>17.4946975708008</v>
+        <v>17.4946956634521</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1544" t="n">
-        <v>18.0930500030518</v>
+        <v>18.0930480957031</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>19.5750007629395</v>
       </c>
       <c r="G1548" t="n">
-        <v>18.5916786193848</v>
+        <v>18.5916767120361</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>19.0550003051758</v>
       </c>
       <c r="G1550" t="n">
-        <v>18.0977993011475</v>
+        <v>18.0977973937988</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>19.25</v>
       </c>
       <c r="G1555" t="n">
-        <v>18.2830047607422</v>
+        <v>18.2830028533936</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G1559" t="n">
-        <v>18.6819038391113</v>
+        <v>18.68190574646</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>19.7649993896484</v>
       </c>
       <c r="G1560" t="n">
-        <v>18.7721309661865</v>
+        <v>18.7721328735352</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>19.7950000762939</v>
       </c>
       <c r="G1561" t="n">
-        <v>18.8006248474121</v>
+        <v>18.8006267547607</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>18.6749992370605</v>
       </c>
       <c r="G1569" t="n">
-        <v>17.7368850708008</v>
+        <v>17.7368869781494</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G1570" t="n">
-        <v>17.12428855896</v>
+        <v>17.1242904663086</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G1571" t="n">
-        <v>15.1867647171021</v>
+        <v>15.1867637634277</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>16.2749996185303</v>
       </c>
       <c r="G1577" t="n">
-        <v>15.4574480056763</v>
+        <v>15.457447052002</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1578" t="n">
-        <v>14.8733406066895</v>
+        <v>14.8733415603638</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G1579" t="n">
-        <v>15.5856657028198</v>
+        <v>15.5856676101685</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1580" t="n">
-        <v>15.7043876647949</v>
+        <v>15.7043867111206</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1581" t="n">
-        <v>15.8610982894897</v>
+        <v>15.8611001968384</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1585" t="n">
-        <v>15.253246307373</v>
+        <v>15.2532482147217</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1586" t="n">
-        <v>15.5191831588745</v>
+        <v>15.5191822052002</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>16.6650009155273</v>
       </c>
       <c r="G1587" t="n">
-        <v>15.82785987854</v>
+        <v>15.8278579711914</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>17.6550006866455</v>
       </c>
       <c r="G1588" t="n">
-        <v>16.7681255340576</v>
+        <v>16.7681274414062</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1589" t="n">
-        <v>16.8678493499756</v>
+        <v>16.8678512573242</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1592" t="n">
-        <v>15.9750719070435</v>
+        <v>15.9750699996948</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1597" t="n">
-        <v>15.0442991256714</v>
+        <v>15.0443000793457</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1598" t="n">
-        <v>15.3387269973755</v>
+        <v>15.3387260437012</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1600" t="n">
-        <v>15.6331539154053</v>
+        <v>15.6331548690796</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1601" t="n">
-        <v>15.6521492004395</v>
+        <v>15.6521482467651</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1602" t="n">
-        <v>15.6996374130249</v>
+        <v>15.6996402740479</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1603" t="n">
-        <v>15.8895902633667</v>
+        <v>15.889591217041</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>16.3299999237061</v>
       </c>
       <c r="G1604" t="n">
-        <v>15.5096855163574</v>
+        <v>15.5096845626831</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1608" t="n">
-        <v>15.1392755508423</v>
+        <v>15.1392765045166</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1609" t="n">
-        <v>15.7851190567017</v>
+        <v>15.7851181030273</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>16.5</v>
       </c>
       <c r="G1610" t="n">
-        <v>15.6711454391479</v>
+        <v>15.6711444854736</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1615" t="n">
-        <v>13.8285980224609</v>
+        <v>13.8285989761353</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1616" t="n">
-        <v>12.8123483657837</v>
+        <v>12.812349319458</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G1620" t="n">
-        <v>15.0158071517944</v>
+        <v>15.0158061981201</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1622" t="n">
-        <v>15.3672199249268</v>
+        <v>15.3672208786011</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1623" t="n">
-        <v>14.9113321304321</v>
+        <v>14.9113311767578</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G1625" t="n">
-        <v>14.8327655792236</v>
+        <v>14.8327665328979</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1627" t="n">
-        <v>14.6870603561401</v>
+        <v>14.6870594024658</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1628" t="n">
-        <v>15.0756072998047</v>
+        <v>15.075608253479</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1632" t="n">
-        <v>15.8915557861328</v>
+        <v>15.8915548324585</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1633" t="n">
-        <v>15.9886903762817</v>
+        <v>15.9886913299561</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1635" t="n">
-        <v>15.9692640304565</v>
+        <v>15.9692649841309</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1640" t="n">
-        <v>13.7545480728149</v>
+        <v>13.7545490264893</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1643" t="n">
-        <v>13.3660020828247</v>
+        <v>13.366003036499</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1644" t="n">
-        <v>13.7254076004028</v>
+        <v>13.7254085540771</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>13.9391088485718</v>
+        <v>13.9391078948975</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1667" t="n">
-        <v>15.6972808837891</v>
+        <v>15.6972818374634</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1669" t="n">
-        <v>16.2315311431885</v>
+        <v>16.2315330505371</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1672" t="n">
-        <v>15.872127532959</v>
+        <v>15.8721265792847</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1676" t="n">
-        <v>16.4646606445312</v>
+        <v>16.4646625518799</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1685" t="n">
-        <v>17.0960502624512</v>
+        <v>17.0960483551025</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1686" t="n">
-        <v>16.9503440856934</v>
+        <v>16.950345993042</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1693" t="n">
-        <v>16.0664024353027</v>
+        <v>16.0664005279541</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>16.1100006103516</v>
       </c>
       <c r="G1695" t="n">
-        <v>15.6487140655518</v>
+        <v>15.6487131118774</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1696" t="n">
-        <v>15.6001434326172</v>
+        <v>15.6001443862915</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1704" t="n">
-        <v>15.1727437973022</v>
+        <v>15.1727428436279</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>14.75</v>
       </c>
       <c r="G1709" t="n">
-        <v>14.327654838562</v>
+        <v>14.3276538848877</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1715" t="n">
-        <v>13.540846824646</v>
+        <v>13.5408477783203</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1716" t="n">
-        <v>13.9391088485718</v>
+        <v>13.9391078948975</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1744" t="n">
-        <v>14.8230514526367</v>
+        <v>14.823052406311</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1749" t="n">
-        <v>16.2315311431885</v>
+        <v>16.2315330505371</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1752" t="n">
-        <v>15.9304094314575</v>
+        <v>15.9304103851318</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1754" t="n">
-        <v>15.9789781570435</v>
+        <v>15.9789791107178</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G1759" t="n">
-        <v>15.7652769088745</v>
+        <v>15.7652759552002</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1761" t="n">
-        <v>16.5229415893555</v>
+        <v>16.5229434967041</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1764" t="n">
-        <v>16.8434944152832</v>
+        <v>16.8434925079346</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1777" t="n">
-        <v>15.9789781570435</v>
+        <v>15.9789791107178</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1780" t="n">
-        <v>15.9789781570435</v>
+        <v>15.9789791107178</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1781" t="n">
-        <v>16.1635360717773</v>
+        <v>16.163537979126</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1798" t="n">
-        <v>17.7954330444336</v>
+        <v>17.795431137085</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1799" t="n">
-        <v>17.9119987487793</v>
+        <v>17.9119968414307</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G1800" t="n">
-        <v>18.0382747650146</v>
+        <v>18.038272857666</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G1829" t="n">
-        <v>18.0382747650146</v>
+        <v>18.038272857666</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1833" t="n">
-        <v>16.5229415893555</v>
+        <v>16.5229434967041</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1835" t="n">
-        <v>16.3189563751221</v>
+        <v>16.3189544677734</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1836" t="n">
-        <v>16.581226348877</v>
+        <v>16.5812244415283</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1845" t="n">
-        <v>16.076114654541</v>
+        <v>16.0761127471924</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1851" t="n">
-        <v>16.0664024353027</v>
+        <v>16.0664005279541</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1860" t="n">
-        <v>15.8818416595459</v>
+        <v>15.8818407058716</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1861" t="n">
-        <v>15.7361364364624</v>
+        <v>15.7361373901367</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1867" t="n">
-        <v>15.6778535842896</v>
+        <v>15.6778526306152</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1872" t="n">
-        <v>15.0756072998047</v>
+        <v>15.075608253479</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1873" t="n">
-        <v>15.085319519043</v>
+        <v>15.0853204727173</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1879" t="n">
-        <v>14.7064876556396</v>
+        <v>14.706488609314</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>7.47499990463257</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>219613</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>7.57999992370605</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>7.32000017166138</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>7.47499990463257</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>7.32999992370605</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>7.32999992370605</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>7.03000020980835</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>6.80499982833862</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>428598</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>7.04500007629395</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>6.80499982833862</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>6.85500001907349</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>6.85500001907349</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>6.96000003814697</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>202830</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>6.98000001907349</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>6.93499994277954</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>6.93499994277954</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>6.92000007629395</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>209432</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>6.85500001907349</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>6.73000001907349</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>6.85500001907349</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>6.85500001907349</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>6.82000017166138</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>209809</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>6.97499990463257</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>6.88500022888184</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>170848</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>6.82999992370605</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>6.82999992370605</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>6.84999990463257</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -421,7 +421,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G2" t="n">
-        <v>18.2763500213623</v>
+        <v>18.2763519287109</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G3" t="n">
-        <v>18.01096534729</v>
+        <v>18.0109615325928</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>17.6836528778076</v>
+        <v>17.683650970459</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G8" t="n">
-        <v>19.408670425415</v>
+        <v>19.4086723327637</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G9" t="n">
-        <v>19.1344356536865</v>
+        <v>19.1344337463379</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G10" t="n">
-        <v>18.8425121307373</v>
+        <v>18.84250831604</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G12" t="n">
-        <v>18.2851982116699</v>
+        <v>18.2851963043213</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G13" t="n">
-        <v>18.0994262695312</v>
+        <v>18.0994243621826</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G14" t="n">
-        <v>17.6394214630127</v>
+        <v>17.6394195556641</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G15" t="n">
-        <v>17.5686511993408</v>
+        <v>17.5686531066895</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G17" t="n">
-        <v>18.0994262695312</v>
+        <v>18.0994243621826</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>17.7632656097412</v>
+        <v>17.7632694244385</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G21" t="n">
-        <v>18.3913516998291</v>
+        <v>18.3913536071777</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>17.9578857421875</v>
+        <v>17.9578838348389</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G25" t="n">
-        <v>18.2586574554443</v>
+        <v>18.258659362793</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G26" t="n">
-        <v>18.0817337036133</v>
+        <v>18.0817317962646</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G27" t="n">
-        <v>17.3563404083252</v>
+        <v>17.3563442230225</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G28" t="n">
-        <v>16.9051837921143</v>
+        <v>16.9051818847656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>17.1617221832275</v>
+        <v>17.1617240905762</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G31" t="n">
-        <v>17.0201835632324</v>
+        <v>17.0201854705811</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G32" t="n">
-        <v>17.48903465271</v>
+        <v>17.4890365600586</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G33" t="n">
-        <v>17.6305751800537</v>
+        <v>17.6305732727051</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>20.8099994659424</v>
       </c>
       <c r="G35" t="n">
-        <v>18.4090461730957</v>
+        <v>18.4090442657471</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G36" t="n">
-        <v>18.4532775878906</v>
+        <v>18.453275680542</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>20.5</v>
       </c>
       <c r="G38" t="n">
-        <v>18.1348094940186</v>
+        <v>18.1348114013672</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G39" t="n">
-        <v>17.3121128082275</v>
+        <v>17.3121070861816</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G40" t="n">
-        <v>17.7632656097412</v>
+        <v>17.7632694244385</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G42" t="n">
-        <v>18.3471183776855</v>
+        <v>18.3471202850342</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G44" t="n">
-        <v>19.001745223999</v>
+        <v>19.0017471313477</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>19.7271347045898</v>
+        <v>19.7271366119385</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G50" t="n">
-        <v>19.3379001617432</v>
+        <v>19.3379020690918</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G51" t="n">
-        <v>19.647518157959</v>
+        <v>19.6475219726562</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G53" t="n">
-        <v>19.1167469024658</v>
+        <v>19.1167449951172</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G54" t="n">
-        <v>19.3379001617432</v>
+        <v>19.3379020690918</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>20.0367546081543</v>
+        <v>20.0367565155029</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>22.8099994659424</v>
       </c>
       <c r="G57" t="n">
-        <v>20.178295135498</v>
+        <v>20.1782932281494</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G58" t="n">
-        <v>19.4971332550049</v>
+        <v>19.4971351623535</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>22.0100002288818</v>
       </c>
       <c r="G59" t="n">
-        <v>19.4705924987793</v>
+        <v>19.4705963134766</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G62" t="n">
-        <v>19.9129085540771</v>
+        <v>19.9129066467285</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G63" t="n">
-        <v>19.8686771392822</v>
+        <v>19.8686752319336</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G64" t="n">
-        <v>19.4971332550049</v>
+        <v>19.4971351623535</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G65" t="n">
-        <v>19.4175186157227</v>
+        <v>19.417516708374</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G66" t="n">
-        <v>18.8690509796143</v>
+        <v>18.8690528869629</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G67" t="n">
-        <v>18.8336658477783</v>
+        <v>18.8336696624756</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G68" t="n">
-        <v>18.5151996612549</v>
+        <v>18.5152015686035</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>18.9486675262451</v>
+        <v>18.9486656188965</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>21.25</v>
       </c>
       <c r="G74" t="n">
-        <v>18.7982807159424</v>
+        <v>18.798282623291</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G76" t="n">
-        <v>19.2936706542969</v>
+        <v>19.2936687469482</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G77" t="n">
-        <v>18.8071269989014</v>
+        <v>18.8071250915527</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G78" t="n">
-        <v>18.3205833435059</v>
+        <v>18.3205814361572</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G80" t="n">
-        <v>17.8251934051514</v>
+        <v>17.8251914978027</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G81" t="n">
-        <v>18.0817337036133</v>
+        <v>18.0817317962646</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G82" t="n">
-        <v>18.0640411376953</v>
+        <v>18.0640430450439</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>18.3117370605469</v>
+        <v>18.3117389678955</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G84" t="n">
-        <v>17.8782691955566</v>
+        <v>17.878267288208</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>18.0021171569824</v>
+        <v>18.0021190643311</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G86" t="n">
-        <v>17.7190380096436</v>
+        <v>17.7190361022949</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G89" t="n">
-        <v>17.1440296173096</v>
+        <v>17.1440334320068</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G91" t="n">
-        <v>17.9844226837158</v>
+        <v>17.9844284057617</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>17.6394214630127</v>
+        <v>17.6394195556641</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G93" t="n">
-        <v>17.4182682037354</v>
+        <v>17.4182662963867</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G94" t="n">
-        <v>18.8336658477783</v>
+        <v>18.8336696624756</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>21.25</v>
       </c>
       <c r="G95" t="n">
-        <v>18.7982807159424</v>
+        <v>18.798282623291</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>18.0640411376953</v>
+        <v>18.0640430450439</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>20.2700004577637</v>
       </c>
       <c r="G97" t="n">
-        <v>17.9313449859619</v>
+        <v>17.9313488006592</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G100" t="n">
-        <v>17.593936920166</v>
+        <v>17.5939388275146</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G102" t="n">
-        <v>17.7025985717773</v>
+        <v>17.7025966644287</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G103" t="n">
-        <v>17.6482639312744</v>
+        <v>17.6482677459717</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G105" t="n">
-        <v>17.593936920166</v>
+        <v>17.5939388275146</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G107" t="n">
-        <v>17.304178237915</v>
+        <v>17.3041763305664</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G111" t="n">
-        <v>17.4852771759033</v>
+        <v>17.4852752685547</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G116" t="n">
-        <v>16.5435523986816</v>
+        <v>16.5435543060303</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G120" t="n">
-        <v>17.9380283355713</v>
+        <v>17.9380264282227</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G121" t="n">
-        <v>17.7297630310059</v>
+        <v>17.7297611236572</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G123" t="n">
-        <v>18.1825122833252</v>
+        <v>18.1825141906738</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G124" t="n">
-        <v>16.8514251708984</v>
+        <v>16.8514232635498</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G126" t="n">
-        <v>16.6793785095215</v>
+        <v>16.6793804168701</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G127" t="n">
-        <v>16.262845993042</v>
+        <v>16.2628440856934</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>16.6069393157959</v>
+        <v>16.6069374084473</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G130" t="n">
-        <v>16.8061504364014</v>
+        <v>16.8061485290527</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G131" t="n">
-        <v>16.8242607116699</v>
+        <v>16.8242568969727</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G135" t="n">
-        <v>16.4439468383789</v>
+        <v>16.4439487457275</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G136" t="n">
-        <v>16.6974906921387</v>
+        <v>16.69748878479</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>17.0325241088867</v>
+        <v>17.0325260162354</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>17.3403949737549</v>
+        <v>17.3403968811035</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G144" t="n">
-        <v>17.9018077850342</v>
+        <v>17.9018096923828</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G145" t="n">
-        <v>18.1372394561768</v>
+        <v>18.1372413635254</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>18.6352672576904</v>
+        <v>18.6352653503418</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G149" t="n">
-        <v>19.0699062347412</v>
+        <v>19.0699081420898</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G150" t="n">
-        <v>19.2147884368896</v>
+        <v>19.2147903442383</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G153" t="n">
-        <v>18.2187366485596</v>
+        <v>18.2187347412109</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G155" t="n">
-        <v>18.5809345245361</v>
+        <v>18.5809364318848</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G159" t="n">
-        <v>18.9431400299072</v>
+        <v>18.9431381225586</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G160" t="n">
-        <v>19.0427417755127</v>
+        <v>19.04274559021</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G161" t="n">
-        <v>18.6624317169189</v>
+        <v>18.6624298095703</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G162" t="n">
-        <v>18.6624317169189</v>
+        <v>18.6624298095703</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>18.4722766876221</v>
+        <v>18.4722785949707</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G164" t="n">
-        <v>18.6171569824219</v>
+        <v>18.6171550750732</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G165" t="n">
-        <v>18.7529830932617</v>
+        <v>18.7529811859131</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>18.9703025817871</v>
+        <v>18.9703044891357</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G168" t="n">
-        <v>18.6081008911133</v>
+        <v>18.6080989837646</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>18.6081008911133</v>
+        <v>18.6080989837646</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>18.6986503601074</v>
+        <v>18.6986541748047</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>21.75</v>
       </c>
       <c r="G178" t="n">
-        <v>19.6947059631348</v>
+        <v>19.6947078704834</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>19.5588836669922</v>
+        <v>19.5588798522949</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>21.4899997711182</v>
       </c>
       <c r="G180" t="n">
-        <v>19.4592781066895</v>
+        <v>19.4592761993408</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G182" t="n">
-        <v>18.8888092041016</v>
+        <v>18.8888072967529</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G184" t="n">
-        <v>19.1332950592041</v>
+        <v>19.1332931518555</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>19.1604595184326</v>
+        <v>19.160457611084</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G187" t="n">
-        <v>19.9391937255859</v>
+        <v>19.9391956329346</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>20.3557224273682</v>
+        <v>20.3557205200195</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G191" t="n">
-        <v>20.3104476928711</v>
+        <v>20.3104496002197</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>20.3919429779053</v>
+        <v>20.3919410705566</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G194" t="n">
-        <v>20.3557224273682</v>
+        <v>20.3557205200195</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>20.6907596588135</v>
+        <v>20.6907577514648</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G197" t="n">
-        <v>20.7994174957275</v>
+        <v>20.7994194030762</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G198" t="n">
-        <v>20.4009990692139</v>
+        <v>20.4009971618652</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G199" t="n">
-        <v>20.1021823883057</v>
+        <v>20.1021842956543</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>20.3647804260254</v>
+        <v>20.3647766113281</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>22.6900005340576</v>
       </c>
       <c r="G202" t="n">
-        <v>20.5458793640137</v>
+        <v>20.5458812713623</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G203" t="n">
-        <v>20.7541465759277</v>
+        <v>20.7541484832764</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G206" t="n">
-        <v>20.2651710510254</v>
+        <v>20.265172958374</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>20.3285579681396</v>
+        <v>20.3285598754883</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G208" t="n">
-        <v>20.3557224273682</v>
+        <v>20.3557205200195</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>22.25</v>
       </c>
       <c r="G210" t="n">
-        <v>20.1474609375</v>
+        <v>20.1474590301514</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G212" t="n">
-        <v>20.500602722168</v>
+        <v>20.5006065368652</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G213" t="n">
-        <v>20.5639877319336</v>
+        <v>20.5639896392822</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G214" t="n">
-        <v>20.1836776733398</v>
+        <v>20.1836795806885</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>21.5900001525879</v>
       </c>
       <c r="G216" t="n">
-        <v>19.5498275756836</v>
+        <v>19.5498237609863</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G217" t="n">
-        <v>19.4139995574951</v>
+        <v>19.4140014648438</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>19.5045528411865</v>
+        <v>19.5045509338379</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G220" t="n">
-        <v>19.7943115234375</v>
+        <v>19.7943096160889</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>19.8305320739746</v>
+        <v>19.8305282592773</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>21.9899997711182</v>
       </c>
       <c r="G223" t="n">
-        <v>19.9120254516602</v>
+        <v>19.9120292663574</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G224" t="n">
-        <v>19.7490367889404</v>
+        <v>19.7490348815918</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.4722766876221</v>
+        <v>18.4722785949707</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G226" t="n">
-        <v>18.0919628143311</v>
+        <v>18.0919647216797</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G228" t="n">
-        <v>18.3273963928223</v>
+        <v>18.3273944854736</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>18.2459030151367</v>
+        <v>18.2459011077881</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G230" t="n">
-        <v>18.0104675292969</v>
+        <v>18.0104694366455</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G231" t="n">
-        <v>17.7388191223145</v>
+        <v>17.7388172149658</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G232" t="n">
-        <v>17.8565311431885</v>
+        <v>17.8565330505371</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>17.8203125</v>
+        <v>17.8203144073486</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>17.6392116546631</v>
+        <v>17.6392135620117</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G235" t="n">
-        <v>18.3455066680908</v>
+        <v>18.3455028533936</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>20.3099994659424</v>
       </c>
       <c r="G236" t="n">
-        <v>18.3907814025879</v>
+        <v>18.3907794952393</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G244" t="n">
-        <v>19.1151847839355</v>
+        <v>19.1151828765869</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G245" t="n">
-        <v>19.5860424041748</v>
+        <v>19.5860443115234</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>21.2700004577637</v>
       </c>
       <c r="G246" t="n">
-        <v>19.260066986084</v>
+        <v>19.2600631713867</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>21.75</v>
       </c>
       <c r="G247" t="n">
-        <v>19.6947059631348</v>
+        <v>19.6947078704834</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G248" t="n">
-        <v>20.2651710510254</v>
+        <v>20.265172958374</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G250" t="n">
-        <v>20.2651710510254</v>
+        <v>20.265172958374</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G253" t="n">
-        <v>20.1293449401855</v>
+        <v>20.1293468475342</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G254" t="n">
-        <v>20.1836776733398</v>
+        <v>20.1836795806885</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>20.1565132141113</v>
+        <v>20.15651512146</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G257" t="n">
-        <v>20.3104476928711</v>
+        <v>20.3104496002197</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G259" t="n">
-        <v>20.6183204650879</v>
+        <v>20.6183185577393</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G260" t="n">
-        <v>21.4785480499268</v>
+        <v>21.4785499572754</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G265" t="n">
-        <v>22.2934989929199</v>
+        <v>22.2935009002686</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>24.6299991607666</v>
       </c>
       <c r="G266" t="n">
-        <v>22.3025588989258</v>
+        <v>22.3025531768799</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G270" t="n">
-        <v>22.818696975708</v>
+        <v>22.8186931610107</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G271" t="n">
-        <v>23.0722351074219</v>
+        <v>23.0722370147705</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>25.5100002288818</v>
       </c>
       <c r="G274" t="n">
-        <v>23.0993995666504</v>
+        <v>23.099401473999</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>22.5923175811768</v>
+        <v>22.5923194885254</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G276" t="n">
-        <v>22.3568878173828</v>
+        <v>22.3568859100342</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>22.9092445373535</v>
+        <v>22.9092426300049</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G278" t="n">
-        <v>22.1757869720459</v>
+        <v>22.1757888793945</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G280" t="n">
-        <v>23.6064834594727</v>
+        <v>23.606481552124</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G283" t="n">
-        <v>23.6427001953125</v>
+        <v>23.6427040100098</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G284" t="n">
-        <v>23.6879749298096</v>
+        <v>23.6879787445068</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G287" t="n">
-        <v>23.7423095703125</v>
+        <v>23.7423076629639</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>23.7241973876953</v>
+        <v>23.7241992950439</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>23.6336479187012</v>
+        <v>23.6336498260498</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>23.6879749298096</v>
+        <v>23.6879787445068</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>26.1700000762939</v>
       </c>
       <c r="G292" t="n">
-        <v>23.6970329284668</v>
+        <v>23.6970310211182</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G293" t="n">
-        <v>23.7241973876953</v>
+        <v>23.7241992950439</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>26.5200004577637</v>
       </c>
       <c r="G294" t="n">
-        <v>24.0139598846436</v>
+        <v>24.0139617919922</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>24.068286895752</v>
+        <v>24.0682888031006</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>23.9777393341064</v>
+        <v>23.9777412414551</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>26.8299999237061</v>
       </c>
       <c r="G298" t="n">
-        <v>24.2946643829346</v>
+        <v>24.2946662902832</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G299" t="n">
-        <v>24.430492401123</v>
+        <v>24.4304885864258</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>28.0400009155273</v>
       </c>
       <c r="G303" t="n">
-        <v>25.3903274536133</v>
+        <v>25.3903255462646</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>25.6710300445557</v>
+        <v>25.6710319519043</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>25.7615833282471</v>
+        <v>25.7615795135498</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>27.3899993896484</v>
       </c>
       <c r="G313" t="n">
-        <v>24.8017482757568</v>
+        <v>24.8017463684082</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>27.1900005340576</v>
       </c>
       <c r="G314" t="n">
-        <v>24.6206455230713</v>
+        <v>24.6206474304199</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>27.5400009155273</v>
       </c>
       <c r="G315" t="n">
-        <v>24.9375743865967</v>
+        <v>24.937572479248</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>28.0200004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>25.3722133636475</v>
+        <v>25.3722152709961</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>25.62575340271</v>
+        <v>25.6257553100586</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>25.1730003356934</v>
+        <v>25.1730041503906</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>27.7900009155273</v>
       </c>
       <c r="G320" t="n">
-        <v>25.163948059082</v>
+        <v>25.1639499664307</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>25.399377822876</v>
+        <v>25.3993797302246</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>27.9300003051758</v>
       </c>
       <c r="G324" t="n">
-        <v>25.2907199859619</v>
+        <v>25.2907180786133</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>27.75</v>
       </c>
       <c r="G325" t="n">
-        <v>25.1277256011963</v>
+        <v>25.1277294158936</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>28.2099990844727</v>
       </c>
       <c r="G327" t="n">
-        <v>25.5442600250244</v>
+        <v>25.5442581176758</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>28.1700000762939</v>
       </c>
       <c r="G329" t="n">
-        <v>25.5080394744873</v>
+        <v>25.5080413818359</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>25.0824508666992</v>
+        <v>25.0824546813965</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G332" t="n">
-        <v>24.7836380004883</v>
+        <v>24.7836399078369</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>26.9699993133545</v>
       </c>
       <c r="G333" t="n">
-        <v>24.4214363098145</v>
+        <v>24.4214344024658</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>24.2674980163574</v>
+        <v>24.2674999237061</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>28.1900005340576</v>
       </c>
       <c r="G337" t="n">
-        <v>25.5261516571045</v>
+        <v>25.5261497497559</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>29.4099998474121</v>
       </c>
       <c r="G340" t="n">
-        <v>26.6308631896973</v>
+        <v>26.6308650970459</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>29.25</v>
       </c>
       <c r="G341" t="n">
-        <v>26.4859809875488</v>
+        <v>26.4859828948975</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>29.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>26.3229942321777</v>
+        <v>26.3229923248291</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G343" t="n">
-        <v>26.676139831543</v>
+        <v>26.6761379241943</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>29</v>
       </c>
       <c r="G345" t="n">
-        <v>26.2596054077148</v>
+        <v>26.2596092224121</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>26.667085647583</v>
+        <v>26.6670837402344</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>29.4099998474121</v>
       </c>
       <c r="G348" t="n">
-        <v>26.6308631896973</v>
+        <v>26.6308650970459</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G349" t="n">
-        <v>26.6036968231201</v>
+        <v>26.6036987304688</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>29</v>
       </c>
       <c r="G351" t="n">
-        <v>26.2596054077148</v>
+        <v>26.2596092224121</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G352" t="n">
-        <v>25.3088302612305</v>
+        <v>25.3088283538818</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>27.9699993133545</v>
       </c>
       <c r="G353" t="n">
-        <v>25.3269386291504</v>
+        <v>25.3269367218018</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>28.5300006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>25.8340225219727</v>
+        <v>25.834020614624</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G355" t="n">
-        <v>25.8984451293945</v>
+        <v>25.8984432220459</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G356" t="n">
-        <v>26.0641059875488</v>
+        <v>26.0641078948975</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>25.2299995422363</v>
       </c>
       <c r="G359" t="n">
-        <v>23.2202453613281</v>
+        <v>23.2202472686768</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>25.1299991607666</v>
       </c>
       <c r="G360" t="n">
-        <v>23.1282119750977</v>
+        <v>23.128210067749</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>22.9625511169434</v>
+        <v>22.962553024292</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>22.8705177307129</v>
+        <v>22.8705196380615</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G364" t="n">
-        <v>23.266263961792</v>
+        <v>23.2662658691406</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>25.25</v>
       </c>
       <c r="G365" t="n">
-        <v>23.238655090332</v>
+        <v>23.2386531829834</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>24</v>
       </c>
       <c r="G368" t="n">
-        <v>22.0882244110107</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>22.3643264770508</v>
+        <v>22.3643283843994</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G373" t="n">
-        <v>22.7416667938232</v>
+        <v>22.7416687011719</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G374" t="n">
-        <v>22.9533500671387</v>
+        <v>22.9533462524414</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>23.2846717834473</v>
+        <v>23.2846698760986</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>25.5200004577637</v>
       </c>
       <c r="G377" t="n">
-        <v>23.4871482849121</v>
+        <v>23.4871463775635</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G378" t="n">
-        <v>23.4319248199463</v>
+        <v>23.4319267272949</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>22.2538890838623</v>
+        <v>22.2538871765137</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G386" t="n">
-        <v>21.5544281005859</v>
+        <v>21.5544242858887</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>21.6740703582764</v>
+        <v>21.674072265625</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>23.5</v>
       </c>
       <c r="G388" t="n">
-        <v>21.6280555725098</v>
+        <v>21.6280536651611</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G392" t="n">
-        <v>21.1218681335449</v>
+        <v>21.1218662261963</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G395" t="n">
-        <v>21.9133605957031</v>
+        <v>21.9133625030518</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G396" t="n">
-        <v>21.8857498168945</v>
+        <v>21.8857517242432</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>23.8700008392334</v>
       </c>
       <c r="G397" t="n">
-        <v>21.9685802459717</v>
+        <v>21.9685821533203</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G400" t="n">
-        <v>22.2170734405518</v>
+        <v>22.2170715332031</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G401" t="n">
-        <v>22.4103450775146</v>
+        <v>22.4103469848633</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G402" t="n">
-        <v>22.5299911499023</v>
+        <v>22.5299892425537</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G403" t="n">
-        <v>22.6312294006348</v>
+        <v>22.6312274932861</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>24</v>
       </c>
       <c r="G406" t="n">
-        <v>22.0882244110107</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G407" t="n">
-        <v>21.4255809783936</v>
+        <v>21.4255790710449</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>24</v>
       </c>
       <c r="G409" t="n">
-        <v>22.0882244110107</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G412" t="n">
-        <v>22.3551273345947</v>
+        <v>22.3551254272461</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G416" t="n">
-        <v>22.7876834869385</v>
+        <v>22.7876853942871</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>21.7661056518555</v>
+        <v>21.7661037445068</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G421" t="n">
-        <v>21.7568988800049</v>
+        <v>21.7569007873535</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G422" t="n">
-        <v>21.9133605957031</v>
+        <v>21.9133625030518</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>24</v>
       </c>
       <c r="G423" t="n">
-        <v>22.0882244110107</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>21.9961929321289</v>
+        <v>21.9961891174316</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G425" t="n">
-        <v>21.701681137085</v>
+        <v>21.7016830444336</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G426" t="n">
-        <v>22.0053958892822</v>
+        <v>22.0053939819336</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G427" t="n">
-        <v>22.2170734405518</v>
+        <v>22.2170715332031</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G428" t="n">
-        <v>22.3551273345947</v>
+        <v>22.3551254272461</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G429" t="n">
-        <v>22.0053958892822</v>
+        <v>22.0053939819336</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G430" t="n">
-        <v>21.9133605957031</v>
+        <v>21.9133625030518</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G432" t="n">
-        <v>22.1250400543213</v>
+        <v>22.1250419616699</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G433" t="n">
-        <v>21.7753105163574</v>
+        <v>21.7753086090088</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>23.9300003051758</v>
       </c>
       <c r="G434" t="n">
-        <v>22.0238037109375</v>
+        <v>22.0238018035889</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G435" t="n">
-        <v>21.9961929321289</v>
+        <v>21.9961891174316</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>21.9041576385498</v>
+        <v>21.9041557312012</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G437" t="n">
-        <v>21.6832733154297</v>
+        <v>21.6832752227783</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G440" t="n">
-        <v>20.9469985961914</v>
+        <v>20.9470024108887</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>20.799747467041</v>
+        <v>20.7997455596924</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>22.9300003051758</v>
       </c>
       <c r="G442" t="n">
-        <v>21.1034603118896</v>
+        <v>21.1034622192383</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>21.9501781463623</v>
+        <v>21.9501762390137</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>23.75</v>
       </c>
       <c r="G448" t="n">
-        <v>21.8581390380859</v>
+        <v>21.8581409454346</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G451" t="n">
-        <v>21.2967319488525</v>
+        <v>21.2967300415039</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G452" t="n">
-        <v>20.9746112823486</v>
+        <v>20.9746131896973</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>20.799747467041</v>
+        <v>20.7997455596924</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>20.9838123321533</v>
+        <v>20.983814239502</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G455" t="n">
-        <v>21.1402702331543</v>
+        <v>21.1402740478516</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G458" t="n">
-        <v>21.0942573547363</v>
+        <v>21.0942554473877</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G459" t="n">
-        <v>21.1586780548096</v>
+        <v>21.1586799621582</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G460" t="n">
-        <v>21.0206298828125</v>
+        <v>21.0206260681152</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G461" t="n">
-        <v>21.0022239685059</v>
+        <v>21.0022220611572</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G462" t="n">
-        <v>20.6340827941895</v>
+        <v>20.6340847015381</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>20.385591506958</v>
+        <v>20.3855895996094</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G465" t="n">
-        <v>20.39479637146</v>
+        <v>20.3947944641113</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G471" t="n">
-        <v>20.8917808532715</v>
+        <v>20.8917827606201</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G472" t="n">
-        <v>21.0206298828125</v>
+        <v>21.0206260681152</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G474" t="n">
-        <v>21.2415103912354</v>
+        <v>21.2415084838867</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G475" t="n">
-        <v>20.9285926818848</v>
+        <v>20.9285945892334</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G476" t="n">
-        <v>20.9469985961914</v>
+        <v>20.9470024108887</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>22</v>
       </c>
       <c r="G478" t="n">
-        <v>20.2475414276123</v>
+        <v>20.2475395202637</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>21.9099998474121</v>
       </c>
       <c r="G479" t="n">
-        <v>20.1647090911865</v>
+        <v>20.1647109985352</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G483" t="n">
-        <v>19.8057746887207</v>
+        <v>19.805778503418</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G484" t="n">
-        <v>19.7321472167969</v>
+        <v>19.7321491241455</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G486" t="n">
-        <v>20.0450649261475</v>
+        <v>20.0450630187988</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>20.4316082000732</v>
+        <v>20.4316101074219</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>20.661693572998</v>
+        <v>20.6616973876953</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G491" t="n">
-        <v>20.9838123321533</v>
+        <v>20.983814239502</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G492" t="n">
-        <v>21.1310691833496</v>
+        <v>21.131067276001</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G494" t="n">
-        <v>21.0482406616211</v>
+        <v>21.0482387542725</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G495" t="n">
-        <v>21.0022239685059</v>
+        <v>21.0022220611572</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G497" t="n">
-        <v>21.1218681335449</v>
+        <v>21.1218662261963</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>23.3099994659424</v>
       </c>
       <c r="G498" t="n">
-        <v>21.4531879425049</v>
+        <v>21.4531898498535</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G501" t="n">
-        <v>20.6708984375</v>
+        <v>20.6708965301514</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>19.4652481079102</v>
+        <v>19.4652500152588</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G511" t="n">
-        <v>20.385591506958</v>
+        <v>20.3855895996094</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>22.7199993133545</v>
       </c>
       <c r="G515" t="n">
-        <v>20.9101886749268</v>
+        <v>20.9101867675781</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>20.1555061340332</v>
+        <v>20.1555042266846</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>20.4316082000732</v>
+        <v>20.4316101074219</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>22</v>
       </c>
       <c r="G523" t="n">
-        <v>20.2475414276123</v>
+        <v>20.2475395202637</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G525" t="n">
-        <v>20.9469985961914</v>
+        <v>20.9470024108887</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G526" t="n">
-        <v>21.7568988800049</v>
+        <v>21.7569007873535</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G527" t="n">
-        <v>21.2967319488525</v>
+        <v>21.2967300415039</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>21.259916305542</v>
+        <v>21.2599182128906</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>21.259916305542</v>
+        <v>21.2599182128906</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>23.2199993133545</v>
       </c>
       <c r="G530" t="n">
-        <v>21.3703556060791</v>
+        <v>21.3703575134277</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>21.1218681335449</v>
+        <v>21.1218662261963</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>22.7299995422363</v>
       </c>
       <c r="G535" t="n">
-        <v>20.9193916320801</v>
+        <v>20.9193897247314</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>22.1100006103516</v>
       </c>
       <c r="G537" t="n">
-        <v>20.3487796783447</v>
+        <v>20.3487777709961</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G538" t="n">
-        <v>20.6340827941895</v>
+        <v>20.6340847015381</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G542" t="n">
-        <v>19.9162158966064</v>
+        <v>19.9162178039551</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>22</v>
       </c>
       <c r="G543" t="n">
-        <v>20.2475414276123</v>
+        <v>20.2475395202637</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G546" t="n">
-        <v>20.6340827941895</v>
+        <v>20.6340847015381</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G548" t="n">
-        <v>20.9838123321533</v>
+        <v>20.983814239502</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G550" t="n">
-        <v>20.9285926818848</v>
+        <v>20.9285945892334</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>22.75</v>
       </c>
       <c r="G551" t="n">
-        <v>20.9377956390381</v>
+        <v>20.9377975463867</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G552" t="n">
-        <v>20.8365573883057</v>
+        <v>20.8365592956543</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G553" t="n">
-        <v>21.2967319488525</v>
+        <v>21.2967300415039</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G555" t="n">
-        <v>20.6248817443848</v>
+        <v>20.6248798370361</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>22.0300006866455</v>
       </c>
       <c r="G556" t="n">
-        <v>20.2751522064209</v>
+        <v>20.2751502990723</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>19.6493186950684</v>
+        <v>19.6493167877197</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G561" t="n">
-        <v>19.999044418335</v>
+        <v>19.9990463256836</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>21.8700008392334</v>
       </c>
       <c r="G564" t="n">
-        <v>20.1278953552246</v>
+        <v>20.1278972625732</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>20.385591506958</v>
+        <v>20.3855895996094</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G574" t="n">
-        <v>20.6340827941895</v>
+        <v>20.6340847015381</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>20.6156768798828</v>
+        <v>20.6156749725342</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>20.385591506958</v>
+        <v>20.3855895996094</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G580" t="n">
-        <v>20.39479637146</v>
+        <v>20.3947944641113</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G581" t="n">
-        <v>20.7261180877686</v>
+        <v>20.7261199951172</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G582" t="n">
-        <v>20.9746112823486</v>
+        <v>20.9746131896973</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>21.2783241271973</v>
+        <v>21.2783260345459</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G586" t="n">
-        <v>21.7753105163574</v>
+        <v>21.7753086090088</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>21.5360202789307</v>
+        <v>21.536018371582</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>21.5360202789307</v>
+        <v>21.536018371582</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G589" t="n">
-        <v>21.7937145233154</v>
+        <v>21.7937164306641</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G590" t="n">
-        <v>22.6496353149414</v>
+        <v>22.64963722229</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>24.5</v>
       </c>
       <c r="G591" t="n">
-        <v>22.5483989715576</v>
+        <v>22.548397064209</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>24.5200004577637</v>
       </c>
       <c r="G594" t="n">
-        <v>22.5668048858643</v>
+        <v>22.5668029785156</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G596" t="n">
-        <v>22.7416667938232</v>
+        <v>22.7416687011719</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>24.5699996948242</v>
       </c>
       <c r="G598" t="n">
-        <v>22.6128196716309</v>
+        <v>22.6128215789795</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G599" t="n">
-        <v>22.6312294006348</v>
+        <v>22.6312274932861</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>22.7324657440186</v>
+        <v>22.7324676513672</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G603" t="n">
-        <v>22.8337001800537</v>
+        <v>22.833703994751</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G604" t="n">
-        <v>22.7692794799805</v>
+        <v>22.7692813873291</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G605" t="n">
-        <v>22.9073314666748</v>
+        <v>22.9073295593262</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G609" t="n">
-        <v>23.3090705871582</v>
+        <v>23.3090686798096</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>23.4118747711182</v>
+        <v>23.4118766784668</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G613" t="n">
-        <v>22.7296142578125</v>
+        <v>22.7296123504639</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>22.6174602508545</v>
+        <v>22.6174621582031</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G616" t="n">
-        <v>23.07541847229</v>
+        <v>23.0754165649414</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>24.8199996948242</v>
       </c>
       <c r="G618" t="n">
-        <v>23.1969165802002</v>
+        <v>23.1969146728516</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G623" t="n">
-        <v>23.1595325469971</v>
+        <v>23.1595344543457</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G626" t="n">
-        <v>23.3838367462158</v>
+        <v>23.3838386535645</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G628" t="n">
-        <v>23.2623405456543</v>
+        <v>23.262336730957</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>21.3899993896484</v>
       </c>
       <c r="G633" t="n">
-        <v>19.9912185668945</v>
+        <v>19.9912166595459</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G634" t="n">
-        <v>19.7388763427734</v>
+        <v>19.7388744354248</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G635" t="n">
-        <v>19.5612983703613</v>
+        <v>19.56130027771</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G636" t="n">
-        <v>19.3089561462402</v>
+        <v>19.3089580535889</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>19.533260345459</v>
+        <v>19.5332622528076</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>19.3463401794434</v>
+        <v>19.346342086792</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G640" t="n">
-        <v>19.0285758972168</v>
+        <v>19.0285739898682</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G642" t="n">
-        <v>18.383695602417</v>
+        <v>18.3836975097656</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>18.6220207214355</v>
+        <v>18.6220188140869</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G646" t="n">
-        <v>18.383695602417</v>
+        <v>18.3836975097656</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G647" t="n">
-        <v>18.603328704834</v>
+        <v>18.6033306121826</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G649" t="n">
-        <v>18.7949237823486</v>
+        <v>18.794921875</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G652" t="n">
-        <v>18.6220207214355</v>
+        <v>18.6220188140869</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>19.875</v>
       </c>
       <c r="G653" t="n">
-        <v>18.5752906799316</v>
+        <v>18.575288772583</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G656" t="n">
-        <v>18.495849609375</v>
+        <v>18.4958515167236</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>17.8042373657227</v>
+        <v>17.8042392730713</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G664" t="n">
-        <v>18.495849609375</v>
+        <v>18.4958515167236</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>20.0699996948242</v>
       </c>
       <c r="G666" t="n">
-        <v>18.7575378417969</v>
+        <v>18.7575359344482</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>19.4850006103516</v>
       </c>
       <c r="G673" t="n">
-        <v>18.2107944488525</v>
+        <v>18.2107963562012</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>19.6650009155273</v>
       </c>
       <c r="G674" t="n">
-        <v>18.3790245056152</v>
+        <v>18.3790264129639</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G675" t="n">
-        <v>19.1407260894775</v>
+        <v>19.1407241821289</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G677" t="n">
-        <v>19.4024181365967</v>
+        <v>19.402416229248</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G680" t="n">
-        <v>19.3650341033936</v>
+        <v>19.3650321960449</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G684" t="n">
-        <v>19.0939960479736</v>
+        <v>19.0939979553223</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G685" t="n">
-        <v>18.7388458251953</v>
+        <v>18.7388439178467</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G687" t="n">
-        <v>19.0566101074219</v>
+        <v>19.0566120147705</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G688" t="n">
-        <v>18.8416519165039</v>
+        <v>18.8416538238525</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G689" t="n">
-        <v>19.6080303192139</v>
+        <v>19.6080284118652</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G691" t="n">
-        <v>19.5239143371582</v>
+        <v>19.5239124298096</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>19.8136425018311</v>
+        <v>19.8136444091797</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G695" t="n">
-        <v>19.7482204437256</v>
+        <v>19.748218536377</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G697" t="n">
-        <v>19.6080303192139</v>
+        <v>19.6080284118652</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>19.7669105529785</v>
+        <v>19.7669143676758</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>21.1700000762939</v>
       </c>
       <c r="G699" t="n">
-        <v>19.7856063842773</v>
+        <v>19.7856044769287</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G701" t="n">
-        <v>19.2809181213379</v>
+        <v>19.2809162139893</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G704" t="n">
-        <v>19.0566101074219</v>
+        <v>19.0566120147705</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G705" t="n">
-        <v>18.8042697906494</v>
+        <v>18.8042678833008</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>18.8790378570557</v>
+        <v>18.8790397644043</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>18.1780834197998</v>
+        <v>18.1780853271484</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>19.1049995422363</v>
       </c>
       <c r="G709" t="n">
-        <v>17.8556442260742</v>
+        <v>17.8556423187256</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G712" t="n">
-        <v>16.9817867279053</v>
+        <v>16.9817886352539</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>19.2049999237061</v>
       </c>
       <c r="G714" t="n">
-        <v>17.9491062164307</v>
+        <v>17.949104309082</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G719" t="n">
-        <v>19.0098819732666</v>
+        <v>19.0098838806152</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G722" t="n">
-        <v>19.645414352417</v>
+        <v>19.6454162597656</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>20.9099998474121</v>
       </c>
       <c r="G724" t="n">
-        <v>19.5426082611084</v>
+        <v>19.542610168457</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>19.5799922943115</v>
+        <v>19.5799942016602</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>20.0005626678467</v>
+        <v>20.0005645751953</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>19.5799922943115</v>
+        <v>19.5799942016602</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>21</v>
       </c>
       <c r="G729" t="n">
-        <v>19.6267204284668</v>
+        <v>19.6267223358154</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G730" t="n">
-        <v>19.0939960479736</v>
+        <v>19.0939979553223</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>19.4865322113037</v>
+        <v>19.4865303039551</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>21</v>
       </c>
       <c r="G734" t="n">
-        <v>19.6267204284668</v>
+        <v>19.6267223358154</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G735" t="n">
-        <v>19.4865322113037</v>
+        <v>19.4865303039551</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>20.75</v>
       </c>
       <c r="G736" t="n">
-        <v>19.3930702209473</v>
+        <v>19.3930721282959</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G738" t="n">
-        <v>18.603328704834</v>
+        <v>18.6033306121826</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>19.0659580230713</v>
+        <v>19.0659599304199</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G742" t="n">
-        <v>19.3650341033936</v>
+        <v>19.3650321960449</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>19.4865322113037</v>
+        <v>19.4865303039551</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>19.533260345459</v>
+        <v>19.5332622528076</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>19.3463401794434</v>
+        <v>19.346342086792</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>19.533260345459</v>
+        <v>19.5332622528076</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>19.206148147583</v>
+        <v>19.2061462402344</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>17.7450008392334</v>
       </c>
       <c r="G757" t="n">
-        <v>16.5845794677734</v>
+        <v>16.5845813751221</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>17.7049999237061</v>
       </c>
       <c r="G758" t="n">
-        <v>16.5471973419189</v>
+        <v>16.5471954345703</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G760" t="n">
-        <v>16.7200984954834</v>
+        <v>16.7200965881348</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>16.4957904815674</v>
+        <v>16.495792388916</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>17.6149997711182</v>
       </c>
       <c r="G764" t="n">
-        <v>16.4630813598633</v>
+        <v>16.4630832672119</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>16.4957904815674</v>
+        <v>16.495792388916</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G769" t="n">
-        <v>16.8415966033936</v>
+        <v>16.8415946960449</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G770" t="n">
-        <v>16.6640224456787</v>
+        <v>16.6640205383301</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>16.5331764221191</v>
+        <v>16.5331783294678</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>16.4957904815674</v>
+        <v>16.495792388916</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G775" t="n">
-        <v>16.5985984802246</v>
+        <v>16.5986003875732</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>17.6149997711182</v>
       </c>
       <c r="G784" t="n">
-        <v>16.4630813598633</v>
+        <v>16.4630832672119</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G787" t="n">
-        <v>16.4957904815674</v>
+        <v>16.495792388916</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G788" t="n">
-        <v>16.523832321167</v>
+        <v>16.5238304138184</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G790" t="n">
-        <v>16.4023323059082</v>
+        <v>16.4023303985596</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G791" t="n">
-        <v>16.299524307251</v>
+        <v>16.2995262145996</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>18.8050003051758</v>
       </c>
       <c r="G797" t="n">
-        <v>17.5752601623535</v>
+        <v>17.5752620697021</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G799" t="n">
-        <v>17.4163780212402</v>
+        <v>17.4163799285889</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>18.4349994659424</v>
       </c>
       <c r="G802" t="n">
-        <v>17.2294578552246</v>
+        <v>17.2294597625732</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>18.6749992370605</v>
       </c>
       <c r="G805" t="n">
-        <v>17.4537620544434</v>
+        <v>17.453763961792</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G806" t="n">
-        <v>17.729471206665</v>
+        <v>17.7294731140137</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G809" t="n">
-        <v>17.4163780212402</v>
+        <v>17.4163799285889</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G812" t="n">
-        <v>17.1687088012695</v>
+        <v>17.1687107086182</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>19.1650009155273</v>
       </c>
       <c r="G815" t="n">
-        <v>17.9117202758789</v>
+        <v>17.9117221832275</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>18.0378932952881</v>
+        <v>18.0378913879395</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G818" t="n">
-        <v>17.7948951721191</v>
+        <v>17.7948970794678</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>18.7250003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>17.5004959106445</v>
+        <v>17.5004940032959</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G826" t="n">
-        <v>17.8696632385254</v>
+        <v>17.8696613311768</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G829" t="n">
-        <v>18.056583404541</v>
+        <v>18.0565814971924</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>19.2250003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>17.9677963256836</v>
+        <v>17.9677982330322</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G834" t="n">
-        <v>17.9070491790771</v>
+        <v>17.9070472717285</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>18.5051937103271</v>
+        <v>18.5051918029785</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>19.625</v>
       </c>
       <c r="G837" t="n">
-        <v>18.3416385650635</v>
+        <v>18.3416366577148</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>19.8549995422363</v>
       </c>
       <c r="G839" t="n">
-        <v>18.5565986633301</v>
+        <v>18.5565967559814</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>19.8449993133545</v>
       </c>
       <c r="G842" t="n">
-        <v>18.5472507476807</v>
+        <v>18.5472526550293</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>18.5051937103271</v>
+        <v>18.5051918029785</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G850" t="n">
-        <v>17.8603172302246</v>
+        <v>17.8603191375732</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>19.9071044921875</v>
+        <v>19.9071006774902</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G860" t="n">
-        <v>19.9735870361328</v>
+        <v>19.9735889434814</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G862" t="n">
-        <v>19.2042751312256</v>
+        <v>19.2042770385742</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G868" t="n">
-        <v>17.7131443023682</v>
+        <v>17.7131423950195</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G873" t="n">
-        <v>19.1757850646973</v>
+        <v>19.1757831573486</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>20.2299995422363</v>
       </c>
       <c r="G876" t="n">
-        <v>19.2137718200684</v>
+        <v>19.213773727417</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G880" t="n">
-        <v>19.6601638793945</v>
+        <v>19.6601657867432</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G884" t="n">
-        <v>19.8026294708252</v>
+        <v>19.8026275634766</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G886" t="n">
-        <v>19.8121280670166</v>
+        <v>19.812126159668</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>20.135046005249</v>
+        <v>20.1350498199463</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>20.2775135040283</v>
+        <v>20.2775115966797</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G895" t="n">
-        <v>19.8406200408936</v>
+        <v>19.8406181335449</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G896" t="n">
-        <v>19.821626663208</v>
+        <v>19.8216247558594</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G897" t="n">
-        <v>19.8501167297363</v>
+        <v>19.850118637085</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G899" t="n">
-        <v>19.8121280670166</v>
+        <v>19.812126159668</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G903" t="n">
-        <v>19.8691139221191</v>
+        <v>19.8691120147705</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G904" t="n">
-        <v>19.9735870361328</v>
+        <v>19.9735889434814</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G905" t="n">
-        <v>19.8691139221191</v>
+        <v>19.8691120147705</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G912" t="n">
-        <v>17.9315872192383</v>
+        <v>17.9315891265869</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>18.5049991607666</v>
       </c>
       <c r="G913" t="n">
-        <v>17.5754261016846</v>
+        <v>17.5754241943359</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G915" t="n">
-        <v>17.2762508392334</v>
+        <v>17.276252746582</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>17.4750003814697</v>
       </c>
       <c r="G921" t="n">
-        <v>16.5971660614014</v>
+        <v>16.59716796875</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G922" t="n">
-        <v>16.2837467193604</v>
+        <v>16.2837448120117</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G929" t="n">
-        <v>16.9485816955566</v>
+        <v>16.948579788208</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G932" t="n">
-        <v>16.4974422454834</v>
+        <v>16.497444152832</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>17.2857494354248</v>
+        <v>17.2857475280762</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G943" t="n">
-        <v>17.2002696990967</v>
+        <v>17.2002716064453</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G946" t="n">
-        <v>16.6968936920166</v>
+        <v>16.696891784668</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G947" t="n">
-        <v>16.7538795471191</v>
+        <v>16.7538776397705</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>17.0849990844727</v>
       </c>
       <c r="G948" t="n">
-        <v>16.2267570495605</v>
+        <v>16.2267551422119</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G951" t="n">
-        <v>16.34547996521</v>
+        <v>16.3454780578613</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>16.9549999237061</v>
       </c>
       <c r="G953" t="n">
-        <v>16.1032886505127</v>
+        <v>16.1032905578613</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>15.4811906814575</v>
+        <v>15.4811916351318</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G956" t="n">
-        <v>15.538179397583</v>
+        <v>15.5381784439087</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>16.3850002288818</v>
       </c>
       <c r="G957" t="n">
-        <v>15.5619230270386</v>
+        <v>15.5619220733643</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>15.4811906814575</v>
+        <v>15.4811916351318</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G967" t="n">
-        <v>15.2722434997559</v>
+        <v>15.2722425460815</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>16.0650005340576</v>
       </c>
       <c r="G968" t="n">
-        <v>15.2579965591431</v>
+        <v>15.2579975128174</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>15.8649997711182</v>
       </c>
       <c r="G970" t="n">
-        <v>15.0680437088013</v>
+        <v>15.068042755127</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G971" t="n">
-        <v>15.0348014831543</v>
+        <v>15.0348024368286</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G972" t="n">
-        <v>15.3197317123413</v>
+        <v>15.319730758667</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G973" t="n">
-        <v>15.960823059082</v>
+        <v>15.9608240127563</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>15.7661218643188</v>
+        <v>15.7661228179932</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G975" t="n">
-        <v>15.8800916671753</v>
+        <v>15.8800926208496</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>16.75</v>
       </c>
       <c r="G976" t="n">
-        <v>15.9085874557495</v>
+        <v>15.9085865020752</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>16.9950008392334</v>
       </c>
       <c r="G978" t="n">
-        <v>16.1412792205811</v>
+        <v>16.1412811279297</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G980" t="n">
-        <v>16.4024658203125</v>
+        <v>16.4024639129639</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G982" t="n">
-        <v>16.5734233856201</v>
+        <v>16.5734252929688</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G983" t="n">
-        <v>16.5734233856201</v>
+        <v>16.5734252929688</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G985" t="n">
-        <v>17.2762508392334</v>
+        <v>17.276252746582</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G987" t="n">
-        <v>16.9723262786865</v>
+        <v>16.9723281860352</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G988" t="n">
-        <v>16.4404563903809</v>
+        <v>16.4404544830322</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G992" t="n">
-        <v>16.4024658203125</v>
+        <v>16.4024639129639</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>17.5</v>
       </c>
       <c r="G993" t="n">
-        <v>16.6209106445312</v>
+        <v>16.6209125518799</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>18.0349998474121</v>
       </c>
       <c r="G996" t="n">
-        <v>17.1290378570557</v>
+        <v>17.129035949707</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G999" t="n">
-        <v>16.6968936920166</v>
+        <v>16.696891784668</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1001" t="n">
-        <v>17.9695796966553</v>
+        <v>17.9695816040039</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>19.0699996948242</v>
       </c>
       <c r="G1002" t="n">
-        <v>18.1120452880859</v>
+        <v>18.1120433807373</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>18.2649993896484</v>
       </c>
       <c r="G1004" t="n">
-        <v>17.3474826812744</v>
+        <v>17.3474807739258</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1009" t="n">
-        <v>17.5421829223633</v>
+        <v>17.5421848297119</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>18.4050006866455</v>
       </c>
       <c r="G1010" t="n">
-        <v>17.4804496765137</v>
+        <v>17.4804515838623</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>18.7450008392334</v>
       </c>
       <c r="G1011" t="n">
-        <v>17.8033714294434</v>
+        <v>17.803373336792</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>19.0750007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>18.1167945861816</v>
+        <v>18.116792678833</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>18.75</v>
       </c>
       <c r="G1015" t="n">
-        <v>17.8081207275391</v>
+        <v>17.8081188201904</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>18.9549999237061</v>
       </c>
       <c r="G1016" t="n">
-        <v>18.0028228759766</v>
+        <v>18.0028209686279</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>18.6149997711182</v>
       </c>
       <c r="G1019" t="n">
-        <v>17.6799030303955</v>
+        <v>17.6799011230469</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1022" t="n">
-        <v>18.0930480957031</v>
+        <v>18.0930500030518</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.90309715271</v>
+        <v>17.9030952453613</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>18.1749992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>17.2620029449463</v>
+        <v>17.2620048522949</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1032" t="n">
-        <v>16.5924186706543</v>
+        <v>16.5924167633057</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G1034" t="n">
-        <v>16.2694969177246</v>
+        <v>16.2694988250732</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1035" t="n">
-        <v>16.2979927062988</v>
+        <v>16.2979907989502</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1037" t="n">
-        <v>15.8468503952026</v>
+        <v>15.8468523025513</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1038" t="n">
-        <v>15.8800916671753</v>
+        <v>15.8800926208496</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>17.0849990844727</v>
       </c>
       <c r="G1040" t="n">
-        <v>16.2267570495605</v>
+        <v>16.2267551422119</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>15.7186326980591</v>
+        <v>15.7186317443848</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.747127532959</v>
+        <v>15.7471265792847</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1047" t="n">
-        <v>15.604660987854</v>
+        <v>15.6046619415283</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>16.3649997711182</v>
       </c>
       <c r="G1051" t="n">
-        <v>15.5429267883301</v>
+        <v>15.5429258346558</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1052" t="n">
-        <v>15.1582717895508</v>
+        <v>15.1582708358765</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1053" t="n">
-        <v>13.8096036911011</v>
+        <v>13.8096027374268</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1054" t="n">
-        <v>13.8665895462036</v>
+        <v>13.8665885925293</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>14.3249998092651</v>
       </c>
       <c r="G1056" t="n">
-        <v>13.6054039001465</v>
+        <v>13.6054029464722</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>13.7650003433228</v>
       </c>
       <c r="G1058" t="n">
-        <v>13.0735340118408</v>
+        <v>13.0735349655151</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G1059" t="n">
-        <v>13.0497894287109</v>
+        <v>13.0497903823853</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>12.6850004196167</v>
       </c>
       <c r="G1062" t="n">
-        <v>12.0477876663208</v>
+        <v>12.0477867126465</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>11.875</v>
       </c>
       <c r="G1063" t="n">
-        <v>11.2784757614136</v>
+        <v>11.2784767150879</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1064" t="n">
-        <v>10.6563787460327</v>
+        <v>10.656379699707</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>10</v>
       </c>
       <c r="G1070" t="n">
-        <v>9.49766445159912</v>
+        <v>9.4976634979248</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1071" t="n">
-        <v>10.6183891296387</v>
+        <v>10.6183881759644</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1072" t="n">
-        <v>11.8625812530518</v>
+        <v>11.8625822067261</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1074" t="n">
-        <v>13.0877799987793</v>
+        <v>13.0877809524536</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>14.1049995422363</v>
       </c>
       <c r="G1075" t="n">
-        <v>13.3964548110962</v>
+        <v>13.3964538574219</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1077" t="n">
-        <v>12.2519865036011</v>
+        <v>12.2519855499268</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1079" t="n">
-        <v>11.4921731948853</v>
+        <v>11.4921741485596</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1080" t="n">
-        <v>11.2072439193726</v>
+        <v>11.2072429656982</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>11.75</v>
       </c>
       <c r="G1081" t="n">
-        <v>11.1597547531128</v>
+        <v>11.1597557067871</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1083" t="n">
-        <v>11.568154335022</v>
+        <v>11.5681552886963</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1086" t="n">
-        <v>11.8625812530518</v>
+        <v>11.8625822067261</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G1087" t="n">
-        <v>11.9765529632568</v>
+        <v>11.9765539169312</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>11.5396604537964</v>
+        <v>11.5396614074707</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>11.4921731948853</v>
+        <v>11.4921741485596</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>10.3999423980713</v>
+        <v>10.3999404907227</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G1095" t="n">
-        <v>10.3809471130371</v>
+        <v>10.3809461593628</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1096" t="n">
-        <v>10.6183891296387</v>
+        <v>10.6183881759644</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1097" t="n">
-        <v>10.7323608398438</v>
+        <v>10.7323598861694</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G1098" t="n">
-        <v>10.9128150939941</v>
+        <v>10.9128160476685</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G1103" t="n">
-        <v>10.3429565429688</v>
+        <v>10.3429555892944</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1104" t="n">
-        <v>10.4094390869141</v>
+        <v>10.4094400405884</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1108" t="n">
-        <v>10.0295333862305</v>
+        <v>10.0295324325562</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G1109" t="n">
-        <v>9.9060640335083</v>
+        <v>9.90606307983398</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1110" t="n">
-        <v>10.4094390869141</v>
+        <v>10.4094400405884</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1111" t="n">
-        <v>10.3999423980713</v>
+        <v>10.3999404907227</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G1112" t="n">
-        <v>9.9060640335083</v>
+        <v>9.90606307983398</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1113" t="n">
-        <v>9.89656639099121</v>
+        <v>9.89656543731689</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G1114" t="n">
-        <v>9.64962673187256</v>
+        <v>9.64962577819824</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1116" t="n">
-        <v>10.4949188232422</v>
+        <v>10.4949178695679</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1117" t="n">
-        <v>10.6183891296387</v>
+        <v>10.6183881759644</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G1119" t="n">
-        <v>11.9005727767944</v>
+        <v>11.9005718231201</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1120" t="n">
-        <v>11.8625812530518</v>
+        <v>11.8625822067261</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G1125" t="n">
-        <v>13.2872314453125</v>
+        <v>13.2872304916382</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>13.5</v>
       </c>
       <c r="G1127" t="n">
-        <v>12.8218460083008</v>
+        <v>12.8218469619751</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1129" t="n">
-        <v>11.7771024703979</v>
+        <v>11.7771034240723</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1130" t="n">
-        <v>12.0620336532593</v>
+        <v>12.062032699585</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1132" t="n">
-        <v>12.2899770736694</v>
+        <v>12.2899761199951</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1133" t="n">
-        <v>12.3089723587036</v>
+        <v>12.3089714050293</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1135" t="n">
-        <v>12.5749073028564</v>
+        <v>12.5749063491821</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1138" t="n">
-        <v>11.8055953979492</v>
+        <v>11.8055963516235</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1139" t="n">
-        <v>11.5111684799194</v>
+        <v>11.5111694335938</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1143" t="n">
-        <v>11.7581071853638</v>
+        <v>11.7581081390381</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1145" t="n">
-        <v>11.5871486663818</v>
+        <v>11.5871496200562</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>11.75</v>
       </c>
       <c r="G1148" t="n">
-        <v>11.1597547531128</v>
+        <v>11.1597557067871</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.9887971878052</v>
+        <v>10.9887962341309</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G1150" t="n">
-        <v>11.1787519454956</v>
+        <v>11.1787509918213</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1151" t="n">
-        <v>10.9887971878052</v>
+        <v>10.9887962341309</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1153" t="n">
-        <v>11.2262382507324</v>
+        <v>11.2262372970581</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1154" t="n">
-        <v>11.2262382507324</v>
+        <v>11.2262372970581</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G1157" t="n">
-        <v>11.1027679443359</v>
+        <v>11.1027688980103</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1158" t="n">
-        <v>11.1312618255615</v>
+        <v>11.1312627792358</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G1159" t="n">
-        <v>11.0267868041992</v>
+        <v>11.0267877578735</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1165" t="n">
-        <v>10.6183891296387</v>
+        <v>10.6183881759644</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>11.75</v>
       </c>
       <c r="G1171" t="n">
-        <v>11.1597547531128</v>
+        <v>11.1597557067871</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G1176" t="n">
-        <v>11.1027679443359</v>
+        <v>11.1027688980103</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1177" t="n">
-        <v>10.9603052139282</v>
+        <v>10.9603033065796</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1179" t="n">
-        <v>10.6563787460327</v>
+        <v>10.656379699707</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>10.7798490524292</v>
+        <v>10.7798500061035</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1185" t="n">
-        <v>11.463680267334</v>
+        <v>11.4636793136597</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>12</v>
       </c>
       <c r="G1186" t="n">
-        <v>11.3971967697144</v>
+        <v>11.3971977233887</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1189" t="n">
-        <v>11.4921731948853</v>
+        <v>11.4921741485596</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>11.5871486663818</v>
+        <v>11.5871496200562</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1197" t="n">
-        <v>12.5179214477539</v>
+        <v>12.5179204940796</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1199" t="n">
-        <v>12.0810289382935</v>
+        <v>12.0810279846191</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>11.4921731948853</v>
+        <v>11.4921741485596</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1201" t="n">
-        <v>11.568154335022</v>
+        <v>11.5681552886963</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1203" t="n">
-        <v>11.463680267334</v>
+        <v>11.4636793136597</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>12.0145444869995</v>
+        <v>12.0145435333252</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G1207" t="n">
-        <v>11.9385633468628</v>
+        <v>11.9385623931885</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G1208" t="n">
-        <v>11.957558631897</v>
+        <v>11.9575576782227</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.1285171508789</v>
+        <v>12.1285181045532</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1212" t="n">
-        <v>12.2804803848267</v>
+        <v>12.2804794311523</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>12.2044973373413</v>
+        <v>12.2044982910156</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1219" t="n">
-        <v>12.4039497375488</v>
+        <v>12.4039487838745</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>12.0145444869995</v>
+        <v>12.0145435333252</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1221" t="n">
-        <v>11.8625812530518</v>
+        <v>11.8625822067261</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1222" t="n">
-        <v>12.8978281021118</v>
+        <v>12.8978271484375</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1223" t="n">
-        <v>12.1950006484985</v>
+        <v>12.1949996948242</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G1225" t="n">
-        <v>11.6726293563843</v>
+        <v>11.67262840271</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G1229" t="n">
-        <v>10.5139141082764</v>
+        <v>10.5139131546021</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G1230" t="n">
-        <v>10.7988433837891</v>
+        <v>10.7988443374634</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1238" t="n">
-        <v>12.8978281021118</v>
+        <v>12.8978271484375</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1240" t="n">
-        <v>13.7146253585815</v>
+        <v>13.7146263122559</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1241" t="n">
-        <v>13.9235754013062</v>
+        <v>13.9235744476318</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1246" t="n">
-        <v>14.6264009475708</v>
+        <v>14.6264019012451</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1247" t="n">
-        <v>14.6264009475708</v>
+        <v>14.6264019012451</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G1248" t="n">
-        <v>14.3129796981812</v>
+        <v>14.3129787445068</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1249" t="n">
-        <v>14.1515188217163</v>
+        <v>14.1515197753906</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>15</v>
       </c>
       <c r="G1250" t="n">
-        <v>14.2464962005615</v>
+        <v>14.2464952468872</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1251" t="n">
-        <v>14.4269514083862</v>
+        <v>14.4269504547119</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G1252" t="n">
-        <v>14.4649419784546</v>
+        <v>14.4649410247803</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1254" t="n">
-        <v>14.4269514083862</v>
+        <v>14.4269504547119</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>15</v>
       </c>
       <c r="G1256" t="n">
-        <v>14.2464962005615</v>
+        <v>14.2464952468872</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G1259" t="n">
-        <v>14.5979089736938</v>
+        <v>14.5979080200195</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1260" t="n">
-        <v>14.7498712539673</v>
+        <v>14.7498722076416</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1263" t="n">
-        <v>14.8543472290039</v>
+        <v>14.8543462753296</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1265" t="n">
-        <v>14.3794631958008</v>
+        <v>14.3794641494751</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1271" t="n">
-        <v>14.9493227005005</v>
+        <v>14.9493217468262</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1272" t="n">
-        <v>14.7688674926758</v>
+        <v>14.7688684463501</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1273" t="n">
-        <v>14.7118816375732</v>
+        <v>14.7118806838989</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1277" t="n">
-        <v>14.4079551696777</v>
+        <v>14.4079561233521</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1279" t="n">
-        <v>14.5314254760742</v>
+        <v>14.5314264297485</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1282" t="n">
-        <v>14.3794631958008</v>
+        <v>14.3794641494751</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G1284" t="n">
-        <v>15.3197317123413</v>
+        <v>15.319730758667</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1286" t="n">
-        <v>14.683388710022</v>
+        <v>14.6833877563477</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1288" t="n">
-        <v>15.8041114807129</v>
+        <v>15.8041133880615</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>16.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>15.6711444854736</v>
+        <v>15.6711454391479</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1290" t="n">
-        <v>15.2627449035645</v>
+        <v>15.2627458572388</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1294" t="n">
-        <v>14.7688674926758</v>
+        <v>14.7688684463501</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1295" t="n">
-        <v>14.6359004974365</v>
+        <v>14.6358995437622</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1296" t="n">
-        <v>14.6264009475708</v>
+        <v>14.6264019012451</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1297" t="n">
-        <v>14.4364500045776</v>
+        <v>14.4364490509033</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1299" t="n">
-        <v>14.7403745651245</v>
+        <v>14.7403755187988</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1302" t="n">
-        <v>15.0822906494141</v>
+        <v>15.0822896957397</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G1304" t="n">
-        <v>14.6928863525391</v>
+        <v>14.6928853988647</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G1306" t="n">
-        <v>14.825852394104</v>
+        <v>14.8258533477783</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1307" t="n">
-        <v>14.7688674926758</v>
+        <v>14.7688684463501</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1312" t="n">
-        <v>15.2627449035645</v>
+        <v>15.2627458572388</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1314" t="n">
-        <v>15.1012859344482</v>
+        <v>15.1012849807739</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G1315" t="n">
-        <v>14.8448476791382</v>
+        <v>14.8448486328125</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1318" t="n">
-        <v>15.8705949783325</v>
+        <v>15.8705959320068</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1320" t="n">
-        <v>16.032054901123</v>
+        <v>16.0320568084717</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1322" t="n">
-        <v>15.9370803833008</v>
+        <v>15.9370794296265</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1323" t="n">
-        <v>15.8800916671753</v>
+        <v>15.8800926208496</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>15.7376289367676</v>
+        <v>15.7376279830933</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1327" t="n">
-        <v>15.7091369628906</v>
+        <v>15.7091360092163</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1329" t="n">
-        <v>15.3102350234985</v>
+        <v>15.3102340698242</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1330" t="n">
-        <v>15.3672208786011</v>
+        <v>15.3672199249268</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1331" t="n">
-        <v>15.3387260437012</v>
+        <v>15.3387269973755</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1332" t="n">
-        <v>15.6996393203735</v>
+        <v>15.6996374130249</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1333" t="n">
-        <v>15.538179397583</v>
+        <v>15.5381784439087</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>16.5149993896484</v>
       </c>
       <c r="G1334" t="n">
-        <v>15.6853904724121</v>
+        <v>15.6853914260864</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G1335" t="n">
-        <v>15.960823059082</v>
+        <v>15.9608240127563</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>16.4449996948242</v>
       </c>
       <c r="G1336" t="n">
-        <v>15.6189069747925</v>
+        <v>15.6189079284668</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>16.4650001525879</v>
       </c>
       <c r="G1338" t="n">
-        <v>15.637903213501</v>
+        <v>15.6379022598267</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1339" t="n">
-        <v>15.8468503952026</v>
+        <v>15.8468523025513</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G1340" t="n">
-        <v>16.2837467193604</v>
+        <v>16.2837448120117</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1341" t="n">
-        <v>16.6968936920166</v>
+        <v>16.696891784668</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>17.625</v>
       </c>
       <c r="G1342" t="n">
-        <v>16.739631652832</v>
+        <v>16.7396335601807</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>17.9349994659424</v>
       </c>
       <c r="G1346" t="n">
-        <v>17.0340576171875</v>
+        <v>17.0340595245361</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G1348" t="n">
-        <v>17.4567031860352</v>
+        <v>17.4567050933838</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1350" t="n">
-        <v>17.0388088226318</v>
+        <v>17.0388107299805</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>18.2049999237061</v>
       </c>
       <c r="G1351" t="n">
-        <v>17.2904987335205</v>
+        <v>17.2904968261719</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>17.9850006103516</v>
       </c>
       <c r="G1352" t="n">
-        <v>17.0815467834473</v>
+        <v>17.0815486907959</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1354" t="n">
-        <v>17.0245609283447</v>
+        <v>17.0245628356934</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>17.875</v>
       </c>
       <c r="G1355" t="n">
-        <v>16.9770736694336</v>
+        <v>16.9770755767822</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1356" t="n">
-        <v>17.5421829223633</v>
+        <v>17.5421848297119</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>18.7450008392334</v>
       </c>
       <c r="G1359" t="n">
-        <v>17.8033714294434</v>
+        <v>17.803373336792</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1360" t="n">
-        <v>17.4187164306641</v>
+        <v>17.4187145233154</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>19.1749992370605</v>
       </c>
       <c r="G1361" t="n">
-        <v>18.2117691040039</v>
+        <v>18.2117710113525</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G1364" t="n">
-        <v>18.1500377655029</v>
+        <v>18.1500358581543</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>19.1949996948242</v>
       </c>
       <c r="G1365" t="n">
-        <v>18.2307662963867</v>
+        <v>18.2307643890381</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1366" t="n">
-        <v>17.9315872192383</v>
+        <v>17.9315891265869</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>18.9050006866455</v>
       </c>
       <c r="G1369" t="n">
-        <v>17.9553337097168</v>
+        <v>17.9553356170654</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1370" t="n">
-        <v>17.6846504211426</v>
+        <v>17.6846523284912</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G1375" t="n">
-        <v>18.3209934234619</v>
+        <v>18.3209953308105</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G1384" t="n">
-        <v>18.3209934234619</v>
+        <v>18.3209953308105</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1389" t="n">
-        <v>18.444465637207</v>
+        <v>18.4444637298584</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1392" t="n">
-        <v>18.5584373474121</v>
+        <v>18.5584354400635</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G1394" t="n">
-        <v>17.8461093902588</v>
+        <v>17.8461112976074</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G1399" t="n">
-        <v>17.1812744140625</v>
+        <v>17.1812725067139</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>18.0650005340576</v>
       </c>
       <c r="G1401" t="n">
-        <v>17.1575317382812</v>
+        <v>17.1575298309326</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G1402" t="n">
-        <v>16.6114120483398</v>
+        <v>16.6114139556885</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>17.375</v>
       </c>
       <c r="G1403" t="n">
-        <v>16.5021896362305</v>
+        <v>16.5021915435791</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1404" t="n">
-        <v>16.6968936920166</v>
+        <v>16.696891784668</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1406" t="n">
-        <v>16.8773498535156</v>
+        <v>16.877347946167</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>16.4449996948242</v>
       </c>
       <c r="G1409" t="n">
-        <v>15.6189069747925</v>
+        <v>15.6189079284668</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>17.3449993133545</v>
       </c>
       <c r="G1414" t="n">
-        <v>16.4736976623535</v>
+        <v>16.4736957550049</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>17.0249996185303</v>
       </c>
       <c r="G1415" t="n">
-        <v>16.1697731018066</v>
+        <v>16.169771194458</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>16.8950004577637</v>
       </c>
       <c r="G1416" t="n">
-        <v>16.0463027954102</v>
+        <v>16.0463047027588</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>16.8449993133545</v>
       </c>
       <c r="G1418" t="n">
-        <v>15.9988136291504</v>
+        <v>15.9988145828247</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>17.0249996185303</v>
       </c>
       <c r="G1420" t="n">
-        <v>16.1697731018066</v>
+        <v>16.169771194458</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G1426" t="n">
-        <v>18.4919528961182</v>
+        <v>18.4919509887695</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>18.5949993133545</v>
       </c>
       <c r="G1428" t="n">
-        <v>17.6609058380127</v>
+        <v>17.6609039306641</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>17.0008163452148</v>
+        <v>17.0008182525635</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G1431" t="n">
-        <v>16.5164356231689</v>
+        <v>16.5164375305176</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>16.5750007629395</v>
       </c>
       <c r="G1433" t="n">
-        <v>15.7423791885376</v>
+        <v>15.7423782348633</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G1435" t="n">
-        <v>15.9275808334351</v>
+        <v>15.9275827407837</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1436" t="n">
-        <v>15.8041114807129</v>
+        <v>15.8041133880615</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>16.8150005340576</v>
       </c>
       <c r="G1437" t="n">
-        <v>15.9703235626221</v>
+        <v>15.9703216552734</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>17.5349998474121</v>
       </c>
       <c r="G1439" t="n">
-        <v>16.6541538238525</v>
+        <v>16.6541519165039</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1441" t="n">
-        <v>16.5734233856201</v>
+        <v>16.5734252929688</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>17.9349994659424</v>
       </c>
       <c r="G1445" t="n">
-        <v>17.0340576171875</v>
+        <v>17.0340595245361</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>18.75</v>
       </c>
       <c r="G1449" t="n">
-        <v>17.8081207275391</v>
+        <v>17.8081188201904</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1452" t="n">
-        <v>16.6968936920166</v>
+        <v>16.696891784668</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1456" t="n">
-        <v>16.9628276824951</v>
+        <v>16.9628295898438</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1458" t="n">
-        <v>17.0245609283447</v>
+        <v>17.0245628356934</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1459" t="n">
-        <v>16.9438323974609</v>
+        <v>16.9438304901123</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1460" t="n">
-        <v>16.8298606872559</v>
+        <v>16.8298587799072</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>17.9850006103516</v>
       </c>
       <c r="G1463" t="n">
-        <v>17.0815467834473</v>
+        <v>17.0815486907959</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1465" t="n">
-        <v>17.0245609283447</v>
+        <v>17.0245628356934</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>17.5949993133545</v>
       </c>
       <c r="G1469" t="n">
-        <v>16.7111396789551</v>
+        <v>16.7111377716064</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>17.0008163452148</v>
+        <v>17.0008182525635</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G1472" t="n">
-        <v>17.2002696990967</v>
+        <v>17.2002716064453</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1474" t="n">
-        <v>16.9438323974609</v>
+        <v>16.9438304901123</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1475" t="n">
-        <v>17.0388088226318</v>
+        <v>17.0388107299805</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>18.125</v>
       </c>
       <c r="G1478" t="n">
-        <v>17.2145156860352</v>
+        <v>17.2145175933838</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>18.3649997711182</v>
       </c>
       <c r="G1479" t="n">
-        <v>17.4424591064453</v>
+        <v>17.4424610137939</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1480" t="n">
-        <v>17.2857494354248</v>
+        <v>17.2857475280762</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G1481" t="n">
-        <v>17.1812744140625</v>
+        <v>17.1812725067139</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>18.6550006866455</v>
       </c>
       <c r="G1484" t="n">
-        <v>17.7178916931152</v>
+        <v>17.7178936004639</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.7911262512207</v>
+        <v>18.7911281585693</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1492" t="n">
-        <v>17.9458351135254</v>
+        <v>17.945837020874</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>18.9240951538086</v>
+        <v>18.92409324646</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1499" t="n">
-        <v>19.1662845611572</v>
+        <v>19.1662864685059</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1500" t="n">
-        <v>19.1662845611572</v>
+        <v>19.1662864685059</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G1504" t="n">
-        <v>19.6221733093262</v>
+        <v>19.6221752166748</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G1506" t="n">
-        <v>19.6316699981689</v>
+        <v>19.6316719055176</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G1508" t="n">
-        <v>19.8691139221191</v>
+        <v>19.8691120147705</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1510" t="n">
-        <v>20.4579696655273</v>
+        <v>20.4579677581787</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1512" t="n">
-        <v>21.0373268127441</v>
+        <v>21.0373229980469</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1514" t="n">
-        <v>20.9898376464844</v>
+        <v>20.9898357391357</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G1517" t="n">
-        <v>20.1635417938232</v>
+        <v>20.1635398864746</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G1518" t="n">
-        <v>20.0970554351807</v>
+        <v>20.0970573425293</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G1520" t="n">
-        <v>20.7144050598145</v>
+        <v>20.7144031524658</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G1521" t="n">
-        <v>21.0278282165527</v>
+        <v>21.0278263092041</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1522" t="n">
-        <v>21.0373268127441</v>
+        <v>21.0373229980469</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G1523" t="n">
-        <v>21.0183277130127</v>
+        <v>21.0183296203613</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G1530" t="n">
-        <v>21.5976867675781</v>
+        <v>21.5976886749268</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G1531" t="n">
-        <v>21.6261825561523</v>
+        <v>21.6261806488037</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G1534" t="n">
-        <v>19.0998020172119</v>
+        <v>19.0998001098633</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G1537" t="n">
-        <v>19.6221733093262</v>
+        <v>19.6221752166748</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G1539" t="n">
-        <v>19.0998020172119</v>
+        <v>19.0998001098633</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G1541" t="n">
-        <v>18.055061340332</v>
+        <v>18.0550594329834</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1542" t="n">
-        <v>17.4946956634521</v>
+        <v>17.4946975708008</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1543" t="n">
-        <v>17.5421829223633</v>
+        <v>17.5421848297119</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1544" t="n">
-        <v>18.0930480957031</v>
+        <v>18.0930500030518</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>18.3649997711182</v>
       </c>
       <c r="G1546" t="n">
-        <v>17.4424591064453</v>
+        <v>17.4424610137939</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>18.9249992370605</v>
       </c>
       <c r="G1547" t="n">
-        <v>17.9743270874023</v>
+        <v>17.974328994751</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1549" t="n">
-        <v>18.5394420623779</v>
+        <v>18.5394401550293</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1551" t="n">
-        <v>17.9458351135254</v>
+        <v>17.945837020874</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G1553" t="n">
-        <v>18.0503101348877</v>
+        <v>18.0503082275391</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>19.25</v>
       </c>
       <c r="G1555" t="n">
-        <v>18.2830009460449</v>
+        <v>18.2830028533936</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G1559" t="n">
-        <v>18.6819038391113</v>
+        <v>18.68190574646</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>19.7950000762939</v>
       </c>
       <c r="G1561" t="n">
-        <v>18.8006248474121</v>
+        <v>18.8006267547607</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1562" t="n">
-        <v>18.5964260101318</v>
+        <v>18.5964241027832</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G1563" t="n">
-        <v>18.7768802642822</v>
+        <v>18.7768821716309</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>19.6450004577637</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.6581592559814</v>
+        <v>18.6581611633301</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>19.4249992370605</v>
       </c>
       <c r="G1567" t="n">
-        <v>18.4492111206055</v>
+        <v>18.4492130279541</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>18.5650005340576</v>
       </c>
       <c r="G1568" t="n">
-        <v>17.6324157714844</v>
+        <v>17.6324119567871</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>15.6149997711182</v>
       </c>
       <c r="G1572" t="n">
-        <v>14.8306016921997</v>
+        <v>14.8306007385254</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>16.7549991607666</v>
       </c>
       <c r="G1574" t="n">
-        <v>15.9133329391479</v>
+        <v>15.9133348464966</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1575" t="n">
-        <v>15.2722434997559</v>
+        <v>15.2722425460815</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>16.2749996185303</v>
       </c>
       <c r="G1577" t="n">
-        <v>15.457447052002</v>
+        <v>15.4574489593506</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G1579" t="n">
-        <v>15.5856666564941</v>
+        <v>15.5856657028198</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>16.0450000762939</v>
       </c>
       <c r="G1584" t="n">
-        <v>15.2390012741089</v>
+        <v>15.2390022277832</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1586" t="n">
-        <v>15.5191831588745</v>
+        <v>15.5191822052002</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>17.6550006866455</v>
       </c>
       <c r="G1588" t="n">
-        <v>16.7681274414062</v>
+        <v>16.7681255340576</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1592" t="n">
-        <v>15.9750709533691</v>
+        <v>15.9750699996948</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1593" t="n">
-        <v>15.2627449035645</v>
+        <v>15.2627458572388</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1596" t="n">
-        <v>14.9493227005005</v>
+        <v>14.9493217468262</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1598" t="n">
-        <v>15.3387260437012</v>
+        <v>15.3387269973755</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1599" t="n">
-        <v>15.4811906814575</v>
+        <v>15.4811916351318</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1600" t="n">
-        <v>15.6331539154053</v>
+        <v>15.6331548690796</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1601" t="n">
-        <v>15.6521482467651</v>
+        <v>15.6521492004395</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1602" t="n">
-        <v>15.6996393203735</v>
+        <v>15.6996374130249</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>16.3299999237061</v>
       </c>
       <c r="G1604" t="n">
-        <v>15.5096845626831</v>
+        <v>15.5096855163574</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1606" t="n">
-        <v>14.7403745651245</v>
+        <v>14.7403755187988</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1609" t="n">
-        <v>15.7851181030273</v>
+        <v>15.7851190567017</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>16.5</v>
       </c>
       <c r="G1610" t="n">
-        <v>15.6711444854736</v>
+        <v>15.6711454391479</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G1611" t="n">
-        <v>15.0348014831543</v>
+        <v>15.0348024368286</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1618" t="n">
-        <v>14.1990079879761</v>
+        <v>14.1990070343018</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1619" t="n">
-        <v>14.9493227005005</v>
+        <v>14.9493217468262</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G1620" t="n">
-        <v>15.0158061981201</v>
+        <v>15.0158071517944</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1622" t="n">
-        <v>15.3672208786011</v>
+        <v>15.3672199249268</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G1625" t="n">
-        <v>14.8327655792236</v>
+        <v>14.8327665328979</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1627" t="n">
-        <v>14.6870603561401</v>
+        <v>14.6870594024658</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1628" t="n">
-        <v>15.0756072998047</v>
+        <v>15.075608253479</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1632" t="n">
-        <v>15.8915557861328</v>
+        <v>15.8915548324585</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1633" t="n">
-        <v>15.9886903762817</v>
+        <v>15.9886913299561</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1635" t="n">
-        <v>15.9692640304565</v>
+        <v>15.9692649841309</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1640" t="n">
-        <v>13.7545480728149</v>
+        <v>13.7545490264893</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1643" t="n">
-        <v>13.3660020828247</v>
+        <v>13.366003036499</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1644" t="n">
-        <v>13.7254076004028</v>
+        <v>13.7254085540771</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>13.9391088485718</v>
+        <v>13.9391078948975</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1667" t="n">
-        <v>15.6972808837891</v>
+        <v>15.6972818374634</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1669" t="n">
-        <v>16.2315311431885</v>
+        <v>16.2315330505371</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1672" t="n">
-        <v>15.872127532959</v>
+        <v>15.8721265792847</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1676" t="n">
-        <v>16.4646606445312</v>
+        <v>16.4646625518799</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1685" t="n">
-        <v>17.0960502624512</v>
+        <v>17.0960483551025</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1686" t="n">
-        <v>16.9503440856934</v>
+        <v>16.950345993042</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1693" t="n">
-        <v>16.0664024353027</v>
+        <v>16.0664005279541</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>16.1100006103516</v>
       </c>
       <c r="G1695" t="n">
-        <v>15.6487140655518</v>
+        <v>15.6487131118774</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1696" t="n">
-        <v>15.6001434326172</v>
+        <v>15.6001443862915</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1704" t="n">
-        <v>15.1727437973022</v>
+        <v>15.1727428436279</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>14.75</v>
       </c>
       <c r="G1709" t="n">
-        <v>14.327654838562</v>
+        <v>14.3276538848877</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1715" t="n">
-        <v>13.540846824646</v>
+        <v>13.5408477783203</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1716" t="n">
-        <v>13.9391088485718</v>
+        <v>13.9391078948975</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1744" t="n">
-        <v>14.8230514526367</v>
+        <v>14.823052406311</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1749" t="n">
-        <v>16.2315311431885</v>
+        <v>16.2315330505371</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1752" t="n">
-        <v>15.9304094314575</v>
+        <v>15.9304103851318</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1754" t="n">
-        <v>15.9789781570435</v>
+        <v>15.9789791107178</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G1759" t="n">
-        <v>15.7652769088745</v>
+        <v>15.7652759552002</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1761" t="n">
-        <v>16.5229415893555</v>
+        <v>16.5229434967041</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1764" t="n">
-        <v>16.8434944152832</v>
+        <v>16.8434925079346</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1777" t="n">
-        <v>15.9789781570435</v>
+        <v>15.9789791107178</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1780" t="n">
-        <v>15.9789781570435</v>
+        <v>15.9789791107178</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1781" t="n">
-        <v>16.1635360717773</v>
+        <v>16.163537979126</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1798" t="n">
-        <v>17.7954330444336</v>
+        <v>17.795431137085</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1799" t="n">
-        <v>17.9119987487793</v>
+        <v>17.9119968414307</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G1800" t="n">
-        <v>18.0382747650146</v>
+        <v>18.038272857666</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G1829" t="n">
-        <v>18.0382747650146</v>
+        <v>18.038272857666</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1833" t="n">
-        <v>16.5229415893555</v>
+        <v>16.5229434967041</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1835" t="n">
-        <v>16.3189563751221</v>
+        <v>16.3189544677734</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1836" t="n">
-        <v>16.581226348877</v>
+        <v>16.5812244415283</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1845" t="n">
-        <v>16.076114654541</v>
+        <v>16.0761127471924</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1851" t="n">
-        <v>16.0664024353027</v>
+        <v>16.0664005279541</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1860" t="n">
-        <v>15.8818416595459</v>
+        <v>15.8818407058716</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1861" t="n">
-        <v>15.7361364364624</v>
+        <v>15.7361373901367</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1867" t="n">
-        <v>15.6778535842896</v>
+        <v>15.6778526306152</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1872" t="n">
-        <v>15.0756072998047</v>
+        <v>15.075608253479</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1873" t="n">
-        <v>15.085319519043</v>
+        <v>15.0853204727173</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1879" t="n">
-        <v>14.7064876556396</v>
+        <v>14.706488609314</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>7.0149998664856</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>503226</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>7.21000003814697</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>6.99499988555908</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>7.01000022888184</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>7.08500003814697</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>7.08500003814697</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -447,7 +447,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G3" t="n">
-        <v>18.0109615325928</v>
+        <v>18.01096534729</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G4" t="n">
-        <v>17.4978828430176</v>
+        <v>17.4978809356689</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>17.9401912689209</v>
+        <v>17.9401969909668</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>17.683650970459</v>
+        <v>17.6836528778076</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G7" t="n">
-        <v>18.2498111724854</v>
+        <v>18.249813079834</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G8" t="n">
-        <v>19.4086723327637</v>
+        <v>19.408670425415</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G9" t="n">
-        <v>19.1344337463379</v>
+        <v>19.1344375610352</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G10" t="n">
-        <v>18.84250831604</v>
+        <v>18.8425102233887</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G12" t="n">
-        <v>18.2851963043213</v>
+        <v>18.2851982116699</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G13" t="n">
-        <v>18.0994243621826</v>
+        <v>18.0994262695312</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G15" t="n">
-        <v>17.5686531066895</v>
+        <v>17.5686550140381</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G16" t="n">
-        <v>18.1878890991211</v>
+        <v>18.1878910064697</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G17" t="n">
-        <v>18.0994243621826</v>
+        <v>18.0994262695312</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G18" t="n">
-        <v>18.4798145294189</v>
+        <v>18.4798164367676</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>18.223274230957</v>
+        <v>18.2232780456543</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>17.7632694244385</v>
+        <v>17.7632713317871</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G21" t="n">
-        <v>18.3913536071777</v>
+        <v>18.3913555145264</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>17.9578838348389</v>
+        <v>17.9578857421875</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G25" t="n">
-        <v>18.258659362793</v>
+        <v>18.2586574554443</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G26" t="n">
-        <v>18.0817317962646</v>
+        <v>18.0817375183105</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G27" t="n">
-        <v>17.3563442230225</v>
+        <v>17.3563423156738</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>17.1617240905762</v>
+        <v>17.1617221832275</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G31" t="n">
-        <v>17.0201854705811</v>
+        <v>17.0201835632324</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G32" t="n">
-        <v>17.4890365600586</v>
+        <v>17.48903465271</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G33" t="n">
-        <v>17.6305732727051</v>
+        <v>17.6305770874023</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G34" t="n">
-        <v>18.4798145294189</v>
+        <v>18.4798164367676</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>20.8099994659424</v>
       </c>
       <c r="G35" t="n">
-        <v>18.4090442657471</v>
+        <v>18.4090423583984</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G36" t="n">
-        <v>18.453275680542</v>
+        <v>18.4532775878906</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>18.9752063751221</v>
+        <v>18.9752044677734</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>20.5</v>
       </c>
       <c r="G38" t="n">
-        <v>18.1348114013672</v>
+        <v>18.1348094940186</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G39" t="n">
-        <v>17.3121070861816</v>
+        <v>17.3121128082275</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G40" t="n">
-        <v>17.7632694244385</v>
+        <v>17.7632713317871</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G44" t="n">
-        <v>19.0017471313477</v>
+        <v>19.001745223999</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G46" t="n">
-        <v>19.3113632202148</v>
+        <v>19.3113594055176</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G52" t="n">
-        <v>19.9836769104004</v>
+        <v>19.983678817749</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G53" t="n">
-        <v>19.1167449951172</v>
+        <v>19.1167469024658</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>20.0367565155029</v>
+        <v>20.0367527008057</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>22.8099994659424</v>
       </c>
       <c r="G57" t="n">
-        <v>20.1782932281494</v>
+        <v>20.178295135498</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G58" t="n">
-        <v>19.4971351623535</v>
+        <v>19.4971370697021</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G60" t="n">
-        <v>18.9663581848145</v>
+        <v>18.9663600921631</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G61" t="n">
-        <v>19.4794425964355</v>
+        <v>19.4794406890869</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G62" t="n">
-        <v>19.9129066467285</v>
+        <v>19.9129085540771</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G64" t="n">
-        <v>19.4971351623535</v>
+        <v>19.4971370697021</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G66" t="n">
-        <v>18.8690528869629</v>
+        <v>18.8690509796143</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G67" t="n">
-        <v>18.8336696624756</v>
+        <v>18.833667755127</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G68" t="n">
-        <v>18.5152015686035</v>
+        <v>18.5151977539062</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>18.9309730529785</v>
+        <v>18.9309711456299</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G70" t="n">
-        <v>18.8955879211426</v>
+        <v>18.8955898284912</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G71" t="n">
-        <v>18.5240459442139</v>
+        <v>18.5240478515625</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G72" t="n">
-        <v>19.3113632202148</v>
+        <v>19.3113594055176</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>21.25</v>
       </c>
       <c r="G74" t="n">
-        <v>18.798282623291</v>
+        <v>18.7982788085938</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G75" t="n">
-        <v>18.8778972625732</v>
+        <v>18.8778953552246</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G77" t="n">
-        <v>18.8071250915527</v>
+        <v>18.8071269989014</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G78" t="n">
-        <v>18.3205814361572</v>
+        <v>18.3205833435059</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>18.3648147583008</v>
+        <v>18.3648128509521</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G80" t="n">
-        <v>17.8251914978027</v>
+        <v>17.8251953125</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G81" t="n">
-        <v>18.0817317962646</v>
+        <v>18.0817375183105</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G82" t="n">
-        <v>18.0640430450439</v>
+        <v>18.0640392303467</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>18.3117389678955</v>
+        <v>18.3117370605469</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G84" t="n">
-        <v>17.878267288208</v>
+        <v>17.8782691955566</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>18.0021190643311</v>
+        <v>18.0021171569824</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G86" t="n">
-        <v>17.7190361022949</v>
+        <v>17.7190399169922</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G89" t="n">
-        <v>17.1440334320068</v>
+        <v>17.1440296173096</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G91" t="n">
-        <v>17.9844284057617</v>
+        <v>17.9844226837158</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G94" t="n">
-        <v>18.8336696624756</v>
+        <v>18.833667755127</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>21.25</v>
       </c>
       <c r="G95" t="n">
-        <v>18.798282623291</v>
+        <v>18.7982788085938</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>18.0640430450439</v>
+        <v>18.0640392303467</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>17.7367286682129</v>
+        <v>17.7367305755615</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G100" t="n">
-        <v>17.5939388275146</v>
+        <v>17.593936920166</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G101" t="n">
-        <v>17.81125831604</v>
+        <v>17.8112602233887</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G103" t="n">
-        <v>17.6482677459717</v>
+        <v>17.648265838623</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G105" t="n">
-        <v>17.5939388275146</v>
+        <v>17.593936920166</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G106" t="n">
-        <v>17.4128379821777</v>
+        <v>17.4128341674805</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>17.4762210845947</v>
+        <v>17.4762191772461</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G109" t="n">
-        <v>17.4762210845947</v>
+        <v>17.4762191772461</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G111" t="n">
-        <v>17.4852752685547</v>
+        <v>17.4852771759033</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>17.7478733062744</v>
+        <v>17.7478713989258</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G114" t="n">
-        <v>17.150239944458</v>
+        <v>17.1502418518066</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G115" t="n">
-        <v>16.7155990600586</v>
+        <v>16.71559715271</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G120" t="n">
-        <v>17.9380264282227</v>
+        <v>17.9380283355713</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G121" t="n">
-        <v>17.7297611236572</v>
+        <v>17.7297630310059</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G123" t="n">
-        <v>18.1825141906738</v>
+        <v>18.1825160980225</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G124" t="n">
-        <v>16.8514232635498</v>
+        <v>16.8514270782471</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>16.3896198272705</v>
+        <v>16.3896179199219</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G126" t="n">
-        <v>16.6793804168701</v>
+        <v>16.6793785095215</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G127" t="n">
-        <v>16.2628440856934</v>
+        <v>16.262845993042</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>18.25</v>
       </c>
       <c r="G128" t="n">
-        <v>16.5254440307617</v>
+        <v>16.5254421234131</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>16.6069374084473</v>
+        <v>16.6069393157959</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G131" t="n">
-        <v>16.8242568969727</v>
+        <v>16.8242588043213</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G134" t="n">
-        <v>16.3624496459961</v>
+        <v>16.3624515533447</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G136" t="n">
-        <v>16.69748878479</v>
+        <v>16.6974868774414</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G137" t="n">
-        <v>17.0959091186523</v>
+        <v>17.095911026001</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G138" t="n">
-        <v>17.1321296691895</v>
+        <v>17.1321315765381</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G139" t="n">
-        <v>17.086856842041</v>
+        <v>17.0868549346924</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G140" t="n">
-        <v>17.150239944458</v>
+        <v>17.1502418518066</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G144" t="n">
-        <v>17.9018096923828</v>
+        <v>17.9018077850342</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G147" t="n">
-        <v>18.7710914611816</v>
+        <v>18.7710933685303</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>18.6352653503418</v>
+        <v>18.6352672576904</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>20.5699996948242</v>
       </c>
       <c r="G151" t="n">
-        <v>18.6262111663818</v>
+        <v>18.6262130737305</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G153" t="n">
-        <v>18.2187347412109</v>
+        <v>18.2187366485596</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G159" t="n">
-        <v>18.9431381225586</v>
+        <v>18.94313621521</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G161" t="n">
-        <v>18.6624298095703</v>
+        <v>18.6624336242676</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G162" t="n">
-        <v>18.6624298095703</v>
+        <v>18.6624336242676</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>18.4722785949707</v>
+        <v>18.4722747802734</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G165" t="n">
-        <v>18.7529811859131</v>
+        <v>18.7529830932617</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>18.9703044891357</v>
+        <v>18.9703025817871</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G168" t="n">
-        <v>18.6080989837646</v>
+        <v>18.6081008911133</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G169" t="n">
-        <v>18.653377532959</v>
+        <v>18.6533794403076</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>18.6080989837646</v>
+        <v>18.6081008911133</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>18.6986541748047</v>
+        <v>18.6986484527588</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>19.106128692627</v>
+        <v>19.1061267852783</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>22</v>
       </c>
       <c r="G177" t="n">
-        <v>19.9210834503174</v>
+        <v>19.9210815429688</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>21.75</v>
       </c>
       <c r="G178" t="n">
-        <v>19.6947078704834</v>
+        <v>19.6947059631348</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>19.5588798522949</v>
+        <v>19.5588817596436</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>21.4899997711182</v>
       </c>
       <c r="G180" t="n">
-        <v>19.4592761993408</v>
+        <v>19.4592742919922</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G181" t="n">
-        <v>19.3143939971924</v>
+        <v>19.314395904541</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G182" t="n">
-        <v>18.8888072967529</v>
+        <v>18.8888092041016</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G185" t="n">
-        <v>18.7710914611816</v>
+        <v>18.7710933685303</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>19.160457611084</v>
+        <v>19.1604595184326</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G187" t="n">
-        <v>19.9391956329346</v>
+        <v>19.9391937255859</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>20.3557205200195</v>
+        <v>20.3557243347168</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G191" t="n">
-        <v>20.3104496002197</v>
+        <v>20.3104476928711</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>20.3919410705566</v>
+        <v>20.3919429779053</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G194" t="n">
-        <v>20.3557205200195</v>
+        <v>20.3557243347168</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>20.6907577514648</v>
+        <v>20.6907596588135</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>20.8446941375732</v>
+        <v>20.8446979522705</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G197" t="n">
-        <v>20.7994194030762</v>
+        <v>20.7994213104248</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G198" t="n">
-        <v>20.4009971618652</v>
+        <v>20.4010009765625</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G199" t="n">
-        <v>20.1021842956543</v>
+        <v>20.1021823883057</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>22.6700000762939</v>
       </c>
       <c r="G200" t="n">
-        <v>20.5277709960938</v>
+        <v>20.5277690887451</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>20.3647766113281</v>
+        <v>20.3647785186768</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G203" t="n">
-        <v>20.7541484832764</v>
+        <v>20.7541446685791</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>20.4191093444824</v>
+        <v>20.4191074371338</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G208" t="n">
-        <v>20.3557205200195</v>
+        <v>20.3557243347168</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G211" t="n">
-        <v>20.2289524078369</v>
+        <v>20.2289543151855</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G212" t="n">
-        <v>20.5006065368652</v>
+        <v>20.5006046295166</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G213" t="n">
-        <v>20.5639896392822</v>
+        <v>20.5639877319336</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>21.5900001525879</v>
       </c>
       <c r="G216" t="n">
-        <v>19.5498237609863</v>
+        <v>19.549825668335</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G217" t="n">
-        <v>19.4140014648438</v>
+        <v>19.4140033721924</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>19.5045509338379</v>
+        <v>19.5045528411865</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G220" t="n">
-        <v>19.7943096160889</v>
+        <v>19.7943134307861</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>19.8305282592773</v>
+        <v>19.830530166626</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>21.9899997711182</v>
       </c>
       <c r="G223" t="n">
-        <v>19.9120292663574</v>
+        <v>19.9120273590088</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.4722785949707</v>
+        <v>18.4722747802734</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G226" t="n">
-        <v>18.0919647216797</v>
+        <v>18.0919628143311</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G227" t="n">
-        <v>18.3002300262451</v>
+        <v>18.3002281188965</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>17.8203144073486</v>
+        <v>17.8203125</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>17.6392135620117</v>
+        <v>17.6392116546631</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G235" t="n">
-        <v>18.3455028533936</v>
+        <v>18.3455047607422</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>19.2872295379639</v>
+        <v>19.2872276306152</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>19.377779006958</v>
+        <v>19.3777770996094</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G244" t="n">
-        <v>19.1151828765869</v>
+        <v>19.1151847839355</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G245" t="n">
-        <v>19.5860443115234</v>
+        <v>19.5860462188721</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>21.75</v>
       </c>
       <c r="G247" t="n">
-        <v>19.6947078704834</v>
+        <v>19.6947059631348</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>22.5</v>
       </c>
       <c r="G249" t="n">
-        <v>20.3738327026367</v>
+        <v>20.3738346099854</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G251" t="n">
-        <v>20.3466682434082</v>
+        <v>20.3466701507568</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>20.2289524078369</v>
+        <v>20.2289543151855</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>20.15651512146</v>
+        <v>20.1565132141113</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G257" t="n">
-        <v>20.3104496002197</v>
+        <v>20.3104476928711</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G259" t="n">
-        <v>20.6183185577393</v>
+        <v>20.6183204650879</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G260" t="n">
-        <v>21.4785499572754</v>
+        <v>21.4785480499268</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G264" t="n">
-        <v>22.2572822570801</v>
+        <v>22.2572803497314</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G265" t="n">
-        <v>22.2935009002686</v>
+        <v>22.2935028076172</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>24.6299991607666</v>
       </c>
       <c r="G266" t="n">
-        <v>22.3025531768799</v>
+        <v>22.3025550842285</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G270" t="n">
-        <v>22.8186931610107</v>
+        <v>22.8186988830566</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G271" t="n">
-        <v>23.0722370147705</v>
+        <v>23.0722351074219</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>25.5699996948242</v>
       </c>
       <c r="G273" t="n">
-        <v>23.1537303924561</v>
+        <v>23.1537284851074</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>25.5100002288818</v>
       </c>
       <c r="G274" t="n">
-        <v>23.099401473999</v>
+        <v>23.0993995666504</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>22.5923194885254</v>
+        <v>22.5923175811768</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G276" t="n">
-        <v>22.3568859100342</v>
+        <v>22.3568878173828</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>22.9092426300049</v>
+        <v>22.9092445373535</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G278" t="n">
-        <v>22.1757888793945</v>
+        <v>22.1757850646973</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>26.2299995422363</v>
       </c>
       <c r="G281" t="n">
-        <v>23.7513618469238</v>
+        <v>23.7513637542725</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G283" t="n">
-        <v>23.6427040100098</v>
+        <v>23.6427021026611</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G284" t="n">
-        <v>23.6879787445068</v>
+        <v>23.6879749298096</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>23.5612087249756</v>
+        <v>23.561206817627</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G286" t="n">
-        <v>23.5612087249756</v>
+        <v>23.561206817627</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G287" t="n">
-        <v>23.7423076629639</v>
+        <v>23.7423057556152</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>23.7241992950439</v>
+        <v>23.7241973876953</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>23.6879787445068</v>
+        <v>23.6879749298096</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>26.1700000762939</v>
       </c>
       <c r="G292" t="n">
-        <v>23.6970310211182</v>
+        <v>23.6970348358154</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G293" t="n">
-        <v>23.7241992950439</v>
+        <v>23.7241973876953</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>26.5200004577637</v>
       </c>
       <c r="G294" t="n">
-        <v>24.0139617919922</v>
+        <v>24.0139579772949</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>24.0682888031006</v>
+        <v>24.0682849884033</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>23.9777412414551</v>
+        <v>23.9777355194092</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>26.8299999237061</v>
       </c>
       <c r="G298" t="n">
-        <v>24.2946662902832</v>
+        <v>24.2946643829346</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G299" t="n">
-        <v>24.4304885864258</v>
+        <v>24.430492401123</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G300" t="n">
-        <v>24.6115913391113</v>
+        <v>24.61159324646</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G304" t="n">
-        <v>25.4265441894531</v>
+        <v>25.4265460968018</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>28.2900009155273</v>
       </c>
       <c r="G305" t="n">
-        <v>25.6167011260986</v>
+        <v>25.6167030334473</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>25.7615795135498</v>
+        <v>25.7615833282471</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>25.5352058410645</v>
+        <v>25.5352077484131</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G310" t="n">
-        <v>24.9556827545166</v>
+        <v>24.955680847168</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>27.5</v>
       </c>
       <c r="G311" t="n">
-        <v>24.9013519287109</v>
+        <v>24.9013538360596</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>27.3899993896484</v>
       </c>
       <c r="G313" t="n">
-        <v>24.8017463684082</v>
+        <v>24.8017482757568</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>27.1900005340576</v>
       </c>
       <c r="G314" t="n">
-        <v>24.6206474304199</v>
+        <v>24.6206455230713</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>27.5400009155273</v>
       </c>
       <c r="G315" t="n">
-        <v>24.937572479248</v>
+        <v>24.9375743865967</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>25.6257553100586</v>
+        <v>25.62575340271</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>25.1730041503906</v>
+        <v>25.173002243042</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>25.3993797302246</v>
+        <v>25.3993759155273</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G322" t="n">
-        <v>25.4265441894531</v>
+        <v>25.4265460968018</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>28.4099998474121</v>
       </c>
       <c r="G323" t="n">
-        <v>25.7253608703613</v>
+        <v>25.7253589630127</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>27.9300003051758</v>
       </c>
       <c r="G324" t="n">
-        <v>25.2907180786133</v>
+        <v>25.2907218933105</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>28.4300003051758</v>
       </c>
       <c r="G326" t="n">
-        <v>25.7434711456299</v>
+        <v>25.7434692382812</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>28.1700000762939</v>
       </c>
       <c r="G329" t="n">
-        <v>25.5080413818359</v>
+        <v>25.5080394744873</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>25.2635536193848</v>
+        <v>25.2635555267334</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G332" t="n">
-        <v>24.7836399078369</v>
+        <v>24.7836380004883</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>24.2674999237061</v>
+        <v>24.2674980163574</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>28.1900005340576</v>
       </c>
       <c r="G337" t="n">
-        <v>25.5261497497559</v>
+        <v>25.5261516571045</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>26.1237831115723</v>
+        <v>26.1237850189209</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>28.9200000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>26.1871662139893</v>
+        <v>26.1871681213379</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>29.4099998474121</v>
       </c>
       <c r="G340" t="n">
-        <v>26.6308650970459</v>
+        <v>26.6308631896973</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>29.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>26.3229923248291</v>
+        <v>26.3229961395264</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G343" t="n">
-        <v>26.6761379241943</v>
+        <v>26.676139831543</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>26.8934593200684</v>
+        <v>26.893461227417</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>29</v>
       </c>
       <c r="G345" t="n">
-        <v>26.2596092224121</v>
+        <v>26.2596073150635</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>26.6670837402344</v>
+        <v>26.667085647583</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G347" t="n">
-        <v>26.9115695953369</v>
+        <v>26.9115676879883</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>29.4099998474121</v>
       </c>
       <c r="G348" t="n">
-        <v>26.6308650970459</v>
+        <v>26.6308631896973</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>29</v>
       </c>
       <c r="G351" t="n">
-        <v>26.2596092224121</v>
+        <v>26.2596073150635</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G352" t="n">
-        <v>25.3088283538818</v>
+        <v>25.3088302612305</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>27.9699993133545</v>
       </c>
       <c r="G353" t="n">
-        <v>25.3269367218018</v>
+        <v>25.326940536499</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>28.5300006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>25.834020614624</v>
+        <v>25.8340244293213</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G355" t="n">
-        <v>25.8984432220459</v>
+        <v>25.8984451293945</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G356" t="n">
-        <v>26.0641078948975</v>
+        <v>26.0641059875488</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>25.2299995422363</v>
       </c>
       <c r="G359" t="n">
-        <v>23.2202472686768</v>
+        <v>23.2202453613281</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>25.1299991607666</v>
       </c>
       <c r="G360" t="n">
-        <v>23.128210067749</v>
+        <v>23.1282138824463</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>22.962553024292</v>
+        <v>22.9625511169434</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>22.8705196380615</v>
+        <v>22.8705177307129</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G363" t="n">
-        <v>22.8613147735596</v>
+        <v>22.8613128662109</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G364" t="n">
-        <v>23.2662658691406</v>
+        <v>23.266263961792</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>24.8700008392334</v>
       </c>
       <c r="G367" t="n">
-        <v>22.8889236450195</v>
+        <v>22.8889255523682</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>24</v>
       </c>
       <c r="G368" t="n">
-        <v>22.0882263183594</v>
+        <v>22.0882244110107</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>22.2262763977051</v>
+        <v>22.2262783050537</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G371" t="n">
-        <v>22.3827342987061</v>
+        <v>22.3827323913574</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G374" t="n">
-        <v>22.9533462524414</v>
+        <v>22.95334815979</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G375" t="n">
-        <v>22.8797206878662</v>
+        <v>22.8797225952148</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G378" t="n">
-        <v>23.4319267272949</v>
+        <v>23.4319248199463</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G379" t="n">
-        <v>22.806095123291</v>
+        <v>22.8060932159424</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G381" t="n">
-        <v>22.6036167144775</v>
+        <v>22.6036186218262</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>22.2538871765137</v>
+        <v>22.2538890838623</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>23.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>21.545223236084</v>
+        <v>21.5452251434326</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>21.4900035858154</v>
+        <v>21.4900016784668</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G386" t="n">
-        <v>21.5544242858887</v>
+        <v>21.5544281005859</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>21.674072265625</v>
+        <v>21.6740703582764</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>23.5</v>
       </c>
       <c r="G388" t="n">
-        <v>21.6280536651611</v>
+        <v>21.6280555725098</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G391" t="n">
-        <v>21.2046985626221</v>
+        <v>21.2046966552734</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G392" t="n">
-        <v>21.1218662261963</v>
+        <v>21.1218681335449</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>23.2700004577637</v>
       </c>
       <c r="G393" t="n">
-        <v>21.416374206543</v>
+        <v>21.4163761138916</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G394" t="n">
-        <v>21.5084114074707</v>
+        <v>21.5084095001221</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G395" t="n">
-        <v>21.9133625030518</v>
+        <v>21.9133586883545</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G396" t="n">
-        <v>21.8857517242432</v>
+        <v>21.8857498168945</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G398" t="n">
-        <v>22.6220245361328</v>
+        <v>22.6220226287842</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G400" t="n">
-        <v>22.2170715332031</v>
+        <v>22.2170734405518</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G401" t="n">
-        <v>22.4103469848633</v>
+        <v>22.4103450775146</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G403" t="n">
-        <v>22.6312274932861</v>
+        <v>22.6312294006348</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G405" t="n">
-        <v>22.5576000213623</v>
+        <v>22.5575981140137</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>24</v>
       </c>
       <c r="G406" t="n">
-        <v>22.0882263183594</v>
+        <v>22.0882244110107</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G407" t="n">
-        <v>21.4255790710449</v>
+        <v>21.4255809783936</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>23.5300006866455</v>
       </c>
       <c r="G408" t="n">
-        <v>21.6556644439697</v>
+        <v>21.6556663513184</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>24</v>
       </c>
       <c r="G409" t="n">
-        <v>22.0882263183594</v>
+        <v>22.0882244110107</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G411" t="n">
-        <v>22.5391941070557</v>
+        <v>22.539192199707</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G415" t="n">
-        <v>22.6220245361328</v>
+        <v>22.6220226287842</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>23.9699993133545</v>
       </c>
       <c r="G420" t="n">
-        <v>22.0606155395508</v>
+        <v>22.0606136322021</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G422" t="n">
-        <v>21.9133625030518</v>
+        <v>21.9133586883545</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>24</v>
       </c>
       <c r="G423" t="n">
-        <v>22.0882263183594</v>
+        <v>22.0882244110107</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>21.9961891174316</v>
+        <v>21.9961910247803</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G427" t="n">
-        <v>22.2170715332031</v>
+        <v>22.2170734405518</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G430" t="n">
-        <v>21.9133625030518</v>
+        <v>21.9133586883545</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>23.7700004577637</v>
       </c>
       <c r="G431" t="n">
-        <v>21.8765468597412</v>
+        <v>21.8765487670898</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G432" t="n">
-        <v>22.1250419616699</v>
+        <v>22.1250400543213</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G433" t="n">
-        <v>21.7753086090088</v>
+        <v>21.7753105163574</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>23.9300003051758</v>
       </c>
       <c r="G434" t="n">
-        <v>22.0238018035889</v>
+        <v>22.0238037109375</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G435" t="n">
-        <v>21.9961891174316</v>
+        <v>21.9961910247803</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G437" t="n">
-        <v>21.6832752227783</v>
+        <v>21.6832733154297</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G438" t="n">
-        <v>20.827356338501</v>
+        <v>20.8273544311523</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G439" t="n">
-        <v>21.0574398040771</v>
+        <v>21.0574378967285</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>20.7997455596924</v>
+        <v>20.799747467041</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>22.9300003051758</v>
       </c>
       <c r="G442" t="n">
-        <v>21.1034622192383</v>
+        <v>21.1034603118896</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>21.0758476257324</v>
+        <v>21.0758495330811</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G444" t="n">
-        <v>21.3243408203125</v>
+        <v>21.3243427276611</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G446" t="n">
-        <v>22.0974292755127</v>
+        <v>22.0974311828613</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>23.75</v>
       </c>
       <c r="G448" t="n">
-        <v>21.8581409454346</v>
+        <v>21.8581390380859</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>22.3827342987061</v>
+        <v>22.3827323913574</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>20.7997455596924</v>
+        <v>20.799747467041</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838123321533</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G455" t="n">
-        <v>21.1402740478516</v>
+        <v>21.1402702331543</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>22.5</v>
       </c>
       <c r="G457" t="n">
-        <v>20.7077102661133</v>
+        <v>20.7077121734619</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G458" t="n">
-        <v>21.0942554473877</v>
+        <v>21.0942573547363</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G460" t="n">
-        <v>21.0206260681152</v>
+        <v>21.0206279754639</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G462" t="n">
-        <v>20.6340847015381</v>
+        <v>20.6340827941895</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G463" t="n">
-        <v>20.4500160217285</v>
+        <v>20.4500179290771</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>20.3855895996094</v>
+        <v>20.385591506958</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G471" t="n">
-        <v>20.8917827606201</v>
+        <v>20.8917808532715</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G472" t="n">
-        <v>21.0206260681152</v>
+        <v>21.0206279754639</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G474" t="n">
-        <v>21.2415084838867</v>
+        <v>21.2415103912354</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>22.5</v>
       </c>
       <c r="G477" t="n">
-        <v>20.7077102661133</v>
+        <v>20.7077121734619</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>22</v>
       </c>
       <c r="G478" t="n">
-        <v>20.2475395202637</v>
+        <v>20.2475414276123</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>21.9099998474121</v>
       </c>
       <c r="G479" t="n">
-        <v>20.1647109985352</v>
+        <v>20.1647071838379</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G480" t="n">
-        <v>20.0910835266113</v>
+        <v>20.0910816192627</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G481" t="n">
-        <v>19.2719764709473</v>
+        <v>19.2719783782959</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G483" t="n">
-        <v>19.805778503418</v>
+        <v>19.8057765960693</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G485" t="n">
-        <v>20.1831169128418</v>
+        <v>20.1831150054932</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G486" t="n">
-        <v>20.0450630187988</v>
+        <v>20.0450668334961</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>20.4316101074219</v>
+        <v>20.4316082000732</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>20.6616973876953</v>
+        <v>20.6616954803467</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G491" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838123321533</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G492" t="n">
-        <v>21.131067276001</v>
+        <v>21.1310691833496</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>22.5</v>
       </c>
       <c r="G493" t="n">
-        <v>20.7077102661133</v>
+        <v>20.7077121734619</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G497" t="n">
-        <v>21.1218662261963</v>
+        <v>21.1218681335449</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>23.3099994659424</v>
       </c>
       <c r="G498" t="n">
-        <v>21.4531898498535</v>
+        <v>21.4531879425049</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>23.2700004577637</v>
       </c>
       <c r="G499" t="n">
-        <v>21.416374206543</v>
+        <v>21.4163761138916</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G502" t="n">
-        <v>20.7721347808838</v>
+        <v>20.7721366882324</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>19.4652500152588</v>
+        <v>19.4652481079102</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G504" t="n">
-        <v>19.7965717315674</v>
+        <v>19.796573638916</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G507" t="n">
-        <v>20.2199287414551</v>
+        <v>20.2199306488037</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G511" t="n">
-        <v>20.3855895996094</v>
+        <v>20.385591506958</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G512" t="n">
-        <v>20.2199287414551</v>
+        <v>20.2199306488037</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>20.5236415863037</v>
+        <v>20.5236434936523</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G517" t="n">
-        <v>20.2659492492676</v>
+        <v>20.2659473419189</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>22.2399997711182</v>
       </c>
       <c r="G518" t="n">
-        <v>20.4684219360352</v>
+        <v>20.4684238433838</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>20.4316101074219</v>
+        <v>20.4316082000732</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G522" t="n">
-        <v>20.4500160217285</v>
+        <v>20.4500179290771</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>22</v>
       </c>
       <c r="G523" t="n">
-        <v>20.2475395202637</v>
+        <v>20.2475414276123</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G524" t="n">
-        <v>20.1739120483398</v>
+        <v>20.1739139556885</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>21.2599182128906</v>
+        <v>21.259916305542</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>21.2599182128906</v>
+        <v>21.259916305542</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G531" t="n">
-        <v>21.5176124572754</v>
+        <v>21.5176105499268</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>21.1218662261963</v>
+        <v>21.1218681335449</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G533" t="n">
-        <v>20.8549652099609</v>
+        <v>20.8549671173096</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G534" t="n">
-        <v>21.3243408203125</v>
+        <v>21.3243427276611</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>22.7299995422363</v>
       </c>
       <c r="G535" t="n">
-        <v>20.9193897247314</v>
+        <v>20.9193916320801</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G538" t="n">
-        <v>20.6340847015381</v>
+        <v>20.6340827941895</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>21.4300003051758</v>
       </c>
       <c r="G540" t="n">
-        <v>19.7229461669922</v>
+        <v>19.7229442596436</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G542" t="n">
-        <v>19.9162178039551</v>
+        <v>19.9162158966064</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>22</v>
       </c>
       <c r="G543" t="n">
-        <v>20.2475395202637</v>
+        <v>20.2475414276123</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G544" t="n">
-        <v>20.5604553222656</v>
+        <v>20.5604572296143</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G545" t="n">
-        <v>20.7169170379639</v>
+        <v>20.7169151306152</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G546" t="n">
-        <v>20.6340847015381</v>
+        <v>20.6340827941895</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G547" t="n">
-        <v>20.4500160217285</v>
+        <v>20.4500179290771</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G548" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838123321533</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G555" t="n">
-        <v>20.6248798370361</v>
+        <v>20.6248817443848</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G557" t="n">
-        <v>20.0910835266113</v>
+        <v>20.0910816192627</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>19.6493167877197</v>
+        <v>19.6493186950684</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G561" t="n">
-        <v>19.9990463256836</v>
+        <v>19.9990501403809</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G568" t="n">
-        <v>20.5236415863037</v>
+        <v>20.5236434936523</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G569" t="n">
-        <v>20.3763885498047</v>
+        <v>20.3763866424561</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>20.3855895996094</v>
+        <v>20.385591506958</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G574" t="n">
-        <v>20.6340847015381</v>
+        <v>20.6340827941895</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>20.6156749725342</v>
+        <v>20.6156768798828</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G578" t="n">
-        <v>20.7169170379639</v>
+        <v>20.7169151306152</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>20.3855895996094</v>
+        <v>20.385591506958</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G581" t="n">
-        <v>20.7261199951172</v>
+        <v>20.7261180877686</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G583" t="n">
-        <v>21.2046985626221</v>
+        <v>21.2046966552734</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>21.2783260345459</v>
+        <v>21.2783241271973</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G586" t="n">
-        <v>21.7753086090088</v>
+        <v>21.7753105163574</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>21.536018371582</v>
+        <v>21.5360202789307</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>21.536018371582</v>
+        <v>21.5360202789307</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G590" t="n">
-        <v>22.64963722229</v>
+        <v>22.6496353149414</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G595" t="n">
-        <v>22.8797206878662</v>
+        <v>22.8797225952148</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>24.5699996948242</v>
       </c>
       <c r="G598" t="n">
-        <v>22.6128215789795</v>
+        <v>22.6128196716309</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G599" t="n">
-        <v>22.6312274932861</v>
+        <v>22.6312294006348</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>22.9165325164795</v>
+        <v>22.9165344238281</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>22.7324676513672</v>
+        <v>22.7324657440186</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G603" t="n">
-        <v>22.833703994751</v>
+        <v>22.8337001800537</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G604" t="n">
-        <v>22.7692813873291</v>
+        <v>22.7692775726318</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G605" t="n">
-        <v>22.9073295593262</v>
+        <v>22.9073314666748</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G606" t="n">
-        <v>23.2754688262939</v>
+        <v>23.2754669189453</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>22.9165325164795</v>
+        <v>22.9165344238281</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G608" t="n">
-        <v>22.991304397583</v>
+        <v>22.9913024902344</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>23.4118766784668</v>
+        <v>23.4118747711182</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G611" t="n">
-        <v>22.9071884155273</v>
+        <v>22.9071865081787</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G612" t="n">
-        <v>22.9819564819336</v>
+        <v>22.9819583892822</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G614" t="n">
-        <v>22.355770111084</v>
+        <v>22.3557720184326</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>22.6174621582031</v>
+        <v>22.6174602508545</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G616" t="n">
-        <v>23.0754165649414</v>
+        <v>23.0754203796387</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>24.8199996948242</v>
       </c>
       <c r="G618" t="n">
-        <v>23.1969146728516</v>
+        <v>23.1969165802002</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>24.3299999237061</v>
       </c>
       <c r="G622" t="n">
-        <v>22.7389583587646</v>
+        <v>22.7389602661133</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G623" t="n">
-        <v>23.1595344543457</v>
+        <v>23.1595306396484</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G628" t="n">
-        <v>23.262336730957</v>
+        <v>23.2623386383057</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G629" t="n">
-        <v>22.9258823394775</v>
+        <v>22.9258804321289</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G630" t="n">
-        <v>20.991247177124</v>
+        <v>20.9912452697754</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>21.3899993896484</v>
       </c>
       <c r="G633" t="n">
-        <v>19.9912166595459</v>
+        <v>19.9912185668945</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G634" t="n">
-        <v>19.7388744354248</v>
+        <v>19.7388782501221</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G636" t="n">
-        <v>19.3089580535889</v>
+        <v>19.3089542388916</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G641" t="n">
-        <v>18.6266956329346</v>
+        <v>18.6266937255859</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>18.6220188140869</v>
+        <v>18.6220207214355</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G648" t="n">
-        <v>18.6360397338867</v>
+        <v>18.6360416412354</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G649" t="n">
-        <v>18.794921875</v>
+        <v>18.7949237823486</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G652" t="n">
-        <v>18.6220188140869</v>
+        <v>18.6220207214355</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>19.875</v>
       </c>
       <c r="G653" t="n">
-        <v>18.575288772583</v>
+        <v>18.5752925872803</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G654" t="n">
-        <v>18.3930435180664</v>
+        <v>18.3930416107178</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G656" t="n">
-        <v>18.4958515167236</v>
+        <v>18.495849609375</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G659" t="n">
-        <v>18.491174697876</v>
+        <v>18.4911766052246</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G660" t="n">
-        <v>18.2435073852539</v>
+        <v>18.2435054779053</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>19.0149993896484</v>
       </c>
       <c r="G662" t="n">
-        <v>17.7715282440186</v>
+        <v>17.7715263366699</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>19.375</v>
       </c>
       <c r="G663" t="n">
-        <v>18.1079864501953</v>
+        <v>18.1079883575439</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G664" t="n">
-        <v>18.4958515167236</v>
+        <v>18.495849609375</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>20.0699996948242</v>
       </c>
       <c r="G666" t="n">
-        <v>18.7575359344482</v>
+        <v>18.7575378417969</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G670" t="n">
-        <v>18.491174697876</v>
+        <v>18.4911766052246</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>19.4850006103516</v>
       </c>
       <c r="G673" t="n">
-        <v>18.2107963562012</v>
+        <v>18.2107944488525</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>19.6650009155273</v>
       </c>
       <c r="G674" t="n">
-        <v>18.3790264129639</v>
+        <v>18.3790245056152</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G675" t="n">
-        <v>19.1407241821289</v>
+        <v>19.1407260894775</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>19.4397983551025</v>
+        <v>19.4398002624512</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G677" t="n">
-        <v>19.402416229248</v>
+        <v>19.4024181365967</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G679" t="n">
-        <v>19.4304542541504</v>
+        <v>19.4304523468018</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>20.5</v>
       </c>
       <c r="G681" t="n">
-        <v>19.1594200134277</v>
+        <v>19.1594181060791</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G684" t="n">
-        <v>19.0939979553223</v>
+        <v>19.0939960479736</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>20.5</v>
       </c>
       <c r="G686" t="n">
-        <v>19.1594200134277</v>
+        <v>19.1594181060791</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G688" t="n">
-        <v>18.8416538238525</v>
+        <v>18.8416519165039</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G689" t="n">
-        <v>19.6080284118652</v>
+        <v>19.6080303192139</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G691" t="n">
-        <v>19.5239124298096</v>
+        <v>19.5239143371582</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>19.8136444091797</v>
+        <v>19.8136425018311</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G697" t="n">
-        <v>19.6080284118652</v>
+        <v>19.6080303192139</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>19.7669143676758</v>
+        <v>19.7669124603271</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>21.1700000762939</v>
       </c>
       <c r="G699" t="n">
-        <v>19.7856044769287</v>
+        <v>19.7856063842773</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G700" t="n">
-        <v>19.5706462860107</v>
+        <v>19.5706443786621</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G705" t="n">
-        <v>18.8042678833008</v>
+        <v>18.8042697906494</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>18.8790397644043</v>
+        <v>18.8790378570557</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>18.1780853271484</v>
+        <v>18.1780834197998</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>18.6453876495361</v>
+        <v>18.6453857421875</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>19.1049995422363</v>
       </c>
       <c r="G709" t="n">
-        <v>17.8556423187256</v>
+        <v>17.8556442260742</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G711" t="n">
-        <v>17.1546878814697</v>
+        <v>17.1546897888184</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G712" t="n">
-        <v>16.9817886352539</v>
+        <v>16.9817867279053</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>19.2049999237061</v>
       </c>
       <c r="G714" t="n">
-        <v>17.949104309082</v>
+        <v>17.9491062164307</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G717" t="n">
-        <v>19.5706462860107</v>
+        <v>19.5706443786621</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>20.5300006866455</v>
       </c>
       <c r="G718" t="n">
-        <v>19.1874580383301</v>
+        <v>19.1874561309814</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G719" t="n">
-        <v>19.0098838806152</v>
+        <v>19.0098819732666</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G723" t="n">
-        <v>19.4771862030029</v>
+        <v>19.4771842956543</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>20.9099998474121</v>
       </c>
       <c r="G724" t="n">
-        <v>19.542610168457</v>
+        <v>19.5426063537598</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>19.5799942016602</v>
+        <v>19.5799922943115</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>20.0005645751953</v>
+        <v>20.0005626678467</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>19.5799942016602</v>
+        <v>19.5799922943115</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>19.4397983551025</v>
+        <v>19.4398002624512</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G730" t="n">
-        <v>19.0939979553223</v>
+        <v>19.0939960479736</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>19.4865303039551</v>
+        <v>19.4865322113037</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G732" t="n">
-        <v>19.4397983551025</v>
+        <v>19.4398002624512</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G733" t="n">
-        <v>19.7014904022217</v>
+        <v>19.701488494873</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G735" t="n">
-        <v>19.4865303039551</v>
+        <v>19.4865322113037</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>20.75</v>
       </c>
       <c r="G736" t="n">
-        <v>19.3930721282959</v>
+        <v>19.3930702209473</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>19.0659599304199</v>
+        <v>19.0659580230713</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>19.4865303039551</v>
+        <v>19.4865322113037</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G747" t="n">
-        <v>19.7014904022217</v>
+        <v>19.701488494873</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G749" t="n">
-        <v>19.4304542541504</v>
+        <v>19.4304523468018</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>20.5</v>
       </c>
       <c r="G750" t="n">
-        <v>19.1594200134277</v>
+        <v>19.1594181060791</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>19.2061462402344</v>
+        <v>19.206148147583</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G753" t="n">
-        <v>18.3930435180664</v>
+        <v>18.3930416107178</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G754" t="n">
-        <v>17.0472106933594</v>
+        <v>17.0472087860107</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G756" t="n">
-        <v>16.8135585784912</v>
+        <v>16.8135566711426</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>17.7049999237061</v>
       </c>
       <c r="G758" t="n">
-        <v>16.5471954345703</v>
+        <v>16.5471973419189</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G760" t="n">
-        <v>16.7200965881348</v>
+        <v>16.7200984954834</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>17.6149997711182</v>
       </c>
       <c r="G764" t="n">
-        <v>16.4630832672119</v>
+        <v>16.4630813598633</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>17.1650009155273</v>
       </c>
       <c r="G765" t="n">
-        <v>16.0425090789795</v>
+        <v>16.0425109863281</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>16.5425224304199</v>
+        <v>16.5425205230713</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G769" t="n">
-        <v>16.8415946960449</v>
+        <v>16.8415966033936</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>16.5331783294678</v>
+        <v>16.5331764221191</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G775" t="n">
-        <v>16.5986003875732</v>
+        <v>16.5985984802246</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G776" t="n">
-        <v>16.8135585784912</v>
+        <v>16.8135566711426</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>17.6149997711182</v>
       </c>
       <c r="G784" t="n">
-        <v>16.4630832672119</v>
+        <v>16.4630813598633</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>17.6350002288818</v>
       </c>
       <c r="G786" t="n">
-        <v>16.4817752838135</v>
+        <v>16.4817733764648</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G788" t="n">
-        <v>16.5238304138184</v>
+        <v>16.523832321167</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G790" t="n">
-        <v>16.4023303985596</v>
+        <v>16.4023323059082</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G791" t="n">
-        <v>16.2995262145996</v>
+        <v>16.299524307251</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>17.1967468261719</v>
+        <v>17.1967449188232</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G799" t="n">
-        <v>17.4163799285889</v>
+        <v>17.4163780212402</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G801" t="n">
-        <v>17.1313228607178</v>
+        <v>17.1313247680664</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>18.4349994659424</v>
       </c>
       <c r="G802" t="n">
-        <v>17.2294597625732</v>
+        <v>17.229455947876</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G806" t="n">
-        <v>17.7294731140137</v>
+        <v>17.729471206665</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G809" t="n">
-        <v>17.4163799285889</v>
+        <v>17.4163780212402</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>18.0249996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>16.8462696075439</v>
+        <v>16.8462677001953</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G812" t="n">
-        <v>17.1687107086182</v>
+        <v>17.1687088012695</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>19.25</v>
       </c>
       <c r="G814" t="n">
-        <v>17.9911594390869</v>
+        <v>17.9911613464355</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>19.1650009155273</v>
       </c>
       <c r="G815" t="n">
-        <v>17.9117221832275</v>
+        <v>17.9117202758789</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G817" t="n">
-        <v>17.6593761444092</v>
+        <v>17.6593780517578</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G818" t="n">
-        <v>17.7948970794678</v>
+        <v>17.7948951721191</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>18.6149997711182</v>
       </c>
       <c r="G822" t="n">
-        <v>17.3976879119873</v>
+        <v>17.3976860046387</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G826" t="n">
-        <v>17.8696613311768</v>
+        <v>17.869665145874</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>19.5949993133545</v>
       </c>
       <c r="G827" t="n">
-        <v>18.3136005401611</v>
+        <v>18.3135986328125</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G829" t="n">
-        <v>18.0565814971924</v>
+        <v>18.056583404541</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>19.5949993133545</v>
       </c>
       <c r="G830" t="n">
-        <v>18.3136005401611</v>
+        <v>18.3135986328125</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G832" t="n">
-        <v>18.0192012786865</v>
+        <v>18.0191993713379</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G834" t="n">
-        <v>17.9070472717285</v>
+        <v>17.9070491790771</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>18.5051918029785</v>
+        <v>18.5051937103271</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>19.625</v>
       </c>
       <c r="G837" t="n">
-        <v>18.3416366577148</v>
+        <v>18.3416385650635</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>19.8549995422363</v>
       </c>
       <c r="G839" t="n">
-        <v>18.5565967559814</v>
+        <v>18.5565986633301</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G840" t="n">
-        <v>18.4397716522217</v>
+        <v>18.439769744873</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>19.8449993133545</v>
       </c>
       <c r="G842" t="n">
-        <v>18.5472526550293</v>
+        <v>18.5472507476807</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>18.5051918029785</v>
+        <v>18.5051937103271</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G844" t="n">
-        <v>18.3930435180664</v>
+        <v>18.3930416107178</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G850" t="n">
-        <v>17.8603191375732</v>
+        <v>17.8603172302246</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>18.06125831604</v>
+        <v>18.0612602233887</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G853" t="n">
-        <v>18.0939693450928</v>
+        <v>18.0939712524414</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>19.9071006774902</v>
+        <v>19.9071025848389</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G862" t="n">
-        <v>19.2042770385742</v>
+        <v>19.204273223877</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G863" t="n">
-        <v>19.4892063140869</v>
+        <v>19.4892082214355</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G868" t="n">
-        <v>17.7131423950195</v>
+        <v>17.7131443023682</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>18.7749996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>17.8318634033203</v>
+        <v>17.8318614959717</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G872" t="n">
-        <v>18.6534118652344</v>
+        <v>18.6534099578857</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>20.2299995422363</v>
       </c>
       <c r="G876" t="n">
-        <v>19.213773727417</v>
+        <v>19.2137718200684</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>19.9850006103516</v>
       </c>
       <c r="G877" t="n">
-        <v>18.9810810089111</v>
+        <v>18.9810829162598</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G880" t="n">
-        <v>19.6601657867432</v>
+        <v>19.6601638793945</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G882" t="n">
-        <v>19.9355964660645</v>
+        <v>19.9355945587158</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G883" t="n">
-        <v>20.0210742950439</v>
+        <v>20.0210762023926</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G884" t="n">
-        <v>19.8026275634766</v>
+        <v>19.8026294708252</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G885" t="n">
-        <v>19.7171497344971</v>
+        <v>19.7171478271484</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G886" t="n">
-        <v>19.812126159668</v>
+        <v>19.8121280670166</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G887" t="n">
-        <v>19.7456436157227</v>
+        <v>19.7456455230713</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>20.1350498199463</v>
+        <v>20.135046005249</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>20.4674644470215</v>
+        <v>20.4674625396729</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>21.5699996948242</v>
       </c>
       <c r="G892" t="n">
-        <v>20.4864597320557</v>
+        <v>20.4864616394043</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G893" t="n">
-        <v>20.2870101928711</v>
+        <v>20.2870121002197</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>20.2775115966797</v>
+        <v>20.2775135040283</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G895" t="n">
-        <v>19.8406181335449</v>
+        <v>19.8406200408936</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G896" t="n">
-        <v>19.8216247558594</v>
+        <v>19.821626663208</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G897" t="n">
-        <v>19.850118637085</v>
+        <v>19.8501167297363</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G899" t="n">
-        <v>19.812126159668</v>
+        <v>19.8121280670166</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G906" t="n">
-        <v>19.9355964660645</v>
+        <v>19.9355945587158</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G907" t="n">
-        <v>19.96409034729</v>
+        <v>19.9640884399414</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G912" t="n">
-        <v>17.9315891265869</v>
+        <v>17.9315872192383</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>18.5049991607666</v>
       </c>
       <c r="G913" t="n">
-        <v>17.5754241943359</v>
+        <v>17.5754261016846</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G914" t="n">
-        <v>17.2952442169189</v>
+        <v>17.2952461242676</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G915" t="n">
-        <v>17.276252746582</v>
+        <v>17.2762508392334</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G917" t="n">
-        <v>17.3854732513428</v>
+        <v>17.3854751586914</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>17.9150009155273</v>
       </c>
       <c r="G920" t="n">
-        <v>17.0150661468506</v>
+        <v>17.015064239502</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>17.6350002288818</v>
       </c>
       <c r="G930" t="n">
-        <v>16.7491321563721</v>
+        <v>16.7491302490234</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>17.7350006103516</v>
       </c>
       <c r="G931" t="n">
-        <v>16.8441066741943</v>
+        <v>16.844108581543</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G935" t="n">
-        <v>16.9248371124268</v>
+        <v>16.9248352050781</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>18.0450000762939</v>
       </c>
       <c r="G939" t="n">
-        <v>17.1385345458984</v>
+        <v>17.1385364532471</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>17.2857475280762</v>
+        <v>17.2857494354248</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G943" t="n">
-        <v>17.2002716064453</v>
+        <v>17.2002696990967</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>17.7350006103516</v>
       </c>
       <c r="G944" t="n">
-        <v>16.8441066741943</v>
+        <v>16.844108581543</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G946" t="n">
-        <v>16.696891784668</v>
+        <v>16.6968936920166</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G947" t="n">
-        <v>16.7538776397705</v>
+        <v>16.7538795471191</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>17.0849990844727</v>
       </c>
       <c r="G948" t="n">
-        <v>16.2267551422119</v>
+        <v>16.2267570495605</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>17.0450000762939</v>
       </c>
       <c r="G949" t="n">
-        <v>16.1887664794922</v>
+        <v>16.1887683868408</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>16.9549999237061</v>
       </c>
       <c r="G953" t="n">
-        <v>16.1032905578613</v>
+        <v>16.1032886505127</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>16.8649997711182</v>
       </c>
       <c r="G954" t="n">
-        <v>16.0178108215332</v>
+        <v>16.0178089141846</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>15.4811916351318</v>
+        <v>15.4811906814575</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G956" t="n">
-        <v>15.5381784439087</v>
+        <v>15.538179397583</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>15.4811916351318</v>
+        <v>15.4811906814575</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>16.4150009155273</v>
       </c>
       <c r="G962" t="n">
-        <v>15.5904159545898</v>
+        <v>15.5904169082642</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G964" t="n">
-        <v>15.680643081665</v>
+        <v>15.6806421279907</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G965" t="n">
-        <v>15.4052095413208</v>
+        <v>15.4052104949951</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G967" t="n">
-        <v>15.2722425460815</v>
+        <v>15.2722434997559</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>16.0650005340576</v>
       </c>
       <c r="G968" t="n">
-        <v>15.2579975128174</v>
+        <v>15.2579965591431</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>15.8649997711182</v>
       </c>
       <c r="G970" t="n">
-        <v>15.068042755127</v>
+        <v>15.0680437088013</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G971" t="n">
-        <v>15.0348024368286</v>
+        <v>15.0348014831543</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G973" t="n">
-        <v>15.9608240127563</v>
+        <v>15.9608249664307</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G975" t="n">
-        <v>15.8800926208496</v>
+        <v>15.8800916671753</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>16.75</v>
       </c>
       <c r="G976" t="n">
-        <v>15.9085865020752</v>
+        <v>15.9085855484009</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G980" t="n">
-        <v>16.4024639129639</v>
+        <v>16.4024658203125</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>17.4549999237061</v>
       </c>
       <c r="G981" t="n">
-        <v>16.5781707763672</v>
+        <v>16.5781726837158</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G982" t="n">
-        <v>16.5734252929688</v>
+        <v>16.5734233856201</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G983" t="n">
-        <v>16.5734252929688</v>
+        <v>16.5734233856201</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G985" t="n">
-        <v>17.276252746582</v>
+        <v>17.2762508392334</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G987" t="n">
-        <v>16.9723281860352</v>
+        <v>16.9723262786865</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G992" t="n">
-        <v>16.4024639129639</v>
+        <v>16.4024658203125</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>17.5</v>
       </c>
       <c r="G993" t="n">
-        <v>16.6209125518799</v>
+        <v>16.6209106445312</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>18.0349998474121</v>
       </c>
       <c r="G996" t="n">
-        <v>17.129035949707</v>
+        <v>17.1290378570557</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>18.0949993133545</v>
       </c>
       <c r="G997" t="n">
-        <v>17.1860218048096</v>
+        <v>17.1860237121582</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G999" t="n">
-        <v>16.696891784668</v>
+        <v>16.6968936920166</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1001" t="n">
-        <v>17.9695816040039</v>
+        <v>17.9695796966553</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>19.0699996948242</v>
       </c>
       <c r="G1002" t="n">
-        <v>18.1120433807373</v>
+        <v>18.1120452880859</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>18.2649993896484</v>
       </c>
       <c r="G1004" t="n">
-        <v>17.3474807739258</v>
+        <v>17.3474826812744</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1005" t="n">
-        <v>17.2477569580078</v>
+        <v>17.2477588653564</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1009" t="n">
-        <v>17.5421848297119</v>
+        <v>17.5421829223633</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>18.4050006866455</v>
       </c>
       <c r="G1010" t="n">
-        <v>17.4804515838623</v>
+        <v>17.4804496765137</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>18.7450008392334</v>
       </c>
       <c r="G1011" t="n">
-        <v>17.803373336792</v>
+        <v>17.8033714294434</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>19.0750007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>18.116792678833</v>
+        <v>18.1167964935303</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>17.8556079864502</v>
+        <v>17.8556060791016</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>18.9549999237061</v>
       </c>
       <c r="G1016" t="n">
-        <v>18.0028209686279</v>
+        <v>18.0028228759766</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>18.6049995422363</v>
       </c>
       <c r="G1017" t="n">
-        <v>17.6704025268555</v>
+        <v>17.6704044342041</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>18.5550003051758</v>
       </c>
       <c r="G1018" t="n">
-        <v>17.6229152679443</v>
+        <v>17.622917175293</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>18.7950000762939</v>
       </c>
       <c r="G1024" t="n">
-        <v>17.8508586883545</v>
+        <v>17.8508605957031</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>18.1749992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>17.2620048522949</v>
+        <v>17.2620029449463</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.2287616729736</v>
+        <v>17.2287635803223</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>15.8611001968384</v>
+        <v>15.8610982894897</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1035" t="n">
-        <v>16.2979907989502</v>
+        <v>16.2979927062988</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1038" t="n">
-        <v>15.8800926208496</v>
+        <v>15.8800916671753</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>17.0849990844727</v>
       </c>
       <c r="G1040" t="n">
-        <v>16.2267551422119</v>
+        <v>16.2267570495605</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>16.6149997711182</v>
       </c>
       <c r="G1042" t="n">
-        <v>15.7803688049316</v>
+        <v>15.7803678512573</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>15.7186317443848</v>
+        <v>15.7186336517334</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>16.1550006866455</v>
       </c>
       <c r="G1044" t="n">
-        <v>15.3434772491455</v>
+        <v>15.3434762954712</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1045" t="n">
-        <v>15.9845676422119</v>
+        <v>15.9845695495605</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.7471265792847</v>
+        <v>15.747127532959</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1048" t="n">
-        <v>15.8611001968384</v>
+        <v>15.8610982894897</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1049" t="n">
-        <v>15.7043857574463</v>
+        <v>15.7043867111206</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1052" t="n">
-        <v>15.1582708358765</v>
+        <v>15.1582717895508</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1053" t="n">
-        <v>13.8096027374268</v>
+        <v>13.8096036911011</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1054" t="n">
-        <v>13.8665885925293</v>
+        <v>13.8665895462036</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>13.7650003433228</v>
       </c>
       <c r="G1058" t="n">
-        <v>13.0735349655151</v>
+        <v>13.0735340118408</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G1059" t="n">
-        <v>13.0497903823853</v>
+        <v>13.0497894287109</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1060" t="n">
-        <v>12.9738092422485</v>
+        <v>12.9738082885742</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>12.6850004196167</v>
       </c>
       <c r="G1062" t="n">
-        <v>12.0477867126465</v>
+        <v>12.0477876663208</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>11.875</v>
       </c>
       <c r="G1063" t="n">
-        <v>11.2784767150879</v>
+        <v>11.2784757614136</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1064" t="n">
-        <v>10.656379699707</v>
+        <v>10.6563787460327</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>11.3549995422363</v>
       </c>
       <c r="G1065" t="n">
-        <v>10.7845964431763</v>
+        <v>10.7845973968506</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>9.5620002746582</v>
       </c>
       <c r="G1066" t="n">
-        <v>9.08166599273682</v>
+        <v>9.08166694641113</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>10.164999961853</v>
       </c>
       <c r="G1067" t="n">
-        <v>9.65437507629395</v>
+        <v>9.65437602996826</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>10</v>
       </c>
       <c r="G1070" t="n">
-        <v>9.4976634979248</v>
+        <v>9.49766445159912</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1071" t="n">
-        <v>10.6183881759644</v>
+        <v>10.6183891296387</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1072" t="n">
-        <v>11.8625822067261</v>
+        <v>11.8625812530518</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1074" t="n">
-        <v>13.0877809524536</v>
+        <v>13.0877799987793</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>14.1049995422363</v>
       </c>
       <c r="G1075" t="n">
-        <v>13.3964538574219</v>
+        <v>13.3964548110962</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1077" t="n">
-        <v>12.2519855499268</v>
+        <v>12.2519865036011</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1079" t="n">
-        <v>11.4921741485596</v>
+        <v>11.4921731948853</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1080" t="n">
-        <v>11.2072429656982</v>
+        <v>11.2072439193726</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>11.75</v>
       </c>
       <c r="G1081" t="n">
-        <v>11.1597557067871</v>
+        <v>11.1597547531128</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1083" t="n">
-        <v>11.5681552886963</v>
+        <v>11.568154335022</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1086" t="n">
-        <v>11.8625822067261</v>
+        <v>11.8625812530518</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G1087" t="n">
-        <v>11.9765539169312</v>
+        <v>11.9765529632568</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1088" t="n">
-        <v>11.4541835784912</v>
+        <v>11.4541826248169</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>11.4921741485596</v>
+        <v>11.4921731948853</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>10.3999404907227</v>
+        <v>10.399941444397</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>11</v>
       </c>
       <c r="G1094" t="n">
-        <v>10.4474306106567</v>
+        <v>10.4474296569824</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G1095" t="n">
-        <v>10.3809461593628</v>
+        <v>10.3809471130371</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1096" t="n">
-        <v>10.6183881759644</v>
+        <v>10.6183891296387</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G1098" t="n">
-        <v>10.9128160476685</v>
+        <v>10.9128150939941</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1099" t="n">
-        <v>10.7228622436523</v>
+        <v>10.722861289978</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G1103" t="n">
-        <v>10.3429555892944</v>
+        <v>10.3429565429688</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1108" t="n">
-        <v>10.0295324325562</v>
+        <v>10.0295333862305</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G1109" t="n">
-        <v>9.90606307983398</v>
+        <v>9.9060640335083</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1111" t="n">
-        <v>10.3999404907227</v>
+        <v>10.399941444397</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G1112" t="n">
-        <v>9.90606307983398</v>
+        <v>9.9060640335083</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1113" t="n">
-        <v>9.89656543731689</v>
+        <v>9.89656639099121</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G1114" t="n">
-        <v>9.64962577819824</v>
+        <v>9.64962673187256</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1116" t="n">
-        <v>10.4949178695679</v>
+        <v>10.4949188232422</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1117" t="n">
-        <v>10.6183881759644</v>
+        <v>10.6183891296387</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G1119" t="n">
-        <v>11.9005718231201</v>
+        <v>11.9005727767944</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1120" t="n">
-        <v>11.8625822067261</v>
+        <v>11.8625812530518</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G1125" t="n">
-        <v>13.2872304916382</v>
+        <v>13.2872314453125</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>13.1542644500732</v>
+        <v>13.1542654037476</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>13.5</v>
       </c>
       <c r="G1127" t="n">
-        <v>12.8218469619751</v>
+        <v>12.8218460083008</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G1128" t="n">
-        <v>11.8815774917603</v>
+        <v>11.8815784454346</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1129" t="n">
-        <v>11.7771034240723</v>
+        <v>11.7771024703979</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1131" t="n">
-        <v>12.1190195083618</v>
+        <v>12.1190185546875</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1132" t="n">
-        <v>12.2899761199951</v>
+        <v>12.2899770736694</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1133" t="n">
-        <v>12.3089714050293</v>
+        <v>12.3089723587036</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>13.25</v>
       </c>
       <c r="G1136" t="n">
-        <v>12.5844049453735</v>
+        <v>12.5844039916992</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1139" t="n">
-        <v>11.5111694335938</v>
+        <v>11.5111684799194</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1140" t="n">
-        <v>11.7296152114868</v>
+        <v>11.7296142578125</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1144" t="n">
-        <v>11.4541835784912</v>
+        <v>11.4541826248169</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1145" t="n">
-        <v>11.5871496200562</v>
+        <v>11.5871486663818</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>11.75</v>
       </c>
       <c r="G1148" t="n">
-        <v>11.1597557067871</v>
+        <v>11.1597547531128</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.9887962341309</v>
+        <v>10.9887971878052</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1151" t="n">
-        <v>10.9887962341309</v>
+        <v>10.9887971878052</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1153" t="n">
-        <v>11.2262372970581</v>
+        <v>11.2262382507324</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1154" t="n">
-        <v>11.2262372970581</v>
+        <v>11.2262382507324</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.2452335357666</v>
+        <v>11.2452344894409</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G1157" t="n">
-        <v>11.1027688980103</v>
+        <v>11.1027679443359</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1158" t="n">
-        <v>11.1312627792358</v>
+        <v>11.1312618255615</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1161" t="n">
-        <v>10.8368349075317</v>
+        <v>10.8368339538574</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1165" t="n">
-        <v>10.6183881759644</v>
+        <v>10.6183891296387</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1167" t="n">
-        <v>10.8368349075317</v>
+        <v>10.8368339538574</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G1170" t="n">
-        <v>10.3619508743286</v>
+        <v>10.3619518280029</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>11.75</v>
       </c>
       <c r="G1171" t="n">
-        <v>11.1597557067871</v>
+        <v>11.1597547531128</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1174" t="n">
-        <v>11.3307132720947</v>
+        <v>11.3307123184204</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G1176" t="n">
-        <v>11.1027688980103</v>
+        <v>11.1027679443359</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1177" t="n">
-        <v>10.9603033065796</v>
+        <v>10.9603042602539</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G1178" t="n">
-        <v>10.7608528137207</v>
+        <v>10.760853767395</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1179" t="n">
-        <v>10.656379699707</v>
+        <v>10.6563787460327</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>10.7798500061035</v>
+        <v>10.7798490524292</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>12</v>
       </c>
       <c r="G1186" t="n">
-        <v>11.3971977233887</v>
+        <v>11.3971967697144</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1188" t="n">
-        <v>11.7960987091064</v>
+        <v>11.7960977554321</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1189" t="n">
-        <v>11.4921741485596</v>
+        <v>11.4921731948853</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1193" t="n">
-        <v>11.4541835784912</v>
+        <v>11.4541826248169</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>11.5871496200562</v>
+        <v>11.5871486663818</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1197" t="n">
-        <v>12.5179204940796</v>
+        <v>12.5179214477539</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1199" t="n">
-        <v>12.0810279846191</v>
+        <v>12.0810289382935</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>11.4921741485596</v>
+        <v>11.4921731948853</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1201" t="n">
-        <v>11.5681552886963</v>
+        <v>11.568154335022</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>12.75</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.1095218658447</v>
+        <v>12.1095209121704</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>12.0145435333252</v>
+        <v>12.0145444869995</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G1207" t="n">
-        <v>11.9385623931885</v>
+        <v>11.9385633468628</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G1208" t="n">
-        <v>11.9575576782227</v>
+        <v>11.957558631897</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1209" t="n">
-        <v>11.9860515594482</v>
+        <v>11.9860506057739</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.1285181045532</v>
+        <v>12.1285171508789</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1212" t="n">
-        <v>12.2804794311523</v>
+        <v>12.2804803848267</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>13.25</v>
       </c>
       <c r="G1215" t="n">
-        <v>12.5844049453735</v>
+        <v>12.5844039916992</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G1217" t="n">
-        <v>12.5464134216309</v>
+        <v>12.5464143753052</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1219" t="n">
-        <v>12.4039487838745</v>
+        <v>12.4039497375488</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>12.0145435333252</v>
+        <v>12.0145444869995</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1221" t="n">
-        <v>11.8625822067261</v>
+        <v>11.8625812530518</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1222" t="n">
-        <v>12.8978271484375</v>
+        <v>12.8978281021118</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G1225" t="n">
-        <v>11.67262840271</v>
+        <v>11.6726293563843</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G1229" t="n">
-        <v>10.5139131546021</v>
+        <v>10.5139141082764</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G1230" t="n">
-        <v>10.7988443374634</v>
+        <v>10.7988433837891</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1232" t="n">
-        <v>11.0647783279419</v>
+        <v>11.0647773742676</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1238" t="n">
-        <v>12.8978271484375</v>
+        <v>12.8978281021118</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1240" t="n">
-        <v>13.7146263122559</v>
+        <v>13.7146253585815</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1246" t="n">
-        <v>14.6264019012451</v>
+        <v>14.6264009475708</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1247" t="n">
-        <v>14.6264019012451</v>
+        <v>14.6264009475708</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1249" t="n">
-        <v>14.1515197753906</v>
+        <v>14.1515188217163</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1251" t="n">
-        <v>14.4269504547119</v>
+        <v>14.4269514083862</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G1252" t="n">
-        <v>14.4649410247803</v>
+        <v>14.4649419784546</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1254" t="n">
-        <v>14.4269504547119</v>
+        <v>14.4269514083862</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1257" t="n">
-        <v>14.4934358596802</v>
+        <v>14.4934349060059</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G1259" t="n">
-        <v>14.5979080200195</v>
+        <v>14.5979089736938</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1260" t="n">
-        <v>14.7498722076416</v>
+        <v>14.7498712539673</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1265" t="n">
-        <v>14.3794641494751</v>
+        <v>14.3794622421265</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G1269" t="n">
-        <v>15.1107835769653</v>
+        <v>15.110782623291</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1271" t="n">
-        <v>14.9493217468262</v>
+        <v>14.9493227005005</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1272" t="n">
-        <v>14.7688684463501</v>
+        <v>14.7688674926758</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1275" t="n">
-        <v>14.5884113311768</v>
+        <v>14.5884103775024</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1282" t="n">
-        <v>14.3794641494751</v>
+        <v>14.3794622421265</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1285" t="n">
-        <v>15.29123878479</v>
+        <v>15.2912397384644</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1286" t="n">
-        <v>14.6833877563477</v>
+        <v>14.683388710022</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>15.0537977218628</v>
+        <v>15.0537967681885</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1288" t="n">
-        <v>15.8041133880615</v>
+        <v>15.8041124343872</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>16.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>15.6711454391479</v>
+        <v>15.6711444854736</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1294" t="n">
-        <v>14.7688684463501</v>
+        <v>14.7688674926758</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1295" t="n">
-        <v>14.6358995437622</v>
+        <v>14.6359004974365</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1296" t="n">
-        <v>14.6264019012451</v>
+        <v>14.6264009475708</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1299" t="n">
-        <v>14.7403755187988</v>
+        <v>14.7403745651245</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1302" t="n">
-        <v>15.0822896957397</v>
+        <v>15.0822906494141</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>15.7700004577637</v>
       </c>
       <c r="G1303" t="n">
-        <v>14.9778165817261</v>
+        <v>14.9778156280518</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G1304" t="n">
-        <v>14.6928853988647</v>
+        <v>14.6928863525391</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G1306" t="n">
-        <v>14.8258533477783</v>
+        <v>14.825852394104</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1307" t="n">
-        <v>14.7688684463501</v>
+        <v>14.7688674926758</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1310" t="n">
-        <v>15.1202812194824</v>
+        <v>15.1202802658081</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G1315" t="n">
-        <v>14.8448486328125</v>
+        <v>14.8448476791382</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1316" t="n">
-        <v>14.9873132705688</v>
+        <v>14.9873123168945</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1318" t="n">
-        <v>15.8705959320068</v>
+        <v>15.8705949783325</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1322" t="n">
-        <v>15.9370794296265</v>
+        <v>15.9370803833008</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1323" t="n">
-        <v>15.8800926208496</v>
+        <v>15.8800916671753</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>15.7376279830933</v>
+        <v>15.7376298904419</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1327" t="n">
-        <v>15.7091360092163</v>
+        <v>15.7091369628906</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1329" t="n">
-        <v>15.3102340698242</v>
+        <v>15.3102350234985</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1333" t="n">
-        <v>15.5381784439087</v>
+        <v>15.538179397583</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>16.5149993896484</v>
       </c>
       <c r="G1334" t="n">
-        <v>15.6853914260864</v>
+        <v>15.6853904724121</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G1335" t="n">
-        <v>15.9608240127563</v>
+        <v>15.9608249664307</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>16.2450008392334</v>
       </c>
       <c r="G1337" t="n">
-        <v>15.428955078125</v>
+        <v>15.4289560317993</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>16.4650001525879</v>
       </c>
       <c r="G1338" t="n">
-        <v>15.6379022598267</v>
+        <v>15.6379041671753</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1341" t="n">
-        <v>16.696891784668</v>
+        <v>16.6968936920166</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>17.7649993896484</v>
       </c>
       <c r="G1344" t="n">
-        <v>16.8725986480713</v>
+        <v>16.8726005554199</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>17.9349994659424</v>
       </c>
       <c r="G1346" t="n">
-        <v>17.0340595245361</v>
+        <v>17.0340576171875</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G1349" t="n">
-        <v>17.3854732513428</v>
+        <v>17.3854751586914</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1350" t="n">
-        <v>17.0388107299805</v>
+        <v>17.0388088226318</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>17.9850006103516</v>
       </c>
       <c r="G1352" t="n">
-        <v>17.0815486907959</v>
+        <v>17.0815467834473</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1353" t="n">
-        <v>16.9248371124268</v>
+        <v>16.9248352050781</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1354" t="n">
-        <v>17.0245628356934</v>
+        <v>17.0245609283447</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>17.875</v>
       </c>
       <c r="G1355" t="n">
-        <v>16.9770755767822</v>
+        <v>16.9770736694336</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1356" t="n">
-        <v>17.5421848297119</v>
+        <v>17.5421829223633</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>18.7450008392334</v>
       </c>
       <c r="G1359" t="n">
-        <v>17.803373336792</v>
+        <v>17.8033714294434</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>19.1749992370605</v>
       </c>
       <c r="G1361" t="n">
-        <v>18.2117710113525</v>
+        <v>18.2117691040039</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1363" t="n">
-        <v>18.1975250244141</v>
+        <v>18.1975231170654</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1366" t="n">
-        <v>17.9315891265869</v>
+        <v>17.9315872192383</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>18.9050006866455</v>
       </c>
       <c r="G1369" t="n">
-        <v>17.9553356170654</v>
+        <v>17.9553337097168</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1370" t="n">
-        <v>17.6846523284912</v>
+        <v>17.6846504211426</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G1375" t="n">
-        <v>18.3209953308105</v>
+        <v>18.3209934234619</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G1378" t="n">
-        <v>18.3542346954346</v>
+        <v>18.3542366027832</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G1380" t="n">
-        <v>18.5299415588379</v>
+        <v>18.5299434661865</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G1382" t="n">
-        <v>18.3542346954346</v>
+        <v>18.3542366027832</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>19.2649993896484</v>
       </c>
       <c r="G1383" t="n">
-        <v>18.297248840332</v>
+        <v>18.2972469329834</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G1384" t="n">
-        <v>18.3209953308105</v>
+        <v>18.3209934234619</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1385" t="n">
-        <v>18.1690311431885</v>
+        <v>18.1690292358398</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1386" t="n">
-        <v>18.1690311431885</v>
+        <v>18.1690292358398</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1387" t="n">
-        <v>18.1690311431885</v>
+        <v>18.1690292358398</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1392" t="n">
-        <v>18.5584354400635</v>
+        <v>18.5584373474121</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>18.0450000762939</v>
       </c>
       <c r="G1396" t="n">
-        <v>17.1385345458984</v>
+        <v>17.1385364532471</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1398" t="n">
-        <v>17.2287616729736</v>
+        <v>17.2287635803223</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G1399" t="n">
-        <v>17.1812725067139</v>
+        <v>17.1812744140625</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>18.0650005340576</v>
       </c>
       <c r="G1401" t="n">
-        <v>17.1575298309326</v>
+        <v>17.1575317382812</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G1402" t="n">
-        <v>16.6114139556885</v>
+        <v>16.6114120483398</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>17.375</v>
       </c>
       <c r="G1403" t="n">
-        <v>16.5021915435791</v>
+        <v>16.5021896362305</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1404" t="n">
-        <v>16.696891784668</v>
+        <v>16.6968936920166</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>17.3449993133545</v>
       </c>
       <c r="G1414" t="n">
-        <v>16.4736957550049</v>
+        <v>16.4736976623535</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>16.8950004577637</v>
       </c>
       <c r="G1416" t="n">
-        <v>16.0463047027588</v>
+        <v>16.0463027954102</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G1417" t="n">
-        <v>16.0368061065674</v>
+        <v>16.0368041992188</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>16.8449993133545</v>
       </c>
       <c r="G1418" t="n">
-        <v>15.9988145828247</v>
+        <v>15.9988136291504</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>16.9150009155273</v>
       </c>
       <c r="G1422" t="n">
-        <v>16.065299987793</v>
+        <v>16.0652980804443</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G1426" t="n">
-        <v>18.4919509887695</v>
+        <v>18.4919528961182</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>18.5949993133545</v>
       </c>
       <c r="G1428" t="n">
-        <v>17.6609039306641</v>
+        <v>17.6609058380127</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>17</v>
       </c>
       <c r="G1434" t="n">
-        <v>16.1460285186768</v>
+        <v>16.1460266113281</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G1435" t="n">
-        <v>15.9275827407837</v>
+        <v>15.9275808334351</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1436" t="n">
-        <v>15.8041133880615</v>
+        <v>15.8041124343872</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>17.5349998474121</v>
       </c>
       <c r="G1439" t="n">
-        <v>16.6541519165039</v>
+        <v>16.6541538238525</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1441" t="n">
-        <v>16.5734252929688</v>
+        <v>16.5734233856201</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>17.9349994659424</v>
       </c>
       <c r="G1445" t="n">
-        <v>17.0340595245361</v>
+        <v>17.0340576171875</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>18.8150005340576</v>
       </c>
       <c r="G1447" t="n">
-        <v>17.8698539733887</v>
+        <v>17.8698558807373</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1452" t="n">
-        <v>16.696891784668</v>
+        <v>16.6968936920166</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1458" t="n">
-        <v>17.0245628356934</v>
+        <v>17.0245609283447</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1460" t="n">
-        <v>16.8298587799072</v>
+        <v>16.8298606872559</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>17.9850006103516</v>
       </c>
       <c r="G1463" t="n">
-        <v>17.0815486907959</v>
+        <v>17.0815467834473</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1465" t="n">
-        <v>17.0245628356934</v>
+        <v>17.0245609283447</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>17.9449996948242</v>
       </c>
       <c r="G1467" t="n">
-        <v>17.0435581207275</v>
+        <v>17.0435562133789</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>17.5949993133545</v>
       </c>
       <c r="G1469" t="n">
-        <v>16.7111377716064</v>
+        <v>16.7111396789551</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G1472" t="n">
-        <v>17.2002716064453</v>
+        <v>17.2002696990967</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1473" t="n">
-        <v>17.2287616729736</v>
+        <v>17.2287635803223</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1475" t="n">
-        <v>17.0388107299805</v>
+        <v>17.0388088226318</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>18.125</v>
       </c>
       <c r="G1478" t="n">
-        <v>17.2145175933838</v>
+        <v>17.2145156860352</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>18.3649997711182</v>
       </c>
       <c r="G1479" t="n">
-        <v>17.4424610137939</v>
+        <v>17.4424591064453</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1480" t="n">
-        <v>17.2857475280762</v>
+        <v>17.2857494354248</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G1481" t="n">
-        <v>17.1812725067139</v>
+        <v>17.1812744140625</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G1488" t="n">
-        <v>18.7009010314941</v>
+        <v>18.7008991241455</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.7911281585693</v>
+        <v>18.7911262512207</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1491" t="n">
-        <v>18.1690311431885</v>
+        <v>18.1690292358398</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1492" t="n">
-        <v>17.945837020874</v>
+        <v>17.9458351135254</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>19.7549991607666</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.7626342773438</v>
+        <v>18.7626323699951</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>18.92409324646</v>
+        <v>18.9240951538086</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1499" t="n">
-        <v>19.1662864685059</v>
+        <v>19.1662845611572</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1500" t="n">
-        <v>19.1662864685059</v>
+        <v>19.1662845611572</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G1504" t="n">
-        <v>19.6221752166748</v>
+        <v>19.6221733093262</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1505" t="n">
-        <v>19.1377925872803</v>
+        <v>19.1377906799316</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G1506" t="n">
-        <v>19.6316719055176</v>
+        <v>19.6316699981689</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G1509" t="n">
-        <v>19.7456436157227</v>
+        <v>19.7456455230713</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1512" t="n">
-        <v>21.0373229980469</v>
+        <v>21.0373268127441</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1513" t="n">
-        <v>21.4457244873047</v>
+        <v>21.4457225799561</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1514" t="n">
-        <v>20.9898357391357</v>
+        <v>20.9898376464844</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1515" t="n">
-        <v>20.7523956298828</v>
+        <v>20.7523975372314</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G1516" t="n">
-        <v>20.6384220123291</v>
+        <v>20.6384239196777</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G1518" t="n">
-        <v>20.0970573425293</v>
+        <v>20.0970554351807</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G1521" t="n">
-        <v>21.0278263092041</v>
+        <v>21.0278282165527</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1522" t="n">
-        <v>21.0373229980469</v>
+        <v>21.0373268127441</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G1526" t="n">
-        <v>21.3982372283936</v>
+        <v>21.3982353210449</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G1528" t="n">
-        <v>21.5691928863525</v>
+        <v>21.5691947937012</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G1530" t="n">
-        <v>21.5976886749268</v>
+        <v>21.5976867675781</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G1532" t="n">
-        <v>19.7171497344971</v>
+        <v>19.7171478271484</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G1534" t="n">
-        <v>19.0998001098633</v>
+        <v>19.0998020172119</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G1537" t="n">
-        <v>19.6221752166748</v>
+        <v>19.6221733093262</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G1539" t="n">
-        <v>19.0998001098633</v>
+        <v>19.0998020172119</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1543" t="n">
-        <v>17.5421848297119</v>
+        <v>17.5421829223633</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>18.3649997711182</v>
       </c>
       <c r="G1546" t="n">
-        <v>17.4424610137939</v>
+        <v>17.4424591064453</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>18.9249992370605</v>
       </c>
       <c r="G1547" t="n">
-        <v>17.974328994751</v>
+        <v>17.9743270874023</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>19.5750007629395</v>
       </c>
       <c r="G1548" t="n">
-        <v>18.5916767120361</v>
+        <v>18.5916786193848</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1551" t="n">
-        <v>17.945837020874</v>
+        <v>17.9458351135254</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G1553" t="n">
-        <v>18.0503082275391</v>
+        <v>18.0503101348877</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G1559" t="n">
-        <v>18.68190574646</v>
+        <v>18.6819038391113</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>19.7950000762939</v>
       </c>
       <c r="G1561" t="n">
-        <v>18.8006267547607</v>
+        <v>18.8006248474121</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1562" t="n">
-        <v>18.5964241027832</v>
+        <v>18.5964260101318</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G1565" t="n">
-        <v>17.9220924377441</v>
+        <v>17.9220905303955</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>18.5650005340576</v>
       </c>
       <c r="G1568" t="n">
-        <v>17.6324119567871</v>
+        <v>17.6324138641357</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>15.6149997711182</v>
       </c>
       <c r="G1572" t="n">
-        <v>14.8306007385254</v>
+        <v>14.8306016921997</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>15.2749996185303</v>
       </c>
       <c r="G1573" t="n">
-        <v>14.5076808929443</v>
+        <v>14.5076818466187</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1575" t="n">
-        <v>15.2722425460815</v>
+        <v>15.2722434997559</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>16.1650009155273</v>
       </c>
       <c r="G1576" t="n">
-        <v>15.3529748916626</v>
+        <v>15.3529739379883</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>16.2749996185303</v>
       </c>
       <c r="G1577" t="n">
-        <v>15.4574489593506</v>
+        <v>15.457447052002</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1580" t="n">
-        <v>15.7043857574463</v>
+        <v>15.7043867111206</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1581" t="n">
-        <v>15.8611001968384</v>
+        <v>15.8610982894897</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1582" t="n">
-        <v>15.81360912323</v>
+        <v>15.8136100769043</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>16.0450000762939</v>
       </c>
       <c r="G1584" t="n">
-        <v>15.2390022277832</v>
+        <v>15.2390012741089</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1585" t="n">
-        <v>15.2532472610474</v>
+        <v>15.253246307373</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1586" t="n">
-        <v>15.5191822052002</v>
+        <v>15.5191831588745</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>16.6650009155273</v>
       </c>
       <c r="G1587" t="n">
-        <v>15.8278579711914</v>
+        <v>15.8278589248657</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1592" t="n">
-        <v>15.9750699996948</v>
+        <v>15.9750709533691</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1595" t="n">
-        <v>14.5884113311768</v>
+        <v>14.5884103775024</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1596" t="n">
-        <v>14.9493217468262</v>
+        <v>14.9493227005005</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1599" t="n">
-        <v>15.4811916351318</v>
+        <v>15.4811906814575</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1600" t="n">
-        <v>15.6331548690796</v>
+        <v>15.633152961731</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1601" t="n">
-        <v>15.6521492004395</v>
+        <v>15.6521482467651</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1606" t="n">
-        <v>14.7403755187988</v>
+        <v>14.7403745651245</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1608" t="n">
-        <v>15.1392755508423</v>
+        <v>15.1392765045166</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1609" t="n">
-        <v>15.7851190567017</v>
+        <v>15.7851181030273</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>16.5</v>
       </c>
       <c r="G1610" t="n">
-        <v>15.6711454391479</v>
+        <v>15.6711444854736</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G1611" t="n">
-        <v>15.0348024368286</v>
+        <v>15.0348014831543</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1614" t="n">
-        <v>14.3224773406982</v>
+        <v>14.3224763870239</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1618" t="n">
-        <v>14.1990070343018</v>
+        <v>14.1990079879761</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1619" t="n">
-        <v>14.9493217468262</v>
+        <v>14.9493227005005</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G1625" t="n">
-        <v>14.8327665328979</v>
+        <v>14.8327655792236</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1627" t="n">
-        <v>14.6870594024658</v>
+        <v>14.6870603561401</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1628" t="n">
-        <v>15.075608253479</v>
+        <v>15.0756072998047</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1632" t="n">
-        <v>15.8915548324585</v>
+        <v>15.8915557861328</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1633" t="n">
-        <v>15.9886913299561</v>
+        <v>15.9886903762817</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1635" t="n">
-        <v>15.9692649841309</v>
+        <v>15.9692640304565</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1640" t="n">
-        <v>13.7545490264893</v>
+        <v>13.7545480728149</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1643" t="n">
-        <v>13.366003036499</v>
+        <v>13.3660020828247</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1644" t="n">
-        <v>13.7254085540771</v>
+        <v>13.7254076004028</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>13.9391078948975</v>
+        <v>13.9391088485718</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1667" t="n">
-        <v>15.6972818374634</v>
+        <v>15.6972808837891</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1669" t="n">
-        <v>16.2315330505371</v>
+        <v>16.2315311431885</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1672" t="n">
-        <v>15.8721265792847</v>
+        <v>15.872127532959</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1676" t="n">
-        <v>16.4646625518799</v>
+        <v>16.4646606445312</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1685" t="n">
-        <v>17.0960483551025</v>
+        <v>17.0960502624512</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1686" t="n">
-        <v>16.950345993042</v>
+        <v>16.9503440856934</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1693" t="n">
-        <v>16.0664005279541</v>
+        <v>16.0664024353027</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>16.1100006103516</v>
       </c>
       <c r="G1695" t="n">
-        <v>15.6487131118774</v>
+        <v>15.6487140655518</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1696" t="n">
-        <v>15.6001443862915</v>
+        <v>15.6001434326172</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1704" t="n">
-        <v>15.1727428436279</v>
+        <v>15.1727437973022</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>14.75</v>
       </c>
       <c r="G1709" t="n">
-        <v>14.3276538848877</v>
+        <v>14.327654838562</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1715" t="n">
-        <v>13.5408477783203</v>
+        <v>13.540846824646</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1716" t="n">
-        <v>13.9391078948975</v>
+        <v>13.9391088485718</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1744" t="n">
-        <v>14.823052406311</v>
+        <v>14.8230514526367</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1749" t="n">
-        <v>16.2315330505371</v>
+        <v>16.2315311431885</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1752" t="n">
-        <v>15.9304103851318</v>
+        <v>15.9304094314575</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1754" t="n">
-        <v>15.9789791107178</v>
+        <v>15.9789781570435</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G1759" t="n">
-        <v>15.7652759552002</v>
+        <v>15.7652769088745</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1761" t="n">
-        <v>16.5229434967041</v>
+        <v>16.5229415893555</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1764" t="n">
-        <v>16.8434925079346</v>
+        <v>16.8434944152832</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1777" t="n">
-        <v>15.9789791107178</v>
+        <v>15.9789781570435</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1780" t="n">
-        <v>15.9789791107178</v>
+        <v>15.9789781570435</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1781" t="n">
-        <v>16.163537979126</v>
+        <v>16.1635360717773</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1798" t="n">
-        <v>17.795431137085</v>
+        <v>17.7954330444336</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1799" t="n">
-        <v>17.9119968414307</v>
+        <v>17.9119987487793</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G1800" t="n">
-        <v>18.038272857666</v>
+        <v>18.0382747650146</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G1829" t="n">
-        <v>18.038272857666</v>
+        <v>18.0382747650146</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1833" t="n">
-        <v>16.5229434967041</v>
+        <v>16.5229415893555</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1835" t="n">
-        <v>16.3189544677734</v>
+        <v>16.3189563751221</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1836" t="n">
-        <v>16.5812244415283</v>
+        <v>16.581226348877</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1845" t="n">
-        <v>16.0761127471924</v>
+        <v>16.076114654541</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1851" t="n">
-        <v>16.0664005279541</v>
+        <v>16.0664024353027</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1860" t="n">
-        <v>15.8818407058716</v>
+        <v>15.8818416595459</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1861" t="n">
-        <v>15.7361373901367</v>
+        <v>15.7361364364624</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1867" t="n">
-        <v>15.6778526306152</v>
+        <v>15.6778535842896</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1872" t="n">
-        <v>15.075608253479</v>
+        <v>15.0756072998047</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1873" t="n">
-        <v>15.0853204727173</v>
+        <v>15.085319519043</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1879" t="n">
-        <v>14.706488609314</v>
+        <v>14.7064876556396</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>7.08500003814697</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>388148</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>7.36499977111816</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>7.0149998664856</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>7.11499977111816</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>7.2649998664856</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>7.2649998664856</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -427,7 +427,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G2" t="n">
-        <v>18.2763519287109</v>
+        <v>18.2763500213623</v>
       </c>
       <c r="H2" t="n">
         <v>1705033</v>
@@ -456,7 +456,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G3" t="n">
-        <v>18.0109634399414</v>
+        <v>18.01096534729</v>
       </c>
       <c r="H3" t="n">
         <v>997627</v>
@@ -514,7 +514,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>17.9401969909668</v>
+        <v>17.9401950836182</v>
       </c>
       <c r="H5" t="n">
         <v>1381959</v>
@@ -572,7 +572,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G7" t="n">
-        <v>18.2498111724854</v>
+        <v>18.2498092651367</v>
       </c>
       <c r="H7" t="n">
         <v>1189444</v>
@@ -630,7 +630,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G9" t="n">
-        <v>19.1344356536865</v>
+        <v>19.1344394683838</v>
       </c>
       <c r="H9" t="n">
         <v>1367537</v>
@@ -659,7 +659,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G10" t="n">
-        <v>18.8425121307373</v>
+        <v>18.84250831604</v>
       </c>
       <c r="H10" t="n">
         <v>1053164</v>
@@ -688,7 +688,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G11" t="n">
-        <v>18.462121963501</v>
+        <v>18.4621238708496</v>
       </c>
       <c r="H11" t="n">
         <v>802632</v>
@@ -746,7 +746,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G13" t="n">
-        <v>18.0994262695312</v>
+        <v>18.0994243621826</v>
       </c>
       <c r="H13" t="n">
         <v>975727</v>
@@ -775,7 +775,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G14" t="n">
-        <v>17.6394214630127</v>
+        <v>17.6394233703613</v>
       </c>
       <c r="H14" t="n">
         <v>943974</v>
@@ -833,7 +833,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G16" t="n">
-        <v>18.1878910064697</v>
+        <v>18.1878871917725</v>
       </c>
       <c r="H16" t="n">
         <v>813843</v>
@@ -862,7 +862,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G17" t="n">
-        <v>18.0994262695312</v>
+        <v>18.0994243621826</v>
       </c>
       <c r="H17" t="n">
         <v>476663</v>
@@ -920,7 +920,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>18.2232761383057</v>
+        <v>18.223274230957</v>
       </c>
       <c r="H19" t="n">
         <v>550218</v>
@@ -978,7 +978,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G21" t="n">
-        <v>18.3913536071777</v>
+        <v>18.3913516998291</v>
       </c>
       <c r="H21" t="n">
         <v>1957322</v>
@@ -1036,7 +1036,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>17.9578857421875</v>
+        <v>17.9578838348389</v>
       </c>
       <c r="H23" t="n">
         <v>725076</v>
@@ -1094,7 +1094,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G25" t="n">
-        <v>18.2586574554443</v>
+        <v>18.2586612701416</v>
       </c>
       <c r="H25" t="n">
         <v>716525</v>
@@ -1123,7 +1123,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G26" t="n">
-        <v>18.0817337036133</v>
+        <v>18.0817356109619</v>
       </c>
       <c r="H26" t="n">
         <v>1482038</v>
@@ -1181,7 +1181,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G28" t="n">
-        <v>16.9051837921143</v>
+        <v>16.9051818847656</v>
       </c>
       <c r="H28" t="n">
         <v>908164</v>
@@ -1210,7 +1210,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>17.1617221832275</v>
+        <v>17.1617202758789</v>
       </c>
       <c r="H29" t="n">
         <v>741895</v>
@@ -1297,7 +1297,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G32" t="n">
-        <v>17.4890365600586</v>
+        <v>17.4890384674072</v>
       </c>
       <c r="H32" t="n">
         <v>658925</v>
@@ -1326,7 +1326,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G33" t="n">
-        <v>17.6305732727051</v>
+        <v>17.6305751800537</v>
       </c>
       <c r="H33" t="n">
         <v>742916</v>
@@ -1384,7 +1384,7 @@
         <v>20.8099994659424</v>
       </c>
       <c r="G35" t="n">
-        <v>18.4090461730957</v>
+        <v>18.4090442657471</v>
       </c>
       <c r="H35" t="n">
         <v>656330</v>
@@ -1471,7 +1471,7 @@
         <v>20.5</v>
       </c>
       <c r="G38" t="n">
-        <v>18.1348133087158</v>
+        <v>18.1348114013672</v>
       </c>
       <c r="H38" t="n">
         <v>591716</v>
@@ -1587,7 +1587,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G42" t="n">
-        <v>18.3471183776855</v>
+        <v>18.3471202850342</v>
       </c>
       <c r="H42" t="n">
         <v>557658</v>
@@ -1616,7 +1616,7 @@
         <v>21.5</v>
       </c>
       <c r="G43" t="n">
-        <v>19.0194339752197</v>
+        <v>19.019437789917</v>
       </c>
       <c r="H43" t="n">
         <v>1151116</v>
@@ -1645,7 +1645,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G44" t="n">
-        <v>19.0017433166504</v>
+        <v>19.001745223999</v>
       </c>
       <c r="H44" t="n">
         <v>479063</v>
@@ -1674,7 +1674,7 @@
         <v>21.3099994659424</v>
       </c>
       <c r="G45" t="n">
-        <v>18.8513565063477</v>
+        <v>18.8513603210449</v>
       </c>
       <c r="H45" t="n">
         <v>368675</v>
@@ -1703,7 +1703,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G46" t="n">
-        <v>19.3113613128662</v>
+        <v>19.3113632202148</v>
       </c>
       <c r="H46" t="n">
         <v>602537</v>
@@ -1761,7 +1761,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>19.9482917785645</v>
+        <v>19.9482898712158</v>
       </c>
       <c r="H48" t="n">
         <v>1078018</v>
@@ -1848,7 +1848,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G51" t="n">
-        <v>19.6475200653076</v>
+        <v>19.6475219726562</v>
       </c>
       <c r="H51" t="n">
         <v>599137</v>
@@ -1877,7 +1877,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G52" t="n">
-        <v>19.9836750030518</v>
+        <v>19.9836769104004</v>
       </c>
       <c r="H52" t="n">
         <v>593798</v>
@@ -1964,7 +1964,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G55" t="n">
-        <v>19.4440593719482</v>
+        <v>19.4440574645996</v>
       </c>
       <c r="H55" t="n">
         <v>774964</v>
@@ -2051,7 +2051,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G58" t="n">
-        <v>19.4971370697021</v>
+        <v>19.4971351623535</v>
       </c>
       <c r="H58" t="n">
         <v>1161092</v>
@@ -2196,7 +2196,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G63" t="n">
-        <v>19.8686771392822</v>
+        <v>19.8686752319336</v>
       </c>
       <c r="H63" t="n">
         <v>732706</v>
@@ -2225,7 +2225,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G64" t="n">
-        <v>19.4971370697021</v>
+        <v>19.4971351623535</v>
       </c>
       <c r="H64" t="n">
         <v>538910</v>
@@ -2254,7 +2254,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G65" t="n">
-        <v>19.417516708374</v>
+        <v>19.4175186157227</v>
       </c>
       <c r="H65" t="n">
         <v>289674</v>
@@ -2283,7 +2283,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G66" t="n">
-        <v>18.8690509796143</v>
+        <v>18.8690490722656</v>
       </c>
       <c r="H66" t="n">
         <v>592054</v>
@@ -2312,7 +2312,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G67" t="n">
-        <v>18.833667755127</v>
+        <v>18.8336696624756</v>
       </c>
       <c r="H67" t="n">
         <v>490898</v>
@@ -2341,7 +2341,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G68" t="n">
-        <v>18.5151996612549</v>
+        <v>18.5152015686035</v>
       </c>
       <c r="H68" t="n">
         <v>449428</v>
@@ -2370,7 +2370,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>18.9309749603271</v>
+        <v>18.9309730529785</v>
       </c>
       <c r="H69" t="n">
         <v>499244</v>
@@ -2428,7 +2428,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G71" t="n">
-        <v>18.5240459442139</v>
+        <v>18.5240440368652</v>
       </c>
       <c r="H71" t="n">
         <v>1288923</v>
@@ -2457,7 +2457,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G72" t="n">
-        <v>19.3113613128662</v>
+        <v>19.3113632202148</v>
       </c>
       <c r="H72" t="n">
         <v>724111</v>
@@ -2486,7 +2486,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>18.9486656188965</v>
+        <v>18.9486637115479</v>
       </c>
       <c r="H73" t="n">
         <v>659167</v>
@@ -2602,7 +2602,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G77" t="n">
-        <v>18.8071269989014</v>
+        <v>18.8071250915527</v>
       </c>
       <c r="H77" t="n">
         <v>725644</v>
@@ -2631,7 +2631,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G78" t="n">
-        <v>18.3205814361572</v>
+        <v>18.3205833435059</v>
       </c>
       <c r="H78" t="n">
         <v>1645887</v>
@@ -2660,7 +2660,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>18.3648147583008</v>
+        <v>18.3648166656494</v>
       </c>
       <c r="H79" t="n">
         <v>1254692</v>
@@ -2689,7 +2689,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G80" t="n">
-        <v>17.8251914978027</v>
+        <v>17.8251934051514</v>
       </c>
       <c r="H80" t="n">
         <v>550622</v>
@@ -2718,7 +2718,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G81" t="n">
-        <v>18.0817337036133</v>
+        <v>18.0817356109619</v>
       </c>
       <c r="H81" t="n">
         <v>609476</v>
@@ -2776,7 +2776,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>18.3117351531982</v>
+        <v>18.3117370605469</v>
       </c>
       <c r="H83" t="n">
         <v>593433</v>
@@ -2805,7 +2805,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G84" t="n">
-        <v>17.8782691955566</v>
+        <v>17.878267288208</v>
       </c>
       <c r="H84" t="n">
         <v>570613</v>
@@ -2834,7 +2834,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>18.0021190643311</v>
+        <v>18.0021209716797</v>
       </c>
       <c r="H85" t="n">
         <v>455661</v>
@@ -2863,7 +2863,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G86" t="n">
-        <v>17.7190361022949</v>
+        <v>17.7190380096436</v>
       </c>
       <c r="H86" t="n">
         <v>401376</v>
@@ -2921,7 +2921,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G88" t="n">
-        <v>17.4448051452637</v>
+        <v>17.444803237915</v>
       </c>
       <c r="H88" t="n">
         <v>546914</v>
@@ -2979,7 +2979,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G90" t="n">
-        <v>17.5509586334229</v>
+        <v>17.5509605407715</v>
       </c>
       <c r="H90" t="n">
         <v>721711</v>
@@ -3008,7 +3008,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G91" t="n">
-        <v>17.9844264984131</v>
+        <v>17.9844245910645</v>
       </c>
       <c r="H91" t="n">
         <v>812214</v>
@@ -3037,7 +3037,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>17.6394214630127</v>
+        <v>17.6394233703613</v>
       </c>
       <c r="H92" t="n">
         <v>678917</v>
@@ -3095,7 +3095,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G94" t="n">
-        <v>18.833667755127</v>
+        <v>18.8336696624756</v>
       </c>
       <c r="H94" t="n">
         <v>1861606</v>
@@ -3211,7 +3211,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>17.7367305755615</v>
+        <v>17.7367286682129</v>
       </c>
       <c r="H98" t="n">
         <v>468652</v>
@@ -3269,7 +3269,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G100" t="n">
-        <v>17.5939388275146</v>
+        <v>17.593936920166</v>
       </c>
       <c r="H100" t="n">
         <v>369286</v>
@@ -3414,7 +3414,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G105" t="n">
-        <v>17.5939388275146</v>
+        <v>17.593936920166</v>
       </c>
       <c r="H105" t="n">
         <v>186318</v>
@@ -3443,7 +3443,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G106" t="n">
-        <v>17.4128360748291</v>
+        <v>17.4128379821777</v>
       </c>
       <c r="H106" t="n">
         <v>450576</v>
@@ -3472,7 +3472,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G107" t="n">
-        <v>17.304178237915</v>
+        <v>17.3041763305664</v>
       </c>
       <c r="H107" t="n">
         <v>353691</v>
@@ -3501,7 +3501,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>17.4762191772461</v>
+        <v>17.4762210845947</v>
       </c>
       <c r="H108" t="n">
         <v>367982</v>
@@ -3530,7 +3530,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G109" t="n">
-        <v>17.4762191772461</v>
+        <v>17.4762210845947</v>
       </c>
       <c r="H109" t="n">
         <v>426168</v>
@@ -3559,7 +3559,7 @@
         <v>19.25</v>
       </c>
       <c r="G110" t="n">
-        <v>17.4309463500977</v>
+        <v>17.4309482574463</v>
       </c>
       <c r="H110" t="n">
         <v>645536</v>
@@ -3588,7 +3588,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G111" t="n">
-        <v>17.4852771759033</v>
+        <v>17.4852752685547</v>
       </c>
       <c r="H111" t="n">
         <v>582475</v>
@@ -3617,7 +3617,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>17.747875213623</v>
+        <v>17.7478733062744</v>
       </c>
       <c r="H112" t="n">
         <v>286254</v>
@@ -3646,7 +3646,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G113" t="n">
-        <v>17.6844902038574</v>
+        <v>17.6844882965088</v>
       </c>
       <c r="H113" t="n">
         <v>347407</v>
@@ -3675,7 +3675,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G114" t="n">
-        <v>17.1502418518066</v>
+        <v>17.150239944458</v>
       </c>
       <c r="H114" t="n">
         <v>471820</v>
@@ -3733,7 +3733,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G116" t="n">
-        <v>16.543550491333</v>
+        <v>16.5435543060303</v>
       </c>
       <c r="H116" t="n">
         <v>483555</v>
@@ -3791,7 +3791,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G118" t="n">
-        <v>17.0778026580811</v>
+        <v>17.0777988433838</v>
       </c>
       <c r="H118" t="n">
         <v>634094</v>
@@ -3849,7 +3849,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G120" t="n">
-        <v>17.9380283355713</v>
+        <v>17.9380302429199</v>
       </c>
       <c r="H120" t="n">
         <v>766211</v>
@@ -3994,7 +3994,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>16.3896179199219</v>
+        <v>16.3896198272705</v>
       </c>
       <c r="H125" t="n">
         <v>973572</v>
@@ -4023,7 +4023,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G126" t="n">
-        <v>16.6793785095215</v>
+        <v>16.6793804168701</v>
       </c>
       <c r="H126" t="n">
         <v>635006</v>
@@ -4081,7 +4081,7 @@
         <v>18.25</v>
       </c>
       <c r="G128" t="n">
-        <v>16.5254402160645</v>
+        <v>16.5254421234131</v>
       </c>
       <c r="H128" t="n">
         <v>558415</v>
@@ -4110,7 +4110,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>16.6069374084473</v>
+        <v>16.6069355010986</v>
       </c>
       <c r="H129" t="n">
         <v>464956</v>
@@ -4139,7 +4139,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G130" t="n">
-        <v>16.8061485290527</v>
+        <v>16.8061504364014</v>
       </c>
       <c r="H130" t="n">
         <v>255804</v>
@@ -4168,7 +4168,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G131" t="n">
-        <v>16.8242588043213</v>
+        <v>16.8242607116699</v>
       </c>
       <c r="H131" t="n">
         <v>503139</v>
@@ -4371,7 +4371,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G138" t="n">
-        <v>17.1321315765381</v>
+        <v>17.1321277618408</v>
       </c>
       <c r="H138" t="n">
         <v>399511</v>
@@ -4429,7 +4429,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G140" t="n">
-        <v>17.1502418518066</v>
+        <v>17.150239944458</v>
       </c>
       <c r="H140" t="n">
         <v>545374</v>
@@ -4458,7 +4458,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>17.0325241088867</v>
+        <v>17.0325260162354</v>
       </c>
       <c r="H141" t="n">
         <v>247627</v>
@@ -4487,7 +4487,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>17.3403949737549</v>
+        <v>17.3403930664062</v>
       </c>
       <c r="H142" t="n">
         <v>734812</v>
@@ -4545,7 +4545,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G144" t="n">
-        <v>17.9018096923828</v>
+        <v>17.9018115997314</v>
       </c>
       <c r="H144" t="n">
         <v>551371</v>
@@ -4574,7 +4574,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G145" t="n">
-        <v>18.1372394561768</v>
+        <v>18.1372413635254</v>
       </c>
       <c r="H145" t="n">
         <v>615453</v>
@@ -4719,7 +4719,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G150" t="n">
-        <v>19.2147884368896</v>
+        <v>19.2147903442383</v>
       </c>
       <c r="H150" t="n">
         <v>859181</v>
@@ -4777,7 +4777,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G152" t="n">
-        <v>18.4994430541992</v>
+        <v>18.4994411468506</v>
       </c>
       <c r="H152" t="n">
         <v>1504019</v>
@@ -4806,7 +4806,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G153" t="n">
-        <v>18.2187347412109</v>
+        <v>18.2187366485596</v>
       </c>
       <c r="H153" t="n">
         <v>1091340</v>
@@ -4922,7 +4922,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G157" t="n">
-        <v>18.4994430541992</v>
+        <v>18.4994411468506</v>
       </c>
       <c r="H157" t="n">
         <v>593471</v>
@@ -5009,7 +5009,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G160" t="n">
-        <v>19.04274559021</v>
+        <v>19.0427436828613</v>
       </c>
       <c r="H160" t="n">
         <v>612736</v>
@@ -5096,7 +5096,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>18.4722766876221</v>
+        <v>18.4722747802734</v>
       </c>
       <c r="H163" t="n">
         <v>404764</v>
@@ -5125,7 +5125,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G164" t="n">
-        <v>18.6171569824219</v>
+        <v>18.6171550750732</v>
       </c>
       <c r="H164" t="n">
         <v>346826</v>
@@ -5154,7 +5154,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G165" t="n">
-        <v>18.7529811859131</v>
+        <v>18.7529830932617</v>
       </c>
       <c r="H165" t="n">
         <v>532932</v>
@@ -5241,7 +5241,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G168" t="n">
-        <v>18.6081027984619</v>
+        <v>18.6081008911133</v>
       </c>
       <c r="H168" t="n">
         <v>405254</v>
@@ -5270,7 +5270,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6533794403076</v>
+        <v>18.653377532959</v>
       </c>
       <c r="H169" t="n">
         <v>409770</v>
@@ -5357,7 +5357,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>18.6081027984619</v>
+        <v>18.6081008911133</v>
       </c>
       <c r="H172" t="n">
         <v>495370</v>
@@ -5502,7 +5502,7 @@
         <v>22</v>
       </c>
       <c r="G177" t="n">
-        <v>19.9210834503174</v>
+        <v>19.9210796356201</v>
       </c>
       <c r="H177" t="n">
         <v>1987857</v>
@@ -5560,7 +5560,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>19.5588798522949</v>
+        <v>19.5588817596436</v>
       </c>
       <c r="H179" t="n">
         <v>770378</v>
@@ -5589,7 +5589,7 @@
         <v>21.4899997711182</v>
       </c>
       <c r="G180" t="n">
-        <v>19.4592742919922</v>
+        <v>19.4592723846436</v>
       </c>
       <c r="H180" t="n">
         <v>700088</v>
@@ -5763,7 +5763,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>19.160457611084</v>
+        <v>19.1604595184326</v>
       </c>
       <c r="H186" t="n">
         <v>685216</v>
@@ -5850,7 +5850,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>20.3557224273682</v>
+        <v>20.3557205200195</v>
       </c>
       <c r="H189" t="n">
         <v>758570</v>
@@ -5908,7 +5908,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G191" t="n">
-        <v>20.3104496002197</v>
+        <v>20.3104476928711</v>
       </c>
       <c r="H191" t="n">
         <v>716381</v>
@@ -5937,7 +5937,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>20.3919429779053</v>
+        <v>20.3919448852539</v>
       </c>
       <c r="H192" t="n">
         <v>676988</v>
@@ -5966,7 +5966,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>20.4643840789795</v>
+        <v>20.4643859863281</v>
       </c>
       <c r="H193" t="n">
         <v>742714</v>
@@ -5995,7 +5995,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G194" t="n">
-        <v>20.3557224273682</v>
+        <v>20.3557205200195</v>
       </c>
       <c r="H194" t="n">
         <v>517237</v>
@@ -6082,7 +6082,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G197" t="n">
-        <v>20.7994213104248</v>
+        <v>20.7994194030762</v>
       </c>
       <c r="H197" t="n">
         <v>492907</v>
@@ -6140,7 +6140,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G199" t="n">
-        <v>20.1021842956543</v>
+        <v>20.1021823883057</v>
       </c>
       <c r="H199" t="n">
         <v>693101</v>
@@ -6198,7 +6198,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>20.3647785186768</v>
+        <v>20.3647766113281</v>
       </c>
       <c r="H201" t="n">
         <v>435292</v>
@@ -6227,7 +6227,7 @@
         <v>22.6900005340576</v>
       </c>
       <c r="G202" t="n">
-        <v>20.5458793640137</v>
+        <v>20.5458812713623</v>
       </c>
       <c r="H202" t="n">
         <v>571600</v>
@@ -6314,7 +6314,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>20.0116348266602</v>
+        <v>20.0116329193115</v>
       </c>
       <c r="H205" t="n">
         <v>933957</v>
@@ -6343,7 +6343,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G206" t="n">
-        <v>20.2651710510254</v>
+        <v>20.265172958374</v>
       </c>
       <c r="H206" t="n">
         <v>579770</v>
@@ -6401,7 +6401,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G208" t="n">
-        <v>20.3557224273682</v>
+        <v>20.3557205200195</v>
       </c>
       <c r="H208" t="n">
         <v>427306</v>
@@ -6430,7 +6430,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G209" t="n">
-        <v>20.03879737854</v>
+        <v>20.0387954711914</v>
       </c>
       <c r="H209" t="n">
         <v>380492</v>
@@ -6459,7 +6459,7 @@
         <v>22.25</v>
       </c>
       <c r="G210" t="n">
-        <v>20.1474609375</v>
+        <v>20.1474590301514</v>
       </c>
       <c r="H210" t="n">
         <v>323432</v>
@@ -6488,7 +6488,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G211" t="n">
-        <v>20.2289524078369</v>
+        <v>20.2289543151855</v>
       </c>
       <c r="H211" t="n">
         <v>476244</v>
@@ -6546,7 +6546,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G213" t="n">
-        <v>20.5639896392822</v>
+        <v>20.5639877319336</v>
       </c>
       <c r="H213" t="n">
         <v>450892</v>
@@ -6575,7 +6575,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G214" t="n">
-        <v>20.1836814880371</v>
+        <v>20.1836795806885</v>
       </c>
       <c r="H214" t="n">
         <v>377674</v>
@@ -6604,7 +6604,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G215" t="n">
-        <v>20.03879737854</v>
+        <v>20.0387954711914</v>
       </c>
       <c r="H215" t="n">
         <v>225022</v>
@@ -6633,7 +6633,7 @@
         <v>21.5900001525879</v>
       </c>
       <c r="G216" t="n">
-        <v>19.549825668335</v>
+        <v>19.5498237609863</v>
       </c>
       <c r="H216" t="n">
         <v>443300</v>
@@ -6691,7 +6691,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>19.5045490264893</v>
+        <v>19.5045509338379</v>
       </c>
       <c r="H218" t="n">
         <v>378528</v>
@@ -6720,7 +6720,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G219" t="n">
-        <v>19.7218723297119</v>
+        <v>19.7218704223633</v>
       </c>
       <c r="H219" t="n">
         <v>366831</v>
@@ -6836,7 +6836,7 @@
         <v>21.9899997711182</v>
       </c>
       <c r="G223" t="n">
-        <v>19.9120273590088</v>
+        <v>19.9120292663574</v>
       </c>
       <c r="H223" t="n">
         <v>433755</v>
@@ -6894,7 +6894,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.4722766876221</v>
+        <v>18.4722747802734</v>
       </c>
       <c r="H225" t="n">
         <v>3206760</v>
@@ -6923,7 +6923,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G226" t="n">
-        <v>18.0919609069824</v>
+        <v>18.0919628143311</v>
       </c>
       <c r="H226" t="n">
         <v>1188113</v>
@@ -6952,7 +6952,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G227" t="n">
-        <v>18.3002300262451</v>
+        <v>18.3002262115479</v>
       </c>
       <c r="H227" t="n">
         <v>568589</v>
@@ -7097,7 +7097,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G232" t="n">
-        <v>17.8565349578857</v>
+        <v>17.8565330505371</v>
       </c>
       <c r="H232" t="n">
         <v>279823</v>
@@ -7358,7 +7358,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>19.2872314453125</v>
+        <v>19.2872276306152</v>
       </c>
       <c r="H241" t="n">
         <v>673068</v>
@@ -7387,7 +7387,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G242" t="n">
-        <v>19.3958892822266</v>
+        <v>19.3958873748779</v>
       </c>
       <c r="H242" t="n">
         <v>455970</v>
@@ -7416,7 +7416,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>19.3777809143066</v>
+        <v>19.3777770996094</v>
       </c>
       <c r="H243" t="n">
         <v>365522</v>
@@ -7445,7 +7445,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G244" t="n">
-        <v>19.1151847839355</v>
+        <v>19.1151828765869</v>
       </c>
       <c r="H244" t="n">
         <v>413169</v>
@@ -7474,7 +7474,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G245" t="n">
-        <v>19.5860443115234</v>
+        <v>19.5860462188721</v>
       </c>
       <c r="H245" t="n">
         <v>394277</v>
@@ -7503,7 +7503,7 @@
         <v>21.2700004577637</v>
       </c>
       <c r="G246" t="n">
-        <v>19.2600650787354</v>
+        <v>19.2600631713867</v>
       </c>
       <c r="H246" t="n">
         <v>348399</v>
@@ -7561,7 +7561,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G248" t="n">
-        <v>20.2651710510254</v>
+        <v>20.265172958374</v>
       </c>
       <c r="H248" t="n">
         <v>1423797</v>
@@ -7590,7 +7590,7 @@
         <v>22.5</v>
       </c>
       <c r="G249" t="n">
-        <v>20.3738327026367</v>
+        <v>20.3738346099854</v>
       </c>
       <c r="H249" t="n">
         <v>417900</v>
@@ -7619,7 +7619,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G250" t="n">
-        <v>20.2651710510254</v>
+        <v>20.265172958374</v>
       </c>
       <c r="H250" t="n">
         <v>491157</v>
@@ -7677,7 +7677,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>20.2380065917969</v>
+        <v>20.2380084991455</v>
       </c>
       <c r="H252" t="n">
         <v>230612</v>
@@ -7735,7 +7735,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G254" t="n">
-        <v>20.1836814880371</v>
+        <v>20.1836795806885</v>
       </c>
       <c r="H254" t="n">
         <v>207491</v>
@@ -7764,7 +7764,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>20.2289524078369</v>
+        <v>20.2289543151855</v>
       </c>
       <c r="H255" t="n">
         <v>284063</v>
@@ -7793,7 +7793,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>20.15651512146</v>
+        <v>20.1565132141113</v>
       </c>
       <c r="H256" t="n">
         <v>178380</v>
@@ -7822,7 +7822,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G257" t="n">
-        <v>20.3104496002197</v>
+        <v>20.3104476928711</v>
       </c>
       <c r="H257" t="n">
         <v>331936</v>
@@ -7938,7 +7938,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G261" t="n">
-        <v>21.5328788757324</v>
+        <v>21.5328769683838</v>
       </c>
       <c r="H261" t="n">
         <v>1128545</v>
@@ -7967,7 +7967,7 @@
         <v>24.3700008392334</v>
       </c>
       <c r="G262" t="n">
-        <v>22.0671272277832</v>
+        <v>22.0671291351318</v>
       </c>
       <c r="H262" t="n">
         <v>1062423</v>
@@ -7996,7 +7996,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G263" t="n">
-        <v>22.0580730438232</v>
+        <v>22.058069229126</v>
       </c>
       <c r="H263" t="n">
         <v>1362031</v>
@@ -8054,7 +8054,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G265" t="n">
-        <v>22.2935028076172</v>
+        <v>22.2935047149658</v>
       </c>
       <c r="H265" t="n">
         <v>1130923</v>
@@ -8083,7 +8083,7 @@
         <v>24.6299991607666</v>
       </c>
       <c r="G266" t="n">
-        <v>22.3025588989258</v>
+        <v>22.3025550842285</v>
       </c>
       <c r="H266" t="n">
         <v>604896</v>
@@ -8112,7 +8112,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>22.3206691741943</v>
+        <v>22.3206653594971</v>
       </c>
       <c r="H267" t="n">
         <v>414459</v>
@@ -8141,7 +8141,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>22.2753925323486</v>
+        <v>22.275390625</v>
       </c>
       <c r="H268" t="n">
         <v>589233</v>
@@ -8170,7 +8170,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G269" t="n">
-        <v>22.2391700744629</v>
+        <v>22.2391738891602</v>
       </c>
       <c r="H269" t="n">
         <v>512480</v>
@@ -8199,7 +8199,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G270" t="n">
-        <v>22.8186931610107</v>
+        <v>22.818696975708</v>
       </c>
       <c r="H270" t="n">
         <v>1130838</v>
@@ -8228,7 +8228,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G271" t="n">
-        <v>23.0722351074219</v>
+        <v>23.0722332000732</v>
       </c>
       <c r="H271" t="n">
         <v>906513</v>
@@ -8286,7 +8286,7 @@
         <v>25.5699996948242</v>
       </c>
       <c r="G273" t="n">
-        <v>23.1537303924561</v>
+        <v>23.1537284851074</v>
       </c>
       <c r="H273" t="n">
         <v>1005467</v>
@@ -8344,7 +8344,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>22.5923175811768</v>
+        <v>22.5923194885254</v>
       </c>
       <c r="H275" t="n">
         <v>775402</v>
@@ -8402,7 +8402,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>22.9092426300049</v>
+        <v>22.9092445373535</v>
       </c>
       <c r="H277" t="n">
         <v>1129609</v>
@@ -8489,7 +8489,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G280" t="n">
-        <v>23.606481552124</v>
+        <v>23.6064834594727</v>
       </c>
       <c r="H280" t="n">
         <v>2579913</v>
@@ -8576,7 +8576,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G283" t="n">
-        <v>23.6427059173584</v>
+        <v>23.6427040100098</v>
       </c>
       <c r="H283" t="n">
         <v>1064235</v>
@@ -8634,7 +8634,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>23.5612049102783</v>
+        <v>23.561206817627</v>
       </c>
       <c r="H285" t="n">
         <v>619704</v>
@@ -8663,7 +8663,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G286" t="n">
-        <v>23.5612049102783</v>
+        <v>23.561206817627</v>
       </c>
       <c r="H286" t="n">
         <v>555021</v>
@@ -8750,7 +8750,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>23.6336479187012</v>
+        <v>23.6336498260498</v>
       </c>
       <c r="H289" t="n">
         <v>404847</v>
@@ -8837,7 +8837,7 @@
         <v>26.1700000762939</v>
       </c>
       <c r="G292" t="n">
-        <v>23.6970329284668</v>
+        <v>23.6970310211182</v>
       </c>
       <c r="H292" t="n">
         <v>236982</v>
@@ -8895,7 +8895,7 @@
         <v>26.5200004577637</v>
       </c>
       <c r="G294" t="n">
-        <v>24.0139617919922</v>
+        <v>24.0139598846436</v>
       </c>
       <c r="H294" t="n">
         <v>741091</v>
@@ -9098,7 +9098,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>24.7655258178711</v>
+        <v>24.7655277252197</v>
       </c>
       <c r="H301" t="n">
         <v>889832</v>
@@ -9156,7 +9156,7 @@
         <v>28.0400009155273</v>
       </c>
       <c r="G303" t="n">
-        <v>25.3903274536133</v>
+        <v>25.3903255462646</v>
       </c>
       <c r="H303" t="n">
         <v>911254</v>
@@ -9243,7 +9243,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>25.6710300445557</v>
+        <v>25.6710338592529</v>
       </c>
       <c r="H306" t="n">
         <v>500694</v>
@@ -9417,7 +9417,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>25.0643424987793</v>
+        <v>25.0643444061279</v>
       </c>
       <c r="H312" t="n">
         <v>650689</v>
@@ -9446,7 +9446,7 @@
         <v>27.3899993896484</v>
       </c>
       <c r="G313" t="n">
-        <v>24.8017463684082</v>
+        <v>24.8017482757568</v>
       </c>
       <c r="H313" t="n">
         <v>332263</v>
@@ -9533,7 +9533,7 @@
         <v>28.0200004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>25.3722171783447</v>
+        <v>25.3722152709961</v>
       </c>
       <c r="H316" t="n">
         <v>452765</v>
@@ -9562,7 +9562,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>25.6257514953613</v>
+        <v>25.62575340271</v>
       </c>
       <c r="H317" t="n">
         <v>349361</v>
@@ -9649,7 +9649,7 @@
         <v>27.7900009155273</v>
       </c>
       <c r="G320" t="n">
-        <v>25.1639499664307</v>
+        <v>25.163948059082</v>
       </c>
       <c r="H320" t="n">
         <v>290259</v>
@@ -9736,7 +9736,7 @@
         <v>28.4099998474121</v>
       </c>
       <c r="G323" t="n">
-        <v>25.7253608703613</v>
+        <v>25.72536277771</v>
       </c>
       <c r="H323" t="n">
         <v>704929</v>
@@ -9794,7 +9794,7 @@
         <v>27.75</v>
       </c>
       <c r="G325" t="n">
-        <v>25.1277294158936</v>
+        <v>25.1277275085449</v>
       </c>
       <c r="H325" t="n">
         <v>265673</v>
@@ -9852,7 +9852,7 @@
         <v>28.2099990844727</v>
       </c>
       <c r="G327" t="n">
-        <v>25.5442600250244</v>
+        <v>25.5442581176758</v>
       </c>
       <c r="H327" t="n">
         <v>365212</v>
@@ -9939,7 +9939,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>25.2635536193848</v>
+        <v>25.2635555267334</v>
       </c>
       <c r="H330" t="n">
         <v>387257</v>
@@ -9968,7 +9968,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>25.0824527740479</v>
+        <v>25.0824546813965</v>
       </c>
       <c r="H331" t="n">
         <v>429583</v>
@@ -9997,7 +9997,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G332" t="n">
-        <v>24.7836380004883</v>
+        <v>24.7836399078369</v>
       </c>
       <c r="H332" t="n">
         <v>660230</v>
@@ -10026,7 +10026,7 @@
         <v>26.9699993133545</v>
       </c>
       <c r="G333" t="n">
-        <v>24.4214344024658</v>
+        <v>24.4214363098145</v>
       </c>
       <c r="H333" t="n">
         <v>775708</v>
@@ -10055,7 +10055,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>24.7655258178711</v>
+        <v>24.7655277252197</v>
       </c>
       <c r="H334" t="n">
         <v>653524</v>
@@ -10142,7 +10142,7 @@
         <v>28.1900005340576</v>
       </c>
       <c r="G337" t="n">
-        <v>25.5261516571045</v>
+        <v>25.5261497497559</v>
       </c>
       <c r="H337" t="n">
         <v>379396</v>
@@ -10200,7 +10200,7 @@
         <v>28.9200000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>26.1871700286865</v>
+        <v>26.1871662139893</v>
       </c>
       <c r="H339" t="n">
         <v>548992</v>
@@ -10229,7 +10229,7 @@
         <v>29.4099998474121</v>
       </c>
       <c r="G340" t="n">
-        <v>26.6308650970459</v>
+        <v>26.6308631896973</v>
       </c>
       <c r="H340" t="n">
         <v>718939</v>
@@ -10258,7 +10258,7 @@
         <v>29.25</v>
       </c>
       <c r="G341" t="n">
-        <v>26.4859828948975</v>
+        <v>26.4859809875488</v>
       </c>
       <c r="H341" t="n">
         <v>324279</v>
@@ -10316,7 +10316,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G343" t="n">
-        <v>26.676139831543</v>
+        <v>26.6761379241943</v>
       </c>
       <c r="H343" t="n">
         <v>498694</v>
@@ -10345,7 +10345,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>26.8934631347656</v>
+        <v>26.893461227417</v>
       </c>
       <c r="H344" t="n">
         <v>349802</v>
@@ -10374,7 +10374,7 @@
         <v>29</v>
       </c>
       <c r="G345" t="n">
-        <v>26.2596092224121</v>
+        <v>26.2596073150635</v>
       </c>
       <c r="H345" t="n">
         <v>806664</v>
@@ -10461,7 +10461,7 @@
         <v>29.4099998474121</v>
       </c>
       <c r="G348" t="n">
-        <v>26.6308650970459</v>
+        <v>26.6308631896973</v>
       </c>
       <c r="H348" t="n">
         <v>196385</v>
@@ -10519,7 +10519,7 @@
         <v>29.3700008392334</v>
       </c>
       <c r="G350" t="n">
-        <v>26.5946426391602</v>
+        <v>26.5946464538574</v>
       </c>
       <c r="H350" t="n">
         <v>150195</v>
@@ -10548,7 +10548,7 @@
         <v>29</v>
       </c>
       <c r="G351" t="n">
-        <v>26.2596092224121</v>
+        <v>26.2596073150635</v>
       </c>
       <c r="H351" t="n">
         <v>536086</v>
@@ -10780,7 +10780,7 @@
         <v>25.2299995422363</v>
       </c>
       <c r="G359" t="n">
-        <v>23.2202472686768</v>
+        <v>23.2202453613281</v>
       </c>
       <c r="H359" t="n">
         <v>2339992</v>
@@ -10838,7 +10838,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>22.9625492095947</v>
+        <v>22.9625511169434</v>
       </c>
       <c r="H361" t="n">
         <v>858119</v>
@@ -10867,7 +10867,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>22.8705158233643</v>
+        <v>22.8705196380615</v>
       </c>
       <c r="H362" t="n">
         <v>814408</v>
@@ -10896,7 +10896,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G363" t="n">
-        <v>22.8613166809082</v>
+        <v>22.8613147735596</v>
       </c>
       <c r="H363" t="n">
         <v>526890</v>
@@ -11041,7 +11041,7 @@
         <v>24</v>
       </c>
       <c r="G368" t="n">
-        <v>22.0882263183594</v>
+        <v>22.0882244110107</v>
       </c>
       <c r="H368" t="n">
         <v>1374366</v>
@@ -11157,7 +11157,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>22.3643264770508</v>
+        <v>22.3643283843994</v>
       </c>
       <c r="H372" t="n">
         <v>603189</v>
@@ -11186,7 +11186,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G373" t="n">
-        <v>22.7416687011719</v>
+        <v>22.7416667938232</v>
       </c>
       <c r="H373" t="n">
         <v>827087</v>
@@ -11215,7 +11215,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G374" t="n">
-        <v>22.95334815979</v>
+        <v>22.9533462524414</v>
       </c>
       <c r="H374" t="n">
         <v>1434500</v>
@@ -11273,7 +11273,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>23.2846698760986</v>
+        <v>23.2846717834473</v>
       </c>
       <c r="H376" t="n">
         <v>596955</v>
@@ -11331,7 +11331,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G378" t="n">
-        <v>23.4319248199463</v>
+        <v>23.4319267272949</v>
       </c>
       <c r="H378" t="n">
         <v>355374</v>
@@ -11418,7 +11418,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G381" t="n">
-        <v>22.6036148071289</v>
+        <v>22.6036186218262</v>
       </c>
       <c r="H381" t="n">
         <v>369901</v>
@@ -11505,7 +11505,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>21.4900016784668</v>
+        <v>21.4900035858154</v>
       </c>
       <c r="H384" t="n">
         <v>361338</v>
@@ -11534,7 +11534,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>21.7200889587402</v>
+        <v>21.7200908660889</v>
       </c>
       <c r="H385" t="n">
         <v>267685</v>
@@ -11563,7 +11563,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G386" t="n">
-        <v>21.5544261932373</v>
+        <v>21.5544242858887</v>
       </c>
       <c r="H386" t="n">
         <v>216910</v>
@@ -11650,7 +11650,7 @@
         <v>23</v>
       </c>
       <c r="G389" t="n">
-        <v>21.1678829193115</v>
+        <v>21.1678810119629</v>
       </c>
       <c r="H389" t="n">
         <v>501698</v>
@@ -11679,7 +11679,7 @@
         <v>23</v>
       </c>
       <c r="G390" t="n">
-        <v>21.1678829193115</v>
+        <v>21.1678810119629</v>
       </c>
       <c r="H390" t="n">
         <v>281095</v>
@@ -11795,7 +11795,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G394" t="n">
-        <v>21.5084075927734</v>
+        <v>21.5084114074707</v>
       </c>
       <c r="H394" t="n">
         <v>401727</v>
@@ -11853,7 +11853,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G396" t="n">
-        <v>21.8857517242432</v>
+        <v>21.8857498168945</v>
       </c>
       <c r="H396" t="n">
         <v>305318</v>
@@ -11940,7 +11940,7 @@
         <v>24.3099994659424</v>
       </c>
       <c r="G399" t="n">
-        <v>22.3735313415527</v>
+        <v>22.3735332489014</v>
       </c>
       <c r="H399" t="n">
         <v>712169</v>
@@ -11969,7 +11969,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G400" t="n">
-        <v>22.2170734405518</v>
+        <v>22.2170753479004</v>
       </c>
       <c r="H400" t="n">
         <v>358847</v>
@@ -12027,7 +12027,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G402" t="n">
-        <v>22.5299892425537</v>
+        <v>22.5299873352051</v>
       </c>
       <c r="H402" t="n">
         <v>279268</v>
@@ -12085,7 +12085,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G404" t="n">
-        <v>22.6404323577881</v>
+        <v>22.6404304504395</v>
       </c>
       <c r="H404" t="n">
         <v>432144</v>
@@ -12143,7 +12143,7 @@
         <v>24</v>
       </c>
       <c r="G406" t="n">
-        <v>22.0882263183594</v>
+        <v>22.0882244110107</v>
       </c>
       <c r="H406" t="n">
         <v>1576783</v>
@@ -12172,7 +12172,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G407" t="n">
-        <v>21.4255790710449</v>
+        <v>21.4255809783936</v>
       </c>
       <c r="H407" t="n">
         <v>844820</v>
@@ -12201,7 +12201,7 @@
         <v>23.5300006866455</v>
       </c>
       <c r="G408" t="n">
-        <v>21.6556644439697</v>
+        <v>21.6556663513184</v>
       </c>
       <c r="H408" t="n">
         <v>610626</v>
@@ -12230,7 +12230,7 @@
         <v>24</v>
       </c>
       <c r="G409" t="n">
-        <v>22.0882263183594</v>
+        <v>22.0882244110107</v>
       </c>
       <c r="H409" t="n">
         <v>517420</v>
@@ -12259,7 +12259,7 @@
         <v>24.1900005340576</v>
       </c>
       <c r="G410" t="n">
-        <v>22.2630920410156</v>
+        <v>22.263090133667</v>
       </c>
       <c r="H410" t="n">
         <v>366457</v>
@@ -12375,7 +12375,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G414" t="n">
-        <v>22.0514125823975</v>
+        <v>22.0514106750488</v>
       </c>
       <c r="H414" t="n">
         <v>315380</v>
@@ -12462,7 +12462,7 @@
         <v>24.2700004577637</v>
       </c>
       <c r="G417" t="n">
-        <v>22.3367176055908</v>
+        <v>22.3367195129395</v>
       </c>
       <c r="H417" t="n">
         <v>583263</v>
@@ -12520,7 +12520,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>21.7661056518555</v>
+        <v>21.7661037445068</v>
       </c>
       <c r="H419" t="n">
         <v>234785</v>
@@ -12549,7 +12549,7 @@
         <v>23.9699993133545</v>
       </c>
       <c r="G420" t="n">
-        <v>22.0606174468994</v>
+        <v>22.0606155395508</v>
       </c>
       <c r="H420" t="n">
         <v>197206</v>
@@ -12578,7 +12578,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G421" t="n">
-        <v>21.7569026947021</v>
+        <v>21.7569007873535</v>
       </c>
       <c r="H421" t="n">
         <v>283848</v>
@@ -12636,7 +12636,7 @@
         <v>24</v>
       </c>
       <c r="G423" t="n">
-        <v>22.0882263183594</v>
+        <v>22.0882244110107</v>
       </c>
       <c r="H423" t="n">
         <v>206329</v>
@@ -12665,7 +12665,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>21.9961929321289</v>
+        <v>21.9961910247803</v>
       </c>
       <c r="H424" t="n">
         <v>138330</v>
@@ -12723,7 +12723,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G426" t="n">
-        <v>22.0053958892822</v>
+        <v>22.0053939819336</v>
       </c>
       <c r="H426" t="n">
         <v>237338</v>
@@ -12752,7 +12752,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G427" t="n">
-        <v>22.2170734405518</v>
+        <v>22.2170753479004</v>
       </c>
       <c r="H427" t="n">
         <v>537878</v>
@@ -12810,7 +12810,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G429" t="n">
-        <v>22.0053958892822</v>
+        <v>22.0053939819336</v>
       </c>
       <c r="H429" t="n">
         <v>233703</v>
@@ -12868,7 +12868,7 @@
         <v>23.7700004577637</v>
       </c>
       <c r="G431" t="n">
-        <v>21.8765487670898</v>
+        <v>21.8765468597412</v>
       </c>
       <c r="H431" t="n">
         <v>297166</v>
@@ -12897,7 +12897,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G432" t="n">
-        <v>22.1250400543213</v>
+        <v>22.1250419616699</v>
       </c>
       <c r="H432" t="n">
         <v>181819</v>
@@ -12955,7 +12955,7 @@
         <v>23.9300003051758</v>
       </c>
       <c r="G434" t="n">
-        <v>22.0238037109375</v>
+        <v>22.0238018035889</v>
       </c>
       <c r="H434" t="n">
         <v>408570</v>
@@ -12984,7 +12984,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G435" t="n">
-        <v>21.9961929321289</v>
+        <v>21.9961910247803</v>
       </c>
       <c r="H435" t="n">
         <v>619938</v>
@@ -13042,7 +13042,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G437" t="n">
-        <v>21.6832752227783</v>
+        <v>21.683277130127</v>
       </c>
       <c r="H437" t="n">
         <v>578488</v>
@@ -13071,7 +13071,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G438" t="n">
-        <v>20.8273544311523</v>
+        <v>20.827356338501</v>
       </c>
       <c r="H438" t="n">
         <v>1417619</v>
@@ -13100,7 +13100,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G439" t="n">
-        <v>21.0574417114258</v>
+        <v>21.0574398040771</v>
       </c>
       <c r="H439" t="n">
         <v>1031440</v>
@@ -13158,7 +13158,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>20.7997455596924</v>
+        <v>20.799747467041</v>
       </c>
       <c r="H441" t="n">
         <v>1083075</v>
@@ -13187,7 +13187,7 @@
         <v>22.9300003051758</v>
       </c>
       <c r="G442" t="n">
-        <v>21.1034622192383</v>
+        <v>21.1034603118896</v>
       </c>
       <c r="H442" t="n">
         <v>361840</v>
@@ -13216,7 +13216,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>21.0758495330811</v>
+        <v>21.0758476257324</v>
       </c>
       <c r="H443" t="n">
         <v>297588</v>
@@ -13245,7 +13245,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G444" t="n">
-        <v>21.3243427276611</v>
+        <v>21.3243408203125</v>
       </c>
       <c r="H444" t="n">
         <v>333907</v>
@@ -13274,7 +13274,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>21.9501762390137</v>
+        <v>21.9501781463623</v>
       </c>
       <c r="H445" t="n">
         <v>1478816</v>
@@ -13303,7 +13303,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G446" t="n">
-        <v>22.0974292755127</v>
+        <v>22.0974311828613</v>
       </c>
       <c r="H446" t="n">
         <v>1051424</v>
@@ -13332,7 +13332,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G447" t="n">
-        <v>22.0514125823975</v>
+        <v>22.0514106750488</v>
       </c>
       <c r="H447" t="n">
         <v>633441</v>
@@ -13361,7 +13361,7 @@
         <v>23.75</v>
       </c>
       <c r="G448" t="n">
-        <v>21.8581409454346</v>
+        <v>21.8581390380859</v>
       </c>
       <c r="H448" t="n">
         <v>541964</v>
@@ -13448,7 +13448,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G451" t="n">
-        <v>21.2967300415039</v>
+        <v>21.2967319488525</v>
       </c>
       <c r="H451" t="n">
         <v>599089</v>
@@ -13477,7 +13477,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G452" t="n">
-        <v>20.9746112823486</v>
+        <v>20.9746131896973</v>
       </c>
       <c r="H452" t="n">
         <v>950234</v>
@@ -13506,7 +13506,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>20.7997455596924</v>
+        <v>20.799747467041</v>
       </c>
       <c r="H453" t="n">
         <v>536977</v>
@@ -13535,7 +13535,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838123321533</v>
       </c>
       <c r="H454" t="n">
         <v>572574</v>
@@ -13564,7 +13564,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G455" t="n">
-        <v>21.1402740478516</v>
+        <v>21.1402721405029</v>
       </c>
       <c r="H455" t="n">
         <v>684839</v>
@@ -13593,7 +13593,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G456" t="n">
-        <v>21.0666446685791</v>
+        <v>21.0666465759277</v>
       </c>
       <c r="H456" t="n">
         <v>654865</v>
@@ -13622,7 +13622,7 @@
         <v>22.5</v>
       </c>
       <c r="G457" t="n">
-        <v>20.7077102661133</v>
+        <v>20.7077121734619</v>
       </c>
       <c r="H457" t="n">
         <v>475690</v>
@@ -13709,7 +13709,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G460" t="n">
-        <v>21.0206279754639</v>
+        <v>21.0206260681152</v>
       </c>
       <c r="H460" t="n">
         <v>386462</v>
@@ -13912,7 +13912,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>19.971435546875</v>
+        <v>19.9714393615723</v>
       </c>
       <c r="H467" t="n">
         <v>1435364</v>
@@ -13941,7 +13941,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>20.0634708404541</v>
+        <v>20.0634727478027</v>
       </c>
       <c r="H468" t="n">
         <v>1097685</v>
@@ -13970,7 +13970,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G469" t="n">
-        <v>20.4868297576904</v>
+        <v>20.4868278503418</v>
       </c>
       <c r="H469" t="n">
         <v>471696</v>
@@ -13999,7 +13999,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G470" t="n">
-        <v>20.7445259094238</v>
+        <v>20.7445278167725</v>
       </c>
       <c r="H470" t="n">
         <v>785130</v>
@@ -14057,7 +14057,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G472" t="n">
-        <v>21.0206279754639</v>
+        <v>21.0206260681152</v>
       </c>
       <c r="H472" t="n">
         <v>601843</v>
@@ -14086,7 +14086,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G473" t="n">
-        <v>21.0666446685791</v>
+        <v>21.0666465759277</v>
       </c>
       <c r="H473" t="n">
         <v>317345</v>
@@ -14115,7 +14115,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G474" t="n">
-        <v>21.2415084838867</v>
+        <v>21.2415103912354</v>
       </c>
       <c r="H474" t="n">
         <v>971079</v>
@@ -14202,7 +14202,7 @@
         <v>22.5</v>
       </c>
       <c r="G477" t="n">
-        <v>20.7077102661133</v>
+        <v>20.7077121734619</v>
       </c>
       <c r="H477" t="n">
         <v>777593</v>
@@ -14231,7 +14231,7 @@
         <v>22</v>
       </c>
       <c r="G478" t="n">
-        <v>20.2475414276123</v>
+        <v>20.247537612915</v>
       </c>
       <c r="H478" t="n">
         <v>750579</v>
@@ -14289,7 +14289,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G480" t="n">
-        <v>20.0910816192627</v>
+        <v>20.0910835266113</v>
       </c>
       <c r="H480" t="n">
         <v>280042</v>
@@ -14318,7 +14318,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G481" t="n">
-        <v>19.2719764709473</v>
+        <v>19.2719745635986</v>
       </c>
       <c r="H481" t="n">
         <v>2609341</v>
@@ -14347,7 +14347,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>19.6953353881836</v>
+        <v>19.695333480835</v>
       </c>
       <c r="H482" t="n">
         <v>1022782</v>
@@ -14434,7 +14434,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G485" t="n">
-        <v>20.1831150054932</v>
+        <v>20.1831169128418</v>
       </c>
       <c r="H485" t="n">
         <v>533863</v>
@@ -14463,7 +14463,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G486" t="n">
-        <v>20.0450649261475</v>
+        <v>20.0450630187988</v>
       </c>
       <c r="H486" t="n">
         <v>455042</v>
@@ -14521,7 +14521,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>20.4316101074219</v>
+        <v>20.4316082000732</v>
       </c>
       <c r="H488" t="n">
         <v>368098</v>
@@ -14550,7 +14550,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G489" t="n">
-        <v>20.5696582794189</v>
+        <v>20.5696601867676</v>
       </c>
       <c r="H489" t="n">
         <v>438572</v>
@@ -14608,7 +14608,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G491" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838123321533</v>
       </c>
       <c r="H491" t="n">
         <v>580090</v>
@@ -14637,7 +14637,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G492" t="n">
-        <v>21.131067276001</v>
+        <v>21.1310653686523</v>
       </c>
       <c r="H492" t="n">
         <v>486588</v>
@@ -14666,7 +14666,7 @@
         <v>22.5</v>
       </c>
       <c r="G493" t="n">
-        <v>20.7077102661133</v>
+        <v>20.7077121734619</v>
       </c>
       <c r="H493" t="n">
         <v>633331</v>
@@ -14811,7 +14811,7 @@
         <v>23.3099994659424</v>
       </c>
       <c r="G498" t="n">
-        <v>21.4531879425049</v>
+        <v>21.4531898498535</v>
       </c>
       <c r="H498" t="n">
         <v>526941</v>
@@ -14898,7 +14898,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G501" t="n">
-        <v>20.6708965301514</v>
+        <v>20.6708946228027</v>
       </c>
       <c r="H501" t="n">
         <v>483213</v>
@@ -14927,7 +14927,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G502" t="n">
-        <v>20.7721328735352</v>
+        <v>20.7721366882324</v>
       </c>
       <c r="H502" t="n">
         <v>621541</v>
@@ -14985,7 +14985,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G504" t="n">
-        <v>19.7965717315674</v>
+        <v>19.796573638916</v>
       </c>
       <c r="H504" t="n">
         <v>852016</v>
@@ -15014,7 +15014,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G505" t="n">
-        <v>19.8609943389893</v>
+        <v>19.8609962463379</v>
       </c>
       <c r="H505" t="n">
         <v>611462</v>
@@ -15043,7 +15043,7 @@
         <v>21.75</v>
       </c>
       <c r="G506" t="n">
-        <v>20.0174560546875</v>
+        <v>20.0174541473389</v>
       </c>
       <c r="H506" t="n">
         <v>379082</v>
@@ -15072,7 +15072,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G507" t="n">
-        <v>20.2199287414551</v>
+        <v>20.2199268341064</v>
       </c>
       <c r="H507" t="n">
         <v>372050</v>
@@ -15130,7 +15130,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>20.2291355133057</v>
+        <v>20.2291316986084</v>
       </c>
       <c r="H509" t="n">
         <v>191733</v>
@@ -15217,7 +15217,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G512" t="n">
-        <v>20.2199287414551</v>
+        <v>20.2199268341064</v>
       </c>
       <c r="H512" t="n">
         <v>214152</v>
@@ -15246,7 +15246,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>20.5236434936523</v>
+        <v>20.5236415863037</v>
       </c>
       <c r="H513" t="n">
         <v>314606</v>
@@ -15304,7 +15304,7 @@
         <v>22.7199993133545</v>
       </c>
       <c r="G515" t="n">
-        <v>20.9101867675781</v>
+        <v>20.9101848602295</v>
       </c>
       <c r="H515" t="n">
         <v>306176</v>
@@ -15449,7 +15449,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G520" t="n">
-        <v>20.4868297576904</v>
+        <v>20.4868278503418</v>
       </c>
       <c r="H520" t="n">
         <v>710973</v>
@@ -15478,7 +15478,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>20.4316101074219</v>
+        <v>20.4316082000732</v>
       </c>
       <c r="H521" t="n">
         <v>164255</v>
@@ -15536,7 +15536,7 @@
         <v>22</v>
       </c>
       <c r="G523" t="n">
-        <v>20.2475414276123</v>
+        <v>20.247537612915</v>
       </c>
       <c r="H523" t="n">
         <v>290730</v>
@@ -15565,7 +15565,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G524" t="n">
-        <v>20.1739120483398</v>
+        <v>20.1739139556885</v>
       </c>
       <c r="H524" t="n">
         <v>499386</v>
@@ -15623,7 +15623,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G526" t="n">
-        <v>21.7569026947021</v>
+        <v>21.7569007873535</v>
       </c>
       <c r="H526" t="n">
         <v>1540488</v>
@@ -15652,7 +15652,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G527" t="n">
-        <v>21.2967300415039</v>
+        <v>21.2967319488525</v>
       </c>
       <c r="H527" t="n">
         <v>604201</v>
@@ -15826,7 +15826,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G533" t="n">
-        <v>20.8549652099609</v>
+        <v>20.8549671173096</v>
       </c>
       <c r="H533" t="n">
         <v>568555</v>
@@ -15855,7 +15855,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G534" t="n">
-        <v>21.3243427276611</v>
+        <v>21.3243408203125</v>
       </c>
       <c r="H534" t="n">
         <v>2061434</v>
@@ -15913,7 +15913,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G536" t="n">
-        <v>20.5052375793457</v>
+        <v>20.5052394866943</v>
       </c>
       <c r="H536" t="n">
         <v>400016</v>
@@ -16087,7 +16087,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G542" t="n">
-        <v>19.9162158966064</v>
+        <v>19.9162178039551</v>
       </c>
       <c r="H542" t="n">
         <v>415655</v>
@@ -16116,7 +16116,7 @@
         <v>22</v>
       </c>
       <c r="G543" t="n">
-        <v>20.2475414276123</v>
+        <v>20.247537612915</v>
       </c>
       <c r="H543" t="n">
         <v>619390</v>
@@ -16145,7 +16145,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G544" t="n">
-        <v>20.5604553222656</v>
+        <v>20.5604572296143</v>
       </c>
       <c r="H544" t="n">
         <v>590508</v>
@@ -16261,7 +16261,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G548" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838123321533</v>
       </c>
       <c r="H548" t="n">
         <v>361715</v>
@@ -16348,7 +16348,7 @@
         <v>22.75</v>
       </c>
       <c r="G551" t="n">
-        <v>20.9377975463867</v>
+        <v>20.9377956390381</v>
       </c>
       <c r="H551" t="n">
         <v>330493</v>
@@ -16406,7 +16406,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G553" t="n">
-        <v>21.2967300415039</v>
+        <v>21.2967319488525</v>
       </c>
       <c r="H553" t="n">
         <v>2496511</v>
@@ -16435,7 +16435,7 @@
         <v>23.4699993133545</v>
       </c>
       <c r="G554" t="n">
-        <v>21.6004428863525</v>
+        <v>21.6004447937012</v>
       </c>
       <c r="H554" t="n">
         <v>754894</v>
@@ -16464,7 +16464,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G555" t="n">
-        <v>20.6248798370361</v>
+        <v>20.6248817443848</v>
       </c>
       <c r="H555" t="n">
         <v>551415</v>
@@ -16493,7 +16493,7 @@
         <v>22.0300006866455</v>
       </c>
       <c r="G556" t="n">
-        <v>20.2751522064209</v>
+        <v>20.2751502990723</v>
       </c>
       <c r="H556" t="n">
         <v>754774</v>
@@ -16522,7 +16522,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G557" t="n">
-        <v>20.0910816192627</v>
+        <v>20.0910835266113</v>
       </c>
       <c r="H557" t="n">
         <v>895894</v>
@@ -16580,7 +16580,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>19.971435546875</v>
+        <v>19.9714393615723</v>
       </c>
       <c r="H559" t="n">
         <v>860738</v>
@@ -16638,7 +16638,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G561" t="n">
-        <v>19.9990482330322</v>
+        <v>19.9990463256836</v>
       </c>
       <c r="H561" t="n">
         <v>740982</v>
@@ -16696,7 +16696,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G563" t="n">
-        <v>19.8609943389893</v>
+        <v>19.8609962463379</v>
       </c>
       <c r="H563" t="n">
         <v>558470</v>
@@ -16725,7 +16725,7 @@
         <v>21.8700008392334</v>
       </c>
       <c r="G564" t="n">
-        <v>20.1278953552246</v>
+        <v>20.1278972625732</v>
       </c>
       <c r="H564" t="n">
         <v>432785</v>
@@ -16754,7 +16754,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G565" t="n">
-        <v>20.3303718566895</v>
+        <v>20.3303737640381</v>
       </c>
       <c r="H565" t="n">
         <v>576204</v>
@@ -16783,7 +16783,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G566" t="n">
-        <v>20.5696582794189</v>
+        <v>20.5696601867676</v>
       </c>
       <c r="H566" t="n">
         <v>548117</v>
@@ -16812,7 +16812,7 @@
         <v>22.6800003051758</v>
       </c>
       <c r="G567" t="n">
-        <v>20.8733749389648</v>
+        <v>20.8733730316162</v>
       </c>
       <c r="H567" t="n">
         <v>588294</v>
@@ -16841,7 +16841,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G568" t="n">
-        <v>20.5236434936523</v>
+        <v>20.5236415863037</v>
       </c>
       <c r="H568" t="n">
         <v>305669</v>
@@ -16870,7 +16870,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G569" t="n">
-        <v>20.3763885498047</v>
+        <v>20.3763866424561</v>
       </c>
       <c r="H569" t="n">
         <v>262537</v>
@@ -16957,7 +16957,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G572" t="n">
-        <v>20.3027610778809</v>
+        <v>20.3027629852295</v>
       </c>
       <c r="H572" t="n">
         <v>439174</v>
@@ -17044,7 +17044,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G575" t="n">
-        <v>20.6432876586914</v>
+        <v>20.6432857513428</v>
       </c>
       <c r="H575" t="n">
         <v>199750</v>
@@ -17073,7 +17073,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>20.6156749725342</v>
+        <v>20.6156787872314</v>
       </c>
       <c r="H576" t="n">
         <v>263654</v>
@@ -17102,7 +17102,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G577" t="n">
-        <v>20.7445259094238</v>
+        <v>20.7445278167725</v>
       </c>
       <c r="H577" t="n">
         <v>342737</v>
@@ -17218,7 +17218,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G581" t="n">
-        <v>20.7261180877686</v>
+        <v>20.7261199951172</v>
       </c>
       <c r="H581" t="n">
         <v>617911</v>
@@ -17247,7 +17247,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G582" t="n">
-        <v>20.9746112823486</v>
+        <v>20.9746131896973</v>
       </c>
       <c r="H582" t="n">
         <v>623938</v>
@@ -17479,7 +17479,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G590" t="n">
-        <v>22.64963722229</v>
+        <v>22.6496353149414</v>
       </c>
       <c r="H590" t="n">
         <v>1399669</v>
@@ -17537,7 +17537,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G592" t="n">
-        <v>22.4195518493652</v>
+        <v>22.419548034668</v>
       </c>
       <c r="H592" t="n">
         <v>493451</v>
@@ -17653,7 +17653,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G596" t="n">
-        <v>22.7416687011719</v>
+        <v>22.7416667938232</v>
       </c>
       <c r="H596" t="n">
         <v>747463</v>
@@ -17682,7 +17682,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>22.6404323577881</v>
+        <v>22.6404304504395</v>
       </c>
       <c r="H597" t="n">
         <v>903419</v>
@@ -17798,7 +17798,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G601" t="n">
-        <v>22.686450958252</v>
+        <v>22.6864471435547</v>
       </c>
       <c r="H601" t="n">
         <v>481261</v>
@@ -17827,7 +17827,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>22.7324676513672</v>
+        <v>22.7324657440186</v>
       </c>
       <c r="H602" t="n">
         <v>336880</v>
@@ -17856,7 +17856,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G603" t="n">
-        <v>22.8337020874023</v>
+        <v>22.833703994751</v>
       </c>
       <c r="H603" t="n">
         <v>232191</v>
@@ -79951,6 +79951,64 @@
         <v>388580</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>7.15999984741211</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>7.30999994277954</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>7.08500003814697</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>7.30999994277954</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>7.30999994277954</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>251205</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>7.38500022888184</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>7.05999994277954</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>7.20499992370605</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>7.20499992370605</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>214707</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -427,7 +427,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G2" t="n">
-        <v>18.2763500213623</v>
+        <v>18.2763519287109</v>
       </c>
       <c r="H2" t="n">
         <v>1705033</v>
@@ -514,7 +514,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>17.9401950836182</v>
+        <v>17.9401931762695</v>
       </c>
       <c r="H5" t="n">
         <v>1381959</v>
@@ -543,7 +543,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>17.6836528778076</v>
+        <v>17.683650970459</v>
       </c>
       <c r="H6" t="n">
         <v>951699</v>
@@ -572,7 +572,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G7" t="n">
-        <v>18.2498092651367</v>
+        <v>18.2498111724854</v>
       </c>
       <c r="H7" t="n">
         <v>1189444</v>
@@ -601,7 +601,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G8" t="n">
-        <v>19.4086723327637</v>
+        <v>19.4086742401123</v>
       </c>
       <c r="H8" t="n">
         <v>2266409</v>
@@ -630,7 +630,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G9" t="n">
-        <v>19.1344394683838</v>
+        <v>19.1344356536865</v>
       </c>
       <c r="H9" t="n">
         <v>1367537</v>
@@ -659,7 +659,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G10" t="n">
-        <v>18.84250831604</v>
+        <v>18.8425121307373</v>
       </c>
       <c r="H10" t="n">
         <v>1053164</v>
@@ -746,7 +746,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G13" t="n">
-        <v>18.0994243621826</v>
+        <v>18.0994262695312</v>
       </c>
       <c r="H13" t="n">
         <v>975727</v>
@@ -775,7 +775,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G14" t="n">
-        <v>17.6394233703613</v>
+        <v>17.6394214630127</v>
       </c>
       <c r="H14" t="n">
         <v>943974</v>
@@ -862,7 +862,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G17" t="n">
-        <v>18.0994243621826</v>
+        <v>18.0994262695312</v>
       </c>
       <c r="H17" t="n">
         <v>476663</v>
@@ -891,7 +891,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G18" t="n">
-        <v>18.4798164367676</v>
+        <v>18.4798145294189</v>
       </c>
       <c r="H18" t="n">
         <v>567890</v>
@@ -949,7 +949,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>17.7632675170898</v>
+        <v>17.7632694244385</v>
       </c>
       <c r="H20" t="n">
         <v>1244898</v>
@@ -978,7 +978,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G21" t="n">
-        <v>18.3913516998291</v>
+        <v>18.3913536071777</v>
       </c>
       <c r="H21" t="n">
         <v>1957322</v>
@@ -1007,7 +1007,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G22" t="n">
-        <v>18.6744327545166</v>
+        <v>18.6744346618652</v>
       </c>
       <c r="H22" t="n">
         <v>1011926</v>
@@ -1036,7 +1036,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>17.9578838348389</v>
+        <v>17.9578857421875</v>
       </c>
       <c r="H23" t="n">
         <v>725076</v>
@@ -1094,7 +1094,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G25" t="n">
-        <v>18.2586612701416</v>
+        <v>18.258659362793</v>
       </c>
       <c r="H25" t="n">
         <v>716525</v>
@@ -1123,7 +1123,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G26" t="n">
-        <v>18.0817356109619</v>
+        <v>18.0817375183105</v>
       </c>
       <c r="H26" t="n">
         <v>1482038</v>
@@ -1181,7 +1181,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G28" t="n">
-        <v>16.9051818847656</v>
+        <v>16.9051856994629</v>
       </c>
       <c r="H28" t="n">
         <v>908164</v>
@@ -1210,7 +1210,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>17.1617202758789</v>
+        <v>17.1617240905762</v>
       </c>
       <c r="H29" t="n">
         <v>741895</v>
@@ -1297,7 +1297,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G32" t="n">
-        <v>17.4890384674072</v>
+        <v>17.48903465271</v>
       </c>
       <c r="H32" t="n">
         <v>658925</v>
@@ -1355,7 +1355,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G34" t="n">
-        <v>18.4798164367676</v>
+        <v>18.4798145294189</v>
       </c>
       <c r="H34" t="n">
         <v>689809</v>
@@ -1529,7 +1529,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G40" t="n">
-        <v>17.7632675170898</v>
+        <v>17.7632694244385</v>
       </c>
       <c r="H40" t="n">
         <v>488362</v>
@@ -1558,7 +1558,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G41" t="n">
-        <v>17.9048080444336</v>
+        <v>17.9048099517822</v>
       </c>
       <c r="H41" t="n">
         <v>422135</v>
@@ -1587,7 +1587,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G42" t="n">
-        <v>18.3471202850342</v>
+        <v>18.3471221923828</v>
       </c>
       <c r="H42" t="n">
         <v>557658</v>
@@ -1616,7 +1616,7 @@
         <v>21.5</v>
       </c>
       <c r="G43" t="n">
-        <v>19.019437789917</v>
+        <v>19.0194358825684</v>
       </c>
       <c r="H43" t="n">
         <v>1151116</v>
@@ -1645,7 +1645,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G44" t="n">
-        <v>19.001745223999</v>
+        <v>19.0017433166504</v>
       </c>
       <c r="H44" t="n">
         <v>479063</v>
@@ -1674,7 +1674,7 @@
         <v>21.3099994659424</v>
       </c>
       <c r="G45" t="n">
-        <v>18.8513603210449</v>
+        <v>18.8513565063477</v>
       </c>
       <c r="H45" t="n">
         <v>368675</v>
@@ -1732,7 +1732,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G47" t="n">
-        <v>19.992525100708</v>
+        <v>19.9925231933594</v>
       </c>
       <c r="H47" t="n">
         <v>1033585</v>
@@ -1761,7 +1761,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>19.9482898712158</v>
+        <v>19.9482917785645</v>
       </c>
       <c r="H48" t="n">
         <v>1078018</v>
@@ -1790,7 +1790,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>19.7271366119385</v>
+        <v>19.7271347045898</v>
       </c>
       <c r="H49" t="n">
         <v>805952</v>
@@ -1848,7 +1848,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G51" t="n">
-        <v>19.6475219726562</v>
+        <v>19.647518157959</v>
       </c>
       <c r="H51" t="n">
         <v>599137</v>
@@ -1906,7 +1906,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G53" t="n">
-        <v>19.1167449951172</v>
+        <v>19.1167430877686</v>
       </c>
       <c r="H53" t="n">
         <v>1070469</v>
@@ -2022,7 +2022,7 @@
         <v>22.8099994659424</v>
       </c>
       <c r="G57" t="n">
-        <v>20.178295135498</v>
+        <v>20.1782932281494</v>
       </c>
       <c r="H57" t="n">
         <v>734678</v>
@@ -2051,7 +2051,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G58" t="n">
-        <v>19.4971351623535</v>
+        <v>19.4971370697021</v>
       </c>
       <c r="H58" t="n">
         <v>1161092</v>
@@ -2138,7 +2138,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G61" t="n">
-        <v>19.4794425964355</v>
+        <v>19.4794406890869</v>
       </c>
       <c r="H61" t="n">
         <v>502164</v>
@@ -2167,7 +2167,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G62" t="n">
-        <v>19.9129085540771</v>
+        <v>19.9129066467285</v>
       </c>
       <c r="H62" t="n">
         <v>491805</v>
@@ -2225,7 +2225,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G64" t="n">
-        <v>19.4971351623535</v>
+        <v>19.4971370697021</v>
       </c>
       <c r="H64" t="n">
         <v>538910</v>
@@ -2312,7 +2312,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G67" t="n">
-        <v>18.8336696624756</v>
+        <v>18.833667755127</v>
       </c>
       <c r="H67" t="n">
         <v>490898</v>
@@ -2341,7 +2341,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G68" t="n">
-        <v>18.5152015686035</v>
+        <v>18.5151996612549</v>
       </c>
       <c r="H68" t="n">
         <v>449428</v>
@@ -2428,7 +2428,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G71" t="n">
-        <v>18.5240440368652</v>
+        <v>18.5240478515625</v>
       </c>
       <c r="H71" t="n">
         <v>1288923</v>
@@ -2486,7 +2486,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>18.9486637115479</v>
+        <v>18.9486656188965</v>
       </c>
       <c r="H73" t="n">
         <v>659167</v>
@@ -2515,7 +2515,7 @@
         <v>21.25</v>
       </c>
       <c r="G74" t="n">
-        <v>18.798282623291</v>
+        <v>18.7982807159424</v>
       </c>
       <c r="H74" t="n">
         <v>401285</v>
@@ -2602,7 +2602,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G77" t="n">
-        <v>18.8071250915527</v>
+        <v>18.8071269989014</v>
       </c>
       <c r="H77" t="n">
         <v>725644</v>
@@ -2631,7 +2631,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G78" t="n">
-        <v>18.3205833435059</v>
+        <v>18.3205814361572</v>
       </c>
       <c r="H78" t="n">
         <v>1645887</v>
@@ -2660,7 +2660,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>18.3648166656494</v>
+        <v>18.3648128509521</v>
       </c>
       <c r="H79" t="n">
         <v>1254692</v>
@@ -2718,7 +2718,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G81" t="n">
-        <v>18.0817356109619</v>
+        <v>18.0817375183105</v>
       </c>
       <c r="H81" t="n">
         <v>609476</v>
@@ -2747,7 +2747,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G82" t="n">
-        <v>18.0640411376953</v>
+        <v>18.0640392303467</v>
       </c>
       <c r="H82" t="n">
         <v>264849</v>
@@ -2805,7 +2805,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G84" t="n">
-        <v>17.878267288208</v>
+        <v>17.8782691955566</v>
       </c>
       <c r="H84" t="n">
         <v>570613</v>
@@ -2834,7 +2834,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>18.0021209716797</v>
+        <v>18.0021171569824</v>
       </c>
       <c r="H85" t="n">
         <v>455661</v>
@@ -2892,7 +2892,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G87" t="n">
-        <v>17.9048080444336</v>
+        <v>17.9048099517822</v>
       </c>
       <c r="H87" t="n">
         <v>346687</v>
@@ -2979,7 +2979,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G90" t="n">
-        <v>17.5509605407715</v>
+        <v>17.5509567260742</v>
       </c>
       <c r="H90" t="n">
         <v>721711</v>
@@ -3008,7 +3008,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G91" t="n">
-        <v>17.9844245910645</v>
+        <v>17.9844226837158</v>
       </c>
       <c r="H91" t="n">
         <v>812214</v>
@@ -3037,7 +3037,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>17.6394233703613</v>
+        <v>17.6394214630127</v>
       </c>
       <c r="H92" t="n">
         <v>678917</v>
@@ -3066,7 +3066,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G93" t="n">
-        <v>17.4182643890381</v>
+        <v>17.4182662963867</v>
       </c>
       <c r="H93" t="n">
         <v>765387</v>
@@ -3095,7 +3095,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G94" t="n">
-        <v>18.8336696624756</v>
+        <v>18.833667755127</v>
       </c>
       <c r="H94" t="n">
         <v>1861606</v>
@@ -3124,7 +3124,7 @@
         <v>21.25</v>
       </c>
       <c r="G95" t="n">
-        <v>18.798282623291</v>
+        <v>18.7982807159424</v>
       </c>
       <c r="H95" t="n">
         <v>742962</v>
@@ -3153,7 +3153,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>18.0640411376953</v>
+        <v>18.0640392303467</v>
       </c>
       <c r="H96" t="n">
         <v>670991</v>
@@ -3211,7 +3211,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>17.7367286682129</v>
+        <v>17.7367305755615</v>
       </c>
       <c r="H98" t="n">
         <v>468652</v>
@@ -3240,7 +3240,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G99" t="n">
-        <v>17.6482677459717</v>
+        <v>17.6482696533203</v>
       </c>
       <c r="H99" t="n">
         <v>692686</v>
@@ -3385,7 +3385,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G104" t="n">
-        <v>17.530553817749</v>
+        <v>17.5305557250977</v>
       </c>
       <c r="H104" t="n">
         <v>453269</v>
@@ -3472,7 +3472,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G107" t="n">
-        <v>17.3041763305664</v>
+        <v>17.304178237915</v>
       </c>
       <c r="H107" t="n">
         <v>353691</v>
@@ -3559,7 +3559,7 @@
         <v>19.25</v>
       </c>
       <c r="G110" t="n">
-        <v>17.4309482574463</v>
+        <v>17.4309463500977</v>
       </c>
       <c r="H110" t="n">
         <v>645536</v>
@@ -3588,7 +3588,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G111" t="n">
-        <v>17.4852752685547</v>
+        <v>17.4852771759033</v>
       </c>
       <c r="H111" t="n">
         <v>582475</v>
@@ -3791,7 +3791,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G118" t="n">
-        <v>17.0777988433838</v>
+        <v>17.0778007507324</v>
       </c>
       <c r="H118" t="n">
         <v>634094</v>
@@ -3820,7 +3820,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>17.8384265899658</v>
+        <v>17.8384246826172</v>
       </c>
       <c r="H119" t="n">
         <v>1228784</v>
@@ -3849,7 +3849,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G120" t="n">
-        <v>17.9380302429199</v>
+        <v>17.9380283355713</v>
       </c>
       <c r="H120" t="n">
         <v>766211</v>
@@ -3878,7 +3878,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G121" t="n">
-        <v>17.7297649383545</v>
+        <v>17.7297630310059</v>
       </c>
       <c r="H121" t="n">
         <v>523740</v>
@@ -3936,7 +3936,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G123" t="n">
-        <v>18.1825141906738</v>
+        <v>18.1825160980225</v>
       </c>
       <c r="H123" t="n">
         <v>467685</v>
@@ -3965,7 +3965,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G124" t="n">
-        <v>16.8514251708984</v>
+        <v>16.8514232635498</v>
       </c>
       <c r="H124" t="n">
         <v>1162990</v>
@@ -4023,7 +4023,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G126" t="n">
-        <v>16.6793804168701</v>
+        <v>16.6793766021729</v>
       </c>
       <c r="H126" t="n">
         <v>635006</v>
@@ -4081,7 +4081,7 @@
         <v>18.25</v>
       </c>
       <c r="G128" t="n">
-        <v>16.5254421234131</v>
+        <v>16.5254402160645</v>
       </c>
       <c r="H128" t="n">
         <v>558415</v>
@@ -4110,7 +4110,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>16.6069355010986</v>
+        <v>16.6069393157959</v>
       </c>
       <c r="H129" t="n">
         <v>464956</v>
@@ -4168,7 +4168,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G131" t="n">
-        <v>16.8242607116699</v>
+        <v>16.8242588043213</v>
       </c>
       <c r="H131" t="n">
         <v>503139</v>
@@ -4284,7 +4284,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G135" t="n">
-        <v>16.4439487457275</v>
+        <v>16.4439468383789</v>
       </c>
       <c r="H135" t="n">
         <v>444582</v>
@@ -4313,7 +4313,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G136" t="n">
-        <v>16.69748878479</v>
+        <v>16.6974906921387</v>
       </c>
       <c r="H136" t="n">
         <v>745932</v>
@@ -4371,7 +4371,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G138" t="n">
-        <v>17.1321277618408</v>
+        <v>17.1321315765381</v>
       </c>
       <c r="H138" t="n">
         <v>399511</v>
@@ -4458,7 +4458,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>17.0325260162354</v>
+        <v>17.0325222015381</v>
       </c>
       <c r="H141" t="n">
         <v>247627</v>
@@ -4545,7 +4545,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G144" t="n">
-        <v>17.9018115997314</v>
+        <v>17.9018096923828</v>
       </c>
       <c r="H144" t="n">
         <v>551371</v>
@@ -4603,7 +4603,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>17.9289722442627</v>
+        <v>17.9289741516113</v>
       </c>
       <c r="H146" t="n">
         <v>894618</v>
@@ -4690,7 +4690,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G149" t="n">
-        <v>19.0699100494385</v>
+        <v>19.0699081420898</v>
       </c>
       <c r="H149" t="n">
         <v>1159289</v>
@@ -4719,7 +4719,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G150" t="n">
-        <v>19.2147903442383</v>
+        <v>19.2147884368896</v>
       </c>
       <c r="H150" t="n">
         <v>859181</v>
@@ -4748,7 +4748,7 @@
         <v>20.5699996948242</v>
       </c>
       <c r="G151" t="n">
-        <v>18.6262130737305</v>
+        <v>18.6262111663818</v>
       </c>
       <c r="H151" t="n">
         <v>1004411</v>
@@ -4835,7 +4835,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G154" t="n">
-        <v>18.7167625427246</v>
+        <v>18.716760635376</v>
       </c>
       <c r="H154" t="n">
         <v>930993</v>
@@ -4893,7 +4893,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G156" t="n">
-        <v>18.762035369873</v>
+        <v>18.7620372772217</v>
       </c>
       <c r="H156" t="n">
         <v>454171</v>
@@ -4980,7 +4980,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G159" t="n">
-        <v>18.94313621521</v>
+        <v>18.9431381225586</v>
       </c>
       <c r="H159" t="n">
         <v>809515</v>
@@ -5009,7 +5009,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G160" t="n">
-        <v>19.0427436828613</v>
+        <v>19.04274559021</v>
       </c>
       <c r="H160" t="n">
         <v>612736</v>
@@ -5096,7 +5096,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>18.4722747802734</v>
+        <v>18.4722728729248</v>
       </c>
       <c r="H163" t="n">
         <v>404764</v>
@@ -5154,7 +5154,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G165" t="n">
-        <v>18.7529830932617</v>
+        <v>18.7529811859131</v>
       </c>
       <c r="H165" t="n">
         <v>532932</v>
@@ -5212,7 +5212,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G167" t="n">
-        <v>18.6805400848389</v>
+        <v>18.6805419921875</v>
       </c>
       <c r="H167" t="n">
         <v>579799</v>
@@ -5270,7 +5270,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G169" t="n">
-        <v>18.653377532959</v>
+        <v>18.6533794403076</v>
       </c>
       <c r="H169" t="n">
         <v>409770</v>
@@ -5299,7 +5299,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G170" t="n">
-        <v>18.7167625427246</v>
+        <v>18.716760635376</v>
       </c>
       <c r="H170" t="n">
         <v>499477</v>
@@ -5415,7 +5415,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>18.6986503601074</v>
+        <v>18.6986522674561</v>
       </c>
       <c r="H174" t="n">
         <v>355898</v>
@@ -5444,7 +5444,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G175" t="n">
-        <v>18.762035369873</v>
+        <v>18.7620372772217</v>
       </c>
       <c r="H175" t="n">
         <v>290570</v>
@@ -5473,7 +5473,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>19.106128692627</v>
+        <v>19.1061267852783</v>
       </c>
       <c r="H176" t="n">
         <v>842459</v>
@@ -5502,7 +5502,7 @@
         <v>22</v>
       </c>
       <c r="G177" t="n">
-        <v>19.9210796356201</v>
+        <v>19.9210815429688</v>
       </c>
       <c r="H177" t="n">
         <v>1987857</v>
@@ -5589,7 +5589,7 @@
         <v>21.4899997711182</v>
       </c>
       <c r="G180" t="n">
-        <v>19.4592723846436</v>
+        <v>19.4592761993408</v>
       </c>
       <c r="H180" t="n">
         <v>700088</v>
@@ -5618,7 +5618,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G181" t="n">
-        <v>19.3143939971924</v>
+        <v>19.314395904541</v>
       </c>
       <c r="H181" t="n">
         <v>672599</v>
@@ -5647,7 +5647,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G182" t="n">
-        <v>18.8888072967529</v>
+        <v>18.8888092041016</v>
       </c>
       <c r="H182" t="n">
         <v>1048604</v>
@@ -5676,7 +5676,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G183" t="n">
-        <v>18.6805400848389</v>
+        <v>18.6805419921875</v>
       </c>
       <c r="H183" t="n">
         <v>1124488</v>
@@ -5763,7 +5763,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>19.1604595184326</v>
+        <v>19.1604614257812</v>
       </c>
       <c r="H186" t="n">
         <v>685216</v>
@@ -5850,7 +5850,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>20.3557205200195</v>
+        <v>20.3557243347168</v>
       </c>
       <c r="H189" t="n">
         <v>758570</v>
@@ -5908,7 +5908,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G191" t="n">
-        <v>20.3104476928711</v>
+        <v>20.3104496002197</v>
       </c>
       <c r="H191" t="n">
         <v>716381</v>
@@ -5937,7 +5937,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>20.3919448852539</v>
+        <v>20.3919429779053</v>
       </c>
       <c r="H192" t="n">
         <v>676988</v>
@@ -5995,7 +5995,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G194" t="n">
-        <v>20.3557205200195</v>
+        <v>20.3557243347168</v>
       </c>
       <c r="H194" t="n">
         <v>517237</v>
@@ -6024,7 +6024,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>20.6907596588135</v>
+        <v>20.6907577514648</v>
       </c>
       <c r="H195" t="n">
         <v>495248</v>
@@ -6082,7 +6082,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G197" t="n">
-        <v>20.7994194030762</v>
+        <v>20.7994213104248</v>
       </c>
       <c r="H197" t="n">
         <v>492907</v>
@@ -6111,7 +6111,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G198" t="n">
-        <v>20.4009990692139</v>
+        <v>20.4010009765625</v>
       </c>
       <c r="H198" t="n">
         <v>504761</v>
@@ -6169,7 +6169,7 @@
         <v>22.6700000762939</v>
       </c>
       <c r="G200" t="n">
-        <v>20.5277690887451</v>
+        <v>20.5277709960938</v>
       </c>
       <c r="H200" t="n">
         <v>729967</v>
@@ -6198,7 +6198,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>20.3647766113281</v>
+        <v>20.3647785186768</v>
       </c>
       <c r="H201" t="n">
         <v>435292</v>
@@ -6227,7 +6227,7 @@
         <v>22.6900005340576</v>
       </c>
       <c r="G202" t="n">
-        <v>20.5458812713623</v>
+        <v>20.5458793640137</v>
       </c>
       <c r="H202" t="n">
         <v>571600</v>
@@ -6285,7 +6285,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>20.4191074371338</v>
+        <v>20.4191093444824</v>
       </c>
       <c r="H204" t="n">
         <v>692871</v>
@@ -6343,7 +6343,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G206" t="n">
-        <v>20.265172958374</v>
+        <v>20.2651710510254</v>
       </c>
       <c r="H206" t="n">
         <v>579770</v>
@@ -6401,7 +6401,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G208" t="n">
-        <v>20.3557205200195</v>
+        <v>20.3557243347168</v>
       </c>
       <c r="H208" t="n">
         <v>427306</v>
@@ -6488,7 +6488,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G211" t="n">
-        <v>20.2289543151855</v>
+        <v>20.2289524078369</v>
       </c>
       <c r="H211" t="n">
         <v>476244</v>
@@ -6517,7 +6517,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G212" t="n">
-        <v>20.5006046295166</v>
+        <v>20.500602722168</v>
       </c>
       <c r="H212" t="n">
         <v>513406</v>
@@ -6546,7 +6546,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G213" t="n">
-        <v>20.5639877319336</v>
+        <v>20.5639896392822</v>
       </c>
       <c r="H213" t="n">
         <v>450892</v>
@@ -6575,7 +6575,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G214" t="n">
-        <v>20.1836795806885</v>
+        <v>20.1836776733398</v>
       </c>
       <c r="H214" t="n">
         <v>377674</v>
@@ -6633,7 +6633,7 @@
         <v>21.5900001525879</v>
       </c>
       <c r="G216" t="n">
-        <v>19.5498237609863</v>
+        <v>19.549825668335</v>
       </c>
       <c r="H216" t="n">
         <v>443300</v>
@@ -6720,7 +6720,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G219" t="n">
-        <v>19.7218704223633</v>
+        <v>19.7218742370605</v>
       </c>
       <c r="H219" t="n">
         <v>366831</v>
@@ -6778,7 +6778,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G221" t="n">
-        <v>19.5226573944092</v>
+        <v>19.5226593017578</v>
       </c>
       <c r="H221" t="n">
         <v>845010</v>
@@ -6836,7 +6836,7 @@
         <v>21.9899997711182</v>
       </c>
       <c r="G223" t="n">
-        <v>19.9120292663574</v>
+        <v>19.9120254516602</v>
       </c>
       <c r="H223" t="n">
         <v>433755</v>
@@ -6865,7 +6865,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G224" t="n">
-        <v>19.7490348815918</v>
+        <v>19.7490386962891</v>
       </c>
       <c r="H224" t="n">
         <v>454641</v>
@@ -6894,7 +6894,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.4722747802734</v>
+        <v>18.4722728729248</v>
       </c>
       <c r="H225" t="n">
         <v>3206760</v>
@@ -6923,7 +6923,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G226" t="n">
-        <v>18.0919628143311</v>
+        <v>18.0919647216797</v>
       </c>
       <c r="H226" t="n">
         <v>1188113</v>
@@ -6952,7 +6952,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G227" t="n">
-        <v>18.3002262115479</v>
+        <v>18.3002300262451</v>
       </c>
       <c r="H227" t="n">
         <v>568589</v>
@@ -6981,7 +6981,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G228" t="n">
-        <v>18.327392578125</v>
+        <v>18.3273963928223</v>
       </c>
       <c r="H228" t="n">
         <v>773547</v>
@@ -7039,7 +7039,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G230" t="n">
-        <v>18.0104675292969</v>
+        <v>18.0104694366455</v>
       </c>
       <c r="H230" t="n">
         <v>460171</v>
@@ -7068,7 +7068,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G231" t="n">
-        <v>17.7388172149658</v>
+        <v>17.7388191223145</v>
       </c>
       <c r="H231" t="n">
         <v>492945</v>
@@ -7126,7 +7126,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>17.8203144073486</v>
+        <v>17.8203125</v>
       </c>
       <c r="H233" t="n">
         <v>203127</v>
@@ -7155,7 +7155,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G234" t="n">
-        <v>17.6392135620117</v>
+        <v>17.6392116546631</v>
       </c>
       <c r="H234" t="n">
         <v>519984</v>
@@ -7184,7 +7184,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G235" t="n">
-        <v>18.3455047607422</v>
+        <v>18.3455066680908</v>
       </c>
       <c r="H235" t="n">
         <v>701529</v>
@@ -7271,7 +7271,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>18.7167625427246</v>
+        <v>18.716760635376</v>
       </c>
       <c r="H238" t="n">
         <v>591668</v>
@@ -7387,7 +7387,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G242" t="n">
-        <v>19.3958873748779</v>
+        <v>19.3958930969238</v>
       </c>
       <c r="H242" t="n">
         <v>455970</v>
@@ -7416,7 +7416,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>19.3777770996094</v>
+        <v>19.377779006958</v>
       </c>
       <c r="H243" t="n">
         <v>365522</v>
@@ -7445,7 +7445,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G244" t="n">
-        <v>19.1151828765869</v>
+        <v>19.1151866912842</v>
       </c>
       <c r="H244" t="n">
         <v>413169</v>
@@ -7474,7 +7474,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G245" t="n">
-        <v>19.5860462188721</v>
+        <v>19.5860443115234</v>
       </c>
       <c r="H245" t="n">
         <v>394277</v>
@@ -7503,7 +7503,7 @@
         <v>21.2700004577637</v>
       </c>
       <c r="G246" t="n">
-        <v>19.2600631713867</v>
+        <v>19.2600650787354</v>
       </c>
       <c r="H246" t="n">
         <v>348399</v>
@@ -7561,7 +7561,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G248" t="n">
-        <v>20.265172958374</v>
+        <v>20.2651710510254</v>
       </c>
       <c r="H248" t="n">
         <v>1423797</v>
@@ -7619,7 +7619,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G250" t="n">
-        <v>20.265172958374</v>
+        <v>20.2651710510254</v>
       </c>
       <c r="H250" t="n">
         <v>491157</v>
@@ -7648,7 +7648,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G251" t="n">
-        <v>20.3466701507568</v>
+        <v>20.3466682434082</v>
       </c>
       <c r="H251" t="n">
         <v>359013</v>
@@ -7735,7 +7735,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G254" t="n">
-        <v>20.1836795806885</v>
+        <v>20.1836776733398</v>
       </c>
       <c r="H254" t="n">
         <v>207491</v>
@@ -7764,7 +7764,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>20.2289543151855</v>
+        <v>20.2289524078369</v>
       </c>
       <c r="H255" t="n">
         <v>284063</v>
@@ -7793,7 +7793,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>20.1565132141113</v>
+        <v>20.1565113067627</v>
       </c>
       <c r="H256" t="n">
         <v>178380</v>
@@ -7822,7 +7822,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G257" t="n">
-        <v>20.3104476928711</v>
+        <v>20.3104496002197</v>
       </c>
       <c r="H257" t="n">
         <v>331936</v>
@@ -7851,7 +7851,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G258" t="n">
-        <v>20.8084774017334</v>
+        <v>20.8084735870361</v>
       </c>
       <c r="H258" t="n">
         <v>291448</v>
@@ -7938,7 +7938,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G261" t="n">
-        <v>21.5328769683838</v>
+        <v>21.5328788757324</v>
       </c>
       <c r="H261" t="n">
         <v>1128545</v>
@@ -7967,7 +7967,7 @@
         <v>24.3700008392334</v>
       </c>
       <c r="G262" t="n">
-        <v>22.0671291351318</v>
+        <v>22.0671272277832</v>
       </c>
       <c r="H262" t="n">
         <v>1062423</v>
@@ -7996,7 +7996,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G263" t="n">
-        <v>22.058069229126</v>
+        <v>22.0580711364746</v>
       </c>
       <c r="H263" t="n">
         <v>1362031</v>
@@ -8054,7 +8054,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G265" t="n">
-        <v>22.2935047149658</v>
+        <v>22.2935028076172</v>
       </c>
       <c r="H265" t="n">
         <v>1130923</v>
@@ -8141,7 +8141,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>22.275390625</v>
+        <v>22.2753925323486</v>
       </c>
       <c r="H268" t="n">
         <v>589233</v>
@@ -8170,7 +8170,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G269" t="n">
-        <v>22.2391738891602</v>
+        <v>22.2391719818115</v>
       </c>
       <c r="H269" t="n">
         <v>512480</v>
@@ -8199,7 +8199,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G270" t="n">
-        <v>22.818696975708</v>
+        <v>22.8186988830566</v>
       </c>
       <c r="H270" t="n">
         <v>1130838</v>
@@ -8228,7 +8228,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G271" t="n">
-        <v>23.0722332000732</v>
+        <v>23.0722351074219</v>
       </c>
       <c r="H271" t="n">
         <v>906513</v>
@@ -8257,7 +8257,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G272" t="n">
-        <v>22.891134262085</v>
+        <v>22.8911361694336</v>
       </c>
       <c r="H272" t="n">
         <v>650968</v>
@@ -8315,7 +8315,7 @@
         <v>25.5100002288818</v>
       </c>
       <c r="G274" t="n">
-        <v>23.099401473999</v>
+        <v>23.0993995666504</v>
       </c>
       <c r="H274" t="n">
         <v>493640</v>
@@ -8344,7 +8344,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>22.5923194885254</v>
+        <v>22.5923175811768</v>
       </c>
       <c r="H275" t="n">
         <v>775402</v>
@@ -8431,7 +8431,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G278" t="n">
-        <v>22.1757869720459</v>
+        <v>22.1757850646973</v>
       </c>
       <c r="H278" t="n">
         <v>1066573</v>
@@ -8460,7 +8460,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G279" t="n">
-        <v>22.1395664215088</v>
+        <v>22.1395645141602</v>
       </c>
       <c r="H279" t="n">
         <v>498087</v>
@@ -8489,7 +8489,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G280" t="n">
-        <v>23.6064834594727</v>
+        <v>23.606481552124</v>
       </c>
       <c r="H280" t="n">
         <v>2579913</v>
@@ -8518,7 +8518,7 @@
         <v>26.2299995422363</v>
       </c>
       <c r="G281" t="n">
-        <v>23.7513637542725</v>
+        <v>23.7513618469238</v>
       </c>
       <c r="H281" t="n">
         <v>1163004</v>
@@ -8576,7 +8576,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G283" t="n">
-        <v>23.6427040100098</v>
+        <v>23.6427021026611</v>
       </c>
       <c r="H283" t="n">
         <v>1064235</v>
@@ -8605,7 +8605,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G284" t="n">
-        <v>23.6879787445068</v>
+        <v>23.6879749298096</v>
       </c>
       <c r="H284" t="n">
         <v>648062</v>
@@ -8721,7 +8721,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>23.7241992950439</v>
+        <v>23.7241973876953</v>
       </c>
       <c r="H288" t="n">
         <v>395279</v>
@@ -8779,7 +8779,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>23.6879787445068</v>
+        <v>23.6879749298096</v>
       </c>
       <c r="H290" t="n">
         <v>721884</v>
@@ -8808,7 +8808,7 @@
         <v>26.3099994659424</v>
       </c>
       <c r="G291" t="n">
-        <v>23.8238010406494</v>
+        <v>23.8238048553467</v>
       </c>
       <c r="H291" t="n">
         <v>504205</v>
@@ -8837,7 +8837,7 @@
         <v>26.1700000762939</v>
       </c>
       <c r="G292" t="n">
-        <v>23.6970310211182</v>
+        <v>23.6970329284668</v>
       </c>
       <c r="H292" t="n">
         <v>236982</v>
@@ -8866,7 +8866,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G293" t="n">
-        <v>23.7241992950439</v>
+        <v>23.7241973876953</v>
       </c>
       <c r="H293" t="n">
         <v>138589</v>
@@ -8895,7 +8895,7 @@
         <v>26.5200004577637</v>
       </c>
       <c r="G294" t="n">
-        <v>24.0139598846436</v>
+        <v>24.0139579772949</v>
       </c>
       <c r="H294" t="n">
         <v>741091</v>
@@ -8924,7 +8924,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G295" t="n">
-        <v>24.285608291626</v>
+        <v>24.2856121063232</v>
       </c>
       <c r="H295" t="n">
         <v>633832</v>
@@ -8982,7 +8982,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>23.9777393341064</v>
+        <v>23.9777374267578</v>
       </c>
       <c r="H297" t="n">
         <v>812325</v>
@@ -9011,7 +9011,7 @@
         <v>26.8299999237061</v>
       </c>
       <c r="G298" t="n">
-        <v>24.2946662902832</v>
+        <v>24.2946643829346</v>
       </c>
       <c r="H298" t="n">
         <v>540551</v>
@@ -9040,7 +9040,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G299" t="n">
-        <v>24.4304885864258</v>
+        <v>24.430492401123</v>
       </c>
       <c r="H299" t="n">
         <v>1219756</v>
@@ -9069,7 +9069,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G300" t="n">
-        <v>24.61159324646</v>
+        <v>24.6115951538086</v>
       </c>
       <c r="H300" t="n">
         <v>640558</v>
@@ -9156,7 +9156,7 @@
         <v>28.0400009155273</v>
       </c>
       <c r="G303" t="n">
-        <v>25.3903255462646</v>
+        <v>25.3903274536133</v>
       </c>
       <c r="H303" t="n">
         <v>911254</v>
@@ -9214,7 +9214,7 @@
         <v>28.2900009155273</v>
       </c>
       <c r="G305" t="n">
-        <v>25.6167011260986</v>
+        <v>25.6167030334473</v>
       </c>
       <c r="H305" t="n">
         <v>800161</v>
@@ -9243,7 +9243,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>25.6710338592529</v>
+        <v>25.6710319519043</v>
       </c>
       <c r="H306" t="n">
         <v>500694</v>
@@ -9272,7 +9272,7 @@
         <v>28.3299999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>25.6529197692871</v>
+        <v>25.6529216766357</v>
       </c>
       <c r="H307" t="n">
         <v>363150</v>
@@ -9359,7 +9359,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G310" t="n">
-        <v>24.955680847168</v>
+        <v>24.9556827545166</v>
       </c>
       <c r="H310" t="n">
         <v>2238630</v>
@@ -9504,7 +9504,7 @@
         <v>27.5400009155273</v>
       </c>
       <c r="G315" t="n">
-        <v>24.937572479248</v>
+        <v>24.9375762939453</v>
       </c>
       <c r="H315" t="n">
         <v>486126</v>
@@ -9533,7 +9533,7 @@
         <v>28.0200004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>25.3722152709961</v>
+        <v>25.3722133636475</v>
       </c>
       <c r="H316" t="n">
         <v>452765</v>
@@ -9591,7 +9591,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G318" t="n">
-        <v>25.2273330688477</v>
+        <v>25.2273349761963</v>
       </c>
       <c r="H318" t="n">
         <v>385409</v>
@@ -9620,7 +9620,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>25.1730041503906</v>
+        <v>25.173002243042</v>
       </c>
       <c r="H319" t="n">
         <v>545914</v>
@@ -9678,7 +9678,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>25.3993797302246</v>
+        <v>25.3993759155273</v>
       </c>
       <c r="H321" t="n">
         <v>203615</v>
@@ -9736,7 +9736,7 @@
         <v>28.4099998474121</v>
       </c>
       <c r="G323" t="n">
-        <v>25.72536277771</v>
+        <v>25.7253589630127</v>
       </c>
       <c r="H323" t="n">
         <v>704929</v>
@@ -9765,7 +9765,7 @@
         <v>27.9300003051758</v>
       </c>
       <c r="G324" t="n">
-        <v>25.2907180786133</v>
+        <v>25.2907199859619</v>
       </c>
       <c r="H324" t="n">
         <v>302233</v>
@@ -9852,7 +9852,7 @@
         <v>28.2099990844727</v>
       </c>
       <c r="G327" t="n">
-        <v>25.5442581176758</v>
+        <v>25.544261932373</v>
       </c>
       <c r="H327" t="n">
         <v>365212</v>
@@ -9881,7 +9881,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G328" t="n">
-        <v>25.4808750152588</v>
+        <v>25.4808731079102</v>
       </c>
       <c r="H328" t="n">
         <v>240731</v>
@@ -9997,7 +9997,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G332" t="n">
-        <v>24.7836399078369</v>
+        <v>24.7836380004883</v>
       </c>
       <c r="H332" t="n">
         <v>660230</v>
@@ -10026,7 +10026,7 @@
         <v>26.9699993133545</v>
       </c>
       <c r="G333" t="n">
-        <v>24.4214363098145</v>
+        <v>24.4214324951172</v>
       </c>
       <c r="H333" t="n">
         <v>775708</v>
@@ -10171,7 +10171,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>26.1237831115723</v>
+        <v>26.1237850189209</v>
       </c>
       <c r="H338" t="n">
         <v>826956</v>
@@ -10229,7 +10229,7 @@
         <v>29.4099998474121</v>
       </c>
       <c r="G340" t="n">
-        <v>26.6308631896973</v>
+        <v>26.6308650970459</v>
       </c>
       <c r="H340" t="n">
         <v>718939</v>
@@ -10258,7 +10258,7 @@
         <v>29.25</v>
       </c>
       <c r="G341" t="n">
-        <v>26.4859809875488</v>
+        <v>26.4859828948975</v>
       </c>
       <c r="H341" t="n">
         <v>324279</v>
@@ -10287,7 +10287,7 @@
         <v>29.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>26.3229923248291</v>
+        <v>26.3229942321777</v>
       </c>
       <c r="H342" t="n">
         <v>296838</v>
@@ -10316,7 +10316,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G343" t="n">
-        <v>26.6761379241943</v>
+        <v>26.6761417388916</v>
       </c>
       <c r="H343" t="n">
         <v>498694</v>
@@ -10374,7 +10374,7 @@
         <v>29</v>
       </c>
       <c r="G345" t="n">
-        <v>26.2596073150635</v>
+        <v>26.2596054077148</v>
       </c>
       <c r="H345" t="n">
         <v>806664</v>
@@ -10432,7 +10432,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G347" t="n">
-        <v>26.9115695953369</v>
+        <v>26.9115676879883</v>
       </c>
       <c r="H347" t="n">
         <v>494059</v>
@@ -10461,7 +10461,7 @@
         <v>29.4099998474121</v>
       </c>
       <c r="G348" t="n">
-        <v>26.6308631896973</v>
+        <v>26.6308650970459</v>
       </c>
       <c r="H348" t="n">
         <v>196385</v>
@@ -10490,7 +10490,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G349" t="n">
-        <v>26.6036987304688</v>
+        <v>26.6036968231201</v>
       </c>
       <c r="H349" t="n">
         <v>284270</v>
@@ -10548,7 +10548,7 @@
         <v>29</v>
       </c>
       <c r="G351" t="n">
-        <v>26.2596073150635</v>
+        <v>26.2596054077148</v>
       </c>
       <c r="H351" t="n">
         <v>536086</v>
@@ -10577,7 +10577,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G352" t="n">
-        <v>25.3088302612305</v>
+        <v>25.3088321685791</v>
       </c>
       <c r="H352" t="n">
         <v>476271</v>
@@ -10664,7 +10664,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G355" t="n">
-        <v>25.8984451293945</v>
+        <v>25.8984432220459</v>
       </c>
       <c r="H355" t="n">
         <v>233836</v>
@@ -10722,7 +10722,7 @@
         <v>26.8500003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>24.71120262146</v>
+        <v>24.7112007141113</v>
       </c>
       <c r="H357" t="n">
         <v>1752974</v>
@@ -10751,7 +10751,7 @@
         <v>25.6599998474121</v>
       </c>
       <c r="G358" t="n">
-        <v>23.6159954071045</v>
+        <v>23.6159934997559</v>
       </c>
       <c r="H358" t="n">
         <v>2202691</v>
@@ -10780,7 +10780,7 @@
         <v>25.2299995422363</v>
       </c>
       <c r="G359" t="n">
-        <v>23.2202453613281</v>
+        <v>23.2202472686768</v>
       </c>
       <c r="H359" t="n">
         <v>2339992</v>
@@ -10867,7 +10867,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>22.8705196380615</v>
+        <v>22.8705177307129</v>
       </c>
       <c r="H362" t="n">
         <v>814408</v>
@@ -10925,7 +10925,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G364" t="n">
-        <v>23.266263961792</v>
+        <v>23.2662658691406</v>
       </c>
       <c r="H364" t="n">
         <v>816109</v>
@@ -10954,7 +10954,7 @@
         <v>25.25</v>
       </c>
       <c r="G365" t="n">
-        <v>23.2386531829834</v>
+        <v>23.238655090332</v>
       </c>
       <c r="H365" t="n">
         <v>396002</v>
@@ -11041,7 +11041,7 @@
         <v>24</v>
       </c>
       <c r="G368" t="n">
-        <v>22.0882244110107</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H368" t="n">
         <v>1374366</v>
@@ -11070,7 +11070,7 @@
         <v>24.25</v>
       </c>
       <c r="G369" t="n">
-        <v>22.3183097839355</v>
+        <v>22.3183116912842</v>
       </c>
       <c r="H369" t="n">
         <v>652180</v>
@@ -11128,7 +11128,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G371" t="n">
-        <v>22.3827342987061</v>
+        <v>22.3827323913574</v>
       </c>
       <c r="H371" t="n">
         <v>349002</v>
@@ -11215,7 +11215,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G374" t="n">
-        <v>22.9533462524414</v>
+        <v>22.9533500671387</v>
       </c>
       <c r="H374" t="n">
         <v>1434500</v>
@@ -11244,7 +11244,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G375" t="n">
-        <v>22.8797206878662</v>
+        <v>22.8797225952148</v>
       </c>
       <c r="H375" t="n">
         <v>368128</v>
@@ -11273,7 +11273,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>23.2846717834473</v>
+        <v>23.2846698760986</v>
       </c>
       <c r="H376" t="n">
         <v>596955</v>
@@ -11331,7 +11331,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G378" t="n">
-        <v>23.4319267272949</v>
+        <v>23.4319248199463</v>
       </c>
       <c r="H378" t="n">
         <v>355374</v>
@@ -11389,7 +11389,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G380" t="n">
-        <v>23.0269737243652</v>
+        <v>23.0269756317139</v>
       </c>
       <c r="H380" t="n">
         <v>525690</v>
@@ -11534,7 +11534,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>21.7200908660889</v>
+        <v>21.7200889587402</v>
       </c>
       <c r="H385" t="n">
         <v>267685</v>
@@ -11563,7 +11563,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G386" t="n">
-        <v>21.5544242858887</v>
+        <v>21.5544281005859</v>
       </c>
       <c r="H386" t="n">
         <v>216910</v>
@@ -11621,7 +11621,7 @@
         <v>23.5</v>
       </c>
       <c r="G388" t="n">
-        <v>21.6280536651611</v>
+        <v>21.6280555725098</v>
       </c>
       <c r="H388" t="n">
         <v>357459</v>
@@ -11650,7 +11650,7 @@
         <v>23</v>
       </c>
       <c r="G389" t="n">
-        <v>21.1678810119629</v>
+        <v>21.1678829193115</v>
       </c>
       <c r="H389" t="n">
         <v>501698</v>
@@ -11679,7 +11679,7 @@
         <v>23</v>
       </c>
       <c r="G390" t="n">
-        <v>21.1678810119629</v>
+        <v>21.1678829193115</v>
       </c>
       <c r="H390" t="n">
         <v>281095</v>
@@ -11708,7 +11708,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G391" t="n">
-        <v>21.2046966552734</v>
+        <v>21.2046985626221</v>
       </c>
       <c r="H391" t="n">
         <v>426099</v>
@@ -11795,7 +11795,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G394" t="n">
-        <v>21.5084114074707</v>
+        <v>21.5084095001221</v>
       </c>
       <c r="H394" t="n">
         <v>401727</v>
@@ -11853,7 +11853,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G396" t="n">
-        <v>21.8857498168945</v>
+        <v>21.8857517242432</v>
       </c>
       <c r="H396" t="n">
         <v>305318</v>
@@ -11940,7 +11940,7 @@
         <v>24.3099994659424</v>
       </c>
       <c r="G399" t="n">
-        <v>22.3735332489014</v>
+        <v>22.3735313415527</v>
       </c>
       <c r="H399" t="n">
         <v>712169</v>
@@ -11969,7 +11969,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G400" t="n">
-        <v>22.2170753479004</v>
+        <v>22.2170734405518</v>
       </c>
       <c r="H400" t="n">
         <v>358847</v>
@@ -11998,7 +11998,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G401" t="n">
-        <v>22.4103469848633</v>
+        <v>22.410343170166</v>
       </c>
       <c r="H401" t="n">
         <v>372937</v>
@@ -12027,7 +12027,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G402" t="n">
-        <v>22.5299873352051</v>
+        <v>22.5299911499023</v>
       </c>
       <c r="H402" t="n">
         <v>279268</v>
@@ -12085,7 +12085,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G404" t="n">
-        <v>22.6404304504395</v>
+        <v>22.6404323577881</v>
       </c>
       <c r="H404" t="n">
         <v>432144</v>
@@ -12114,7 +12114,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G405" t="n">
-        <v>22.5576000213623</v>
+        <v>22.5576019287109</v>
       </c>
       <c r="H405" t="n">
         <v>352700</v>
@@ -12143,7 +12143,7 @@
         <v>24</v>
       </c>
       <c r="G406" t="n">
-        <v>22.0882244110107</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H406" t="n">
         <v>1576783</v>
@@ -12230,7 +12230,7 @@
         <v>24</v>
       </c>
       <c r="G409" t="n">
-        <v>22.0882244110107</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H409" t="n">
         <v>517420</v>
@@ -12259,7 +12259,7 @@
         <v>24.1900005340576</v>
       </c>
       <c r="G410" t="n">
-        <v>22.263090133667</v>
+        <v>22.2630920410156</v>
       </c>
       <c r="H410" t="n">
         <v>366457</v>
@@ -12317,7 +12317,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G412" t="n">
-        <v>22.3551254272461</v>
+        <v>22.3551273345947</v>
       </c>
       <c r="H412" t="n">
         <v>262904</v>
@@ -12346,7 +12346,7 @@
         <v>24.25</v>
       </c>
       <c r="G413" t="n">
-        <v>22.3183097839355</v>
+        <v>22.3183116912842</v>
       </c>
       <c r="H413" t="n">
         <v>259593</v>
@@ -12375,7 +12375,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G414" t="n">
-        <v>22.0514106750488</v>
+        <v>22.0514125823975</v>
       </c>
       <c r="H414" t="n">
         <v>315380</v>
@@ -12462,7 +12462,7 @@
         <v>24.2700004577637</v>
       </c>
       <c r="G417" t="n">
-        <v>22.3367195129395</v>
+        <v>22.3367176055908</v>
       </c>
       <c r="H417" t="n">
         <v>583263</v>
@@ -12491,7 +12491,7 @@
         <v>24.0300006866455</v>
       </c>
       <c r="G418" t="n">
-        <v>22.1158351898193</v>
+        <v>22.115837097168</v>
       </c>
       <c r="H418" t="n">
         <v>245071</v>
@@ -12636,7 +12636,7 @@
         <v>24</v>
       </c>
       <c r="G423" t="n">
-        <v>22.0882244110107</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H423" t="n">
         <v>206329</v>
@@ -12694,7 +12694,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G425" t="n">
-        <v>21.7016830444336</v>
+        <v>21.701681137085</v>
       </c>
       <c r="H425" t="n">
         <v>416770</v>
@@ -12723,7 +12723,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G426" t="n">
-        <v>22.0053939819336</v>
+        <v>22.0053958892822</v>
       </c>
       <c r="H426" t="n">
         <v>237338</v>
@@ -12752,7 +12752,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G427" t="n">
-        <v>22.2170753479004</v>
+        <v>22.2170734405518</v>
       </c>
       <c r="H427" t="n">
         <v>537878</v>
@@ -12781,7 +12781,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G428" t="n">
-        <v>22.3551254272461</v>
+        <v>22.3551273345947</v>
       </c>
       <c r="H428" t="n">
         <v>451750</v>
@@ -12810,7 +12810,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G429" t="n">
-        <v>22.0053939819336</v>
+        <v>22.0053958892822</v>
       </c>
       <c r="H429" t="n">
         <v>233703</v>
@@ -12897,7 +12897,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G432" t="n">
-        <v>22.1250419616699</v>
+        <v>22.1250400543213</v>
       </c>
       <c r="H432" t="n">
         <v>181819</v>
@@ -12926,7 +12926,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G433" t="n">
-        <v>21.7753105163574</v>
+        <v>21.7753086090088</v>
       </c>
       <c r="H433" t="n">
         <v>453628</v>
@@ -13042,7 +13042,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G437" t="n">
-        <v>21.683277130127</v>
+        <v>21.6832733154297</v>
       </c>
       <c r="H437" t="n">
         <v>578488</v>
@@ -13071,7 +13071,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G438" t="n">
-        <v>20.827356338501</v>
+        <v>20.8273544311523</v>
       </c>
       <c r="H438" t="n">
         <v>1417619</v>
@@ -13129,7 +13129,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G440" t="n">
-        <v>20.9470024108887</v>
+        <v>20.9469985961914</v>
       </c>
       <c r="H440" t="n">
         <v>418634</v>
@@ -13187,7 +13187,7 @@
         <v>22.9300003051758</v>
       </c>
       <c r="G442" t="n">
-        <v>21.1034603118896</v>
+        <v>21.103458404541</v>
       </c>
       <c r="H442" t="n">
         <v>361840</v>
@@ -13245,7 +13245,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G444" t="n">
-        <v>21.3243408203125</v>
+        <v>21.3243427276611</v>
       </c>
       <c r="H444" t="n">
         <v>333907</v>
@@ -13274,7 +13274,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>21.9501781463623</v>
+        <v>21.9501762390137</v>
       </c>
       <c r="H445" t="n">
         <v>1478816</v>
@@ -13303,7 +13303,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G446" t="n">
-        <v>22.0974311828613</v>
+        <v>22.0974292755127</v>
       </c>
       <c r="H446" t="n">
         <v>1051424</v>
@@ -13332,7 +13332,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G447" t="n">
-        <v>22.0514106750488</v>
+        <v>22.0514125823975</v>
       </c>
       <c r="H447" t="n">
         <v>633441</v>
@@ -13361,7 +13361,7 @@
         <v>23.75</v>
       </c>
       <c r="G448" t="n">
-        <v>21.8581390380859</v>
+        <v>21.8581371307373</v>
       </c>
       <c r="H448" t="n">
         <v>541964</v>
@@ -13390,7 +13390,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>22.3827342987061</v>
+        <v>22.3827323913574</v>
       </c>
       <c r="H449" t="n">
         <v>855777</v>
@@ -13419,7 +13419,7 @@
         <v>23.5100002288818</v>
       </c>
       <c r="G450" t="n">
-        <v>21.6372585296631</v>
+        <v>21.6372566223145</v>
       </c>
       <c r="H450" t="n">
         <v>1176964</v>
@@ -13477,7 +13477,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G452" t="n">
-        <v>20.9746131896973</v>
+        <v>20.9746112823486</v>
       </c>
       <c r="H452" t="n">
         <v>950234</v>
@@ -13535,7 +13535,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>20.9838123321533</v>
+        <v>20.983814239502</v>
       </c>
       <c r="H454" t="n">
         <v>572574</v>
@@ -13593,7 +13593,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G456" t="n">
-        <v>21.0666465759277</v>
+        <v>21.0666446685791</v>
       </c>
       <c r="H456" t="n">
         <v>654865</v>
@@ -13622,7 +13622,7 @@
         <v>22.5</v>
       </c>
       <c r="G457" t="n">
-        <v>20.7077121734619</v>
+        <v>20.7077102661133</v>
       </c>
       <c r="H457" t="n">
         <v>475690</v>
@@ -13651,7 +13651,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G458" t="n">
-        <v>21.0942554473877</v>
+        <v>21.0942573547363</v>
       </c>
       <c r="H458" t="n">
         <v>987915</v>
@@ -13680,7 +13680,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G459" t="n">
-        <v>21.1586799621582</v>
+        <v>21.1586780548096</v>
       </c>
       <c r="H459" t="n">
         <v>440417</v>
@@ -13709,7 +13709,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G460" t="n">
-        <v>21.0206260681152</v>
+        <v>21.0206317901611</v>
       </c>
       <c r="H460" t="n">
         <v>386462</v>
@@ -13883,7 +13883,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G466" t="n">
-        <v>20.0082511901855</v>
+        <v>20.0082492828369</v>
       </c>
       <c r="H466" t="n">
         <v>1396902</v>
@@ -13912,7 +13912,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>19.9714393615723</v>
+        <v>19.9714374542236</v>
       </c>
       <c r="H467" t="n">
         <v>1435364</v>
@@ -13941,7 +13941,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>20.0634727478027</v>
+        <v>20.0634708404541</v>
       </c>
       <c r="H468" t="n">
         <v>1097685</v>
@@ -13999,7 +13999,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G470" t="n">
-        <v>20.7445278167725</v>
+        <v>20.7445259094238</v>
       </c>
       <c r="H470" t="n">
         <v>785130</v>
@@ -14057,7 +14057,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G472" t="n">
-        <v>21.0206260681152</v>
+        <v>21.0206317901611</v>
       </c>
       <c r="H472" t="n">
         <v>601843</v>
@@ -14086,7 +14086,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G473" t="n">
-        <v>21.0666465759277</v>
+        <v>21.0666446685791</v>
       </c>
       <c r="H473" t="n">
         <v>317345</v>
@@ -14144,7 +14144,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G475" t="n">
-        <v>20.9285945892334</v>
+        <v>20.9285926818848</v>
       </c>
       <c r="H475" t="n">
         <v>884159</v>
@@ -14173,7 +14173,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G476" t="n">
-        <v>20.9470024108887</v>
+        <v>20.9469985961914</v>
       </c>
       <c r="H476" t="n">
         <v>584780</v>
@@ -14202,7 +14202,7 @@
         <v>22.5</v>
       </c>
       <c r="G477" t="n">
-        <v>20.7077121734619</v>
+        <v>20.7077102661133</v>
       </c>
       <c r="H477" t="n">
         <v>777593</v>
@@ -14231,7 +14231,7 @@
         <v>22</v>
       </c>
       <c r="G478" t="n">
-        <v>20.247537612915</v>
+        <v>20.2475414276123</v>
       </c>
       <c r="H478" t="n">
         <v>750579</v>
@@ -14318,7 +14318,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G481" t="n">
-        <v>19.2719745635986</v>
+        <v>19.2719783782959</v>
       </c>
       <c r="H481" t="n">
         <v>2609341</v>
@@ -14376,7 +14376,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G483" t="n">
-        <v>19.8057765960693</v>
+        <v>19.8057746887207</v>
       </c>
       <c r="H483" t="n">
         <v>546959</v>
@@ -14405,7 +14405,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G484" t="n">
-        <v>19.7321491241455</v>
+        <v>19.7321472167969</v>
       </c>
       <c r="H484" t="n">
         <v>421554</v>
@@ -14463,7 +14463,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G486" t="n">
-        <v>20.0450630187988</v>
+        <v>20.0450668334961</v>
       </c>
       <c r="H486" t="n">
         <v>455042</v>
@@ -14608,7 +14608,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G491" t="n">
-        <v>20.9838123321533</v>
+        <v>20.983814239502</v>
       </c>
       <c r="H491" t="n">
         <v>580090</v>
@@ -14637,7 +14637,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G492" t="n">
-        <v>21.1310653686523</v>
+        <v>21.1310691833496</v>
       </c>
       <c r="H492" t="n">
         <v>486588</v>
@@ -14666,7 +14666,7 @@
         <v>22.5</v>
       </c>
       <c r="G493" t="n">
-        <v>20.7077121734619</v>
+        <v>20.7077102661133</v>
       </c>
       <c r="H493" t="n">
         <v>633331</v>
@@ -14869,7 +14869,7 @@
         <v>22.6100006103516</v>
       </c>
       <c r="G500" t="n">
-        <v>20.8089485168457</v>
+        <v>20.8089504241943</v>
       </c>
       <c r="H500" t="n">
         <v>1494988</v>
@@ -14898,7 +14898,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G501" t="n">
-        <v>20.6708946228027</v>
+        <v>20.6708965301514</v>
       </c>
       <c r="H501" t="n">
         <v>483213</v>
@@ -14927,7 +14927,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G502" t="n">
-        <v>20.7721366882324</v>
+        <v>20.7721347808838</v>
       </c>
       <c r="H502" t="n">
         <v>621541</v>
@@ -14985,7 +14985,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G504" t="n">
-        <v>19.796573638916</v>
+        <v>19.7965717315674</v>
       </c>
       <c r="H504" t="n">
         <v>852016</v>
@@ -15072,7 +15072,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G507" t="n">
-        <v>20.2199268341064</v>
+        <v>20.2199287414551</v>
       </c>
       <c r="H507" t="n">
         <v>372050</v>
@@ -15130,7 +15130,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>20.2291316986084</v>
+        <v>20.229133605957</v>
       </c>
       <c r="H509" t="n">
         <v>191733</v>
@@ -15217,7 +15217,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G512" t="n">
-        <v>20.2199268341064</v>
+        <v>20.2199287414551</v>
       </c>
       <c r="H512" t="n">
         <v>214152</v>
@@ -15304,7 +15304,7 @@
         <v>22.7199993133545</v>
       </c>
       <c r="G515" t="n">
-        <v>20.9101848602295</v>
+        <v>20.9101867675781</v>
       </c>
       <c r="H515" t="n">
         <v>306176</v>
@@ -15391,7 +15391,7 @@
         <v>22.2399997711182</v>
       </c>
       <c r="G518" t="n">
-        <v>20.4684219360352</v>
+        <v>20.4684238433838</v>
       </c>
       <c r="H518" t="n">
         <v>324669</v>
@@ -15420,7 +15420,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>20.1555061340332</v>
+        <v>20.1555042266846</v>
       </c>
       <c r="H519" t="n">
         <v>434900</v>
@@ -15536,7 +15536,7 @@
         <v>22</v>
       </c>
       <c r="G523" t="n">
-        <v>20.247537612915</v>
+        <v>20.2475414276123</v>
       </c>
       <c r="H523" t="n">
         <v>290730</v>
@@ -15594,7 +15594,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G525" t="n">
-        <v>20.9470024108887</v>
+        <v>20.9469985961914</v>
       </c>
       <c r="H525" t="n">
         <v>908844</v>
@@ -15681,7 +15681,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>21.2599182128906</v>
+        <v>21.259916305542</v>
       </c>
       <c r="H528" t="n">
         <v>954306</v>
@@ -15710,7 +15710,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>21.2599182128906</v>
+        <v>21.259916305542</v>
       </c>
       <c r="H529" t="n">
         <v>726158</v>
@@ -15768,7 +15768,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G531" t="n">
-        <v>21.5176105499268</v>
+        <v>21.5176124572754</v>
       </c>
       <c r="H531" t="n">
         <v>399997</v>
@@ -15855,7 +15855,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G534" t="n">
-        <v>21.3243408203125</v>
+        <v>21.3243427276611</v>
       </c>
       <c r="H534" t="n">
         <v>2061434</v>
@@ -15913,7 +15913,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G536" t="n">
-        <v>20.5052394866943</v>
+        <v>20.5052375793457</v>
       </c>
       <c r="H536" t="n">
         <v>400016</v>
@@ -15942,7 +15942,7 @@
         <v>22.1100006103516</v>
       </c>
       <c r="G537" t="n">
-        <v>20.3487777709961</v>
+        <v>20.3487796783447</v>
       </c>
       <c r="H537" t="n">
         <v>482372</v>
@@ -16058,7 +16058,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G541" t="n">
-        <v>20.0082511901855</v>
+        <v>20.0082492828369</v>
       </c>
       <c r="H541" t="n">
         <v>190751</v>
@@ -16116,7 +16116,7 @@
         <v>22</v>
       </c>
       <c r="G543" t="n">
-        <v>20.247537612915</v>
+        <v>20.2475414276123</v>
       </c>
       <c r="H543" t="n">
         <v>619390</v>
@@ -16145,7 +16145,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G544" t="n">
-        <v>20.5604572296143</v>
+        <v>20.5604553222656</v>
       </c>
       <c r="H544" t="n">
         <v>590508</v>
@@ -16174,7 +16174,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G545" t="n">
-        <v>20.7169170379639</v>
+        <v>20.7169151306152</v>
       </c>
       <c r="H545" t="n">
         <v>416813</v>
@@ -16261,7 +16261,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G548" t="n">
-        <v>20.9838123321533</v>
+        <v>20.983814239502</v>
       </c>
       <c r="H548" t="n">
         <v>361715</v>
@@ -16319,7 +16319,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G550" t="n">
-        <v>20.9285945892334</v>
+        <v>20.9285926818848</v>
       </c>
       <c r="H550" t="n">
         <v>308603</v>
@@ -16348,7 +16348,7 @@
         <v>22.75</v>
       </c>
       <c r="G551" t="n">
-        <v>20.9377956390381</v>
+        <v>20.9377975463867</v>
       </c>
       <c r="H551" t="n">
         <v>330493</v>
@@ -16377,7 +16377,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G552" t="n">
-        <v>20.8365592956543</v>
+        <v>20.8365573883057</v>
       </c>
       <c r="H552" t="n">
         <v>218015</v>
@@ -16493,7 +16493,7 @@
         <v>22.0300006866455</v>
       </c>
       <c r="G556" t="n">
-        <v>20.2751502990723</v>
+        <v>20.2751522064209</v>
       </c>
       <c r="H556" t="n">
         <v>754774</v>
@@ -16580,7 +16580,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>19.9714393615723</v>
+        <v>19.9714374542236</v>
       </c>
       <c r="H559" t="n">
         <v>860738</v>
@@ -16638,7 +16638,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G561" t="n">
-        <v>19.9990463256836</v>
+        <v>19.999044418335</v>
       </c>
       <c r="H561" t="n">
         <v>740982</v>
@@ -16725,7 +16725,7 @@
         <v>21.8700008392334</v>
       </c>
       <c r="G564" t="n">
-        <v>20.1278972625732</v>
+        <v>20.1278953552246</v>
       </c>
       <c r="H564" t="n">
         <v>432785</v>
@@ -16754,7 +16754,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G565" t="n">
-        <v>20.3303737640381</v>
+        <v>20.3303699493408</v>
       </c>
       <c r="H565" t="n">
         <v>576204</v>
@@ -16870,7 +16870,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G569" t="n">
-        <v>20.3763866424561</v>
+        <v>20.3763904571533</v>
       </c>
       <c r="H569" t="n">
         <v>262537</v>
@@ -17044,7 +17044,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G575" t="n">
-        <v>20.6432857513428</v>
+        <v>20.6432876586914</v>
       </c>
       <c r="H575" t="n">
         <v>199750</v>
@@ -17073,7 +17073,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>20.6156787872314</v>
+        <v>20.6156768798828</v>
       </c>
       <c r="H576" t="n">
         <v>263654</v>
@@ -17102,7 +17102,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G577" t="n">
-        <v>20.7445278167725</v>
+        <v>20.7445259094238</v>
       </c>
       <c r="H577" t="n">
         <v>342737</v>
@@ -17131,7 +17131,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G578" t="n">
-        <v>20.7169170379639</v>
+        <v>20.7169151306152</v>
       </c>
       <c r="H578" t="n">
         <v>410183</v>
@@ -17218,7 +17218,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G581" t="n">
-        <v>20.7261199951172</v>
+        <v>20.7261180877686</v>
       </c>
       <c r="H581" t="n">
         <v>617911</v>
@@ -17247,7 +17247,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G582" t="n">
-        <v>20.9746131896973</v>
+        <v>20.9746112823486</v>
       </c>
       <c r="H582" t="n">
         <v>623938</v>
@@ -17276,7 +17276,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G583" t="n">
-        <v>21.2046966552734</v>
+        <v>21.2046985626221</v>
       </c>
       <c r="H583" t="n">
         <v>434729</v>
@@ -17305,7 +17305,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>21.2783260345459</v>
+        <v>21.2783241271973</v>
       </c>
       <c r="H584" t="n">
         <v>190641</v>
@@ -17363,7 +17363,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G586" t="n">
-        <v>21.7753105163574</v>
+        <v>21.7753086090088</v>
       </c>
       <c r="H586" t="n">
         <v>733370</v>
@@ -17450,7 +17450,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G589" t="n">
-        <v>21.7937164306641</v>
+        <v>21.7937145233154</v>
       </c>
       <c r="H589" t="n">
         <v>611824</v>
@@ -17508,7 +17508,7 @@
         <v>24.5</v>
       </c>
       <c r="G591" t="n">
-        <v>22.548397064209</v>
+        <v>22.5483989715576</v>
       </c>
       <c r="H591" t="n">
         <v>1072195</v>
@@ -17537,7 +17537,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G592" t="n">
-        <v>22.419548034668</v>
+        <v>22.4195499420166</v>
       </c>
       <c r="H592" t="n">
         <v>493451</v>
@@ -17624,7 +17624,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G595" t="n">
-        <v>22.8797206878662</v>
+        <v>22.8797225952148</v>
       </c>
       <c r="H595" t="n">
         <v>677550</v>
@@ -17682,7 +17682,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>22.6404304504395</v>
+        <v>22.6404323577881</v>
       </c>
       <c r="H597" t="n">
         <v>903419</v>
@@ -17711,7 +17711,7 @@
         <v>24.5699996948242</v>
       </c>
       <c r="G598" t="n">
-        <v>22.6128215789795</v>
+        <v>22.6128177642822</v>
       </c>
       <c r="H598" t="n">
         <v>293934</v>
@@ -17769,7 +17769,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>22.9165325164795</v>
+        <v>22.9165344238281</v>
       </c>
       <c r="H600" t="n">
         <v>543073</v>
@@ -17856,7 +17856,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G603" t="n">
-        <v>22.833703994751</v>
+        <v>22.8337020874023</v>
       </c>
       <c r="H603" t="n">
         <v>232191</v>
@@ -17885,7 +17885,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G604" t="n">
-        <v>22.7692794799805</v>
+        <v>22.7692775726318</v>
       </c>
       <c r="H604" t="n">
         <v>300428</v>
@@ -17914,7 +17914,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G605" t="n">
-        <v>22.9073295593262</v>
+        <v>22.9073314666748</v>
       </c>
       <c r="H605" t="n">
         <v>415746</v>
@@ -17943,7 +17943,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G606" t="n">
-        <v>23.2754669189453</v>
+        <v>23.2754707336426</v>
       </c>
       <c r="H606" t="n">
         <v>719915</v>
@@ -17972,7 +17972,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>22.9165325164795</v>
+        <v>22.9165344238281</v>
       </c>
       <c r="H607" t="n">
         <v>378581</v>
@@ -18001,7 +18001,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G608" t="n">
-        <v>22.9913024902344</v>
+        <v>22.991304397583</v>
       </c>
       <c r="H608" t="n">
         <v>259914</v>
@@ -18030,7 +18030,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G609" t="n">
-        <v>23.3090686798096</v>
+        <v>23.3090705871582</v>
       </c>
       <c r="H609" t="n">
         <v>451695</v>
@@ -18117,7 +18117,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G612" t="n">
-        <v>22.9819583892822</v>
+        <v>22.9819564819336</v>
       </c>
       <c r="H612" t="n">
         <v>524215</v>
@@ -18146,7 +18146,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G613" t="n">
-        <v>22.7296123504639</v>
+        <v>22.7296142578125</v>
       </c>
       <c r="H613" t="n">
         <v>339316</v>
@@ -18175,7 +18175,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G614" t="n">
-        <v>22.3557720184326</v>
+        <v>22.355770111084</v>
       </c>
       <c r="H614" t="n">
         <v>700947</v>
@@ -18233,7 +18233,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G616" t="n">
-        <v>23.0754203796387</v>
+        <v>23.07541847229</v>
       </c>
       <c r="H616" t="n">
         <v>441644</v>
@@ -18407,7 +18407,7 @@
         <v>24.3299999237061</v>
       </c>
       <c r="G622" t="n">
-        <v>22.7389602661133</v>
+        <v>22.7389583587646</v>
       </c>
       <c r="H622" t="n">
         <v>507897</v>
@@ -18581,7 +18581,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G628" t="n">
-        <v>23.262336730957</v>
+        <v>23.2623405456543</v>
       </c>
       <c r="H628" t="n">
         <v>200051</v>
@@ -18639,7 +18639,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G630" t="n">
-        <v>20.9912452697754</v>
+        <v>20.991247177124</v>
       </c>
       <c r="H630" t="n">
         <v>3551454</v>
@@ -18726,7 +18726,7 @@
         <v>21.3899993896484</v>
       </c>
       <c r="G633" t="n">
-        <v>19.9912166595459</v>
+        <v>19.9912185668945</v>
       </c>
       <c r="H633" t="n">
         <v>537735</v>
@@ -18784,7 +18784,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G635" t="n">
-        <v>19.5613021850586</v>
+        <v>19.5612983703613</v>
       </c>
       <c r="H635" t="n">
         <v>788412</v>
@@ -18842,7 +18842,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>19.5332622528076</v>
+        <v>19.533260345459</v>
       </c>
       <c r="H637" t="n">
         <v>512477</v>
@@ -18871,7 +18871,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G638" t="n">
-        <v>19.4958782196045</v>
+        <v>19.4958763122559</v>
       </c>
       <c r="H638" t="n">
         <v>703698</v>
@@ -18900,7 +18900,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>19.346342086792</v>
+        <v>19.3463401794434</v>
       </c>
       <c r="H639" t="n">
         <v>480213</v>
@@ -18987,7 +18987,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G642" t="n">
-        <v>18.3836975097656</v>
+        <v>18.383695602417</v>
       </c>
       <c r="H642" t="n">
         <v>773362</v>
@@ -19016,7 +19016,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G643" t="n">
-        <v>18.0752735137939</v>
+        <v>18.0752754211426</v>
       </c>
       <c r="H643" t="n">
         <v>1161319</v>
@@ -19074,7 +19074,7 @@
         <v>19.3449993133545</v>
       </c>
       <c r="G645" t="n">
-        <v>18.0799503326416</v>
+        <v>18.079948425293</v>
       </c>
       <c r="H645" t="n">
         <v>718306</v>
@@ -19103,7 +19103,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G646" t="n">
-        <v>18.3836975097656</v>
+        <v>18.383695602417</v>
       </c>
       <c r="H646" t="n">
         <v>373552</v>
@@ -19132,7 +19132,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G647" t="n">
-        <v>18.6033306121826</v>
+        <v>18.603328704834</v>
       </c>
       <c r="H647" t="n">
         <v>410650</v>
@@ -19161,7 +19161,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G648" t="n">
-        <v>18.6360416412354</v>
+        <v>18.6360397338867</v>
       </c>
       <c r="H648" t="n">
         <v>360124</v>
@@ -19422,7 +19422,7 @@
         <v>19.7250003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>18.4350986480713</v>
+        <v>18.4351005554199</v>
       </c>
       <c r="H657" t="n">
         <v>260719</v>
@@ -19451,7 +19451,7 @@
         <v>19.6749992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>18.3883686065674</v>
+        <v>18.388370513916</v>
       </c>
       <c r="H658" t="n">
         <v>425030</v>
@@ -19538,7 +19538,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>17.8042392730713</v>
+        <v>17.8042373657227</v>
       </c>
       <c r="H661" t="n">
         <v>581210</v>
@@ -19567,7 +19567,7 @@
         <v>19.0149993896484</v>
       </c>
       <c r="G662" t="n">
-        <v>17.7715263366699</v>
+        <v>17.7715282440186</v>
       </c>
       <c r="H662" t="n">
         <v>552026</v>
@@ -19654,7 +19654,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G665" t="n">
-        <v>18.6734218597412</v>
+        <v>18.6734237670898</v>
       </c>
       <c r="H665" t="n">
         <v>384784</v>
@@ -19712,7 +19712,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G667" t="n">
-        <v>18.7294998168945</v>
+        <v>18.7295017242432</v>
       </c>
       <c r="H667" t="n">
         <v>363161</v>
@@ -19741,7 +19741,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G668" t="n">
-        <v>18.6734218597412</v>
+        <v>18.6734237670898</v>
       </c>
       <c r="H668" t="n">
         <v>269268</v>
@@ -19886,7 +19886,7 @@
         <v>19.4850006103516</v>
       </c>
       <c r="G673" t="n">
-        <v>18.2107963562012</v>
+        <v>18.2107944488525</v>
       </c>
       <c r="H673" t="n">
         <v>377383</v>
@@ -19973,7 +19973,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>19.4398002624512</v>
+        <v>19.4397983551025</v>
       </c>
       <c r="H676" t="n">
         <v>781937</v>
@@ -20089,7 +20089,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G680" t="n">
-        <v>19.3650302886963</v>
+        <v>19.3650341033936</v>
       </c>
       <c r="H680" t="n">
         <v>208015</v>
@@ -20118,7 +20118,7 @@
         <v>20.5</v>
       </c>
       <c r="G681" t="n">
-        <v>19.1594181060791</v>
+        <v>19.1594200134277</v>
       </c>
       <c r="H681" t="n">
         <v>262991</v>
@@ -20234,7 +20234,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G685" t="n">
-        <v>18.7388439178467</v>
+        <v>18.7388458251953</v>
       </c>
       <c r="H685" t="n">
         <v>362000</v>
@@ -20263,7 +20263,7 @@
         <v>20.5</v>
       </c>
       <c r="G686" t="n">
-        <v>19.1594181060791</v>
+        <v>19.1594200134277</v>
       </c>
       <c r="H686" t="n">
         <v>375929</v>
@@ -20292,7 +20292,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G687" t="n">
-        <v>19.0566120147705</v>
+        <v>19.0566101074219</v>
       </c>
       <c r="H687" t="n">
         <v>411927</v>
@@ -20350,7 +20350,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G689" t="n">
-        <v>19.6080284118652</v>
+        <v>19.6080303192139</v>
       </c>
       <c r="H689" t="n">
         <v>1702447</v>
@@ -20437,7 +20437,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G692" t="n">
-        <v>19.4211082458496</v>
+        <v>19.4211101531982</v>
       </c>
       <c r="H692" t="n">
         <v>207950</v>
@@ -20495,7 +20495,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G694" t="n">
-        <v>20.0753345489502</v>
+        <v>20.0753326416016</v>
       </c>
       <c r="H694" t="n">
         <v>493504</v>
@@ -20553,7 +20553,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G696" t="n">
-        <v>20.0192546844482</v>
+        <v>20.0192565917969</v>
       </c>
       <c r="H696" t="n">
         <v>722231</v>
@@ -20582,7 +20582,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G697" t="n">
-        <v>19.6080284118652</v>
+        <v>19.6080303192139</v>
       </c>
       <c r="H697" t="n">
         <v>362558</v>
@@ -20611,7 +20611,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>19.7669124603271</v>
+        <v>19.7669105529785</v>
       </c>
       <c r="H698" t="n">
         <v>331792</v>
@@ -20640,7 +20640,7 @@
         <v>21.1700000762939</v>
       </c>
       <c r="G699" t="n">
-        <v>19.7856044769287</v>
+        <v>19.7856063842773</v>
       </c>
       <c r="H699" t="n">
         <v>160234</v>
@@ -20669,7 +20669,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G700" t="n">
-        <v>19.5706443786621</v>
+        <v>19.5706462860107</v>
       </c>
       <c r="H700" t="n">
         <v>276548</v>
@@ -20698,7 +20698,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G701" t="n">
-        <v>19.2809162139893</v>
+        <v>19.2809181213379</v>
       </c>
       <c r="H701" t="n">
         <v>334676</v>
@@ -20785,7 +20785,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G704" t="n">
-        <v>19.0566120147705</v>
+        <v>19.0566101074219</v>
       </c>
       <c r="H704" t="n">
         <v>303150</v>
@@ -20872,7 +20872,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>18.1780853271484</v>
+        <v>18.1780834197998</v>
       </c>
       <c r="H707" t="n">
         <v>397647</v>
@@ -20901,7 +20901,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>18.6453857421875</v>
+        <v>18.6453876495361</v>
       </c>
       <c r="H708" t="n">
         <v>698237</v>
@@ -20988,7 +20988,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G711" t="n">
-        <v>17.1546897888184</v>
+        <v>17.1546878814697</v>
       </c>
       <c r="H711" t="n">
         <v>1871086</v>
@@ -21017,7 +21017,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G712" t="n">
-        <v>16.9817886352539</v>
+        <v>16.9817867279053</v>
       </c>
       <c r="H712" t="n">
         <v>290212</v>
@@ -21046,7 +21046,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G713" t="n">
-        <v>18.1360244750977</v>
+        <v>18.1360263824463</v>
       </c>
       <c r="H713" t="n">
         <v>712846</v>
@@ -21162,7 +21162,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G717" t="n">
-        <v>19.5706443786621</v>
+        <v>19.5706462860107</v>
       </c>
       <c r="H717" t="n">
         <v>1765099</v>
@@ -21191,7 +21191,7 @@
         <v>20.5300006866455</v>
       </c>
       <c r="G718" t="n">
-        <v>19.1874561309814</v>
+        <v>19.1874580383301</v>
       </c>
       <c r="H718" t="n">
         <v>665558</v>
@@ -21307,7 +21307,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G722" t="n">
-        <v>19.6454162597656</v>
+        <v>19.645414352417</v>
       </c>
       <c r="H722" t="n">
         <v>418618</v>
@@ -21365,7 +21365,7 @@
         <v>20.9099998474121</v>
       </c>
       <c r="G724" t="n">
-        <v>19.5426063537598</v>
+        <v>19.5426082611084</v>
       </c>
       <c r="H724" t="n">
         <v>436766</v>
@@ -21481,7 +21481,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>19.4398002624512</v>
+        <v>19.4397983551025</v>
       </c>
       <c r="H728" t="n">
         <v>482531</v>
@@ -21510,7 +21510,7 @@
         <v>21</v>
       </c>
       <c r="G729" t="n">
-        <v>19.6267242431641</v>
+        <v>19.6267204284668</v>
       </c>
       <c r="H729" t="n">
         <v>286056</v>
@@ -21568,7 +21568,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>19.4865303039551</v>
+        <v>19.4865322113037</v>
       </c>
       <c r="H731" t="n">
         <v>1336171</v>
@@ -21597,7 +21597,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G732" t="n">
-        <v>19.4398002624512</v>
+        <v>19.4397983551025</v>
       </c>
       <c r="H732" t="n">
         <v>371674</v>
@@ -21626,7 +21626,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G733" t="n">
-        <v>19.701488494873</v>
+        <v>19.7014904022217</v>
       </c>
       <c r="H733" t="n">
         <v>369031</v>
@@ -21655,7 +21655,7 @@
         <v>21</v>
       </c>
       <c r="G734" t="n">
-        <v>19.6267242431641</v>
+        <v>19.6267204284668</v>
       </c>
       <c r="H734" t="n">
         <v>247340</v>
@@ -21684,7 +21684,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G735" t="n">
-        <v>19.4865303039551</v>
+        <v>19.4865322113037</v>
       </c>
       <c r="H735" t="n">
         <v>490522</v>
@@ -21742,7 +21742,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G737" t="n">
-        <v>18.7481937408447</v>
+        <v>18.7481918334961</v>
       </c>
       <c r="H737" t="n">
         <v>720359</v>
@@ -21771,7 +21771,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G738" t="n">
-        <v>18.6033306121826</v>
+        <v>18.603328704834</v>
       </c>
       <c r="H738" t="n">
         <v>681345</v>
@@ -21887,7 +21887,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G742" t="n">
-        <v>19.3650302886963</v>
+        <v>19.3650341033936</v>
       </c>
       <c r="H742" t="n">
         <v>414130</v>
@@ -21916,7 +21916,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>19.4865303039551</v>
+        <v>19.4865322113037</v>
       </c>
       <c r="H743" t="n">
         <v>259557</v>
@@ -21945,7 +21945,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>19.5332622528076</v>
+        <v>19.533260345459</v>
       </c>
       <c r="H744" t="n">
         <v>282711</v>
@@ -22003,7 +22003,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>19.346342086792</v>
+        <v>19.3463401794434</v>
       </c>
       <c r="H746" t="n">
         <v>177553</v>
@@ -22032,7 +22032,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G747" t="n">
-        <v>19.701488494873</v>
+        <v>19.7014904022217</v>
       </c>
       <c r="H747" t="n">
         <v>368527</v>
@@ -22061,7 +22061,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>19.5332622528076</v>
+        <v>19.533260345459</v>
       </c>
       <c r="H748" t="n">
         <v>211502</v>
@@ -22119,7 +22119,7 @@
         <v>20.5</v>
       </c>
       <c r="G750" t="n">
-        <v>19.1594181060791</v>
+        <v>19.1594200134277</v>
       </c>
       <c r="H750" t="n">
         <v>466560</v>
@@ -22177,7 +22177,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G752" t="n">
-        <v>18.6734218597412</v>
+        <v>18.6734237670898</v>
       </c>
       <c r="H752" t="n">
         <v>502005</v>
@@ -22264,7 +22264,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G755" t="n">
-        <v>16.710750579834</v>
+        <v>16.7107524871826</v>
       </c>
       <c r="H755" t="n">
         <v>1685708</v>
@@ -22293,7 +22293,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G756" t="n">
-        <v>16.8135566711426</v>
+        <v>16.8135585784912</v>
       </c>
       <c r="H756" t="n">
         <v>831352</v>
@@ -22322,7 +22322,7 @@
         <v>17.7450008392334</v>
       </c>
       <c r="G757" t="n">
-        <v>16.5845813751221</v>
+        <v>16.5845794677734</v>
       </c>
       <c r="H757" t="n">
         <v>666545</v>
@@ -22409,7 +22409,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G760" t="n">
-        <v>16.7200965881348</v>
+        <v>16.7200984954834</v>
       </c>
       <c r="H760" t="n">
         <v>542452</v>
@@ -22438,7 +22438,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>16.4957942962646</v>
+        <v>16.4957904815674</v>
       </c>
       <c r="H761" t="n">
         <v>1354957</v>
@@ -22467,7 +22467,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G762" t="n">
-        <v>16.7528076171875</v>
+        <v>16.7528095245361</v>
       </c>
       <c r="H762" t="n">
         <v>600695</v>
@@ -22612,7 +22612,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>16.4957942962646</v>
+        <v>16.4957904815674</v>
       </c>
       <c r="H767" t="n">
         <v>341314</v>
@@ -22641,7 +22641,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>16.5425205230713</v>
+        <v>16.5425224304199</v>
       </c>
       <c r="H768" t="n">
         <v>424881</v>
@@ -22670,7 +22670,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G769" t="n">
-        <v>16.8415946960449</v>
+        <v>16.8415966033936</v>
       </c>
       <c r="H769" t="n">
         <v>570466</v>
@@ -22699,7 +22699,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G770" t="n">
-        <v>16.6640205383301</v>
+        <v>16.6640224456787</v>
       </c>
       <c r="H770" t="n">
         <v>368576</v>
@@ -22728,7 +22728,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>16.5331783294678</v>
+        <v>16.5331764221191</v>
       </c>
       <c r="H771" t="n">
         <v>921657</v>
@@ -22757,7 +22757,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>16.4957942962646</v>
+        <v>16.4957904815674</v>
       </c>
       <c r="H772" t="n">
         <v>357653</v>
@@ -22815,7 +22815,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G774" t="n">
-        <v>16.6827144622803</v>
+        <v>16.6827125549316</v>
       </c>
       <c r="H774" t="n">
         <v>202822</v>
@@ -22844,7 +22844,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G775" t="n">
-        <v>16.5986003875732</v>
+        <v>16.5985984802246</v>
       </c>
       <c r="H775" t="n">
         <v>272556</v>
@@ -22873,7 +22873,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G776" t="n">
-        <v>16.8135566711426</v>
+        <v>16.8135585784912</v>
       </c>
       <c r="H776" t="n">
         <v>396353</v>
@@ -22902,7 +22902,7 @@
         <v>17.5750007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>16.4256954193115</v>
+        <v>16.4256973266602</v>
       </c>
       <c r="H777" t="n">
         <v>608356</v>
@@ -23018,7 +23018,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>16.4490642547607</v>
+        <v>16.4490623474121</v>
       </c>
       <c r="H781" t="n">
         <v>395429</v>
@@ -23076,7 +23076,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>16.2154102325439</v>
+        <v>16.2154121398926</v>
       </c>
       <c r="H783" t="n">
         <v>411875</v>
@@ -23163,7 +23163,7 @@
         <v>17.6350002288818</v>
       </c>
       <c r="G786" t="n">
-        <v>16.4817733764648</v>
+        <v>16.4817752838135</v>
       </c>
       <c r="H786" t="n">
         <v>617266</v>
@@ -23192,7 +23192,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G787" t="n">
-        <v>16.4957942962646</v>
+        <v>16.4957904815674</v>
       </c>
       <c r="H787" t="n">
         <v>375724</v>
@@ -23221,7 +23221,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G788" t="n">
-        <v>16.5238304138184</v>
+        <v>16.523832321167</v>
       </c>
       <c r="H788" t="n">
         <v>412006</v>
@@ -23308,7 +23308,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G791" t="n">
-        <v>16.2995262145996</v>
+        <v>16.299524307251</v>
       </c>
       <c r="H791" t="n">
         <v>193986</v>
@@ -23482,7 +23482,7 @@
         <v>18.8050003051758</v>
       </c>
       <c r="G797" t="n">
-        <v>17.5752620697021</v>
+        <v>17.5752601623535</v>
       </c>
       <c r="H797" t="n">
         <v>620074</v>
@@ -23511,7 +23511,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G798" t="n">
-        <v>17.5518989562988</v>
+        <v>17.5518970489502</v>
       </c>
       <c r="H798" t="n">
         <v>379392</v>
@@ -23598,7 +23598,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G801" t="n">
-        <v>17.1313247680664</v>
+        <v>17.1313228607178</v>
       </c>
       <c r="H801" t="n">
         <v>192081</v>
@@ -23685,7 +23685,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G804" t="n">
-        <v>17.4397430419922</v>
+        <v>17.4397449493408</v>
       </c>
       <c r="H804" t="n">
         <v>202890</v>
@@ -23714,7 +23714,7 @@
         <v>18.6749992370605</v>
       </c>
       <c r="G805" t="n">
-        <v>17.453763961792</v>
+        <v>17.4537620544434</v>
       </c>
       <c r="H805" t="n">
         <v>268791</v>
@@ -23743,7 +23743,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G806" t="n">
-        <v>17.7294731140137</v>
+        <v>17.729471206665</v>
       </c>
       <c r="H806" t="n">
         <v>991047</v>
@@ -23772,7 +23772,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G807" t="n">
-        <v>17.6547012329102</v>
+        <v>17.6547031402588</v>
       </c>
       <c r="H807" t="n">
         <v>467189</v>
@@ -23888,7 +23888,7 @@
         <v>18.0249996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>16.8462677001953</v>
+        <v>16.8462696075439</v>
       </c>
       <c r="H811" t="n">
         <v>347878</v>
@@ -23917,7 +23917,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G812" t="n">
-        <v>17.1687107086182</v>
+        <v>17.1687088012695</v>
       </c>
       <c r="H812" t="n">
         <v>816646</v>
@@ -23975,7 +23975,7 @@
         <v>19.25</v>
       </c>
       <c r="G814" t="n">
-        <v>17.9911613464355</v>
+        <v>17.9911594390869</v>
       </c>
       <c r="H814" t="n">
         <v>2684040</v>
@@ -24004,7 +24004,7 @@
         <v>19.1650009155273</v>
       </c>
       <c r="G815" t="n">
-        <v>17.9117221832275</v>
+        <v>17.9117202758789</v>
       </c>
       <c r="H815" t="n">
         <v>871578</v>
@@ -24033,7 +24033,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>18.0378913879395</v>
+        <v>18.0378932952881</v>
       </c>
       <c r="H816" t="n">
         <v>507095</v>
@@ -24091,7 +24091,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G818" t="n">
-        <v>17.7948970794678</v>
+        <v>17.7948951721191</v>
       </c>
       <c r="H818" t="n">
         <v>347549</v>
@@ -24294,7 +24294,7 @@
         <v>18.7250003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>17.5004920959473</v>
+        <v>17.5004959106445</v>
       </c>
       <c r="H825" t="n">
         <v>295760</v>
@@ -24323,7 +24323,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G826" t="n">
-        <v>17.869665145874</v>
+        <v>17.8696632385254</v>
       </c>
       <c r="H826" t="n">
         <v>493818</v>
@@ -24352,7 +24352,7 @@
         <v>19.5949993133545</v>
       </c>
       <c r="G827" t="n">
-        <v>18.3135986328125</v>
+        <v>18.3136005401611</v>
       </c>
       <c r="H827" t="n">
         <v>659382</v>
@@ -24439,7 +24439,7 @@
         <v>19.5949993133545</v>
       </c>
       <c r="G830" t="n">
-        <v>18.3135986328125</v>
+        <v>18.3136005401611</v>
       </c>
       <c r="H830" t="n">
         <v>585086</v>
@@ -24497,7 +24497,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G832" t="n">
-        <v>18.0191993713379</v>
+        <v>18.0192012786865</v>
       </c>
       <c r="H832" t="n">
         <v>294577</v>
@@ -24526,7 +24526,7 @@
         <v>19.2250003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>17.9677982330322</v>
+        <v>17.9677963256836</v>
       </c>
       <c r="H833" t="n">
         <v>203838</v>
@@ -24555,7 +24555,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G834" t="n">
-        <v>17.9070472717285</v>
+        <v>17.9070491790771</v>
       </c>
       <c r="H834" t="n">
         <v>384646</v>
@@ -24642,7 +24642,7 @@
         <v>19.625</v>
       </c>
       <c r="G837" t="n">
-        <v>18.3416366577148</v>
+        <v>18.3416385650635</v>
       </c>
       <c r="H837" t="n">
         <v>166982</v>
@@ -24700,7 +24700,7 @@
         <v>19.8549995422363</v>
       </c>
       <c r="G839" t="n">
-        <v>18.5565967559814</v>
+        <v>18.5565986633301</v>
       </c>
       <c r="H839" t="n">
         <v>1014974</v>
@@ -24729,7 +24729,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G840" t="n">
-        <v>18.439769744873</v>
+        <v>18.4397716522217</v>
       </c>
       <c r="H840" t="n">
         <v>677306</v>
@@ -24787,7 +24787,7 @@
         <v>19.8449993133545</v>
       </c>
       <c r="G842" t="n">
-        <v>18.5472526550293</v>
+        <v>18.5472507476807</v>
       </c>
       <c r="H842" t="n">
         <v>1177361</v>
@@ -24932,7 +24932,7 @@
         <v>19.6550006866455</v>
       </c>
       <c r="G847" t="n">
-        <v>18.3696765899658</v>
+        <v>18.3696784973145</v>
       </c>
       <c r="H847" t="n">
         <v>707866</v>
@@ -24961,7 +24961,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G848" t="n">
-        <v>18.5893077850342</v>
+        <v>18.5893096923828</v>
       </c>
       <c r="H848" t="n">
         <v>547458</v>
@@ -25048,7 +25048,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>18.0612602233887</v>
+        <v>18.06125831604</v>
       </c>
       <c r="H851" t="n">
         <v>377774</v>
@@ -25106,7 +25106,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G853" t="n">
-        <v>18.0939712524414</v>
+        <v>18.0939693450928</v>
       </c>
       <c r="H853" t="n">
         <v>637823</v>
@@ -25164,7 +25164,7 @@
         <v>19.3449993133545</v>
       </c>
       <c r="G855" t="n">
-        <v>18.0799503326416</v>
+        <v>18.079948425293</v>
       </c>
       <c r="H855" t="n">
         <v>510434</v>
@@ -25251,7 +25251,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>19.9071006774902</v>
+        <v>19.9071044921875</v>
       </c>
       <c r="H858" t="n">
         <v>565898</v>
@@ -25309,7 +25309,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G860" t="n">
-        <v>19.9735889434814</v>
+        <v>19.9735870361328</v>
       </c>
       <c r="H860" t="n">
         <v>461424</v>
@@ -25425,7 +25425,7 @@
         <v>20.1299991607666</v>
       </c>
       <c r="G864" t="n">
-        <v>19.1187973022461</v>
+        <v>19.1187953948975</v>
       </c>
       <c r="H864" t="n">
         <v>286413</v>
@@ -25454,7 +25454,7 @@
         <v>20.25</v>
       </c>
       <c r="G865" t="n">
-        <v>19.2327709197998</v>
+        <v>19.2327690124512</v>
       </c>
       <c r="H865" t="n">
         <v>775254</v>
@@ -25512,7 +25512,7 @@
         <v>19.4150009155273</v>
       </c>
       <c r="G867" t="n">
-        <v>18.4397144317627</v>
+        <v>18.4397163391113</v>
       </c>
       <c r="H867" t="n">
         <v>1040614</v>
@@ -25541,7 +25541,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G868" t="n">
-        <v>17.7131423950195</v>
+        <v>17.7131443023682</v>
       </c>
       <c r="H868" t="n">
         <v>1061282</v>
@@ -25628,7 +25628,7 @@
         <v>19.3449993133545</v>
       </c>
       <c r="G871" t="n">
-        <v>18.3732318878174</v>
+        <v>18.3732299804688</v>
       </c>
       <c r="H871" t="n">
         <v>782917</v>
@@ -25657,7 +25657,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G872" t="n">
-        <v>18.6534099578857</v>
+        <v>18.6534118652344</v>
       </c>
       <c r="H872" t="n">
         <v>633892</v>
@@ -25686,7 +25686,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G873" t="n">
-        <v>19.1757831573486</v>
+        <v>19.1757850646973</v>
       </c>
       <c r="H873" t="n">
         <v>957501</v>
@@ -25744,7 +25744,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G875" t="n">
-        <v>19.2802581787109</v>
+        <v>19.2802562713623</v>
       </c>
       <c r="H875" t="n">
         <v>413859</v>
@@ -26034,7 +26034,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G885" t="n">
-        <v>19.7171478271484</v>
+        <v>19.7171497344971</v>
       </c>
       <c r="H885" t="n">
         <v>182928</v>
@@ -26092,7 +26092,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G887" t="n">
-        <v>19.7456455230713</v>
+        <v>19.7456436157227</v>
       </c>
       <c r="H887" t="n">
         <v>232823</v>
@@ -26150,7 +26150,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>20.1350479125977</v>
+        <v>20.135046005249</v>
       </c>
       <c r="H889" t="n">
         <v>497289</v>
@@ -26179,7 +26179,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G890" t="n">
-        <v>20.1920318603516</v>
+        <v>20.1920337677002</v>
       </c>
       <c r="H890" t="n">
         <v>370813</v>
@@ -26266,7 +26266,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G893" t="n">
-        <v>20.2870121002197</v>
+        <v>20.2870101928711</v>
       </c>
       <c r="H893" t="n">
         <v>452737</v>
@@ -26324,7 +26324,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G895" t="n">
-        <v>19.8406181335449</v>
+        <v>19.8406200408936</v>
       </c>
       <c r="H895" t="n">
         <v>452815</v>
@@ -26411,7 +26411,7 @@
         <v>21.0100002288818</v>
       </c>
       <c r="G898" t="n">
-        <v>19.95458984375</v>
+        <v>19.9545917510986</v>
       </c>
       <c r="H898" t="n">
         <v>301844</v>
@@ -26469,7 +26469,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G900" t="n">
-        <v>19.9071006774902</v>
+        <v>19.9071025848389</v>
       </c>
       <c r="H900" t="n">
         <v>398965</v>
@@ -26556,7 +26556,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G903" t="n">
-        <v>19.8691120147705</v>
+        <v>19.8691139221191</v>
       </c>
       <c r="H903" t="n">
         <v>427160</v>
@@ -26585,7 +26585,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G904" t="n">
-        <v>19.9735889434814</v>
+        <v>19.9735870361328</v>
       </c>
       <c r="H904" t="n">
         <v>428652</v>
@@ -26614,7 +26614,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G905" t="n">
-        <v>19.8691120147705</v>
+        <v>19.8691139221191</v>
       </c>
       <c r="H905" t="n">
         <v>312833</v>
@@ -26672,7 +26672,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G907" t="n">
-        <v>19.9640884399414</v>
+        <v>19.96409034729</v>
       </c>
       <c r="H907" t="n">
         <v>595451</v>
@@ -26701,7 +26701,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G908" t="n">
-        <v>20.0020809173584</v>
+        <v>20.0020790100098</v>
       </c>
       <c r="H908" t="n">
         <v>361424</v>
@@ -26817,7 +26817,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G912" t="n">
-        <v>17.9315891265869</v>
+        <v>17.9315872192383</v>
       </c>
       <c r="H912" t="n">
         <v>1210342</v>
@@ -26846,7 +26846,7 @@
         <v>18.5049991607666</v>
       </c>
       <c r="G913" t="n">
-        <v>17.5754241943359</v>
+        <v>17.5754261016846</v>
       </c>
       <c r="H913" t="n">
         <v>1014008</v>
@@ -26904,7 +26904,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G915" t="n">
-        <v>17.276252746582</v>
+        <v>17.2762508392334</v>
       </c>
       <c r="H915" t="n">
         <v>705843</v>
@@ -27049,7 +27049,7 @@
         <v>17.9150009155273</v>
       </c>
       <c r="G920" t="n">
-        <v>17.015064239502</v>
+        <v>17.0150661468506</v>
       </c>
       <c r="H920" t="n">
         <v>386059</v>
@@ -27078,7 +27078,7 @@
         <v>17.4750003814697</v>
       </c>
       <c r="G921" t="n">
-        <v>16.5971698760986</v>
+        <v>16.5971660614014</v>
       </c>
       <c r="H921" t="n">
         <v>361687</v>
@@ -27107,7 +27107,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G922" t="n">
-        <v>16.2837448120117</v>
+        <v>16.2837467193604</v>
       </c>
       <c r="H922" t="n">
         <v>717691</v>
@@ -27339,7 +27339,7 @@
         <v>17.6350002288818</v>
       </c>
       <c r="G930" t="n">
-        <v>16.7491302490234</v>
+        <v>16.7491321563721</v>
       </c>
       <c r="H930" t="n">
         <v>638773</v>
@@ -27397,7 +27397,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G932" t="n">
-        <v>16.497444152832</v>
+        <v>16.4974422454834</v>
       </c>
       <c r="H932" t="n">
         <v>1271538</v>
@@ -27455,7 +27455,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G934" t="n">
-        <v>16.630407333374</v>
+        <v>16.6304092407227</v>
       </c>
       <c r="H934" t="n">
         <v>241190</v>
@@ -27658,7 +27658,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>17.2857475280762</v>
+        <v>17.2857494354248</v>
       </c>
       <c r="H941" t="n">
         <v>1106208</v>
@@ -27803,7 +27803,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G946" t="n">
-        <v>16.696891784668</v>
+        <v>16.6968936920166</v>
       </c>
       <c r="H946" t="n">
         <v>612651</v>
@@ -27832,7 +27832,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G947" t="n">
-        <v>16.7538776397705</v>
+        <v>16.7538795471191</v>
       </c>
       <c r="H947" t="n">
         <v>467332</v>
@@ -27948,7 +27948,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G951" t="n">
-        <v>16.3454780578613</v>
+        <v>16.34547996521</v>
       </c>
       <c r="H951" t="n">
         <v>647943</v>
@@ -28006,7 +28006,7 @@
         <v>16.9549999237061</v>
       </c>
       <c r="G953" t="n">
-        <v>16.1032905578613</v>
+        <v>16.1032886505127</v>
       </c>
       <c r="H953" t="n">
         <v>508993</v>
@@ -28035,7 +28035,7 @@
         <v>16.8649997711182</v>
       </c>
       <c r="G954" t="n">
-        <v>16.0178089141846</v>
+        <v>16.0178108215332</v>
       </c>
       <c r="H954" t="n">
         <v>543115</v>
@@ -28064,7 +28064,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>15.4811916351318</v>
+        <v>15.4811906814575</v>
       </c>
       <c r="H955" t="n">
         <v>881171</v>
@@ -28122,7 +28122,7 @@
         <v>16.3850002288818</v>
       </c>
       <c r="G957" t="n">
-        <v>15.5619211196899</v>
+        <v>15.5619230270386</v>
       </c>
       <c r="H957" t="n">
         <v>387332</v>
@@ -28151,7 +28151,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>15.4811916351318</v>
+        <v>15.4811906814575</v>
       </c>
       <c r="H958" t="n">
         <v>462839</v>
@@ -28267,7 +28267,7 @@
         <v>16.4150009155273</v>
       </c>
       <c r="G962" t="n">
-        <v>15.5904169082642</v>
+        <v>15.5904159545898</v>
       </c>
       <c r="H962" t="n">
         <v>1017946</v>
@@ -28354,7 +28354,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G965" t="n">
-        <v>15.4052104949951</v>
+        <v>15.4052095413208</v>
       </c>
       <c r="H965" t="n">
         <v>687418</v>
@@ -28528,7 +28528,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G971" t="n">
-        <v>15.0348024368286</v>
+        <v>15.0348014831543</v>
       </c>
       <c r="H971" t="n">
         <v>371138</v>
@@ -28557,7 +28557,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G972" t="n">
-        <v>15.319730758667</v>
+        <v>15.3197317123413</v>
       </c>
       <c r="H972" t="n">
         <v>1080701</v>
@@ -28586,7 +28586,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G973" t="n">
-        <v>15.9608240127563</v>
+        <v>15.960823059082</v>
       </c>
       <c r="H973" t="n">
         <v>1840392</v>
@@ -28615,7 +28615,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>15.7661228179932</v>
+        <v>15.7661218643188</v>
       </c>
       <c r="H974" t="n">
         <v>975396</v>
@@ -28644,7 +28644,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G975" t="n">
-        <v>15.8800926208496</v>
+        <v>15.8800916671753</v>
       </c>
       <c r="H975" t="n">
         <v>437079</v>
@@ -28673,7 +28673,7 @@
         <v>16.75</v>
       </c>
       <c r="G976" t="n">
-        <v>15.9085865020752</v>
+        <v>15.9085874557495</v>
       </c>
       <c r="H976" t="n">
         <v>419109</v>
@@ -28731,7 +28731,7 @@
         <v>16.9950008392334</v>
       </c>
       <c r="G978" t="n">
-        <v>16.1412811279297</v>
+        <v>16.1412792205811</v>
       </c>
       <c r="H978" t="n">
         <v>604860</v>
@@ -28789,7 +28789,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G980" t="n">
-        <v>16.4024639129639</v>
+        <v>16.4024658203125</v>
       </c>
       <c r="H980" t="n">
         <v>649759</v>
@@ -28818,7 +28818,7 @@
         <v>17.4549999237061</v>
       </c>
       <c r="G981" t="n">
-        <v>16.5781726837158</v>
+        <v>16.5781707763672</v>
       </c>
       <c r="H981" t="n">
         <v>834030</v>
@@ -28934,7 +28934,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G985" t="n">
-        <v>17.276252746582</v>
+        <v>17.2762508392334</v>
       </c>
       <c r="H985" t="n">
         <v>2378807</v>
@@ -28992,7 +28992,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G987" t="n">
-        <v>16.9723281860352</v>
+        <v>16.9723262786865</v>
       </c>
       <c r="H987" t="n">
         <v>808302</v>
@@ -29021,7 +29021,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G988" t="n">
-        <v>16.4404544830322</v>
+        <v>16.4404563903809</v>
       </c>
       <c r="H988" t="n">
         <v>893679</v>
@@ -29137,7 +29137,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G992" t="n">
-        <v>16.4024639129639</v>
+        <v>16.4024658203125</v>
       </c>
       <c r="H992" t="n">
         <v>280506</v>
@@ -29166,7 +29166,7 @@
         <v>17.5</v>
       </c>
       <c r="G993" t="n">
-        <v>16.6209125518799</v>
+        <v>16.6209106445312</v>
       </c>
       <c r="H993" t="n">
         <v>356739</v>
@@ -29282,7 +29282,7 @@
         <v>18.0949993133545</v>
       </c>
       <c r="G997" t="n">
-        <v>17.1860237121582</v>
+        <v>17.1860218048096</v>
       </c>
       <c r="H997" t="n">
         <v>470813</v>
@@ -29340,7 +29340,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G999" t="n">
-        <v>16.696891784668</v>
+        <v>16.6968936920166</v>
       </c>
       <c r="H999" t="n">
         <v>376183</v>
@@ -29398,7 +29398,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1001" t="n">
-        <v>17.9695816040039</v>
+        <v>17.9695796966553</v>
       </c>
       <c r="H1001" t="n">
         <v>2939433</v>
@@ -29427,7 +29427,7 @@
         <v>19.0699996948242</v>
       </c>
       <c r="G1002" t="n">
-        <v>18.1120433807373</v>
+        <v>18.1120452880859</v>
       </c>
       <c r="H1002" t="n">
         <v>1385148</v>
@@ -29630,7 +29630,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1009" t="n">
-        <v>17.5421848297119</v>
+        <v>17.5421829223633</v>
       </c>
       <c r="H1009" t="n">
         <v>335089</v>
@@ -29659,7 +29659,7 @@
         <v>18.4050006866455</v>
       </c>
       <c r="G1010" t="n">
-        <v>17.4804515838623</v>
+        <v>17.4804496765137</v>
       </c>
       <c r="H1010" t="n">
         <v>357823</v>
@@ -29833,7 +29833,7 @@
         <v>18.9549999237061</v>
       </c>
       <c r="G1016" t="n">
-        <v>18.0028209686279</v>
+        <v>18.0028228759766</v>
       </c>
       <c r="H1016" t="n">
         <v>252759</v>
@@ -29920,7 +29920,7 @@
         <v>18.6149997711182</v>
       </c>
       <c r="G1019" t="n">
-        <v>17.6799011230469</v>
+        <v>17.6799030303955</v>
       </c>
       <c r="H1019" t="n">
         <v>233888</v>
@@ -29949,7 +29949,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1020" t="n">
-        <v>17.9885768890381</v>
+        <v>17.9885749816895</v>
       </c>
       <c r="H1020" t="n">
         <v>339183</v>
@@ -30007,7 +30007,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1022" t="n">
-        <v>18.0930500030518</v>
+        <v>18.0930480957031</v>
       </c>
       <c r="H1022" t="n">
         <v>323583</v>
@@ -30036,7 +30036,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.9030952453613</v>
+        <v>17.90309715271</v>
       </c>
       <c r="H1023" t="n">
         <v>285927</v>
@@ -30297,7 +30297,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1032" t="n">
-        <v>16.5924167633057</v>
+        <v>16.5924186706543</v>
       </c>
       <c r="H1032" t="n">
         <v>390989</v>
@@ -30326,7 +30326,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>15.8610982894897</v>
+        <v>15.8611001968384</v>
       </c>
       <c r="H1033" t="n">
         <v>1029610</v>
@@ -30355,7 +30355,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G1034" t="n">
-        <v>16.2694988250732</v>
+        <v>16.2694969177246</v>
       </c>
       <c r="H1034" t="n">
         <v>539194</v>
@@ -30384,7 +30384,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1035" t="n">
-        <v>16.2979907989502</v>
+        <v>16.2979927062988</v>
       </c>
       <c r="H1035" t="n">
         <v>782661</v>
@@ -30442,7 +30442,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1037" t="n">
-        <v>15.8468523025513</v>
+        <v>15.8468503952026</v>
       </c>
       <c r="H1037" t="n">
         <v>727617</v>
@@ -30471,7 +30471,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1038" t="n">
-        <v>15.8800926208496</v>
+        <v>15.8800916671753</v>
       </c>
       <c r="H1038" t="n">
         <v>489487</v>
@@ -30500,7 +30500,7 @@
         <v>17.1849994659424</v>
       </c>
       <c r="G1039" t="n">
-        <v>16.3217334747314</v>
+        <v>16.3217353820801</v>
       </c>
       <c r="H1039" t="n">
         <v>601850</v>
@@ -30587,7 +30587,7 @@
         <v>16.6149997711182</v>
       </c>
       <c r="G1042" t="n">
-        <v>15.780366897583</v>
+        <v>15.7803688049316</v>
       </c>
       <c r="H1042" t="n">
         <v>513424</v>
@@ -30616,7 +30616,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>15.7186336517334</v>
+        <v>15.7186326980591</v>
       </c>
       <c r="H1043" t="n">
         <v>350977</v>
@@ -30645,7 +30645,7 @@
         <v>16.1550006866455</v>
       </c>
       <c r="G1044" t="n">
-        <v>15.3434762954712</v>
+        <v>15.3434772491455</v>
       </c>
       <c r="H1044" t="n">
         <v>964969</v>
@@ -30703,7 +30703,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.7471265792847</v>
+        <v>15.747127532959</v>
       </c>
       <c r="H1046" t="n">
         <v>537095</v>
@@ -30732,7 +30732,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1047" t="n">
-        <v>15.6046619415283</v>
+        <v>15.604660987854</v>
       </c>
       <c r="H1047" t="n">
         <v>418169</v>
@@ -30761,7 +30761,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1048" t="n">
-        <v>15.8610982894897</v>
+        <v>15.8611001968384</v>
       </c>
       <c r="H1048" t="n">
         <v>559116</v>
@@ -30790,7 +30790,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1049" t="n">
-        <v>15.7043876647949</v>
+        <v>15.7043857574463</v>
       </c>
       <c r="H1049" t="n">
         <v>541345</v>
@@ -30819,7 +30819,7 @@
         <v>16.7250003814697</v>
       </c>
       <c r="G1050" t="n">
-        <v>15.8848447799683</v>
+        <v>15.8848428726196</v>
       </c>
       <c r="H1050" t="n">
         <v>924015</v>
@@ -30848,7 +30848,7 @@
         <v>16.3649997711182</v>
       </c>
       <c r="G1051" t="n">
-        <v>15.5429258346558</v>
+        <v>15.5429267883301</v>
       </c>
       <c r="H1051" t="n">
         <v>743062</v>
@@ -30906,7 +30906,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1053" t="n">
-        <v>13.8096027374268</v>
+        <v>13.8096036911011</v>
       </c>
       <c r="H1053" t="n">
         <v>1675625</v>
@@ -30935,7 +30935,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1054" t="n">
-        <v>13.8665885925293</v>
+        <v>13.8665895462036</v>
       </c>
       <c r="H1054" t="n">
         <v>928355</v>
@@ -30993,7 +30993,7 @@
         <v>14.3249998092651</v>
       </c>
       <c r="G1056" t="n">
-        <v>13.6054029464722</v>
+        <v>13.6054039001465</v>
       </c>
       <c r="H1056" t="n">
         <v>1069741</v>
@@ -31051,7 +31051,7 @@
         <v>13.7650003433228</v>
       </c>
       <c r="G1058" t="n">
-        <v>13.0735349655151</v>
+        <v>13.0735340118408</v>
       </c>
       <c r="H1058" t="n">
         <v>1414108</v>
@@ -31080,7 +31080,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G1059" t="n">
-        <v>13.0497903823853</v>
+        <v>13.0497894287109</v>
       </c>
       <c r="H1059" t="n">
         <v>657128</v>
@@ -31109,7 +31109,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1060" t="n">
-        <v>12.9738082885742</v>
+        <v>12.9738092422485</v>
       </c>
       <c r="H1060" t="n">
         <v>551132</v>
@@ -31196,7 +31196,7 @@
         <v>11.875</v>
       </c>
       <c r="G1063" t="n">
-        <v>11.2784767150879</v>
+        <v>11.2784757614136</v>
       </c>
       <c r="H1063" t="n">
         <v>1481021</v>
@@ -31225,7 +31225,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1064" t="n">
-        <v>10.656379699707</v>
+        <v>10.6563787460327</v>
       </c>
       <c r="H1064" t="n">
         <v>1089886</v>
@@ -31486,7 +31486,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1073" t="n">
-        <v>12.1665086746216</v>
+        <v>12.1665077209473</v>
       </c>
       <c r="H1073" t="n">
         <v>740515</v>
@@ -31573,7 +31573,7 @@
         <v>13.6549997329712</v>
       </c>
       <c r="G1076" t="n">
-        <v>12.9690589904785</v>
+        <v>12.9690599441528</v>
       </c>
       <c r="H1076" t="n">
         <v>932291</v>
@@ -31689,7 +31689,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1080" t="n">
-        <v>11.2072429656982</v>
+        <v>11.2072439193726</v>
       </c>
       <c r="H1080" t="n">
         <v>455495</v>
@@ -31718,7 +31718,7 @@
         <v>11.75</v>
       </c>
       <c r="G1081" t="n">
-        <v>11.1597557067871</v>
+        <v>11.1597547531128</v>
       </c>
       <c r="H1081" t="n">
         <v>279618</v>
@@ -31776,7 +31776,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1083" t="n">
-        <v>11.5681552886963</v>
+        <v>11.568154335022</v>
       </c>
       <c r="H1083" t="n">
         <v>348740</v>
@@ -31979,7 +31979,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>11.5396614074707</v>
+        <v>11.5396604537964</v>
       </c>
       <c r="H1090" t="n">
         <v>351112</v>
@@ -32066,7 +32066,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>10.399941444397</v>
+        <v>10.3999423980713</v>
       </c>
       <c r="H1093" t="n">
         <v>1163920</v>
@@ -32182,7 +32182,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1097" t="n">
-        <v>10.7323598861694</v>
+        <v>10.7323608398438</v>
       </c>
       <c r="H1097" t="n">
         <v>436691</v>
@@ -32211,7 +32211,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G1098" t="n">
-        <v>10.9128160476685</v>
+        <v>10.9128150939941</v>
       </c>
       <c r="H1098" t="n">
         <v>336811</v>
@@ -32269,7 +32269,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1100" t="n">
-        <v>10.3049650192261</v>
+        <v>10.3049659729004</v>
       </c>
       <c r="H1100" t="n">
         <v>318771</v>
@@ -32356,7 +32356,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G1103" t="n">
-        <v>10.3429555892944</v>
+        <v>10.3429565429688</v>
       </c>
       <c r="H1103" t="n">
         <v>387905</v>
@@ -32385,7 +32385,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1104" t="n">
-        <v>10.4094400405884</v>
+        <v>10.4094390869141</v>
       </c>
       <c r="H1104" t="n">
         <v>459706</v>
@@ -32414,7 +32414,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1105" t="n">
-        <v>10.2574777603149</v>
+        <v>10.2574768066406</v>
       </c>
       <c r="H1105" t="n">
         <v>431190</v>
@@ -32443,7 +32443,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1106" t="n">
-        <v>10.2574777603149</v>
+        <v>10.2574768066406</v>
       </c>
       <c r="H1106" t="n">
         <v>542953</v>
@@ -32472,7 +32472,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1107" t="n">
-        <v>10.2574777603149</v>
+        <v>10.2574768066406</v>
       </c>
       <c r="H1107" t="n">
         <v>2225485</v>
@@ -32559,7 +32559,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1110" t="n">
-        <v>10.4094400405884</v>
+        <v>10.4094390869141</v>
       </c>
       <c r="H1110" t="n">
         <v>778843</v>
@@ -32588,7 +32588,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1111" t="n">
-        <v>10.399941444397</v>
+        <v>10.3999423980713</v>
       </c>
       <c r="H1111" t="n">
         <v>2429677</v>
@@ -32646,7 +32646,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1113" t="n">
-        <v>9.89656543731689</v>
+        <v>9.89656639099121</v>
       </c>
       <c r="H1113" t="n">
         <v>673326</v>
@@ -32675,7 +32675,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G1114" t="n">
-        <v>9.64962577819824</v>
+        <v>9.64962673187256</v>
       </c>
       <c r="H1114" t="n">
         <v>646937</v>
@@ -32791,7 +32791,7 @@
         <v>13</v>
       </c>
       <c r="G1118" t="n">
-        <v>12.3469619750977</v>
+        <v>12.346962928772</v>
       </c>
       <c r="H1118" t="n">
         <v>3283790</v>
@@ -33110,7 +33110,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1129" t="n">
-        <v>11.7771034240723</v>
+        <v>11.7771024703979</v>
       </c>
       <c r="H1129" t="n">
         <v>738839</v>
@@ -33139,7 +33139,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1130" t="n">
-        <v>12.062032699585</v>
+        <v>12.0620336532593</v>
       </c>
       <c r="H1130" t="n">
         <v>882931</v>
@@ -33168,7 +33168,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1131" t="n">
-        <v>12.1190185546875</v>
+        <v>12.1190195083618</v>
       </c>
       <c r="H1131" t="n">
         <v>1075221</v>
@@ -33197,7 +33197,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1132" t="n">
-        <v>12.2899761199951</v>
+        <v>12.2899770736694</v>
       </c>
       <c r="H1132" t="n">
         <v>994782</v>
@@ -33284,7 +33284,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1135" t="n">
-        <v>12.5749063491821</v>
+        <v>12.5749073028564</v>
       </c>
       <c r="H1135" t="n">
         <v>672115</v>
@@ -33313,7 +33313,7 @@
         <v>13.25</v>
       </c>
       <c r="G1136" t="n">
-        <v>12.5844039916992</v>
+        <v>12.5844049453735</v>
       </c>
       <c r="H1136" t="n">
         <v>819274</v>
@@ -33371,7 +33371,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1138" t="n">
-        <v>11.8055963516235</v>
+        <v>11.8055953979492</v>
       </c>
       <c r="H1138" t="n">
         <v>819399</v>
@@ -33400,7 +33400,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1139" t="n">
-        <v>11.5111694335938</v>
+        <v>11.5111684799194</v>
       </c>
       <c r="H1139" t="n">
         <v>692062</v>
@@ -33429,7 +33429,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1140" t="n">
-        <v>11.7296142578125</v>
+        <v>11.7296152114868</v>
       </c>
       <c r="H1140" t="n">
         <v>688432</v>
@@ -33516,7 +33516,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1143" t="n">
-        <v>11.7581081390381</v>
+        <v>11.7581071853638</v>
       </c>
       <c r="H1143" t="n">
         <v>523414</v>
@@ -33574,7 +33574,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1145" t="n">
-        <v>11.5871496200562</v>
+        <v>11.5871486663818</v>
       </c>
       <c r="H1145" t="n">
         <v>444536</v>
@@ -33661,7 +33661,7 @@
         <v>11.75</v>
       </c>
       <c r="G1148" t="n">
-        <v>11.1597557067871</v>
+        <v>11.1597547531128</v>
       </c>
       <c r="H1148" t="n">
         <v>392868</v>
@@ -33719,7 +33719,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G1150" t="n">
-        <v>11.1787509918213</v>
+        <v>11.1787519454956</v>
       </c>
       <c r="H1150" t="n">
         <v>464530</v>
@@ -33806,7 +33806,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1153" t="n">
-        <v>11.2262372970581</v>
+        <v>11.2262382507324</v>
       </c>
       <c r="H1153" t="n">
         <v>1341026</v>
@@ -33835,7 +33835,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1154" t="n">
-        <v>11.2262372970581</v>
+        <v>11.2262382507324</v>
       </c>
       <c r="H1154" t="n">
         <v>532994</v>
@@ -33864,7 +33864,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.2452344894409</v>
+        <v>11.2452335357666</v>
       </c>
       <c r="H1155" t="n">
         <v>321721</v>
@@ -33980,7 +33980,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G1159" t="n">
-        <v>11.0267877578735</v>
+        <v>11.0267868041992</v>
       </c>
       <c r="H1159" t="n">
         <v>350758</v>
@@ -34038,7 +34038,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1161" t="n">
-        <v>10.8368339538574</v>
+        <v>10.8368349075317</v>
       </c>
       <c r="H1161" t="n">
         <v>402699</v>
@@ -34183,7 +34183,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G1166" t="n">
-        <v>10.5708990097046</v>
+        <v>10.5708999633789</v>
       </c>
       <c r="H1166" t="n">
         <v>361104</v>
@@ -34212,7 +34212,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1167" t="n">
-        <v>10.8368339538574</v>
+        <v>10.8368349075317</v>
       </c>
       <c r="H1167" t="n">
         <v>457270</v>
@@ -34328,7 +34328,7 @@
         <v>11.75</v>
       </c>
       <c r="G1171" t="n">
-        <v>11.1597557067871</v>
+        <v>11.1597547531128</v>
       </c>
       <c r="H1171" t="n">
         <v>1028230</v>
@@ -34502,7 +34502,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1177" t="n">
-        <v>10.9603033065796</v>
+        <v>10.9603052139282</v>
       </c>
       <c r="H1177" t="n">
         <v>198677</v>
@@ -34531,7 +34531,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G1178" t="n">
-        <v>10.760853767395</v>
+        <v>10.7608528137207</v>
       </c>
       <c r="H1178" t="n">
         <v>232544</v>
@@ -34560,7 +34560,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1179" t="n">
-        <v>10.656379699707</v>
+        <v>10.6563787460327</v>
       </c>
       <c r="H1179" t="n">
         <v>345130</v>
@@ -34647,7 +34647,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G1182" t="n">
-        <v>11.6156415939331</v>
+        <v>11.6156425476074</v>
       </c>
       <c r="H1182" t="n">
         <v>1276301</v>
@@ -34734,7 +34734,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1185" t="n">
-        <v>11.4636793136597</v>
+        <v>11.463680267334</v>
       </c>
       <c r="H1185" t="n">
         <v>306240</v>
@@ -34763,7 +34763,7 @@
         <v>12</v>
       </c>
       <c r="G1186" t="n">
-        <v>11.3971977233887</v>
+        <v>11.3971967697144</v>
       </c>
       <c r="H1186" t="n">
         <v>396498</v>
@@ -35053,7 +35053,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>11.5871496200562</v>
+        <v>11.5871486663818</v>
       </c>
       <c r="H1196" t="n">
         <v>508547</v>
@@ -35140,7 +35140,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1199" t="n">
-        <v>12.0810279846191</v>
+        <v>12.0810289382935</v>
       </c>
       <c r="H1199" t="n">
         <v>1709385</v>
@@ -35198,7 +35198,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1201" t="n">
-        <v>11.5681552886963</v>
+        <v>11.568154335022</v>
       </c>
       <c r="H1201" t="n">
         <v>458047</v>
@@ -35256,7 +35256,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1203" t="n">
-        <v>11.4636793136597</v>
+        <v>11.463680267334</v>
       </c>
       <c r="H1203" t="n">
         <v>441998</v>
@@ -35285,7 +35285,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1204" t="n">
-        <v>11.6061449050903</v>
+        <v>11.6061458587646</v>
       </c>
       <c r="H1204" t="n">
         <v>1410532</v>
@@ -35314,7 +35314,7 @@
         <v>12.75</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.1095209121704</v>
+        <v>12.1095218658447</v>
       </c>
       <c r="H1205" t="n">
         <v>796074</v>
@@ -35372,7 +35372,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G1207" t="n">
-        <v>11.9385623931885</v>
+        <v>11.9385633468628</v>
       </c>
       <c r="H1207" t="n">
         <v>356217</v>
@@ -35459,7 +35459,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.1285181045532</v>
+        <v>12.1285171508789</v>
       </c>
       <c r="H1210" t="n">
         <v>425924</v>
@@ -35604,7 +35604,7 @@
         <v>13.25</v>
       </c>
       <c r="G1215" t="n">
-        <v>12.5844039916992</v>
+        <v>12.5844049453735</v>
       </c>
       <c r="H1215" t="n">
         <v>280270</v>
@@ -35662,7 +35662,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G1217" t="n">
-        <v>12.5464143753052</v>
+        <v>12.5464134216309</v>
       </c>
       <c r="H1217" t="n">
         <v>251308</v>
@@ -35691,7 +35691,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>12.2044982910156</v>
+        <v>12.2044973373413</v>
       </c>
       <c r="H1218" t="n">
         <v>348352</v>
@@ -35894,7 +35894,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G1225" t="n">
-        <v>11.67262840271</v>
+        <v>11.6726293563843</v>
       </c>
       <c r="H1225" t="n">
         <v>244312</v>
@@ -36010,7 +36010,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G1229" t="n">
-        <v>10.5139131546021</v>
+        <v>10.5139141082764</v>
       </c>
       <c r="H1229" t="n">
         <v>356718</v>
@@ -36039,7 +36039,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G1230" t="n">
-        <v>10.7988443374634</v>
+        <v>10.7988433837891</v>
       </c>
       <c r="H1230" t="n">
         <v>307755</v>
@@ -36358,7 +36358,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1241" t="n">
-        <v>13.9235744476318</v>
+        <v>13.9235754013062</v>
       </c>
       <c r="H1241" t="n">
         <v>633097</v>
@@ -36503,7 +36503,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1246" t="n">
-        <v>14.6264019012451</v>
+        <v>14.6264009475708</v>
       </c>
       <c r="H1246" t="n">
         <v>823200</v>
@@ -36532,7 +36532,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1247" t="n">
-        <v>14.6264019012451</v>
+        <v>14.6264009475708</v>
       </c>
       <c r="H1247" t="n">
         <v>353223</v>
@@ -36561,7 +36561,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G1248" t="n">
-        <v>14.3129787445068</v>
+        <v>14.3129796981812</v>
       </c>
       <c r="H1248" t="n">
         <v>692581</v>
@@ -36590,7 +36590,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1249" t="n">
-        <v>14.1515197753906</v>
+        <v>14.1515188217163</v>
       </c>
       <c r="H1249" t="n">
         <v>195884</v>
@@ -36619,7 +36619,7 @@
         <v>15</v>
       </c>
       <c r="G1250" t="n">
-        <v>14.2464952468872</v>
+        <v>14.2464962005615</v>
       </c>
       <c r="H1250" t="n">
         <v>463570</v>
@@ -36648,7 +36648,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1251" t="n">
-        <v>14.4269504547119</v>
+        <v>14.4269514083862</v>
       </c>
       <c r="H1251" t="n">
         <v>257275</v>
@@ -36677,7 +36677,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G1252" t="n">
-        <v>14.4649410247803</v>
+        <v>14.4649419784546</v>
       </c>
       <c r="H1252" t="n">
         <v>207534</v>
@@ -36735,7 +36735,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1254" t="n">
-        <v>14.4269504547119</v>
+        <v>14.4269514083862</v>
       </c>
       <c r="H1254" t="n">
         <v>513139</v>
@@ -36793,7 +36793,7 @@
         <v>15</v>
       </c>
       <c r="G1256" t="n">
-        <v>14.2464952468872</v>
+        <v>14.2464962005615</v>
       </c>
       <c r="H1256" t="n">
         <v>190883</v>
@@ -36822,7 +36822,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1257" t="n">
-        <v>14.4934349060059</v>
+        <v>14.4934358596802</v>
       </c>
       <c r="H1257" t="n">
         <v>484047</v>
@@ -36996,7 +36996,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1263" t="n">
-        <v>14.8543462753296</v>
+        <v>14.8543472290039</v>
       </c>
       <c r="H1263" t="n">
         <v>350866</v>
@@ -37083,7 +37083,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1266" t="n">
-        <v>14.5694169998169</v>
+        <v>14.5694160461426</v>
       </c>
       <c r="H1266" t="n">
         <v>283816</v>
@@ -37170,7 +37170,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G1269" t="n">
-        <v>15.110782623291</v>
+        <v>15.1107835769653</v>
       </c>
       <c r="H1269" t="n">
         <v>607990</v>
@@ -37257,7 +37257,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1272" t="n">
-        <v>14.7688684463501</v>
+        <v>14.7688674926758</v>
       </c>
       <c r="H1272" t="n">
         <v>366392</v>
@@ -37286,7 +37286,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1273" t="n">
-        <v>14.7118806838989</v>
+        <v>14.7118816375732</v>
       </c>
       <c r="H1273" t="n">
         <v>165183</v>
@@ -37315,7 +37315,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1274" t="n">
-        <v>14.5694169998169</v>
+        <v>14.5694160461426</v>
       </c>
       <c r="H1274" t="n">
         <v>239953</v>
@@ -37402,7 +37402,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1277" t="n">
-        <v>14.4079561233521</v>
+        <v>14.4079551696777</v>
       </c>
       <c r="H1277" t="n">
         <v>195856</v>
@@ -37460,7 +37460,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1279" t="n">
-        <v>14.5314264297485</v>
+        <v>14.5314254760742</v>
       </c>
       <c r="H1279" t="n">
         <v>147746</v>
@@ -37605,7 +37605,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G1284" t="n">
-        <v>15.319730758667</v>
+        <v>15.3197317123413</v>
       </c>
       <c r="H1284" t="n">
         <v>1360458</v>
@@ -37750,7 +37750,7 @@
         <v>16.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>15.6711454391479</v>
+        <v>15.6711444854736</v>
       </c>
       <c r="H1289" t="n">
         <v>398306</v>
@@ -37779,7 +37779,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1290" t="n">
-        <v>15.2627458572388</v>
+        <v>15.2627449035645</v>
       </c>
       <c r="H1290" t="n">
         <v>357033</v>
@@ -37895,7 +37895,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1294" t="n">
-        <v>14.7688684463501</v>
+        <v>14.7688674926758</v>
       </c>
       <c r="H1294" t="n">
         <v>377443</v>
@@ -37924,7 +37924,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1295" t="n">
-        <v>14.6358995437622</v>
+        <v>14.6359004974365</v>
       </c>
       <c r="H1295" t="n">
         <v>532047</v>
@@ -37953,7 +37953,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1296" t="n">
-        <v>14.6264019012451</v>
+        <v>14.6264009475708</v>
       </c>
       <c r="H1296" t="n">
         <v>395492</v>
@@ -37982,7 +37982,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1297" t="n">
-        <v>14.4364490509033</v>
+        <v>14.4364500045776</v>
       </c>
       <c r="H1297" t="n">
         <v>842933</v>
@@ -38127,7 +38127,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1302" t="n">
-        <v>15.0822896957397</v>
+        <v>15.0822906494141</v>
       </c>
       <c r="H1302" t="n">
         <v>305294</v>
@@ -38185,7 +38185,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G1304" t="n">
-        <v>14.6928853988647</v>
+        <v>14.6928863525391</v>
       </c>
       <c r="H1304" t="n">
         <v>429827</v>
@@ -38243,7 +38243,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G1306" t="n">
-        <v>14.8258533477783</v>
+        <v>14.825852394104</v>
       </c>
       <c r="H1306" t="n">
         <v>104373</v>
@@ -38272,7 +38272,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1307" t="n">
-        <v>14.7688684463501</v>
+        <v>14.7688674926758</v>
       </c>
       <c r="H1307" t="n">
         <v>123902</v>
@@ -38359,7 +38359,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1310" t="n">
-        <v>15.1202802658081</v>
+        <v>15.1202812194824</v>
       </c>
       <c r="H1310" t="n">
         <v>191702</v>
@@ -38417,7 +38417,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1312" t="n">
-        <v>15.2627458572388</v>
+        <v>15.2627449035645</v>
       </c>
       <c r="H1312" t="n">
         <v>448450</v>
@@ -38475,7 +38475,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1314" t="n">
-        <v>15.1012849807739</v>
+        <v>15.1012859344482</v>
       </c>
       <c r="H1314" t="n">
         <v>135045</v>
@@ -38504,7 +38504,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G1315" t="n">
-        <v>14.8448486328125</v>
+        <v>14.8448476791382</v>
       </c>
       <c r="H1315" t="n">
         <v>523922</v>
@@ -38533,7 +38533,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1316" t="n">
-        <v>14.9873123168945</v>
+        <v>14.9873132705688</v>
       </c>
       <c r="H1316" t="n">
         <v>239674</v>
@@ -38591,7 +38591,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1318" t="n">
-        <v>15.8705940246582</v>
+        <v>15.8705949783325</v>
       </c>
       <c r="H1318" t="n">
         <v>1686726</v>
@@ -38649,7 +38649,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1320" t="n">
-        <v>16.0320568084717</v>
+        <v>16.032054901123</v>
       </c>
       <c r="H1320" t="n">
         <v>326028</v>
@@ -38707,7 +38707,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1322" t="n">
-        <v>15.9370794296265</v>
+        <v>15.9370803833008</v>
       </c>
       <c r="H1322" t="n">
         <v>436612</v>
@@ -38736,7 +38736,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1323" t="n">
-        <v>15.8800926208496</v>
+        <v>15.8800916671753</v>
       </c>
       <c r="H1323" t="n">
         <v>189508</v>
@@ -38765,7 +38765,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>15.7376298904419</v>
+        <v>15.7376289367676</v>
       </c>
       <c r="H1324" t="n">
         <v>266463</v>
@@ -38852,7 +38852,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1327" t="n">
-        <v>15.7091379165649</v>
+        <v>15.7091369628906</v>
       </c>
       <c r="H1327" t="n">
         <v>255834</v>
@@ -38939,7 +38939,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1330" t="n">
-        <v>15.3672199249268</v>
+        <v>15.3672208786011</v>
       </c>
       <c r="H1330" t="n">
         <v>273867</v>
@@ -38968,7 +38968,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1331" t="n">
-        <v>15.3387269973755</v>
+        <v>15.3387260437012</v>
       </c>
       <c r="H1331" t="n">
         <v>147455</v>
@@ -38997,7 +38997,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1332" t="n">
-        <v>15.6996374130249</v>
+        <v>15.6996393203735</v>
       </c>
       <c r="H1332" t="n">
         <v>267931</v>
@@ -39055,7 +39055,7 @@
         <v>16.5149993896484</v>
       </c>
       <c r="G1334" t="n">
-        <v>15.6853914260864</v>
+        <v>15.6853904724121</v>
       </c>
       <c r="H1334" t="n">
         <v>173736</v>
@@ -39084,7 +39084,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G1335" t="n">
-        <v>15.9608240127563</v>
+        <v>15.960823059082</v>
       </c>
       <c r="H1335" t="n">
         <v>327422</v>
@@ -39113,7 +39113,7 @@
         <v>16.4449996948242</v>
       </c>
       <c r="G1336" t="n">
-        <v>15.6189079284668</v>
+        <v>15.6189069747925</v>
       </c>
       <c r="H1336" t="n">
         <v>353065</v>
@@ -39200,7 +39200,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1339" t="n">
-        <v>15.8468523025513</v>
+        <v>15.8468503952026</v>
       </c>
       <c r="H1339" t="n">
         <v>183071</v>
@@ -39229,7 +39229,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G1340" t="n">
-        <v>16.2837448120117</v>
+        <v>16.2837467193604</v>
       </c>
       <c r="H1340" t="n">
         <v>635746</v>
@@ -39258,7 +39258,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1341" t="n">
-        <v>16.696891784668</v>
+        <v>16.6968936920166</v>
       </c>
       <c r="H1341" t="n">
         <v>594110</v>
@@ -39316,7 +39316,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1343" t="n">
-        <v>16.8678493499756</v>
+        <v>16.8678512573242</v>
       </c>
       <c r="H1343" t="n">
         <v>319643</v>
@@ -39345,7 +39345,7 @@
         <v>17.7649993896484</v>
       </c>
       <c r="G1344" t="n">
-        <v>16.8726005554199</v>
+        <v>16.8725986480713</v>
       </c>
       <c r="H1344" t="n">
         <v>279966</v>
@@ -39403,7 +39403,7 @@
         <v>17.9349994659424</v>
       </c>
       <c r="G1346" t="n">
-        <v>17.0340595245361</v>
+        <v>17.0340576171875</v>
       </c>
       <c r="H1346" t="n">
         <v>476173</v>
@@ -39432,7 +39432,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1347" t="n">
-        <v>17.5136947631836</v>
+        <v>17.513692855835</v>
       </c>
       <c r="H1347" t="n">
         <v>624272</v>
@@ -39461,7 +39461,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G1348" t="n">
-        <v>17.4567070007324</v>
+        <v>17.4567031860352</v>
       </c>
       <c r="H1348" t="n">
         <v>598052</v>
@@ -39519,7 +39519,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1350" t="n">
-        <v>17.0388107299805</v>
+        <v>17.0388088226318</v>
       </c>
       <c r="H1350" t="n">
         <v>312332</v>
@@ -39548,7 +39548,7 @@
         <v>18.2049999237061</v>
       </c>
       <c r="G1351" t="n">
-        <v>17.2904968261719</v>
+        <v>17.2904987335205</v>
       </c>
       <c r="H1351" t="n">
         <v>262686</v>
@@ -39693,7 +39693,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1356" t="n">
-        <v>17.5421848297119</v>
+        <v>17.5421829223633</v>
       </c>
       <c r="H1356" t="n">
         <v>453013</v>
@@ -39809,7 +39809,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1360" t="n">
-        <v>17.4187145233154</v>
+        <v>17.4187164306641</v>
       </c>
       <c r="H1360" t="n">
         <v>267867</v>
@@ -39896,7 +39896,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1363" t="n">
-        <v>18.1975231170654</v>
+        <v>18.1975250244141</v>
       </c>
       <c r="H1363" t="n">
         <v>262496</v>
@@ -39925,7 +39925,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G1364" t="n">
-        <v>18.1500358581543</v>
+        <v>18.1500377655029</v>
       </c>
       <c r="H1364" t="n">
         <v>98181</v>
@@ -39954,7 +39954,7 @@
         <v>19.1949996948242</v>
       </c>
       <c r="G1365" t="n">
-        <v>18.2307643890381</v>
+        <v>18.2307662963867</v>
       </c>
       <c r="H1365" t="n">
         <v>224548</v>
@@ -39983,7 +39983,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1366" t="n">
-        <v>17.9315891265869</v>
+        <v>17.9315872192383</v>
       </c>
       <c r="H1366" t="n">
         <v>223880</v>
@@ -40070,7 +40070,7 @@
         <v>18.9050006866455</v>
       </c>
       <c r="G1369" t="n">
-        <v>17.9553356170654</v>
+        <v>17.9553337097168</v>
       </c>
       <c r="H1369" t="n">
         <v>202418</v>
@@ -40157,7 +40157,7 @@
         <v>18.9950008392334</v>
       </c>
       <c r="G1372" t="n">
-        <v>18.0408115386963</v>
+        <v>18.0408134460449</v>
       </c>
       <c r="H1372" t="n">
         <v>393300</v>
@@ -40244,7 +40244,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G1375" t="n">
-        <v>18.3209953308105</v>
+        <v>18.3209934234619</v>
       </c>
       <c r="H1375" t="n">
         <v>342018</v>
@@ -40331,7 +40331,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G1378" t="n">
-        <v>18.3542366027832</v>
+        <v>18.3542346954346</v>
       </c>
       <c r="H1378" t="n">
         <v>205617</v>
@@ -40360,7 +40360,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G1379" t="n">
-        <v>18.3969764709473</v>
+        <v>18.3969745635986</v>
       </c>
       <c r="H1379" t="n">
         <v>310977</v>
@@ -40418,7 +40418,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G1381" t="n">
-        <v>18.3969764709473</v>
+        <v>18.3969745635986</v>
       </c>
       <c r="H1381" t="n">
         <v>206770</v>
@@ -40447,7 +40447,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G1382" t="n">
-        <v>18.3542366027832</v>
+        <v>18.3542346954346</v>
       </c>
       <c r="H1382" t="n">
         <v>357274</v>
@@ -40505,7 +40505,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G1384" t="n">
-        <v>18.3209953308105</v>
+        <v>18.3209934234619</v>
       </c>
       <c r="H1384" t="n">
         <v>156305</v>
@@ -40650,7 +40650,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1389" t="n">
-        <v>18.4444618225098</v>
+        <v>18.444465637207</v>
       </c>
       <c r="H1389" t="n">
         <v>662703</v>
@@ -40737,7 +40737,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1392" t="n">
-        <v>18.5584354400635</v>
+        <v>18.5584373474121</v>
       </c>
       <c r="H1392" t="n">
         <v>213666</v>
@@ -40795,7 +40795,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G1394" t="n">
-        <v>17.8461112976074</v>
+        <v>17.8461093902588</v>
       </c>
       <c r="H1394" t="n">
         <v>862640</v>
@@ -40940,7 +40940,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G1399" t="n">
-        <v>17.1812725067139</v>
+        <v>17.1812744140625</v>
       </c>
       <c r="H1399" t="n">
         <v>154193</v>
@@ -40998,7 +40998,7 @@
         <v>18.0650005340576</v>
       </c>
       <c r="G1401" t="n">
-        <v>17.1575298309326</v>
+        <v>17.1575317382812</v>
       </c>
       <c r="H1401" t="n">
         <v>174374</v>
@@ -41027,7 +41027,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G1402" t="n">
-        <v>16.6114139556885</v>
+        <v>16.6114120483398</v>
       </c>
       <c r="H1402" t="n">
         <v>421366</v>
@@ -41085,7 +41085,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1404" t="n">
-        <v>16.696891784668</v>
+        <v>16.6968936920166</v>
       </c>
       <c r="H1404" t="n">
         <v>233955</v>
@@ -41143,7 +41143,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1406" t="n">
-        <v>16.877347946167</v>
+        <v>16.8773498535156</v>
       </c>
       <c r="H1406" t="n">
         <v>162700</v>
@@ -41230,7 +41230,7 @@
         <v>16.4449996948242</v>
       </c>
       <c r="G1409" t="n">
-        <v>15.6189079284668</v>
+        <v>15.6189069747925</v>
       </c>
       <c r="H1409" t="n">
         <v>429152</v>
@@ -41288,7 +41288,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>16.098539352417</v>
+        <v>16.0985412597656</v>
       </c>
       <c r="H1411" t="n">
         <v>459504</v>
@@ -41317,7 +41317,7 @@
         <v>16.8549995422363</v>
       </c>
       <c r="G1412" t="n">
-        <v>16.0083103179932</v>
+        <v>16.0083122253418</v>
       </c>
       <c r="H1412" t="n">
         <v>257458</v>
@@ -41462,7 +41462,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G1417" t="n">
-        <v>16.0368041992188</v>
+        <v>16.0368061065674</v>
       </c>
       <c r="H1417" t="n">
         <v>142262</v>
@@ -41491,7 +41491,7 @@
         <v>16.8449993133545</v>
       </c>
       <c r="G1418" t="n">
-        <v>15.9988145828247</v>
+        <v>15.9988136291504</v>
       </c>
       <c r="H1418" t="n">
         <v>242095</v>
@@ -41665,7 +41665,7 @@
         <v>18.0149993896484</v>
       </c>
       <c r="G1424" t="n">
-        <v>17.1100425720215</v>
+        <v>17.1100406646729</v>
       </c>
       <c r="H1424" t="n">
         <v>818896</v>
@@ -41723,7 +41723,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G1426" t="n">
-        <v>18.4919509887695</v>
+        <v>18.4919528961182</v>
       </c>
       <c r="H1426" t="n">
         <v>1825372</v>
@@ -41810,7 +41810,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>17.0008182525635</v>
+        <v>17.0008163452148</v>
       </c>
       <c r="H1429" t="n">
         <v>840706</v>
@@ -41926,7 +41926,7 @@
         <v>16.5750007629395</v>
       </c>
       <c r="G1433" t="n">
-        <v>15.7423782348633</v>
+        <v>15.7423791885376</v>
       </c>
       <c r="H1433" t="n">
         <v>814180</v>
@@ -42042,7 +42042,7 @@
         <v>16.8150005340576</v>
       </c>
       <c r="G1437" t="n">
-        <v>15.9703216552734</v>
+        <v>15.9703235626221</v>
       </c>
       <c r="H1437" t="n">
         <v>478682</v>
@@ -42071,7 +42071,7 @@
         <v>17.1849994659424</v>
       </c>
       <c r="G1438" t="n">
-        <v>16.3217334747314</v>
+        <v>16.3217353820801</v>
       </c>
       <c r="H1438" t="n">
         <v>606081</v>
@@ -42216,7 +42216,7 @@
         <v>17.1849994659424</v>
       </c>
       <c r="G1443" t="n">
-        <v>16.3217334747314</v>
+        <v>16.3217353820801</v>
       </c>
       <c r="H1443" t="n">
         <v>519520</v>
@@ -42274,7 +42274,7 @@
         <v>17.9349994659424</v>
       </c>
       <c r="G1445" t="n">
-        <v>17.0340595245361</v>
+        <v>17.0340576171875</v>
       </c>
       <c r="H1445" t="n">
         <v>595270</v>
@@ -42332,7 +42332,7 @@
         <v>18.8150005340576</v>
       </c>
       <c r="G1447" t="n">
-        <v>17.8698558807373</v>
+        <v>17.8698539733887</v>
       </c>
       <c r="H1447" t="n">
         <v>642098</v>
@@ -42477,7 +42477,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1452" t="n">
-        <v>16.696891784668</v>
+        <v>16.6968936920166</v>
       </c>
       <c r="H1452" t="n">
         <v>351433</v>
@@ -42535,7 +42535,7 @@
         <v>17.6049995422363</v>
       </c>
       <c r="G1454" t="n">
-        <v>16.7206363677979</v>
+        <v>16.7206382751465</v>
       </c>
       <c r="H1454" t="n">
         <v>381572</v>
@@ -42593,7 +42593,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1456" t="n">
-        <v>16.9628295898438</v>
+        <v>16.9628276824951</v>
       </c>
       <c r="H1456" t="n">
         <v>490557</v>
@@ -42680,7 +42680,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1459" t="n">
-        <v>16.9438304901123</v>
+        <v>16.9438323974609</v>
       </c>
       <c r="H1459" t="n">
         <v>262741</v>
@@ -42709,7 +42709,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1460" t="n">
-        <v>16.8298587799072</v>
+        <v>16.8298606872559</v>
       </c>
       <c r="H1460" t="n">
         <v>299762</v>
@@ -42825,7 +42825,7 @@
         <v>17.7250003814697</v>
       </c>
       <c r="G1464" t="n">
-        <v>16.8346118927002</v>
+        <v>16.8346099853516</v>
       </c>
       <c r="H1464" t="n">
         <v>272853</v>
@@ -42912,7 +42912,7 @@
         <v>17.9449996948242</v>
       </c>
       <c r="G1467" t="n">
-        <v>17.0435562133789</v>
+        <v>17.0435581207275</v>
       </c>
       <c r="H1467" t="n">
         <v>317629</v>
@@ -43028,7 +43028,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>17.0008182525635</v>
+        <v>17.0008163452148</v>
       </c>
       <c r="H1471" t="n">
         <v>312375</v>
@@ -43115,7 +43115,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1474" t="n">
-        <v>16.9438304901123</v>
+        <v>16.9438323974609</v>
       </c>
       <c r="H1474" t="n">
         <v>321911</v>
@@ -43144,7 +43144,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1475" t="n">
-        <v>17.0388107299805</v>
+        <v>17.0388088226318</v>
       </c>
       <c r="H1475" t="n">
         <v>189745</v>
@@ -43289,7 +43289,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1480" t="n">
-        <v>17.2857475280762</v>
+        <v>17.2857494354248</v>
       </c>
       <c r="H1480" t="n">
         <v>256636</v>
@@ -43318,7 +43318,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G1481" t="n">
-        <v>17.1812725067139</v>
+        <v>17.1812744140625</v>
       </c>
       <c r="H1481" t="n">
         <v>127358</v>
@@ -43405,7 +43405,7 @@
         <v>18.6550006866455</v>
       </c>
       <c r="G1484" t="n">
-        <v>17.7178936004639</v>
+        <v>17.7178916931152</v>
       </c>
       <c r="H1484" t="n">
         <v>210630</v>
@@ -43550,7 +43550,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.7911281585693</v>
+        <v>18.7911262512207</v>
       </c>
       <c r="H1489" t="n">
         <v>580958</v>
@@ -43579,7 +43579,7 @@
         <v>19.9750003814697</v>
       </c>
       <c r="G1490" t="n">
-        <v>18.9715824127197</v>
+        <v>18.9715843200684</v>
       </c>
       <c r="H1490" t="n">
         <v>760653</v>
@@ -43637,7 +43637,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1492" t="n">
-        <v>17.945837020874</v>
+        <v>17.9458351135254</v>
       </c>
       <c r="H1492" t="n">
         <v>698032</v>
@@ -43782,7 +43782,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1497" t="n">
-        <v>19.3752326965332</v>
+        <v>19.3752346038818</v>
       </c>
       <c r="H1497" t="n">
         <v>697296</v>
@@ -43811,7 +43811,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>18.92409324646</v>
+        <v>18.9240951538086</v>
       </c>
       <c r="H1498" t="n">
         <v>727935</v>
@@ -43840,7 +43840,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1499" t="n">
-        <v>19.1662864685059</v>
+        <v>19.1662845611572</v>
       </c>
       <c r="H1499" t="n">
         <v>633946</v>
@@ -43869,7 +43869,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1500" t="n">
-        <v>19.1662864685059</v>
+        <v>19.1662845611572</v>
       </c>
       <c r="H1500" t="n">
         <v>447223</v>
@@ -43956,7 +43956,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1503" t="n">
-        <v>19.2802581787109</v>
+        <v>19.2802562713623</v>
       </c>
       <c r="H1503" t="n">
         <v>1562946</v>
@@ -44014,7 +44014,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1505" t="n">
-        <v>19.1377906799316</v>
+        <v>19.1377925872803</v>
       </c>
       <c r="H1505" t="n">
         <v>842589</v>
@@ -44043,7 +44043,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G1506" t="n">
-        <v>19.6316719055176</v>
+        <v>19.6316699981689</v>
       </c>
       <c r="H1506" t="n">
         <v>470641</v>
@@ -44101,7 +44101,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G1508" t="n">
-        <v>19.8691120147705</v>
+        <v>19.8691139221191</v>
       </c>
       <c r="H1508" t="n">
         <v>577156</v>
@@ -44130,7 +44130,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G1509" t="n">
-        <v>19.7456455230713</v>
+        <v>19.7456436157227</v>
       </c>
       <c r="H1509" t="n">
         <v>293466</v>
@@ -44159,7 +44159,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1510" t="n">
-        <v>20.4579677581787</v>
+        <v>20.4579696655273</v>
       </c>
       <c r="H1510" t="n">
         <v>712388</v>
@@ -44217,7 +44217,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1512" t="n">
-        <v>21.0373249053955</v>
+        <v>21.0373268127441</v>
       </c>
       <c r="H1512" t="n">
         <v>923182</v>
@@ -44362,7 +44362,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G1517" t="n">
-        <v>20.1635398864746</v>
+        <v>20.1635417938232</v>
       </c>
       <c r="H1517" t="n">
         <v>373968</v>
@@ -44391,7 +44391,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G1518" t="n">
-        <v>20.0970573425293</v>
+        <v>20.0970554351807</v>
       </c>
       <c r="H1518" t="n">
         <v>537973</v>
@@ -44449,7 +44449,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G1520" t="n">
-        <v>20.7144031524658</v>
+        <v>20.7144050598145</v>
       </c>
       <c r="H1520" t="n">
         <v>644433</v>
@@ -44478,7 +44478,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G1521" t="n">
-        <v>21.0278263092041</v>
+        <v>21.0278282165527</v>
       </c>
       <c r="H1521" t="n">
         <v>354406</v>
@@ -44507,7 +44507,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1522" t="n">
-        <v>21.0373249053955</v>
+        <v>21.0373268127441</v>
       </c>
       <c r="H1522" t="n">
         <v>216817</v>
@@ -44536,7 +44536,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G1523" t="n">
-        <v>21.0183296203613</v>
+        <v>21.0183277130127</v>
       </c>
       <c r="H1523" t="n">
         <v>163933</v>
@@ -44739,7 +44739,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G1530" t="n">
-        <v>21.5976886749268</v>
+        <v>21.5976867675781</v>
       </c>
       <c r="H1530" t="n">
         <v>280104</v>
@@ -44768,7 +44768,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G1531" t="n">
-        <v>21.6261806488037</v>
+        <v>21.6261825561523</v>
       </c>
       <c r="H1531" t="n">
         <v>356048</v>
@@ -44797,7 +44797,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G1532" t="n">
-        <v>19.7171478271484</v>
+        <v>19.7171497344971</v>
       </c>
       <c r="H1532" t="n">
         <v>1855644</v>
@@ -44971,7 +44971,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1538" t="n">
-        <v>19.2802581787109</v>
+        <v>19.2802562713623</v>
       </c>
       <c r="H1538" t="n">
         <v>526926</v>
@@ -45058,7 +45058,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G1541" t="n">
-        <v>18.0550594329834</v>
+        <v>18.055061340332</v>
       </c>
       <c r="H1541" t="n">
         <v>598933</v>
@@ -45087,7 +45087,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1542" t="n">
-        <v>17.4946975708008</v>
+        <v>17.4946956634521</v>
       </c>
       <c r="H1542" t="n">
         <v>915612</v>
@@ -45116,7 +45116,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1543" t="n">
-        <v>17.5421848297119</v>
+        <v>17.5421829223633</v>
       </c>
       <c r="H1543" t="n">
         <v>553477</v>
@@ -45145,7 +45145,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1544" t="n">
-        <v>18.0930500030518</v>
+        <v>18.0930480957031</v>
       </c>
       <c r="H1544" t="n">
         <v>460206</v>
@@ -45261,7 +45261,7 @@
         <v>19.5750007629395</v>
       </c>
       <c r="G1548" t="n">
-        <v>18.5916786193848</v>
+        <v>18.5916767120361</v>
       </c>
       <c r="H1548" t="n">
         <v>502931</v>
@@ -45290,7 +45290,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1549" t="n">
-        <v>18.5394401550293</v>
+        <v>18.5394420623779</v>
       </c>
       <c r="H1549" t="n">
         <v>396132</v>
@@ -45348,7 +45348,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1551" t="n">
-        <v>17.945837020874</v>
+        <v>17.9458351135254</v>
       </c>
       <c r="H1551" t="n">
         <v>261232</v>
@@ -45377,7 +45377,7 @@
         <v>18.9950008392334</v>
       </c>
       <c r="G1552" t="n">
-        <v>18.0408115386963</v>
+        <v>18.0408134460449</v>
       </c>
       <c r="H1552" t="n">
         <v>178538</v>
@@ -45406,7 +45406,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G1553" t="n">
-        <v>18.0503082275391</v>
+        <v>18.0503101348877</v>
       </c>
       <c r="H1553" t="n">
         <v>183351</v>
@@ -45464,7 +45464,7 @@
         <v>19.25</v>
       </c>
       <c r="G1555" t="n">
-        <v>18.2830047607422</v>
+        <v>18.2830009460449</v>
       </c>
       <c r="H1555" t="n">
         <v>246876</v>
@@ -45667,7 +45667,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1562" t="n">
-        <v>18.5964241027832</v>
+        <v>18.5964260101318</v>
       </c>
       <c r="H1562" t="n">
         <v>209980</v>
@@ -45696,7 +45696,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G1563" t="n">
-        <v>18.7768821716309</v>
+        <v>18.7768802642822</v>
       </c>
       <c r="H1563" t="n">
         <v>334413</v>
@@ -45783,7 +45783,7 @@
         <v>19.6450004577637</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.6581611633301</v>
+        <v>18.6581592559814</v>
       </c>
       <c r="H1566" t="n">
         <v>358435</v>
@@ -45841,7 +45841,7 @@
         <v>18.5650005340576</v>
       </c>
       <c r="G1568" t="n">
-        <v>17.6324138641357</v>
+        <v>17.6324157714844</v>
       </c>
       <c r="H1568" t="n">
         <v>299563</v>
@@ -45870,7 +45870,7 @@
         <v>18.6749992370605</v>
       </c>
       <c r="G1569" t="n">
-        <v>17.7368850708008</v>
+        <v>17.7368869781494</v>
       </c>
       <c r="H1569" t="n">
         <v>339103</v>
@@ -45928,7 +45928,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G1571" t="n">
-        <v>15.1867647171021</v>
+        <v>15.1867637634277</v>
       </c>
       <c r="H1571" t="n">
         <v>1215929</v>
@@ -45986,7 +45986,7 @@
         <v>15.2749996185303</v>
       </c>
       <c r="G1573" t="n">
-        <v>14.5076818466187</v>
+        <v>14.5076808929443</v>
       </c>
       <c r="H1573" t="n">
         <v>715448</v>
@@ -46015,7 +46015,7 @@
         <v>16.7549991607666</v>
       </c>
       <c r="G1574" t="n">
-        <v>15.9133348464966</v>
+        <v>15.9133329391479</v>
       </c>
       <c r="H1574" t="n">
         <v>1254789</v>
@@ -46073,7 +46073,7 @@
         <v>16.1650009155273</v>
       </c>
       <c r="G1576" t="n">
-        <v>15.3529739379883</v>
+        <v>15.3529748916626</v>
       </c>
       <c r="H1576" t="n">
         <v>678377</v>
@@ -46102,7 +46102,7 @@
         <v>16.2749996185303</v>
       </c>
       <c r="G1577" t="n">
-        <v>15.4574480056763</v>
+        <v>15.457447052002</v>
       </c>
       <c r="H1577" t="n">
         <v>667193</v>
@@ -46131,7 +46131,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1578" t="n">
-        <v>14.8733406066895</v>
+        <v>14.8733415603638</v>
       </c>
       <c r="H1578" t="n">
         <v>505703</v>
@@ -46160,7 +46160,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G1579" t="n">
-        <v>15.5856657028198</v>
+        <v>15.5856666564941</v>
       </c>
       <c r="H1579" t="n">
         <v>678989</v>
@@ -46189,7 +46189,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1580" t="n">
-        <v>15.7043876647949</v>
+        <v>15.7043857574463</v>
       </c>
       <c r="H1580" t="n">
         <v>591416</v>
@@ -46218,7 +46218,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1581" t="n">
-        <v>15.8610982894897</v>
+        <v>15.8611001968384</v>
       </c>
       <c r="H1581" t="n">
         <v>285487</v>
@@ -46334,7 +46334,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1585" t="n">
-        <v>15.253246307373</v>
+        <v>15.2532472610474</v>
       </c>
       <c r="H1585" t="n">
         <v>212871</v>
@@ -46392,7 +46392,7 @@
         <v>16.6650009155273</v>
       </c>
       <c r="G1587" t="n">
-        <v>15.82785987854</v>
+        <v>15.8278579711914</v>
       </c>
       <c r="H1587" t="n">
         <v>215883</v>
@@ -46421,7 +46421,7 @@
         <v>17.6550006866455</v>
       </c>
       <c r="G1588" t="n">
-        <v>16.7681255340576</v>
+        <v>16.7681274414062</v>
       </c>
       <c r="H1588" t="n">
         <v>512570</v>
@@ -46450,7 +46450,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1589" t="n">
-        <v>16.8678493499756</v>
+        <v>16.8678512573242</v>
       </c>
       <c r="H1589" t="n">
         <v>278806</v>
@@ -46537,7 +46537,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1592" t="n">
-        <v>15.9750719070435</v>
+        <v>15.9750709533691</v>
       </c>
       <c r="H1592" t="n">
         <v>499755</v>
@@ -46566,7 +46566,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1593" t="n">
-        <v>15.2627458572388</v>
+        <v>15.2627449035645</v>
       </c>
       <c r="H1593" t="n">
         <v>528848</v>
@@ -46711,7 +46711,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1598" t="n">
-        <v>15.3387269973755</v>
+        <v>15.3387260437012</v>
       </c>
       <c r="H1598" t="n">
         <v>634313</v>
@@ -46740,7 +46740,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1599" t="n">
-        <v>15.4811916351318</v>
+        <v>15.4811906814575</v>
       </c>
       <c r="H1599" t="n">
         <v>368053</v>
@@ -46798,7 +46798,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1601" t="n">
-        <v>15.6521492004395</v>
+        <v>15.6521482467651</v>
       </c>
       <c r="H1601" t="n">
         <v>164090</v>
@@ -46827,7 +46827,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1602" t="n">
-        <v>15.6996374130249</v>
+        <v>15.6996393203735</v>
       </c>
       <c r="H1602" t="n">
         <v>249471</v>
@@ -46885,7 +46885,7 @@
         <v>16.3299999237061</v>
       </c>
       <c r="G1604" t="n">
-        <v>15.5096855163574</v>
+        <v>15.5096845626831</v>
       </c>
       <c r="H1604" t="n">
         <v>267467</v>
@@ -47030,7 +47030,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1609" t="n">
-        <v>15.7851190567017</v>
+        <v>15.7851181030273</v>
       </c>
       <c r="H1609" t="n">
         <v>431470</v>
@@ -47059,7 +47059,7 @@
         <v>16.5</v>
       </c>
       <c r="G1610" t="n">
-        <v>15.6711454391479</v>
+        <v>15.6711444854736</v>
       </c>
       <c r="H1610" t="n">
         <v>196339</v>
@@ -47088,7 +47088,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G1611" t="n">
-        <v>15.0348024368286</v>
+        <v>15.0348014831543</v>
       </c>
       <c r="H1611" t="n">
         <v>1097109</v>
@@ -47204,7 +47204,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1615" t="n">
-        <v>13.8285980224609</v>
+        <v>13.8285989761353</v>
       </c>
       <c r="H1615" t="n">
         <v>1055241</v>
@@ -47291,7 +47291,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1618" t="n">
-        <v>14.1990070343018</v>
+        <v>14.1990079879761</v>
       </c>
       <c r="H1618" t="n">
         <v>610192</v>
@@ -47349,7 +47349,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G1620" t="n">
-        <v>15.0158071517944</v>
+        <v>15.0158061981201</v>
       </c>
       <c r="H1620" t="n">
         <v>321594</v>
@@ -47407,7 +47407,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1622" t="n">
-        <v>15.3672199249268</v>
+        <v>15.3672208786011</v>
       </c>
       <c r="H1622" t="n">
         <v>545962</v>
@@ -80009,6 +80009,35 @@
         <v>214707</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>7.01999998092651</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>7.1399998664856</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>6.58500003814697</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>6.6100001335144</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>6.6100001335144</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>1300540</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -456,7 +456,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G3" t="n">
-        <v>18.01096534729</v>
+        <v>18.0109634399414</v>
       </c>
       <c r="H3" t="n">
         <v>997627</v>
@@ -485,7 +485,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G4" t="n">
-        <v>17.4978809356689</v>
+        <v>17.4978828430176</v>
       </c>
       <c r="H4" t="n">
         <v>985547</v>
@@ -514,7 +514,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>17.9401931762695</v>
+        <v>17.9401912689209</v>
       </c>
       <c r="H5" t="n">
         <v>1381959</v>
@@ -659,7 +659,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G10" t="n">
-        <v>18.8425121307373</v>
+        <v>18.8425102233887</v>
       </c>
       <c r="H10" t="n">
         <v>1053164</v>
@@ -688,7 +688,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G11" t="n">
-        <v>18.4621238708496</v>
+        <v>18.462121963501</v>
       </c>
       <c r="H11" t="n">
         <v>802632</v>
@@ -746,7 +746,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G13" t="n">
-        <v>18.0994262695312</v>
+        <v>18.0994243621826</v>
       </c>
       <c r="H13" t="n">
         <v>975727</v>
@@ -775,7 +775,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G14" t="n">
-        <v>17.6394214630127</v>
+        <v>17.6394195556641</v>
       </c>
       <c r="H14" t="n">
         <v>943974</v>
@@ -833,7 +833,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G16" t="n">
-        <v>18.1878871917725</v>
+        <v>18.1878890991211</v>
       </c>
       <c r="H16" t="n">
         <v>813843</v>
@@ -862,7 +862,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G17" t="n">
-        <v>18.0994262695312</v>
+        <v>18.0994243621826</v>
       </c>
       <c r="H17" t="n">
         <v>476663</v>
@@ -920,7 +920,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>18.223274230957</v>
+        <v>18.2232761383057</v>
       </c>
       <c r="H19" t="n">
         <v>550218</v>
@@ -949,7 +949,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>17.7632694244385</v>
+        <v>17.7632713317871</v>
       </c>
       <c r="H20" t="n">
         <v>1244898</v>
@@ -1007,7 +1007,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G22" t="n">
-        <v>18.6744346618652</v>
+        <v>18.6744327545166</v>
       </c>
       <c r="H22" t="n">
         <v>1011926</v>
@@ -1036,7 +1036,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>17.9578857421875</v>
+        <v>17.9578838348389</v>
       </c>
       <c r="H23" t="n">
         <v>725076</v>
@@ -1065,7 +1065,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G24" t="n">
-        <v>18.2055835723877</v>
+        <v>18.2055797576904</v>
       </c>
       <c r="H24" t="n">
         <v>1897967</v>
@@ -1094,7 +1094,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G25" t="n">
-        <v>18.258659362793</v>
+        <v>18.2586574554443</v>
       </c>
       <c r="H25" t="n">
         <v>716525</v>
@@ -1123,7 +1123,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G26" t="n">
-        <v>18.0817375183105</v>
+        <v>18.0817356109619</v>
       </c>
       <c r="H26" t="n">
         <v>1482038</v>
@@ -1152,7 +1152,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G27" t="n">
-        <v>17.3563442230225</v>
+        <v>17.3563423156738</v>
       </c>
       <c r="H27" t="n">
         <v>875683</v>
@@ -1181,7 +1181,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G28" t="n">
-        <v>16.9051856994629</v>
+        <v>16.9051837921143</v>
       </c>
       <c r="H28" t="n">
         <v>908164</v>
@@ -1239,7 +1239,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G30" t="n">
-        <v>16.6486415863037</v>
+        <v>16.6486434936523</v>
       </c>
       <c r="H30" t="n">
         <v>1048393</v>
@@ -1413,7 +1413,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G36" t="n">
-        <v>18.453275680542</v>
+        <v>18.4532775878906</v>
       </c>
       <c r="H36" t="n">
         <v>500284</v>
@@ -1442,7 +1442,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>18.9752063751221</v>
+        <v>18.9752044677734</v>
       </c>
       <c r="H37" t="n">
         <v>534225</v>
@@ -1471,7 +1471,7 @@
         <v>20.5</v>
       </c>
       <c r="G38" t="n">
-        <v>18.1348114013672</v>
+        <v>18.1348133087158</v>
       </c>
       <c r="H38" t="n">
         <v>591716</v>
@@ -1500,7 +1500,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G39" t="n">
-        <v>17.3121109008789</v>
+        <v>17.3121089935303</v>
       </c>
       <c r="H39" t="n">
         <v>1119066</v>
@@ -1529,7 +1529,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G40" t="n">
-        <v>17.7632694244385</v>
+        <v>17.7632713317871</v>
       </c>
       <c r="H40" t="n">
         <v>488362</v>
@@ -1558,7 +1558,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G41" t="n">
-        <v>17.9048099517822</v>
+        <v>17.9048080444336</v>
       </c>
       <c r="H41" t="n">
         <v>422135</v>
@@ -1616,7 +1616,7 @@
         <v>21.5</v>
       </c>
       <c r="G43" t="n">
-        <v>19.0194358825684</v>
+        <v>19.019437789917</v>
       </c>
       <c r="H43" t="n">
         <v>1151116</v>
@@ -1674,7 +1674,7 @@
         <v>21.3099994659424</v>
       </c>
       <c r="G45" t="n">
-        <v>18.8513565063477</v>
+        <v>18.8513584136963</v>
       </c>
       <c r="H45" t="n">
         <v>368675</v>
@@ -1703,7 +1703,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G46" t="n">
-        <v>19.3113632202148</v>
+        <v>19.3113613128662</v>
       </c>
       <c r="H46" t="n">
         <v>602537</v>
@@ -1790,7 +1790,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>19.7271347045898</v>
+        <v>19.7271366119385</v>
       </c>
       <c r="H49" t="n">
         <v>805952</v>
@@ -1848,7 +1848,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G51" t="n">
-        <v>19.647518157959</v>
+        <v>19.6475200653076</v>
       </c>
       <c r="H51" t="n">
         <v>599137</v>
@@ -1877,7 +1877,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G52" t="n">
-        <v>19.9836769104004</v>
+        <v>19.983678817749</v>
       </c>
       <c r="H52" t="n">
         <v>593798</v>
@@ -1906,7 +1906,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G53" t="n">
-        <v>19.1167430877686</v>
+        <v>19.1167449951172</v>
       </c>
       <c r="H53" t="n">
         <v>1070469</v>
@@ -2080,7 +2080,7 @@
         <v>22.0100002288818</v>
       </c>
       <c r="G59" t="n">
-        <v>19.4705944061279</v>
+        <v>19.4705963134766</v>
       </c>
       <c r="H59" t="n">
         <v>731623</v>
@@ -2109,7 +2109,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G60" t="n">
-        <v>18.9663600921631</v>
+        <v>18.9663581848145</v>
       </c>
       <c r="H60" t="n">
         <v>524013</v>
@@ -2138,7 +2138,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G61" t="n">
-        <v>19.4794406890869</v>
+        <v>19.4794387817383</v>
       </c>
       <c r="H61" t="n">
         <v>502164</v>
@@ -2283,7 +2283,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G66" t="n">
-        <v>18.8690490722656</v>
+        <v>18.8690509796143</v>
       </c>
       <c r="H66" t="n">
         <v>592054</v>
@@ -2341,7 +2341,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G68" t="n">
-        <v>18.5151996612549</v>
+        <v>18.5151977539062</v>
       </c>
       <c r="H68" t="n">
         <v>449428</v>
@@ -2370,7 +2370,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>18.9309730529785</v>
+        <v>18.9309749603271</v>
       </c>
       <c r="H69" t="n">
         <v>499244</v>
@@ -2428,7 +2428,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G71" t="n">
-        <v>18.5240478515625</v>
+        <v>18.5240497589111</v>
       </c>
       <c r="H71" t="n">
         <v>1288923</v>
@@ -2457,7 +2457,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G72" t="n">
-        <v>19.3113632202148</v>
+        <v>19.3113613128662</v>
       </c>
       <c r="H72" t="n">
         <v>724111</v>
@@ -2515,7 +2515,7 @@
         <v>21.25</v>
       </c>
       <c r="G74" t="n">
-        <v>18.7982807159424</v>
+        <v>18.7982788085938</v>
       </c>
       <c r="H74" t="n">
         <v>401285</v>
@@ -2544,7 +2544,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G75" t="n">
-        <v>18.8778972625732</v>
+        <v>18.8778953552246</v>
       </c>
       <c r="H75" t="n">
         <v>347479</v>
@@ -2718,7 +2718,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G81" t="n">
-        <v>18.0817375183105</v>
+        <v>18.0817356109619</v>
       </c>
       <c r="H81" t="n">
         <v>609476</v>
@@ -2747,7 +2747,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G82" t="n">
-        <v>18.0640392303467</v>
+        <v>18.0640411376953</v>
       </c>
       <c r="H82" t="n">
         <v>264849</v>
@@ -2834,7 +2834,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>18.0021171569824</v>
+        <v>18.0021190643311</v>
       </c>
       <c r="H85" t="n">
         <v>455661</v>
@@ -2892,7 +2892,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G87" t="n">
-        <v>17.9048099517822</v>
+        <v>17.9048080444336</v>
       </c>
       <c r="H87" t="n">
         <v>346687</v>
@@ -2921,7 +2921,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G88" t="n">
-        <v>17.444803237915</v>
+        <v>17.4448013305664</v>
       </c>
       <c r="H88" t="n">
         <v>546914</v>
@@ -2950,7 +2950,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G89" t="n">
-        <v>17.1440315246582</v>
+        <v>17.1440277099609</v>
       </c>
       <c r="H89" t="n">
         <v>741696</v>
@@ -3008,7 +3008,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G91" t="n">
-        <v>17.9844226837158</v>
+        <v>17.9844245910645</v>
       </c>
       <c r="H91" t="n">
         <v>812214</v>
@@ -3037,7 +3037,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>17.6394214630127</v>
+        <v>17.6394195556641</v>
       </c>
       <c r="H92" t="n">
         <v>678917</v>
@@ -3124,7 +3124,7 @@
         <v>21.25</v>
       </c>
       <c r="G95" t="n">
-        <v>18.7982807159424</v>
+        <v>18.7982788085938</v>
       </c>
       <c r="H95" t="n">
         <v>742962</v>
@@ -3153,7 +3153,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>18.0640392303467</v>
+        <v>18.0640411376953</v>
       </c>
       <c r="H96" t="n">
         <v>670991</v>
@@ -3298,7 +3298,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G101" t="n">
-        <v>17.81125831604</v>
+        <v>17.8112602233887</v>
       </c>
       <c r="H101" t="n">
         <v>334331</v>
@@ -3327,7 +3327,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G102" t="n">
-        <v>17.7025985717773</v>
+        <v>17.702600479126</v>
       </c>
       <c r="H102" t="n">
         <v>848652</v>
@@ -3385,7 +3385,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G104" t="n">
-        <v>17.5305557250977</v>
+        <v>17.530553817749</v>
       </c>
       <c r="H104" t="n">
         <v>453269</v>
@@ -3443,7 +3443,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G106" t="n">
-        <v>17.4128379821777</v>
+        <v>17.4128360748291</v>
       </c>
       <c r="H106" t="n">
         <v>450576</v>
@@ -3472,7 +3472,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G107" t="n">
-        <v>17.304178237915</v>
+        <v>17.3041763305664</v>
       </c>
       <c r="H107" t="n">
         <v>353691</v>
@@ -3501,7 +3501,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>17.4762210845947</v>
+        <v>17.4762191772461</v>
       </c>
       <c r="H108" t="n">
         <v>367982</v>
@@ -3530,7 +3530,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G109" t="n">
-        <v>17.4762210845947</v>
+        <v>17.4762191772461</v>
       </c>
       <c r="H109" t="n">
         <v>426168</v>
@@ -3559,7 +3559,7 @@
         <v>19.25</v>
       </c>
       <c r="G110" t="n">
-        <v>17.4309463500977</v>
+        <v>17.430944442749</v>
       </c>
       <c r="H110" t="n">
         <v>645536</v>
@@ -3588,7 +3588,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G111" t="n">
-        <v>17.4852771759033</v>
+        <v>17.485279083252</v>
       </c>
       <c r="H111" t="n">
         <v>582475</v>
@@ -3617,7 +3617,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>17.7478733062744</v>
+        <v>17.747875213623</v>
       </c>
       <c r="H112" t="n">
         <v>286254</v>
@@ -3733,7 +3733,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G116" t="n">
-        <v>16.5435543060303</v>
+        <v>16.5435523986816</v>
       </c>
       <c r="H116" t="n">
         <v>483555</v>
@@ -3791,7 +3791,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G118" t="n">
-        <v>17.0778007507324</v>
+        <v>17.0778026580811</v>
       </c>
       <c r="H118" t="n">
         <v>634094</v>
@@ -3878,7 +3878,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G121" t="n">
-        <v>17.7297630310059</v>
+        <v>17.7297649383545</v>
       </c>
       <c r="H121" t="n">
         <v>523740</v>
@@ -3907,7 +3907,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G122" t="n">
-        <v>17.8655872344971</v>
+        <v>17.8655891418457</v>
       </c>
       <c r="H122" t="n">
         <v>478133</v>
@@ -3965,7 +3965,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G124" t="n">
-        <v>16.8514232635498</v>
+        <v>16.8514251708984</v>
       </c>
       <c r="H124" t="n">
         <v>1162990</v>
@@ -3994,7 +3994,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>16.3896198272705</v>
+        <v>16.3896179199219</v>
       </c>
       <c r="H125" t="n">
         <v>973572</v>
@@ -4168,7 +4168,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G131" t="n">
-        <v>16.8242588043213</v>
+        <v>16.8242568969727</v>
       </c>
       <c r="H131" t="n">
         <v>503139</v>
@@ -4197,7 +4197,7 @@
         <v>17.75</v>
       </c>
       <c r="G132" t="n">
-        <v>16.0726909637451</v>
+        <v>16.0726928710938</v>
       </c>
       <c r="H132" t="n">
         <v>575432</v>
@@ -4313,7 +4313,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G136" t="n">
-        <v>16.6974906921387</v>
+        <v>16.69748878479</v>
       </c>
       <c r="H136" t="n">
         <v>745932</v>
@@ -4400,7 +4400,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G139" t="n">
-        <v>17.086856842041</v>
+        <v>17.0868587493896</v>
       </c>
       <c r="H139" t="n">
         <v>861033</v>
@@ -4458,7 +4458,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>17.0325222015381</v>
+        <v>17.0325241088867</v>
       </c>
       <c r="H141" t="n">
         <v>247627</v>
@@ -4487,7 +4487,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>17.3403930664062</v>
+        <v>17.3403949737549</v>
       </c>
       <c r="H142" t="n">
         <v>734812</v>
@@ -4516,7 +4516,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G143" t="n">
-        <v>17.8655872344971</v>
+        <v>17.8655891418457</v>
       </c>
       <c r="H143" t="n">
         <v>769870</v>
@@ -4574,7 +4574,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G145" t="n">
-        <v>18.1372413635254</v>
+        <v>18.1372394561768</v>
       </c>
       <c r="H145" t="n">
         <v>615453</v>
@@ -4632,7 +4632,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G147" t="n">
-        <v>18.7710914611816</v>
+        <v>18.771089553833</v>
       </c>
       <c r="H147" t="n">
         <v>1164581</v>
@@ -4690,7 +4690,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G149" t="n">
-        <v>19.0699081420898</v>
+        <v>19.0699100494385</v>
       </c>
       <c r="H149" t="n">
         <v>1159289</v>
@@ -4748,7 +4748,7 @@
         <v>20.5699996948242</v>
       </c>
       <c r="G151" t="n">
-        <v>18.6262111663818</v>
+        <v>18.6262130737305</v>
       </c>
       <c r="H151" t="n">
         <v>1004411</v>
@@ -4777,7 +4777,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G152" t="n">
-        <v>18.4994411468506</v>
+        <v>18.4994430541992</v>
       </c>
       <c r="H152" t="n">
         <v>1504019</v>
@@ -4806,7 +4806,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G153" t="n">
-        <v>18.2187366485596</v>
+        <v>18.2187347412109</v>
       </c>
       <c r="H153" t="n">
         <v>1091340</v>
@@ -4835,7 +4835,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G154" t="n">
-        <v>18.716760635376</v>
+        <v>18.7167625427246</v>
       </c>
       <c r="H154" t="n">
         <v>930993</v>
@@ -4864,7 +4864,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G155" t="n">
-        <v>18.5809383392334</v>
+        <v>18.580940246582</v>
       </c>
       <c r="H155" t="n">
         <v>402078</v>
@@ -4893,7 +4893,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G156" t="n">
-        <v>18.7620372772217</v>
+        <v>18.762035369873</v>
       </c>
       <c r="H156" t="n">
         <v>454171</v>
@@ -4922,7 +4922,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G157" t="n">
-        <v>18.4994411468506</v>
+        <v>18.4994430541992</v>
       </c>
       <c r="H157" t="n">
         <v>593471</v>
@@ -4980,7 +4980,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G159" t="n">
-        <v>18.9431381225586</v>
+        <v>18.94313621521</v>
       </c>
       <c r="H159" t="n">
         <v>809515</v>
@@ -5038,7 +5038,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G161" t="n">
-        <v>18.6624317169189</v>
+        <v>18.6624336242676</v>
       </c>
       <c r="H161" t="n">
         <v>488367</v>
@@ -5067,7 +5067,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G162" t="n">
-        <v>18.6624317169189</v>
+        <v>18.6624336242676</v>
       </c>
       <c r="H162" t="n">
         <v>278516</v>
@@ -5096,7 +5096,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>18.4722728729248</v>
+        <v>18.4722747802734</v>
       </c>
       <c r="H163" t="n">
         <v>404764</v>
@@ -5154,7 +5154,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G165" t="n">
-        <v>18.7529811859131</v>
+        <v>18.7529792785645</v>
       </c>
       <c r="H165" t="n">
         <v>532932</v>
@@ -5241,7 +5241,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G168" t="n">
-        <v>18.6081008911133</v>
+        <v>18.6081027984619</v>
       </c>
       <c r="H168" t="n">
         <v>405254</v>
@@ -5299,7 +5299,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G170" t="n">
-        <v>18.716760635376</v>
+        <v>18.7167625427246</v>
       </c>
       <c r="H170" t="n">
         <v>499477</v>
@@ -5328,7 +5328,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G171" t="n">
-        <v>18.5175514221191</v>
+        <v>18.5175533294678</v>
       </c>
       <c r="H171" t="n">
         <v>467980</v>
@@ -5357,7 +5357,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>18.6081008911133</v>
+        <v>18.6081027984619</v>
       </c>
       <c r="H172" t="n">
         <v>495370</v>
@@ -5386,7 +5386,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G173" t="n">
-        <v>18.8706970214844</v>
+        <v>18.870698928833</v>
       </c>
       <c r="H173" t="n">
         <v>440037</v>
@@ -5415,7 +5415,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>18.6986522674561</v>
+        <v>18.6986484527588</v>
       </c>
       <c r="H174" t="n">
         <v>355898</v>
@@ -5444,7 +5444,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G175" t="n">
-        <v>18.7620372772217</v>
+        <v>18.762035369873</v>
       </c>
       <c r="H175" t="n">
         <v>290570</v>
@@ -5473,7 +5473,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>19.1061267852783</v>
+        <v>19.106128692627</v>
       </c>
       <c r="H176" t="n">
         <v>842459</v>
@@ -5560,7 +5560,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>19.5588817596436</v>
+        <v>19.5588798522949</v>
       </c>
       <c r="H179" t="n">
         <v>770378</v>
@@ -5589,7 +5589,7 @@
         <v>21.4899997711182</v>
       </c>
       <c r="G180" t="n">
-        <v>19.4592761993408</v>
+        <v>19.4592742919922</v>
       </c>
       <c r="H180" t="n">
         <v>700088</v>
@@ -5618,7 +5618,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G181" t="n">
-        <v>19.314395904541</v>
+        <v>19.3143939971924</v>
       </c>
       <c r="H181" t="n">
         <v>672599</v>
@@ -5734,7 +5734,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G185" t="n">
-        <v>18.7710914611816</v>
+        <v>18.771089553833</v>
       </c>
       <c r="H185" t="n">
         <v>702087</v>
@@ -5763,7 +5763,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>19.1604614257812</v>
+        <v>19.160457611084</v>
       </c>
       <c r="H186" t="n">
         <v>685216</v>
@@ -5792,7 +5792,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G187" t="n">
-        <v>19.9391937255859</v>
+        <v>19.9391918182373</v>
       </c>
       <c r="H187" t="n">
         <v>831000</v>
@@ -5966,7 +5966,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>20.4643859863281</v>
+        <v>20.4643840789795</v>
       </c>
       <c r="H193" t="n">
         <v>742714</v>
@@ -6024,7 +6024,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>20.6907577514648</v>
+        <v>20.6907596588135</v>
       </c>
       <c r="H195" t="n">
         <v>495248</v>
@@ -6053,7 +6053,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>20.8446960449219</v>
+        <v>20.8446979522705</v>
       </c>
       <c r="H196" t="n">
         <v>733993</v>
@@ -6111,7 +6111,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G198" t="n">
-        <v>20.4010009765625</v>
+        <v>20.4009990692139</v>
       </c>
       <c r="H198" t="n">
         <v>504761</v>
@@ -6140,7 +6140,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G199" t="n">
-        <v>20.1021823883057</v>
+        <v>20.1021842956543</v>
       </c>
       <c r="H199" t="n">
         <v>693101</v>
@@ -6169,7 +6169,7 @@
         <v>22.6700000762939</v>
       </c>
       <c r="G200" t="n">
-        <v>20.5277709960938</v>
+        <v>20.5277690887451</v>
       </c>
       <c r="H200" t="n">
         <v>729967</v>
@@ -6372,7 +6372,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>20.3285598754883</v>
+        <v>20.3285579681396</v>
       </c>
       <c r="H207" t="n">
         <v>362070</v>
@@ -6430,7 +6430,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G209" t="n">
-        <v>20.0387954711914</v>
+        <v>20.03879737854</v>
       </c>
       <c r="H209" t="n">
         <v>380492</v>
@@ -6459,7 +6459,7 @@
         <v>22.25</v>
       </c>
       <c r="G210" t="n">
-        <v>20.1474590301514</v>
+        <v>20.1474609375</v>
       </c>
       <c r="H210" t="n">
         <v>323432</v>
@@ -6517,7 +6517,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G212" t="n">
-        <v>20.500602722168</v>
+        <v>20.5006046295166</v>
       </c>
       <c r="H212" t="n">
         <v>513406</v>
@@ -6604,7 +6604,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G215" t="n">
-        <v>20.0387954711914</v>
+        <v>20.03879737854</v>
       </c>
       <c r="H215" t="n">
         <v>225022</v>
@@ -6633,7 +6633,7 @@
         <v>21.5900001525879</v>
       </c>
       <c r="G216" t="n">
-        <v>19.549825668335</v>
+        <v>19.5498237609863</v>
       </c>
       <c r="H216" t="n">
         <v>443300</v>
@@ -6662,7 +6662,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G217" t="n">
-        <v>19.4139995574951</v>
+        <v>19.4140014648438</v>
       </c>
       <c r="H217" t="n">
         <v>328652</v>
@@ -6836,7 +6836,7 @@
         <v>21.9899997711182</v>
       </c>
       <c r="G223" t="n">
-        <v>19.9120254516602</v>
+        <v>19.9120273590088</v>
       </c>
       <c r="H223" t="n">
         <v>433755</v>
@@ -6865,7 +6865,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G224" t="n">
-        <v>19.7490386962891</v>
+        <v>19.7490367889404</v>
       </c>
       <c r="H224" t="n">
         <v>454641</v>
@@ -6894,7 +6894,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.4722728729248</v>
+        <v>18.4722747802734</v>
       </c>
       <c r="H225" t="n">
         <v>3206760</v>
@@ -6981,7 +6981,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G228" t="n">
-        <v>18.3273963928223</v>
+        <v>18.3273944854736</v>
       </c>
       <c r="H228" t="n">
         <v>773547</v>
@@ -7097,7 +7097,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G232" t="n">
-        <v>17.8565330505371</v>
+        <v>17.8565349578857</v>
       </c>
       <c r="H232" t="n">
         <v>279823</v>
@@ -7271,7 +7271,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>18.716760635376</v>
+        <v>18.7167625427246</v>
       </c>
       <c r="H238" t="n">
         <v>591668</v>
@@ -7300,7 +7300,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G239" t="n">
-        <v>18.8706970214844</v>
+        <v>18.870698928833</v>
       </c>
       <c r="H239" t="n">
         <v>825902</v>
@@ -7358,7 +7358,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>19.2872276306152</v>
+        <v>19.2872295379639</v>
       </c>
       <c r="H241" t="n">
         <v>673068</v>
@@ -7387,7 +7387,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G242" t="n">
-        <v>19.3958930969238</v>
+        <v>19.3958911895752</v>
       </c>
       <c r="H242" t="n">
         <v>455970</v>
@@ -7416,7 +7416,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>19.377779006958</v>
+        <v>19.3777809143066</v>
       </c>
       <c r="H243" t="n">
         <v>365522</v>
@@ -7503,7 +7503,7 @@
         <v>21.2700004577637</v>
       </c>
       <c r="G246" t="n">
-        <v>19.2600650787354</v>
+        <v>19.260066986084</v>
       </c>
       <c r="H246" t="n">
         <v>348399</v>
@@ -7677,7 +7677,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>20.2380084991455</v>
+        <v>20.2380065917969</v>
       </c>
       <c r="H252" t="n">
         <v>230612</v>
@@ -7706,7 +7706,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G253" t="n">
-        <v>20.1293468475342</v>
+        <v>20.1293487548828</v>
       </c>
       <c r="H253" t="n">
         <v>311609</v>
@@ -7793,7 +7793,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>20.1565113067627</v>
+        <v>20.1565132141113</v>
       </c>
       <c r="H256" t="n">
         <v>178380</v>
@@ -7851,7 +7851,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G258" t="n">
-        <v>20.8084735870361</v>
+        <v>20.8084774017334</v>
       </c>
       <c r="H258" t="n">
         <v>291448</v>
@@ -7996,7 +7996,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G263" t="n">
-        <v>22.0580711364746</v>
+        <v>22.0580730438232</v>
       </c>
       <c r="H263" t="n">
         <v>1362031</v>
@@ -8054,7 +8054,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G265" t="n">
-        <v>22.2935028076172</v>
+        <v>22.2935047149658</v>
       </c>
       <c r="H265" t="n">
         <v>1130923</v>
@@ -8083,7 +8083,7 @@
         <v>24.6299991607666</v>
       </c>
       <c r="G266" t="n">
-        <v>22.3025550842285</v>
+        <v>22.3025569915771</v>
       </c>
       <c r="H266" t="n">
         <v>604896</v>
@@ -8112,7 +8112,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>22.3206653594971</v>
+        <v>22.3206672668457</v>
       </c>
       <c r="H267" t="n">
         <v>414459</v>
@@ -8170,7 +8170,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G269" t="n">
-        <v>22.2391719818115</v>
+        <v>22.2391700744629</v>
       </c>
       <c r="H269" t="n">
         <v>512480</v>
@@ -8199,7 +8199,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G270" t="n">
-        <v>22.8186988830566</v>
+        <v>22.8186950683594</v>
       </c>
       <c r="H270" t="n">
         <v>1130838</v>
@@ -8228,7 +8228,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G271" t="n">
-        <v>23.0722351074219</v>
+        <v>23.0722370147705</v>
       </c>
       <c r="H271" t="n">
         <v>906513</v>
@@ -8257,7 +8257,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G272" t="n">
-        <v>22.8911361694336</v>
+        <v>22.891134262085</v>
       </c>
       <c r="H272" t="n">
         <v>650968</v>
@@ -8286,7 +8286,7 @@
         <v>25.5699996948242</v>
       </c>
       <c r="G273" t="n">
-        <v>23.1537284851074</v>
+        <v>23.1537322998047</v>
       </c>
       <c r="H273" t="n">
         <v>1005467</v>
@@ -8344,7 +8344,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>22.5923175811768</v>
+        <v>22.5923156738281</v>
       </c>
       <c r="H275" t="n">
         <v>775402</v>
@@ -8460,7 +8460,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G279" t="n">
-        <v>22.1395645141602</v>
+        <v>22.1395664215088</v>
       </c>
       <c r="H279" t="n">
         <v>498087</v>
@@ -8576,7 +8576,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G283" t="n">
-        <v>23.6427021026611</v>
+        <v>23.6427040100098</v>
       </c>
       <c r="H283" t="n">
         <v>1064235</v>
@@ -8605,7 +8605,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G284" t="n">
-        <v>23.6879749298096</v>
+        <v>23.6879787445068</v>
       </c>
       <c r="H284" t="n">
         <v>648062</v>
@@ -8779,7 +8779,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>23.6879749298096</v>
+        <v>23.6879787445068</v>
       </c>
       <c r="H290" t="n">
         <v>721884</v>
@@ -8808,7 +8808,7 @@
         <v>26.3099994659424</v>
       </c>
       <c r="G291" t="n">
-        <v>23.8238048553467</v>
+        <v>23.823802947998</v>
       </c>
       <c r="H291" t="n">
         <v>504205</v>
@@ -8895,7 +8895,7 @@
         <v>26.5200004577637</v>
       </c>
       <c r="G294" t="n">
-        <v>24.0139579772949</v>
+        <v>24.0139617919922</v>
       </c>
       <c r="H294" t="n">
         <v>741091</v>
@@ -8924,7 +8924,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G295" t="n">
-        <v>24.2856121063232</v>
+        <v>24.2856101989746</v>
       </c>
       <c r="H295" t="n">
         <v>633832</v>
@@ -8953,7 +8953,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>24.0682888031006</v>
+        <v>24.068286895752</v>
       </c>
       <c r="H296" t="n">
         <v>653226</v>
@@ -8982,7 +8982,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>23.9777374267578</v>
+        <v>23.9777355194092</v>
       </c>
       <c r="H297" t="n">
         <v>812325</v>
@@ -9040,7 +9040,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G299" t="n">
-        <v>24.430492401123</v>
+        <v>24.4304904937744</v>
       </c>
       <c r="H299" t="n">
         <v>1219756</v>
@@ -9069,7 +9069,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G300" t="n">
-        <v>24.6115951538086</v>
+        <v>24.61159324646</v>
       </c>
       <c r="H300" t="n">
         <v>640558</v>
@@ -9098,7 +9098,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>24.7655277252197</v>
+        <v>24.7655258178711</v>
       </c>
       <c r="H301" t="n">
         <v>889832</v>
@@ -9156,7 +9156,7 @@
         <v>28.0400009155273</v>
       </c>
       <c r="G303" t="n">
-        <v>25.3903274536133</v>
+        <v>25.3903255462646</v>
       </c>
       <c r="H303" t="n">
         <v>911254</v>
@@ -9214,7 +9214,7 @@
         <v>28.2900009155273</v>
       </c>
       <c r="G305" t="n">
-        <v>25.6167030334473</v>
+        <v>25.6167011260986</v>
       </c>
       <c r="H305" t="n">
         <v>800161</v>
@@ -9243,7 +9243,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>25.6710319519043</v>
+        <v>25.6710300445557</v>
       </c>
       <c r="H306" t="n">
         <v>500694</v>
@@ -9272,7 +9272,7 @@
         <v>28.3299999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>25.6529216766357</v>
+        <v>25.6529197692871</v>
       </c>
       <c r="H307" t="n">
         <v>363150</v>
@@ -9301,7 +9301,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>25.7615833282471</v>
+        <v>25.7615814208984</v>
       </c>
       <c r="H308" t="n">
         <v>601915</v>
@@ -9359,7 +9359,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G310" t="n">
-        <v>24.9556827545166</v>
+        <v>24.955680847168</v>
       </c>
       <c r="H310" t="n">
         <v>2238630</v>
@@ -9417,7 +9417,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>25.0643444061279</v>
+        <v>25.0643424987793</v>
       </c>
       <c r="H312" t="n">
         <v>650689</v>
@@ -9446,7 +9446,7 @@
         <v>27.3899993896484</v>
       </c>
       <c r="G313" t="n">
-        <v>24.8017482757568</v>
+        <v>24.8017463684082</v>
       </c>
       <c r="H313" t="n">
         <v>332263</v>
@@ -9475,7 +9475,7 @@
         <v>27.1900005340576</v>
       </c>
       <c r="G314" t="n">
-        <v>24.6206455230713</v>
+        <v>24.6206474304199</v>
       </c>
       <c r="H314" t="n">
         <v>412801</v>
@@ -9533,7 +9533,7 @@
         <v>28.0200004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>25.3722133636475</v>
+        <v>25.3722152709961</v>
       </c>
       <c r="H316" t="n">
         <v>452765</v>
@@ -9562,7 +9562,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>25.62575340271</v>
+        <v>25.6257514953613</v>
       </c>
       <c r="H317" t="n">
         <v>349361</v>
@@ -9591,7 +9591,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G318" t="n">
-        <v>25.2273349761963</v>
+        <v>25.2273330688477</v>
       </c>
       <c r="H318" t="n">
         <v>385409</v>
@@ -9620,7 +9620,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>25.173002243042</v>
+        <v>25.1730041503906</v>
       </c>
       <c r="H319" t="n">
         <v>545914</v>
@@ -9649,7 +9649,7 @@
         <v>27.7900009155273</v>
       </c>
       <c r="G320" t="n">
-        <v>25.163948059082</v>
+        <v>25.1639499664307</v>
       </c>
       <c r="H320" t="n">
         <v>290259</v>
@@ -9678,7 +9678,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>25.3993759155273</v>
+        <v>25.3993797302246</v>
       </c>
       <c r="H321" t="n">
         <v>203615</v>
@@ -9794,7 +9794,7 @@
         <v>27.75</v>
       </c>
       <c r="G325" t="n">
-        <v>25.1277275085449</v>
+        <v>25.1277294158936</v>
       </c>
       <c r="H325" t="n">
         <v>265673</v>
@@ -9823,7 +9823,7 @@
         <v>28.4300003051758</v>
       </c>
       <c r="G326" t="n">
-        <v>25.7434730529785</v>
+        <v>25.7434711456299</v>
       </c>
       <c r="H326" t="n">
         <v>405081</v>
@@ -9852,7 +9852,7 @@
         <v>28.2099990844727</v>
       </c>
       <c r="G327" t="n">
-        <v>25.544261932373</v>
+        <v>25.5442600250244</v>
       </c>
       <c r="H327" t="n">
         <v>365212</v>
@@ -9881,7 +9881,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G328" t="n">
-        <v>25.4808731079102</v>
+        <v>25.4808750152588</v>
       </c>
       <c r="H328" t="n">
         <v>240731</v>
@@ -9968,7 +9968,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>25.0824546813965</v>
+        <v>25.0824527740479</v>
       </c>
       <c r="H331" t="n">
         <v>429583</v>
@@ -10055,7 +10055,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>24.7655277252197</v>
+        <v>24.7655258178711</v>
       </c>
       <c r="H334" t="n">
         <v>653524</v>
@@ -10084,7 +10084,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>24.2674980163574</v>
+        <v>24.2674999237061</v>
       </c>
       <c r="H335" t="n">
         <v>589692</v>
@@ -10142,7 +10142,7 @@
         <v>28.1900005340576</v>
       </c>
       <c r="G337" t="n">
-        <v>25.5261497497559</v>
+        <v>25.5261516571045</v>
       </c>
       <c r="H337" t="n">
         <v>379396</v>
@@ -10200,7 +10200,7 @@
         <v>28.9200000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>26.1871662139893</v>
+        <v>26.1871700286865</v>
       </c>
       <c r="H339" t="n">
         <v>548992</v>
@@ -10258,7 +10258,7 @@
         <v>29.25</v>
       </c>
       <c r="G341" t="n">
-        <v>26.4859828948975</v>
+        <v>26.4859848022461</v>
       </c>
       <c r="H341" t="n">
         <v>324279</v>
@@ -10287,7 +10287,7 @@
         <v>29.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>26.3229942321777</v>
+        <v>26.3229923248291</v>
       </c>
       <c r="H342" t="n">
         <v>296838</v>
@@ -10316,7 +10316,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G343" t="n">
-        <v>26.6761417388916</v>
+        <v>26.676139831543</v>
       </c>
       <c r="H343" t="n">
         <v>498694</v>
@@ -10345,7 +10345,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>26.893461227417</v>
+        <v>26.8934631347656</v>
       </c>
       <c r="H344" t="n">
         <v>349802</v>
@@ -10374,7 +10374,7 @@
         <v>29</v>
       </c>
       <c r="G345" t="n">
-        <v>26.2596054077148</v>
+        <v>26.2596092224121</v>
       </c>
       <c r="H345" t="n">
         <v>806664</v>
@@ -10432,7 +10432,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G347" t="n">
-        <v>26.9115676879883</v>
+        <v>26.9115695953369</v>
       </c>
       <c r="H347" t="n">
         <v>494059</v>
@@ -10519,7 +10519,7 @@
         <v>29.3700008392334</v>
       </c>
       <c r="G350" t="n">
-        <v>26.5946464538574</v>
+        <v>26.5946445465088</v>
       </c>
       <c r="H350" t="n">
         <v>150195</v>
@@ -10548,7 +10548,7 @@
         <v>29</v>
       </c>
       <c r="G351" t="n">
-        <v>26.2596054077148</v>
+        <v>26.2596092224121</v>
       </c>
       <c r="H351" t="n">
         <v>536086</v>
@@ -10606,7 +10606,7 @@
         <v>27.9699993133545</v>
       </c>
       <c r="G353" t="n">
-        <v>25.3269386291504</v>
+        <v>25.326940536499</v>
       </c>
       <c r="H353" t="n">
         <v>304075</v>
@@ -10664,7 +10664,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G355" t="n">
-        <v>25.8984432220459</v>
+        <v>25.8984451293945</v>
       </c>
       <c r="H355" t="n">
         <v>233836</v>
@@ -10722,7 +10722,7 @@
         <v>26.8500003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>24.7112007141113</v>
+        <v>24.71120262146</v>
       </c>
       <c r="H357" t="n">
         <v>1752974</v>
@@ -10751,7 +10751,7 @@
         <v>25.6599998474121</v>
       </c>
       <c r="G358" t="n">
-        <v>23.6159934997559</v>
+        <v>23.6159954071045</v>
       </c>
       <c r="H358" t="n">
         <v>2202691</v>
@@ -10809,7 +10809,7 @@
         <v>25.1299991607666</v>
       </c>
       <c r="G360" t="n">
-        <v>23.1282119750977</v>
+        <v>23.1282138824463</v>
       </c>
       <c r="H360" t="n">
         <v>474720</v>
@@ -10838,7 +10838,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>22.9625511169434</v>
+        <v>22.9625492095947</v>
       </c>
       <c r="H361" t="n">
         <v>858119</v>
@@ -10867,7 +10867,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>22.8705177307129</v>
+        <v>22.8705158233643</v>
       </c>
       <c r="H362" t="n">
         <v>814408</v>
@@ -10925,7 +10925,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G364" t="n">
-        <v>23.2662658691406</v>
+        <v>23.266263961792</v>
       </c>
       <c r="H364" t="n">
         <v>816109</v>
@@ -10954,7 +10954,7 @@
         <v>25.25</v>
       </c>
       <c r="G365" t="n">
-        <v>23.238655090332</v>
+        <v>23.2386531829834</v>
       </c>
       <c r="H365" t="n">
         <v>396002</v>
@@ -11012,7 +11012,7 @@
         <v>24.8700008392334</v>
       </c>
       <c r="G367" t="n">
-        <v>22.8889236450195</v>
+        <v>22.8889255523682</v>
       </c>
       <c r="H367" t="n">
         <v>383043</v>
@@ -11041,7 +11041,7 @@
         <v>24</v>
       </c>
       <c r="G368" t="n">
-        <v>22.0882263183594</v>
+        <v>22.0882244110107</v>
       </c>
       <c r="H368" t="n">
         <v>1374366</v>
@@ -11070,7 +11070,7 @@
         <v>24.25</v>
       </c>
       <c r="G369" t="n">
-        <v>22.3183116912842</v>
+        <v>22.3183097839355</v>
       </c>
       <c r="H369" t="n">
         <v>652180</v>
@@ -11157,7 +11157,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>22.3643283843994</v>
+        <v>22.3643264770508</v>
       </c>
       <c r="H372" t="n">
         <v>603189</v>
@@ -11186,7 +11186,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G373" t="n">
-        <v>22.7416667938232</v>
+        <v>22.7416687011719</v>
       </c>
       <c r="H373" t="n">
         <v>827087</v>
@@ -11215,7 +11215,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G374" t="n">
-        <v>22.9533500671387</v>
+        <v>22.95334815979</v>
       </c>
       <c r="H374" t="n">
         <v>1434500</v>
@@ -11244,7 +11244,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G375" t="n">
-        <v>22.8797225952148</v>
+        <v>22.8797206878662</v>
       </c>
       <c r="H375" t="n">
         <v>368128</v>
@@ -11389,7 +11389,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G380" t="n">
-        <v>23.0269756317139</v>
+        <v>23.0269737243652</v>
       </c>
       <c r="H380" t="n">
         <v>525690</v>
@@ -11418,7 +11418,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G381" t="n">
-        <v>22.6036186218262</v>
+        <v>22.6036167144775</v>
       </c>
       <c r="H381" t="n">
         <v>369901</v>
@@ -11447,7 +11447,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>22.2538871765137</v>
+        <v>22.2538890838623</v>
       </c>
       <c r="H382" t="n">
         <v>540961</v>
@@ -11476,7 +11476,7 @@
         <v>23.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>21.545223236084</v>
+        <v>21.5452251434326</v>
       </c>
       <c r="H383" t="n">
         <v>915042</v>
@@ -11505,7 +11505,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>21.4900035858154</v>
+        <v>21.4900016784668</v>
       </c>
       <c r="H384" t="n">
         <v>361338</v>
@@ -11650,7 +11650,7 @@
         <v>23</v>
       </c>
       <c r="G389" t="n">
-        <v>21.1678829193115</v>
+        <v>21.1678848266602</v>
       </c>
       <c r="H389" t="n">
         <v>501698</v>
@@ -11679,7 +11679,7 @@
         <v>23</v>
       </c>
       <c r="G390" t="n">
-        <v>21.1678829193115</v>
+        <v>21.1678848266602</v>
       </c>
       <c r="H390" t="n">
         <v>281095</v>
@@ -11795,7 +11795,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G394" t="n">
-        <v>21.5084095001221</v>
+        <v>21.5084075927734</v>
       </c>
       <c r="H394" t="n">
         <v>401727</v>
@@ -11824,7 +11824,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G395" t="n">
-        <v>21.9133605957031</v>
+        <v>21.9133586883545</v>
       </c>
       <c r="H395" t="n">
         <v>698768</v>
@@ -11998,7 +11998,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G401" t="n">
-        <v>22.410343170166</v>
+        <v>22.4103450775146</v>
       </c>
       <c r="H401" t="n">
         <v>372937</v>
@@ -12114,7 +12114,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G405" t="n">
-        <v>22.5576019287109</v>
+        <v>22.5575981140137</v>
       </c>
       <c r="H405" t="n">
         <v>352700</v>
@@ -12143,7 +12143,7 @@
         <v>24</v>
       </c>
       <c r="G406" t="n">
-        <v>22.0882263183594</v>
+        <v>22.0882244110107</v>
       </c>
       <c r="H406" t="n">
         <v>1576783</v>
@@ -12172,7 +12172,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G407" t="n">
-        <v>21.4255809783936</v>
+        <v>21.4255790710449</v>
       </c>
       <c r="H407" t="n">
         <v>844820</v>
@@ -12230,7 +12230,7 @@
         <v>24</v>
       </c>
       <c r="G409" t="n">
-        <v>22.0882263183594</v>
+        <v>22.0882244110107</v>
       </c>
       <c r="H409" t="n">
         <v>517420</v>
@@ -12346,7 +12346,7 @@
         <v>24.25</v>
       </c>
       <c r="G413" t="n">
-        <v>22.3183116912842</v>
+        <v>22.3183097839355</v>
       </c>
       <c r="H413" t="n">
         <v>259593</v>
@@ -12491,7 +12491,7 @@
         <v>24.0300006866455</v>
       </c>
       <c r="G418" t="n">
-        <v>22.115837097168</v>
+        <v>22.1158351898193</v>
       </c>
       <c r="H418" t="n">
         <v>245071</v>
@@ -12520,7 +12520,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>21.7661037445068</v>
+        <v>21.7661056518555</v>
       </c>
       <c r="H419" t="n">
         <v>234785</v>
@@ -12607,7 +12607,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G422" t="n">
-        <v>21.9133605957031</v>
+        <v>21.9133586883545</v>
       </c>
       <c r="H422" t="n">
         <v>171029</v>
@@ -12636,7 +12636,7 @@
         <v>24</v>
       </c>
       <c r="G423" t="n">
-        <v>22.0882263183594</v>
+        <v>22.0882244110107</v>
       </c>
       <c r="H423" t="n">
         <v>206329</v>
@@ -12665,7 +12665,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>21.9961910247803</v>
+        <v>21.9961929321289</v>
       </c>
       <c r="H424" t="n">
         <v>138330</v>
@@ -12694,7 +12694,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G425" t="n">
-        <v>21.701681137085</v>
+        <v>21.7016830444336</v>
       </c>
       <c r="H425" t="n">
         <v>416770</v>
@@ -12839,7 +12839,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G430" t="n">
-        <v>21.9133605957031</v>
+        <v>21.9133586883545</v>
       </c>
       <c r="H430" t="n">
         <v>185988</v>
@@ -12868,7 +12868,7 @@
         <v>23.7700004577637</v>
       </c>
       <c r="G431" t="n">
-        <v>21.8765468597412</v>
+        <v>21.8765487670898</v>
       </c>
       <c r="H431" t="n">
         <v>297166</v>
@@ -12955,7 +12955,7 @@
         <v>23.9300003051758</v>
       </c>
       <c r="G434" t="n">
-        <v>22.0238018035889</v>
+        <v>22.0238037109375</v>
       </c>
       <c r="H434" t="n">
         <v>408570</v>
@@ -12984,7 +12984,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G435" t="n">
-        <v>21.9961910247803</v>
+        <v>21.9961929321289</v>
       </c>
       <c r="H435" t="n">
         <v>619938</v>
@@ -13013,7 +13013,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>21.9041557312012</v>
+        <v>21.9041576385498</v>
       </c>
       <c r="H436" t="n">
         <v>1117273</v>
@@ -13129,7 +13129,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G440" t="n">
-        <v>20.9469985961914</v>
+        <v>20.9470024108887</v>
       </c>
       <c r="H440" t="n">
         <v>418634</v>
@@ -13158,7 +13158,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>20.799747467041</v>
+        <v>20.7997455596924</v>
       </c>
       <c r="H441" t="n">
         <v>1083075</v>
@@ -13187,7 +13187,7 @@
         <v>22.9300003051758</v>
       </c>
       <c r="G442" t="n">
-        <v>21.103458404541</v>
+        <v>21.1034622192383</v>
       </c>
       <c r="H442" t="n">
         <v>361840</v>
@@ -13216,7 +13216,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>21.0758476257324</v>
+        <v>21.0758495330811</v>
       </c>
       <c r="H443" t="n">
         <v>297588</v>
@@ -13361,7 +13361,7 @@
         <v>23.75</v>
       </c>
       <c r="G448" t="n">
-        <v>21.8581371307373</v>
+        <v>21.8581390380859</v>
       </c>
       <c r="H448" t="n">
         <v>541964</v>
@@ -13419,7 +13419,7 @@
         <v>23.5100002288818</v>
       </c>
       <c r="G450" t="n">
-        <v>21.6372566223145</v>
+        <v>21.6372585296631</v>
       </c>
       <c r="H450" t="n">
         <v>1176964</v>
@@ -13448,7 +13448,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G451" t="n">
-        <v>21.2967319488525</v>
+        <v>21.2967300415039</v>
       </c>
       <c r="H451" t="n">
         <v>599089</v>
@@ -13506,7 +13506,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>20.799747467041</v>
+        <v>20.7997455596924</v>
       </c>
       <c r="H453" t="n">
         <v>536977</v>
@@ -13535,7 +13535,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838123321533</v>
       </c>
       <c r="H454" t="n">
         <v>572574</v>
@@ -13680,7 +13680,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G459" t="n">
-        <v>21.1586780548096</v>
+        <v>21.1586799621582</v>
       </c>
       <c r="H459" t="n">
         <v>440417</v>
@@ -13709,7 +13709,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G460" t="n">
-        <v>21.0206317901611</v>
+        <v>21.0206279754639</v>
       </c>
       <c r="H460" t="n">
         <v>386462</v>
@@ -13796,7 +13796,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G463" t="n">
-        <v>20.4500160217285</v>
+        <v>20.4500179290771</v>
       </c>
       <c r="H463" t="n">
         <v>772283</v>
@@ -13883,7 +13883,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G466" t="n">
-        <v>20.0082492828369</v>
+        <v>20.0082511901855</v>
       </c>
       <c r="H466" t="n">
         <v>1396902</v>
@@ -13970,7 +13970,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G469" t="n">
-        <v>20.4868278503418</v>
+        <v>20.4868297576904</v>
       </c>
       <c r="H469" t="n">
         <v>471696</v>
@@ -14028,7 +14028,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G471" t="n">
-        <v>20.8917827606201</v>
+        <v>20.8917808532715</v>
       </c>
       <c r="H471" t="n">
         <v>504871</v>
@@ -14057,7 +14057,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G472" t="n">
-        <v>21.0206317901611</v>
+        <v>21.0206279754639</v>
       </c>
       <c r="H472" t="n">
         <v>601843</v>
@@ -14144,7 +14144,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G475" t="n">
-        <v>20.9285926818848</v>
+        <v>20.9285945892334</v>
       </c>
       <c r="H475" t="n">
         <v>884159</v>
@@ -14173,7 +14173,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G476" t="n">
-        <v>20.9469985961914</v>
+        <v>20.9470024108887</v>
       </c>
       <c r="H476" t="n">
         <v>584780</v>
@@ -14289,7 +14289,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G480" t="n">
-        <v>20.0910835266113</v>
+        <v>20.0910816192627</v>
       </c>
       <c r="H480" t="n">
         <v>280042</v>
@@ -14347,7 +14347,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>19.695333480835</v>
+        <v>19.6953353881836</v>
       </c>
       <c r="H482" t="n">
         <v>1022782</v>
@@ -14376,7 +14376,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G483" t="n">
-        <v>19.8057746887207</v>
+        <v>19.8057765960693</v>
       </c>
       <c r="H483" t="n">
         <v>546959</v>
@@ -14405,7 +14405,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G484" t="n">
-        <v>19.7321472167969</v>
+        <v>19.7321491241455</v>
       </c>
       <c r="H484" t="n">
         <v>421554</v>
@@ -14434,7 +14434,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G485" t="n">
-        <v>20.1831169128418</v>
+        <v>20.1831150054932</v>
       </c>
       <c r="H485" t="n">
         <v>533863</v>
@@ -14521,7 +14521,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>20.4316082000732</v>
+        <v>20.4316101074219</v>
       </c>
       <c r="H488" t="n">
         <v>368098</v>
@@ -14550,7 +14550,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G489" t="n">
-        <v>20.5696601867676</v>
+        <v>20.5696582794189</v>
       </c>
       <c r="H489" t="n">
         <v>438572</v>
@@ -14579,7 +14579,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>20.6616954803467</v>
+        <v>20.661693572998</v>
       </c>
       <c r="H490" t="n">
         <v>354523</v>
@@ -14608,7 +14608,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G491" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838123321533</v>
       </c>
       <c r="H491" t="n">
         <v>580090</v>
@@ -14811,7 +14811,7 @@
         <v>23.3099994659424</v>
       </c>
       <c r="G498" t="n">
-        <v>21.4531898498535</v>
+        <v>21.4531879425049</v>
       </c>
       <c r="H498" t="n">
         <v>526941</v>
@@ -14869,7 +14869,7 @@
         <v>22.6100006103516</v>
       </c>
       <c r="G500" t="n">
-        <v>20.8089504241943</v>
+        <v>20.8089485168457</v>
       </c>
       <c r="H500" t="n">
         <v>1494988</v>
@@ -15014,7 +15014,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G505" t="n">
-        <v>19.8609962463379</v>
+        <v>19.8609943389893</v>
       </c>
       <c r="H505" t="n">
         <v>611462</v>
@@ -15072,7 +15072,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G507" t="n">
-        <v>20.2199287414551</v>
+        <v>20.2199306488037</v>
       </c>
       <c r="H507" t="n">
         <v>372050</v>
@@ -15130,7 +15130,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>20.229133605957</v>
+        <v>20.2291355133057</v>
       </c>
       <c r="H509" t="n">
         <v>191733</v>
@@ -15217,7 +15217,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G512" t="n">
-        <v>20.2199287414551</v>
+        <v>20.2199306488037</v>
       </c>
       <c r="H512" t="n">
         <v>214152</v>
@@ -15246,7 +15246,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>20.5236415863037</v>
+        <v>20.523645401001</v>
       </c>
       <c r="H513" t="n">
         <v>314606</v>
@@ -15362,7 +15362,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G517" t="n">
-        <v>20.2659492492676</v>
+        <v>20.2659473419189</v>
       </c>
       <c r="H517" t="n">
         <v>876136</v>
@@ -15449,7 +15449,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G520" t="n">
-        <v>20.4868278503418</v>
+        <v>20.4868297576904</v>
       </c>
       <c r="H520" t="n">
         <v>710973</v>
@@ -15478,7 +15478,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>20.4316082000732</v>
+        <v>20.4316101074219</v>
       </c>
       <c r="H521" t="n">
         <v>164255</v>
@@ -15507,7 +15507,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G522" t="n">
-        <v>20.4500160217285</v>
+        <v>20.4500179290771</v>
       </c>
       <c r="H522" t="n">
         <v>256718</v>
@@ -15565,7 +15565,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G524" t="n">
-        <v>20.1739139556885</v>
+        <v>20.1739120483398</v>
       </c>
       <c r="H524" t="n">
         <v>499386</v>
@@ -15594,7 +15594,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G525" t="n">
-        <v>20.9469985961914</v>
+        <v>20.9470024108887</v>
       </c>
       <c r="H525" t="n">
         <v>908844</v>
@@ -15652,7 +15652,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G527" t="n">
-        <v>21.2967319488525</v>
+        <v>21.2967300415039</v>
       </c>
       <c r="H527" t="n">
         <v>604201</v>
@@ -15681,7 +15681,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>21.259916305542</v>
+        <v>21.2599182128906</v>
       </c>
       <c r="H528" t="n">
         <v>954306</v>
@@ -15710,7 +15710,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>21.259916305542</v>
+        <v>21.2599182128906</v>
       </c>
       <c r="H529" t="n">
         <v>726158</v>
@@ -15768,7 +15768,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G531" t="n">
-        <v>21.5176124572754</v>
+        <v>21.5176105499268</v>
       </c>
       <c r="H531" t="n">
         <v>399997</v>
@@ -15884,7 +15884,7 @@
         <v>22.7299995422363</v>
       </c>
       <c r="G535" t="n">
-        <v>20.9193897247314</v>
+        <v>20.9193916320801</v>
       </c>
       <c r="H535" t="n">
         <v>452147</v>
@@ -15942,7 +15942,7 @@
         <v>22.1100006103516</v>
       </c>
       <c r="G537" t="n">
-        <v>20.3487796783447</v>
+        <v>20.3487777709961</v>
       </c>
       <c r="H537" t="n">
         <v>482372</v>
@@ -16058,7 +16058,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G541" t="n">
-        <v>20.0082492828369</v>
+        <v>20.0082511901855</v>
       </c>
       <c r="H541" t="n">
         <v>190751</v>
@@ -16087,7 +16087,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G542" t="n">
-        <v>19.9162178039551</v>
+        <v>19.9162158966064</v>
       </c>
       <c r="H542" t="n">
         <v>415655</v>
@@ -16232,7 +16232,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G547" t="n">
-        <v>20.4500160217285</v>
+        <v>20.4500179290771</v>
       </c>
       <c r="H547" t="n">
         <v>182552</v>
@@ -16261,7 +16261,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G548" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838123321533</v>
       </c>
       <c r="H548" t="n">
         <v>361715</v>
@@ -16319,7 +16319,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G550" t="n">
-        <v>20.9285926818848</v>
+        <v>20.9285945892334</v>
       </c>
       <c r="H550" t="n">
         <v>308603</v>
@@ -16377,7 +16377,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G552" t="n">
-        <v>20.8365573883057</v>
+        <v>20.8365592956543</v>
       </c>
       <c r="H552" t="n">
         <v>218015</v>
@@ -16406,7 +16406,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G553" t="n">
-        <v>21.2967319488525</v>
+        <v>21.2967300415039</v>
       </c>
       <c r="H553" t="n">
         <v>2496511</v>
@@ -16435,7 +16435,7 @@
         <v>23.4699993133545</v>
       </c>
       <c r="G554" t="n">
-        <v>21.6004447937012</v>
+        <v>21.6004428863525</v>
       </c>
       <c r="H554" t="n">
         <v>754894</v>
@@ -16464,7 +16464,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G555" t="n">
-        <v>20.6248817443848</v>
+        <v>20.6248798370361</v>
       </c>
       <c r="H555" t="n">
         <v>551415</v>
@@ -16522,7 +16522,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G557" t="n">
-        <v>20.0910835266113</v>
+        <v>20.0910816192627</v>
       </c>
       <c r="H557" t="n">
         <v>895894</v>
@@ -16609,7 +16609,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>19.6493186950684</v>
+        <v>19.649320602417</v>
       </c>
       <c r="H560" t="n">
         <v>1050485</v>
@@ -16638,7 +16638,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G561" t="n">
-        <v>19.999044418335</v>
+        <v>19.9990482330322</v>
       </c>
       <c r="H561" t="n">
         <v>740982</v>
@@ -16696,7 +16696,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G563" t="n">
-        <v>19.8609962463379</v>
+        <v>19.8609943389893</v>
       </c>
       <c r="H563" t="n">
         <v>558470</v>
@@ -16725,7 +16725,7 @@
         <v>21.8700008392334</v>
       </c>
       <c r="G564" t="n">
-        <v>20.1278953552246</v>
+        <v>20.1278972625732</v>
       </c>
       <c r="H564" t="n">
         <v>432785</v>
@@ -16783,7 +16783,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G566" t="n">
-        <v>20.5696601867676</v>
+        <v>20.5696582794189</v>
       </c>
       <c r="H566" t="n">
         <v>548117</v>
@@ -16812,7 +16812,7 @@
         <v>22.6800003051758</v>
       </c>
       <c r="G567" t="n">
-        <v>20.8733730316162</v>
+        <v>20.8733749389648</v>
       </c>
       <c r="H567" t="n">
         <v>588294</v>
@@ -16841,7 +16841,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G568" t="n">
-        <v>20.5236415863037</v>
+        <v>20.523645401001</v>
       </c>
       <c r="H568" t="n">
         <v>305669</v>
@@ -16870,7 +16870,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G569" t="n">
-        <v>20.3763904571533</v>
+        <v>20.3763885498047</v>
       </c>
       <c r="H569" t="n">
         <v>262537</v>
@@ -16957,7 +16957,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G572" t="n">
-        <v>20.3027629852295</v>
+        <v>20.3027610778809</v>
       </c>
       <c r="H572" t="n">
         <v>439174</v>
@@ -17073,7 +17073,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>20.6156768798828</v>
+        <v>20.6156749725342</v>
       </c>
       <c r="H576" t="n">
         <v>263654</v>
@@ -17305,7 +17305,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>21.2783241271973</v>
+        <v>21.2783260345459</v>
       </c>
       <c r="H584" t="n">
         <v>190641</v>
@@ -17392,7 +17392,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>21.5360202789307</v>
+        <v>21.536018371582</v>
       </c>
       <c r="H587" t="n">
         <v>858748</v>
@@ -17421,7 +17421,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>21.5360202789307</v>
+        <v>21.536018371582</v>
       </c>
       <c r="H588" t="n">
         <v>693444</v>
@@ -17450,7 +17450,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G589" t="n">
-        <v>21.7937145233154</v>
+        <v>21.7937183380127</v>
       </c>
       <c r="H589" t="n">
         <v>611824</v>
@@ -17508,7 +17508,7 @@
         <v>24.5</v>
       </c>
       <c r="G591" t="n">
-        <v>22.5483989715576</v>
+        <v>22.548397064209</v>
       </c>
       <c r="H591" t="n">
         <v>1072195</v>
@@ -17537,7 +17537,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G592" t="n">
-        <v>22.4195499420166</v>
+        <v>22.4195518493652</v>
       </c>
       <c r="H592" t="n">
         <v>493451</v>
@@ -17624,7 +17624,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G595" t="n">
-        <v>22.8797225952148</v>
+        <v>22.8797206878662</v>
       </c>
       <c r="H595" t="n">
         <v>677550</v>
@@ -17653,7 +17653,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G596" t="n">
-        <v>22.7416667938232</v>
+        <v>22.7416687011719</v>
       </c>
       <c r="H596" t="n">
         <v>747463</v>
@@ -17711,7 +17711,7 @@
         <v>24.5699996948242</v>
       </c>
       <c r="G598" t="n">
-        <v>22.6128177642822</v>
+        <v>22.6128196716309</v>
       </c>
       <c r="H598" t="n">
         <v>293934</v>
@@ -17769,7 +17769,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>22.9165344238281</v>
+        <v>22.9165325164795</v>
       </c>
       <c r="H600" t="n">
         <v>543073</v>
@@ -17798,7 +17798,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G601" t="n">
-        <v>22.6864471435547</v>
+        <v>22.6864490509033</v>
       </c>
       <c r="H601" t="n">
         <v>481261</v>
@@ -17827,7 +17827,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>22.7324657440186</v>
+        <v>22.7324676513672</v>
       </c>
       <c r="H602" t="n">
         <v>336880</v>
@@ -17885,7 +17885,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G604" t="n">
-        <v>22.7692775726318</v>
+        <v>22.7692794799805</v>
       </c>
       <c r="H604" t="n">
         <v>300428</v>
@@ -17943,7 +17943,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G606" t="n">
-        <v>23.2754707336426</v>
+        <v>23.2754669189453</v>
       </c>
       <c r="H606" t="n">
         <v>719915</v>
@@ -17972,7 +17972,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>22.9165344238281</v>
+        <v>22.9165325164795</v>
       </c>
       <c r="H607" t="n">
         <v>378581</v>
@@ -18001,7 +18001,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G608" t="n">
-        <v>22.991304397583</v>
+        <v>22.9913024902344</v>
       </c>
       <c r="H608" t="n">
         <v>259914</v>
@@ -18030,7 +18030,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G609" t="n">
-        <v>23.3090705871582</v>
+        <v>23.3090686798096</v>
       </c>
       <c r="H609" t="n">
         <v>451695</v>
@@ -18088,7 +18088,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G611" t="n">
-        <v>22.9071884155273</v>
+        <v>22.9071865081787</v>
       </c>
       <c r="H611" t="n">
         <v>487106</v>
@@ -18117,7 +18117,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G612" t="n">
-        <v>22.9819564819336</v>
+        <v>22.9819583892822</v>
       </c>
       <c r="H612" t="n">
         <v>524215</v>
@@ -18146,7 +18146,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G613" t="n">
-        <v>22.7296142578125</v>
+        <v>22.7296123504639</v>
       </c>
       <c r="H613" t="n">
         <v>339316</v>
@@ -18175,7 +18175,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G614" t="n">
-        <v>22.355770111084</v>
+        <v>22.3557720184326</v>
       </c>
       <c r="H614" t="n">
         <v>700947</v>
@@ -18233,7 +18233,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G616" t="n">
-        <v>23.07541847229</v>
+        <v>23.0754203796387</v>
       </c>
       <c r="H616" t="n">
         <v>441644</v>
@@ -18407,7 +18407,7 @@
         <v>24.3299999237061</v>
       </c>
       <c r="G622" t="n">
-        <v>22.7389583587646</v>
+        <v>22.7389602661133</v>
       </c>
       <c r="H622" t="n">
         <v>507897</v>
@@ -18436,7 +18436,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G623" t="n">
-        <v>23.1595325469971</v>
+        <v>23.1595306396484</v>
       </c>
       <c r="H623" t="n">
         <v>393598</v>
@@ -18523,7 +18523,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G626" t="n">
-        <v>23.3838367462158</v>
+        <v>23.3838386535645</v>
       </c>
       <c r="H626" t="n">
         <v>354528</v>
@@ -18581,7 +18581,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G628" t="n">
-        <v>23.2623405456543</v>
+        <v>23.2623386383057</v>
       </c>
       <c r="H628" t="n">
         <v>200051</v>
@@ -18610,7 +18610,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G629" t="n">
-        <v>22.9258823394775</v>
+        <v>22.9258804321289</v>
       </c>
       <c r="H629" t="n">
         <v>273653</v>
@@ -18639,7 +18639,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G630" t="n">
-        <v>20.991247177124</v>
+        <v>20.9912452697754</v>
       </c>
       <c r="H630" t="n">
         <v>3551454</v>
@@ -18755,7 +18755,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G634" t="n">
-        <v>19.7388763427734</v>
+        <v>19.7388782501221</v>
       </c>
       <c r="H634" t="n">
         <v>776810</v>
@@ -18784,7 +18784,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G635" t="n">
-        <v>19.5612983703613</v>
+        <v>19.56130027771</v>
       </c>
       <c r="H635" t="n">
         <v>788412</v>
@@ -18813,7 +18813,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G636" t="n">
-        <v>19.3089561462402</v>
+        <v>19.3089542388916</v>
       </c>
       <c r="H636" t="n">
         <v>671130</v>
@@ -18842,7 +18842,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>19.533260345459</v>
+        <v>19.5332622528076</v>
       </c>
       <c r="H637" t="n">
         <v>512477</v>
@@ -18900,7 +18900,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>19.3463401794434</v>
+        <v>19.346342086792</v>
       </c>
       <c r="H639" t="n">
         <v>480213</v>
@@ -18929,7 +18929,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G640" t="n">
-        <v>19.0285758972168</v>
+        <v>19.0285739898682</v>
       </c>
       <c r="H640" t="n">
         <v>403933</v>
@@ -18958,7 +18958,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G641" t="n">
-        <v>18.6266956329346</v>
+        <v>18.6266937255859</v>
       </c>
       <c r="H641" t="n">
         <v>874180</v>
@@ -18987,7 +18987,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G642" t="n">
-        <v>18.383695602417</v>
+        <v>18.3836975097656</v>
       </c>
       <c r="H642" t="n">
         <v>773362</v>
@@ -19103,7 +19103,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G646" t="n">
-        <v>18.383695602417</v>
+        <v>18.3836975097656</v>
       </c>
       <c r="H646" t="n">
         <v>373552</v>
@@ -19132,7 +19132,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G647" t="n">
-        <v>18.603328704834</v>
+        <v>18.6033306121826</v>
       </c>
       <c r="H647" t="n">
         <v>410650</v>
@@ -19161,7 +19161,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G648" t="n">
-        <v>18.6360397338867</v>
+        <v>18.6360416412354</v>
       </c>
       <c r="H648" t="n">
         <v>360124</v>
@@ -19306,7 +19306,7 @@
         <v>19.875</v>
       </c>
       <c r="G653" t="n">
-        <v>18.5752906799316</v>
+        <v>18.5752925872803</v>
       </c>
       <c r="H653" t="n">
         <v>336549</v>
@@ -19335,7 +19335,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G654" t="n">
-        <v>18.3930435180664</v>
+        <v>18.3930416107178</v>
       </c>
       <c r="H654" t="n">
         <v>659845</v>
@@ -19480,7 +19480,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G659" t="n">
-        <v>18.491174697876</v>
+        <v>18.4911766052246</v>
       </c>
       <c r="H659" t="n">
         <v>448603</v>
@@ -19509,7 +19509,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G660" t="n">
-        <v>18.2435073852539</v>
+        <v>18.2435054779053</v>
       </c>
       <c r="H660" t="n">
         <v>1645512</v>
@@ -19538,7 +19538,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>17.8042373657227</v>
+        <v>17.8042392730713</v>
       </c>
       <c r="H661" t="n">
         <v>581210</v>
@@ -19567,7 +19567,7 @@
         <v>19.0149993896484</v>
       </c>
       <c r="G662" t="n">
-        <v>17.7715282440186</v>
+        <v>17.7715263366699</v>
       </c>
       <c r="H662" t="n">
         <v>552026</v>
@@ -19596,7 +19596,7 @@
         <v>19.375</v>
       </c>
       <c r="G663" t="n">
-        <v>18.1079864501953</v>
+        <v>18.1079883575439</v>
       </c>
       <c r="H663" t="n">
         <v>697033</v>
@@ -19799,7 +19799,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G670" t="n">
-        <v>18.491174697876</v>
+        <v>18.4911766052246</v>
       </c>
       <c r="H670" t="n">
         <v>378568</v>
@@ -19973,7 +19973,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>19.4397983551025</v>
+        <v>19.4398002624512</v>
       </c>
       <c r="H676" t="n">
         <v>781937</v>
@@ -20060,7 +20060,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G679" t="n">
-        <v>19.4304542541504</v>
+        <v>19.4304523468018</v>
       </c>
       <c r="H679" t="n">
         <v>207201</v>
@@ -20089,7 +20089,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G680" t="n">
-        <v>19.3650341033936</v>
+        <v>19.3650321960449</v>
       </c>
       <c r="H680" t="n">
         <v>208015</v>
@@ -20118,7 +20118,7 @@
         <v>20.5</v>
       </c>
       <c r="G681" t="n">
-        <v>19.1594200134277</v>
+        <v>19.1594181060791</v>
       </c>
       <c r="H681" t="n">
         <v>262991</v>
@@ -20234,7 +20234,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G685" t="n">
-        <v>18.7388458251953</v>
+        <v>18.7388439178467</v>
       </c>
       <c r="H685" t="n">
         <v>362000</v>
@@ -20263,7 +20263,7 @@
         <v>20.5</v>
       </c>
       <c r="G686" t="n">
-        <v>19.1594200134277</v>
+        <v>19.1594181060791</v>
       </c>
       <c r="H686" t="n">
         <v>375929</v>
@@ -20292,7 +20292,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G687" t="n">
-        <v>19.0566101074219</v>
+        <v>19.0566120147705</v>
       </c>
       <c r="H687" t="n">
         <v>411927</v>
@@ -20524,7 +20524,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G695" t="n">
-        <v>19.7482204437256</v>
+        <v>19.748218536377</v>
       </c>
       <c r="H695" t="n">
         <v>450623</v>
@@ -20611,7 +20611,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>19.7669105529785</v>
+        <v>19.7669124603271</v>
       </c>
       <c r="H698" t="n">
         <v>331792</v>
@@ -20669,7 +20669,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G700" t="n">
-        <v>19.5706462860107</v>
+        <v>19.5706443786621</v>
       </c>
       <c r="H700" t="n">
         <v>276548</v>
@@ -20698,7 +20698,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G701" t="n">
-        <v>19.2809181213379</v>
+        <v>19.2809162139893</v>
       </c>
       <c r="H701" t="n">
         <v>334676</v>
@@ -20785,7 +20785,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G704" t="n">
-        <v>19.0566101074219</v>
+        <v>19.0566120147705</v>
       </c>
       <c r="H704" t="n">
         <v>303150</v>
@@ -20901,7 +20901,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>18.6453876495361</v>
+        <v>18.6453857421875</v>
       </c>
       <c r="H708" t="n">
         <v>698237</v>
@@ -20988,7 +20988,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G711" t="n">
-        <v>17.1546878814697</v>
+        <v>17.1546897888184</v>
       </c>
       <c r="H711" t="n">
         <v>1871086</v>
@@ -21162,7 +21162,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G717" t="n">
-        <v>19.5706462860107</v>
+        <v>19.5706443786621</v>
       </c>
       <c r="H717" t="n">
         <v>1765099</v>
@@ -21191,7 +21191,7 @@
         <v>20.5300006866455</v>
       </c>
       <c r="G718" t="n">
-        <v>19.1874580383301</v>
+        <v>19.1874561309814</v>
       </c>
       <c r="H718" t="n">
         <v>665558</v>
@@ -21307,7 +21307,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G722" t="n">
-        <v>19.645414352417</v>
+        <v>19.6454162597656</v>
       </c>
       <c r="H722" t="n">
         <v>418618</v>
@@ -21336,7 +21336,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G723" t="n">
-        <v>19.4771862030029</v>
+        <v>19.4771842956543</v>
       </c>
       <c r="H723" t="n">
         <v>299258</v>
@@ -21365,7 +21365,7 @@
         <v>20.9099998474121</v>
       </c>
       <c r="G724" t="n">
-        <v>19.5426082611084</v>
+        <v>19.5426063537598</v>
       </c>
       <c r="H724" t="n">
         <v>436766</v>
@@ -21481,7 +21481,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>19.4397983551025</v>
+        <v>19.4398002624512</v>
       </c>
       <c r="H728" t="n">
         <v>482531</v>
@@ -21510,7 +21510,7 @@
         <v>21</v>
       </c>
       <c r="G729" t="n">
-        <v>19.6267204284668</v>
+        <v>19.6267223358154</v>
       </c>
       <c r="H729" t="n">
         <v>286056</v>
@@ -21597,7 +21597,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G732" t="n">
-        <v>19.4397983551025</v>
+        <v>19.4398002624512</v>
       </c>
       <c r="H732" t="n">
         <v>371674</v>
@@ -21626,7 +21626,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G733" t="n">
-        <v>19.7014904022217</v>
+        <v>19.701488494873</v>
       </c>
       <c r="H733" t="n">
         <v>369031</v>
@@ -21655,7 +21655,7 @@
         <v>21</v>
       </c>
       <c r="G734" t="n">
-        <v>19.6267204284668</v>
+        <v>19.6267223358154</v>
       </c>
       <c r="H734" t="n">
         <v>247340</v>
@@ -21771,7 +21771,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G738" t="n">
-        <v>18.603328704834</v>
+        <v>18.6033306121826</v>
       </c>
       <c r="H738" t="n">
         <v>681345</v>
@@ -21887,7 +21887,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G742" t="n">
-        <v>19.3650341033936</v>
+        <v>19.3650321960449</v>
       </c>
       <c r="H742" t="n">
         <v>414130</v>
@@ -21945,7 +21945,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>19.533260345459</v>
+        <v>19.5332622528076</v>
       </c>
       <c r="H744" t="n">
         <v>282711</v>
@@ -22003,7 +22003,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>19.3463401794434</v>
+        <v>19.346342086792</v>
       </c>
       <c r="H746" t="n">
         <v>177553</v>
@@ -22032,7 +22032,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G747" t="n">
-        <v>19.7014904022217</v>
+        <v>19.701488494873</v>
       </c>
       <c r="H747" t="n">
         <v>368527</v>
@@ -22061,7 +22061,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>19.533260345459</v>
+        <v>19.5332622528076</v>
       </c>
       <c r="H748" t="n">
         <v>211502</v>
@@ -22090,7 +22090,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G749" t="n">
-        <v>19.4304542541504</v>
+        <v>19.4304523468018</v>
       </c>
       <c r="H749" t="n">
         <v>241093</v>
@@ -22119,7 +22119,7 @@
         <v>20.5</v>
       </c>
       <c r="G750" t="n">
-        <v>19.1594200134277</v>
+        <v>19.1594181060791</v>
       </c>
       <c r="H750" t="n">
         <v>466560</v>
@@ -22206,7 +22206,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G753" t="n">
-        <v>18.3930435180664</v>
+        <v>18.3930416107178</v>
       </c>
       <c r="H753" t="n">
         <v>452457</v>
@@ -22235,7 +22235,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G754" t="n">
-        <v>17.0472106933594</v>
+        <v>17.0472087860107</v>
       </c>
       <c r="H754" t="n">
         <v>1928028</v>
@@ -22293,7 +22293,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G756" t="n">
-        <v>16.8135585784912</v>
+        <v>16.8135566711426</v>
       </c>
       <c r="H756" t="n">
         <v>831352</v>
@@ -22322,7 +22322,7 @@
         <v>17.7450008392334</v>
       </c>
       <c r="G757" t="n">
-        <v>16.5845794677734</v>
+        <v>16.5845813751221</v>
       </c>
       <c r="H757" t="n">
         <v>666545</v>
@@ -22438,7 +22438,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>16.4957904815674</v>
+        <v>16.495792388916</v>
       </c>
       <c r="H761" t="n">
         <v>1354957</v>
@@ -22554,7 +22554,7 @@
         <v>17.1650009155273</v>
       </c>
       <c r="G765" t="n">
-        <v>16.0425090789795</v>
+        <v>16.0425109863281</v>
       </c>
       <c r="H765" t="n">
         <v>452946</v>
@@ -22612,7 +22612,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>16.4957904815674</v>
+        <v>16.495792388916</v>
       </c>
       <c r="H767" t="n">
         <v>341314</v>
@@ -22641,7 +22641,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>16.5425224304199</v>
+        <v>16.5425205230713</v>
       </c>
       <c r="H768" t="n">
         <v>424881</v>
@@ -22699,7 +22699,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G770" t="n">
-        <v>16.6640224456787</v>
+        <v>16.6640205383301</v>
       </c>
       <c r="H770" t="n">
         <v>368576</v>
@@ -22757,7 +22757,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>16.4957904815674</v>
+        <v>16.495792388916</v>
       </c>
       <c r="H772" t="n">
         <v>357653</v>
@@ -22873,7 +22873,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G776" t="n">
-        <v>16.8135585784912</v>
+        <v>16.8135566711426</v>
       </c>
       <c r="H776" t="n">
         <v>396353</v>
@@ -23163,7 +23163,7 @@
         <v>17.6350002288818</v>
       </c>
       <c r="G786" t="n">
-        <v>16.4817752838135</v>
+        <v>16.4817733764648</v>
       </c>
       <c r="H786" t="n">
         <v>617266</v>
@@ -23192,7 +23192,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G787" t="n">
-        <v>16.4957904815674</v>
+        <v>16.495792388916</v>
       </c>
       <c r="H787" t="n">
         <v>375724</v>
@@ -23424,7 +23424,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>17.1967468261719</v>
+        <v>17.1967449188232</v>
       </c>
       <c r="H795" t="n">
         <v>665839</v>
@@ -23482,7 +23482,7 @@
         <v>18.8050003051758</v>
       </c>
       <c r="G797" t="n">
-        <v>17.5752601623535</v>
+        <v>17.5752620697021</v>
       </c>
       <c r="H797" t="n">
         <v>620074</v>
@@ -23598,7 +23598,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G801" t="n">
-        <v>17.1313228607178</v>
+        <v>17.1313247680664</v>
       </c>
       <c r="H801" t="n">
         <v>192081</v>
@@ -23627,7 +23627,7 @@
         <v>18.4349994659424</v>
       </c>
       <c r="G802" t="n">
-        <v>17.2294578552246</v>
+        <v>17.229455947876</v>
       </c>
       <c r="H802" t="n">
         <v>234504</v>
@@ -23714,7 +23714,7 @@
         <v>18.6749992370605</v>
       </c>
       <c r="G805" t="n">
-        <v>17.4537620544434</v>
+        <v>17.453763961792</v>
       </c>
       <c r="H805" t="n">
         <v>268791</v>
@@ -23888,7 +23888,7 @@
         <v>18.0249996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>16.8462696075439</v>
+        <v>16.8462677001953</v>
       </c>
       <c r="H811" t="n">
         <v>347878</v>
@@ -23975,7 +23975,7 @@
         <v>19.25</v>
       </c>
       <c r="G814" t="n">
-        <v>17.9911594390869</v>
+        <v>17.9911613464355</v>
       </c>
       <c r="H814" t="n">
         <v>2684040</v>
@@ -24033,7 +24033,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>18.0378932952881</v>
+        <v>18.0378913879395</v>
       </c>
       <c r="H816" t="n">
         <v>507095</v>
@@ -24062,7 +24062,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G817" t="n">
-        <v>17.6593761444092</v>
+        <v>17.6593780517578</v>
       </c>
       <c r="H817" t="n">
         <v>1770207</v>
@@ -24207,7 +24207,7 @@
         <v>18.6149997711182</v>
       </c>
       <c r="G822" t="n">
-        <v>17.3976879119873</v>
+        <v>17.3976860046387</v>
       </c>
       <c r="H822" t="n">
         <v>242884</v>
@@ -24294,7 +24294,7 @@
         <v>18.7250003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>17.5004959106445</v>
+        <v>17.5004940032959</v>
       </c>
       <c r="H825" t="n">
         <v>295760</v>
@@ -24323,7 +24323,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G826" t="n">
-        <v>17.8696632385254</v>
+        <v>17.869665145874</v>
       </c>
       <c r="H826" t="n">
         <v>493818</v>
@@ -24352,7 +24352,7 @@
         <v>19.5949993133545</v>
       </c>
       <c r="G827" t="n">
-        <v>18.3136005401611</v>
+        <v>18.3135986328125</v>
       </c>
       <c r="H827" t="n">
         <v>659382</v>
@@ -24439,7 +24439,7 @@
         <v>19.5949993133545</v>
       </c>
       <c r="G830" t="n">
-        <v>18.3136005401611</v>
+        <v>18.3135986328125</v>
       </c>
       <c r="H830" t="n">
         <v>585086</v>
@@ -24497,7 +24497,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G832" t="n">
-        <v>18.0192012786865</v>
+        <v>18.0191993713379</v>
       </c>
       <c r="H832" t="n">
         <v>294577</v>
@@ -24526,7 +24526,7 @@
         <v>19.2250003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>17.9677963256836</v>
+        <v>17.9677982330322</v>
       </c>
       <c r="H833" t="n">
         <v>203838</v>
@@ -24729,7 +24729,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G840" t="n">
-        <v>18.4397716522217</v>
+        <v>18.439769744873</v>
       </c>
       <c r="H840" t="n">
         <v>677306</v>
@@ -24845,7 +24845,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G844" t="n">
-        <v>18.3930435180664</v>
+        <v>18.3930416107178</v>
       </c>
       <c r="H844" t="n">
         <v>178961</v>
@@ -25048,7 +25048,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>18.06125831604</v>
+        <v>18.0612602233887</v>
       </c>
       <c r="H851" t="n">
         <v>377774</v>
@@ -25106,7 +25106,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G853" t="n">
-        <v>18.0939693450928</v>
+        <v>18.0939712524414</v>
       </c>
       <c r="H853" t="n">
         <v>637823</v>
@@ -25251,7 +25251,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>19.9071044921875</v>
+        <v>19.9071025848389</v>
       </c>
       <c r="H858" t="n">
         <v>565898</v>
@@ -25309,7 +25309,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G860" t="n">
-        <v>19.9735870361328</v>
+        <v>19.9735889434814</v>
       </c>
       <c r="H860" t="n">
         <v>461424</v>
@@ -25367,7 +25367,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G862" t="n">
-        <v>19.2042751312256</v>
+        <v>19.204273223877</v>
       </c>
       <c r="H862" t="n">
         <v>641183</v>
@@ -25396,7 +25396,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G863" t="n">
-        <v>19.4892063140869</v>
+        <v>19.4892082214355</v>
       </c>
       <c r="H863" t="n">
         <v>347100</v>
@@ -25599,7 +25599,7 @@
         <v>18.7749996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>17.8318634033203</v>
+        <v>17.8318614959717</v>
       </c>
       <c r="H870" t="n">
         <v>489772</v>
@@ -25657,7 +25657,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G872" t="n">
-        <v>18.6534118652344</v>
+        <v>18.6534099578857</v>
       </c>
       <c r="H872" t="n">
         <v>633892</v>
@@ -25686,7 +25686,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G873" t="n">
-        <v>19.1757850646973</v>
+        <v>19.1757831573486</v>
       </c>
       <c r="H873" t="n">
         <v>957501</v>
@@ -25802,7 +25802,7 @@
         <v>19.9850006103516</v>
       </c>
       <c r="G877" t="n">
-        <v>18.9810810089111</v>
+        <v>18.9810829162598</v>
       </c>
       <c r="H877" t="n">
         <v>573025</v>
@@ -25947,7 +25947,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G882" t="n">
-        <v>19.9355964660645</v>
+        <v>19.9355945587158</v>
       </c>
       <c r="H882" t="n">
         <v>321156</v>
@@ -25976,7 +25976,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G883" t="n">
-        <v>20.0210742950439</v>
+        <v>20.0210762023926</v>
       </c>
       <c r="H883" t="n">
         <v>323070</v>
@@ -26034,7 +26034,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G885" t="n">
-        <v>19.7171497344971</v>
+        <v>19.7171478271484</v>
       </c>
       <c r="H885" t="n">
         <v>182928</v>
@@ -26092,7 +26092,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G887" t="n">
-        <v>19.7456436157227</v>
+        <v>19.7456455230713</v>
       </c>
       <c r="H887" t="n">
         <v>232823</v>
@@ -26208,7 +26208,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>20.4674644470215</v>
+        <v>20.4674625396729</v>
       </c>
       <c r="H891" t="n">
         <v>463182</v>
@@ -26237,7 +26237,7 @@
         <v>21.5699996948242</v>
       </c>
       <c r="G892" t="n">
-        <v>20.4864597320557</v>
+        <v>20.4864616394043</v>
       </c>
       <c r="H892" t="n">
         <v>439206</v>
@@ -26266,7 +26266,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G893" t="n">
-        <v>20.2870101928711</v>
+        <v>20.2870121002197</v>
       </c>
       <c r="H893" t="n">
         <v>452737</v>
@@ -26556,7 +26556,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G903" t="n">
-        <v>19.8691139221191</v>
+        <v>19.8691120147705</v>
       </c>
       <c r="H903" t="n">
         <v>427160</v>
@@ -26585,7 +26585,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G904" t="n">
-        <v>19.9735870361328</v>
+        <v>19.9735889434814</v>
       </c>
       <c r="H904" t="n">
         <v>428652</v>
@@ -26614,7 +26614,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G905" t="n">
-        <v>19.8691139221191</v>
+        <v>19.8691120147705</v>
       </c>
       <c r="H905" t="n">
         <v>312833</v>
@@ -26643,7 +26643,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G906" t="n">
-        <v>19.9355964660645</v>
+        <v>19.9355945587158</v>
       </c>
       <c r="H906" t="n">
         <v>288708</v>
@@ -26672,7 +26672,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G907" t="n">
-        <v>19.96409034729</v>
+        <v>19.9640884399414</v>
       </c>
       <c r="H907" t="n">
         <v>595451</v>
@@ -26875,7 +26875,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G914" t="n">
-        <v>17.2952442169189</v>
+        <v>17.2952461242676</v>
       </c>
       <c r="H914" t="n">
         <v>665988</v>
@@ -26962,7 +26962,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G917" t="n">
-        <v>17.3854732513428</v>
+        <v>17.3854751586914</v>
       </c>
       <c r="H917" t="n">
         <v>278040</v>
@@ -27049,7 +27049,7 @@
         <v>17.9150009155273</v>
       </c>
       <c r="G920" t="n">
-        <v>17.0150661468506</v>
+        <v>17.015064239502</v>
       </c>
       <c r="H920" t="n">
         <v>386059</v>
@@ -27078,7 +27078,7 @@
         <v>17.4750003814697</v>
       </c>
       <c r="G921" t="n">
-        <v>16.5971660614014</v>
+        <v>16.59716796875</v>
       </c>
       <c r="H921" t="n">
         <v>361687</v>
@@ -27107,7 +27107,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G922" t="n">
-        <v>16.2837467193604</v>
+        <v>16.2837448120117</v>
       </c>
       <c r="H922" t="n">
         <v>717691</v>
@@ -27310,7 +27310,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G929" t="n">
-        <v>16.9485816955566</v>
+        <v>16.948579788208</v>
       </c>
       <c r="H929" t="n">
         <v>294893</v>
@@ -27339,7 +27339,7 @@
         <v>17.6350002288818</v>
       </c>
       <c r="G930" t="n">
-        <v>16.7491321563721</v>
+        <v>16.7491302490234</v>
       </c>
       <c r="H930" t="n">
         <v>638773</v>
@@ -27368,7 +27368,7 @@
         <v>17.7350006103516</v>
       </c>
       <c r="G931" t="n">
-        <v>16.8441066741943</v>
+        <v>16.844108581543</v>
       </c>
       <c r="H931" t="n">
         <v>237897</v>
@@ -27397,7 +27397,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G932" t="n">
-        <v>16.4974422454834</v>
+        <v>16.497444152832</v>
       </c>
       <c r="H932" t="n">
         <v>1271538</v>
@@ -27484,7 +27484,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G935" t="n">
-        <v>16.9248371124268</v>
+        <v>16.9248352050781</v>
       </c>
       <c r="H935" t="n">
         <v>526819</v>
@@ -27600,7 +27600,7 @@
         <v>18.0450000762939</v>
       </c>
       <c r="G939" t="n">
-        <v>17.1385345458984</v>
+        <v>17.1385364532471</v>
       </c>
       <c r="H939" t="n">
         <v>587734</v>
@@ -27745,7 +27745,7 @@
         <v>17.7350006103516</v>
       </c>
       <c r="G944" t="n">
-        <v>16.8441066741943</v>
+        <v>16.844108581543</v>
       </c>
       <c r="H944" t="n">
         <v>503594</v>
@@ -27890,7 +27890,7 @@
         <v>17.0450000762939</v>
       </c>
       <c r="G949" t="n">
-        <v>16.1887664794922</v>
+        <v>16.1887683868408</v>
       </c>
       <c r="H949" t="n">
         <v>847682</v>
@@ -27948,7 +27948,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G951" t="n">
-        <v>16.34547996521</v>
+        <v>16.3454780578613</v>
       </c>
       <c r="H951" t="n">
         <v>647943</v>
@@ -28035,7 +28035,7 @@
         <v>16.8649997711182</v>
       </c>
       <c r="G954" t="n">
-        <v>16.0178108215332</v>
+        <v>16.0178089141846</v>
       </c>
       <c r="H954" t="n">
         <v>543115</v>
@@ -28122,7 +28122,7 @@
         <v>16.3850002288818</v>
       </c>
       <c r="G957" t="n">
-        <v>15.5619230270386</v>
+        <v>15.5619220733643</v>
       </c>
       <c r="H957" t="n">
         <v>387332</v>
@@ -28267,7 +28267,7 @@
         <v>16.4150009155273</v>
       </c>
       <c r="G962" t="n">
-        <v>15.5904159545898</v>
+        <v>15.5904169082642</v>
       </c>
       <c r="H962" t="n">
         <v>1017946</v>
@@ -28325,7 +28325,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G964" t="n">
-        <v>15.680643081665</v>
+        <v>15.6806421279907</v>
       </c>
       <c r="H964" t="n">
         <v>425280</v>
@@ -28354,7 +28354,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G965" t="n">
-        <v>15.4052095413208</v>
+        <v>15.4052104949951</v>
       </c>
       <c r="H965" t="n">
         <v>687418</v>
@@ -28557,7 +28557,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G972" t="n">
-        <v>15.3197317123413</v>
+        <v>15.319730758667</v>
       </c>
       <c r="H972" t="n">
         <v>1080701</v>
@@ -28586,7 +28586,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G973" t="n">
-        <v>15.960823059082</v>
+        <v>15.9608249664307</v>
       </c>
       <c r="H973" t="n">
         <v>1840392</v>
@@ -28615,7 +28615,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>15.7661218643188</v>
+        <v>15.7661228179932</v>
       </c>
       <c r="H974" t="n">
         <v>975396</v>
@@ -28673,7 +28673,7 @@
         <v>16.75</v>
       </c>
       <c r="G976" t="n">
-        <v>15.9085874557495</v>
+        <v>15.9085855484009</v>
       </c>
       <c r="H976" t="n">
         <v>419109</v>
@@ -28731,7 +28731,7 @@
         <v>16.9950008392334</v>
       </c>
       <c r="G978" t="n">
-        <v>16.1412792205811</v>
+        <v>16.1412811279297</v>
       </c>
       <c r="H978" t="n">
         <v>604860</v>
@@ -28818,7 +28818,7 @@
         <v>17.4549999237061</v>
       </c>
       <c r="G981" t="n">
-        <v>16.5781707763672</v>
+        <v>16.5781726837158</v>
       </c>
       <c r="H981" t="n">
         <v>834030</v>
@@ -29021,7 +29021,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G988" t="n">
-        <v>16.4404563903809</v>
+        <v>16.4404544830322</v>
       </c>
       <c r="H988" t="n">
         <v>893679</v>
@@ -29282,7 +29282,7 @@
         <v>18.0949993133545</v>
       </c>
       <c r="G997" t="n">
-        <v>17.1860218048096</v>
+        <v>17.1860237121582</v>
       </c>
       <c r="H997" t="n">
         <v>470813</v>
@@ -29514,7 +29514,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1005" t="n">
-        <v>17.2477569580078</v>
+        <v>17.2477588653564</v>
       </c>
       <c r="H1005" t="n">
         <v>439993</v>
@@ -29717,7 +29717,7 @@
         <v>19.0750007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>18.1167945861816</v>
+        <v>18.1167964935303</v>
       </c>
       <c r="H1012" t="n">
         <v>838667</v>
@@ -29775,7 +29775,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>17.8556079864502</v>
+        <v>17.8556060791016</v>
       </c>
       <c r="H1014" t="n">
         <v>268982</v>
@@ -29804,7 +29804,7 @@
         <v>18.75</v>
       </c>
       <c r="G1015" t="n">
-        <v>17.8081207275391</v>
+        <v>17.8081188201904</v>
       </c>
       <c r="H1015" t="n">
         <v>216874</v>
@@ -29862,7 +29862,7 @@
         <v>18.6049995422363</v>
       </c>
       <c r="G1017" t="n">
-        <v>17.6704025268555</v>
+        <v>17.6704044342041</v>
       </c>
       <c r="H1017" t="n">
         <v>345428</v>
@@ -29891,7 +29891,7 @@
         <v>18.5550003051758</v>
       </c>
       <c r="G1018" t="n">
-        <v>17.6229152679443</v>
+        <v>17.622917175293</v>
       </c>
       <c r="H1018" t="n">
         <v>319106</v>
@@ -29920,7 +29920,7 @@
         <v>18.6149997711182</v>
       </c>
       <c r="G1019" t="n">
-        <v>17.6799030303955</v>
+        <v>17.6799011230469</v>
       </c>
       <c r="H1019" t="n">
         <v>233888</v>
@@ -30007,7 +30007,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1022" t="n">
-        <v>18.0930480957031</v>
+        <v>18.0930500030518</v>
       </c>
       <c r="H1022" t="n">
         <v>323583</v>
@@ -30036,7 +30036,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.90309715271</v>
+        <v>17.9030952453613</v>
       </c>
       <c r="H1023" t="n">
         <v>285927</v>
@@ -30065,7 +30065,7 @@
         <v>18.7950000762939</v>
       </c>
       <c r="G1024" t="n">
-        <v>17.8508586883545</v>
+        <v>17.8508605957031</v>
       </c>
       <c r="H1024" t="n">
         <v>286349</v>
@@ -30181,7 +30181,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.2287616729736</v>
+        <v>17.2287635803223</v>
       </c>
       <c r="H1028" t="n">
         <v>252655</v>
@@ -30297,7 +30297,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1032" t="n">
-        <v>16.5924186706543</v>
+        <v>16.5924167633057</v>
       </c>
       <c r="H1032" t="n">
         <v>390989</v>
@@ -30326,7 +30326,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>15.8611001968384</v>
+        <v>15.8610982894897</v>
       </c>
       <c r="H1033" t="n">
         <v>1029610</v>
@@ -30355,7 +30355,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G1034" t="n">
-        <v>16.2694969177246</v>
+        <v>16.2694988250732</v>
       </c>
       <c r="H1034" t="n">
         <v>539194</v>
@@ -30442,7 +30442,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1037" t="n">
-        <v>15.8468503952026</v>
+        <v>15.8468523025513</v>
       </c>
       <c r="H1037" t="n">
         <v>727617</v>
@@ -30587,7 +30587,7 @@
         <v>16.6149997711182</v>
       </c>
       <c r="G1042" t="n">
-        <v>15.7803688049316</v>
+        <v>15.7803678512573</v>
       </c>
       <c r="H1042" t="n">
         <v>513424</v>
@@ -30616,7 +30616,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>15.7186326980591</v>
+        <v>15.7186336517334</v>
       </c>
       <c r="H1043" t="n">
         <v>350977</v>
@@ -30645,7 +30645,7 @@
         <v>16.1550006866455</v>
       </c>
       <c r="G1044" t="n">
-        <v>15.3434772491455</v>
+        <v>15.3434762954712</v>
       </c>
       <c r="H1044" t="n">
         <v>964969</v>
@@ -30674,7 +30674,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1045" t="n">
-        <v>15.9845676422119</v>
+        <v>15.9845695495605</v>
       </c>
       <c r="H1045" t="n">
         <v>961466</v>
@@ -30732,7 +30732,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1047" t="n">
-        <v>15.604660987854</v>
+        <v>15.6046619415283</v>
       </c>
       <c r="H1047" t="n">
         <v>418169</v>
@@ -30761,7 +30761,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1048" t="n">
-        <v>15.8611001968384</v>
+        <v>15.8610982894897</v>
       </c>
       <c r="H1048" t="n">
         <v>559116</v>
@@ -30790,7 +30790,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1049" t="n">
-        <v>15.7043857574463</v>
+        <v>15.7043867111206</v>
       </c>
       <c r="H1049" t="n">
         <v>541345</v>
@@ -30848,7 +30848,7 @@
         <v>16.3649997711182</v>
       </c>
       <c r="G1051" t="n">
-        <v>15.5429267883301</v>
+        <v>15.5429258346558</v>
       </c>
       <c r="H1051" t="n">
         <v>743062</v>
@@ -30993,7 +30993,7 @@
         <v>14.3249998092651</v>
       </c>
       <c r="G1056" t="n">
-        <v>13.6054039001465</v>
+        <v>13.6054029464722</v>
       </c>
       <c r="H1056" t="n">
         <v>1069741</v>
@@ -31109,7 +31109,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1060" t="n">
-        <v>12.9738092422485</v>
+        <v>12.9738082885742</v>
       </c>
       <c r="H1060" t="n">
         <v>551132</v>
@@ -31254,7 +31254,7 @@
         <v>11.3549995422363</v>
       </c>
       <c r="G1065" t="n">
-        <v>10.7845964431763</v>
+        <v>10.7845973968506</v>
       </c>
       <c r="H1065" t="n">
         <v>1903661</v>
@@ -31283,7 +31283,7 @@
         <v>9.5620002746582</v>
       </c>
       <c r="G1066" t="n">
-        <v>9.08166599273682</v>
+        <v>9.08166694641113</v>
       </c>
       <c r="H1066" t="n">
         <v>1982873</v>
@@ -31312,7 +31312,7 @@
         <v>10.164999961853</v>
       </c>
       <c r="G1067" t="n">
-        <v>9.65437507629395</v>
+        <v>9.65437602996826</v>
       </c>
       <c r="H1067" t="n">
         <v>1497885</v>
@@ -31921,7 +31921,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1088" t="n">
-        <v>11.4541835784912</v>
+        <v>11.4541826248169</v>
       </c>
       <c r="H1088" t="n">
         <v>536555</v>
@@ -31979,7 +31979,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>11.5396604537964</v>
+        <v>11.5396614074707</v>
       </c>
       <c r="H1090" t="n">
         <v>351112</v>
@@ -32066,7 +32066,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>10.3999423980713</v>
+        <v>10.399941444397</v>
       </c>
       <c r="H1093" t="n">
         <v>1163920</v>
@@ -32095,7 +32095,7 @@
         <v>11</v>
       </c>
       <c r="G1094" t="n">
-        <v>10.4474306106567</v>
+        <v>10.4474296569824</v>
       </c>
       <c r="H1094" t="n">
         <v>374895</v>
@@ -32182,7 +32182,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1097" t="n">
-        <v>10.7323608398438</v>
+        <v>10.7323598861694</v>
       </c>
       <c r="H1097" t="n">
         <v>436691</v>
@@ -32240,7 +32240,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1099" t="n">
-        <v>10.7228622436523</v>
+        <v>10.722861289978</v>
       </c>
       <c r="H1099" t="n">
         <v>461067</v>
@@ -32385,7 +32385,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1104" t="n">
-        <v>10.4094390869141</v>
+        <v>10.4094400405884</v>
       </c>
       <c r="H1104" t="n">
         <v>459706</v>
@@ -32559,7 +32559,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1110" t="n">
-        <v>10.4094390869141</v>
+        <v>10.4094400405884</v>
       </c>
       <c r="H1110" t="n">
         <v>778843</v>
@@ -32588,7 +32588,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1111" t="n">
-        <v>10.3999423980713</v>
+        <v>10.399941444397</v>
       </c>
       <c r="H1111" t="n">
         <v>2429677</v>
@@ -33023,7 +33023,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>13.1542644500732</v>
+        <v>13.1542654037476</v>
       </c>
       <c r="H1126" t="n">
         <v>1935626</v>
@@ -33081,7 +33081,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G1128" t="n">
-        <v>11.8815774917603</v>
+        <v>11.8815784454346</v>
       </c>
       <c r="H1128" t="n">
         <v>1152534</v>
@@ -33139,7 +33139,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1130" t="n">
-        <v>12.0620336532593</v>
+        <v>12.062032699585</v>
       </c>
       <c r="H1130" t="n">
         <v>882931</v>
@@ -33168,7 +33168,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1131" t="n">
-        <v>12.1190195083618</v>
+        <v>12.1190185546875</v>
       </c>
       <c r="H1131" t="n">
         <v>1075221</v>
@@ -33284,7 +33284,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1135" t="n">
-        <v>12.5749073028564</v>
+        <v>12.5749063491821</v>
       </c>
       <c r="H1135" t="n">
         <v>672115</v>
@@ -33313,7 +33313,7 @@
         <v>13.25</v>
       </c>
       <c r="G1136" t="n">
-        <v>12.5844049453735</v>
+        <v>12.5844039916992</v>
       </c>
       <c r="H1136" t="n">
         <v>819274</v>
@@ -33371,7 +33371,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1138" t="n">
-        <v>11.8055953979492</v>
+        <v>11.8055963516235</v>
       </c>
       <c r="H1138" t="n">
         <v>819399</v>
@@ -33429,7 +33429,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1140" t="n">
-        <v>11.7296152114868</v>
+        <v>11.7296142578125</v>
       </c>
       <c r="H1140" t="n">
         <v>688432</v>
@@ -33516,7 +33516,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1143" t="n">
-        <v>11.7581071853638</v>
+        <v>11.7581081390381</v>
       </c>
       <c r="H1143" t="n">
         <v>523414</v>
@@ -33545,7 +33545,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1144" t="n">
-        <v>11.4541835784912</v>
+        <v>11.4541826248169</v>
       </c>
       <c r="H1144" t="n">
         <v>491409</v>
@@ -33719,7 +33719,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G1150" t="n">
-        <v>11.1787519454956</v>
+        <v>11.1787509918213</v>
       </c>
       <c r="H1150" t="n">
         <v>464530</v>
@@ -33864,7 +33864,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.2452335357666</v>
+        <v>11.2452344894409</v>
       </c>
       <c r="H1155" t="n">
         <v>321721</v>
@@ -33980,7 +33980,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G1159" t="n">
-        <v>11.0267868041992</v>
+        <v>11.0267877578735</v>
       </c>
       <c r="H1159" t="n">
         <v>350758</v>
@@ -34038,7 +34038,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1161" t="n">
-        <v>10.8368349075317</v>
+        <v>10.8368339538574</v>
       </c>
       <c r="H1161" t="n">
         <v>402699</v>
@@ -34212,7 +34212,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1167" t="n">
-        <v>10.8368349075317</v>
+        <v>10.8368339538574</v>
       </c>
       <c r="H1167" t="n">
         <v>457270</v>
@@ -34299,7 +34299,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G1170" t="n">
-        <v>10.3619508743286</v>
+        <v>10.3619518280029</v>
       </c>
       <c r="H1170" t="n">
         <v>512127</v>
@@ -34415,7 +34415,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1174" t="n">
-        <v>11.3307132720947</v>
+        <v>11.3307123184204</v>
       </c>
       <c r="H1174" t="n">
         <v>653648</v>
@@ -34502,7 +34502,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1177" t="n">
-        <v>10.9603052139282</v>
+        <v>10.9603042602539</v>
       </c>
       <c r="H1177" t="n">
         <v>198677</v>
@@ -34531,7 +34531,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G1178" t="n">
-        <v>10.7608528137207</v>
+        <v>10.760853767395</v>
       </c>
       <c r="H1178" t="n">
         <v>232544</v>
@@ -34734,7 +34734,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1185" t="n">
-        <v>11.463680267334</v>
+        <v>11.4636793136597</v>
       </c>
       <c r="H1185" t="n">
         <v>306240</v>
@@ -34821,7 +34821,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1188" t="n">
-        <v>11.7960987091064</v>
+        <v>11.7960977554321</v>
       </c>
       <c r="H1188" t="n">
         <v>437652</v>
@@ -34966,7 +34966,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1193" t="n">
-        <v>11.4541835784912</v>
+        <v>11.4541826248169</v>
       </c>
       <c r="H1193" t="n">
         <v>306311</v>
@@ -35256,7 +35256,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1203" t="n">
-        <v>11.463680267334</v>
+        <v>11.4636793136597</v>
       </c>
       <c r="H1203" t="n">
         <v>441998</v>
@@ -35314,7 +35314,7 @@
         <v>12.75</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.1095218658447</v>
+        <v>12.1095209121704</v>
       </c>
       <c r="H1205" t="n">
         <v>796074</v>
@@ -35430,7 +35430,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1209" t="n">
-        <v>11.9860515594482</v>
+        <v>11.9860506057739</v>
       </c>
       <c r="H1209" t="n">
         <v>375319</v>
@@ -35604,7 +35604,7 @@
         <v>13.25</v>
       </c>
       <c r="G1215" t="n">
-        <v>12.5844049453735</v>
+        <v>12.5844039916992</v>
       </c>
       <c r="H1215" t="n">
         <v>280270</v>
@@ -35662,7 +35662,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G1217" t="n">
-        <v>12.5464134216309</v>
+        <v>12.5464143753052</v>
       </c>
       <c r="H1217" t="n">
         <v>251308</v>
@@ -35691,7 +35691,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>12.2044973373413</v>
+        <v>12.2044982910156</v>
       </c>
       <c r="H1218" t="n">
         <v>348352</v>
@@ -35836,7 +35836,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1223" t="n">
-        <v>12.1950006484985</v>
+        <v>12.1949996948242</v>
       </c>
       <c r="H1223" t="n">
         <v>1001856</v>
@@ -36097,7 +36097,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1232" t="n">
-        <v>11.0647783279419</v>
+        <v>11.0647773742676</v>
       </c>
       <c r="H1232" t="n">
         <v>309563</v>
@@ -36358,7 +36358,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1241" t="n">
-        <v>13.9235754013062</v>
+        <v>13.9235744476318</v>
       </c>
       <c r="H1241" t="n">
         <v>633097</v>
@@ -36561,7 +36561,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G1248" t="n">
-        <v>14.3129796981812</v>
+        <v>14.3129787445068</v>
       </c>
       <c r="H1248" t="n">
         <v>692581</v>
@@ -36619,7 +36619,7 @@
         <v>15</v>
       </c>
       <c r="G1250" t="n">
-        <v>14.2464962005615</v>
+        <v>14.2464952468872</v>
       </c>
       <c r="H1250" t="n">
         <v>463570</v>
@@ -36793,7 +36793,7 @@
         <v>15</v>
       </c>
       <c r="G1256" t="n">
-        <v>14.2464962005615</v>
+        <v>14.2464952468872</v>
       </c>
       <c r="H1256" t="n">
         <v>190883</v>
@@ -36822,7 +36822,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1257" t="n">
-        <v>14.4934358596802</v>
+        <v>14.4934349060059</v>
       </c>
       <c r="H1257" t="n">
         <v>484047</v>
@@ -36996,7 +36996,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1263" t="n">
-        <v>14.8543472290039</v>
+        <v>14.8543462753296</v>
       </c>
       <c r="H1263" t="n">
         <v>350866</v>
@@ -37054,7 +37054,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1265" t="n">
-        <v>14.3794631958008</v>
+        <v>14.3794622421265</v>
       </c>
       <c r="H1265" t="n">
         <v>369816</v>
@@ -37170,7 +37170,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G1269" t="n">
-        <v>15.1107835769653</v>
+        <v>15.110782623291</v>
       </c>
       <c r="H1269" t="n">
         <v>607990</v>
@@ -37286,7 +37286,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1273" t="n">
-        <v>14.7118816375732</v>
+        <v>14.7118806838989</v>
       </c>
       <c r="H1273" t="n">
         <v>165183</v>
@@ -37344,7 +37344,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1275" t="n">
-        <v>14.5884113311768</v>
+        <v>14.5884103775024</v>
       </c>
       <c r="H1275" t="n">
         <v>203927</v>
@@ -37402,7 +37402,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1277" t="n">
-        <v>14.4079551696777</v>
+        <v>14.4079561233521</v>
       </c>
       <c r="H1277" t="n">
         <v>195856</v>
@@ -37460,7 +37460,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1279" t="n">
-        <v>14.5314254760742</v>
+        <v>14.5314264297485</v>
       </c>
       <c r="H1279" t="n">
         <v>147746</v>
@@ -37547,7 +37547,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1282" t="n">
-        <v>14.3794631958008</v>
+        <v>14.3794622421265</v>
       </c>
       <c r="H1282" t="n">
         <v>310366</v>
@@ -37605,7 +37605,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G1284" t="n">
-        <v>15.3197317123413</v>
+        <v>15.319730758667</v>
       </c>
       <c r="H1284" t="n">
         <v>1360458</v>
@@ -37634,7 +37634,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1285" t="n">
-        <v>15.29123878479</v>
+        <v>15.2912397384644</v>
       </c>
       <c r="H1285" t="n">
         <v>324871</v>
@@ -37692,7 +37692,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>15.0537977218628</v>
+        <v>15.0537967681885</v>
       </c>
       <c r="H1287" t="n">
         <v>418867</v>
@@ -37721,7 +37721,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1288" t="n">
-        <v>15.8041114807129</v>
+        <v>15.8041124343872</v>
       </c>
       <c r="H1288" t="n">
         <v>1007744</v>
@@ -37779,7 +37779,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1290" t="n">
-        <v>15.2627449035645</v>
+        <v>15.2627458572388</v>
       </c>
       <c r="H1290" t="n">
         <v>357033</v>
@@ -37982,7 +37982,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1297" t="n">
-        <v>14.4364500045776</v>
+        <v>14.4364490509033</v>
       </c>
       <c r="H1297" t="n">
         <v>842933</v>
@@ -38156,7 +38156,7 @@
         <v>15.7700004577637</v>
       </c>
       <c r="G1303" t="n">
-        <v>14.9778165817261</v>
+        <v>14.9778156280518</v>
       </c>
       <c r="H1303" t="n">
         <v>274608</v>
@@ -38359,7 +38359,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1310" t="n">
-        <v>15.1202812194824</v>
+        <v>15.1202802658081</v>
       </c>
       <c r="H1310" t="n">
         <v>191702</v>
@@ -38417,7 +38417,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1312" t="n">
-        <v>15.2627449035645</v>
+        <v>15.2627458572388</v>
       </c>
       <c r="H1312" t="n">
         <v>448450</v>
@@ -38475,7 +38475,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1314" t="n">
-        <v>15.1012859344482</v>
+        <v>15.1012849807739</v>
       </c>
       <c r="H1314" t="n">
         <v>135045</v>
@@ -38533,7 +38533,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1316" t="n">
-        <v>14.9873132705688</v>
+        <v>14.9873123168945</v>
       </c>
       <c r="H1316" t="n">
         <v>239674</v>
@@ -38649,7 +38649,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1320" t="n">
-        <v>16.032054901123</v>
+        <v>16.0320568084717</v>
       </c>
       <c r="H1320" t="n">
         <v>326028</v>
@@ -38765,7 +38765,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>15.7376289367676</v>
+        <v>15.7376298904419</v>
       </c>
       <c r="H1324" t="n">
         <v>266463</v>
@@ -38939,7 +38939,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1330" t="n">
-        <v>15.3672208786011</v>
+        <v>15.3672199249268</v>
       </c>
       <c r="H1330" t="n">
         <v>273867</v>
@@ -38968,7 +38968,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1331" t="n">
-        <v>15.3387260437012</v>
+        <v>15.3387269973755</v>
       </c>
       <c r="H1331" t="n">
         <v>147455</v>
@@ -38997,7 +38997,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1332" t="n">
-        <v>15.6996393203735</v>
+        <v>15.6996374130249</v>
       </c>
       <c r="H1332" t="n">
         <v>267931</v>
@@ -39084,7 +39084,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G1335" t="n">
-        <v>15.960823059082</v>
+        <v>15.9608249664307</v>
       </c>
       <c r="H1335" t="n">
         <v>327422</v>
@@ -39113,7 +39113,7 @@
         <v>16.4449996948242</v>
       </c>
       <c r="G1336" t="n">
-        <v>15.6189069747925</v>
+        <v>15.6189079284668</v>
       </c>
       <c r="H1336" t="n">
         <v>353065</v>
@@ -39142,7 +39142,7 @@
         <v>16.2450008392334</v>
       </c>
       <c r="G1337" t="n">
-        <v>15.428955078125</v>
+        <v>15.4289560317993</v>
       </c>
       <c r="H1337" t="n">
         <v>389353</v>
@@ -39171,7 +39171,7 @@
         <v>16.4650001525879</v>
       </c>
       <c r="G1338" t="n">
-        <v>15.637903213501</v>
+        <v>15.6379041671753</v>
       </c>
       <c r="H1338" t="n">
         <v>344519</v>
@@ -39200,7 +39200,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1339" t="n">
-        <v>15.8468503952026</v>
+        <v>15.8468523025513</v>
       </c>
       <c r="H1339" t="n">
         <v>183071</v>
@@ -39229,7 +39229,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G1340" t="n">
-        <v>16.2837467193604</v>
+        <v>16.2837448120117</v>
       </c>
       <c r="H1340" t="n">
         <v>635746</v>
@@ -39287,7 +39287,7 @@
         <v>17.625</v>
       </c>
       <c r="G1342" t="n">
-        <v>16.739631652832</v>
+        <v>16.7396335601807</v>
       </c>
       <c r="H1342" t="n">
         <v>365703</v>
@@ -39345,7 +39345,7 @@
         <v>17.7649993896484</v>
       </c>
       <c r="G1344" t="n">
-        <v>16.8725986480713</v>
+        <v>16.8726005554199</v>
       </c>
       <c r="H1344" t="n">
         <v>279966</v>
@@ -39461,7 +39461,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G1348" t="n">
-        <v>17.4567031860352</v>
+        <v>17.4567050933838</v>
       </c>
       <c r="H1348" t="n">
         <v>598052</v>
@@ -39490,7 +39490,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G1349" t="n">
-        <v>17.3854732513428</v>
+        <v>17.3854751586914</v>
       </c>
       <c r="H1349" t="n">
         <v>274320</v>
@@ -39548,7 +39548,7 @@
         <v>18.2049999237061</v>
       </c>
       <c r="G1351" t="n">
-        <v>17.2904987335205</v>
+        <v>17.2904968261719</v>
       </c>
       <c r="H1351" t="n">
         <v>262686</v>
@@ -39606,7 +39606,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1353" t="n">
-        <v>16.9248371124268</v>
+        <v>16.9248352050781</v>
       </c>
       <c r="H1353" t="n">
         <v>308039</v>
@@ -39809,7 +39809,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1360" t="n">
-        <v>17.4187164306641</v>
+        <v>17.4187145233154</v>
       </c>
       <c r="H1360" t="n">
         <v>267867</v>
@@ -39896,7 +39896,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1363" t="n">
-        <v>18.1975250244141</v>
+        <v>18.1975231170654</v>
       </c>
       <c r="H1363" t="n">
         <v>262496</v>
@@ -39925,7 +39925,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G1364" t="n">
-        <v>18.1500377655029</v>
+        <v>18.1500358581543</v>
       </c>
       <c r="H1364" t="n">
         <v>98181</v>
@@ -39954,7 +39954,7 @@
         <v>19.1949996948242</v>
       </c>
       <c r="G1365" t="n">
-        <v>18.2307662963867</v>
+        <v>18.2307643890381</v>
       </c>
       <c r="H1365" t="n">
         <v>224548</v>
@@ -40331,7 +40331,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G1378" t="n">
-        <v>18.3542346954346</v>
+        <v>18.3542366027832</v>
       </c>
       <c r="H1378" t="n">
         <v>205617</v>
@@ -40389,7 +40389,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G1380" t="n">
-        <v>18.5299415588379</v>
+        <v>18.5299434661865</v>
       </c>
       <c r="H1380" t="n">
         <v>478383</v>
@@ -40447,7 +40447,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G1382" t="n">
-        <v>18.3542346954346</v>
+        <v>18.3542366027832</v>
       </c>
       <c r="H1382" t="n">
         <v>357274</v>
@@ -40476,7 +40476,7 @@
         <v>19.2649993896484</v>
       </c>
       <c r="G1383" t="n">
-        <v>18.297248840332</v>
+        <v>18.2972469329834</v>
       </c>
       <c r="H1383" t="n">
         <v>283276</v>
@@ -40534,7 +40534,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1385" t="n">
-        <v>18.1690311431885</v>
+        <v>18.1690292358398</v>
       </c>
       <c r="H1385" t="n">
         <v>242704</v>
@@ -40563,7 +40563,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1386" t="n">
-        <v>18.1690311431885</v>
+        <v>18.1690292358398</v>
       </c>
       <c r="H1386" t="n">
         <v>248014</v>
@@ -40592,7 +40592,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1387" t="n">
-        <v>18.1690311431885</v>
+        <v>18.1690292358398</v>
       </c>
       <c r="H1387" t="n">
         <v>176230</v>
@@ -40650,7 +40650,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1389" t="n">
-        <v>18.444465637207</v>
+        <v>18.4444637298584</v>
       </c>
       <c r="H1389" t="n">
         <v>662703</v>
@@ -40795,7 +40795,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G1394" t="n">
-        <v>17.8461093902588</v>
+        <v>17.8461112976074</v>
       </c>
       <c r="H1394" t="n">
         <v>862640</v>
@@ -40853,7 +40853,7 @@
         <v>18.0450000762939</v>
       </c>
       <c r="G1396" t="n">
-        <v>17.1385345458984</v>
+        <v>17.1385364532471</v>
       </c>
       <c r="H1396" t="n">
         <v>475104</v>
@@ -40911,7 +40911,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1398" t="n">
-        <v>17.2287616729736</v>
+        <v>17.2287635803223</v>
       </c>
       <c r="H1398" t="n">
         <v>182994</v>
@@ -41143,7 +41143,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1406" t="n">
-        <v>16.8773498535156</v>
+        <v>16.877347946167</v>
       </c>
       <c r="H1406" t="n">
         <v>162700</v>
@@ -41230,7 +41230,7 @@
         <v>16.4449996948242</v>
       </c>
       <c r="G1409" t="n">
-        <v>15.6189069747925</v>
+        <v>15.6189079284668</v>
       </c>
       <c r="H1409" t="n">
         <v>429152</v>
@@ -41404,7 +41404,7 @@
         <v>17.0249996185303</v>
       </c>
       <c r="G1415" t="n">
-        <v>16.1697731018066</v>
+        <v>16.169771194458</v>
       </c>
       <c r="H1415" t="n">
         <v>183230</v>
@@ -41462,7 +41462,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G1417" t="n">
-        <v>16.0368061065674</v>
+        <v>16.0368041992188</v>
       </c>
       <c r="H1417" t="n">
         <v>142262</v>
@@ -41549,7 +41549,7 @@
         <v>17.0249996185303</v>
       </c>
       <c r="G1420" t="n">
-        <v>16.1697731018066</v>
+        <v>16.169771194458</v>
       </c>
       <c r="H1420" t="n">
         <v>205910</v>
@@ -41607,7 +41607,7 @@
         <v>16.9150009155273</v>
       </c>
       <c r="G1422" t="n">
-        <v>16.065299987793</v>
+        <v>16.0652980804443</v>
       </c>
       <c r="H1422" t="n">
         <v>166040</v>
@@ -41810,7 +41810,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>17.0008163452148</v>
+        <v>17.0008182525635</v>
       </c>
       <c r="H1429" t="n">
         <v>840706</v>
@@ -41868,7 +41868,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G1431" t="n">
-        <v>16.5164356231689</v>
+        <v>16.5164375305176</v>
       </c>
       <c r="H1431" t="n">
         <v>523484</v>
@@ -41926,7 +41926,7 @@
         <v>16.5750007629395</v>
       </c>
       <c r="G1433" t="n">
-        <v>15.7423791885376</v>
+        <v>15.7423782348633</v>
       </c>
       <c r="H1433" t="n">
         <v>814180</v>
@@ -41955,7 +41955,7 @@
         <v>17</v>
       </c>
       <c r="G1434" t="n">
-        <v>16.1460285186768</v>
+        <v>16.1460266113281</v>
       </c>
       <c r="H1434" t="n">
         <v>1076069</v>
@@ -42013,7 +42013,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1436" t="n">
-        <v>15.8041114807129</v>
+        <v>15.8041124343872</v>
       </c>
       <c r="H1436" t="n">
         <v>400962</v>
@@ -42042,7 +42042,7 @@
         <v>16.8150005340576</v>
       </c>
       <c r="G1437" t="n">
-        <v>15.9703235626221</v>
+        <v>15.9703216552734</v>
       </c>
       <c r="H1437" t="n">
         <v>478682</v>
@@ -42332,7 +42332,7 @@
         <v>18.8150005340576</v>
       </c>
       <c r="G1447" t="n">
-        <v>17.8698539733887</v>
+        <v>17.8698558807373</v>
       </c>
       <c r="H1447" t="n">
         <v>642098</v>
@@ -42390,7 +42390,7 @@
         <v>18.75</v>
       </c>
       <c r="G1449" t="n">
-        <v>17.8081207275391</v>
+        <v>17.8081188201904</v>
       </c>
       <c r="H1449" t="n">
         <v>438443</v>
@@ -42593,7 +42593,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1456" t="n">
-        <v>16.9628276824951</v>
+        <v>16.9628295898438</v>
       </c>
       <c r="H1456" t="n">
         <v>490557</v>
@@ -42680,7 +42680,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1459" t="n">
-        <v>16.9438323974609</v>
+        <v>16.9438304901123</v>
       </c>
       <c r="H1459" t="n">
         <v>262741</v>
@@ -42912,7 +42912,7 @@
         <v>17.9449996948242</v>
       </c>
       <c r="G1467" t="n">
-        <v>17.0435581207275</v>
+        <v>17.0435562133789</v>
       </c>
       <c r="H1467" t="n">
         <v>317629</v>
@@ -43028,7 +43028,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>17.0008163452148</v>
+        <v>17.0008182525635</v>
       </c>
       <c r="H1471" t="n">
         <v>312375</v>
@@ -43086,7 +43086,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1473" t="n">
-        <v>17.2287616729736</v>
+        <v>17.2287635803223</v>
       </c>
       <c r="H1473" t="n">
         <v>227595</v>
@@ -43115,7 +43115,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1474" t="n">
-        <v>16.9438323974609</v>
+        <v>16.9438304901123</v>
       </c>
       <c r="H1474" t="n">
         <v>321911</v>
@@ -43405,7 +43405,7 @@
         <v>18.6550006866455</v>
       </c>
       <c r="G1484" t="n">
-        <v>17.7178916931152</v>
+        <v>17.7178936004639</v>
       </c>
       <c r="H1484" t="n">
         <v>210630</v>
@@ -43521,7 +43521,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G1488" t="n">
-        <v>18.7009010314941</v>
+        <v>18.7008991241455</v>
       </c>
       <c r="H1488" t="n">
         <v>1068687</v>
@@ -43608,7 +43608,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1491" t="n">
-        <v>18.1690311431885</v>
+        <v>18.1690292358398</v>
       </c>
       <c r="H1491" t="n">
         <v>2245063</v>
@@ -43724,7 +43724,7 @@
         <v>19.7549991607666</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.7626342773438</v>
+        <v>18.7626323699951</v>
       </c>
       <c r="H1495" t="n">
         <v>366254</v>
@@ -44014,7 +44014,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1505" t="n">
-        <v>19.1377925872803</v>
+        <v>19.1377906799316</v>
       </c>
       <c r="H1505" t="n">
         <v>842589</v>
@@ -44101,7 +44101,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G1508" t="n">
-        <v>19.8691139221191</v>
+        <v>19.8691120147705</v>
       </c>
       <c r="H1508" t="n">
         <v>577156</v>
@@ -44130,7 +44130,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G1509" t="n">
-        <v>19.7456436157227</v>
+        <v>19.7456455230713</v>
       </c>
       <c r="H1509" t="n">
         <v>293466</v>
@@ -44159,7 +44159,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1510" t="n">
-        <v>20.4579696655273</v>
+        <v>20.4579677581787</v>
       </c>
       <c r="H1510" t="n">
         <v>712388</v>
@@ -44246,7 +44246,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1513" t="n">
-        <v>21.4457244873047</v>
+        <v>21.4457225799561</v>
       </c>
       <c r="H1513" t="n">
         <v>927272</v>
@@ -44304,7 +44304,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1515" t="n">
-        <v>20.7523956298828</v>
+        <v>20.7523975372314</v>
       </c>
       <c r="H1515" t="n">
         <v>480679</v>
@@ -44333,7 +44333,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G1516" t="n">
-        <v>20.6384220123291</v>
+        <v>20.6384239196777</v>
       </c>
       <c r="H1516" t="n">
         <v>670811</v>
@@ -44362,7 +44362,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G1517" t="n">
-        <v>20.1635417938232</v>
+        <v>20.1635398864746</v>
       </c>
       <c r="H1517" t="n">
         <v>373968</v>
@@ -44449,7 +44449,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G1520" t="n">
-        <v>20.7144050598145</v>
+        <v>20.7144031524658</v>
       </c>
       <c r="H1520" t="n">
         <v>644433</v>
@@ -44536,7 +44536,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G1523" t="n">
-        <v>21.0183277130127</v>
+        <v>21.0183296203613</v>
       </c>
       <c r="H1523" t="n">
         <v>163933</v>
@@ -44623,7 +44623,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G1526" t="n">
-        <v>21.3982372283936</v>
+        <v>21.3982353210449</v>
       </c>
       <c r="H1526" t="n">
         <v>218266</v>
@@ -44681,7 +44681,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G1528" t="n">
-        <v>21.5691928863525</v>
+        <v>21.5691947937012</v>
       </c>
       <c r="H1528" t="n">
         <v>290973</v>
@@ -44768,7 +44768,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G1531" t="n">
-        <v>21.6261825561523</v>
+        <v>21.6261806488037</v>
       </c>
       <c r="H1531" t="n">
         <v>356048</v>
@@ -44797,7 +44797,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G1532" t="n">
-        <v>19.7171497344971</v>
+        <v>19.7171478271484</v>
       </c>
       <c r="H1532" t="n">
         <v>1855644</v>
@@ -45058,7 +45058,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G1541" t="n">
-        <v>18.055061340332</v>
+        <v>18.0550594329834</v>
       </c>
       <c r="H1541" t="n">
         <v>598933</v>
@@ -45087,7 +45087,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1542" t="n">
-        <v>17.4946956634521</v>
+        <v>17.4946975708008</v>
       </c>
       <c r="H1542" t="n">
         <v>915612</v>
@@ -45145,7 +45145,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1544" t="n">
-        <v>18.0930480957031</v>
+        <v>18.0930500030518</v>
       </c>
       <c r="H1544" t="n">
         <v>460206</v>
@@ -45261,7 +45261,7 @@
         <v>19.5750007629395</v>
       </c>
       <c r="G1548" t="n">
-        <v>18.5916767120361</v>
+        <v>18.5916786193848</v>
       </c>
       <c r="H1548" t="n">
         <v>502931</v>
@@ -45290,7 +45290,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1549" t="n">
-        <v>18.5394420623779</v>
+        <v>18.5394401550293</v>
       </c>
       <c r="H1549" t="n">
         <v>396132</v>
@@ -45464,7 +45464,7 @@
         <v>19.25</v>
       </c>
       <c r="G1555" t="n">
-        <v>18.2830009460449</v>
+        <v>18.2830028533936</v>
       </c>
       <c r="H1555" t="n">
         <v>246876</v>
@@ -45696,7 +45696,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G1563" t="n">
-        <v>18.7768802642822</v>
+        <v>18.7768821716309</v>
       </c>
       <c r="H1563" t="n">
         <v>334413</v>
@@ -45754,7 +45754,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G1565" t="n">
-        <v>17.9220924377441</v>
+        <v>17.9220905303955</v>
       </c>
       <c r="H1565" t="n">
         <v>422325</v>
@@ -45783,7 +45783,7 @@
         <v>19.6450004577637</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.6581592559814</v>
+        <v>18.6581611633301</v>
       </c>
       <c r="H1566" t="n">
         <v>358435</v>
@@ -45812,7 +45812,7 @@
         <v>19.4249992370605</v>
       </c>
       <c r="G1567" t="n">
-        <v>18.4492111206055</v>
+        <v>18.4492130279541</v>
       </c>
       <c r="H1567" t="n">
         <v>352955</v>
@@ -45841,7 +45841,7 @@
         <v>18.5650005340576</v>
       </c>
       <c r="G1568" t="n">
-        <v>17.6324157714844</v>
+        <v>17.6324138641357</v>
       </c>
       <c r="H1568" t="n">
         <v>299563</v>
@@ -45986,7 +45986,7 @@
         <v>15.2749996185303</v>
       </c>
       <c r="G1573" t="n">
-        <v>14.5076808929443</v>
+        <v>14.5076818466187</v>
       </c>
       <c r="H1573" t="n">
         <v>715448</v>
@@ -46015,7 +46015,7 @@
         <v>16.7549991607666</v>
       </c>
       <c r="G1574" t="n">
-        <v>15.9133329391479</v>
+        <v>15.9133348464966</v>
       </c>
       <c r="H1574" t="n">
         <v>1254789</v>
@@ -46073,7 +46073,7 @@
         <v>16.1650009155273</v>
       </c>
       <c r="G1576" t="n">
-        <v>15.3529748916626</v>
+        <v>15.3529739379883</v>
       </c>
       <c r="H1576" t="n">
         <v>678377</v>
@@ -46160,7 +46160,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G1579" t="n">
-        <v>15.5856666564941</v>
+        <v>15.5856657028198</v>
       </c>
       <c r="H1579" t="n">
         <v>678989</v>
@@ -46189,7 +46189,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1580" t="n">
-        <v>15.7043857574463</v>
+        <v>15.7043867111206</v>
       </c>
       <c r="H1580" t="n">
         <v>591416</v>
@@ -46218,7 +46218,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1581" t="n">
-        <v>15.8611001968384</v>
+        <v>15.8610982894897</v>
       </c>
       <c r="H1581" t="n">
         <v>285487</v>
@@ -46247,7 +46247,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1582" t="n">
-        <v>15.81360912323</v>
+        <v>15.8136100769043</v>
       </c>
       <c r="H1582" t="n">
         <v>267348</v>
@@ -46334,7 +46334,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1585" t="n">
-        <v>15.2532472610474</v>
+        <v>15.253246307373</v>
       </c>
       <c r="H1585" t="n">
         <v>212871</v>
@@ -46392,7 +46392,7 @@
         <v>16.6650009155273</v>
       </c>
       <c r="G1587" t="n">
-        <v>15.8278579711914</v>
+        <v>15.8278589248657</v>
       </c>
       <c r="H1587" t="n">
         <v>215883</v>
@@ -46421,7 +46421,7 @@
         <v>17.6550006866455</v>
       </c>
       <c r="G1588" t="n">
-        <v>16.7681274414062</v>
+        <v>16.7681255340576</v>
       </c>
       <c r="H1588" t="n">
         <v>512570</v>
@@ -46566,7 +46566,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1593" t="n">
-        <v>15.2627449035645</v>
+        <v>15.2627458572388</v>
       </c>
       <c r="H1593" t="n">
         <v>528848</v>
@@ -46624,7 +46624,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1595" t="n">
-        <v>14.5884113311768</v>
+        <v>14.5884103775024</v>
       </c>
       <c r="H1595" t="n">
         <v>514601</v>
@@ -46711,7 +46711,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1598" t="n">
-        <v>15.3387260437012</v>
+        <v>15.3387269973755</v>
       </c>
       <c r="H1598" t="n">
         <v>634313</v>
@@ -46769,7 +46769,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1600" t="n">
-        <v>15.6331539154053</v>
+        <v>15.633152961731</v>
       </c>
       <c r="H1600" t="n">
         <v>220814</v>
@@ -46827,7 +46827,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1602" t="n">
-        <v>15.6996393203735</v>
+        <v>15.6996374130249</v>
       </c>
       <c r="H1602" t="n">
         <v>249471</v>
@@ -46885,7 +46885,7 @@
         <v>16.3299999237061</v>
       </c>
       <c r="G1604" t="n">
-        <v>15.5096845626831</v>
+        <v>15.5096855163574</v>
       </c>
       <c r="H1604" t="n">
         <v>267467</v>
@@ -47001,7 +47001,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1608" t="n">
-        <v>15.1392755508423</v>
+        <v>15.1392765045166</v>
       </c>
       <c r="H1608" t="n">
         <v>257315</v>
@@ -47175,7 +47175,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1614" t="n">
-        <v>14.3224773406982</v>
+        <v>14.3224763870239</v>
       </c>
       <c r="H1614" t="n">
         <v>449472</v>
@@ -47349,7 +47349,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G1620" t="n">
-        <v>15.0158061981201</v>
+        <v>15.0158071517944</v>
       </c>
       <c r="H1620" t="n">
         <v>321594</v>
@@ -47407,7 +47407,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1622" t="n">
-        <v>15.3672208786011</v>
+        <v>15.3672199249268</v>
       </c>
       <c r="H1622" t="n">
         <v>545962</v>
@@ -80038,6 +80038,35 @@
         <v>1300540</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>6.55999994277954</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>6.71000003814697</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>6.42000007629395</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>6.65500020980835</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>6.65500020980835</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>539191</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -427,7 +427,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G2" t="n">
-        <v>18.2763519287109</v>
+        <v>18.2763538360596</v>
       </c>
       <c r="H2" t="n">
         <v>1705033</v>
@@ -514,7 +514,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>17.9401912689209</v>
+        <v>17.9401931762695</v>
       </c>
       <c r="H5" t="n">
         <v>1381959</v>
@@ -572,7 +572,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G7" t="n">
-        <v>18.2498111724854</v>
+        <v>18.249813079834</v>
       </c>
       <c r="H7" t="n">
         <v>1189444</v>
@@ -601,7 +601,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G8" t="n">
-        <v>19.4086742401123</v>
+        <v>19.4086723327637</v>
       </c>
       <c r="H8" t="n">
         <v>2266409</v>
@@ -630,7 +630,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G9" t="n">
-        <v>19.1344356536865</v>
+        <v>19.1344394683838</v>
       </c>
       <c r="H9" t="n">
         <v>1367537</v>
@@ -688,7 +688,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G11" t="n">
-        <v>18.462121963501</v>
+        <v>18.4621238708496</v>
       </c>
       <c r="H11" t="n">
         <v>802632</v>
@@ -717,7 +717,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G12" t="n">
-        <v>18.2851963043213</v>
+        <v>18.2851982116699</v>
       </c>
       <c r="H12" t="n">
         <v>939035</v>
@@ -920,7 +920,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>18.2232761383057</v>
+        <v>18.2232723236084</v>
       </c>
       <c r="H19" t="n">
         <v>550218</v>
@@ -949,7 +949,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>17.7632713317871</v>
+        <v>17.7632694244385</v>
       </c>
       <c r="H20" t="n">
         <v>1244898</v>
@@ -1036,7 +1036,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>17.9578838348389</v>
+        <v>17.9578876495361</v>
       </c>
       <c r="H23" t="n">
         <v>725076</v>
@@ -1065,7 +1065,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G24" t="n">
-        <v>18.2055797576904</v>
+        <v>18.2055835723877</v>
       </c>
       <c r="H24" t="n">
         <v>1897967</v>
@@ -1094,7 +1094,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G25" t="n">
-        <v>18.2586574554443</v>
+        <v>18.2586555480957</v>
       </c>
       <c r="H25" t="n">
         <v>716525</v>
@@ -1123,7 +1123,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G26" t="n">
-        <v>18.0817356109619</v>
+        <v>18.0817337036133</v>
       </c>
       <c r="H26" t="n">
         <v>1482038</v>
@@ -1210,7 +1210,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>17.1617240905762</v>
+        <v>17.1617221832275</v>
       </c>
       <c r="H29" t="n">
         <v>741895</v>
@@ -1239,7 +1239,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G30" t="n">
-        <v>16.6486434936523</v>
+        <v>16.6486415863037</v>
       </c>
       <c r="H30" t="n">
         <v>1048393</v>
@@ -1268,7 +1268,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G31" t="n">
-        <v>17.0201835632324</v>
+        <v>17.0201816558838</v>
       </c>
       <c r="H31" t="n">
         <v>474221</v>
@@ -1297,7 +1297,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G32" t="n">
-        <v>17.48903465271</v>
+        <v>17.4890365600586</v>
       </c>
       <c r="H32" t="n">
         <v>658925</v>
@@ -1442,7 +1442,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>18.9752044677734</v>
+        <v>18.9752063751221</v>
       </c>
       <c r="H37" t="n">
         <v>534225</v>
@@ -1471,7 +1471,7 @@
         <v>20.5</v>
       </c>
       <c r="G38" t="n">
-        <v>18.1348133087158</v>
+        <v>18.1348114013672</v>
       </c>
       <c r="H38" t="n">
         <v>591716</v>
@@ -1529,7 +1529,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G40" t="n">
-        <v>17.7632713317871</v>
+        <v>17.7632694244385</v>
       </c>
       <c r="H40" t="n">
         <v>488362</v>
@@ -1558,7 +1558,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G41" t="n">
-        <v>17.9048080444336</v>
+        <v>17.9048099517822</v>
       </c>
       <c r="H41" t="n">
         <v>422135</v>
@@ -1587,7 +1587,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G42" t="n">
-        <v>18.3471221923828</v>
+        <v>18.3471202850342</v>
       </c>
       <c r="H42" t="n">
         <v>557658</v>
@@ -1616,7 +1616,7 @@
         <v>21.5</v>
       </c>
       <c r="G43" t="n">
-        <v>19.019437789917</v>
+        <v>19.0194358825684</v>
       </c>
       <c r="H43" t="n">
         <v>1151116</v>
@@ -1703,7 +1703,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G46" t="n">
-        <v>19.3113613128662</v>
+        <v>19.3113632202148</v>
       </c>
       <c r="H46" t="n">
         <v>602537</v>
@@ -1761,7 +1761,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>19.9482917785645</v>
+        <v>19.9482936859131</v>
       </c>
       <c r="H48" t="n">
         <v>1078018</v>
@@ -1790,7 +1790,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>19.7271366119385</v>
+        <v>19.7271347045898</v>
       </c>
       <c r="H49" t="n">
         <v>805952</v>
@@ -2022,7 +2022,7 @@
         <v>22.8099994659424</v>
       </c>
       <c r="G57" t="n">
-        <v>20.1782932281494</v>
+        <v>20.178295135498</v>
       </c>
       <c r="H57" t="n">
         <v>734678</v>
@@ -2051,7 +2051,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G58" t="n">
-        <v>19.4971370697021</v>
+        <v>19.4971332550049</v>
       </c>
       <c r="H58" t="n">
         <v>1161092</v>
@@ -2109,7 +2109,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G60" t="n">
-        <v>18.9663581848145</v>
+        <v>18.9663562774658</v>
       </c>
       <c r="H60" t="n">
         <v>524013</v>
@@ -2138,7 +2138,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G61" t="n">
-        <v>19.4794387817383</v>
+        <v>19.4794406890869</v>
       </c>
       <c r="H61" t="n">
         <v>502164</v>
@@ -2196,7 +2196,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G63" t="n">
-        <v>19.8686752319336</v>
+        <v>19.868673324585</v>
       </c>
       <c r="H63" t="n">
         <v>732706</v>
@@ -2225,7 +2225,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G64" t="n">
-        <v>19.4971370697021</v>
+        <v>19.4971332550049</v>
       </c>
       <c r="H64" t="n">
         <v>538910</v>
@@ -2254,7 +2254,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G65" t="n">
-        <v>19.4175186157227</v>
+        <v>19.417516708374</v>
       </c>
       <c r="H65" t="n">
         <v>289674</v>
@@ -2312,7 +2312,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G67" t="n">
-        <v>18.833667755127</v>
+        <v>18.8336658477783</v>
       </c>
       <c r="H67" t="n">
         <v>490898</v>
@@ -2341,7 +2341,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G68" t="n">
-        <v>18.5151977539062</v>
+        <v>18.5151996612549</v>
       </c>
       <c r="H68" t="n">
         <v>449428</v>
@@ -2370,7 +2370,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>18.9309749603271</v>
+        <v>18.9309730529785</v>
       </c>
       <c r="H69" t="n">
         <v>499244</v>
@@ -2399,7 +2399,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G70" t="n">
-        <v>18.8955898284912</v>
+        <v>18.8955917358398</v>
       </c>
       <c r="H70" t="n">
         <v>395996</v>
@@ -2428,7 +2428,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G71" t="n">
-        <v>18.5240497589111</v>
+        <v>18.5240478515625</v>
       </c>
       <c r="H71" t="n">
         <v>1288923</v>
@@ -2457,7 +2457,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G72" t="n">
-        <v>19.3113613128662</v>
+        <v>19.3113632202148</v>
       </c>
       <c r="H72" t="n">
         <v>724111</v>
@@ -2486,7 +2486,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>18.9486656188965</v>
+        <v>18.9486675262451</v>
       </c>
       <c r="H73" t="n">
         <v>659167</v>
@@ -2544,7 +2544,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G75" t="n">
-        <v>18.8778953552246</v>
+        <v>18.877893447876</v>
       </c>
       <c r="H75" t="n">
         <v>347479</v>
@@ -2602,7 +2602,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G77" t="n">
-        <v>18.8071269989014</v>
+        <v>18.8071250915527</v>
       </c>
       <c r="H77" t="n">
         <v>725644</v>
@@ -2718,7 +2718,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G81" t="n">
-        <v>18.0817356109619</v>
+        <v>18.0817337036133</v>
       </c>
       <c r="H81" t="n">
         <v>609476</v>
@@ -2747,7 +2747,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G82" t="n">
-        <v>18.0640411376953</v>
+        <v>18.0640392303467</v>
       </c>
       <c r="H82" t="n">
         <v>264849</v>
@@ -2776,7 +2776,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>18.3117370605469</v>
+        <v>18.3117351531982</v>
       </c>
       <c r="H83" t="n">
         <v>593433</v>
@@ -2863,7 +2863,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G86" t="n">
-        <v>17.7190380096436</v>
+        <v>17.7190399169922</v>
       </c>
       <c r="H86" t="n">
         <v>401376</v>
@@ -2892,7 +2892,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G87" t="n">
-        <v>17.9048080444336</v>
+        <v>17.9048099517822</v>
       </c>
       <c r="H87" t="n">
         <v>346687</v>
@@ -2921,7 +2921,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G88" t="n">
-        <v>17.4448013305664</v>
+        <v>17.444803237915</v>
       </c>
       <c r="H88" t="n">
         <v>546914</v>
@@ -2950,7 +2950,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G89" t="n">
-        <v>17.1440277099609</v>
+        <v>17.1440296173096</v>
       </c>
       <c r="H89" t="n">
         <v>741696</v>
@@ -2979,7 +2979,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G90" t="n">
-        <v>17.5509567260742</v>
+        <v>17.5509586334229</v>
       </c>
       <c r="H90" t="n">
         <v>721711</v>
@@ -3095,7 +3095,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G94" t="n">
-        <v>18.833667755127</v>
+        <v>18.8336658477783</v>
       </c>
       <c r="H94" t="n">
         <v>1861606</v>
@@ -3153,7 +3153,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>18.0640411376953</v>
+        <v>18.0640392303467</v>
       </c>
       <c r="H96" t="n">
         <v>670991</v>
@@ -3182,7 +3182,7 @@
         <v>20.2700004577637</v>
       </c>
       <c r="G97" t="n">
-        <v>17.9313488006592</v>
+        <v>17.9313468933105</v>
       </c>
       <c r="H97" t="n">
         <v>352423</v>
@@ -3240,7 +3240,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G99" t="n">
-        <v>17.6482696533203</v>
+        <v>17.6482677459717</v>
       </c>
       <c r="H99" t="n">
         <v>692686</v>
@@ -3298,7 +3298,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G101" t="n">
-        <v>17.8112602233887</v>
+        <v>17.8112564086914</v>
       </c>
       <c r="H101" t="n">
         <v>334331</v>
@@ -3327,7 +3327,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G102" t="n">
-        <v>17.702600479126</v>
+        <v>17.7025985717773</v>
       </c>
       <c r="H102" t="n">
         <v>848652</v>
@@ -3385,7 +3385,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G104" t="n">
-        <v>17.530553817749</v>
+        <v>17.5305519104004</v>
       </c>
       <c r="H104" t="n">
         <v>453269</v>
@@ -3559,7 +3559,7 @@
         <v>19.25</v>
       </c>
       <c r="G110" t="n">
-        <v>17.430944442749</v>
+        <v>17.4309463500977</v>
       </c>
       <c r="H110" t="n">
         <v>645536</v>
@@ -3588,7 +3588,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G111" t="n">
-        <v>17.485279083252</v>
+        <v>17.4852752685547</v>
       </c>
       <c r="H111" t="n">
         <v>582475</v>
@@ -3762,7 +3762,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G117" t="n">
-        <v>17.0415802001953</v>
+        <v>17.0415782928467</v>
       </c>
       <c r="H117" t="n">
         <v>604342</v>
@@ -3791,7 +3791,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G118" t="n">
-        <v>17.0778026580811</v>
+        <v>17.0778007507324</v>
       </c>
       <c r="H118" t="n">
         <v>634094</v>
@@ -3878,7 +3878,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G121" t="n">
-        <v>17.7297649383545</v>
+        <v>17.7297611236572</v>
       </c>
       <c r="H121" t="n">
         <v>523740</v>
@@ -3936,7 +3936,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G123" t="n">
-        <v>18.1825160980225</v>
+        <v>18.1825141906738</v>
       </c>
       <c r="H123" t="n">
         <v>467685</v>
@@ -3965,7 +3965,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G124" t="n">
-        <v>16.8514251708984</v>
+        <v>16.8514232635498</v>
       </c>
       <c r="H124" t="n">
         <v>1162990</v>
@@ -4023,7 +4023,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G126" t="n">
-        <v>16.6793766021729</v>
+        <v>16.6793785095215</v>
       </c>
       <c r="H126" t="n">
         <v>635006</v>
@@ -4081,7 +4081,7 @@
         <v>18.25</v>
       </c>
       <c r="G128" t="n">
-        <v>16.5254402160645</v>
+        <v>16.5254440307617</v>
       </c>
       <c r="H128" t="n">
         <v>558415</v>
@@ -4110,7 +4110,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>16.6069393157959</v>
+        <v>16.6069374084473</v>
       </c>
       <c r="H129" t="n">
         <v>464956</v>
@@ -4168,7 +4168,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G131" t="n">
-        <v>16.8242568969727</v>
+        <v>16.8242588043213</v>
       </c>
       <c r="H131" t="n">
         <v>503139</v>
@@ -4197,7 +4197,7 @@
         <v>17.75</v>
       </c>
       <c r="G132" t="n">
-        <v>16.0726928710938</v>
+        <v>16.0726909637451</v>
       </c>
       <c r="H132" t="n">
         <v>575432</v>
@@ -4284,7 +4284,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G135" t="n">
-        <v>16.4439468383789</v>
+        <v>16.4439487457275</v>
       </c>
       <c r="H135" t="n">
         <v>444582</v>
@@ -4342,7 +4342,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G137" t="n">
-        <v>17.095911026001</v>
+        <v>17.0959072113037</v>
       </c>
       <c r="H137" t="n">
         <v>684185</v>
@@ -4400,7 +4400,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G139" t="n">
-        <v>17.0868587493896</v>
+        <v>17.0868530273438</v>
       </c>
       <c r="H139" t="n">
         <v>861033</v>
@@ -4458,7 +4458,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>17.0325241088867</v>
+        <v>17.0325260162354</v>
       </c>
       <c r="H141" t="n">
         <v>247627</v>
@@ -4487,7 +4487,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>17.3403949737549</v>
+        <v>17.3403930664062</v>
       </c>
       <c r="H142" t="n">
         <v>734812</v>
@@ -4574,7 +4574,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G145" t="n">
-        <v>18.1372394561768</v>
+        <v>18.1372413635254</v>
       </c>
       <c r="H145" t="n">
         <v>615453</v>
@@ -4632,7 +4632,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G147" t="n">
-        <v>18.771089553833</v>
+        <v>18.7710914611816</v>
       </c>
       <c r="H147" t="n">
         <v>1164581</v>
@@ -4690,7 +4690,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G149" t="n">
-        <v>19.0699100494385</v>
+        <v>19.0699081420898</v>
       </c>
       <c r="H149" t="n">
         <v>1159289</v>
@@ -4777,7 +4777,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G152" t="n">
-        <v>18.4994430541992</v>
+        <v>18.4994411468506</v>
       </c>
       <c r="H152" t="n">
         <v>1504019</v>
@@ -4864,7 +4864,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G155" t="n">
-        <v>18.580940246582</v>
+        <v>18.5809383392334</v>
       </c>
       <c r="H155" t="n">
         <v>402078</v>
@@ -4893,7 +4893,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G156" t="n">
-        <v>18.762035369873</v>
+        <v>18.7620372772217</v>
       </c>
       <c r="H156" t="n">
         <v>454171</v>
@@ -4922,7 +4922,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G157" t="n">
-        <v>18.4994430541992</v>
+        <v>18.4994411468506</v>
       </c>
       <c r="H157" t="n">
         <v>593471</v>
@@ -4951,7 +4951,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G158" t="n">
-        <v>18.8073139190674</v>
+        <v>18.807315826416</v>
       </c>
       <c r="H158" t="n">
         <v>652271</v>
@@ -5009,7 +5009,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G160" t="n">
-        <v>19.04274559021</v>
+        <v>19.0427436828613</v>
       </c>
       <c r="H160" t="n">
         <v>612736</v>
@@ -5096,7 +5096,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>18.4722747802734</v>
+        <v>18.4722766876221</v>
       </c>
       <c r="H163" t="n">
         <v>404764</v>
@@ -5183,7 +5183,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>18.9703025817871</v>
+        <v>18.9703044891357</v>
       </c>
       <c r="H166" t="n">
         <v>796139</v>
@@ -5241,7 +5241,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G168" t="n">
-        <v>18.6081027984619</v>
+        <v>18.6080989837646</v>
       </c>
       <c r="H168" t="n">
         <v>405254</v>
@@ -5270,7 +5270,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6533794403076</v>
+        <v>18.6533756256104</v>
       </c>
       <c r="H169" t="n">
         <v>409770</v>
@@ -5357,7 +5357,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>18.6081027984619</v>
+        <v>18.6080989837646</v>
       </c>
       <c r="H172" t="n">
         <v>495370</v>
@@ -5415,7 +5415,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>18.6986484527588</v>
+        <v>18.6986503601074</v>
       </c>
       <c r="H174" t="n">
         <v>355898</v>
@@ -5444,7 +5444,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G175" t="n">
-        <v>18.762035369873</v>
+        <v>18.7620372772217</v>
       </c>
       <c r="H175" t="n">
         <v>290570</v>
@@ -5473,7 +5473,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>19.106128692627</v>
+        <v>19.1061305999756</v>
       </c>
       <c r="H176" t="n">
         <v>842459</v>
@@ -5502,7 +5502,7 @@
         <v>22</v>
       </c>
       <c r="G177" t="n">
-        <v>19.9210815429688</v>
+        <v>19.9210796356201</v>
       </c>
       <c r="H177" t="n">
         <v>1987857</v>
@@ -5560,7 +5560,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>19.5588798522949</v>
+        <v>19.5588817596436</v>
       </c>
       <c r="H179" t="n">
         <v>770378</v>
@@ -5618,7 +5618,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G181" t="n">
-        <v>19.3143939971924</v>
+        <v>19.314395904541</v>
       </c>
       <c r="H181" t="n">
         <v>672599</v>
@@ -5734,7 +5734,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G185" t="n">
-        <v>18.771089553833</v>
+        <v>18.7710914611816</v>
       </c>
       <c r="H185" t="n">
         <v>702087</v>
@@ -5850,7 +5850,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>20.3557243347168</v>
+        <v>20.3557224273682</v>
       </c>
       <c r="H189" t="n">
         <v>758570</v>
@@ -5937,7 +5937,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>20.3919429779053</v>
+        <v>20.3919448852539</v>
       </c>
       <c r="H192" t="n">
         <v>676988</v>
@@ -5995,7 +5995,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G194" t="n">
-        <v>20.3557243347168</v>
+        <v>20.3557224273682</v>
       </c>
       <c r="H194" t="n">
         <v>517237</v>
@@ -6024,7 +6024,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>20.6907596588135</v>
+        <v>20.6907577514648</v>
       </c>
       <c r="H195" t="n">
         <v>495248</v>
@@ -6053,7 +6053,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>20.8446979522705</v>
+        <v>20.8446941375732</v>
       </c>
       <c r="H196" t="n">
         <v>733993</v>
@@ -6140,7 +6140,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G199" t="n">
-        <v>20.1021842956543</v>
+        <v>20.1021823883057</v>
       </c>
       <c r="H199" t="n">
         <v>693101</v>
@@ -6227,7 +6227,7 @@
         <v>22.6900005340576</v>
       </c>
       <c r="G202" t="n">
-        <v>20.5458793640137</v>
+        <v>20.5458812713623</v>
       </c>
       <c r="H202" t="n">
         <v>571600</v>
@@ -6343,7 +6343,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G206" t="n">
-        <v>20.2651710510254</v>
+        <v>20.265172958374</v>
       </c>
       <c r="H206" t="n">
         <v>579770</v>
@@ -6372,7 +6372,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>20.3285579681396</v>
+        <v>20.3285598754883</v>
       </c>
       <c r="H207" t="n">
         <v>362070</v>
@@ -6401,7 +6401,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G208" t="n">
-        <v>20.3557243347168</v>
+        <v>20.3557224273682</v>
       </c>
       <c r="H208" t="n">
         <v>427306</v>
@@ -6459,7 +6459,7 @@
         <v>22.25</v>
       </c>
       <c r="G210" t="n">
-        <v>20.1474609375</v>
+        <v>20.1474590301514</v>
       </c>
       <c r="H210" t="n">
         <v>323432</v>
@@ -6488,7 +6488,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G211" t="n">
-        <v>20.2289524078369</v>
+        <v>20.2289543151855</v>
       </c>
       <c r="H211" t="n">
         <v>476244</v>
@@ -6633,7 +6633,7 @@
         <v>21.5900001525879</v>
       </c>
       <c r="G216" t="n">
-        <v>19.5498237609863</v>
+        <v>19.549825668335</v>
       </c>
       <c r="H216" t="n">
         <v>443300</v>
@@ -6662,7 +6662,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G217" t="n">
-        <v>19.4140014648438</v>
+        <v>19.4139995574951</v>
       </c>
       <c r="H217" t="n">
         <v>328652</v>
@@ -6720,7 +6720,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G219" t="n">
-        <v>19.7218742370605</v>
+        <v>19.7218704223633</v>
       </c>
       <c r="H219" t="n">
         <v>366831</v>
@@ -6778,7 +6778,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G221" t="n">
-        <v>19.5226593017578</v>
+        <v>19.5226612091064</v>
       </c>
       <c r="H221" t="n">
         <v>845010</v>
@@ -6807,7 +6807,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>19.830530166626</v>
+        <v>19.8305320739746</v>
       </c>
       <c r="H222" t="n">
         <v>720123</v>
@@ -6865,7 +6865,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G224" t="n">
-        <v>19.7490367889404</v>
+        <v>19.7490348815918</v>
       </c>
       <c r="H224" t="n">
         <v>454641</v>
@@ -6894,7 +6894,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.4722747802734</v>
+        <v>18.4722766876221</v>
       </c>
       <c r="H225" t="n">
         <v>3206760</v>
@@ -6923,7 +6923,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G226" t="n">
-        <v>18.0919647216797</v>
+        <v>18.0919666290283</v>
       </c>
       <c r="H226" t="n">
         <v>1188113</v>
@@ -6981,7 +6981,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G228" t="n">
-        <v>18.3273944854736</v>
+        <v>18.3273963928223</v>
       </c>
       <c r="H228" t="n">
         <v>773547</v>
@@ -7068,7 +7068,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G231" t="n">
-        <v>17.7388191223145</v>
+        <v>17.7388172149658</v>
       </c>
       <c r="H231" t="n">
         <v>492945</v>
@@ -7097,7 +7097,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G232" t="n">
-        <v>17.8565349578857</v>
+        <v>17.8565330505371</v>
       </c>
       <c r="H232" t="n">
         <v>279823</v>
@@ -7126,7 +7126,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>17.8203125</v>
+        <v>17.8203105926514</v>
       </c>
       <c r="H233" t="n">
         <v>203127</v>
@@ -7213,7 +7213,7 @@
         <v>20.3099994659424</v>
       </c>
       <c r="G236" t="n">
-        <v>18.3907794952393</v>
+        <v>18.3907814025879</v>
       </c>
       <c r="H236" t="n">
         <v>402506</v>
@@ -7242,7 +7242,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G237" t="n">
-        <v>18.8073139190674</v>
+        <v>18.807315826416</v>
       </c>
       <c r="H237" t="n">
         <v>711240</v>
@@ -7329,7 +7329,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>19.151403427124</v>
+        <v>19.1514053344727</v>
       </c>
       <c r="H240" t="n">
         <v>521430</v>
@@ -7358,7 +7358,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>19.2872295379639</v>
+        <v>19.2872276306152</v>
       </c>
       <c r="H241" t="n">
         <v>673068</v>
@@ -7416,7 +7416,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>19.3777809143066</v>
+        <v>19.377779006958</v>
       </c>
       <c r="H243" t="n">
         <v>365522</v>
@@ -7445,7 +7445,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G244" t="n">
-        <v>19.1151866912842</v>
+        <v>19.1151847839355</v>
       </c>
       <c r="H244" t="n">
         <v>413169</v>
@@ -7474,7 +7474,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G245" t="n">
-        <v>19.5860443115234</v>
+        <v>19.5860462188721</v>
       </c>
       <c r="H245" t="n">
         <v>394277</v>
@@ -7503,7 +7503,7 @@
         <v>21.2700004577637</v>
       </c>
       <c r="G246" t="n">
-        <v>19.260066986084</v>
+        <v>19.2600650787354</v>
       </c>
       <c r="H246" t="n">
         <v>348399</v>
@@ -7561,7 +7561,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G248" t="n">
-        <v>20.2651710510254</v>
+        <v>20.265172958374</v>
       </c>
       <c r="H248" t="n">
         <v>1423797</v>
@@ -7590,7 +7590,7 @@
         <v>22.5</v>
       </c>
       <c r="G249" t="n">
-        <v>20.3738346099854</v>
+        <v>20.373836517334</v>
       </c>
       <c r="H249" t="n">
         <v>417900</v>
@@ -7619,7 +7619,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G250" t="n">
-        <v>20.2651710510254</v>
+        <v>20.265172958374</v>
       </c>
       <c r="H250" t="n">
         <v>491157</v>
@@ -7648,7 +7648,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G251" t="n">
-        <v>20.3466682434082</v>
+        <v>20.3466663360596</v>
       </c>
       <c r="H251" t="n">
         <v>359013</v>
@@ -7677,7 +7677,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>20.2380065917969</v>
+        <v>20.2380104064941</v>
       </c>
       <c r="H252" t="n">
         <v>230612</v>
@@ -7706,7 +7706,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G253" t="n">
-        <v>20.1293487548828</v>
+        <v>20.1293468475342</v>
       </c>
       <c r="H253" t="n">
         <v>311609</v>
@@ -7764,7 +7764,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>20.2289524078369</v>
+        <v>20.2289543151855</v>
       </c>
       <c r="H255" t="n">
         <v>284063</v>
@@ -7851,7 +7851,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G258" t="n">
-        <v>20.8084774017334</v>
+        <v>20.8084754943848</v>
       </c>
       <c r="H258" t="n">
         <v>291448</v>
@@ -7880,7 +7880,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G259" t="n">
-        <v>20.6183204650879</v>
+        <v>20.6183223724365</v>
       </c>
       <c r="H259" t="n">
         <v>666000</v>
@@ -7909,7 +7909,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G260" t="n">
-        <v>21.4785480499268</v>
+        <v>21.4785461425781</v>
       </c>
       <c r="H260" t="n">
         <v>1705785</v>
@@ -7967,7 +7967,7 @@
         <v>24.3700008392334</v>
       </c>
       <c r="G262" t="n">
-        <v>22.0671272277832</v>
+        <v>22.0671291351318</v>
       </c>
       <c r="H262" t="n">
         <v>1062423</v>
@@ -7996,7 +7996,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G263" t="n">
-        <v>22.0580730438232</v>
+        <v>22.0580711364746</v>
       </c>
       <c r="H263" t="n">
         <v>1362031</v>
@@ -8025,7 +8025,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G264" t="n">
-        <v>22.2572822570801</v>
+        <v>22.2572803497314</v>
       </c>
       <c r="H264" t="n">
         <v>869802</v>
@@ -8054,7 +8054,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G265" t="n">
-        <v>22.2935047149658</v>
+        <v>22.2935028076172</v>
       </c>
       <c r="H265" t="n">
         <v>1130923</v>
@@ -8083,7 +8083,7 @@
         <v>24.6299991607666</v>
       </c>
       <c r="G266" t="n">
-        <v>22.3025569915771</v>
+        <v>22.3025550842285</v>
       </c>
       <c r="H266" t="n">
         <v>604896</v>
@@ -8228,7 +8228,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G271" t="n">
-        <v>23.0722370147705</v>
+        <v>23.0722332000732</v>
       </c>
       <c r="H271" t="n">
         <v>906513</v>
@@ -8286,7 +8286,7 @@
         <v>25.5699996948242</v>
       </c>
       <c r="G273" t="n">
-        <v>23.1537322998047</v>
+        <v>23.1537303924561</v>
       </c>
       <c r="H273" t="n">
         <v>1005467</v>
@@ -8431,7 +8431,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G278" t="n">
-        <v>22.1757850646973</v>
+        <v>22.1757869720459</v>
       </c>
       <c r="H278" t="n">
         <v>1066573</v>
@@ -8547,7 +8547,7 @@
         <v>26.6399993896484</v>
       </c>
       <c r="G282" t="n">
-        <v>24.1226196289062</v>
+        <v>24.1226215362549</v>
       </c>
       <c r="H282" t="n">
         <v>1541926</v>
@@ -8605,7 +8605,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G284" t="n">
-        <v>23.6879787445068</v>
+        <v>23.6879768371582</v>
       </c>
       <c r="H284" t="n">
         <v>648062</v>
@@ -8634,7 +8634,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>23.561206817627</v>
+        <v>23.5612049102783</v>
       </c>
       <c r="H285" t="n">
         <v>619704</v>
@@ -8663,7 +8663,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G286" t="n">
-        <v>23.561206817627</v>
+        <v>23.5612049102783</v>
       </c>
       <c r="H286" t="n">
         <v>555021</v>
@@ -8692,7 +8692,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G287" t="n">
-        <v>23.7423057556152</v>
+        <v>23.7423076629639</v>
       </c>
       <c r="H287" t="n">
         <v>609350</v>
@@ -8721,7 +8721,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>23.7241973876953</v>
+        <v>23.7241992950439</v>
       </c>
       <c r="H288" t="n">
         <v>395279</v>
@@ -8750,7 +8750,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>23.6336498260498</v>
+        <v>23.6336479187012</v>
       </c>
       <c r="H289" t="n">
         <v>404847</v>
@@ -8779,7 +8779,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>23.6879787445068</v>
+        <v>23.6879768371582</v>
       </c>
       <c r="H290" t="n">
         <v>721884</v>
@@ -8837,7 +8837,7 @@
         <v>26.1700000762939</v>
       </c>
       <c r="G292" t="n">
-        <v>23.6970329284668</v>
+        <v>23.6970310211182</v>
       </c>
       <c r="H292" t="n">
         <v>236982</v>
@@ -8866,7 +8866,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G293" t="n">
-        <v>23.7241973876953</v>
+        <v>23.7241992950439</v>
       </c>
       <c r="H293" t="n">
         <v>138589</v>
@@ -8895,7 +8895,7 @@
         <v>26.5200004577637</v>
       </c>
       <c r="G294" t="n">
-        <v>24.0139617919922</v>
+        <v>24.0139579772949</v>
       </c>
       <c r="H294" t="n">
         <v>741091</v>
@@ -8953,7 +8953,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>24.068286895752</v>
+        <v>24.0682907104492</v>
       </c>
       <c r="H296" t="n">
         <v>653226</v>
@@ -8982,7 +8982,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>23.9777355194092</v>
+        <v>23.9777374267578</v>
       </c>
       <c r="H297" t="n">
         <v>812325</v>
@@ -9098,7 +9098,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>24.7655258178711</v>
+        <v>24.7655277252197</v>
       </c>
       <c r="H301" t="n">
         <v>889832</v>
@@ -9127,7 +9127,7 @@
         <v>27.8199996948242</v>
       </c>
       <c r="G302" t="n">
-        <v>25.1911125183105</v>
+        <v>25.1911144256592</v>
       </c>
       <c r="H302" t="n">
         <v>596382</v>
@@ -9214,7 +9214,7 @@
         <v>28.2900009155273</v>
       </c>
       <c r="G305" t="n">
-        <v>25.6167011260986</v>
+        <v>25.6167030334473</v>
       </c>
       <c r="H305" t="n">
         <v>800161</v>
@@ -9243,7 +9243,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>25.6710300445557</v>
+        <v>25.6710319519043</v>
       </c>
       <c r="H306" t="n">
         <v>500694</v>
@@ -9272,7 +9272,7 @@
         <v>28.3299999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>25.6529197692871</v>
+        <v>25.6529216766357</v>
       </c>
       <c r="H307" t="n">
         <v>363150</v>
@@ -9417,7 +9417,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>25.0643424987793</v>
+        <v>25.0643444061279</v>
       </c>
       <c r="H312" t="n">
         <v>650689</v>
@@ -9446,7 +9446,7 @@
         <v>27.3899993896484</v>
       </c>
       <c r="G313" t="n">
-        <v>24.8017463684082</v>
+        <v>24.8017482757568</v>
       </c>
       <c r="H313" t="n">
         <v>332263</v>
@@ -9533,7 +9533,7 @@
         <v>28.0200004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>25.3722152709961</v>
+        <v>25.3722133636475</v>
       </c>
       <c r="H316" t="n">
         <v>452765</v>
@@ -9562,7 +9562,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>25.6257514953613</v>
+        <v>25.62575340271</v>
       </c>
       <c r="H317" t="n">
         <v>349361</v>
@@ -9591,7 +9591,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G318" t="n">
-        <v>25.2273330688477</v>
+        <v>25.2273349761963</v>
       </c>
       <c r="H318" t="n">
         <v>385409</v>
@@ -9620,7 +9620,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>25.1730041503906</v>
+        <v>25.173002243042</v>
       </c>
       <c r="H319" t="n">
         <v>545914</v>
@@ -9794,7 +9794,7 @@
         <v>27.75</v>
       </c>
       <c r="G325" t="n">
-        <v>25.1277294158936</v>
+        <v>25.1277275085449</v>
       </c>
       <c r="H325" t="n">
         <v>265673</v>
@@ -9852,7 +9852,7 @@
         <v>28.2099990844727</v>
       </c>
       <c r="G327" t="n">
-        <v>25.5442600250244</v>
+        <v>25.5442581176758</v>
       </c>
       <c r="H327" t="n">
         <v>365212</v>
@@ -9968,7 +9968,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>25.0824527740479</v>
+        <v>25.0824565887451</v>
       </c>
       <c r="H331" t="n">
         <v>429583</v>
@@ -9997,7 +9997,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G332" t="n">
-        <v>24.7836380004883</v>
+        <v>24.7836360931396</v>
       </c>
       <c r="H332" t="n">
         <v>660230</v>
@@ -10026,7 +10026,7 @@
         <v>26.9699993133545</v>
       </c>
       <c r="G333" t="n">
-        <v>24.4214324951172</v>
+        <v>24.4214344024658</v>
       </c>
       <c r="H333" t="n">
         <v>775708</v>
@@ -10055,7 +10055,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>24.7655258178711</v>
+        <v>24.7655277252197</v>
       </c>
       <c r="H334" t="n">
         <v>653524</v>
@@ -10084,7 +10084,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>24.2674999237061</v>
+        <v>24.2674980163574</v>
       </c>
       <c r="H335" t="n">
         <v>589692</v>
@@ -10113,7 +10113,7 @@
         <v>27.8199996948242</v>
       </c>
       <c r="G336" t="n">
-        <v>25.1911125183105</v>
+        <v>25.1911144256592</v>
       </c>
       <c r="H336" t="n">
         <v>667783</v>
@@ -10200,7 +10200,7 @@
         <v>28.9200000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>26.1871700286865</v>
+        <v>26.1871662139893</v>
       </c>
       <c r="H339" t="n">
         <v>548992</v>
@@ -10258,7 +10258,7 @@
         <v>29.25</v>
       </c>
       <c r="G341" t="n">
-        <v>26.4859848022461</v>
+        <v>26.4859828948975</v>
       </c>
       <c r="H341" t="n">
         <v>324279</v>
@@ -10287,7 +10287,7 @@
         <v>29.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>26.3229923248291</v>
+        <v>26.3229942321777</v>
       </c>
       <c r="H342" t="n">
         <v>296838</v>
@@ -10316,7 +10316,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G343" t="n">
-        <v>26.676139831543</v>
+        <v>26.6761379241943</v>
       </c>
       <c r="H343" t="n">
         <v>498694</v>
@@ -10345,7 +10345,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>26.8934631347656</v>
+        <v>26.893461227417</v>
       </c>
       <c r="H344" t="n">
         <v>349802</v>
@@ -10374,7 +10374,7 @@
         <v>29</v>
       </c>
       <c r="G345" t="n">
-        <v>26.2596092224121</v>
+        <v>26.2596073150635</v>
       </c>
       <c r="H345" t="n">
         <v>806664</v>
@@ -10403,7 +10403,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>26.667085647583</v>
+        <v>26.6670837402344</v>
       </c>
       <c r="H346" t="n">
         <v>297569</v>
@@ -10490,7 +10490,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G349" t="n">
-        <v>26.6036968231201</v>
+        <v>26.6036987304688</v>
       </c>
       <c r="H349" t="n">
         <v>284270</v>
@@ -10519,7 +10519,7 @@
         <v>29.3700008392334</v>
       </c>
       <c r="G350" t="n">
-        <v>26.5946445465088</v>
+        <v>26.5946464538574</v>
       </c>
       <c r="H350" t="n">
         <v>150195</v>
@@ -10548,7 +10548,7 @@
         <v>29</v>
       </c>
       <c r="G351" t="n">
-        <v>26.2596092224121</v>
+        <v>26.2596073150635</v>
       </c>
       <c r="H351" t="n">
         <v>536086</v>
@@ -10577,7 +10577,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G352" t="n">
-        <v>25.3088321685791</v>
+        <v>25.3088302612305</v>
       </c>
       <c r="H352" t="n">
         <v>476271</v>
@@ -10664,7 +10664,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G355" t="n">
-        <v>25.8984451293945</v>
+        <v>25.8984432220459</v>
       </c>
       <c r="H355" t="n">
         <v>233836</v>
@@ -10751,7 +10751,7 @@
         <v>25.6599998474121</v>
       </c>
       <c r="G358" t="n">
-        <v>23.6159954071045</v>
+        <v>23.6159934997559</v>
       </c>
       <c r="H358" t="n">
         <v>2202691</v>
@@ -10780,7 +10780,7 @@
         <v>25.2299995422363</v>
       </c>
       <c r="G359" t="n">
-        <v>23.2202472686768</v>
+        <v>23.2202453613281</v>
       </c>
       <c r="H359" t="n">
         <v>2339992</v>
@@ -10809,7 +10809,7 @@
         <v>25.1299991607666</v>
       </c>
       <c r="G360" t="n">
-        <v>23.1282138824463</v>
+        <v>23.1282119750977</v>
       </c>
       <c r="H360" t="n">
         <v>474720</v>
@@ -10838,7 +10838,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>22.9625492095947</v>
+        <v>22.9625511169434</v>
       </c>
       <c r="H361" t="n">
         <v>858119</v>
@@ -10867,7 +10867,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>22.8705158233643</v>
+        <v>22.8705177307129</v>
       </c>
       <c r="H362" t="n">
         <v>814408</v>
@@ -10896,7 +10896,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G363" t="n">
-        <v>22.8613147735596</v>
+        <v>22.8613128662109</v>
       </c>
       <c r="H363" t="n">
         <v>526890</v>
@@ -10925,7 +10925,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G364" t="n">
-        <v>23.266263961792</v>
+        <v>23.2662658691406</v>
       </c>
       <c r="H364" t="n">
         <v>816109</v>
@@ -11012,7 +11012,7 @@
         <v>24.8700008392334</v>
       </c>
       <c r="G367" t="n">
-        <v>22.8889255523682</v>
+        <v>22.8889236450195</v>
       </c>
       <c r="H367" t="n">
         <v>383043</v>
@@ -11070,7 +11070,7 @@
         <v>24.25</v>
       </c>
       <c r="G369" t="n">
-        <v>22.3183097839355</v>
+        <v>22.3183116912842</v>
       </c>
       <c r="H369" t="n">
         <v>652180</v>
@@ -11128,7 +11128,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G371" t="n">
-        <v>22.3827323913574</v>
+        <v>22.3827342987061</v>
       </c>
       <c r="H371" t="n">
         <v>349002</v>
@@ -11157,7 +11157,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>22.3643264770508</v>
+        <v>22.3643283843994</v>
       </c>
       <c r="H372" t="n">
         <v>603189</v>
@@ -11186,7 +11186,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G373" t="n">
-        <v>22.7416687011719</v>
+        <v>22.7416667938232</v>
       </c>
       <c r="H373" t="n">
         <v>827087</v>
@@ -11244,7 +11244,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G375" t="n">
-        <v>22.8797206878662</v>
+        <v>22.8797225952148</v>
       </c>
       <c r="H375" t="n">
         <v>368128</v>
@@ -11273,7 +11273,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>23.2846698760986</v>
+        <v>23.2846717834473</v>
       </c>
       <c r="H376" t="n">
         <v>596955</v>
@@ -11360,7 +11360,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G379" t="n">
-        <v>22.8060932159424</v>
+        <v>22.806095123291</v>
       </c>
       <c r="H379" t="n">
         <v>684365</v>
@@ -11389,7 +11389,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G380" t="n">
-        <v>23.0269737243652</v>
+        <v>23.0269775390625</v>
       </c>
       <c r="H380" t="n">
         <v>525690</v>
@@ -11476,7 +11476,7 @@
         <v>23.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>21.5452251434326</v>
+        <v>21.545223236084</v>
       </c>
       <c r="H383" t="n">
         <v>915042</v>
@@ -11650,7 +11650,7 @@
         <v>23</v>
       </c>
       <c r="G389" t="n">
-        <v>21.1678848266602</v>
+        <v>21.1678829193115</v>
       </c>
       <c r="H389" t="n">
         <v>501698</v>
@@ -11679,7 +11679,7 @@
         <v>23</v>
       </c>
       <c r="G390" t="n">
-        <v>21.1678848266602</v>
+        <v>21.1678829193115</v>
       </c>
       <c r="H390" t="n">
         <v>281095</v>
@@ -11795,7 +11795,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G394" t="n">
-        <v>21.5084075927734</v>
+        <v>21.5084095001221</v>
       </c>
       <c r="H394" t="n">
         <v>401727</v>
@@ -11824,7 +11824,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G395" t="n">
-        <v>21.9133586883545</v>
+        <v>21.9133605957031</v>
       </c>
       <c r="H395" t="n">
         <v>698768</v>
@@ -11853,7 +11853,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G396" t="n">
-        <v>21.8857517242432</v>
+        <v>21.8857498168945</v>
       </c>
       <c r="H396" t="n">
         <v>305318</v>
@@ -11882,7 +11882,7 @@
         <v>23.8700008392334</v>
       </c>
       <c r="G397" t="n">
-        <v>21.9685821533203</v>
+        <v>21.9685802459717</v>
       </c>
       <c r="H397" t="n">
         <v>424576</v>
@@ -11969,7 +11969,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G400" t="n">
-        <v>22.2170734405518</v>
+        <v>22.2170715332031</v>
       </c>
       <c r="H400" t="n">
         <v>358847</v>
@@ -12114,7 +12114,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G405" t="n">
-        <v>22.5575981140137</v>
+        <v>22.5576019287109</v>
       </c>
       <c r="H405" t="n">
         <v>352700</v>
@@ -12172,7 +12172,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G407" t="n">
-        <v>21.4255790710449</v>
+        <v>21.4255809783936</v>
       </c>
       <c r="H407" t="n">
         <v>844820</v>
@@ -12259,7 +12259,7 @@
         <v>24.1900005340576</v>
       </c>
       <c r="G410" t="n">
-        <v>22.2630920410156</v>
+        <v>22.263090133667</v>
       </c>
       <c r="H410" t="n">
         <v>366457</v>
@@ -12288,7 +12288,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G411" t="n">
-        <v>22.539192199707</v>
+        <v>22.5391941070557</v>
       </c>
       <c r="H411" t="n">
         <v>497939</v>
@@ -12346,7 +12346,7 @@
         <v>24.25</v>
       </c>
       <c r="G413" t="n">
-        <v>22.3183097839355</v>
+        <v>22.3183116912842</v>
       </c>
       <c r="H413" t="n">
         <v>259593</v>
@@ -12462,7 +12462,7 @@
         <v>24.2700004577637</v>
       </c>
       <c r="G417" t="n">
-        <v>22.3367176055908</v>
+        <v>22.3367195129395</v>
       </c>
       <c r="H417" t="n">
         <v>583263</v>
@@ -12491,7 +12491,7 @@
         <v>24.0300006866455</v>
       </c>
       <c r="G418" t="n">
-        <v>22.1158351898193</v>
+        <v>22.115837097168</v>
       </c>
       <c r="H418" t="n">
         <v>245071</v>
@@ -12520,7 +12520,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>21.7661056518555</v>
+        <v>21.7661037445068</v>
       </c>
       <c r="H419" t="n">
         <v>234785</v>
@@ -12578,7 +12578,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G421" t="n">
-        <v>21.7569007873535</v>
+        <v>21.7568988800049</v>
       </c>
       <c r="H421" t="n">
         <v>283848</v>
@@ -12607,7 +12607,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G422" t="n">
-        <v>21.9133586883545</v>
+        <v>21.9133605957031</v>
       </c>
       <c r="H422" t="n">
         <v>171029</v>
@@ -12665,7 +12665,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>21.9961929321289</v>
+        <v>21.9961910247803</v>
       </c>
       <c r="H424" t="n">
         <v>138330</v>
@@ -12694,7 +12694,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G425" t="n">
-        <v>21.7016830444336</v>
+        <v>21.701681137085</v>
       </c>
       <c r="H425" t="n">
         <v>416770</v>
@@ -12723,7 +12723,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G426" t="n">
-        <v>22.0053958892822</v>
+        <v>22.0053939819336</v>
       </c>
       <c r="H426" t="n">
         <v>237338</v>
@@ -12752,7 +12752,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G427" t="n">
-        <v>22.2170734405518</v>
+        <v>22.2170715332031</v>
       </c>
       <c r="H427" t="n">
         <v>537878</v>
@@ -12810,7 +12810,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G429" t="n">
-        <v>22.0053958892822</v>
+        <v>22.0053939819336</v>
       </c>
       <c r="H429" t="n">
         <v>233703</v>
@@ -12839,7 +12839,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G430" t="n">
-        <v>21.9133586883545</v>
+        <v>21.9133605957031</v>
       </c>
       <c r="H430" t="n">
         <v>185988</v>
@@ -12868,7 +12868,7 @@
         <v>23.7700004577637</v>
       </c>
       <c r="G431" t="n">
-        <v>21.8765487670898</v>
+        <v>21.8765468597412</v>
       </c>
       <c r="H431" t="n">
         <v>297166</v>
@@ -12897,7 +12897,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G432" t="n">
-        <v>22.1250400543213</v>
+        <v>22.1250419616699</v>
       </c>
       <c r="H432" t="n">
         <v>181819</v>
@@ -12955,7 +12955,7 @@
         <v>23.9300003051758</v>
       </c>
       <c r="G434" t="n">
-        <v>22.0238037109375</v>
+        <v>22.0238018035889</v>
       </c>
       <c r="H434" t="n">
         <v>408570</v>
@@ -12984,7 +12984,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G435" t="n">
-        <v>21.9961929321289</v>
+        <v>21.9961910247803</v>
       </c>
       <c r="H435" t="n">
         <v>619938</v>
@@ -13071,7 +13071,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G438" t="n">
-        <v>20.8273544311523</v>
+        <v>20.827356338501</v>
       </c>
       <c r="H438" t="n">
         <v>1417619</v>
@@ -13129,7 +13129,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G440" t="n">
-        <v>20.9470024108887</v>
+        <v>20.94700050354</v>
       </c>
       <c r="H440" t="n">
         <v>418634</v>
@@ -13187,7 +13187,7 @@
         <v>22.9300003051758</v>
       </c>
       <c r="G442" t="n">
-        <v>21.1034622192383</v>
+        <v>21.1034603118896</v>
       </c>
       <c r="H442" t="n">
         <v>361840</v>
@@ -13390,7 +13390,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>22.3827323913574</v>
+        <v>22.3827342987061</v>
       </c>
       <c r="H449" t="n">
         <v>855777</v>
@@ -13448,7 +13448,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G451" t="n">
-        <v>21.2967300415039</v>
+        <v>21.2967319488525</v>
       </c>
       <c r="H451" t="n">
         <v>599089</v>
@@ -13622,7 +13622,7 @@
         <v>22.5</v>
       </c>
       <c r="G457" t="n">
-        <v>20.7077102661133</v>
+        <v>20.7077121734619</v>
       </c>
       <c r="H457" t="n">
         <v>475690</v>
@@ -13680,7 +13680,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G459" t="n">
-        <v>21.1586799621582</v>
+        <v>21.1586780548096</v>
       </c>
       <c r="H459" t="n">
         <v>440417</v>
@@ -13796,7 +13796,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G463" t="n">
-        <v>20.4500179290771</v>
+        <v>20.4500160217285</v>
       </c>
       <c r="H463" t="n">
         <v>772283</v>
@@ -13854,7 +13854,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G465" t="n">
-        <v>20.3947944641113</v>
+        <v>20.39479637146</v>
       </c>
       <c r="H465" t="n">
         <v>664948</v>
@@ -13883,7 +13883,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G466" t="n">
-        <v>20.0082511901855</v>
+        <v>20.0082492828369</v>
       </c>
       <c r="H466" t="n">
         <v>1396902</v>
@@ -13912,7 +13912,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>19.9714374542236</v>
+        <v>19.9714393615723</v>
       </c>
       <c r="H467" t="n">
         <v>1435364</v>
@@ -14115,7 +14115,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G474" t="n">
-        <v>21.2415103912354</v>
+        <v>21.2415084838867</v>
       </c>
       <c r="H474" t="n">
         <v>971079</v>
@@ -14144,7 +14144,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G475" t="n">
-        <v>20.9285945892334</v>
+        <v>20.9285926818848</v>
       </c>
       <c r="H475" t="n">
         <v>884159</v>
@@ -14173,7 +14173,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G476" t="n">
-        <v>20.9470024108887</v>
+        <v>20.94700050354</v>
       </c>
       <c r="H476" t="n">
         <v>584780</v>
@@ -14202,7 +14202,7 @@
         <v>22.5</v>
       </c>
       <c r="G477" t="n">
-        <v>20.7077102661133</v>
+        <v>20.7077121734619</v>
       </c>
       <c r="H477" t="n">
         <v>777593</v>
@@ -14231,7 +14231,7 @@
         <v>22</v>
       </c>
       <c r="G478" t="n">
-        <v>20.2475414276123</v>
+        <v>20.2475395202637</v>
       </c>
       <c r="H478" t="n">
         <v>750579</v>
@@ -14289,7 +14289,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G480" t="n">
-        <v>20.0910816192627</v>
+        <v>20.0910835266113</v>
       </c>
       <c r="H480" t="n">
         <v>280042</v>
@@ -14318,7 +14318,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G481" t="n">
-        <v>19.2719783782959</v>
+        <v>19.2719764709473</v>
       </c>
       <c r="H481" t="n">
         <v>2609341</v>
@@ -14347,7 +14347,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>19.6953353881836</v>
+        <v>19.695333480835</v>
       </c>
       <c r="H482" t="n">
         <v>1022782</v>
@@ -14376,7 +14376,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G483" t="n">
-        <v>19.8057765960693</v>
+        <v>19.8057746887207</v>
       </c>
       <c r="H483" t="n">
         <v>546959</v>
@@ -14405,7 +14405,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G484" t="n">
-        <v>19.7321491241455</v>
+        <v>19.7321472167969</v>
       </c>
       <c r="H484" t="n">
         <v>421554</v>
@@ -14434,7 +14434,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G485" t="n">
-        <v>20.1831150054932</v>
+        <v>20.1831169128418</v>
       </c>
       <c r="H485" t="n">
         <v>533863</v>
@@ -14463,7 +14463,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G486" t="n">
-        <v>20.0450668334961</v>
+        <v>20.0450649261475</v>
       </c>
       <c r="H486" t="n">
         <v>455042</v>
@@ -14492,7 +14492,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>20.2935581207275</v>
+        <v>20.2935562133789</v>
       </c>
       <c r="H487" t="n">
         <v>410849</v>
@@ -14521,7 +14521,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>20.4316101074219</v>
+        <v>20.4316082000732</v>
       </c>
       <c r="H488" t="n">
         <v>368098</v>
@@ -14550,7 +14550,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G489" t="n">
-        <v>20.5696582794189</v>
+        <v>20.5696620941162</v>
       </c>
       <c r="H489" t="n">
         <v>438572</v>
@@ -14579,7 +14579,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>20.661693572998</v>
+        <v>20.6616954803467</v>
       </c>
       <c r="H490" t="n">
         <v>354523</v>
@@ -14666,7 +14666,7 @@
         <v>22.5</v>
       </c>
       <c r="G493" t="n">
-        <v>20.7077102661133</v>
+        <v>20.7077121734619</v>
       </c>
       <c r="H493" t="n">
         <v>633331</v>
@@ -14956,7 +14956,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>19.4652481079102</v>
+        <v>19.4652500152588</v>
       </c>
       <c r="H503" t="n">
         <v>2465735</v>
@@ -15014,7 +15014,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G505" t="n">
-        <v>19.8609943389893</v>
+        <v>19.8609962463379</v>
       </c>
       <c r="H505" t="n">
         <v>611462</v>
@@ -15072,7 +15072,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G507" t="n">
-        <v>20.2199306488037</v>
+        <v>20.2199287414551</v>
       </c>
       <c r="H507" t="n">
         <v>372050</v>
@@ -15101,7 +15101,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G508" t="n">
-        <v>20.2935581207275</v>
+        <v>20.2935562133789</v>
       </c>
       <c r="H508" t="n">
         <v>210477</v>
@@ -15130,7 +15130,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>20.2291355133057</v>
+        <v>20.229133605957</v>
       </c>
       <c r="H509" t="n">
         <v>191733</v>
@@ -15159,7 +15159,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>20.2935581207275</v>
+        <v>20.2935562133789</v>
       </c>
       <c r="H510" t="n">
         <v>222355</v>
@@ -15217,7 +15217,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G512" t="n">
-        <v>20.2199306488037</v>
+        <v>20.2199287414551</v>
       </c>
       <c r="H512" t="n">
         <v>214152</v>
@@ -15246,7 +15246,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>20.523645401001</v>
+        <v>20.5236415863037</v>
       </c>
       <c r="H513" t="n">
         <v>314606</v>
@@ -15391,7 +15391,7 @@
         <v>22.2399997711182</v>
       </c>
       <c r="G518" t="n">
-        <v>20.4684238433838</v>
+        <v>20.4684219360352</v>
       </c>
       <c r="H518" t="n">
         <v>324669</v>
@@ -15478,7 +15478,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>20.4316101074219</v>
+        <v>20.4316082000732</v>
       </c>
       <c r="H521" t="n">
         <v>164255</v>
@@ -15507,7 +15507,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G522" t="n">
-        <v>20.4500179290771</v>
+        <v>20.4500160217285</v>
       </c>
       <c r="H522" t="n">
         <v>256718</v>
@@ -15536,7 +15536,7 @@
         <v>22</v>
       </c>
       <c r="G523" t="n">
-        <v>20.2475414276123</v>
+        <v>20.2475395202637</v>
       </c>
       <c r="H523" t="n">
         <v>290730</v>
@@ -15565,7 +15565,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G524" t="n">
-        <v>20.1739120483398</v>
+        <v>20.1739139556885</v>
       </c>
       <c r="H524" t="n">
         <v>499386</v>
@@ -15594,7 +15594,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G525" t="n">
-        <v>20.9470024108887</v>
+        <v>20.94700050354</v>
       </c>
       <c r="H525" t="n">
         <v>908844</v>
@@ -15623,7 +15623,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G526" t="n">
-        <v>21.7569007873535</v>
+        <v>21.7568988800049</v>
       </c>
       <c r="H526" t="n">
         <v>1540488</v>
@@ -15652,7 +15652,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G527" t="n">
-        <v>21.2967300415039</v>
+        <v>21.2967319488525</v>
       </c>
       <c r="H527" t="n">
         <v>604201</v>
@@ -15681,7 +15681,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>21.2599182128906</v>
+        <v>21.259916305542</v>
       </c>
       <c r="H528" t="n">
         <v>954306</v>
@@ -15710,7 +15710,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>21.2599182128906</v>
+        <v>21.259916305542</v>
       </c>
       <c r="H529" t="n">
         <v>726158</v>
@@ -15768,7 +15768,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G531" t="n">
-        <v>21.5176105499268</v>
+        <v>21.5176124572754</v>
       </c>
       <c r="H531" t="n">
         <v>399997</v>
@@ -15942,7 +15942,7 @@
         <v>22.1100006103516</v>
       </c>
       <c r="G537" t="n">
-        <v>20.3487777709961</v>
+        <v>20.3487796783447</v>
       </c>
       <c r="H537" t="n">
         <v>482372</v>
@@ -16000,7 +16000,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G539" t="n">
-        <v>20.0266590118408</v>
+        <v>20.0266571044922</v>
       </c>
       <c r="H539" t="n">
         <v>614365</v>
@@ -16029,7 +16029,7 @@
         <v>21.4300003051758</v>
       </c>
       <c r="G540" t="n">
-        <v>19.7229442596436</v>
+        <v>19.7229461669922</v>
       </c>
       <c r="H540" t="n">
         <v>544614</v>
@@ -16058,7 +16058,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G541" t="n">
-        <v>20.0082511901855</v>
+        <v>20.0082492828369</v>
       </c>
       <c r="H541" t="n">
         <v>190751</v>
@@ -16116,7 +16116,7 @@
         <v>22</v>
       </c>
       <c r="G543" t="n">
-        <v>20.2475414276123</v>
+        <v>20.2475395202637</v>
       </c>
       <c r="H543" t="n">
         <v>619390</v>
@@ -16232,7 +16232,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G547" t="n">
-        <v>20.4500179290771</v>
+        <v>20.4500160217285</v>
       </c>
       <c r="H547" t="n">
         <v>182552</v>
@@ -16319,7 +16319,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G550" t="n">
-        <v>20.9285945892334</v>
+        <v>20.9285926818848</v>
       </c>
       <c r="H550" t="n">
         <v>308603</v>
@@ -16348,7 +16348,7 @@
         <v>22.75</v>
       </c>
       <c r="G551" t="n">
-        <v>20.9377975463867</v>
+        <v>20.9377956390381</v>
       </c>
       <c r="H551" t="n">
         <v>330493</v>
@@ -16406,7 +16406,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G553" t="n">
-        <v>21.2967300415039</v>
+        <v>21.2967319488525</v>
       </c>
       <c r="H553" t="n">
         <v>2496511</v>
@@ -16435,7 +16435,7 @@
         <v>23.4699993133545</v>
       </c>
       <c r="G554" t="n">
-        <v>21.6004428863525</v>
+        <v>21.6004447937012</v>
       </c>
       <c r="H554" t="n">
         <v>754894</v>
@@ -16464,7 +16464,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G555" t="n">
-        <v>20.6248798370361</v>
+        <v>20.6248817443848</v>
       </c>
       <c r="H555" t="n">
         <v>551415</v>
@@ -16522,7 +16522,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G557" t="n">
-        <v>20.0910816192627</v>
+        <v>20.0910835266113</v>
       </c>
       <c r="H557" t="n">
         <v>895894</v>
@@ -16551,7 +16551,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>20.1094875335693</v>
+        <v>20.109489440918</v>
       </c>
       <c r="H558" t="n">
         <v>598799</v>
@@ -16580,7 +16580,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>19.9714374542236</v>
+        <v>19.9714393615723</v>
       </c>
       <c r="H559" t="n">
         <v>860738</v>
@@ -16609,7 +16609,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>19.649320602417</v>
+        <v>19.6493186950684</v>
       </c>
       <c r="H560" t="n">
         <v>1050485</v>
@@ -16638,7 +16638,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G561" t="n">
-        <v>19.9990482330322</v>
+        <v>19.9990463256836</v>
       </c>
       <c r="H561" t="n">
         <v>740982</v>
@@ -16667,7 +16667,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>20.1094875335693</v>
+        <v>20.109489440918</v>
       </c>
       <c r="H562" t="n">
         <v>392838</v>
@@ -16696,7 +16696,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G563" t="n">
-        <v>19.8609943389893</v>
+        <v>19.8609962463379</v>
       </c>
       <c r="H563" t="n">
         <v>558470</v>
@@ -16783,7 +16783,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G566" t="n">
-        <v>20.5696582794189</v>
+        <v>20.5696620941162</v>
       </c>
       <c r="H566" t="n">
         <v>548117</v>
@@ -16841,7 +16841,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G568" t="n">
-        <v>20.523645401001</v>
+        <v>20.5236415863037</v>
       </c>
       <c r="H568" t="n">
         <v>305669</v>
@@ -16928,7 +16928,7 @@
         <v>22.3099994659424</v>
       </c>
       <c r="G571" t="n">
-        <v>20.5328464508057</v>
+        <v>20.532844543457</v>
       </c>
       <c r="H571" t="n">
         <v>211904</v>
@@ -17073,7 +17073,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>20.6156749725342</v>
+        <v>20.6156768798828</v>
       </c>
       <c r="H576" t="n">
         <v>263654</v>
@@ -17189,7 +17189,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G580" t="n">
-        <v>20.3947944641113</v>
+        <v>20.39479637146</v>
       </c>
       <c r="H580" t="n">
         <v>589931</v>
@@ -17305,7 +17305,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>21.2783260345459</v>
+        <v>21.2783241271973</v>
       </c>
       <c r="H584" t="n">
         <v>190641</v>
@@ -17450,7 +17450,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G589" t="n">
-        <v>21.7937183380127</v>
+        <v>21.7937164306641</v>
       </c>
       <c r="H589" t="n">
         <v>611824</v>
@@ -17508,7 +17508,7 @@
         <v>24.5</v>
       </c>
       <c r="G591" t="n">
-        <v>22.548397064209</v>
+        <v>22.5483989715576</v>
       </c>
       <c r="H591" t="n">
         <v>1072195</v>
@@ -17537,7 +17537,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G592" t="n">
-        <v>22.4195518493652</v>
+        <v>22.4195499420166</v>
       </c>
       <c r="H592" t="n">
         <v>493451</v>
@@ -17595,7 +17595,7 @@
         <v>24.5200004577637</v>
       </c>
       <c r="G594" t="n">
-        <v>22.5668029785156</v>
+        <v>22.5668048858643</v>
       </c>
       <c r="H594" t="n">
         <v>527263</v>
@@ -17624,7 +17624,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G595" t="n">
-        <v>22.8797206878662</v>
+        <v>22.8797225952148</v>
       </c>
       <c r="H595" t="n">
         <v>677550</v>
@@ -17653,7 +17653,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G596" t="n">
-        <v>22.7416687011719</v>
+        <v>22.7416667938232</v>
       </c>
       <c r="H596" t="n">
         <v>747463</v>
@@ -17798,7 +17798,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G601" t="n">
-        <v>22.6864490509033</v>
+        <v>22.6864471435547</v>
       </c>
       <c r="H601" t="n">
         <v>481261</v>
@@ -17827,7 +17827,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>22.7324676513672</v>
+        <v>22.7324638366699</v>
       </c>
       <c r="H602" t="n">
         <v>336880</v>
@@ -17885,7 +17885,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G604" t="n">
-        <v>22.7692794799805</v>
+        <v>22.7692813873291</v>
       </c>
       <c r="H604" t="n">
         <v>300428</v>
@@ -17914,7 +17914,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G605" t="n">
-        <v>22.9073314666748</v>
+        <v>22.9073295593262</v>
       </c>
       <c r="H605" t="n">
         <v>415746</v>
@@ -17943,7 +17943,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G606" t="n">
-        <v>23.2754669189453</v>
+        <v>23.2754707336426</v>
       </c>
       <c r="H606" t="n">
         <v>719915</v>
@@ -18001,7 +18001,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G608" t="n">
-        <v>22.9913024902344</v>
+        <v>22.991304397583</v>
       </c>
       <c r="H608" t="n">
         <v>259914</v>
@@ -18088,7 +18088,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G611" t="n">
-        <v>22.9071865081787</v>
+        <v>22.907190322876</v>
       </c>
       <c r="H611" t="n">
         <v>487106</v>
@@ -18117,7 +18117,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G612" t="n">
-        <v>22.9819583892822</v>
+        <v>22.9819564819336</v>
       </c>
       <c r="H612" t="n">
         <v>524215</v>
@@ -18146,7 +18146,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G613" t="n">
-        <v>22.7296123504639</v>
+        <v>22.7296142578125</v>
       </c>
       <c r="H613" t="n">
         <v>339316</v>
@@ -18175,7 +18175,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G614" t="n">
-        <v>22.3557720184326</v>
+        <v>22.355770111084</v>
       </c>
       <c r="H614" t="n">
         <v>700947</v>
@@ -18233,7 +18233,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G616" t="n">
-        <v>23.0754203796387</v>
+        <v>23.07541847229</v>
       </c>
       <c r="H616" t="n">
         <v>441644</v>
@@ -18262,7 +18262,7 @@
         <v>24.9899997711182</v>
       </c>
       <c r="G617" t="n">
-        <v>23.3557987213135</v>
+        <v>23.3557968139648</v>
       </c>
       <c r="H617" t="n">
         <v>414529</v>
@@ -18407,7 +18407,7 @@
         <v>24.3299999237061</v>
       </c>
       <c r="G622" t="n">
-        <v>22.7389602661133</v>
+        <v>22.7389583587646</v>
       </c>
       <c r="H622" t="n">
         <v>507897</v>
@@ -18436,7 +18436,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G623" t="n">
-        <v>23.1595306396484</v>
+        <v>23.1595325469971</v>
       </c>
       <c r="H623" t="n">
         <v>393598</v>
@@ -18494,7 +18494,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>23.5053367614746</v>
+        <v>23.505334854126</v>
       </c>
       <c r="H625" t="n">
         <v>253050</v>
@@ -18610,7 +18610,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G629" t="n">
-        <v>22.9258804321289</v>
+        <v>22.9258823394775</v>
       </c>
       <c r="H629" t="n">
         <v>273653</v>
@@ -18668,7 +18668,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G631" t="n">
-        <v>20.3370227813721</v>
+        <v>20.3370208740234</v>
       </c>
       <c r="H631" t="n">
         <v>1272365</v>
@@ -18697,7 +18697,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G632" t="n">
-        <v>20.3370227813721</v>
+        <v>20.3370208740234</v>
       </c>
       <c r="H632" t="n">
         <v>880006</v>
@@ -18755,7 +18755,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G634" t="n">
-        <v>19.7388782501221</v>
+        <v>19.7388763427734</v>
       </c>
       <c r="H634" t="n">
         <v>776810</v>
@@ -18784,7 +18784,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G635" t="n">
-        <v>19.56130027771</v>
+        <v>19.5612983703613</v>
       </c>
       <c r="H635" t="n">
         <v>788412</v>
@@ -18813,7 +18813,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G636" t="n">
-        <v>19.3089542388916</v>
+        <v>19.3089561462402</v>
       </c>
       <c r="H636" t="n">
         <v>671130</v>
@@ -18842,7 +18842,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>19.5332622528076</v>
+        <v>19.533260345459</v>
       </c>
       <c r="H637" t="n">
         <v>512477</v>
@@ -18900,7 +18900,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>19.346342086792</v>
+        <v>19.3463401794434</v>
       </c>
       <c r="H639" t="n">
         <v>480213</v>
@@ -18987,7 +18987,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G642" t="n">
-        <v>18.3836975097656</v>
+        <v>18.383695602417</v>
       </c>
       <c r="H642" t="n">
         <v>773362</v>
@@ -19103,7 +19103,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G646" t="n">
-        <v>18.3836975097656</v>
+        <v>18.383695602417</v>
       </c>
       <c r="H646" t="n">
         <v>373552</v>
@@ -19132,7 +19132,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G647" t="n">
-        <v>18.6033306121826</v>
+        <v>18.603328704834</v>
       </c>
       <c r="H647" t="n">
         <v>410650</v>
@@ -19161,7 +19161,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G648" t="n">
-        <v>18.6360416412354</v>
+        <v>18.6360378265381</v>
       </c>
       <c r="H648" t="n">
         <v>360124</v>
@@ -19248,7 +19248,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G651" t="n">
-        <v>18.7201557159424</v>
+        <v>18.720157623291</v>
       </c>
       <c r="H651" t="n">
         <v>386178</v>
@@ -19306,7 +19306,7 @@
         <v>19.875</v>
       </c>
       <c r="G653" t="n">
-        <v>18.5752925872803</v>
+        <v>18.5752906799316</v>
       </c>
       <c r="H653" t="n">
         <v>336549</v>
@@ -19335,7 +19335,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G654" t="n">
-        <v>18.3930416107178</v>
+        <v>18.3930435180664</v>
       </c>
       <c r="H654" t="n">
         <v>659845</v>
@@ -19364,7 +19364,7 @@
         <v>19.8250007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>18.5285606384277</v>
+        <v>18.5285587310791</v>
       </c>
       <c r="H655" t="n">
         <v>472136</v>
@@ -19480,7 +19480,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G659" t="n">
-        <v>18.4911766052246</v>
+        <v>18.491174697876</v>
       </c>
       <c r="H659" t="n">
         <v>448603</v>
@@ -19567,7 +19567,7 @@
         <v>19.0149993896484</v>
       </c>
       <c r="G662" t="n">
-        <v>17.7715263366699</v>
+        <v>17.7715282440186</v>
       </c>
       <c r="H662" t="n">
         <v>552026</v>
@@ -19654,7 +19654,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G665" t="n">
-        <v>18.6734237670898</v>
+        <v>18.6734256744385</v>
       </c>
       <c r="H665" t="n">
         <v>384784</v>
@@ -19741,7 +19741,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G668" t="n">
-        <v>18.6734237670898</v>
+        <v>18.6734256744385</v>
       </c>
       <c r="H668" t="n">
         <v>269268</v>
@@ -19770,7 +19770,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G669" t="n">
-        <v>18.7201557159424</v>
+        <v>18.720157623291</v>
       </c>
       <c r="H669" t="n">
         <v>247847</v>
@@ -19799,7 +19799,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G670" t="n">
-        <v>18.4911766052246</v>
+        <v>18.491174697876</v>
       </c>
       <c r="H670" t="n">
         <v>378568</v>
@@ -19944,7 +19944,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G675" t="n">
-        <v>19.1407260894775</v>
+        <v>19.1407241821289</v>
       </c>
       <c r="H675" t="n">
         <v>1646978</v>
@@ -20002,7 +20002,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G677" t="n">
-        <v>19.4024181365967</v>
+        <v>19.402416229248</v>
       </c>
       <c r="H677" t="n">
         <v>410160</v>
@@ -20060,7 +20060,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G679" t="n">
-        <v>19.4304523468018</v>
+        <v>19.430456161499</v>
       </c>
       <c r="H679" t="n">
         <v>207201</v>
@@ -20118,7 +20118,7 @@
         <v>20.5</v>
       </c>
       <c r="G681" t="n">
-        <v>19.1594181060791</v>
+        <v>19.1594200134277</v>
       </c>
       <c r="H681" t="n">
         <v>262991</v>
@@ -20234,7 +20234,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G685" t="n">
-        <v>18.7388439178467</v>
+        <v>18.7388458251953</v>
       </c>
       <c r="H685" t="n">
         <v>362000</v>
@@ -20263,7 +20263,7 @@
         <v>20.5</v>
       </c>
       <c r="G686" t="n">
-        <v>19.1594181060791</v>
+        <v>19.1594200134277</v>
       </c>
       <c r="H686" t="n">
         <v>375929</v>
@@ -20292,7 +20292,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G687" t="n">
-        <v>19.0566120147705</v>
+        <v>19.0566101074219</v>
       </c>
       <c r="H687" t="n">
         <v>411927</v>
@@ -20495,7 +20495,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G694" t="n">
-        <v>20.0753326416016</v>
+        <v>20.0753307342529</v>
       </c>
       <c r="H694" t="n">
         <v>493504</v>
@@ -20669,7 +20669,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G700" t="n">
-        <v>19.5706443786621</v>
+        <v>19.5706462860107</v>
       </c>
       <c r="H700" t="n">
         <v>276548</v>
@@ -20698,7 +20698,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G701" t="n">
-        <v>19.2809162139893</v>
+        <v>19.2809181213379</v>
       </c>
       <c r="H701" t="n">
         <v>334676</v>
@@ -20756,7 +20756,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G703" t="n">
-        <v>18.8977298736572</v>
+        <v>18.8977279663086</v>
       </c>
       <c r="H703" t="n">
         <v>336450</v>
@@ -20785,7 +20785,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G704" t="n">
-        <v>19.0566120147705</v>
+        <v>19.0566101074219</v>
       </c>
       <c r="H704" t="n">
         <v>303150</v>
@@ -20843,7 +20843,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>18.8790378570557</v>
+        <v>18.879035949707</v>
       </c>
       <c r="H706" t="n">
         <v>303793</v>
@@ -20988,7 +20988,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G711" t="n">
-        <v>17.1546897888184</v>
+        <v>17.1546878814697</v>
       </c>
       <c r="H711" t="n">
         <v>1871086</v>
@@ -21133,7 +21133,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G716" t="n">
-        <v>18.2154674530029</v>
+        <v>18.2154693603516</v>
       </c>
       <c r="H716" t="n">
         <v>327778</v>
@@ -21162,7 +21162,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G717" t="n">
-        <v>19.5706443786621</v>
+        <v>19.5706462860107</v>
       </c>
       <c r="H717" t="n">
         <v>1765099</v>
@@ -21191,7 +21191,7 @@
         <v>20.5300006866455</v>
       </c>
       <c r="G718" t="n">
-        <v>19.1874561309814</v>
+        <v>19.1874580383301</v>
       </c>
       <c r="H718" t="n">
         <v>665558</v>
@@ -21249,7 +21249,7 @@
         <v>20.9699993133545</v>
       </c>
       <c r="G720" t="n">
-        <v>19.5986843109131</v>
+        <v>19.5986824035645</v>
       </c>
       <c r="H720" t="n">
         <v>628747</v>
@@ -21307,7 +21307,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G722" t="n">
-        <v>19.6454162597656</v>
+        <v>19.6454124450684</v>
       </c>
       <c r="H722" t="n">
         <v>418618</v>
@@ -21336,7 +21336,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G723" t="n">
-        <v>19.4771842956543</v>
+        <v>19.4771862030029</v>
       </c>
       <c r="H723" t="n">
         <v>299258</v>
@@ -21365,7 +21365,7 @@
         <v>20.9099998474121</v>
       </c>
       <c r="G724" t="n">
-        <v>19.5426063537598</v>
+        <v>19.5426082611084</v>
       </c>
       <c r="H724" t="n">
         <v>436766</v>
@@ -21510,7 +21510,7 @@
         <v>21</v>
       </c>
       <c r="G729" t="n">
-        <v>19.6267223358154</v>
+        <v>19.6267204284668</v>
       </c>
       <c r="H729" t="n">
         <v>286056</v>
@@ -21626,7 +21626,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G733" t="n">
-        <v>19.701488494873</v>
+        <v>19.7014904022217</v>
       </c>
       <c r="H733" t="n">
         <v>369031</v>
@@ -21655,7 +21655,7 @@
         <v>21</v>
       </c>
       <c r="G734" t="n">
-        <v>19.6267223358154</v>
+        <v>19.6267204284668</v>
       </c>
       <c r="H734" t="n">
         <v>247340</v>
@@ -21771,7 +21771,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G738" t="n">
-        <v>18.6033306121826</v>
+        <v>18.603328704834</v>
       </c>
       <c r="H738" t="n">
         <v>681345</v>
@@ -21945,7 +21945,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>19.5332622528076</v>
+        <v>19.533260345459</v>
       </c>
       <c r="H744" t="n">
         <v>282711</v>
@@ -22003,7 +22003,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>19.346342086792</v>
+        <v>19.3463401794434</v>
       </c>
       <c r="H746" t="n">
         <v>177553</v>
@@ -22032,7 +22032,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G747" t="n">
-        <v>19.701488494873</v>
+        <v>19.7014904022217</v>
       </c>
       <c r="H747" t="n">
         <v>368527</v>
@@ -22061,7 +22061,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>19.5332622528076</v>
+        <v>19.533260345459</v>
       </c>
       <c r="H748" t="n">
         <v>211502</v>
@@ -22090,7 +22090,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G749" t="n">
-        <v>19.4304523468018</v>
+        <v>19.430456161499</v>
       </c>
       <c r="H749" t="n">
         <v>241093</v>
@@ -22119,7 +22119,7 @@
         <v>20.5</v>
       </c>
       <c r="G750" t="n">
-        <v>19.1594181060791</v>
+        <v>19.1594200134277</v>
       </c>
       <c r="H750" t="n">
         <v>466560</v>
@@ -22177,7 +22177,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G752" t="n">
-        <v>18.6734237670898</v>
+        <v>18.6734256744385</v>
       </c>
       <c r="H752" t="n">
         <v>502005</v>
@@ -22206,7 +22206,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G753" t="n">
-        <v>18.3930416107178</v>
+        <v>18.3930435180664</v>
       </c>
       <c r="H753" t="n">
         <v>452457</v>
@@ -22293,7 +22293,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G756" t="n">
-        <v>16.8135566711426</v>
+        <v>16.8135585784912</v>
       </c>
       <c r="H756" t="n">
         <v>831352</v>
@@ -22322,7 +22322,7 @@
         <v>17.7450008392334</v>
       </c>
       <c r="G757" t="n">
-        <v>16.5845813751221</v>
+        <v>16.5845794677734</v>
       </c>
       <c r="H757" t="n">
         <v>666545</v>
@@ -22351,7 +22351,7 @@
         <v>17.7049999237061</v>
       </c>
       <c r="G758" t="n">
-        <v>16.5471973419189</v>
+        <v>16.5471954345703</v>
       </c>
       <c r="H758" t="n">
         <v>636977</v>
@@ -22496,7 +22496,7 @@
         <v>17.6550006866455</v>
       </c>
       <c r="G763" t="n">
-        <v>16.500467300415</v>
+        <v>16.5004653930664</v>
       </c>
       <c r="H763" t="n">
         <v>514163</v>
@@ -22554,7 +22554,7 @@
         <v>17.1650009155273</v>
       </c>
       <c r="G765" t="n">
-        <v>16.0425109863281</v>
+        <v>16.0425090789795</v>
       </c>
       <c r="H765" t="n">
         <v>452946</v>
@@ -22641,7 +22641,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>16.5425205230713</v>
+        <v>16.5425224304199</v>
       </c>
       <c r="H768" t="n">
         <v>424881</v>
@@ -22670,7 +22670,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G769" t="n">
-        <v>16.8415966033936</v>
+        <v>16.8415985107422</v>
       </c>
       <c r="H769" t="n">
         <v>570466</v>
@@ -22873,7 +22873,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G776" t="n">
-        <v>16.8135566711426</v>
+        <v>16.8135585784912</v>
       </c>
       <c r="H776" t="n">
         <v>396353</v>
@@ -22902,7 +22902,7 @@
         <v>17.5750007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>16.4256973266602</v>
+        <v>16.4256992340088</v>
       </c>
       <c r="H777" t="n">
         <v>608356</v>
@@ -22931,7 +22931,7 @@
         <v>17.2549991607666</v>
       </c>
       <c r="G778" t="n">
-        <v>16.1266212463379</v>
+        <v>16.1266231536865</v>
       </c>
       <c r="H778" t="n">
         <v>546458</v>
@@ -22989,7 +22989,7 @@
         <v>17.2549991607666</v>
       </c>
       <c r="G780" t="n">
-        <v>16.1266212463379</v>
+        <v>16.1266231536865</v>
       </c>
       <c r="H780" t="n">
         <v>354071</v>
@@ -23018,7 +23018,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>16.4490623474121</v>
+        <v>16.4490642547607</v>
       </c>
       <c r="H781" t="n">
         <v>395429</v>
@@ -23047,7 +23047,7 @@
         <v>17.3250007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>16.192045211792</v>
+        <v>16.1920471191406</v>
       </c>
       <c r="H782" t="n">
         <v>289549</v>
@@ -23308,7 +23308,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G791" t="n">
-        <v>16.299524307251</v>
+        <v>16.2995262145996</v>
       </c>
       <c r="H791" t="n">
         <v>193986</v>
@@ -23424,7 +23424,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>17.1967449188232</v>
+        <v>17.1967468261719</v>
       </c>
       <c r="H795" t="n">
         <v>665839</v>
@@ -23453,7 +23453,7 @@
         <v>18.4249992370605</v>
       </c>
       <c r="G796" t="n">
-        <v>17.2201118469238</v>
+        <v>17.2201099395752</v>
       </c>
       <c r="H796" t="n">
         <v>464002</v>
@@ -23569,7 +23569,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G800" t="n">
-        <v>17.1079597473145</v>
+        <v>17.1079616546631</v>
       </c>
       <c r="H800" t="n">
         <v>417559</v>
@@ -23598,7 +23598,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G801" t="n">
-        <v>17.1313247680664</v>
+        <v>17.1313228607178</v>
       </c>
       <c r="H801" t="n">
         <v>192081</v>
@@ -23627,7 +23627,7 @@
         <v>18.4349994659424</v>
       </c>
       <c r="G802" t="n">
-        <v>17.229455947876</v>
+        <v>17.2294578552246</v>
       </c>
       <c r="H802" t="n">
         <v>234504</v>
@@ -23714,7 +23714,7 @@
         <v>18.6749992370605</v>
       </c>
       <c r="G805" t="n">
-        <v>17.453763961792</v>
+        <v>17.4537620544434</v>
       </c>
       <c r="H805" t="n">
         <v>268791</v>
@@ -23772,7 +23772,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G807" t="n">
-        <v>17.6547031402588</v>
+        <v>17.6547012329102</v>
       </c>
       <c r="H807" t="n">
         <v>467189</v>
@@ -23859,7 +23859,7 @@
         <v>18.3449993133545</v>
       </c>
       <c r="G810" t="n">
-        <v>17.1453418731689</v>
+        <v>17.1453437805176</v>
       </c>
       <c r="H810" t="n">
         <v>752218</v>
@@ -23888,7 +23888,7 @@
         <v>18.0249996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>16.8462677001953</v>
+        <v>16.8462715148926</v>
       </c>
       <c r="H811" t="n">
         <v>347878</v>
@@ -24004,7 +24004,7 @@
         <v>19.1650009155273</v>
       </c>
       <c r="G815" t="n">
-        <v>17.9117202758789</v>
+        <v>17.9117221832275</v>
       </c>
       <c r="H815" t="n">
         <v>871578</v>
@@ -24033,7 +24033,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>18.0378913879395</v>
+        <v>18.0378932952881</v>
       </c>
       <c r="H816" t="n">
         <v>507095</v>
@@ -24062,7 +24062,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G817" t="n">
-        <v>17.6593780517578</v>
+        <v>17.6593761444092</v>
       </c>
       <c r="H817" t="n">
         <v>1770207</v>
@@ -24120,7 +24120,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G819" t="n">
-        <v>17.6360130310059</v>
+        <v>17.6360111236572</v>
       </c>
       <c r="H819" t="n">
         <v>378751</v>
@@ -24149,7 +24149,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G820" t="n">
-        <v>17.6360130310059</v>
+        <v>17.6360111236572</v>
       </c>
       <c r="H820" t="n">
         <v>272696</v>
@@ -24178,7 +24178,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G821" t="n">
-        <v>17.3275928497314</v>
+        <v>17.3275909423828</v>
       </c>
       <c r="H821" t="n">
         <v>825446</v>
@@ -24265,7 +24265,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G824" t="n">
-        <v>17.6360130310059</v>
+        <v>17.6360111236572</v>
       </c>
       <c r="H824" t="n">
         <v>353996</v>
@@ -24294,7 +24294,7 @@
         <v>18.7250003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>17.5004940032959</v>
+        <v>17.5004959106445</v>
       </c>
       <c r="H825" t="n">
         <v>295760</v>
@@ -24323,7 +24323,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G826" t="n">
-        <v>17.869665145874</v>
+        <v>17.8696632385254</v>
       </c>
       <c r="H826" t="n">
         <v>493818</v>
@@ -24352,7 +24352,7 @@
         <v>19.5949993133545</v>
       </c>
       <c r="G827" t="n">
-        <v>18.3135986328125</v>
+        <v>18.3136005401611</v>
       </c>
       <c r="H827" t="n">
         <v>659382</v>
@@ -24381,7 +24381,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G828" t="n">
-        <v>18.2154674530029</v>
+        <v>18.2154693603516</v>
       </c>
       <c r="H828" t="n">
         <v>396423</v>
@@ -24439,7 +24439,7 @@
         <v>19.5949993133545</v>
       </c>
       <c r="G830" t="n">
-        <v>18.3135986328125</v>
+        <v>18.3136005401611</v>
       </c>
       <c r="H830" t="n">
         <v>585086</v>
@@ -24497,7 +24497,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G832" t="n">
-        <v>18.0191993713379</v>
+        <v>18.0192012786865</v>
       </c>
       <c r="H832" t="n">
         <v>294577</v>
@@ -24526,7 +24526,7 @@
         <v>19.2250003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>17.9677982330322</v>
+        <v>17.9677963256836</v>
       </c>
       <c r="H833" t="n">
         <v>203838</v>
@@ -24555,7 +24555,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G834" t="n">
-        <v>17.9070491790771</v>
+        <v>17.9070472717285</v>
       </c>
       <c r="H834" t="n">
         <v>384646</v>
@@ -24729,7 +24729,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G840" t="n">
-        <v>18.439769744873</v>
+        <v>18.4397716522217</v>
       </c>
       <c r="H840" t="n">
         <v>677306</v>
@@ -24758,7 +24758,7 @@
         <v>19.8250007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>18.5285606384277</v>
+        <v>18.5285587310791</v>
       </c>
       <c r="H841" t="n">
         <v>479730</v>
@@ -24787,7 +24787,7 @@
         <v>19.8449993133545</v>
       </c>
       <c r="G842" t="n">
-        <v>18.5472507476807</v>
+        <v>18.5472526550293</v>
       </c>
       <c r="H842" t="n">
         <v>1177361</v>
@@ -24845,7 +24845,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G844" t="n">
-        <v>18.3930416107178</v>
+        <v>18.3930435180664</v>
       </c>
       <c r="H844" t="n">
         <v>178961</v>
@@ -24874,7 +24874,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G845" t="n">
-        <v>18.3089275360107</v>
+        <v>18.3089256286621</v>
       </c>
       <c r="H845" t="n">
         <v>193879</v>
@@ -25106,7 +25106,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G853" t="n">
-        <v>18.0939712524414</v>
+        <v>18.0939693450928</v>
       </c>
       <c r="H853" t="n">
         <v>637823</v>
@@ -25193,7 +25193,7 @@
         <v>21.25</v>
       </c>
       <c r="G856" t="n">
-        <v>19.8603744506836</v>
+        <v>19.860372543335</v>
       </c>
       <c r="H856" t="n">
         <v>4085499</v>
@@ -25251,7 +25251,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>19.9071025848389</v>
+        <v>19.9071044921875</v>
       </c>
       <c r="H858" t="n">
         <v>565898</v>
@@ -80067,6 +80067,35 @@
         <v>539191</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>6.64499998092651</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>6.64499998092651</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>6.15500020980835</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>6.19500017166138</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>6.19500017166138</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>980389</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -427,7 +427,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G2" t="n">
-        <v>18.2763538360596</v>
+        <v>18.2763519287109</v>
       </c>
       <c r="H2" t="n">
         <v>1705033</v>
@@ -456,7 +456,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G3" t="n">
-        <v>18.0109634399414</v>
+        <v>18.0109672546387</v>
       </c>
       <c r="H3" t="n">
         <v>997627</v>
@@ -485,7 +485,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G4" t="n">
-        <v>17.4978828430176</v>
+        <v>17.4978809356689</v>
       </c>
       <c r="H4" t="n">
         <v>985547</v>
@@ -514,7 +514,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>17.9401931762695</v>
+        <v>17.9401912689209</v>
       </c>
       <c r="H5" t="n">
         <v>1381959</v>
@@ -630,7 +630,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G9" t="n">
-        <v>19.1344394683838</v>
+        <v>19.1344375610352</v>
       </c>
       <c r="H9" t="n">
         <v>1367537</v>
@@ -659,7 +659,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G10" t="n">
-        <v>18.8425102233887</v>
+        <v>18.84250831604</v>
       </c>
       <c r="H10" t="n">
         <v>1053164</v>
@@ -746,7 +746,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G13" t="n">
-        <v>18.0994243621826</v>
+        <v>18.0994262695312</v>
       </c>
       <c r="H13" t="n">
         <v>975727</v>
@@ -775,7 +775,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G14" t="n">
-        <v>17.6394195556641</v>
+        <v>17.6394233703613</v>
       </c>
       <c r="H14" t="n">
         <v>943974</v>
@@ -804,7 +804,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G15" t="n">
-        <v>17.5686531066895</v>
+        <v>17.5686550140381</v>
       </c>
       <c r="H15" t="n">
         <v>1002361</v>
@@ -833,7 +833,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G16" t="n">
-        <v>18.1878890991211</v>
+        <v>18.1878910064697</v>
       </c>
       <c r="H16" t="n">
         <v>813843</v>
@@ -862,7 +862,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G17" t="n">
-        <v>18.0994243621826</v>
+        <v>18.0994262695312</v>
       </c>
       <c r="H17" t="n">
         <v>476663</v>
@@ -920,7 +920,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>18.2232723236084</v>
+        <v>18.223274230957</v>
       </c>
       <c r="H19" t="n">
         <v>550218</v>
@@ -949,7 +949,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>17.7632694244385</v>
+        <v>17.7632675170898</v>
       </c>
       <c r="H20" t="n">
         <v>1244898</v>
@@ -978,7 +978,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G21" t="n">
-        <v>18.3913536071777</v>
+        <v>18.3913516998291</v>
       </c>
       <c r="H21" t="n">
         <v>1957322</v>
@@ -1036,7 +1036,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>17.9578876495361</v>
+        <v>17.9578838348389</v>
       </c>
       <c r="H23" t="n">
         <v>725076</v>
@@ -1065,7 +1065,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G24" t="n">
-        <v>18.2055835723877</v>
+        <v>18.2055816650391</v>
       </c>
       <c r="H24" t="n">
         <v>1897967</v>
@@ -1210,7 +1210,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>17.1617221832275</v>
+        <v>17.1617240905762</v>
       </c>
       <c r="H29" t="n">
         <v>741895</v>
@@ -1268,7 +1268,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G31" t="n">
-        <v>17.0201816558838</v>
+        <v>17.0201835632324</v>
       </c>
       <c r="H31" t="n">
         <v>474221</v>
@@ -1297,7 +1297,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G32" t="n">
-        <v>17.4890365600586</v>
+        <v>17.48903465271</v>
       </c>
       <c r="H32" t="n">
         <v>658925</v>
@@ -1384,7 +1384,7 @@
         <v>20.8099994659424</v>
       </c>
       <c r="G35" t="n">
-        <v>18.4090442657471</v>
+        <v>18.4090423583984</v>
       </c>
       <c r="H35" t="n">
         <v>656330</v>
@@ -1413,7 +1413,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G36" t="n">
-        <v>18.4532775878906</v>
+        <v>18.4532794952393</v>
       </c>
       <c r="H36" t="n">
         <v>500284</v>
@@ -1442,7 +1442,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>18.9752063751221</v>
+        <v>18.9752044677734</v>
       </c>
       <c r="H37" t="n">
         <v>534225</v>
@@ -1529,7 +1529,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G40" t="n">
-        <v>17.7632694244385</v>
+        <v>17.7632675170898</v>
       </c>
       <c r="H40" t="n">
         <v>488362</v>
@@ -1558,7 +1558,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G41" t="n">
-        <v>17.9048099517822</v>
+        <v>17.9048080444336</v>
       </c>
       <c r="H41" t="n">
         <v>422135</v>
@@ -1587,7 +1587,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G42" t="n">
-        <v>18.3471202850342</v>
+        <v>18.3471183776855</v>
       </c>
       <c r="H42" t="n">
         <v>557658</v>
@@ -1616,7 +1616,7 @@
         <v>21.5</v>
       </c>
       <c r="G43" t="n">
-        <v>19.0194358825684</v>
+        <v>19.0194339752197</v>
       </c>
       <c r="H43" t="n">
         <v>1151116</v>
@@ -1645,7 +1645,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G44" t="n">
-        <v>19.0017433166504</v>
+        <v>19.001745223999</v>
       </c>
       <c r="H44" t="n">
         <v>479063</v>
@@ -1703,7 +1703,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G46" t="n">
-        <v>19.3113632202148</v>
+        <v>19.3113613128662</v>
       </c>
       <c r="H46" t="n">
         <v>602537</v>
@@ -1790,7 +1790,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>19.7271347045898</v>
+        <v>19.7271366119385</v>
       </c>
       <c r="H49" t="n">
         <v>805952</v>
@@ -1848,7 +1848,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G51" t="n">
-        <v>19.6475200653076</v>
+        <v>19.6475219726562</v>
       </c>
       <c r="H51" t="n">
         <v>599137</v>
@@ -1877,7 +1877,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G52" t="n">
-        <v>19.983678817749</v>
+        <v>19.9836769104004</v>
       </c>
       <c r="H52" t="n">
         <v>593798</v>
@@ -1964,7 +1964,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G55" t="n">
-        <v>19.4440574645996</v>
+        <v>19.444055557251</v>
       </c>
       <c r="H55" t="n">
         <v>774964</v>
@@ -1993,7 +1993,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>20.0367546081543</v>
+        <v>20.0367527008057</v>
       </c>
       <c r="H56" t="n">
         <v>1462491</v>
@@ -2051,7 +2051,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G58" t="n">
-        <v>19.4971332550049</v>
+        <v>19.4971370697021</v>
       </c>
       <c r="H58" t="n">
         <v>1161092</v>
@@ -2109,7 +2109,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G60" t="n">
-        <v>18.9663562774658</v>
+        <v>18.9663600921631</v>
       </c>
       <c r="H60" t="n">
         <v>524013</v>
@@ -2167,7 +2167,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G62" t="n">
-        <v>19.9129066467285</v>
+        <v>19.9129104614258</v>
       </c>
       <c r="H62" t="n">
         <v>491805</v>
@@ -2196,7 +2196,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G63" t="n">
-        <v>19.868673324585</v>
+        <v>19.8686752319336</v>
       </c>
       <c r="H63" t="n">
         <v>732706</v>
@@ -2225,7 +2225,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G64" t="n">
-        <v>19.4971332550049</v>
+        <v>19.4971370697021</v>
       </c>
       <c r="H64" t="n">
         <v>538910</v>
@@ -2254,7 +2254,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G65" t="n">
-        <v>19.417516708374</v>
+        <v>19.4175186157227</v>
       </c>
       <c r="H65" t="n">
         <v>289674</v>
@@ -2312,7 +2312,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G67" t="n">
-        <v>18.8336658477783</v>
+        <v>18.833667755127</v>
       </c>
       <c r="H67" t="n">
         <v>490898</v>
@@ -2341,7 +2341,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G68" t="n">
-        <v>18.5151996612549</v>
+        <v>18.5152015686035</v>
       </c>
       <c r="H68" t="n">
         <v>449428</v>
@@ -2399,7 +2399,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G70" t="n">
-        <v>18.8955917358398</v>
+        <v>18.8955898284912</v>
       </c>
       <c r="H70" t="n">
         <v>395996</v>
@@ -2428,7 +2428,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G71" t="n">
-        <v>18.5240478515625</v>
+        <v>18.5240440368652</v>
       </c>
       <c r="H71" t="n">
         <v>1288923</v>
@@ -2457,7 +2457,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G72" t="n">
-        <v>19.3113632202148</v>
+        <v>19.3113613128662</v>
       </c>
       <c r="H72" t="n">
         <v>724111</v>
@@ -2544,7 +2544,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G75" t="n">
-        <v>18.877893447876</v>
+        <v>18.8778972625732</v>
       </c>
       <c r="H75" t="n">
         <v>347479</v>
@@ -2602,7 +2602,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G77" t="n">
-        <v>18.8071250915527</v>
+        <v>18.8071269989014</v>
       </c>
       <c r="H77" t="n">
         <v>725644</v>
@@ -2631,7 +2631,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G78" t="n">
-        <v>18.3205814361572</v>
+        <v>18.3205833435059</v>
       </c>
       <c r="H78" t="n">
         <v>1645887</v>
@@ -2689,7 +2689,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G80" t="n">
-        <v>17.8251934051514</v>
+        <v>17.8251914978027</v>
       </c>
       <c r="H80" t="n">
         <v>550622</v>
@@ -2747,7 +2747,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G82" t="n">
-        <v>18.0640392303467</v>
+        <v>18.0640411376953</v>
       </c>
       <c r="H82" t="n">
         <v>264849</v>
@@ -2776,7 +2776,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>18.3117351531982</v>
+        <v>18.3117370605469</v>
       </c>
       <c r="H83" t="n">
         <v>593433</v>
@@ -2805,7 +2805,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G84" t="n">
-        <v>17.8782691955566</v>
+        <v>17.878267288208</v>
       </c>
       <c r="H84" t="n">
         <v>570613</v>
@@ -2834,7 +2834,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>18.0021190643311</v>
+        <v>18.0021171569824</v>
       </c>
       <c r="H85" t="n">
         <v>455661</v>
@@ -2892,7 +2892,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G87" t="n">
-        <v>17.9048099517822</v>
+        <v>17.9048080444336</v>
       </c>
       <c r="H87" t="n">
         <v>346687</v>
@@ -2921,7 +2921,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G88" t="n">
-        <v>17.444803237915</v>
+        <v>17.4448013305664</v>
       </c>
       <c r="H88" t="n">
         <v>546914</v>
@@ -3037,7 +3037,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>17.6394195556641</v>
+        <v>17.6394233703613</v>
       </c>
       <c r="H92" t="n">
         <v>678917</v>
@@ -3095,7 +3095,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G94" t="n">
-        <v>18.8336658477783</v>
+        <v>18.833667755127</v>
       </c>
       <c r="H94" t="n">
         <v>1861606</v>
@@ -3153,7 +3153,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>18.0640392303467</v>
+        <v>18.0640411376953</v>
       </c>
       <c r="H96" t="n">
         <v>670991</v>
@@ -3182,7 +3182,7 @@
         <v>20.2700004577637</v>
       </c>
       <c r="G97" t="n">
-        <v>17.9313468933105</v>
+        <v>17.9313507080078</v>
       </c>
       <c r="H97" t="n">
         <v>352423</v>
@@ -3269,7 +3269,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G100" t="n">
-        <v>17.593936920166</v>
+        <v>17.5939388275146</v>
       </c>
       <c r="H100" t="n">
         <v>369286</v>
@@ -3327,7 +3327,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G102" t="n">
-        <v>17.7025985717773</v>
+        <v>17.7025966644287</v>
       </c>
       <c r="H102" t="n">
         <v>848652</v>
@@ -3414,7 +3414,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G105" t="n">
-        <v>17.593936920166</v>
+        <v>17.5939388275146</v>
       </c>
       <c r="H105" t="n">
         <v>186318</v>
@@ -3443,7 +3443,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G106" t="n">
-        <v>17.4128360748291</v>
+        <v>17.4128322601318</v>
       </c>
       <c r="H106" t="n">
         <v>450576</v>
@@ -3472,7 +3472,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G107" t="n">
-        <v>17.3041763305664</v>
+        <v>17.304178237915</v>
       </c>
       <c r="H107" t="n">
         <v>353691</v>
@@ -3617,7 +3617,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>17.747875213623</v>
+        <v>17.7478733062744</v>
       </c>
       <c r="H112" t="n">
         <v>286254</v>
@@ -3704,7 +3704,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G115" t="n">
-        <v>16.7155990600586</v>
+        <v>16.71559715271</v>
       </c>
       <c r="H115" t="n">
         <v>541514</v>
@@ -3733,7 +3733,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G116" t="n">
-        <v>16.5435523986816</v>
+        <v>16.5435543060303</v>
       </c>
       <c r="H116" t="n">
         <v>483555</v>
@@ -3820,7 +3820,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>17.8384246826172</v>
+        <v>17.8384227752686</v>
       </c>
       <c r="H119" t="n">
         <v>1228784</v>
@@ -3878,7 +3878,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G121" t="n">
-        <v>17.7297611236572</v>
+        <v>17.7297649383545</v>
       </c>
       <c r="H121" t="n">
         <v>523740</v>
@@ -4052,7 +4052,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G127" t="n">
-        <v>16.262845993042</v>
+        <v>16.2628479003906</v>
       </c>
       <c r="H127" t="n">
         <v>670056</v>
@@ -4081,7 +4081,7 @@
         <v>18.25</v>
       </c>
       <c r="G128" t="n">
-        <v>16.5254440307617</v>
+        <v>16.5254421234131</v>
       </c>
       <c r="H128" t="n">
         <v>558415</v>
@@ -4110,7 +4110,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>16.6069374084473</v>
+        <v>16.6069393157959</v>
       </c>
       <c r="H129" t="n">
         <v>464956</v>
@@ -4139,7 +4139,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G130" t="n">
-        <v>16.8061504364014</v>
+        <v>16.8061485290527</v>
       </c>
       <c r="H130" t="n">
         <v>255804</v>
@@ -4197,7 +4197,7 @@
         <v>17.75</v>
       </c>
       <c r="G132" t="n">
-        <v>16.0726909637451</v>
+        <v>16.0726928710938</v>
       </c>
       <c r="H132" t="n">
         <v>575432</v>
@@ -4284,7 +4284,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G135" t="n">
-        <v>16.4439487457275</v>
+        <v>16.4439468383789</v>
       </c>
       <c r="H135" t="n">
         <v>444582</v>
@@ -4342,7 +4342,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G137" t="n">
-        <v>17.0959072113037</v>
+        <v>17.0959091186523</v>
       </c>
       <c r="H137" t="n">
         <v>684185</v>
@@ -4371,7 +4371,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G138" t="n">
-        <v>17.1321315765381</v>
+        <v>17.1321296691895</v>
       </c>
       <c r="H138" t="n">
         <v>399511</v>
@@ -4400,7 +4400,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G139" t="n">
-        <v>17.0868530273438</v>
+        <v>17.0868549346924</v>
       </c>
       <c r="H139" t="n">
         <v>861033</v>
@@ -4487,7 +4487,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>17.3403930664062</v>
+        <v>17.3403968811035</v>
       </c>
       <c r="H142" t="n">
         <v>734812</v>
@@ -4545,7 +4545,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G144" t="n">
-        <v>17.9018096923828</v>
+        <v>17.9018077850342</v>
       </c>
       <c r="H144" t="n">
         <v>551371</v>
@@ -4574,7 +4574,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G145" t="n">
-        <v>18.1372413635254</v>
+        <v>18.1372394561768</v>
       </c>
       <c r="H145" t="n">
         <v>615453</v>
@@ -4603,7 +4603,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>17.9289741516113</v>
+        <v>17.9289722442627</v>
       </c>
       <c r="H146" t="n">
         <v>894618</v>
@@ -4661,7 +4661,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>18.6352672576904</v>
+        <v>18.6352653503418</v>
       </c>
       <c r="H148" t="n">
         <v>873688</v>
@@ -4690,7 +4690,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G149" t="n">
-        <v>19.0699081420898</v>
+        <v>19.0699062347412</v>
       </c>
       <c r="H149" t="n">
         <v>1159289</v>
@@ -4748,7 +4748,7 @@
         <v>20.5699996948242</v>
       </c>
       <c r="G151" t="n">
-        <v>18.6262130737305</v>
+        <v>18.6262111663818</v>
       </c>
       <c r="H151" t="n">
         <v>1004411</v>
@@ -4777,7 +4777,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G152" t="n">
-        <v>18.4994411468506</v>
+        <v>18.4994430541992</v>
       </c>
       <c r="H152" t="n">
         <v>1504019</v>
@@ -4806,7 +4806,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G153" t="n">
-        <v>18.2187347412109</v>
+        <v>18.2187366485596</v>
       </c>
       <c r="H153" t="n">
         <v>1091340</v>
@@ -4864,7 +4864,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G155" t="n">
-        <v>18.5809383392334</v>
+        <v>18.5809364318848</v>
       </c>
       <c r="H155" t="n">
         <v>402078</v>
@@ -4922,7 +4922,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G157" t="n">
-        <v>18.4994411468506</v>
+        <v>18.4994430541992</v>
       </c>
       <c r="H157" t="n">
         <v>593471</v>
@@ -4951,7 +4951,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G158" t="n">
-        <v>18.807315826416</v>
+        <v>18.8073139190674</v>
       </c>
       <c r="H158" t="n">
         <v>652271</v>
@@ -5009,7 +5009,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G160" t="n">
-        <v>19.0427436828613</v>
+        <v>19.0427417755127</v>
       </c>
       <c r="H160" t="n">
         <v>612736</v>
@@ -5125,7 +5125,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G164" t="n">
-        <v>18.6171550750732</v>
+        <v>18.6171569824219</v>
       </c>
       <c r="H164" t="n">
         <v>346826</v>
@@ -5154,7 +5154,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G165" t="n">
-        <v>18.7529792785645</v>
+        <v>18.7529811859131</v>
       </c>
       <c r="H165" t="n">
         <v>532932</v>
@@ -5328,7 +5328,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G171" t="n">
-        <v>18.5175533294678</v>
+        <v>18.5175514221191</v>
       </c>
       <c r="H171" t="n">
         <v>467980</v>
@@ -5502,7 +5502,7 @@
         <v>22</v>
       </c>
       <c r="G177" t="n">
-        <v>19.9210796356201</v>
+        <v>19.9210815429688</v>
       </c>
       <c r="H177" t="n">
         <v>1987857</v>
@@ -5560,7 +5560,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>19.5588817596436</v>
+        <v>19.5588798522949</v>
       </c>
       <c r="H179" t="n">
         <v>770378</v>
@@ -5589,7 +5589,7 @@
         <v>21.4899997711182</v>
       </c>
       <c r="G180" t="n">
-        <v>19.4592742919922</v>
+        <v>19.4592761993408</v>
       </c>
       <c r="H180" t="n">
         <v>700088</v>
@@ -5763,7 +5763,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>19.160457611084</v>
+        <v>19.1604595184326</v>
       </c>
       <c r="H186" t="n">
         <v>685216</v>
@@ -5966,7 +5966,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>20.4643840789795</v>
+        <v>20.4643859863281</v>
       </c>
       <c r="H193" t="n">
         <v>742714</v>
@@ -6024,7 +6024,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>20.6907577514648</v>
+        <v>20.6907615661621</v>
       </c>
       <c r="H195" t="n">
         <v>495248</v>
@@ -6111,7 +6111,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G198" t="n">
-        <v>20.4009990692139</v>
+        <v>20.4010009765625</v>
       </c>
       <c r="H198" t="n">
         <v>504761</v>
@@ -6198,7 +6198,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>20.3647785186768</v>
+        <v>20.3647804260254</v>
       </c>
       <c r="H201" t="n">
         <v>435292</v>
@@ -6227,7 +6227,7 @@
         <v>22.6900005340576</v>
       </c>
       <c r="G202" t="n">
-        <v>20.5458812713623</v>
+        <v>20.545877456665</v>
       </c>
       <c r="H202" t="n">
         <v>571600</v>
@@ -6256,7 +6256,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G203" t="n">
-        <v>20.7541465759277</v>
+        <v>20.7541446685791</v>
       </c>
       <c r="H203" t="n">
         <v>761654</v>
@@ -6314,7 +6314,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>20.0116329193115</v>
+        <v>20.0116310119629</v>
       </c>
       <c r="H205" t="n">
         <v>933957</v>
@@ -6343,7 +6343,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G206" t="n">
-        <v>20.265172958374</v>
+        <v>20.2651710510254</v>
       </c>
       <c r="H206" t="n">
         <v>579770</v>
@@ -6372,7 +6372,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>20.3285598754883</v>
+        <v>20.3285579681396</v>
       </c>
       <c r="H207" t="n">
         <v>362070</v>
@@ -6459,7 +6459,7 @@
         <v>22.25</v>
       </c>
       <c r="G210" t="n">
-        <v>20.1474590301514</v>
+        <v>20.1474571228027</v>
       </c>
       <c r="H210" t="n">
         <v>323432</v>
@@ -6546,7 +6546,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G213" t="n">
-        <v>20.5639896392822</v>
+        <v>20.5639877319336</v>
       </c>
       <c r="H213" t="n">
         <v>450892</v>
@@ -6575,7 +6575,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G214" t="n">
-        <v>20.1836776733398</v>
+        <v>20.1836795806885</v>
       </c>
       <c r="H214" t="n">
         <v>377674</v>
@@ -6662,7 +6662,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G217" t="n">
-        <v>19.4139995574951</v>
+        <v>19.4140033721924</v>
       </c>
       <c r="H217" t="n">
         <v>328652</v>
@@ -6691,7 +6691,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>19.5045509338379</v>
+        <v>19.5045528411865</v>
       </c>
       <c r="H218" t="n">
         <v>378528</v>
@@ -6720,7 +6720,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G219" t="n">
-        <v>19.7218704223633</v>
+        <v>19.7218723297119</v>
       </c>
       <c r="H219" t="n">
         <v>366831</v>
@@ -6778,7 +6778,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G221" t="n">
-        <v>19.5226612091064</v>
+        <v>19.5226593017578</v>
       </c>
       <c r="H221" t="n">
         <v>845010</v>
@@ -6836,7 +6836,7 @@
         <v>21.9899997711182</v>
       </c>
       <c r="G223" t="n">
-        <v>19.9120273590088</v>
+        <v>19.9120254516602</v>
       </c>
       <c r="H223" t="n">
         <v>433755</v>
@@ -6865,7 +6865,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G224" t="n">
-        <v>19.7490348815918</v>
+        <v>19.7490367889404</v>
       </c>
       <c r="H224" t="n">
         <v>454641</v>
@@ -6923,7 +6923,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G226" t="n">
-        <v>18.0919666290283</v>
+        <v>18.0919628143311</v>
       </c>
       <c r="H226" t="n">
         <v>1188113</v>
@@ -6952,7 +6952,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G227" t="n">
-        <v>18.3002300262451</v>
+        <v>18.3002281188965</v>
       </c>
       <c r="H227" t="n">
         <v>568589</v>
@@ -6981,7 +6981,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G228" t="n">
-        <v>18.3273963928223</v>
+        <v>18.3273944854736</v>
       </c>
       <c r="H228" t="n">
         <v>773547</v>
@@ -7010,7 +7010,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>18.2458992004395</v>
+        <v>18.2459011077881</v>
       </c>
       <c r="H229" t="n">
         <v>502752</v>
@@ -7068,7 +7068,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G231" t="n">
-        <v>17.7388172149658</v>
+        <v>17.7388153076172</v>
       </c>
       <c r="H231" t="n">
         <v>492945</v>
@@ -7126,7 +7126,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>17.8203105926514</v>
+        <v>17.8203125</v>
       </c>
       <c r="H233" t="n">
         <v>203127</v>
@@ -7213,7 +7213,7 @@
         <v>20.3099994659424</v>
       </c>
       <c r="G236" t="n">
-        <v>18.3907814025879</v>
+        <v>18.3907794952393</v>
       </c>
       <c r="H236" t="n">
         <v>402506</v>
@@ -7242,7 +7242,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G237" t="n">
-        <v>18.807315826416</v>
+        <v>18.8073139190674</v>
       </c>
       <c r="H237" t="n">
         <v>711240</v>
@@ -7358,7 +7358,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>19.2872276306152</v>
+        <v>19.2872257232666</v>
       </c>
       <c r="H241" t="n">
         <v>673068</v>
@@ -7387,7 +7387,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G242" t="n">
-        <v>19.3958911895752</v>
+        <v>19.3958892822266</v>
       </c>
       <c r="H242" t="n">
         <v>455970</v>
@@ -7474,7 +7474,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G245" t="n">
-        <v>19.5860462188721</v>
+        <v>19.5860443115234</v>
       </c>
       <c r="H245" t="n">
         <v>394277</v>
@@ -7561,7 +7561,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G248" t="n">
-        <v>20.265172958374</v>
+        <v>20.2651710510254</v>
       </c>
       <c r="H248" t="n">
         <v>1423797</v>
@@ -7619,7 +7619,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G250" t="n">
-        <v>20.265172958374</v>
+        <v>20.2651710510254</v>
       </c>
       <c r="H250" t="n">
         <v>491157</v>
@@ -7648,7 +7648,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G251" t="n">
-        <v>20.3466663360596</v>
+        <v>20.3466682434082</v>
       </c>
       <c r="H251" t="n">
         <v>359013</v>
@@ -7677,7 +7677,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>20.2380104064941</v>
+        <v>20.2380065917969</v>
       </c>
       <c r="H252" t="n">
         <v>230612</v>
@@ -7706,7 +7706,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G253" t="n">
-        <v>20.1293468475342</v>
+        <v>20.1293487548828</v>
       </c>
       <c r="H253" t="n">
         <v>311609</v>
@@ -7735,7 +7735,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G254" t="n">
-        <v>20.1836776733398</v>
+        <v>20.1836795806885</v>
       </c>
       <c r="H254" t="n">
         <v>207491</v>
@@ -7880,7 +7880,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G259" t="n">
-        <v>20.6183223724365</v>
+        <v>20.6183204650879</v>
       </c>
       <c r="H259" t="n">
         <v>666000</v>
@@ -7909,7 +7909,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G260" t="n">
-        <v>21.4785461425781</v>
+        <v>21.4785480499268</v>
       </c>
       <c r="H260" t="n">
         <v>1705785</v>
@@ -7967,7 +7967,7 @@
         <v>24.3700008392334</v>
       </c>
       <c r="G262" t="n">
-        <v>22.0671291351318</v>
+        <v>22.0671272277832</v>
       </c>
       <c r="H262" t="n">
         <v>1062423</v>
@@ -8025,7 +8025,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G264" t="n">
-        <v>22.2572803497314</v>
+        <v>22.2572822570801</v>
       </c>
       <c r="H264" t="n">
         <v>869802</v>
@@ -8054,7 +8054,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G265" t="n">
-        <v>22.2935028076172</v>
+        <v>22.2935009002686</v>
       </c>
       <c r="H265" t="n">
         <v>1130923</v>
@@ -8083,7 +8083,7 @@
         <v>24.6299991607666</v>
       </c>
       <c r="G266" t="n">
-        <v>22.3025550842285</v>
+        <v>22.3025569915771</v>
       </c>
       <c r="H266" t="n">
         <v>604896</v>
@@ -8170,7 +8170,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G269" t="n">
-        <v>22.2391700744629</v>
+        <v>22.2391719818115</v>
       </c>
       <c r="H269" t="n">
         <v>512480</v>
@@ -8257,7 +8257,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G272" t="n">
-        <v>22.891134262085</v>
+        <v>22.8911361694336</v>
       </c>
       <c r="H272" t="n">
         <v>650968</v>
@@ -8344,7 +8344,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>22.5923156738281</v>
+        <v>22.5923194885254</v>
       </c>
       <c r="H275" t="n">
         <v>775402</v>
@@ -8373,7 +8373,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G276" t="n">
-        <v>22.3568878173828</v>
+        <v>22.3568859100342</v>
       </c>
       <c r="H276" t="n">
         <v>736861</v>
@@ -8402,7 +8402,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>22.9092445373535</v>
+        <v>22.9092426300049</v>
       </c>
       <c r="H277" t="n">
         <v>1129609</v>
@@ -8431,7 +8431,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G278" t="n">
-        <v>22.1757869720459</v>
+        <v>22.1757850646973</v>
       </c>
       <c r="H278" t="n">
         <v>1066573</v>
@@ -8460,7 +8460,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G279" t="n">
-        <v>22.1395664215088</v>
+        <v>22.1395645141602</v>
       </c>
       <c r="H279" t="n">
         <v>498087</v>
@@ -8518,7 +8518,7 @@
         <v>26.2299995422363</v>
       </c>
       <c r="G281" t="n">
-        <v>23.7513618469238</v>
+        <v>23.7513599395752</v>
       </c>
       <c r="H281" t="n">
         <v>1163004</v>
@@ -8547,7 +8547,7 @@
         <v>26.6399993896484</v>
       </c>
       <c r="G282" t="n">
-        <v>24.1226215362549</v>
+        <v>24.1226196289062</v>
       </c>
       <c r="H282" t="n">
         <v>1541926</v>
@@ -8634,7 +8634,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>23.5612049102783</v>
+        <v>23.5612087249756</v>
       </c>
       <c r="H285" t="n">
         <v>619704</v>
@@ -8663,7 +8663,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G286" t="n">
-        <v>23.5612049102783</v>
+        <v>23.5612087249756</v>
       </c>
       <c r="H286" t="n">
         <v>555021</v>
@@ -8721,7 +8721,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>23.7241992950439</v>
+        <v>23.7241973876953</v>
       </c>
       <c r="H288" t="n">
         <v>395279</v>
@@ -8837,7 +8837,7 @@
         <v>26.1700000762939</v>
       </c>
       <c r="G292" t="n">
-        <v>23.6970310211182</v>
+        <v>23.6970329284668</v>
       </c>
       <c r="H292" t="n">
         <v>236982</v>
@@ -8866,7 +8866,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G293" t="n">
-        <v>23.7241992950439</v>
+        <v>23.7241973876953</v>
       </c>
       <c r="H293" t="n">
         <v>138589</v>
@@ -8953,7 +8953,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>24.0682907104492</v>
+        <v>24.0682888031006</v>
       </c>
       <c r="H296" t="n">
         <v>653226</v>
@@ -8982,7 +8982,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>23.9777374267578</v>
+        <v>23.9777355194092</v>
       </c>
       <c r="H297" t="n">
         <v>812325</v>
@@ -9011,7 +9011,7 @@
         <v>26.8299999237061</v>
       </c>
       <c r="G298" t="n">
-        <v>24.2946643829346</v>
+        <v>24.2946662902832</v>
       </c>
       <c r="H298" t="n">
         <v>540551</v>
@@ -9040,7 +9040,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G299" t="n">
-        <v>24.4304904937744</v>
+        <v>24.4304885864258</v>
       </c>
       <c r="H299" t="n">
         <v>1219756</v>
@@ -9185,7 +9185,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G304" t="n">
-        <v>25.4265460968018</v>
+        <v>25.4265441894531</v>
       </c>
       <c r="H304" t="n">
         <v>549504</v>
@@ -9243,7 +9243,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>25.6710319519043</v>
+        <v>25.6710300445557</v>
       </c>
       <c r="H306" t="n">
         <v>500694</v>
@@ -9388,7 +9388,7 @@
         <v>27.5</v>
       </c>
       <c r="G311" t="n">
-        <v>24.9013519287109</v>
+        <v>24.9013538360596</v>
       </c>
       <c r="H311" t="n">
         <v>1035739</v>
@@ -9475,7 +9475,7 @@
         <v>27.1900005340576</v>
       </c>
       <c r="G314" t="n">
-        <v>24.6206474304199</v>
+        <v>24.6206455230713</v>
       </c>
       <c r="H314" t="n">
         <v>412801</v>
@@ -9533,7 +9533,7 @@
         <v>28.0200004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>25.3722133636475</v>
+        <v>25.3722152709961</v>
       </c>
       <c r="H316" t="n">
         <v>452765</v>
@@ -9591,7 +9591,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G318" t="n">
-        <v>25.2273349761963</v>
+        <v>25.2273368835449</v>
       </c>
       <c r="H318" t="n">
         <v>385409</v>
@@ -9678,7 +9678,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>25.3993797302246</v>
+        <v>25.399377822876</v>
       </c>
       <c r="H321" t="n">
         <v>203615</v>
@@ -9707,7 +9707,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G322" t="n">
-        <v>25.4265460968018</v>
+        <v>25.4265441894531</v>
       </c>
       <c r="H322" t="n">
         <v>230403</v>
@@ -9794,7 +9794,7 @@
         <v>27.75</v>
       </c>
       <c r="G325" t="n">
-        <v>25.1277275085449</v>
+        <v>25.1277294158936</v>
       </c>
       <c r="H325" t="n">
         <v>265673</v>
@@ -9823,7 +9823,7 @@
         <v>28.4300003051758</v>
       </c>
       <c r="G326" t="n">
-        <v>25.7434711456299</v>
+        <v>25.7434730529785</v>
       </c>
       <c r="H326" t="n">
         <v>405081</v>
@@ -9939,7 +9939,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>25.2635555267334</v>
+        <v>25.2635536193848</v>
       </c>
       <c r="H330" t="n">
         <v>387257</v>
@@ -9968,7 +9968,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>25.0824565887451</v>
+        <v>25.0824546813965</v>
       </c>
       <c r="H331" t="n">
         <v>429583</v>
@@ -9997,7 +9997,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G332" t="n">
-        <v>24.7836360931396</v>
+        <v>24.7836399078369</v>
       </c>
       <c r="H332" t="n">
         <v>660230</v>
@@ -10084,7 +10084,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>24.2674980163574</v>
+        <v>24.2674999237061</v>
       </c>
       <c r="H335" t="n">
         <v>589692</v>
@@ -10142,7 +10142,7 @@
         <v>28.1900005340576</v>
       </c>
       <c r="G337" t="n">
-        <v>25.5261516571045</v>
+        <v>25.5261497497559</v>
       </c>
       <c r="H337" t="n">
         <v>379396</v>
@@ -10171,7 +10171,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>26.1237850189209</v>
+        <v>26.1237831115723</v>
       </c>
       <c r="H338" t="n">
         <v>826956</v>
@@ -10200,7 +10200,7 @@
         <v>28.9200000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>26.1871662139893</v>
+        <v>26.1871681213379</v>
       </c>
       <c r="H339" t="n">
         <v>548992</v>
@@ -10258,7 +10258,7 @@
         <v>29.25</v>
       </c>
       <c r="G341" t="n">
-        <v>26.4859828948975</v>
+        <v>26.4859867095947</v>
       </c>
       <c r="H341" t="n">
         <v>324279</v>
@@ -10316,7 +10316,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G343" t="n">
-        <v>26.6761379241943</v>
+        <v>26.676139831543</v>
       </c>
       <c r="H343" t="n">
         <v>498694</v>
@@ -10374,7 +10374,7 @@
         <v>29</v>
       </c>
       <c r="G345" t="n">
-        <v>26.2596073150635</v>
+        <v>26.2596092224121</v>
       </c>
       <c r="H345" t="n">
         <v>806664</v>
@@ -10403,7 +10403,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>26.6670837402344</v>
+        <v>26.667085647583</v>
       </c>
       <c r="H346" t="n">
         <v>297569</v>
@@ -10519,7 +10519,7 @@
         <v>29.3700008392334</v>
       </c>
       <c r="G350" t="n">
-        <v>26.5946464538574</v>
+        <v>26.5946445465088</v>
       </c>
       <c r="H350" t="n">
         <v>150195</v>
@@ -10548,7 +10548,7 @@
         <v>29</v>
       </c>
       <c r="G351" t="n">
-        <v>26.2596073150635</v>
+        <v>26.2596092224121</v>
       </c>
       <c r="H351" t="n">
         <v>536086</v>
@@ -10606,7 +10606,7 @@
         <v>27.9699993133545</v>
       </c>
       <c r="G353" t="n">
-        <v>25.326940536499</v>
+        <v>25.3269386291504</v>
       </c>
       <c r="H353" t="n">
         <v>304075</v>
@@ -10635,7 +10635,7 @@
         <v>28.5300006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>25.8340225219727</v>
+        <v>25.8340244293213</v>
       </c>
       <c r="H354" t="n">
         <v>490864</v>
@@ -10664,7 +10664,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G355" t="n">
-        <v>25.8984432220459</v>
+        <v>25.8984451293945</v>
       </c>
       <c r="H355" t="n">
         <v>233836</v>
@@ -10693,7 +10693,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G356" t="n">
-        <v>26.0641059875488</v>
+        <v>26.0641040802002</v>
       </c>
       <c r="H356" t="n">
         <v>340042</v>
@@ -10780,7 +10780,7 @@
         <v>25.2299995422363</v>
       </c>
       <c r="G359" t="n">
-        <v>23.2202453613281</v>
+        <v>23.2202472686768</v>
       </c>
       <c r="H359" t="n">
         <v>2339992</v>
@@ -10954,7 +10954,7 @@
         <v>25.25</v>
       </c>
       <c r="G365" t="n">
-        <v>23.2386531829834</v>
+        <v>23.238655090332</v>
       </c>
       <c r="H365" t="n">
         <v>396002</v>
@@ -10983,7 +10983,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G366" t="n">
-        <v>23.0453834533691</v>
+        <v>23.0453815460205</v>
       </c>
       <c r="H366" t="n">
         <v>445068</v>
@@ -11041,7 +11041,7 @@
         <v>24</v>
       </c>
       <c r="G368" t="n">
-        <v>22.0882244110107</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H368" t="n">
         <v>1374366</v>
@@ -11157,7 +11157,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>22.3643283843994</v>
+        <v>22.3643264770508</v>
       </c>
       <c r="H372" t="n">
         <v>603189</v>
@@ -11186,7 +11186,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G373" t="n">
-        <v>22.7416667938232</v>
+        <v>22.7416687011719</v>
       </c>
       <c r="H373" t="n">
         <v>827087</v>
@@ -11215,7 +11215,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G374" t="n">
-        <v>22.95334815979</v>
+        <v>22.9533500671387</v>
       </c>
       <c r="H374" t="n">
         <v>1434500</v>
@@ -11273,7 +11273,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>23.2846717834473</v>
+        <v>23.28466796875</v>
       </c>
       <c r="H376" t="n">
         <v>596955</v>
@@ -11331,7 +11331,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G378" t="n">
-        <v>23.4319248199463</v>
+        <v>23.4319267272949</v>
       </c>
       <c r="H378" t="n">
         <v>355374</v>
@@ -11360,7 +11360,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G379" t="n">
-        <v>22.806095123291</v>
+        <v>22.8060932159424</v>
       </c>
       <c r="H379" t="n">
         <v>684365</v>
@@ -11418,7 +11418,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G381" t="n">
-        <v>22.6036167144775</v>
+        <v>22.6036186218262</v>
       </c>
       <c r="H381" t="n">
         <v>369901</v>
@@ -11447,7 +11447,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>22.2538890838623</v>
+        <v>22.2538871765137</v>
       </c>
       <c r="H382" t="n">
         <v>540961</v>
@@ -11505,7 +11505,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>21.4900016784668</v>
+        <v>21.4900035858154</v>
       </c>
       <c r="H384" t="n">
         <v>361338</v>
@@ -11592,7 +11592,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>21.6740703582764</v>
+        <v>21.674072265625</v>
       </c>
       <c r="H387" t="n">
         <v>321536</v>
@@ -11737,7 +11737,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G392" t="n">
-        <v>21.1218681335449</v>
+        <v>21.1218662261963</v>
       </c>
       <c r="H392" t="n">
         <v>933779</v>
@@ -11853,7 +11853,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G396" t="n">
-        <v>21.8857498168945</v>
+        <v>21.8857517242432</v>
       </c>
       <c r="H396" t="n">
         <v>305318</v>
@@ -11882,7 +11882,7 @@
         <v>23.8700008392334</v>
       </c>
       <c r="G397" t="n">
-        <v>21.9685802459717</v>
+        <v>21.9685821533203</v>
       </c>
       <c r="H397" t="n">
         <v>424576</v>
@@ -11940,7 +11940,7 @@
         <v>24.3099994659424</v>
       </c>
       <c r="G399" t="n">
-        <v>22.3735313415527</v>
+        <v>22.3735332489014</v>
       </c>
       <c r="H399" t="n">
         <v>712169</v>
@@ -11969,7 +11969,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G400" t="n">
-        <v>22.2170715332031</v>
+        <v>22.2170734405518</v>
       </c>
       <c r="H400" t="n">
         <v>358847</v>
@@ -11998,7 +11998,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G401" t="n">
-        <v>22.4103450775146</v>
+        <v>22.410343170166</v>
       </c>
       <c r="H401" t="n">
         <v>372937</v>
@@ -12056,7 +12056,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G403" t="n">
-        <v>22.6312294006348</v>
+        <v>22.6312274932861</v>
       </c>
       <c r="H403" t="n">
         <v>246554</v>
@@ -12114,7 +12114,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G405" t="n">
-        <v>22.5576019287109</v>
+        <v>22.5576000213623</v>
       </c>
       <c r="H405" t="n">
         <v>352700</v>
@@ -12143,7 +12143,7 @@
         <v>24</v>
       </c>
       <c r="G406" t="n">
-        <v>22.0882244110107</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H406" t="n">
         <v>1576783</v>
@@ -12172,7 +12172,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G407" t="n">
-        <v>21.4255809783936</v>
+        <v>21.4255790710449</v>
       </c>
       <c r="H407" t="n">
         <v>844820</v>
@@ -12230,7 +12230,7 @@
         <v>24</v>
       </c>
       <c r="G409" t="n">
-        <v>22.0882244110107</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H409" t="n">
         <v>517420</v>
@@ -12259,7 +12259,7 @@
         <v>24.1900005340576</v>
       </c>
       <c r="G410" t="n">
-        <v>22.263090133667</v>
+        <v>22.2630920410156</v>
       </c>
       <c r="H410" t="n">
         <v>366457</v>
@@ -12288,7 +12288,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G411" t="n">
-        <v>22.5391941070557</v>
+        <v>22.539192199707</v>
       </c>
       <c r="H411" t="n">
         <v>497939</v>
@@ -12462,7 +12462,7 @@
         <v>24.2700004577637</v>
       </c>
       <c r="G417" t="n">
-        <v>22.3367195129395</v>
+        <v>22.3367176055908</v>
       </c>
       <c r="H417" t="n">
         <v>583263</v>
@@ -12520,7 +12520,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>21.7661037445068</v>
+        <v>21.7661056518555</v>
       </c>
       <c r="H419" t="n">
         <v>234785</v>
@@ -12549,7 +12549,7 @@
         <v>23.9699993133545</v>
       </c>
       <c r="G420" t="n">
-        <v>22.0606155395508</v>
+        <v>22.0606136322021</v>
       </c>
       <c r="H420" t="n">
         <v>197206</v>
@@ -12578,7 +12578,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G421" t="n">
-        <v>21.7568988800049</v>
+        <v>21.7569026947021</v>
       </c>
       <c r="H421" t="n">
         <v>283848</v>
@@ -12636,7 +12636,7 @@
         <v>24</v>
       </c>
       <c r="G423" t="n">
-        <v>22.0882244110107</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H423" t="n">
         <v>206329</v>
@@ -12723,7 +12723,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G426" t="n">
-        <v>22.0053939819336</v>
+        <v>22.0053958892822</v>
       </c>
       <c r="H426" t="n">
         <v>237338</v>
@@ -12752,7 +12752,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G427" t="n">
-        <v>22.2170715332031</v>
+        <v>22.2170734405518</v>
       </c>
       <c r="H427" t="n">
         <v>537878</v>
@@ -12810,7 +12810,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G429" t="n">
-        <v>22.0053939819336</v>
+        <v>22.0053958892822</v>
       </c>
       <c r="H429" t="n">
         <v>233703</v>
@@ -12897,7 +12897,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G432" t="n">
-        <v>22.1250419616699</v>
+        <v>22.1250400543213</v>
       </c>
       <c r="H432" t="n">
         <v>181819</v>
@@ -12955,7 +12955,7 @@
         <v>23.9300003051758</v>
       </c>
       <c r="G434" t="n">
-        <v>22.0238018035889</v>
+        <v>22.0238037109375</v>
       </c>
       <c r="H434" t="n">
         <v>408570</v>
@@ -13013,7 +13013,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>21.9041576385498</v>
+        <v>21.9041557312012</v>
       </c>
       <c r="H436" t="n">
         <v>1117273</v>
@@ -13100,7 +13100,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G439" t="n">
-        <v>21.0574398040771</v>
+        <v>21.0574417114258</v>
       </c>
       <c r="H439" t="n">
         <v>1031440</v>
@@ -13158,7 +13158,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>20.7997455596924</v>
+        <v>20.799747467041</v>
       </c>
       <c r="H441" t="n">
         <v>1083075</v>
@@ -13187,7 +13187,7 @@
         <v>22.9300003051758</v>
       </c>
       <c r="G442" t="n">
-        <v>21.1034603118896</v>
+        <v>21.103458404541</v>
       </c>
       <c r="H442" t="n">
         <v>361840</v>
@@ -13216,7 +13216,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>21.0758495330811</v>
+        <v>21.0758476257324</v>
       </c>
       <c r="H443" t="n">
         <v>297588</v>
@@ -13274,7 +13274,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>21.9501762390137</v>
+        <v>21.950174331665</v>
       </c>
       <c r="H445" t="n">
         <v>1478816</v>
@@ -13361,7 +13361,7 @@
         <v>23.75</v>
       </c>
       <c r="G448" t="n">
-        <v>21.8581390380859</v>
+        <v>21.8581371307373</v>
       </c>
       <c r="H448" t="n">
         <v>541964</v>
@@ -13419,7 +13419,7 @@
         <v>23.5100002288818</v>
       </c>
       <c r="G450" t="n">
-        <v>21.6372585296631</v>
+        <v>21.6372566223145</v>
       </c>
       <c r="H450" t="n">
         <v>1176964</v>
@@ -13448,7 +13448,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G451" t="n">
-        <v>21.2967319488525</v>
+        <v>21.2967300415039</v>
       </c>
       <c r="H451" t="n">
         <v>599089</v>
@@ -13477,7 +13477,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G452" t="n">
-        <v>20.9746112823486</v>
+        <v>20.9746131896973</v>
       </c>
       <c r="H452" t="n">
         <v>950234</v>
@@ -13506,7 +13506,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>20.7997455596924</v>
+        <v>20.799747467041</v>
       </c>
       <c r="H453" t="n">
         <v>536977</v>
@@ -13535,7 +13535,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>20.9838123321533</v>
+        <v>20.983814239502</v>
       </c>
       <c r="H454" t="n">
         <v>572574</v>
@@ -13622,7 +13622,7 @@
         <v>22.5</v>
       </c>
       <c r="G457" t="n">
-        <v>20.7077121734619</v>
+        <v>20.7077102661133</v>
       </c>
       <c r="H457" t="n">
         <v>475690</v>
@@ -13651,7 +13651,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G458" t="n">
-        <v>21.0942573547363</v>
+        <v>21.0942554473877</v>
       </c>
       <c r="H458" t="n">
         <v>987915</v>
@@ -13709,7 +13709,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G460" t="n">
-        <v>21.0206279754639</v>
+        <v>21.0206298828125</v>
       </c>
       <c r="H460" t="n">
         <v>386462</v>
@@ -13854,7 +13854,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G465" t="n">
-        <v>20.39479637146</v>
+        <v>20.3947925567627</v>
       </c>
       <c r="H465" t="n">
         <v>664948</v>
@@ -13883,7 +13883,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G466" t="n">
-        <v>20.0082492828369</v>
+        <v>20.0082511901855</v>
       </c>
       <c r="H466" t="n">
         <v>1396902</v>
@@ -13912,7 +13912,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>19.9714393615723</v>
+        <v>19.9714374542236</v>
       </c>
       <c r="H467" t="n">
         <v>1435364</v>
@@ -13970,7 +13970,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G469" t="n">
-        <v>20.4868297576904</v>
+        <v>20.4868278503418</v>
       </c>
       <c r="H469" t="n">
         <v>471696</v>
@@ -14057,7 +14057,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G472" t="n">
-        <v>21.0206279754639</v>
+        <v>21.0206298828125</v>
       </c>
       <c r="H472" t="n">
         <v>601843</v>
@@ -14115,7 +14115,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G474" t="n">
-        <v>21.2415084838867</v>
+        <v>21.2415103912354</v>
       </c>
       <c r="H474" t="n">
         <v>971079</v>
@@ -14144,7 +14144,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G475" t="n">
-        <v>20.9285926818848</v>
+        <v>20.9285945892334</v>
       </c>
       <c r="H475" t="n">
         <v>884159</v>
@@ -14202,7 +14202,7 @@
         <v>22.5</v>
       </c>
       <c r="G477" t="n">
-        <v>20.7077121734619</v>
+        <v>20.7077102661133</v>
       </c>
       <c r="H477" t="n">
         <v>777593</v>
@@ -14231,7 +14231,7 @@
         <v>22</v>
       </c>
       <c r="G478" t="n">
-        <v>20.2475395202637</v>
+        <v>20.2475414276123</v>
       </c>
       <c r="H478" t="n">
         <v>750579</v>
@@ -14289,7 +14289,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G480" t="n">
-        <v>20.0910835266113</v>
+        <v>20.0910816192627</v>
       </c>
       <c r="H480" t="n">
         <v>280042</v>
@@ -14318,7 +14318,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G481" t="n">
-        <v>19.2719764709473</v>
+        <v>19.2719783782959</v>
       </c>
       <c r="H481" t="n">
         <v>2609341</v>
@@ -14492,7 +14492,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>20.2935562133789</v>
+        <v>20.2935581207275</v>
       </c>
       <c r="H487" t="n">
         <v>410849</v>
@@ -14550,7 +14550,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G489" t="n">
-        <v>20.5696620941162</v>
+        <v>20.5696601867676</v>
       </c>
       <c r="H489" t="n">
         <v>438572</v>
@@ -14579,7 +14579,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>20.6616954803467</v>
+        <v>20.661693572998</v>
       </c>
       <c r="H490" t="n">
         <v>354523</v>
@@ -14608,7 +14608,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G491" t="n">
-        <v>20.9838123321533</v>
+        <v>20.983814239502</v>
       </c>
       <c r="H491" t="n">
         <v>580090</v>
@@ -14666,7 +14666,7 @@
         <v>22.5</v>
       </c>
       <c r="G493" t="n">
-        <v>20.7077121734619</v>
+        <v>20.7077102661133</v>
       </c>
       <c r="H493" t="n">
         <v>633331</v>
@@ -14695,7 +14695,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G494" t="n">
-        <v>21.0482387542725</v>
+        <v>21.0482406616211</v>
       </c>
       <c r="H494" t="n">
         <v>362134</v>
@@ -14782,7 +14782,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G497" t="n">
-        <v>21.1218681335449</v>
+        <v>21.1218662261963</v>
       </c>
       <c r="H497" t="n">
         <v>298866</v>
@@ -14811,7 +14811,7 @@
         <v>23.3099994659424</v>
       </c>
       <c r="G498" t="n">
-        <v>21.4531879425049</v>
+        <v>21.4531898498535</v>
       </c>
       <c r="H498" t="n">
         <v>526941</v>
@@ -14927,7 +14927,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G502" t="n">
-        <v>20.7721347808838</v>
+        <v>20.7721366882324</v>
       </c>
       <c r="H502" t="n">
         <v>621541</v>
@@ -14956,7 +14956,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>19.4652500152588</v>
+        <v>19.4652481079102</v>
       </c>
       <c r="H503" t="n">
         <v>2465735</v>
@@ -14985,7 +14985,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G504" t="n">
-        <v>19.7965717315674</v>
+        <v>19.796573638916</v>
       </c>
       <c r="H504" t="n">
         <v>852016</v>
@@ -15101,7 +15101,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G508" t="n">
-        <v>20.2935562133789</v>
+        <v>20.2935581207275</v>
       </c>
       <c r="H508" t="n">
         <v>210477</v>
@@ -15130,7 +15130,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>20.229133605957</v>
+        <v>20.2291355133057</v>
       </c>
       <c r="H509" t="n">
         <v>191733</v>
@@ -15159,7 +15159,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>20.2935562133789</v>
+        <v>20.2935581207275</v>
       </c>
       <c r="H510" t="n">
         <v>222355</v>
@@ -15391,7 +15391,7 @@
         <v>22.2399997711182</v>
       </c>
       <c r="G518" t="n">
-        <v>20.4684219360352</v>
+        <v>20.4684238433838</v>
       </c>
       <c r="H518" t="n">
         <v>324669</v>
@@ -15449,7 +15449,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G520" t="n">
-        <v>20.4868297576904</v>
+        <v>20.4868278503418</v>
       </c>
       <c r="H520" t="n">
         <v>710973</v>
@@ -15536,7 +15536,7 @@
         <v>22</v>
       </c>
       <c r="G523" t="n">
-        <v>20.2475395202637</v>
+        <v>20.2475414276123</v>
       </c>
       <c r="H523" t="n">
         <v>290730</v>
@@ -15565,7 +15565,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G524" t="n">
-        <v>20.1739139556885</v>
+        <v>20.1739120483398</v>
       </c>
       <c r="H524" t="n">
         <v>499386</v>
@@ -15623,7 +15623,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G526" t="n">
-        <v>21.7568988800049</v>
+        <v>21.7569026947021</v>
       </c>
       <c r="H526" t="n">
         <v>1540488</v>
@@ -15652,7 +15652,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G527" t="n">
-        <v>21.2967319488525</v>
+        <v>21.2967300415039</v>
       </c>
       <c r="H527" t="n">
         <v>604201</v>
@@ -15681,7 +15681,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>21.259916305542</v>
+        <v>21.2599182128906</v>
       </c>
       <c r="H528" t="n">
         <v>954306</v>
@@ -15710,7 +15710,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>21.259916305542</v>
+        <v>21.2599182128906</v>
       </c>
       <c r="H529" t="n">
         <v>726158</v>
@@ -15797,7 +15797,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>21.1218681335449</v>
+        <v>21.1218662261963</v>
       </c>
       <c r="H532" t="n">
         <v>424239</v>
@@ -15884,7 +15884,7 @@
         <v>22.7299995422363</v>
       </c>
       <c r="G535" t="n">
-        <v>20.9193916320801</v>
+        <v>20.9193897247314</v>
       </c>
       <c r="H535" t="n">
         <v>452147</v>
@@ -16000,7 +16000,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G539" t="n">
-        <v>20.0266571044922</v>
+        <v>20.0266590118408</v>
       </c>
       <c r="H539" t="n">
         <v>614365</v>
@@ -16058,7 +16058,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G541" t="n">
-        <v>20.0082492828369</v>
+        <v>20.0082511901855</v>
       </c>
       <c r="H541" t="n">
         <v>190751</v>
@@ -16087,7 +16087,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G542" t="n">
-        <v>19.9162158966064</v>
+        <v>19.9162178039551</v>
       </c>
       <c r="H542" t="n">
         <v>415655</v>
@@ -16116,7 +16116,7 @@
         <v>22</v>
       </c>
       <c r="G543" t="n">
-        <v>20.2475395202637</v>
+        <v>20.2475414276123</v>
       </c>
       <c r="H543" t="n">
         <v>619390</v>
@@ -16145,7 +16145,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G544" t="n">
-        <v>20.5604553222656</v>
+        <v>20.5604572296143</v>
       </c>
       <c r="H544" t="n">
         <v>590508</v>
@@ -16261,7 +16261,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G548" t="n">
-        <v>20.9838123321533</v>
+        <v>20.983814239502</v>
       </c>
       <c r="H548" t="n">
         <v>361715</v>
@@ -16319,7 +16319,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G550" t="n">
-        <v>20.9285926818848</v>
+        <v>20.9285945892334</v>
       </c>
       <c r="H550" t="n">
         <v>308603</v>
@@ -16348,7 +16348,7 @@
         <v>22.75</v>
       </c>
       <c r="G551" t="n">
-        <v>20.9377956390381</v>
+        <v>20.9377975463867</v>
       </c>
       <c r="H551" t="n">
         <v>330493</v>
@@ -16377,7 +16377,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G552" t="n">
-        <v>20.8365592956543</v>
+        <v>20.8365573883057</v>
       </c>
       <c r="H552" t="n">
         <v>218015</v>
@@ -16406,7 +16406,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G553" t="n">
-        <v>21.2967319488525</v>
+        <v>21.2967300415039</v>
       </c>
       <c r="H553" t="n">
         <v>2496511</v>
@@ -16464,7 +16464,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G555" t="n">
-        <v>20.6248817443848</v>
+        <v>20.6248836517334</v>
       </c>
       <c r="H555" t="n">
         <v>551415</v>
@@ -16522,7 +16522,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G557" t="n">
-        <v>20.0910835266113</v>
+        <v>20.0910816192627</v>
       </c>
       <c r="H557" t="n">
         <v>895894</v>
@@ -16551,7 +16551,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>20.109489440918</v>
+        <v>20.1094875335693</v>
       </c>
       <c r="H558" t="n">
         <v>598799</v>
@@ -16580,7 +16580,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>19.9714393615723</v>
+        <v>19.9714374542236</v>
       </c>
       <c r="H559" t="n">
         <v>860738</v>
@@ -16667,7 +16667,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>20.109489440918</v>
+        <v>20.1094875335693</v>
       </c>
       <c r="H562" t="n">
         <v>392838</v>
@@ -16783,7 +16783,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G566" t="n">
-        <v>20.5696620941162</v>
+        <v>20.5696601867676</v>
       </c>
       <c r="H566" t="n">
         <v>548117</v>
@@ -16812,7 +16812,7 @@
         <v>22.6800003051758</v>
       </c>
       <c r="G567" t="n">
-        <v>20.8733749389648</v>
+        <v>20.8733730316162</v>
       </c>
       <c r="H567" t="n">
         <v>588294</v>
@@ -16928,7 +16928,7 @@
         <v>22.3099994659424</v>
       </c>
       <c r="G571" t="n">
-        <v>20.532844543457</v>
+        <v>20.5328464508057</v>
       </c>
       <c r="H571" t="n">
         <v>211904</v>
@@ -17044,7 +17044,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G575" t="n">
-        <v>20.6432876586914</v>
+        <v>20.64328956604</v>
       </c>
       <c r="H575" t="n">
         <v>199750</v>
@@ -17073,7 +17073,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>20.6156768798828</v>
+        <v>20.6156749725342</v>
       </c>
       <c r="H576" t="n">
         <v>263654</v>
@@ -17189,7 +17189,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G580" t="n">
-        <v>20.39479637146</v>
+        <v>20.3947925567627</v>
       </c>
       <c r="H580" t="n">
         <v>589931</v>
@@ -17247,7 +17247,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G582" t="n">
-        <v>20.9746112823486</v>
+        <v>20.9746131896973</v>
       </c>
       <c r="H582" t="n">
         <v>623938</v>
@@ -17305,7 +17305,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>21.2783241271973</v>
+        <v>21.2783260345459</v>
       </c>
       <c r="H584" t="n">
         <v>190641</v>
@@ -17334,7 +17334,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G585" t="n">
-        <v>21.3151378631592</v>
+        <v>21.3151359558105</v>
       </c>
       <c r="H585" t="n">
         <v>732771</v>
@@ -17392,7 +17392,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>21.536018371582</v>
+        <v>21.5360202789307</v>
       </c>
       <c r="H587" t="n">
         <v>858748</v>
@@ -17421,7 +17421,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>21.536018371582</v>
+        <v>21.5360202789307</v>
       </c>
       <c r="H588" t="n">
         <v>693444</v>
@@ -17450,7 +17450,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G589" t="n">
-        <v>21.7937164306641</v>
+        <v>21.7937145233154</v>
       </c>
       <c r="H589" t="n">
         <v>611824</v>
@@ -17479,7 +17479,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G590" t="n">
-        <v>22.6496353149414</v>
+        <v>22.6496334075928</v>
       </c>
       <c r="H590" t="n">
         <v>1399669</v>
@@ -17595,7 +17595,7 @@
         <v>24.5200004577637</v>
       </c>
       <c r="G594" t="n">
-        <v>22.5668048858643</v>
+        <v>22.5668029785156</v>
       </c>
       <c r="H594" t="n">
         <v>527263</v>
@@ -17653,7 +17653,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G596" t="n">
-        <v>22.7416667938232</v>
+        <v>22.7416687011719</v>
       </c>
       <c r="H596" t="n">
         <v>747463</v>
@@ -17740,7 +17740,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G599" t="n">
-        <v>22.6312294006348</v>
+        <v>22.6312274932861</v>
       </c>
       <c r="H599" t="n">
         <v>1281081</v>
@@ -17769,7 +17769,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>22.9165325164795</v>
+        <v>22.9165344238281</v>
       </c>
       <c r="H600" t="n">
         <v>543073</v>
@@ -17827,7 +17827,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>22.7324638366699</v>
+        <v>22.7324657440186</v>
       </c>
       <c r="H602" t="n">
         <v>336880</v>
@@ -17885,7 +17885,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G604" t="n">
-        <v>22.7692813873291</v>
+        <v>22.7692775726318</v>
       </c>
       <c r="H604" t="n">
         <v>300428</v>
@@ -17914,7 +17914,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G605" t="n">
-        <v>22.9073295593262</v>
+        <v>22.9073314666748</v>
       </c>
       <c r="H605" t="n">
         <v>415746</v>
@@ -17943,7 +17943,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G606" t="n">
-        <v>23.2754707336426</v>
+        <v>23.2754688262939</v>
       </c>
       <c r="H606" t="n">
         <v>719915</v>
@@ -17972,7 +17972,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>22.9165325164795</v>
+        <v>22.9165344238281</v>
       </c>
       <c r="H607" t="n">
         <v>378581</v>
@@ -18030,7 +18030,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G609" t="n">
-        <v>23.3090686798096</v>
+        <v>23.3090705871582</v>
       </c>
       <c r="H609" t="n">
         <v>451695</v>
@@ -18088,7 +18088,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G611" t="n">
-        <v>22.907190322876</v>
+        <v>22.9071884155273</v>
       </c>
       <c r="H611" t="n">
         <v>487106</v>
@@ -18146,7 +18146,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G613" t="n">
-        <v>22.7296142578125</v>
+        <v>22.7296123504639</v>
       </c>
       <c r="H613" t="n">
         <v>339316</v>
@@ -18204,7 +18204,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>22.6174602508545</v>
+        <v>22.6174621582031</v>
       </c>
       <c r="H615" t="n">
         <v>501155</v>
@@ -18233,7 +18233,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G616" t="n">
-        <v>23.07541847229</v>
+        <v>23.0754165649414</v>
       </c>
       <c r="H616" t="n">
         <v>441644</v>
@@ -18262,7 +18262,7 @@
         <v>24.9899997711182</v>
       </c>
       <c r="G617" t="n">
-        <v>23.3557968139648</v>
+        <v>23.3557987213135</v>
       </c>
       <c r="H617" t="n">
         <v>414529</v>
@@ -18494,7 +18494,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>23.505334854126</v>
+        <v>23.5053367614746</v>
       </c>
       <c r="H625" t="n">
         <v>253050</v>
@@ -18639,7 +18639,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G630" t="n">
-        <v>20.9912452697754</v>
+        <v>20.991247177124</v>
       </c>
       <c r="H630" t="n">
         <v>3551454</v>
@@ -18668,7 +18668,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G631" t="n">
-        <v>20.3370208740234</v>
+        <v>20.3370227813721</v>
       </c>
       <c r="H631" t="n">
         <v>1272365</v>
@@ -18697,7 +18697,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G632" t="n">
-        <v>20.3370208740234</v>
+        <v>20.3370227813721</v>
       </c>
       <c r="H632" t="n">
         <v>880006</v>
@@ -18813,7 +18813,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G636" t="n">
-        <v>19.3089561462402</v>
+        <v>19.3089542388916</v>
       </c>
       <c r="H636" t="n">
         <v>671130</v>
@@ -18900,7 +18900,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>19.3463401794434</v>
+        <v>19.346342086792</v>
       </c>
       <c r="H639" t="n">
         <v>480213</v>
@@ -18929,7 +18929,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G640" t="n">
-        <v>19.0285739898682</v>
+        <v>19.0285758972168</v>
       </c>
       <c r="H640" t="n">
         <v>403933</v>
@@ -18958,7 +18958,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G641" t="n">
-        <v>18.6266937255859</v>
+        <v>18.6266956329346</v>
       </c>
       <c r="H641" t="n">
         <v>874180</v>
@@ -19161,7 +19161,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G648" t="n">
-        <v>18.6360378265381</v>
+        <v>18.6360397338867</v>
       </c>
       <c r="H648" t="n">
         <v>360124</v>
@@ -19219,7 +19219,7 @@
         <v>20.0900001525879</v>
       </c>
       <c r="G650" t="n">
-        <v>18.7762317657471</v>
+        <v>18.7762298583984</v>
       </c>
       <c r="H650" t="n">
         <v>526322</v>
@@ -19248,7 +19248,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G651" t="n">
-        <v>18.720157623291</v>
+        <v>18.7201557159424</v>
       </c>
       <c r="H651" t="n">
         <v>386178</v>
@@ -19306,7 +19306,7 @@
         <v>19.875</v>
       </c>
       <c r="G653" t="n">
-        <v>18.5752906799316</v>
+        <v>18.5752925872803</v>
       </c>
       <c r="H653" t="n">
         <v>336549</v>
@@ -19335,7 +19335,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G654" t="n">
-        <v>18.3930435180664</v>
+        <v>18.3930416107178</v>
       </c>
       <c r="H654" t="n">
         <v>659845</v>
@@ -19364,7 +19364,7 @@
         <v>19.8250007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>18.5285587310791</v>
+        <v>18.5285606384277</v>
       </c>
       <c r="H655" t="n">
         <v>472136</v>
@@ -19509,7 +19509,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G660" t="n">
-        <v>18.2435054779053</v>
+        <v>18.2435073852539</v>
       </c>
       <c r="H660" t="n">
         <v>1645512</v>
@@ -19596,7 +19596,7 @@
         <v>19.375</v>
       </c>
       <c r="G663" t="n">
-        <v>18.1079883575439</v>
+        <v>18.1079864501953</v>
       </c>
       <c r="H663" t="n">
         <v>697033</v>
@@ -19654,7 +19654,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G665" t="n">
-        <v>18.6734256744385</v>
+        <v>18.6734237670898</v>
       </c>
       <c r="H665" t="n">
         <v>384784</v>
@@ -19741,7 +19741,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G668" t="n">
-        <v>18.6734256744385</v>
+        <v>18.6734237670898</v>
       </c>
       <c r="H668" t="n">
         <v>269268</v>
@@ -19770,7 +19770,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G669" t="n">
-        <v>18.720157623291</v>
+        <v>18.7201557159424</v>
       </c>
       <c r="H669" t="n">
         <v>247847</v>
@@ -19944,7 +19944,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G675" t="n">
-        <v>19.1407241821289</v>
+        <v>19.1407260894775</v>
       </c>
       <c r="H675" t="n">
         <v>1646978</v>
@@ -20060,7 +20060,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G679" t="n">
-        <v>19.430456161499</v>
+        <v>19.4304523468018</v>
       </c>
       <c r="H679" t="n">
         <v>207201</v>
@@ -20118,7 +20118,7 @@
         <v>20.5</v>
       </c>
       <c r="G681" t="n">
-        <v>19.1594200134277</v>
+        <v>19.1594181060791</v>
       </c>
       <c r="H681" t="n">
         <v>262991</v>
@@ -20147,7 +20147,7 @@
         <v>20.5100002288818</v>
       </c>
       <c r="G682" t="n">
-        <v>19.1687660217285</v>
+        <v>19.1687679290771</v>
       </c>
       <c r="H682" t="n">
         <v>127650</v>
@@ -20263,7 +20263,7 @@
         <v>20.5</v>
       </c>
       <c r="G686" t="n">
-        <v>19.1594200134277</v>
+        <v>19.1594181060791</v>
       </c>
       <c r="H686" t="n">
         <v>375929</v>
@@ -20292,7 +20292,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G687" t="n">
-        <v>19.0566101074219</v>
+        <v>19.0566120147705</v>
       </c>
       <c r="H687" t="n">
         <v>411927</v>
@@ -20321,7 +20321,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G688" t="n">
-        <v>18.8416519165039</v>
+        <v>18.8416538238525</v>
       </c>
       <c r="H688" t="n">
         <v>335800</v>
@@ -20466,7 +20466,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>19.8136425018311</v>
+        <v>19.8136405944824</v>
       </c>
       <c r="H693" t="n">
         <v>277253</v>
@@ -20640,7 +20640,7 @@
         <v>21.1700000762939</v>
       </c>
       <c r="G699" t="n">
-        <v>19.7856063842773</v>
+        <v>19.7856044769287</v>
       </c>
       <c r="H699" t="n">
         <v>160234</v>
@@ -20756,7 +20756,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G703" t="n">
-        <v>18.8977279663086</v>
+        <v>18.8977298736572</v>
       </c>
       <c r="H703" t="n">
         <v>336450</v>
@@ -20785,7 +20785,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G704" t="n">
-        <v>19.0566101074219</v>
+        <v>19.0566120147705</v>
       </c>
       <c r="H704" t="n">
         <v>303150</v>
@@ -20843,7 +20843,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>18.879035949707</v>
+        <v>18.8790378570557</v>
       </c>
       <c r="H706" t="n">
         <v>303793</v>
@@ -20901,7 +20901,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>18.6453857421875</v>
+        <v>18.6453876495361</v>
       </c>
       <c r="H708" t="n">
         <v>698237</v>
@@ -20930,7 +20930,7 @@
         <v>19.1049995422363</v>
       </c>
       <c r="G709" t="n">
-        <v>17.8556442260742</v>
+        <v>17.8556423187256</v>
       </c>
       <c r="H709" t="n">
         <v>1289181</v>
@@ -20988,7 +20988,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G711" t="n">
-        <v>17.1546878814697</v>
+        <v>17.1546897888184</v>
       </c>
       <c r="H711" t="n">
         <v>1871086</v>
@@ -21075,7 +21075,7 @@
         <v>19.2049999237061</v>
       </c>
       <c r="G714" t="n">
-        <v>17.9491062164307</v>
+        <v>17.949104309082</v>
       </c>
       <c r="H714" t="n">
         <v>391842</v>
@@ -21133,7 +21133,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G716" t="n">
-        <v>18.2154693603516</v>
+        <v>18.2154655456543</v>
       </c>
       <c r="H716" t="n">
         <v>327778</v>
@@ -21220,7 +21220,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G719" t="n">
-        <v>19.0098819732666</v>
+        <v>19.0098838806152</v>
       </c>
       <c r="H719" t="n">
         <v>746830</v>
@@ -21249,7 +21249,7 @@
         <v>20.9699993133545</v>
       </c>
       <c r="G720" t="n">
-        <v>19.5986824035645</v>
+        <v>19.5986843109131</v>
       </c>
       <c r="H720" t="n">
         <v>628747</v>
@@ -21307,7 +21307,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G722" t="n">
-        <v>19.6454124450684</v>
+        <v>19.645414352417</v>
       </c>
       <c r="H722" t="n">
         <v>418618</v>
@@ -21365,7 +21365,7 @@
         <v>20.9099998474121</v>
       </c>
       <c r="G724" t="n">
-        <v>19.5426082611084</v>
+        <v>19.5426063537598</v>
       </c>
       <c r="H724" t="n">
         <v>436766</v>
@@ -21423,7 +21423,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>20.0005626678467</v>
+        <v>20.0005645751953</v>
       </c>
       <c r="H726" t="n">
         <v>543208</v>
@@ -21626,7 +21626,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G733" t="n">
-        <v>19.7014904022217</v>
+        <v>19.701488494873</v>
       </c>
       <c r="H733" t="n">
         <v>369031</v>
@@ -21713,7 +21713,7 @@
         <v>20.75</v>
       </c>
       <c r="G736" t="n">
-        <v>19.3930702209473</v>
+        <v>19.3930721282959</v>
       </c>
       <c r="H736" t="n">
         <v>268555</v>
@@ -21800,7 +21800,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>18.7855777740479</v>
+        <v>18.7855796813965</v>
       </c>
       <c r="H739" t="n">
         <v>486148</v>
@@ -21829,7 +21829,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>18.7855777740479</v>
+        <v>18.7855796813965</v>
       </c>
       <c r="H740" t="n">
         <v>351777</v>
@@ -22003,7 +22003,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>19.3463401794434</v>
+        <v>19.346342086792</v>
       </c>
       <c r="H746" t="n">
         <v>177553</v>
@@ -22032,7 +22032,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G747" t="n">
-        <v>19.7014904022217</v>
+        <v>19.701488494873</v>
       </c>
       <c r="H747" t="n">
         <v>368527</v>
@@ -22090,7 +22090,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G749" t="n">
-        <v>19.430456161499</v>
+        <v>19.4304523468018</v>
       </c>
       <c r="H749" t="n">
         <v>241093</v>
@@ -22119,7 +22119,7 @@
         <v>20.5</v>
       </c>
       <c r="G750" t="n">
-        <v>19.1594200134277</v>
+        <v>19.1594181060791</v>
       </c>
       <c r="H750" t="n">
         <v>466560</v>
@@ -22148,7 +22148,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>19.206148147583</v>
+        <v>19.2061462402344</v>
       </c>
       <c r="H751" t="n">
         <v>366498</v>
@@ -22177,7 +22177,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G752" t="n">
-        <v>18.6734256744385</v>
+        <v>18.6734237670898</v>
       </c>
       <c r="H752" t="n">
         <v>502005</v>
@@ -22206,7 +22206,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G753" t="n">
-        <v>18.3930435180664</v>
+        <v>18.3930416107178</v>
       </c>
       <c r="H753" t="n">
         <v>452457</v>
@@ -22235,7 +22235,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G754" t="n">
-        <v>17.0472087860107</v>
+        <v>17.0472106933594</v>
       </c>
       <c r="H754" t="n">
         <v>1928028</v>
@@ -22293,7 +22293,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G756" t="n">
-        <v>16.8135585784912</v>
+        <v>16.8135566711426</v>
       </c>
       <c r="H756" t="n">
         <v>831352</v>
@@ -22438,7 +22438,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>16.495792388916</v>
+        <v>16.4957904815674</v>
       </c>
       <c r="H761" t="n">
         <v>1354957</v>
@@ -22496,7 +22496,7 @@
         <v>17.6550006866455</v>
       </c>
       <c r="G763" t="n">
-        <v>16.5004653930664</v>
+        <v>16.500467300415</v>
       </c>
       <c r="H763" t="n">
         <v>514163</v>
@@ -22612,7 +22612,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>16.495792388916</v>
+        <v>16.4957904815674</v>
       </c>
       <c r="H767" t="n">
         <v>341314</v>
@@ -22699,7 +22699,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G770" t="n">
-        <v>16.6640205383301</v>
+        <v>16.6640224456787</v>
       </c>
       <c r="H770" t="n">
         <v>368576</v>
@@ -22757,7 +22757,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>16.495792388916</v>
+        <v>16.4957904815674</v>
       </c>
       <c r="H772" t="n">
         <v>357653</v>
@@ -22873,7 +22873,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G776" t="n">
-        <v>16.8135585784912</v>
+        <v>16.8135566711426</v>
       </c>
       <c r="H776" t="n">
         <v>396353</v>
@@ -22902,7 +22902,7 @@
         <v>17.5750007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>16.4256992340088</v>
+        <v>16.4256973266602</v>
       </c>
       <c r="H777" t="n">
         <v>608356</v>
@@ -22931,7 +22931,7 @@
         <v>17.2549991607666</v>
       </c>
       <c r="G778" t="n">
-        <v>16.1266231536865</v>
+        <v>16.1266212463379</v>
       </c>
       <c r="H778" t="n">
         <v>546458</v>
@@ -22989,7 +22989,7 @@
         <v>17.2549991607666</v>
       </c>
       <c r="G780" t="n">
-        <v>16.1266231536865</v>
+        <v>16.1266212463379</v>
       </c>
       <c r="H780" t="n">
         <v>354071</v>
@@ -23047,7 +23047,7 @@
         <v>17.3250007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>16.1920471191406</v>
+        <v>16.192045211792</v>
       </c>
       <c r="H782" t="n">
         <v>289549</v>
@@ -23192,7 +23192,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G787" t="n">
-        <v>16.495792388916</v>
+        <v>16.4957904815674</v>
       </c>
       <c r="H787" t="n">
         <v>375724</v>
@@ -23221,7 +23221,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G788" t="n">
-        <v>16.523832321167</v>
+        <v>16.5238304138184</v>
       </c>
       <c r="H788" t="n">
         <v>412006</v>
@@ -23308,7 +23308,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G791" t="n">
-        <v>16.2995262145996</v>
+        <v>16.299524307251</v>
       </c>
       <c r="H791" t="n">
         <v>193986</v>
@@ -23424,7 +23424,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>17.1967468261719</v>
+        <v>17.1967449188232</v>
       </c>
       <c r="H795" t="n">
         <v>665839</v>
@@ -23453,7 +23453,7 @@
         <v>18.4249992370605</v>
       </c>
       <c r="G796" t="n">
-        <v>17.2201099395752</v>
+        <v>17.2201118469238</v>
       </c>
       <c r="H796" t="n">
         <v>464002</v>
@@ -23482,7 +23482,7 @@
         <v>18.8050003051758</v>
       </c>
       <c r="G797" t="n">
-        <v>17.5752620697021</v>
+        <v>17.5752601623535</v>
       </c>
       <c r="H797" t="n">
         <v>620074</v>
@@ -23656,7 +23656,7 @@
         <v>18.7150001525879</v>
       </c>
       <c r="G803" t="n">
-        <v>17.4911479949951</v>
+        <v>17.4911499023438</v>
       </c>
       <c r="H803" t="n">
         <v>440741</v>
@@ -23772,7 +23772,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G807" t="n">
-        <v>17.6547012329102</v>
+        <v>17.6547050476074</v>
       </c>
       <c r="H807" t="n">
         <v>467189</v>
@@ -23859,7 +23859,7 @@
         <v>18.3449993133545</v>
       </c>
       <c r="G810" t="n">
-        <v>17.1453437805176</v>
+        <v>17.1453418731689</v>
       </c>
       <c r="H810" t="n">
         <v>752218</v>
@@ -23888,7 +23888,7 @@
         <v>18.0249996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>16.8462715148926</v>
+        <v>16.8462696075439</v>
       </c>
       <c r="H811" t="n">
         <v>347878</v>
@@ -24004,7 +24004,7 @@
         <v>19.1650009155273</v>
       </c>
       <c r="G815" t="n">
-        <v>17.9117221832275</v>
+        <v>17.9117183685303</v>
       </c>
       <c r="H815" t="n">
         <v>871578</v>
@@ -24120,7 +24120,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G819" t="n">
-        <v>17.6360111236572</v>
+        <v>17.6360130310059</v>
       </c>
       <c r="H819" t="n">
         <v>378751</v>
@@ -24149,7 +24149,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G820" t="n">
-        <v>17.6360111236572</v>
+        <v>17.6360130310059</v>
       </c>
       <c r="H820" t="n">
         <v>272696</v>
@@ -24178,7 +24178,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G821" t="n">
-        <v>17.3275909423828</v>
+        <v>17.3275928497314</v>
       </c>
       <c r="H821" t="n">
         <v>825446</v>
@@ -24207,7 +24207,7 @@
         <v>18.6149997711182</v>
       </c>
       <c r="G822" t="n">
-        <v>17.3976860046387</v>
+        <v>17.3976879119873</v>
       </c>
       <c r="H822" t="n">
         <v>242884</v>
@@ -24265,7 +24265,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G824" t="n">
-        <v>17.6360111236572</v>
+        <v>17.6360130310059</v>
       </c>
       <c r="H824" t="n">
         <v>353996</v>
@@ -24294,7 +24294,7 @@
         <v>18.7250003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>17.5004959106445</v>
+        <v>17.5004940032959</v>
       </c>
       <c r="H825" t="n">
         <v>295760</v>
@@ -24381,7 +24381,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G828" t="n">
-        <v>18.2154693603516</v>
+        <v>18.2154655456543</v>
       </c>
       <c r="H828" t="n">
         <v>396423</v>
@@ -24410,7 +24410,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G829" t="n">
-        <v>18.056583404541</v>
+        <v>18.0565814971924</v>
       </c>
       <c r="H829" t="n">
         <v>523051</v>
@@ -24584,7 +24584,7 @@
         <v>20</v>
       </c>
       <c r="G835" t="n">
-        <v>18.6921157836914</v>
+        <v>18.69211769104</v>
       </c>
       <c r="H835" t="n">
         <v>1417756</v>
@@ -24613,7 +24613,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>18.5051937103271</v>
+        <v>18.5051918029785</v>
       </c>
       <c r="H836" t="n">
         <v>706748</v>
@@ -24700,7 +24700,7 @@
         <v>19.8549995422363</v>
       </c>
       <c r="G839" t="n">
-        <v>18.5565986633301</v>
+        <v>18.5565967559814</v>
       </c>
       <c r="H839" t="n">
         <v>1014974</v>
@@ -24729,7 +24729,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G840" t="n">
-        <v>18.4397716522217</v>
+        <v>18.439769744873</v>
       </c>
       <c r="H840" t="n">
         <v>677306</v>
@@ -24758,7 +24758,7 @@
         <v>19.8250007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>18.5285587310791</v>
+        <v>18.5285606384277</v>
       </c>
       <c r="H841" t="n">
         <v>479730</v>
@@ -24816,7 +24816,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>18.5051937103271</v>
+        <v>18.5051918029785</v>
       </c>
       <c r="H843" t="n">
         <v>242255</v>
@@ -24845,7 +24845,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G844" t="n">
-        <v>18.3930435180664</v>
+        <v>18.3930416107178</v>
       </c>
       <c r="H844" t="n">
         <v>178961</v>
@@ -24874,7 +24874,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G845" t="n">
-        <v>18.3089256286621</v>
+        <v>18.3089294433594</v>
       </c>
       <c r="H845" t="n">
         <v>193879</v>
@@ -25019,7 +25019,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G850" t="n">
-        <v>17.8603172302246</v>
+        <v>17.8603191375732</v>
       </c>
       <c r="H850" t="n">
         <v>346909</v>
@@ -25048,7 +25048,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>18.0612602233887</v>
+        <v>18.06125831604</v>
       </c>
       <c r="H851" t="n">
         <v>377774</v>
@@ -25077,7 +25077,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G852" t="n">
-        <v>17.5986270904541</v>
+        <v>17.5986289978027</v>
       </c>
       <c r="H852" t="n">
         <v>400400</v>
@@ -25193,7 +25193,7 @@
         <v>21.25</v>
       </c>
       <c r="G856" t="n">
-        <v>19.860372543335</v>
+        <v>19.8603744506836</v>
       </c>
       <c r="H856" t="n">
         <v>4085499</v>
@@ -25251,7 +25251,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>19.9071044921875</v>
+        <v>19.9071025848389</v>
       </c>
       <c r="H858" t="n">
         <v>565898</v>
@@ -25309,7 +25309,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G860" t="n">
-        <v>19.9735889434814</v>
+        <v>19.9735870361328</v>
       </c>
       <c r="H860" t="n">
         <v>461424</v>
@@ -25367,7 +25367,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G862" t="n">
-        <v>19.204273223877</v>
+        <v>19.2042751312256</v>
       </c>
       <c r="H862" t="n">
         <v>641183</v>
@@ -25396,7 +25396,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G863" t="n">
-        <v>19.4892082214355</v>
+        <v>19.4892063140869</v>
       </c>
       <c r="H863" t="n">
         <v>347100</v>
@@ -25599,7 +25599,7 @@
         <v>18.7749996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>17.8318614959717</v>
+        <v>17.8318634033203</v>
       </c>
       <c r="H870" t="n">
         <v>489772</v>
@@ -25657,7 +25657,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G872" t="n">
-        <v>18.6534099578857</v>
+        <v>18.6534118652344</v>
       </c>
       <c r="H872" t="n">
         <v>633892</v>
@@ -25686,7 +25686,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G873" t="n">
-        <v>19.1757831573486</v>
+        <v>19.1757850646973</v>
       </c>
       <c r="H873" t="n">
         <v>957501</v>
@@ -25802,7 +25802,7 @@
         <v>19.9850006103516</v>
       </c>
       <c r="G877" t="n">
-        <v>18.9810829162598</v>
+        <v>18.9810810089111</v>
       </c>
       <c r="H877" t="n">
         <v>573025</v>
@@ -25947,7 +25947,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G882" t="n">
-        <v>19.9355945587158</v>
+        <v>19.9355964660645</v>
       </c>
       <c r="H882" t="n">
         <v>321156</v>
@@ -25976,7 +25976,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G883" t="n">
-        <v>20.0210762023926</v>
+        <v>20.0210742950439</v>
       </c>
       <c r="H883" t="n">
         <v>323070</v>
@@ -26034,7 +26034,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G885" t="n">
-        <v>19.7171478271484</v>
+        <v>19.7171497344971</v>
       </c>
       <c r="H885" t="n">
         <v>182928</v>
@@ -26092,7 +26092,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G887" t="n">
-        <v>19.7456455230713</v>
+        <v>19.7456436157227</v>
       </c>
       <c r="H887" t="n">
         <v>232823</v>
@@ -26208,7 +26208,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>20.4674625396729</v>
+        <v>20.4674644470215</v>
       </c>
       <c r="H891" t="n">
         <v>463182</v>
@@ -26237,7 +26237,7 @@
         <v>21.5699996948242</v>
       </c>
       <c r="G892" t="n">
-        <v>20.4864616394043</v>
+        <v>20.4864597320557</v>
       </c>
       <c r="H892" t="n">
         <v>439206</v>
@@ -26266,7 +26266,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G893" t="n">
-        <v>20.2870121002197</v>
+        <v>20.2870101928711</v>
       </c>
       <c r="H893" t="n">
         <v>452737</v>
@@ -26556,7 +26556,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G903" t="n">
-        <v>19.8691120147705</v>
+        <v>19.8691139221191</v>
       </c>
       <c r="H903" t="n">
         <v>427160</v>
@@ -26585,7 +26585,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G904" t="n">
-        <v>19.9735889434814</v>
+        <v>19.9735870361328</v>
       </c>
       <c r="H904" t="n">
         <v>428652</v>
@@ -26614,7 +26614,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G905" t="n">
-        <v>19.8691120147705</v>
+        <v>19.8691139221191</v>
       </c>
       <c r="H905" t="n">
         <v>312833</v>
@@ -26643,7 +26643,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G906" t="n">
-        <v>19.9355945587158</v>
+        <v>19.9355964660645</v>
       </c>
       <c r="H906" t="n">
         <v>288708</v>
@@ -26672,7 +26672,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G907" t="n">
-        <v>19.9640884399414</v>
+        <v>19.96409034729</v>
       </c>
       <c r="H907" t="n">
         <v>595451</v>
@@ -26875,7 +26875,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G914" t="n">
-        <v>17.2952461242676</v>
+        <v>17.2952442169189</v>
       </c>
       <c r="H914" t="n">
         <v>665988</v>
@@ -26962,7 +26962,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G917" t="n">
-        <v>17.3854751586914</v>
+        <v>17.3854732513428</v>
       </c>
       <c r="H917" t="n">
         <v>278040</v>
@@ -27049,7 +27049,7 @@
         <v>17.9150009155273</v>
       </c>
       <c r="G920" t="n">
-        <v>17.015064239502</v>
+        <v>17.0150661468506</v>
       </c>
       <c r="H920" t="n">
         <v>386059</v>
@@ -27078,7 +27078,7 @@
         <v>17.4750003814697</v>
       </c>
       <c r="G921" t="n">
-        <v>16.59716796875</v>
+        <v>16.5971660614014</v>
       </c>
       <c r="H921" t="n">
         <v>361687</v>
@@ -27107,7 +27107,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G922" t="n">
-        <v>16.2837448120117</v>
+        <v>16.2837467193604</v>
       </c>
       <c r="H922" t="n">
         <v>717691</v>
@@ -27310,7 +27310,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G929" t="n">
-        <v>16.948579788208</v>
+        <v>16.9485816955566</v>
       </c>
       <c r="H929" t="n">
         <v>294893</v>
@@ -27339,7 +27339,7 @@
         <v>17.6350002288818</v>
       </c>
       <c r="G930" t="n">
-        <v>16.7491302490234</v>
+        <v>16.7491321563721</v>
       </c>
       <c r="H930" t="n">
         <v>638773</v>
@@ -27368,7 +27368,7 @@
         <v>17.7350006103516</v>
       </c>
       <c r="G931" t="n">
-        <v>16.844108581543</v>
+        <v>16.8441066741943</v>
       </c>
       <c r="H931" t="n">
         <v>237897</v>
@@ -27397,7 +27397,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G932" t="n">
-        <v>16.497444152832</v>
+        <v>16.4974422454834</v>
       </c>
       <c r="H932" t="n">
         <v>1271538</v>
@@ -27484,7 +27484,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G935" t="n">
-        <v>16.9248352050781</v>
+        <v>16.9248371124268</v>
       </c>
       <c r="H935" t="n">
         <v>526819</v>
@@ -27600,7 +27600,7 @@
         <v>18.0450000762939</v>
       </c>
       <c r="G939" t="n">
-        <v>17.1385364532471</v>
+        <v>17.1385345458984</v>
       </c>
       <c r="H939" t="n">
         <v>587734</v>
@@ -27745,7 +27745,7 @@
         <v>17.7350006103516</v>
       </c>
       <c r="G944" t="n">
-        <v>16.844108581543</v>
+        <v>16.8441066741943</v>
       </c>
       <c r="H944" t="n">
         <v>503594</v>
@@ -27890,7 +27890,7 @@
         <v>17.0450000762939</v>
       </c>
       <c r="G949" t="n">
-        <v>16.1887683868408</v>
+        <v>16.1887664794922</v>
       </c>
       <c r="H949" t="n">
         <v>847682</v>
@@ -27948,7 +27948,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G951" t="n">
-        <v>16.3454780578613</v>
+        <v>16.34547996521</v>
       </c>
       <c r="H951" t="n">
         <v>647943</v>
@@ -28035,7 +28035,7 @@
         <v>16.8649997711182</v>
       </c>
       <c r="G954" t="n">
-        <v>16.0178089141846</v>
+        <v>16.0178108215332</v>
       </c>
       <c r="H954" t="n">
         <v>543115</v>
@@ -28122,7 +28122,7 @@
         <v>16.3850002288818</v>
       </c>
       <c r="G957" t="n">
-        <v>15.5619220733643</v>
+        <v>15.5619230270386</v>
       </c>
       <c r="H957" t="n">
         <v>387332</v>
@@ -28267,7 +28267,7 @@
         <v>16.4150009155273</v>
       </c>
       <c r="G962" t="n">
-        <v>15.5904169082642</v>
+        <v>15.5904159545898</v>
       </c>
       <c r="H962" t="n">
         <v>1017946</v>
@@ -28325,7 +28325,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G964" t="n">
-        <v>15.6806421279907</v>
+        <v>15.680643081665</v>
       </c>
       <c r="H964" t="n">
         <v>425280</v>
@@ -28354,7 +28354,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G965" t="n">
-        <v>15.4052104949951</v>
+        <v>15.4052095413208</v>
       </c>
       <c r="H965" t="n">
         <v>687418</v>
@@ -28557,7 +28557,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G972" t="n">
-        <v>15.319730758667</v>
+        <v>15.3197317123413</v>
       </c>
       <c r="H972" t="n">
         <v>1080701</v>
@@ -28586,7 +28586,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G973" t="n">
-        <v>15.9608249664307</v>
+        <v>15.960823059082</v>
       </c>
       <c r="H973" t="n">
         <v>1840392</v>
@@ -28615,7 +28615,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>15.7661228179932</v>
+        <v>15.7661218643188</v>
       </c>
       <c r="H974" t="n">
         <v>975396</v>
@@ -28673,7 +28673,7 @@
         <v>16.75</v>
       </c>
       <c r="G976" t="n">
-        <v>15.9085855484009</v>
+        <v>15.9085874557495</v>
       </c>
       <c r="H976" t="n">
         <v>419109</v>
@@ -28731,7 +28731,7 @@
         <v>16.9950008392334</v>
       </c>
       <c r="G978" t="n">
-        <v>16.1412811279297</v>
+        <v>16.1412792205811</v>
       </c>
       <c r="H978" t="n">
         <v>604860</v>
@@ -28818,7 +28818,7 @@
         <v>17.4549999237061</v>
       </c>
       <c r="G981" t="n">
-        <v>16.5781726837158</v>
+        <v>16.5781707763672</v>
       </c>
       <c r="H981" t="n">
         <v>834030</v>
@@ -29021,7 +29021,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G988" t="n">
-        <v>16.4404544830322</v>
+        <v>16.4404563903809</v>
       </c>
       <c r="H988" t="n">
         <v>893679</v>
@@ -29282,7 +29282,7 @@
         <v>18.0949993133545</v>
       </c>
       <c r="G997" t="n">
-        <v>17.1860237121582</v>
+        <v>17.1860218048096</v>
       </c>
       <c r="H997" t="n">
         <v>470813</v>
@@ -29514,7 +29514,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1005" t="n">
-        <v>17.2477588653564</v>
+        <v>17.2477569580078</v>
       </c>
       <c r="H1005" t="n">
         <v>439993</v>
@@ -29717,7 +29717,7 @@
         <v>19.0750007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>18.1167964935303</v>
+        <v>18.1167945861816</v>
       </c>
       <c r="H1012" t="n">
         <v>838667</v>
@@ -29775,7 +29775,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>17.8556060791016</v>
+        <v>17.8556079864502</v>
       </c>
       <c r="H1014" t="n">
         <v>268982</v>
@@ -29804,7 +29804,7 @@
         <v>18.75</v>
       </c>
       <c r="G1015" t="n">
-        <v>17.8081188201904</v>
+        <v>17.8081207275391</v>
       </c>
       <c r="H1015" t="n">
         <v>216874</v>
@@ -29862,7 +29862,7 @@
         <v>18.6049995422363</v>
       </c>
       <c r="G1017" t="n">
-        <v>17.6704044342041</v>
+        <v>17.6704025268555</v>
       </c>
       <c r="H1017" t="n">
         <v>345428</v>
@@ -29891,7 +29891,7 @@
         <v>18.5550003051758</v>
       </c>
       <c r="G1018" t="n">
-        <v>17.622917175293</v>
+        <v>17.6229152679443</v>
       </c>
       <c r="H1018" t="n">
         <v>319106</v>
@@ -29920,7 +29920,7 @@
         <v>18.6149997711182</v>
       </c>
       <c r="G1019" t="n">
-        <v>17.6799011230469</v>
+        <v>17.6799030303955</v>
       </c>
       <c r="H1019" t="n">
         <v>233888</v>
@@ -30007,7 +30007,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1022" t="n">
-        <v>18.0930500030518</v>
+        <v>18.0930480957031</v>
       </c>
       <c r="H1022" t="n">
         <v>323583</v>
@@ -30036,7 +30036,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.9030952453613</v>
+        <v>17.90309715271</v>
       </c>
       <c r="H1023" t="n">
         <v>285927</v>
@@ -30065,7 +30065,7 @@
         <v>18.7950000762939</v>
       </c>
       <c r="G1024" t="n">
-        <v>17.8508605957031</v>
+        <v>17.8508586883545</v>
       </c>
       <c r="H1024" t="n">
         <v>286349</v>
@@ -30181,7 +30181,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.2287635803223</v>
+        <v>17.2287616729736</v>
       </c>
       <c r="H1028" t="n">
         <v>252655</v>
@@ -30297,7 +30297,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1032" t="n">
-        <v>16.5924167633057</v>
+        <v>16.5924186706543</v>
       </c>
       <c r="H1032" t="n">
         <v>390989</v>
@@ -30326,7 +30326,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>15.8610982894897</v>
+        <v>15.8611001968384</v>
       </c>
       <c r="H1033" t="n">
         <v>1029610</v>
@@ -30355,7 +30355,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G1034" t="n">
-        <v>16.2694988250732</v>
+        <v>16.2694969177246</v>
       </c>
       <c r="H1034" t="n">
         <v>539194</v>
@@ -30442,7 +30442,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1037" t="n">
-        <v>15.8468523025513</v>
+        <v>15.8468503952026</v>
       </c>
       <c r="H1037" t="n">
         <v>727617</v>
@@ -30587,7 +30587,7 @@
         <v>16.6149997711182</v>
       </c>
       <c r="G1042" t="n">
-        <v>15.7803678512573</v>
+        <v>15.7803688049316</v>
       </c>
       <c r="H1042" t="n">
         <v>513424</v>
@@ -30616,7 +30616,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>15.7186336517334</v>
+        <v>15.7186326980591</v>
       </c>
       <c r="H1043" t="n">
         <v>350977</v>
@@ -30645,7 +30645,7 @@
         <v>16.1550006866455</v>
       </c>
       <c r="G1044" t="n">
-        <v>15.3434762954712</v>
+        <v>15.3434772491455</v>
       </c>
       <c r="H1044" t="n">
         <v>964969</v>
@@ -30674,7 +30674,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1045" t="n">
-        <v>15.9845695495605</v>
+        <v>15.9845676422119</v>
       </c>
       <c r="H1045" t="n">
         <v>961466</v>
@@ -30732,7 +30732,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1047" t="n">
-        <v>15.6046619415283</v>
+        <v>15.604660987854</v>
       </c>
       <c r="H1047" t="n">
         <v>418169</v>
@@ -30761,7 +30761,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1048" t="n">
-        <v>15.8610982894897</v>
+        <v>15.8611001968384</v>
       </c>
       <c r="H1048" t="n">
         <v>559116</v>
@@ -30790,7 +30790,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1049" t="n">
-        <v>15.7043867111206</v>
+        <v>15.7043857574463</v>
       </c>
       <c r="H1049" t="n">
         <v>541345</v>
@@ -30848,7 +30848,7 @@
         <v>16.3649997711182</v>
       </c>
       <c r="G1051" t="n">
-        <v>15.5429258346558</v>
+        <v>15.5429267883301</v>
       </c>
       <c r="H1051" t="n">
         <v>743062</v>
@@ -30993,7 +30993,7 @@
         <v>14.3249998092651</v>
       </c>
       <c r="G1056" t="n">
-        <v>13.6054029464722</v>
+        <v>13.6054039001465</v>
       </c>
       <c r="H1056" t="n">
         <v>1069741</v>
@@ -31109,7 +31109,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1060" t="n">
-        <v>12.9738082885742</v>
+        <v>12.9738092422485</v>
       </c>
       <c r="H1060" t="n">
         <v>551132</v>
@@ -31254,7 +31254,7 @@
         <v>11.3549995422363</v>
       </c>
       <c r="G1065" t="n">
-        <v>10.7845973968506</v>
+        <v>10.7845964431763</v>
       </c>
       <c r="H1065" t="n">
         <v>1903661</v>
@@ -31283,7 +31283,7 @@
         <v>9.5620002746582</v>
       </c>
       <c r="G1066" t="n">
-        <v>9.08166694641113</v>
+        <v>9.08166599273682</v>
       </c>
       <c r="H1066" t="n">
         <v>1982873</v>
@@ -31312,7 +31312,7 @@
         <v>10.164999961853</v>
       </c>
       <c r="G1067" t="n">
-        <v>9.65437602996826</v>
+        <v>9.65437507629395</v>
       </c>
       <c r="H1067" t="n">
         <v>1497885</v>
@@ -31921,7 +31921,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1088" t="n">
-        <v>11.4541826248169</v>
+        <v>11.4541835784912</v>
       </c>
       <c r="H1088" t="n">
         <v>536555</v>
@@ -31979,7 +31979,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>11.5396614074707</v>
+        <v>11.5396604537964</v>
       </c>
       <c r="H1090" t="n">
         <v>351112</v>
@@ -32066,7 +32066,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>10.399941444397</v>
+        <v>10.3999423980713</v>
       </c>
       <c r="H1093" t="n">
         <v>1163920</v>
@@ -32095,7 +32095,7 @@
         <v>11</v>
       </c>
       <c r="G1094" t="n">
-        <v>10.4474296569824</v>
+        <v>10.4474306106567</v>
       </c>
       <c r="H1094" t="n">
         <v>374895</v>
@@ -32182,7 +32182,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1097" t="n">
-        <v>10.7323598861694</v>
+        <v>10.7323608398438</v>
       </c>
       <c r="H1097" t="n">
         <v>436691</v>
@@ -32240,7 +32240,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1099" t="n">
-        <v>10.722861289978</v>
+        <v>10.7228622436523</v>
       </c>
       <c r="H1099" t="n">
         <v>461067</v>
@@ -32385,7 +32385,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1104" t="n">
-        <v>10.4094400405884</v>
+        <v>10.4094390869141</v>
       </c>
       <c r="H1104" t="n">
         <v>459706</v>
@@ -32559,7 +32559,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1110" t="n">
-        <v>10.4094400405884</v>
+        <v>10.4094390869141</v>
       </c>
       <c r="H1110" t="n">
         <v>778843</v>
@@ -32588,7 +32588,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1111" t="n">
-        <v>10.399941444397</v>
+        <v>10.3999423980713</v>
       </c>
       <c r="H1111" t="n">
         <v>2429677</v>
@@ -33023,7 +33023,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>13.1542654037476</v>
+        <v>13.1542644500732</v>
       </c>
       <c r="H1126" t="n">
         <v>1935626</v>
@@ -33081,7 +33081,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G1128" t="n">
-        <v>11.8815784454346</v>
+        <v>11.8815774917603</v>
       </c>
       <c r="H1128" t="n">
         <v>1152534</v>
@@ -33139,7 +33139,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1130" t="n">
-        <v>12.062032699585</v>
+        <v>12.0620336532593</v>
       </c>
       <c r="H1130" t="n">
         <v>882931</v>
@@ -33168,7 +33168,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1131" t="n">
-        <v>12.1190185546875</v>
+        <v>12.1190195083618</v>
       </c>
       <c r="H1131" t="n">
         <v>1075221</v>
@@ -33284,7 +33284,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1135" t="n">
-        <v>12.5749063491821</v>
+        <v>12.5749073028564</v>
       </c>
       <c r="H1135" t="n">
         <v>672115</v>
@@ -33313,7 +33313,7 @@
         <v>13.25</v>
       </c>
       <c r="G1136" t="n">
-        <v>12.5844039916992</v>
+        <v>12.5844049453735</v>
       </c>
       <c r="H1136" t="n">
         <v>819274</v>
@@ -33371,7 +33371,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1138" t="n">
-        <v>11.8055963516235</v>
+        <v>11.8055953979492</v>
       </c>
       <c r="H1138" t="n">
         <v>819399</v>
@@ -33429,7 +33429,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1140" t="n">
-        <v>11.7296142578125</v>
+        <v>11.7296152114868</v>
       </c>
       <c r="H1140" t="n">
         <v>688432</v>
@@ -33516,7 +33516,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1143" t="n">
-        <v>11.7581081390381</v>
+        <v>11.7581071853638</v>
       </c>
       <c r="H1143" t="n">
         <v>523414</v>
@@ -33545,7 +33545,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1144" t="n">
-        <v>11.4541826248169</v>
+        <v>11.4541835784912</v>
       </c>
       <c r="H1144" t="n">
         <v>491409</v>
@@ -33719,7 +33719,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G1150" t="n">
-        <v>11.1787509918213</v>
+        <v>11.1787519454956</v>
       </c>
       <c r="H1150" t="n">
         <v>464530</v>
@@ -33864,7 +33864,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.2452344894409</v>
+        <v>11.2452335357666</v>
       </c>
       <c r="H1155" t="n">
         <v>321721</v>
@@ -33980,7 +33980,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G1159" t="n">
-        <v>11.0267877578735</v>
+        <v>11.0267868041992</v>
       </c>
       <c r="H1159" t="n">
         <v>350758</v>
@@ -34038,7 +34038,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1161" t="n">
-        <v>10.8368339538574</v>
+        <v>10.8368349075317</v>
       </c>
       <c r="H1161" t="n">
         <v>402699</v>
@@ -34212,7 +34212,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1167" t="n">
-        <v>10.8368339538574</v>
+        <v>10.8368349075317</v>
       </c>
       <c r="H1167" t="n">
         <v>457270</v>
@@ -34299,7 +34299,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G1170" t="n">
-        <v>10.3619518280029</v>
+        <v>10.3619508743286</v>
       </c>
       <c r="H1170" t="n">
         <v>512127</v>
@@ -34415,7 +34415,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1174" t="n">
-        <v>11.3307123184204</v>
+        <v>11.3307132720947</v>
       </c>
       <c r="H1174" t="n">
         <v>653648</v>
@@ -34502,7 +34502,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1177" t="n">
-        <v>10.9603042602539</v>
+        <v>10.9603052139282</v>
       </c>
       <c r="H1177" t="n">
         <v>198677</v>
@@ -34531,7 +34531,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G1178" t="n">
-        <v>10.760853767395</v>
+        <v>10.7608528137207</v>
       </c>
       <c r="H1178" t="n">
         <v>232544</v>
@@ -34734,7 +34734,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1185" t="n">
-        <v>11.4636793136597</v>
+        <v>11.463680267334</v>
       </c>
       <c r="H1185" t="n">
         <v>306240</v>
@@ -34821,7 +34821,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1188" t="n">
-        <v>11.7960977554321</v>
+        <v>11.7960987091064</v>
       </c>
       <c r="H1188" t="n">
         <v>437652</v>
@@ -34966,7 +34966,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1193" t="n">
-        <v>11.4541826248169</v>
+        <v>11.4541835784912</v>
       </c>
       <c r="H1193" t="n">
         <v>306311</v>
@@ -35256,7 +35256,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1203" t="n">
-        <v>11.4636793136597</v>
+        <v>11.463680267334</v>
       </c>
       <c r="H1203" t="n">
         <v>441998</v>
@@ -35314,7 +35314,7 @@
         <v>12.75</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.1095209121704</v>
+        <v>12.1095218658447</v>
       </c>
       <c r="H1205" t="n">
         <v>796074</v>
@@ -35430,7 +35430,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1209" t="n">
-        <v>11.9860506057739</v>
+        <v>11.9860515594482</v>
       </c>
       <c r="H1209" t="n">
         <v>375319</v>
@@ -35604,7 +35604,7 @@
         <v>13.25</v>
       </c>
       <c r="G1215" t="n">
-        <v>12.5844039916992</v>
+        <v>12.5844049453735</v>
       </c>
       <c r="H1215" t="n">
         <v>280270</v>
@@ -35662,7 +35662,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G1217" t="n">
-        <v>12.5464143753052</v>
+        <v>12.5464134216309</v>
       </c>
       <c r="H1217" t="n">
         <v>251308</v>
@@ -35691,7 +35691,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>12.2044982910156</v>
+        <v>12.2044973373413</v>
       </c>
       <c r="H1218" t="n">
         <v>348352</v>
@@ -35836,7 +35836,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1223" t="n">
-        <v>12.1949996948242</v>
+        <v>12.1950006484985</v>
       </c>
       <c r="H1223" t="n">
         <v>1001856</v>
@@ -36097,7 +36097,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1232" t="n">
-        <v>11.0647773742676</v>
+        <v>11.0647783279419</v>
       </c>
       <c r="H1232" t="n">
         <v>309563</v>
@@ -36358,7 +36358,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1241" t="n">
-        <v>13.9235744476318</v>
+        <v>13.9235754013062</v>
       </c>
       <c r="H1241" t="n">
         <v>633097</v>
@@ -36561,7 +36561,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G1248" t="n">
-        <v>14.3129787445068</v>
+        <v>14.3129796981812</v>
       </c>
       <c r="H1248" t="n">
         <v>692581</v>
@@ -36619,7 +36619,7 @@
         <v>15</v>
       </c>
       <c r="G1250" t="n">
-        <v>14.2464952468872</v>
+        <v>14.2464962005615</v>
       </c>
       <c r="H1250" t="n">
         <v>463570</v>
@@ -36793,7 +36793,7 @@
         <v>15</v>
       </c>
       <c r="G1256" t="n">
-        <v>14.2464952468872</v>
+        <v>14.2464962005615</v>
       </c>
       <c r="H1256" t="n">
         <v>190883</v>
@@ -36822,7 +36822,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1257" t="n">
-        <v>14.4934349060059</v>
+        <v>14.4934358596802</v>
       </c>
       <c r="H1257" t="n">
         <v>484047</v>
@@ -36996,7 +36996,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1263" t="n">
-        <v>14.8543462753296</v>
+        <v>14.8543472290039</v>
       </c>
       <c r="H1263" t="n">
         <v>350866</v>
@@ -37054,7 +37054,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1265" t="n">
-        <v>14.3794622421265</v>
+        <v>14.3794631958008</v>
       </c>
       <c r="H1265" t="n">
         <v>369816</v>
@@ -37170,7 +37170,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G1269" t="n">
-        <v>15.110782623291</v>
+        <v>15.1107835769653</v>
       </c>
       <c r="H1269" t="n">
         <v>607990</v>
@@ -37286,7 +37286,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1273" t="n">
-        <v>14.7118806838989</v>
+        <v>14.7118816375732</v>
       </c>
       <c r="H1273" t="n">
         <v>165183</v>
@@ -37344,7 +37344,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1275" t="n">
-        <v>14.5884103775024</v>
+        <v>14.5884113311768</v>
       </c>
       <c r="H1275" t="n">
         <v>203927</v>
@@ -37402,7 +37402,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1277" t="n">
-        <v>14.4079561233521</v>
+        <v>14.4079551696777</v>
       </c>
       <c r="H1277" t="n">
         <v>195856</v>
@@ -37460,7 +37460,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1279" t="n">
-        <v>14.5314264297485</v>
+        <v>14.5314254760742</v>
       </c>
       <c r="H1279" t="n">
         <v>147746</v>
@@ -37547,7 +37547,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1282" t="n">
-        <v>14.3794622421265</v>
+        <v>14.3794631958008</v>
       </c>
       <c r="H1282" t="n">
         <v>310366</v>
@@ -37605,7 +37605,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G1284" t="n">
-        <v>15.319730758667</v>
+        <v>15.3197317123413</v>
       </c>
       <c r="H1284" t="n">
         <v>1360458</v>
@@ -37634,7 +37634,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1285" t="n">
-        <v>15.2912397384644</v>
+        <v>15.29123878479</v>
       </c>
       <c r="H1285" t="n">
         <v>324871</v>
@@ -37692,7 +37692,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>15.0537967681885</v>
+        <v>15.0537977218628</v>
       </c>
       <c r="H1287" t="n">
         <v>418867</v>
@@ -37721,7 +37721,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1288" t="n">
-        <v>15.8041124343872</v>
+        <v>15.8041114807129</v>
       </c>
       <c r="H1288" t="n">
         <v>1007744</v>
@@ -37779,7 +37779,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1290" t="n">
-        <v>15.2627458572388</v>
+        <v>15.2627449035645</v>
       </c>
       <c r="H1290" t="n">
         <v>357033</v>
@@ -37982,7 +37982,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1297" t="n">
-        <v>14.4364490509033</v>
+        <v>14.4364500045776</v>
       </c>
       <c r="H1297" t="n">
         <v>842933</v>
@@ -38156,7 +38156,7 @@
         <v>15.7700004577637</v>
       </c>
       <c r="G1303" t="n">
-        <v>14.9778156280518</v>
+        <v>14.9778165817261</v>
       </c>
       <c r="H1303" t="n">
         <v>274608</v>
@@ -38359,7 +38359,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1310" t="n">
-        <v>15.1202802658081</v>
+        <v>15.1202812194824</v>
       </c>
       <c r="H1310" t="n">
         <v>191702</v>
@@ -38417,7 +38417,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1312" t="n">
-        <v>15.2627458572388</v>
+        <v>15.2627449035645</v>
       </c>
       <c r="H1312" t="n">
         <v>448450</v>
@@ -38475,7 +38475,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1314" t="n">
-        <v>15.1012849807739</v>
+        <v>15.1012859344482</v>
       </c>
       <c r="H1314" t="n">
         <v>135045</v>
@@ -38533,7 +38533,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1316" t="n">
-        <v>14.9873123168945</v>
+        <v>14.9873132705688</v>
       </c>
       <c r="H1316" t="n">
         <v>239674</v>
@@ -38649,7 +38649,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1320" t="n">
-        <v>16.0320568084717</v>
+        <v>16.032054901123</v>
       </c>
       <c r="H1320" t="n">
         <v>326028</v>
@@ -38765,7 +38765,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>15.7376298904419</v>
+        <v>15.7376289367676</v>
       </c>
       <c r="H1324" t="n">
         <v>266463</v>
@@ -38939,7 +38939,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1330" t="n">
-        <v>15.3672199249268</v>
+        <v>15.3672208786011</v>
       </c>
       <c r="H1330" t="n">
         <v>273867</v>
@@ -38968,7 +38968,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1331" t="n">
-        <v>15.3387269973755</v>
+        <v>15.3387260437012</v>
       </c>
       <c r="H1331" t="n">
         <v>147455</v>
@@ -38997,7 +38997,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1332" t="n">
-        <v>15.6996374130249</v>
+        <v>15.6996393203735</v>
       </c>
       <c r="H1332" t="n">
         <v>267931</v>
@@ -39084,7 +39084,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G1335" t="n">
-        <v>15.9608249664307</v>
+        <v>15.960823059082</v>
       </c>
       <c r="H1335" t="n">
         <v>327422</v>
@@ -39113,7 +39113,7 @@
         <v>16.4449996948242</v>
       </c>
       <c r="G1336" t="n">
-        <v>15.6189079284668</v>
+        <v>15.6189069747925</v>
       </c>
       <c r="H1336" t="n">
         <v>353065</v>
@@ -39142,7 +39142,7 @@
         <v>16.2450008392334</v>
       </c>
       <c r="G1337" t="n">
-        <v>15.4289560317993</v>
+        <v>15.428955078125</v>
       </c>
       <c r="H1337" t="n">
         <v>389353</v>
@@ -39171,7 +39171,7 @@
         <v>16.4650001525879</v>
       </c>
       <c r="G1338" t="n">
-        <v>15.6379041671753</v>
+        <v>15.637903213501</v>
       </c>
       <c r="H1338" t="n">
         <v>344519</v>
@@ -39200,7 +39200,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1339" t="n">
-        <v>15.8468523025513</v>
+        <v>15.8468503952026</v>
       </c>
       <c r="H1339" t="n">
         <v>183071</v>
@@ -39229,7 +39229,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G1340" t="n">
-        <v>16.2837448120117</v>
+        <v>16.2837467193604</v>
       </c>
       <c r="H1340" t="n">
         <v>635746</v>
@@ -39287,7 +39287,7 @@
         <v>17.625</v>
       </c>
       <c r="G1342" t="n">
-        <v>16.7396335601807</v>
+        <v>16.739631652832</v>
       </c>
       <c r="H1342" t="n">
         <v>365703</v>
@@ -39345,7 +39345,7 @@
         <v>17.7649993896484</v>
       </c>
       <c r="G1344" t="n">
-        <v>16.8726005554199</v>
+        <v>16.8725986480713</v>
       </c>
       <c r="H1344" t="n">
         <v>279966</v>
@@ -39461,7 +39461,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G1348" t="n">
-        <v>17.4567050933838</v>
+        <v>17.4567031860352</v>
       </c>
       <c r="H1348" t="n">
         <v>598052</v>
@@ -39490,7 +39490,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G1349" t="n">
-        <v>17.3854751586914</v>
+        <v>17.3854732513428</v>
       </c>
       <c r="H1349" t="n">
         <v>274320</v>
@@ -39548,7 +39548,7 @@
         <v>18.2049999237061</v>
       </c>
       <c r="G1351" t="n">
-        <v>17.2904968261719</v>
+        <v>17.2904987335205</v>
       </c>
       <c r="H1351" t="n">
         <v>262686</v>
@@ -39606,7 +39606,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1353" t="n">
-        <v>16.9248352050781</v>
+        <v>16.9248371124268</v>
       </c>
       <c r="H1353" t="n">
         <v>308039</v>
@@ -39809,7 +39809,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1360" t="n">
-        <v>17.4187145233154</v>
+        <v>17.4187164306641</v>
       </c>
       <c r="H1360" t="n">
         <v>267867</v>
@@ -39896,7 +39896,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1363" t="n">
-        <v>18.1975231170654</v>
+        <v>18.1975250244141</v>
       </c>
       <c r="H1363" t="n">
         <v>262496</v>
@@ -39925,7 +39925,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G1364" t="n">
-        <v>18.1500358581543</v>
+        <v>18.1500377655029</v>
       </c>
       <c r="H1364" t="n">
         <v>98181</v>
@@ -39954,7 +39954,7 @@
         <v>19.1949996948242</v>
       </c>
       <c r="G1365" t="n">
-        <v>18.2307643890381</v>
+        <v>18.2307662963867</v>
       </c>
       <c r="H1365" t="n">
         <v>224548</v>
@@ -40331,7 +40331,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G1378" t="n">
-        <v>18.3542366027832</v>
+        <v>18.3542346954346</v>
       </c>
       <c r="H1378" t="n">
         <v>205617</v>
@@ -40389,7 +40389,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G1380" t="n">
-        <v>18.5299434661865</v>
+        <v>18.5299415588379</v>
       </c>
       <c r="H1380" t="n">
         <v>478383</v>
@@ -40447,7 +40447,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G1382" t="n">
-        <v>18.3542366027832</v>
+        <v>18.3542346954346</v>
       </c>
       <c r="H1382" t="n">
         <v>357274</v>
@@ -40476,7 +40476,7 @@
         <v>19.2649993896484</v>
       </c>
       <c r="G1383" t="n">
-        <v>18.2972469329834</v>
+        <v>18.297248840332</v>
       </c>
       <c r="H1383" t="n">
         <v>283276</v>
@@ -40534,7 +40534,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1385" t="n">
-        <v>18.1690292358398</v>
+        <v>18.1690311431885</v>
       </c>
       <c r="H1385" t="n">
         <v>242704</v>
@@ -40563,7 +40563,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1386" t="n">
-        <v>18.1690292358398</v>
+        <v>18.1690311431885</v>
       </c>
       <c r="H1386" t="n">
         <v>248014</v>
@@ -40592,7 +40592,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1387" t="n">
-        <v>18.1690292358398</v>
+        <v>18.1690311431885</v>
       </c>
       <c r="H1387" t="n">
         <v>176230</v>
@@ -40650,7 +40650,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1389" t="n">
-        <v>18.4444637298584</v>
+        <v>18.444465637207</v>
       </c>
       <c r="H1389" t="n">
         <v>662703</v>
@@ -40795,7 +40795,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G1394" t="n">
-        <v>17.8461112976074</v>
+        <v>17.8461093902588</v>
       </c>
       <c r="H1394" t="n">
         <v>862640</v>
@@ -40853,7 +40853,7 @@
         <v>18.0450000762939</v>
       </c>
       <c r="G1396" t="n">
-        <v>17.1385364532471</v>
+        <v>17.1385345458984</v>
       </c>
       <c r="H1396" t="n">
         <v>475104</v>
@@ -40911,7 +40911,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1398" t="n">
-        <v>17.2287635803223</v>
+        <v>17.2287616729736</v>
       </c>
       <c r="H1398" t="n">
         <v>182994</v>
@@ -41143,7 +41143,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1406" t="n">
-        <v>16.877347946167</v>
+        <v>16.8773498535156</v>
       </c>
       <c r="H1406" t="n">
         <v>162700</v>
@@ -41230,7 +41230,7 @@
         <v>16.4449996948242</v>
       </c>
       <c r="G1409" t="n">
-        <v>15.6189079284668</v>
+        <v>15.6189069747925</v>
       </c>
       <c r="H1409" t="n">
         <v>429152</v>
@@ -41404,7 +41404,7 @@
         <v>17.0249996185303</v>
       </c>
       <c r="G1415" t="n">
-        <v>16.169771194458</v>
+        <v>16.1697731018066</v>
       </c>
       <c r="H1415" t="n">
         <v>183230</v>
@@ -41462,7 +41462,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G1417" t="n">
-        <v>16.0368041992188</v>
+        <v>16.0368061065674</v>
       </c>
       <c r="H1417" t="n">
         <v>142262</v>
@@ -41549,7 +41549,7 @@
         <v>17.0249996185303</v>
       </c>
       <c r="G1420" t="n">
-        <v>16.169771194458</v>
+        <v>16.1697731018066</v>
       </c>
       <c r="H1420" t="n">
         <v>205910</v>
@@ -41607,7 +41607,7 @@
         <v>16.9150009155273</v>
       </c>
       <c r="G1422" t="n">
-        <v>16.0652980804443</v>
+        <v>16.065299987793</v>
       </c>
       <c r="H1422" t="n">
         <v>166040</v>
@@ -41810,7 +41810,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>17.0008182525635</v>
+        <v>17.0008163452148</v>
       </c>
       <c r="H1429" t="n">
         <v>840706</v>
@@ -41868,7 +41868,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G1431" t="n">
-        <v>16.5164375305176</v>
+        <v>16.5164356231689</v>
       </c>
       <c r="H1431" t="n">
         <v>523484</v>
@@ -41926,7 +41926,7 @@
         <v>16.5750007629395</v>
       </c>
       <c r="G1433" t="n">
-        <v>15.7423782348633</v>
+        <v>15.7423791885376</v>
       </c>
       <c r="H1433" t="n">
         <v>814180</v>
@@ -41955,7 +41955,7 @@
         <v>17</v>
       </c>
       <c r="G1434" t="n">
-        <v>16.1460266113281</v>
+        <v>16.1460285186768</v>
       </c>
       <c r="H1434" t="n">
         <v>1076069</v>
@@ -42013,7 +42013,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1436" t="n">
-        <v>15.8041124343872</v>
+        <v>15.8041114807129</v>
       </c>
       <c r="H1436" t="n">
         <v>400962</v>
@@ -42042,7 +42042,7 @@
         <v>16.8150005340576</v>
       </c>
       <c r="G1437" t="n">
-        <v>15.9703216552734</v>
+        <v>15.9703235626221</v>
       </c>
       <c r="H1437" t="n">
         <v>478682</v>
@@ -42332,7 +42332,7 @@
         <v>18.8150005340576</v>
       </c>
       <c r="G1447" t="n">
-        <v>17.8698558807373</v>
+        <v>17.8698539733887</v>
       </c>
       <c r="H1447" t="n">
         <v>642098</v>
@@ -42390,7 +42390,7 @@
         <v>18.75</v>
       </c>
       <c r="G1449" t="n">
-        <v>17.8081188201904</v>
+        <v>17.8081207275391</v>
       </c>
       <c r="H1449" t="n">
         <v>438443</v>
@@ -42593,7 +42593,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1456" t="n">
-        <v>16.9628295898438</v>
+        <v>16.9628276824951</v>
       </c>
       <c r="H1456" t="n">
         <v>490557</v>
@@ -42680,7 +42680,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1459" t="n">
-        <v>16.9438304901123</v>
+        <v>16.9438323974609</v>
       </c>
       <c r="H1459" t="n">
         <v>262741</v>
@@ -42912,7 +42912,7 @@
         <v>17.9449996948242</v>
       </c>
       <c r="G1467" t="n">
-        <v>17.0435562133789</v>
+        <v>17.0435581207275</v>
       </c>
       <c r="H1467" t="n">
         <v>317629</v>
@@ -43028,7 +43028,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>17.0008182525635</v>
+        <v>17.0008163452148</v>
       </c>
       <c r="H1471" t="n">
         <v>312375</v>
@@ -43086,7 +43086,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1473" t="n">
-        <v>17.2287635803223</v>
+        <v>17.2287616729736</v>
       </c>
       <c r="H1473" t="n">
         <v>227595</v>
@@ -43115,7 +43115,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1474" t="n">
-        <v>16.9438304901123</v>
+        <v>16.9438323974609</v>
       </c>
       <c r="H1474" t="n">
         <v>321911</v>
@@ -43405,7 +43405,7 @@
         <v>18.6550006866455</v>
       </c>
       <c r="G1484" t="n">
-        <v>17.7178936004639</v>
+        <v>17.7178916931152</v>
       </c>
       <c r="H1484" t="n">
         <v>210630</v>
@@ -43521,7 +43521,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G1488" t="n">
-        <v>18.7008991241455</v>
+        <v>18.7009010314941</v>
       </c>
       <c r="H1488" t="n">
         <v>1068687</v>
@@ -43608,7 +43608,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1491" t="n">
-        <v>18.1690292358398</v>
+        <v>18.1690311431885</v>
       </c>
       <c r="H1491" t="n">
         <v>2245063</v>
@@ -43724,7 +43724,7 @@
         <v>19.7549991607666</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.7626323699951</v>
+        <v>18.7626342773438</v>
       </c>
       <c r="H1495" t="n">
         <v>366254</v>
@@ -44014,7 +44014,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1505" t="n">
-        <v>19.1377906799316</v>
+        <v>19.1377925872803</v>
       </c>
       <c r="H1505" t="n">
         <v>842589</v>
@@ -44101,7 +44101,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G1508" t="n">
-        <v>19.8691120147705</v>
+        <v>19.8691139221191</v>
       </c>
       <c r="H1508" t="n">
         <v>577156</v>
@@ -44130,7 +44130,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G1509" t="n">
-        <v>19.7456455230713</v>
+        <v>19.7456436157227</v>
       </c>
       <c r="H1509" t="n">
         <v>293466</v>
@@ -44159,7 +44159,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1510" t="n">
-        <v>20.4579677581787</v>
+        <v>20.4579696655273</v>
       </c>
       <c r="H1510" t="n">
         <v>712388</v>
@@ -44246,7 +44246,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1513" t="n">
-        <v>21.4457225799561</v>
+        <v>21.4457244873047</v>
       </c>
       <c r="H1513" t="n">
         <v>927272</v>
@@ -44304,7 +44304,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1515" t="n">
-        <v>20.7523975372314</v>
+        <v>20.7523956298828</v>
       </c>
       <c r="H1515" t="n">
         <v>480679</v>
@@ -44333,7 +44333,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G1516" t="n">
-        <v>20.6384239196777</v>
+        <v>20.6384220123291</v>
       </c>
       <c r="H1516" t="n">
         <v>670811</v>
@@ -44362,7 +44362,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G1517" t="n">
-        <v>20.1635398864746</v>
+        <v>20.1635417938232</v>
       </c>
       <c r="H1517" t="n">
         <v>373968</v>
@@ -44449,7 +44449,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G1520" t="n">
-        <v>20.7144031524658</v>
+        <v>20.7144050598145</v>
       </c>
       <c r="H1520" t="n">
         <v>644433</v>
@@ -44536,7 +44536,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G1523" t="n">
-        <v>21.0183296203613</v>
+        <v>21.0183277130127</v>
       </c>
       <c r="H1523" t="n">
         <v>163933</v>
@@ -44623,7 +44623,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G1526" t="n">
-        <v>21.3982353210449</v>
+        <v>21.3982372283936</v>
       </c>
       <c r="H1526" t="n">
         <v>218266</v>
@@ -44681,7 +44681,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G1528" t="n">
-        <v>21.5691947937012</v>
+        <v>21.5691928863525</v>
       </c>
       <c r="H1528" t="n">
         <v>290973</v>
@@ -44768,7 +44768,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G1531" t="n">
-        <v>21.6261806488037</v>
+        <v>21.6261825561523</v>
       </c>
       <c r="H1531" t="n">
         <v>356048</v>
@@ -44797,7 +44797,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G1532" t="n">
-        <v>19.7171478271484</v>
+        <v>19.7171497344971</v>
       </c>
       <c r="H1532" t="n">
         <v>1855644</v>
@@ -45058,7 +45058,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G1541" t="n">
-        <v>18.0550594329834</v>
+        <v>18.055061340332</v>
       </c>
       <c r="H1541" t="n">
         <v>598933</v>
@@ -45087,7 +45087,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1542" t="n">
-        <v>17.4946975708008</v>
+        <v>17.4946956634521</v>
       </c>
       <c r="H1542" t="n">
         <v>915612</v>
@@ -45145,7 +45145,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1544" t="n">
-        <v>18.0930500030518</v>
+        <v>18.0930480957031</v>
       </c>
       <c r="H1544" t="n">
         <v>460206</v>
@@ -45261,7 +45261,7 @@
         <v>19.5750007629395</v>
       </c>
       <c r="G1548" t="n">
-        <v>18.5916786193848</v>
+        <v>18.5916767120361</v>
       </c>
       <c r="H1548" t="n">
         <v>502931</v>
@@ -45290,7 +45290,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1549" t="n">
-        <v>18.5394401550293</v>
+        <v>18.5394420623779</v>
       </c>
       <c r="H1549" t="n">
         <v>396132</v>
@@ -45464,7 +45464,7 @@
         <v>19.25</v>
       </c>
       <c r="G1555" t="n">
-        <v>18.2830028533936</v>
+        <v>18.2830009460449</v>
       </c>
       <c r="H1555" t="n">
         <v>246876</v>
@@ -45696,7 +45696,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G1563" t="n">
-        <v>18.7768821716309</v>
+        <v>18.7768802642822</v>
       </c>
       <c r="H1563" t="n">
         <v>334413</v>
@@ -45754,7 +45754,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G1565" t="n">
-        <v>17.9220905303955</v>
+        <v>17.9220924377441</v>
       </c>
       <c r="H1565" t="n">
         <v>422325</v>
@@ -45783,7 +45783,7 @@
         <v>19.6450004577637</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.6581611633301</v>
+        <v>18.6581592559814</v>
       </c>
       <c r="H1566" t="n">
         <v>358435</v>
@@ -45812,7 +45812,7 @@
         <v>19.4249992370605</v>
       </c>
       <c r="G1567" t="n">
-        <v>18.4492130279541</v>
+        <v>18.4492111206055</v>
       </c>
       <c r="H1567" t="n">
         <v>352955</v>
@@ -45841,7 +45841,7 @@
         <v>18.5650005340576</v>
       </c>
       <c r="G1568" t="n">
-        <v>17.6324138641357</v>
+        <v>17.6324157714844</v>
       </c>
       <c r="H1568" t="n">
         <v>299563</v>
@@ -45986,7 +45986,7 @@
         <v>15.2749996185303</v>
       </c>
       <c r="G1573" t="n">
-        <v>14.5076818466187</v>
+        <v>14.5076808929443</v>
       </c>
       <c r="H1573" t="n">
         <v>715448</v>
@@ -46015,7 +46015,7 @@
         <v>16.7549991607666</v>
       </c>
       <c r="G1574" t="n">
-        <v>15.9133348464966</v>
+        <v>15.9133329391479</v>
       </c>
       <c r="H1574" t="n">
         <v>1254789</v>
@@ -46073,7 +46073,7 @@
         <v>16.1650009155273</v>
       </c>
       <c r="G1576" t="n">
-        <v>15.3529739379883</v>
+        <v>15.3529748916626</v>
       </c>
       <c r="H1576" t="n">
         <v>678377</v>
@@ -46160,7 +46160,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G1579" t="n">
-        <v>15.5856657028198</v>
+        <v>15.5856666564941</v>
       </c>
       <c r="H1579" t="n">
         <v>678989</v>
@@ -46189,7 +46189,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1580" t="n">
-        <v>15.7043867111206</v>
+        <v>15.7043857574463</v>
       </c>
       <c r="H1580" t="n">
         <v>591416</v>
@@ -46218,7 +46218,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1581" t="n">
-        <v>15.8610982894897</v>
+        <v>15.8611001968384</v>
       </c>
       <c r="H1581" t="n">
         <v>285487</v>
@@ -46247,7 +46247,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1582" t="n">
-        <v>15.8136100769043</v>
+        <v>15.81360912323</v>
       </c>
       <c r="H1582" t="n">
         <v>267348</v>
@@ -46334,7 +46334,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1585" t="n">
-        <v>15.253246307373</v>
+        <v>15.2532472610474</v>
       </c>
       <c r="H1585" t="n">
         <v>212871</v>
@@ -46392,7 +46392,7 @@
         <v>16.6650009155273</v>
       </c>
       <c r="G1587" t="n">
-        <v>15.8278589248657</v>
+        <v>15.8278579711914</v>
       </c>
       <c r="H1587" t="n">
         <v>215883</v>
@@ -46421,7 +46421,7 @@
         <v>17.6550006866455</v>
       </c>
       <c r="G1588" t="n">
-        <v>16.7681255340576</v>
+        <v>16.7681274414062</v>
       </c>
       <c r="H1588" t="n">
         <v>512570</v>
@@ -46566,7 +46566,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1593" t="n">
-        <v>15.2627458572388</v>
+        <v>15.2627449035645</v>
       </c>
       <c r="H1593" t="n">
         <v>528848</v>
@@ -46624,7 +46624,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1595" t="n">
-        <v>14.5884103775024</v>
+        <v>14.5884113311768</v>
       </c>
       <c r="H1595" t="n">
         <v>514601</v>
@@ -46711,7 +46711,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1598" t="n">
-        <v>15.3387269973755</v>
+        <v>15.3387260437012</v>
       </c>
       <c r="H1598" t="n">
         <v>634313</v>
@@ -46769,7 +46769,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1600" t="n">
-        <v>15.633152961731</v>
+        <v>15.6331539154053</v>
       </c>
       <c r="H1600" t="n">
         <v>220814</v>
@@ -46827,7 +46827,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1602" t="n">
-        <v>15.6996374130249</v>
+        <v>15.6996393203735</v>
       </c>
       <c r="H1602" t="n">
         <v>249471</v>
@@ -46885,7 +46885,7 @@
         <v>16.3299999237061</v>
       </c>
       <c r="G1604" t="n">
-        <v>15.5096855163574</v>
+        <v>15.5096845626831</v>
       </c>
       <c r="H1604" t="n">
         <v>267467</v>
@@ -47001,7 +47001,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1608" t="n">
-        <v>15.1392765045166</v>
+        <v>15.1392755508423</v>
       </c>
       <c r="H1608" t="n">
         <v>257315</v>
@@ -47175,7 +47175,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1614" t="n">
-        <v>14.3224763870239</v>
+        <v>14.3224773406982</v>
       </c>
       <c r="H1614" t="n">
         <v>449472</v>
@@ -47349,7 +47349,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G1620" t="n">
-        <v>15.0158071517944</v>
+        <v>15.0158061981201</v>
       </c>
       <c r="H1620" t="n">
         <v>321594</v>
@@ -47407,7 +47407,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1622" t="n">
-        <v>15.3672199249268</v>
+        <v>15.3672208786011</v>
       </c>
       <c r="H1622" t="n">
         <v>545962</v>
@@ -80096,6 +80096,35 @@
         <v>980389</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>6.23000001907349</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>6.47499990463257</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>6.23000001907349</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>6.31500005722046</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>6.31500005722046</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>363116</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -514,7 +514,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>17.9401912689209</v>
+        <v>17.9401931762695</v>
       </c>
       <c r="H5" t="n">
         <v>1381959</v>
@@ -543,7 +543,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>17.683650970459</v>
+        <v>17.6836528778076</v>
       </c>
       <c r="H6" t="n">
         <v>951699</v>
@@ -659,7 +659,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G10" t="n">
-        <v>18.84250831604</v>
+        <v>18.8425102233887</v>
       </c>
       <c r="H10" t="n">
         <v>1053164</v>
@@ -688,7 +688,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G11" t="n">
-        <v>18.4621238708496</v>
+        <v>18.4621257781982</v>
       </c>
       <c r="H11" t="n">
         <v>802632</v>
@@ -717,7 +717,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G12" t="n">
-        <v>18.2851982116699</v>
+        <v>18.2852001190186</v>
       </c>
       <c r="H12" t="n">
         <v>939035</v>
@@ -833,7 +833,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G16" t="n">
-        <v>18.1878910064697</v>
+        <v>18.1878890991211</v>
       </c>
       <c r="H16" t="n">
         <v>813843</v>
@@ -891,7 +891,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G18" t="n">
-        <v>18.4798145294189</v>
+        <v>18.4798126220703</v>
       </c>
       <c r="H18" t="n">
         <v>567890</v>
@@ -920,7 +920,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>18.223274230957</v>
+        <v>18.2232723236084</v>
       </c>
       <c r="H19" t="n">
         <v>550218</v>
@@ -1007,7 +1007,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G22" t="n">
-        <v>18.6744327545166</v>
+        <v>18.674430847168</v>
       </c>
       <c r="H22" t="n">
         <v>1011926</v>
@@ -1181,7 +1181,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G28" t="n">
-        <v>16.9051837921143</v>
+        <v>16.9051818847656</v>
       </c>
       <c r="H28" t="n">
         <v>908164</v>
@@ -1239,7 +1239,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G30" t="n">
-        <v>16.6486415863037</v>
+        <v>16.6486396789551</v>
       </c>
       <c r="H30" t="n">
         <v>1048393</v>
@@ -1297,7 +1297,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G32" t="n">
-        <v>17.48903465271</v>
+        <v>17.4890365600586</v>
       </c>
       <c r="H32" t="n">
         <v>658925</v>
@@ -1355,7 +1355,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G34" t="n">
-        <v>18.4798145294189</v>
+        <v>18.4798126220703</v>
       </c>
       <c r="H34" t="n">
         <v>689809</v>
@@ -1413,7 +1413,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G36" t="n">
-        <v>18.4532794952393</v>
+        <v>18.4532775878906</v>
       </c>
       <c r="H36" t="n">
         <v>500284</v>
@@ -1471,7 +1471,7 @@
         <v>20.5</v>
       </c>
       <c r="G38" t="n">
-        <v>18.1348114013672</v>
+        <v>18.1348133087158</v>
       </c>
       <c r="H38" t="n">
         <v>591716</v>
@@ -1558,7 +1558,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G41" t="n">
-        <v>17.9048080444336</v>
+        <v>17.9048099517822</v>
       </c>
       <c r="H41" t="n">
         <v>422135</v>
@@ -1587,7 +1587,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G42" t="n">
-        <v>18.3471183776855</v>
+        <v>18.3471202850342</v>
       </c>
       <c r="H42" t="n">
         <v>557658</v>
@@ -1732,7 +1732,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G47" t="n">
-        <v>19.9925231933594</v>
+        <v>19.992525100708</v>
       </c>
       <c r="H47" t="n">
         <v>1033585</v>
@@ -1790,7 +1790,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>19.7271366119385</v>
+        <v>19.7271347045898</v>
       </c>
       <c r="H49" t="n">
         <v>805952</v>
@@ -1819,7 +1819,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G50" t="n">
-        <v>19.3379020690918</v>
+        <v>19.3379039764404</v>
       </c>
       <c r="H50" t="n">
         <v>900267</v>
@@ -1848,7 +1848,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G51" t="n">
-        <v>19.6475219726562</v>
+        <v>19.6475200653076</v>
       </c>
       <c r="H51" t="n">
         <v>599137</v>
@@ -1906,7 +1906,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G53" t="n">
-        <v>19.1167449951172</v>
+        <v>19.1167469024658</v>
       </c>
       <c r="H53" t="n">
         <v>1070469</v>
@@ -1935,7 +1935,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G54" t="n">
-        <v>19.3379020690918</v>
+        <v>19.3379039764404</v>
       </c>
       <c r="H54" t="n">
         <v>460963</v>
@@ -1993,7 +1993,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>20.0367527008057</v>
+        <v>20.0367546081543</v>
       </c>
       <c r="H56" t="n">
         <v>1462491</v>
@@ -2051,7 +2051,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G58" t="n">
-        <v>19.4971370697021</v>
+        <v>19.4971351623535</v>
       </c>
       <c r="H58" t="n">
         <v>1161092</v>
@@ -2080,7 +2080,7 @@
         <v>22.0100002288818</v>
       </c>
       <c r="G59" t="n">
-        <v>19.4705963134766</v>
+        <v>19.4705944061279</v>
       </c>
       <c r="H59" t="n">
         <v>731623</v>
@@ -2138,7 +2138,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G61" t="n">
-        <v>19.4794406890869</v>
+        <v>19.4794445037842</v>
       </c>
       <c r="H61" t="n">
         <v>502164</v>
@@ -2225,7 +2225,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G64" t="n">
-        <v>19.4971370697021</v>
+        <v>19.4971351623535</v>
       </c>
       <c r="H64" t="n">
         <v>538910</v>
@@ -2283,7 +2283,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G66" t="n">
-        <v>18.8690509796143</v>
+        <v>18.8690490722656</v>
       </c>
       <c r="H66" t="n">
         <v>592054</v>
@@ -2341,7 +2341,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G68" t="n">
-        <v>18.5152015686035</v>
+        <v>18.5151996612549</v>
       </c>
       <c r="H68" t="n">
         <v>449428</v>
@@ -2486,7 +2486,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>18.9486675262451</v>
+        <v>18.9486656188965</v>
       </c>
       <c r="H73" t="n">
         <v>659167</v>
@@ -2544,7 +2544,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G75" t="n">
-        <v>18.8778972625732</v>
+        <v>18.8778991699219</v>
       </c>
       <c r="H75" t="n">
         <v>347479</v>
@@ -2602,7 +2602,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G77" t="n">
-        <v>18.8071269989014</v>
+        <v>18.8071250915527</v>
       </c>
       <c r="H77" t="n">
         <v>725644</v>
@@ -2660,7 +2660,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>18.3648128509521</v>
+        <v>18.3648147583008</v>
       </c>
       <c r="H79" t="n">
         <v>1254692</v>
@@ -2805,7 +2805,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G84" t="n">
-        <v>17.878267288208</v>
+        <v>17.8782691955566</v>
       </c>
       <c r="H84" t="n">
         <v>570613</v>
@@ -2834,7 +2834,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>18.0021171569824</v>
+        <v>18.0021190643311</v>
       </c>
       <c r="H85" t="n">
         <v>455661</v>
@@ -2863,7 +2863,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G86" t="n">
-        <v>17.7190399169922</v>
+        <v>17.7190418243408</v>
       </c>
       <c r="H86" t="n">
         <v>401376</v>
@@ -2892,7 +2892,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G87" t="n">
-        <v>17.9048080444336</v>
+        <v>17.9048099517822</v>
       </c>
       <c r="H87" t="n">
         <v>346687</v>
@@ -2921,7 +2921,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G88" t="n">
-        <v>17.4448013305664</v>
+        <v>17.444803237915</v>
       </c>
       <c r="H88" t="n">
         <v>546914</v>
@@ -3182,7 +3182,7 @@
         <v>20.2700004577637</v>
       </c>
       <c r="G97" t="n">
-        <v>17.9313507080078</v>
+        <v>17.9313488006592</v>
       </c>
       <c r="H97" t="n">
         <v>352423</v>
@@ -3385,7 +3385,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G104" t="n">
-        <v>17.5305519104004</v>
+        <v>17.530553817749</v>
       </c>
       <c r="H104" t="n">
         <v>453269</v>
@@ -3443,7 +3443,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G106" t="n">
-        <v>17.4128322601318</v>
+        <v>17.4128360748291</v>
       </c>
       <c r="H106" t="n">
         <v>450576</v>
@@ -3472,7 +3472,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G107" t="n">
-        <v>17.304178237915</v>
+        <v>17.3041763305664</v>
       </c>
       <c r="H107" t="n">
         <v>353691</v>
@@ -3501,7 +3501,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>17.4762191772461</v>
+        <v>17.4762210845947</v>
       </c>
       <c r="H108" t="n">
         <v>367982</v>
@@ -3530,7 +3530,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G109" t="n">
-        <v>17.4762191772461</v>
+        <v>17.4762210845947</v>
       </c>
       <c r="H109" t="n">
         <v>426168</v>
@@ -3617,7 +3617,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>17.7478733062744</v>
+        <v>17.7478713989258</v>
       </c>
       <c r="H112" t="n">
         <v>286254</v>
@@ -3646,7 +3646,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G113" t="n">
-        <v>17.6844882965088</v>
+        <v>17.6844863891602</v>
       </c>
       <c r="H113" t="n">
         <v>347407</v>
@@ -3675,7 +3675,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G114" t="n">
-        <v>17.150239944458</v>
+        <v>17.1502418518066</v>
       </c>
       <c r="H114" t="n">
         <v>471820</v>
@@ -3704,7 +3704,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G115" t="n">
-        <v>16.71559715271</v>
+        <v>16.7155990600586</v>
       </c>
       <c r="H115" t="n">
         <v>541514</v>
@@ -3733,7 +3733,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G116" t="n">
-        <v>16.5435543060303</v>
+        <v>16.5435523986816</v>
       </c>
       <c r="H116" t="n">
         <v>483555</v>
@@ -3791,7 +3791,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G118" t="n">
-        <v>17.0778007507324</v>
+        <v>17.0777988433838</v>
       </c>
       <c r="H118" t="n">
         <v>634094</v>
@@ -3878,7 +3878,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G121" t="n">
-        <v>17.7297649383545</v>
+        <v>17.7297630310059</v>
       </c>
       <c r="H121" t="n">
         <v>523740</v>
@@ -3907,7 +3907,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G122" t="n">
-        <v>17.8655891418457</v>
+        <v>17.8655872344971</v>
       </c>
       <c r="H122" t="n">
         <v>478133</v>
@@ -3936,7 +3936,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G123" t="n">
-        <v>18.1825141906738</v>
+        <v>18.1825160980225</v>
       </c>
       <c r="H123" t="n">
         <v>467685</v>
@@ -3994,7 +3994,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>16.3896179199219</v>
+        <v>16.3896198272705</v>
       </c>
       <c r="H125" t="n">
         <v>973572</v>
@@ -4023,7 +4023,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G126" t="n">
-        <v>16.6793785095215</v>
+        <v>16.6793804168701</v>
       </c>
       <c r="H126" t="n">
         <v>635006</v>
@@ -4139,7 +4139,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G130" t="n">
-        <v>16.8061485290527</v>
+        <v>16.8061466217041</v>
       </c>
       <c r="H130" t="n">
         <v>255804</v>
@@ -4168,7 +4168,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G131" t="n">
-        <v>16.8242588043213</v>
+        <v>16.8242568969727</v>
       </c>
       <c r="H131" t="n">
         <v>503139</v>
@@ -4197,7 +4197,7 @@
         <v>17.75</v>
       </c>
       <c r="G132" t="n">
-        <v>16.0726928710938</v>
+        <v>16.0726909637451</v>
       </c>
       <c r="H132" t="n">
         <v>575432</v>
@@ -4226,7 +4226,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G133" t="n">
-        <v>15.8734798431396</v>
+        <v>15.8734788894653</v>
       </c>
       <c r="H133" t="n">
         <v>652419</v>
@@ -4255,7 +4255,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G134" t="n">
-        <v>16.3624515533447</v>
+        <v>16.3624534606934</v>
       </c>
       <c r="H134" t="n">
         <v>562960</v>
@@ -4400,7 +4400,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G139" t="n">
-        <v>17.0868549346924</v>
+        <v>17.086856842041</v>
       </c>
       <c r="H139" t="n">
         <v>861033</v>
@@ -4429,7 +4429,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G140" t="n">
-        <v>17.150239944458</v>
+        <v>17.1502418518066</v>
       </c>
       <c r="H140" t="n">
         <v>545374</v>
@@ -4516,7 +4516,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G143" t="n">
-        <v>17.8655891418457</v>
+        <v>17.8655872344971</v>
       </c>
       <c r="H143" t="n">
         <v>769870</v>
@@ -4545,7 +4545,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G144" t="n">
-        <v>17.9018077850342</v>
+        <v>17.9018096923828</v>
       </c>
       <c r="H144" t="n">
         <v>551371</v>
@@ -4632,7 +4632,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G147" t="n">
-        <v>18.7710914611816</v>
+        <v>18.7710933685303</v>
       </c>
       <c r="H147" t="n">
         <v>1164581</v>
@@ -4661,7 +4661,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>18.6352653503418</v>
+        <v>18.6352634429932</v>
       </c>
       <c r="H148" t="n">
         <v>873688</v>
@@ -4719,7 +4719,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G150" t="n">
-        <v>19.2147884368896</v>
+        <v>19.214786529541</v>
       </c>
       <c r="H150" t="n">
         <v>859181</v>
@@ -4748,7 +4748,7 @@
         <v>20.5699996948242</v>
       </c>
       <c r="G151" t="n">
-        <v>18.6262111663818</v>
+        <v>18.6262092590332</v>
       </c>
       <c r="H151" t="n">
         <v>1004411</v>
@@ -4835,7 +4835,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G154" t="n">
-        <v>18.7167625427246</v>
+        <v>18.716760635376</v>
       </c>
       <c r="H154" t="n">
         <v>930993</v>
@@ -4893,7 +4893,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G156" t="n">
-        <v>18.7620372772217</v>
+        <v>18.762035369873</v>
       </c>
       <c r="H156" t="n">
         <v>454171</v>
@@ -4951,7 +4951,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G158" t="n">
-        <v>18.8073139190674</v>
+        <v>18.8073120117188</v>
       </c>
       <c r="H158" t="n">
         <v>652271</v>
@@ -4980,7 +4980,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G159" t="n">
-        <v>18.94313621521</v>
+        <v>18.9431381225586</v>
       </c>
       <c r="H159" t="n">
         <v>809515</v>
@@ -5038,7 +5038,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G161" t="n">
-        <v>18.6624336242676</v>
+        <v>18.6624317169189</v>
       </c>
       <c r="H161" t="n">
         <v>488367</v>
@@ -5067,7 +5067,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G162" t="n">
-        <v>18.6624336242676</v>
+        <v>18.6624317169189</v>
       </c>
       <c r="H162" t="n">
         <v>278516</v>
@@ -5096,7 +5096,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>18.4722766876221</v>
+        <v>18.4722785949707</v>
       </c>
       <c r="H163" t="n">
         <v>404764</v>
@@ -5270,7 +5270,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6533756256104</v>
+        <v>18.653377532959</v>
       </c>
       <c r="H169" t="n">
         <v>409770</v>
@@ -5299,7 +5299,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G170" t="n">
-        <v>18.7167625427246</v>
+        <v>18.716760635376</v>
       </c>
       <c r="H170" t="n">
         <v>499477</v>
@@ -5444,7 +5444,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G175" t="n">
-        <v>18.7620372772217</v>
+        <v>18.762035369873</v>
       </c>
       <c r="H175" t="n">
         <v>290570</v>
@@ -5589,7 +5589,7 @@
         <v>21.4899997711182</v>
       </c>
       <c r="G180" t="n">
-        <v>19.4592761993408</v>
+        <v>19.4592742919922</v>
       </c>
       <c r="H180" t="n">
         <v>700088</v>
@@ -5734,7 +5734,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G185" t="n">
-        <v>18.7710914611816</v>
+        <v>18.7710933685303</v>
       </c>
       <c r="H185" t="n">
         <v>702087</v>
@@ -5792,7 +5792,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G187" t="n">
-        <v>19.9391918182373</v>
+        <v>19.9391937255859</v>
       </c>
       <c r="H187" t="n">
         <v>831000</v>
@@ -5821,7 +5821,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G188" t="n">
-        <v>20.4553298950195</v>
+        <v>20.4553279876709</v>
       </c>
       <c r="H188" t="n">
         <v>1218252</v>
@@ -5879,7 +5879,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G190" t="n">
-        <v>20.4553298950195</v>
+        <v>20.4553279876709</v>
       </c>
       <c r="H190" t="n">
         <v>521478</v>
@@ -5937,7 +5937,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>20.3919448852539</v>
+        <v>20.3919429779053</v>
       </c>
       <c r="H192" t="n">
         <v>676988</v>
@@ -6053,7 +6053,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>20.8446941375732</v>
+        <v>20.8446960449219</v>
       </c>
       <c r="H196" t="n">
         <v>733993</v>
@@ -6082,7 +6082,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G197" t="n">
-        <v>20.7994213104248</v>
+        <v>20.7994194030762</v>
       </c>
       <c r="H197" t="n">
         <v>492907</v>
@@ -6140,7 +6140,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G199" t="n">
-        <v>20.1021823883057</v>
+        <v>20.1021842956543</v>
       </c>
       <c r="H199" t="n">
         <v>693101</v>
@@ -6256,7 +6256,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G203" t="n">
-        <v>20.7541446685791</v>
+        <v>20.7541465759277</v>
       </c>
       <c r="H203" t="n">
         <v>761654</v>
@@ -6285,7 +6285,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>20.4191093444824</v>
+        <v>20.4191074371338</v>
       </c>
       <c r="H204" t="n">
         <v>692871</v>
@@ -6343,7 +6343,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G206" t="n">
-        <v>20.2651710510254</v>
+        <v>20.265172958374</v>
       </c>
       <c r="H206" t="n">
         <v>579770</v>
@@ -6691,7 +6691,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>19.5045528411865</v>
+        <v>19.5045509338379</v>
       </c>
       <c r="H218" t="n">
         <v>378528</v>
@@ -6749,7 +6749,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G220" t="n">
-        <v>19.7943115234375</v>
+        <v>19.7943134307861</v>
       </c>
       <c r="H220" t="n">
         <v>211848</v>
@@ -6807,7 +6807,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>19.8305320739746</v>
+        <v>19.830530166626</v>
       </c>
       <c r="H222" t="n">
         <v>720123</v>
@@ -6836,7 +6836,7 @@
         <v>21.9899997711182</v>
       </c>
       <c r="G223" t="n">
-        <v>19.9120254516602</v>
+        <v>19.9120273590088</v>
       </c>
       <c r="H223" t="n">
         <v>433755</v>
@@ -6894,7 +6894,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.4722766876221</v>
+        <v>18.4722785949707</v>
       </c>
       <c r="H225" t="n">
         <v>3206760</v>
@@ -6923,7 +6923,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G226" t="n">
-        <v>18.0919628143311</v>
+        <v>18.0919647216797</v>
       </c>
       <c r="H226" t="n">
         <v>1188113</v>
@@ -6952,7 +6952,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G227" t="n">
-        <v>18.3002281188965</v>
+        <v>18.3002300262451</v>
       </c>
       <c r="H227" t="n">
         <v>568589</v>
@@ -6981,7 +6981,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G228" t="n">
-        <v>18.3273944854736</v>
+        <v>18.3273963928223</v>
       </c>
       <c r="H228" t="n">
         <v>773547</v>
@@ -7010,7 +7010,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>18.2459011077881</v>
+        <v>18.2458992004395</v>
       </c>
       <c r="H229" t="n">
         <v>502752</v>
@@ -7039,7 +7039,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G230" t="n">
-        <v>18.0104694366455</v>
+        <v>18.0104675292969</v>
       </c>
       <c r="H230" t="n">
         <v>460171</v>
@@ -7068,7 +7068,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G231" t="n">
-        <v>17.7388153076172</v>
+        <v>17.7388172149658</v>
       </c>
       <c r="H231" t="n">
         <v>492945</v>
@@ -7242,7 +7242,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G237" t="n">
-        <v>18.8073139190674</v>
+        <v>18.8073120117188</v>
       </c>
       <c r="H237" t="n">
         <v>711240</v>
@@ -7271,7 +7271,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>18.7167625427246</v>
+        <v>18.716760635376</v>
       </c>
       <c r="H238" t="n">
         <v>591668</v>
@@ -7358,7 +7358,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>19.2872257232666</v>
+        <v>19.2872276306152</v>
       </c>
       <c r="H241" t="n">
         <v>673068</v>
@@ -7503,7 +7503,7 @@
         <v>21.2700004577637</v>
       </c>
       <c r="G246" t="n">
-        <v>19.2600650787354</v>
+        <v>19.260066986084</v>
       </c>
       <c r="H246" t="n">
         <v>348399</v>
@@ -7561,7 +7561,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G248" t="n">
-        <v>20.2651710510254</v>
+        <v>20.265172958374</v>
       </c>
       <c r="H248" t="n">
         <v>1423797</v>
@@ -7590,7 +7590,7 @@
         <v>22.5</v>
       </c>
       <c r="G249" t="n">
-        <v>20.373836517334</v>
+        <v>20.3738346099854</v>
       </c>
       <c r="H249" t="n">
         <v>417900</v>
@@ -7619,7 +7619,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G250" t="n">
-        <v>20.2651710510254</v>
+        <v>20.265172958374</v>
       </c>
       <c r="H250" t="n">
         <v>491157</v>
@@ -7648,7 +7648,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G251" t="n">
-        <v>20.3466682434082</v>
+        <v>20.3466663360596</v>
       </c>
       <c r="H251" t="n">
         <v>359013</v>
@@ -7677,7 +7677,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>20.2380065917969</v>
+        <v>20.2380084991455</v>
       </c>
       <c r="H252" t="n">
         <v>230612</v>
@@ -7909,7 +7909,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G260" t="n">
-        <v>21.4785480499268</v>
+        <v>21.4785461425781</v>
       </c>
       <c r="H260" t="n">
         <v>1705785</v>
@@ -7996,7 +7996,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G263" t="n">
-        <v>22.0580711364746</v>
+        <v>22.0580730438232</v>
       </c>
       <c r="H263" t="n">
         <v>1362031</v>
@@ -8025,7 +8025,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G264" t="n">
-        <v>22.2572822570801</v>
+        <v>22.2572803497314</v>
       </c>
       <c r="H264" t="n">
         <v>869802</v>
@@ -8054,7 +8054,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G265" t="n">
-        <v>22.2935009002686</v>
+        <v>22.2935028076172</v>
       </c>
       <c r="H265" t="n">
         <v>1130923</v>
@@ -8170,7 +8170,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G269" t="n">
-        <v>22.2391719818115</v>
+        <v>22.2391700744629</v>
       </c>
       <c r="H269" t="n">
         <v>512480</v>
@@ -8286,7 +8286,7 @@
         <v>25.5699996948242</v>
       </c>
       <c r="G273" t="n">
-        <v>23.1537303924561</v>
+        <v>23.1537284851074</v>
       </c>
       <c r="H273" t="n">
         <v>1005467</v>
@@ -8373,7 +8373,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G276" t="n">
-        <v>22.3568859100342</v>
+        <v>22.3568840026855</v>
       </c>
       <c r="H276" t="n">
         <v>736861</v>
@@ -8402,7 +8402,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>22.9092426300049</v>
+        <v>22.9092445373535</v>
       </c>
       <c r="H277" t="n">
         <v>1129609</v>
@@ -8431,7 +8431,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G278" t="n">
-        <v>22.1757850646973</v>
+        <v>22.1757869720459</v>
       </c>
       <c r="H278" t="n">
         <v>1066573</v>
@@ -8489,7 +8489,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G280" t="n">
-        <v>23.606481552124</v>
+        <v>23.6064834594727</v>
       </c>
       <c r="H280" t="n">
         <v>2579913</v>
@@ -8518,7 +8518,7 @@
         <v>26.2299995422363</v>
       </c>
       <c r="G281" t="n">
-        <v>23.7513599395752</v>
+        <v>23.7513618469238</v>
       </c>
       <c r="H281" t="n">
         <v>1163004</v>
@@ -8547,7 +8547,7 @@
         <v>26.6399993896484</v>
       </c>
       <c r="G282" t="n">
-        <v>24.1226196289062</v>
+        <v>24.1226177215576</v>
       </c>
       <c r="H282" t="n">
         <v>1541926</v>
@@ -8721,7 +8721,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>23.7241973876953</v>
+        <v>23.7241992950439</v>
       </c>
       <c r="H288" t="n">
         <v>395279</v>
@@ -8866,7 +8866,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G293" t="n">
-        <v>23.7241973876953</v>
+        <v>23.7241992950439</v>
       </c>
       <c r="H293" t="n">
         <v>138589</v>
@@ -8953,7 +8953,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>24.0682888031006</v>
+        <v>24.068286895752</v>
       </c>
       <c r="H296" t="n">
         <v>653226</v>
@@ -9011,7 +9011,7 @@
         <v>26.8299999237061</v>
       </c>
       <c r="G298" t="n">
-        <v>24.2946662902832</v>
+        <v>24.2946643829346</v>
       </c>
       <c r="H298" t="n">
         <v>540551</v>
@@ -9156,7 +9156,7 @@
         <v>28.0400009155273</v>
       </c>
       <c r="G303" t="n">
-        <v>25.3903255462646</v>
+        <v>25.390323638916</v>
       </c>
       <c r="H303" t="n">
         <v>911254</v>
@@ -9185,7 +9185,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G304" t="n">
-        <v>25.4265441894531</v>
+        <v>25.4265460968018</v>
       </c>
       <c r="H304" t="n">
         <v>549504</v>
@@ -9243,7 +9243,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>25.6710300445557</v>
+        <v>25.671028137207</v>
       </c>
       <c r="H306" t="n">
         <v>500694</v>
@@ -9301,7 +9301,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>25.7615814208984</v>
+        <v>25.7615795135498</v>
       </c>
       <c r="H308" t="n">
         <v>601915</v>
@@ -9359,7 +9359,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G310" t="n">
-        <v>24.955680847168</v>
+        <v>24.9556827545166</v>
       </c>
       <c r="H310" t="n">
         <v>2238630</v>
@@ -9388,7 +9388,7 @@
         <v>27.5</v>
       </c>
       <c r="G311" t="n">
-        <v>24.9013538360596</v>
+        <v>24.9013519287109</v>
       </c>
       <c r="H311" t="n">
         <v>1035739</v>
@@ -9417,7 +9417,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>25.0643444061279</v>
+        <v>25.0643424987793</v>
       </c>
       <c r="H312" t="n">
         <v>650689</v>
@@ -9504,7 +9504,7 @@
         <v>27.5400009155273</v>
       </c>
       <c r="G315" t="n">
-        <v>24.9375762939453</v>
+        <v>24.937572479248</v>
       </c>
       <c r="H315" t="n">
         <v>486126</v>
@@ -9562,7 +9562,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>25.62575340271</v>
+        <v>25.6257553100586</v>
       </c>
       <c r="H317" t="n">
         <v>349361</v>
@@ -9591,7 +9591,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G318" t="n">
-        <v>25.2273368835449</v>
+        <v>25.2273349761963</v>
       </c>
       <c r="H318" t="n">
         <v>385409</v>
@@ -9678,7 +9678,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>25.399377822876</v>
+        <v>25.3993797302246</v>
       </c>
       <c r="H321" t="n">
         <v>203615</v>
@@ -9707,7 +9707,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G322" t="n">
-        <v>25.4265441894531</v>
+        <v>25.4265460968018</v>
       </c>
       <c r="H322" t="n">
         <v>230403</v>
@@ -9736,7 +9736,7 @@
         <v>28.4099998474121</v>
       </c>
       <c r="G323" t="n">
-        <v>25.7253589630127</v>
+        <v>25.72536277771</v>
       </c>
       <c r="H323" t="n">
         <v>704929</v>
@@ -9765,7 +9765,7 @@
         <v>27.9300003051758</v>
       </c>
       <c r="G324" t="n">
-        <v>25.2907199859619</v>
+        <v>25.2907180786133</v>
       </c>
       <c r="H324" t="n">
         <v>302233</v>
@@ -9794,7 +9794,7 @@
         <v>27.75</v>
       </c>
       <c r="G325" t="n">
-        <v>25.1277294158936</v>
+        <v>25.1277275085449</v>
       </c>
       <c r="H325" t="n">
         <v>265673</v>
@@ -9823,7 +9823,7 @@
         <v>28.4300003051758</v>
       </c>
       <c r="G326" t="n">
-        <v>25.7434730529785</v>
+        <v>25.7434711456299</v>
       </c>
       <c r="H326" t="n">
         <v>405081</v>
@@ -9852,7 +9852,7 @@
         <v>28.2099990844727</v>
       </c>
       <c r="G327" t="n">
-        <v>25.5442581176758</v>
+        <v>25.5442600250244</v>
       </c>
       <c r="H327" t="n">
         <v>365212</v>
@@ -9910,7 +9910,7 @@
         <v>28.1700000762939</v>
       </c>
       <c r="G329" t="n">
-        <v>25.5080413818359</v>
+        <v>25.5080394744873</v>
       </c>
       <c r="H329" t="n">
         <v>343434</v>
@@ -9939,7 +9939,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>25.2635536193848</v>
+        <v>25.2635517120361</v>
       </c>
       <c r="H330" t="n">
         <v>387257</v>
@@ -9997,7 +9997,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G332" t="n">
-        <v>24.7836399078369</v>
+        <v>24.7836418151855</v>
       </c>
       <c r="H332" t="n">
         <v>660230</v>
@@ -10084,7 +10084,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>24.2674999237061</v>
+        <v>24.2674980163574</v>
       </c>
       <c r="H335" t="n">
         <v>589692</v>
@@ -10142,7 +10142,7 @@
         <v>28.1900005340576</v>
       </c>
       <c r="G337" t="n">
-        <v>25.5261497497559</v>
+        <v>25.5261516571045</v>
       </c>
       <c r="H337" t="n">
         <v>379396</v>
@@ -10287,7 +10287,7 @@
         <v>29.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>26.3229942321777</v>
+        <v>26.3229923248291</v>
       </c>
       <c r="H342" t="n">
         <v>296838</v>
@@ -10316,7 +10316,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G343" t="n">
-        <v>26.676139831543</v>
+        <v>26.6761379241943</v>
       </c>
       <c r="H343" t="n">
         <v>498694</v>
@@ -10374,7 +10374,7 @@
         <v>29</v>
       </c>
       <c r="G345" t="n">
-        <v>26.2596092224121</v>
+        <v>26.2596073150635</v>
       </c>
       <c r="H345" t="n">
         <v>806664</v>
@@ -10403,7 +10403,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>26.667085647583</v>
+        <v>26.6670875549316</v>
       </c>
       <c r="H346" t="n">
         <v>297569</v>
@@ -10432,7 +10432,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G347" t="n">
-        <v>26.9115695953369</v>
+        <v>26.9115676879883</v>
       </c>
       <c r="H347" t="n">
         <v>494059</v>
@@ -10490,7 +10490,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G349" t="n">
-        <v>26.6036987304688</v>
+        <v>26.6037006378174</v>
       </c>
       <c r="H349" t="n">
         <v>284270</v>
@@ -10519,7 +10519,7 @@
         <v>29.3700008392334</v>
       </c>
       <c r="G350" t="n">
-        <v>26.5946445465088</v>
+        <v>26.5946464538574</v>
       </c>
       <c r="H350" t="n">
         <v>150195</v>
@@ -10548,7 +10548,7 @@
         <v>29</v>
       </c>
       <c r="G351" t="n">
-        <v>26.2596092224121</v>
+        <v>26.2596073150635</v>
       </c>
       <c r="H351" t="n">
         <v>536086</v>
@@ -10635,7 +10635,7 @@
         <v>28.5300006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>25.8340244293213</v>
+        <v>25.8340225219727</v>
       </c>
       <c r="H354" t="n">
         <v>490864</v>
@@ -10693,7 +10693,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G356" t="n">
-        <v>26.0641040802002</v>
+        <v>26.0641059875488</v>
       </c>
       <c r="H356" t="n">
         <v>340042</v>
@@ -10751,7 +10751,7 @@
         <v>25.6599998474121</v>
       </c>
       <c r="G358" t="n">
-        <v>23.6159934997559</v>
+        <v>23.6159954071045</v>
       </c>
       <c r="H358" t="n">
         <v>2202691</v>
@@ -10838,7 +10838,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>22.9625511169434</v>
+        <v>22.9625492095947</v>
       </c>
       <c r="H361" t="n">
         <v>858119</v>
@@ -11041,7 +11041,7 @@
         <v>24</v>
       </c>
       <c r="G368" t="n">
-        <v>22.0882263183594</v>
+        <v>22.088228225708</v>
       </c>
       <c r="H368" t="n">
         <v>1374366</v>
@@ -11157,7 +11157,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>22.3643264770508</v>
+        <v>22.3643283843994</v>
       </c>
       <c r="H372" t="n">
         <v>603189</v>
@@ -11273,7 +11273,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>23.28466796875</v>
+        <v>23.2846698760986</v>
       </c>
       <c r="H376" t="n">
         <v>596955</v>
@@ -11302,7 +11302,7 @@
         <v>25.5200004577637</v>
       </c>
       <c r="G377" t="n">
-        <v>23.4871463775635</v>
+        <v>23.4871482849121</v>
       </c>
       <c r="H377" t="n">
         <v>514656</v>
@@ -11331,7 +11331,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G378" t="n">
-        <v>23.4319267272949</v>
+        <v>23.4319248199463</v>
       </c>
       <c r="H378" t="n">
         <v>355374</v>
@@ -11389,7 +11389,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G380" t="n">
-        <v>23.0269775390625</v>
+        <v>23.0269737243652</v>
       </c>
       <c r="H380" t="n">
         <v>525690</v>
@@ -11418,7 +11418,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G381" t="n">
-        <v>22.6036186218262</v>
+        <v>22.6036167144775</v>
       </c>
       <c r="H381" t="n">
         <v>369901</v>
@@ -11447,7 +11447,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>22.2538871765137</v>
+        <v>22.253885269165</v>
       </c>
       <c r="H382" t="n">
         <v>540961</v>
@@ -11476,7 +11476,7 @@
         <v>23.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>21.545223236084</v>
+        <v>21.5452213287354</v>
       </c>
       <c r="H383" t="n">
         <v>915042</v>
@@ -11563,7 +11563,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G386" t="n">
-        <v>21.5544281005859</v>
+        <v>21.5544261932373</v>
       </c>
       <c r="H386" t="n">
         <v>216910</v>
@@ -11592,7 +11592,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>21.674072265625</v>
+        <v>21.6740684509277</v>
       </c>
       <c r="H387" t="n">
         <v>321536</v>
@@ -11621,7 +11621,7 @@
         <v>23.5</v>
       </c>
       <c r="G388" t="n">
-        <v>21.6280555725098</v>
+        <v>21.6280536651611</v>
       </c>
       <c r="H388" t="n">
         <v>357459</v>
@@ -11708,7 +11708,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G391" t="n">
-        <v>21.2046985626221</v>
+        <v>21.2046966552734</v>
       </c>
       <c r="H391" t="n">
         <v>426099</v>
@@ -11882,7 +11882,7 @@
         <v>23.8700008392334</v>
       </c>
       <c r="G397" t="n">
-        <v>21.9685821533203</v>
+        <v>21.9685840606689</v>
       </c>
       <c r="H397" t="n">
         <v>424576</v>
@@ -11940,7 +11940,7 @@
         <v>24.3099994659424</v>
       </c>
       <c r="G399" t="n">
-        <v>22.3735332489014</v>
+        <v>22.3735313415527</v>
       </c>
       <c r="H399" t="n">
         <v>712169</v>
@@ -11998,7 +11998,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G401" t="n">
-        <v>22.410343170166</v>
+        <v>22.4103450775146</v>
       </c>
       <c r="H401" t="n">
         <v>372937</v>
@@ -12085,7 +12085,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G404" t="n">
-        <v>22.6404323577881</v>
+        <v>22.6404342651367</v>
       </c>
       <c r="H404" t="n">
         <v>432144</v>
@@ -12143,7 +12143,7 @@
         <v>24</v>
       </c>
       <c r="G406" t="n">
-        <v>22.0882263183594</v>
+        <v>22.088228225708</v>
       </c>
       <c r="H406" t="n">
         <v>1576783</v>
@@ -12230,7 +12230,7 @@
         <v>24</v>
       </c>
       <c r="G409" t="n">
-        <v>22.0882263183594</v>
+        <v>22.088228225708</v>
       </c>
       <c r="H409" t="n">
         <v>517420</v>
@@ -12317,7 +12317,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G412" t="n">
-        <v>22.3551273345947</v>
+        <v>22.3551254272461</v>
       </c>
       <c r="H412" t="n">
         <v>262904</v>
@@ -12375,7 +12375,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G414" t="n">
-        <v>22.0514125823975</v>
+        <v>22.0514106750488</v>
       </c>
       <c r="H414" t="n">
         <v>315380</v>
@@ -12462,7 +12462,7 @@
         <v>24.2700004577637</v>
       </c>
       <c r="G417" t="n">
-        <v>22.3367176055908</v>
+        <v>22.3367195129395</v>
       </c>
       <c r="H417" t="n">
         <v>583263</v>
@@ -12491,7 +12491,7 @@
         <v>24.0300006866455</v>
       </c>
       <c r="G418" t="n">
-        <v>22.115837097168</v>
+        <v>22.1158351898193</v>
       </c>
       <c r="H418" t="n">
         <v>245071</v>
@@ -12549,7 +12549,7 @@
         <v>23.9699993133545</v>
       </c>
       <c r="G420" t="n">
-        <v>22.0606136322021</v>
+        <v>22.0606155395508</v>
       </c>
       <c r="H420" t="n">
         <v>197206</v>
@@ -12636,7 +12636,7 @@
         <v>24</v>
       </c>
       <c r="G423" t="n">
-        <v>22.0882263183594</v>
+        <v>22.088228225708</v>
       </c>
       <c r="H423" t="n">
         <v>206329</v>
@@ -12665,7 +12665,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>21.9961910247803</v>
+        <v>21.9961929321289</v>
       </c>
       <c r="H424" t="n">
         <v>138330</v>
@@ -12781,7 +12781,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G428" t="n">
-        <v>22.3551273345947</v>
+        <v>22.3551254272461</v>
       </c>
       <c r="H428" t="n">
         <v>451750</v>
@@ -12955,7 +12955,7 @@
         <v>23.9300003051758</v>
       </c>
       <c r="G434" t="n">
-        <v>22.0238037109375</v>
+        <v>22.0238018035889</v>
       </c>
       <c r="H434" t="n">
         <v>408570</v>
@@ -12984,7 +12984,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G435" t="n">
-        <v>21.9961910247803</v>
+        <v>21.9961929321289</v>
       </c>
       <c r="H435" t="n">
         <v>619938</v>
@@ -13071,7 +13071,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G438" t="n">
-        <v>20.827356338501</v>
+        <v>20.8273544311523</v>
       </c>
       <c r="H438" t="n">
         <v>1417619</v>
@@ -13245,7 +13245,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G444" t="n">
-        <v>21.3243427276611</v>
+        <v>21.3243408203125</v>
       </c>
       <c r="H444" t="n">
         <v>333907</v>
@@ -13332,7 +13332,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G447" t="n">
-        <v>22.0514125823975</v>
+        <v>22.0514106750488</v>
       </c>
       <c r="H447" t="n">
         <v>633441</v>
@@ -13448,7 +13448,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G451" t="n">
-        <v>21.2967300415039</v>
+        <v>21.2967319488525</v>
       </c>
       <c r="H451" t="n">
         <v>599089</v>
@@ -13477,7 +13477,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G452" t="n">
-        <v>20.9746131896973</v>
+        <v>20.9746112823486</v>
       </c>
       <c r="H452" t="n">
         <v>950234</v>
@@ -13535,7 +13535,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838161468506</v>
       </c>
       <c r="H454" t="n">
         <v>572574</v>
@@ -13593,7 +13593,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G456" t="n">
-        <v>21.0666446685791</v>
+        <v>21.0666427612305</v>
       </c>
       <c r="H456" t="n">
         <v>654865</v>
@@ -13680,7 +13680,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G459" t="n">
-        <v>21.1586780548096</v>
+        <v>21.1586799621582</v>
       </c>
       <c r="H459" t="n">
         <v>440417</v>
@@ -13738,7 +13738,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G461" t="n">
-        <v>21.0022220611572</v>
+        <v>21.0022201538086</v>
       </c>
       <c r="H461" t="n">
         <v>547355</v>
@@ -14086,7 +14086,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G473" t="n">
-        <v>21.0666446685791</v>
+        <v>21.0666427612305</v>
       </c>
       <c r="H473" t="n">
         <v>317345</v>
@@ -14144,7 +14144,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G475" t="n">
-        <v>20.9285945892334</v>
+        <v>20.9285907745361</v>
       </c>
       <c r="H475" t="n">
         <v>884159</v>
@@ -14318,7 +14318,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G481" t="n">
-        <v>19.2719783782959</v>
+        <v>19.2719764709473</v>
       </c>
       <c r="H481" t="n">
         <v>2609341</v>
@@ -14376,7 +14376,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G483" t="n">
-        <v>19.8057746887207</v>
+        <v>19.8057765960693</v>
       </c>
       <c r="H483" t="n">
         <v>546959</v>
@@ -14405,7 +14405,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G484" t="n">
-        <v>19.7321472167969</v>
+        <v>19.7321491241455</v>
       </c>
       <c r="H484" t="n">
         <v>421554</v>
@@ -14463,7 +14463,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G486" t="n">
-        <v>20.0450649261475</v>
+        <v>20.0450668334961</v>
       </c>
       <c r="H486" t="n">
         <v>455042</v>
@@ -14521,7 +14521,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>20.4316082000732</v>
+        <v>20.4316101074219</v>
       </c>
       <c r="H488" t="n">
         <v>368098</v>
@@ -14579,7 +14579,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>20.661693572998</v>
+        <v>20.6616954803467</v>
       </c>
       <c r="H490" t="n">
         <v>354523</v>
@@ -14608,7 +14608,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G491" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838161468506</v>
       </c>
       <c r="H491" t="n">
         <v>580090</v>
@@ -14724,7 +14724,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G495" t="n">
-        <v>21.0022220611572</v>
+        <v>21.0022201538086</v>
       </c>
       <c r="H495" t="n">
         <v>401957</v>
@@ -14927,7 +14927,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G502" t="n">
-        <v>20.7721366882324</v>
+        <v>20.7721347808838</v>
       </c>
       <c r="H502" t="n">
         <v>621541</v>
@@ -15043,7 +15043,7 @@
         <v>21.75</v>
       </c>
       <c r="G506" t="n">
-        <v>20.0174541473389</v>
+        <v>20.0174522399902</v>
       </c>
       <c r="H506" t="n">
         <v>379082</v>
@@ -15130,7 +15130,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>20.2291355133057</v>
+        <v>20.229133605957</v>
       </c>
       <c r="H509" t="n">
         <v>191733</v>
@@ -15362,7 +15362,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G517" t="n">
-        <v>20.2659473419189</v>
+        <v>20.2659492492676</v>
       </c>
       <c r="H517" t="n">
         <v>876136</v>
@@ -15478,7 +15478,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>20.4316082000732</v>
+        <v>20.4316101074219</v>
       </c>
       <c r="H521" t="n">
         <v>164255</v>
@@ -15565,7 +15565,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G524" t="n">
-        <v>20.1739120483398</v>
+        <v>20.1739139556885</v>
       </c>
       <c r="H524" t="n">
         <v>499386</v>
@@ -15652,7 +15652,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G527" t="n">
-        <v>21.2967300415039</v>
+        <v>21.2967319488525</v>
       </c>
       <c r="H527" t="n">
         <v>604201</v>
@@ -15739,7 +15739,7 @@
         <v>23.2199993133545</v>
       </c>
       <c r="G530" t="n">
-        <v>21.3703575134277</v>
+        <v>21.3703556060791</v>
       </c>
       <c r="H530" t="n">
         <v>398389</v>
@@ -15855,7 +15855,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G534" t="n">
-        <v>21.3243427276611</v>
+        <v>21.3243408203125</v>
       </c>
       <c r="H534" t="n">
         <v>2061434</v>
@@ -15884,7 +15884,7 @@
         <v>22.7299995422363</v>
       </c>
       <c r="G535" t="n">
-        <v>20.9193897247314</v>
+        <v>20.9193916320801</v>
       </c>
       <c r="H535" t="n">
         <v>452147</v>
@@ -15913,7 +15913,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G536" t="n">
-        <v>20.5052375793457</v>
+        <v>20.5052356719971</v>
       </c>
       <c r="H536" t="n">
         <v>400016</v>
@@ -16029,7 +16029,7 @@
         <v>21.4300003051758</v>
       </c>
       <c r="G540" t="n">
-        <v>19.7229461669922</v>
+        <v>19.7229442596436</v>
       </c>
       <c r="H540" t="n">
         <v>544614</v>
@@ -16145,7 +16145,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G544" t="n">
-        <v>20.5604572296143</v>
+        <v>20.5604553222656</v>
       </c>
       <c r="H544" t="n">
         <v>590508</v>
@@ -16261,7 +16261,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G548" t="n">
-        <v>20.983814239502</v>
+        <v>20.9838161468506</v>
       </c>
       <c r="H548" t="n">
         <v>361715</v>
@@ -16319,7 +16319,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G550" t="n">
-        <v>20.9285945892334</v>
+        <v>20.9285907745361</v>
       </c>
       <c r="H550" t="n">
         <v>308603</v>
@@ -16406,7 +16406,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G553" t="n">
-        <v>21.2967300415039</v>
+        <v>21.2967319488525</v>
       </c>
       <c r="H553" t="n">
         <v>2496511</v>
@@ -16464,7 +16464,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G555" t="n">
-        <v>20.6248836517334</v>
+        <v>20.6248798370361</v>
       </c>
       <c r="H555" t="n">
         <v>551415</v>
@@ -16493,7 +16493,7 @@
         <v>22.0300006866455</v>
       </c>
       <c r="G556" t="n">
-        <v>20.2751522064209</v>
+        <v>20.2751502990723</v>
       </c>
       <c r="H556" t="n">
         <v>754774</v>
@@ -16551,7 +16551,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>20.1094875335693</v>
+        <v>20.109489440918</v>
       </c>
       <c r="H558" t="n">
         <v>598799</v>
@@ -16609,7 +16609,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>19.6493186950684</v>
+        <v>19.6493167877197</v>
       </c>
       <c r="H560" t="n">
         <v>1050485</v>
@@ -16667,7 +16667,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>20.1094875335693</v>
+        <v>20.109489440918</v>
       </c>
       <c r="H562" t="n">
         <v>392838</v>
@@ -16725,7 +16725,7 @@
         <v>21.8700008392334</v>
       </c>
       <c r="G564" t="n">
-        <v>20.1278972625732</v>
+        <v>20.1278953552246</v>
       </c>
       <c r="H564" t="n">
         <v>432785</v>
@@ -17073,7 +17073,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>20.6156749725342</v>
+        <v>20.6156787872314</v>
       </c>
       <c r="H576" t="n">
         <v>263654</v>
@@ -17247,7 +17247,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G582" t="n">
-        <v>20.9746131896973</v>
+        <v>20.9746112823486</v>
       </c>
       <c r="H582" t="n">
         <v>623938</v>
@@ -17276,7 +17276,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G583" t="n">
-        <v>21.2046985626221</v>
+        <v>21.2046966552734</v>
       </c>
       <c r="H583" t="n">
         <v>434729</v>
@@ -17305,7 +17305,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>21.2783260345459</v>
+        <v>21.2783241271973</v>
       </c>
       <c r="H584" t="n">
         <v>190641</v>
@@ -17334,7 +17334,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G585" t="n">
-        <v>21.3151359558105</v>
+        <v>21.3151378631592</v>
       </c>
       <c r="H585" t="n">
         <v>732771</v>
@@ -17479,7 +17479,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G590" t="n">
-        <v>22.6496334075928</v>
+        <v>22.6496353149414</v>
       </c>
       <c r="H590" t="n">
         <v>1399669</v>
@@ -17537,7 +17537,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G592" t="n">
-        <v>22.4195499420166</v>
+        <v>22.419548034668</v>
       </c>
       <c r="H592" t="n">
         <v>493451</v>
@@ -17566,7 +17566,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G593" t="n">
-        <v>22.2078685760498</v>
+        <v>22.2078704833984</v>
       </c>
       <c r="H593" t="n">
         <v>551639</v>
@@ -17682,7 +17682,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>22.6404323577881</v>
+        <v>22.6404342651367</v>
       </c>
       <c r="H597" t="n">
         <v>903419</v>
@@ -17856,7 +17856,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G603" t="n">
-        <v>22.8337020874023</v>
+        <v>22.833703994751</v>
       </c>
       <c r="H603" t="n">
         <v>232191</v>
@@ -17914,7 +17914,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G605" t="n">
-        <v>22.9073314666748</v>
+        <v>22.9073295593262</v>
       </c>
       <c r="H605" t="n">
         <v>415746</v>
@@ -18030,7 +18030,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G609" t="n">
-        <v>23.3090705871582</v>
+        <v>23.3090686798096</v>
       </c>
       <c r="H609" t="n">
         <v>451695</v>
@@ -18059,7 +18059,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>23.4118747711182</v>
+        <v>23.4118728637695</v>
       </c>
       <c r="H610" t="n">
         <v>373820</v>
@@ -18175,7 +18175,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G614" t="n">
-        <v>22.355770111084</v>
+        <v>22.3557720184326</v>
       </c>
       <c r="H614" t="n">
         <v>700947</v>
@@ -18204,7 +18204,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>22.6174621582031</v>
+        <v>22.6174602508545</v>
       </c>
       <c r="H615" t="n">
         <v>501155</v>
@@ -18523,7 +18523,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G626" t="n">
-        <v>23.3838386535645</v>
+        <v>23.3838367462158</v>
       </c>
       <c r="H626" t="n">
         <v>354528</v>
@@ -18610,7 +18610,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G629" t="n">
-        <v>22.9258823394775</v>
+        <v>22.9258804321289</v>
       </c>
       <c r="H629" t="n">
         <v>273653</v>
@@ -18639,7 +18639,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G630" t="n">
-        <v>20.991247177124</v>
+        <v>20.9912452697754</v>
       </c>
       <c r="H630" t="n">
         <v>3551454</v>
@@ -18726,7 +18726,7 @@
         <v>21.3899993896484</v>
       </c>
       <c r="G633" t="n">
-        <v>19.9912185668945</v>
+        <v>19.9912166595459</v>
       </c>
       <c r="H633" t="n">
         <v>537735</v>
@@ -18784,7 +18784,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G635" t="n">
-        <v>19.5612983703613</v>
+        <v>19.56130027771</v>
       </c>
       <c r="H635" t="n">
         <v>788412</v>
@@ -18813,7 +18813,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G636" t="n">
-        <v>19.3089542388916</v>
+        <v>19.3089561462402</v>
       </c>
       <c r="H636" t="n">
         <v>671130</v>
@@ -18871,7 +18871,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G638" t="n">
-        <v>19.4958763122559</v>
+        <v>19.4958782196045</v>
       </c>
       <c r="H638" t="n">
         <v>703698</v>
@@ -18958,7 +18958,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G641" t="n">
-        <v>18.6266956329346</v>
+        <v>18.6266937255859</v>
       </c>
       <c r="H641" t="n">
         <v>874180</v>
@@ -18987,7 +18987,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G642" t="n">
-        <v>18.383695602417</v>
+        <v>18.3836975097656</v>
       </c>
       <c r="H642" t="n">
         <v>773362</v>
@@ -19045,7 +19045,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>18.6220207214355</v>
+        <v>18.6220188140869</v>
       </c>
       <c r="H644" t="n">
         <v>804400</v>
@@ -19103,7 +19103,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G646" t="n">
-        <v>18.383695602417</v>
+        <v>18.3836975097656</v>
       </c>
       <c r="H646" t="n">
         <v>373552</v>
@@ -19161,7 +19161,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G648" t="n">
-        <v>18.6360397338867</v>
+        <v>18.6360416412354</v>
       </c>
       <c r="H648" t="n">
         <v>360124</v>
@@ -19248,7 +19248,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G651" t="n">
-        <v>18.7201557159424</v>
+        <v>18.7201538085938</v>
       </c>
       <c r="H651" t="n">
         <v>386178</v>
@@ -19277,7 +19277,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G652" t="n">
-        <v>18.6220207214355</v>
+        <v>18.6220188140869</v>
       </c>
       <c r="H652" t="n">
         <v>445187</v>
@@ -19306,7 +19306,7 @@
         <v>19.875</v>
       </c>
       <c r="G653" t="n">
-        <v>18.5752925872803</v>
+        <v>18.5752906799316</v>
       </c>
       <c r="H653" t="n">
         <v>336549</v>
@@ -19364,7 +19364,7 @@
         <v>19.8250007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>18.5285606384277</v>
+        <v>18.5285625457764</v>
       </c>
       <c r="H655" t="n">
         <v>472136</v>
@@ -19451,7 +19451,7 @@
         <v>19.6749992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>18.388370513916</v>
+        <v>18.3883686065674</v>
       </c>
       <c r="H658" t="n">
         <v>425030</v>
@@ -19480,7 +19480,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G659" t="n">
-        <v>18.491174697876</v>
+        <v>18.4911766052246</v>
       </c>
       <c r="H659" t="n">
         <v>448603</v>
@@ -19509,7 +19509,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G660" t="n">
-        <v>18.2435073852539</v>
+        <v>18.2435054779053</v>
       </c>
       <c r="H660" t="n">
         <v>1645512</v>
@@ -19596,7 +19596,7 @@
         <v>19.375</v>
       </c>
       <c r="G663" t="n">
-        <v>18.1079864501953</v>
+        <v>18.1079883575439</v>
       </c>
       <c r="H663" t="n">
         <v>697033</v>
@@ -19712,7 +19712,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G667" t="n">
-        <v>18.7295017242432</v>
+        <v>18.7294998168945</v>
       </c>
       <c r="H667" t="n">
         <v>363161</v>
@@ -19770,7 +19770,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G669" t="n">
-        <v>18.7201557159424</v>
+        <v>18.7201538085938</v>
       </c>
       <c r="H669" t="n">
         <v>247847</v>
@@ -19799,7 +19799,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G670" t="n">
-        <v>18.491174697876</v>
+        <v>18.4911766052246</v>
       </c>
       <c r="H670" t="n">
         <v>378568</v>
@@ -19828,7 +19828,7 @@
         <v>19.5550003051758</v>
       </c>
       <c r="G671" t="n">
-        <v>18.276216506958</v>
+        <v>18.2762184143066</v>
       </c>
       <c r="H671" t="n">
         <v>210250</v>
@@ -19857,7 +19857,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G672" t="n">
-        <v>18.2528514862061</v>
+        <v>18.2528533935547</v>
       </c>
       <c r="H672" t="n">
         <v>202041</v>
@@ -19944,7 +19944,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G675" t="n">
-        <v>19.1407260894775</v>
+        <v>19.1407279968262</v>
       </c>
       <c r="H675" t="n">
         <v>1646978</v>
@@ -20060,7 +20060,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G679" t="n">
-        <v>19.4304523468018</v>
+        <v>19.4304542541504</v>
       </c>
       <c r="H679" t="n">
         <v>207201</v>
@@ -20147,7 +20147,7 @@
         <v>20.5100002288818</v>
       </c>
       <c r="G682" t="n">
-        <v>19.1687679290771</v>
+        <v>19.1687660217285</v>
       </c>
       <c r="H682" t="n">
         <v>127650</v>
@@ -20176,7 +20176,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>19.1126899719238</v>
+        <v>19.1126880645752</v>
       </c>
       <c r="H683" t="n">
         <v>405539</v>
@@ -20321,7 +20321,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G688" t="n">
-        <v>18.8416538238525</v>
+        <v>18.8416519165039</v>
       </c>
       <c r="H688" t="n">
         <v>335800</v>
@@ -20350,7 +20350,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G689" t="n">
-        <v>19.6080303192139</v>
+        <v>19.6080284118652</v>
       </c>
       <c r="H689" t="n">
         <v>1702447</v>
@@ -20379,7 +20379,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>19.2528800964355</v>
+        <v>19.2528820037842</v>
       </c>
       <c r="H690" t="n">
         <v>521428</v>
@@ -20408,7 +20408,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G691" t="n">
-        <v>19.5239143371582</v>
+        <v>19.5239162445068</v>
       </c>
       <c r="H691" t="n">
         <v>181397</v>
@@ -20437,7 +20437,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G692" t="n">
-        <v>19.4211101531982</v>
+        <v>19.4211082458496</v>
       </c>
       <c r="H692" t="n">
         <v>207950</v>
@@ -20466,7 +20466,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>19.8136405944824</v>
+        <v>19.8136425018311</v>
       </c>
       <c r="H693" t="n">
         <v>277253</v>
@@ -20524,7 +20524,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G695" t="n">
-        <v>19.748218536377</v>
+        <v>19.7482204437256</v>
       </c>
       <c r="H695" t="n">
         <v>450623</v>
@@ -20582,7 +20582,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G697" t="n">
-        <v>19.6080303192139</v>
+        <v>19.6080284118652</v>
       </c>
       <c r="H697" t="n">
         <v>362558</v>
@@ -20756,7 +20756,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G703" t="n">
-        <v>18.8977298736572</v>
+        <v>18.8977279663086</v>
       </c>
       <c r="H703" t="n">
         <v>336450</v>
@@ -20814,7 +20814,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G705" t="n">
-        <v>18.8042697906494</v>
+        <v>18.804271697998</v>
       </c>
       <c r="H705" t="n">
         <v>237961</v>
@@ -20872,7 +20872,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>18.1780834197998</v>
+        <v>18.1780853271484</v>
       </c>
       <c r="H707" t="n">
         <v>397647</v>
@@ -20930,7 +20930,7 @@
         <v>19.1049995422363</v>
       </c>
       <c r="G709" t="n">
-        <v>17.8556423187256</v>
+        <v>17.8556442260742</v>
       </c>
       <c r="H709" t="n">
         <v>1289181</v>
@@ -21017,7 +21017,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G712" t="n">
-        <v>16.9817867279053</v>
+        <v>16.9817886352539</v>
       </c>
       <c r="H712" t="n">
         <v>290212</v>
@@ -21046,7 +21046,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G713" t="n">
-        <v>18.1360263824463</v>
+        <v>18.1360244750977</v>
       </c>
       <c r="H713" t="n">
         <v>712846</v>
@@ -21133,7 +21133,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G716" t="n">
-        <v>18.2154655456543</v>
+        <v>18.2154674530029</v>
       </c>
       <c r="H716" t="n">
         <v>327778</v>
@@ -21220,7 +21220,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G719" t="n">
-        <v>19.0098838806152</v>
+        <v>19.0098819732666</v>
       </c>
       <c r="H719" t="n">
         <v>746830</v>
@@ -21249,7 +21249,7 @@
         <v>20.9699993133545</v>
       </c>
       <c r="G720" t="n">
-        <v>19.5986843109131</v>
+        <v>19.5986824035645</v>
       </c>
       <c r="H720" t="n">
         <v>628747</v>
@@ -21307,7 +21307,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G722" t="n">
-        <v>19.645414352417</v>
+        <v>19.6454124450684</v>
       </c>
       <c r="H722" t="n">
         <v>418618</v>
@@ -21626,7 +21626,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G733" t="n">
-        <v>19.701488494873</v>
+        <v>19.7014904022217</v>
       </c>
       <c r="H733" t="n">
         <v>369031</v>
@@ -21713,7 +21713,7 @@
         <v>20.75</v>
       </c>
       <c r="G736" t="n">
-        <v>19.3930721282959</v>
+        <v>19.3930702209473</v>
       </c>
       <c r="H736" t="n">
         <v>268555</v>
@@ -21800,7 +21800,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>18.7855796813965</v>
+        <v>18.7855758666992</v>
       </c>
       <c r="H739" t="n">
         <v>486148</v>
@@ -21829,7 +21829,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>18.7855796813965</v>
+        <v>18.7855758666992</v>
       </c>
       <c r="H740" t="n">
         <v>351777</v>
@@ -22032,7 +22032,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G747" t="n">
-        <v>19.701488494873</v>
+        <v>19.7014904022217</v>
       </c>
       <c r="H747" t="n">
         <v>368527</v>
@@ -22090,7 +22090,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G749" t="n">
-        <v>19.4304523468018</v>
+        <v>19.4304542541504</v>
       </c>
       <c r="H749" t="n">
         <v>241093</v>
@@ -22322,7 +22322,7 @@
         <v>17.7450008392334</v>
       </c>
       <c r="G757" t="n">
-        <v>16.5845794677734</v>
+        <v>16.5845813751221</v>
       </c>
       <c r="H757" t="n">
         <v>666545</v>
@@ -22351,7 +22351,7 @@
         <v>17.7049999237061</v>
       </c>
       <c r="G758" t="n">
-        <v>16.5471954345703</v>
+        <v>16.5471973419189</v>
       </c>
       <c r="H758" t="n">
         <v>636977</v>
@@ -22409,7 +22409,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G760" t="n">
-        <v>16.7200984954834</v>
+        <v>16.7200965881348</v>
       </c>
       <c r="H760" t="n">
         <v>542452</v>
@@ -22438,7 +22438,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>16.4957904815674</v>
+        <v>16.495792388916</v>
       </c>
       <c r="H761" t="n">
         <v>1354957</v>
@@ -22525,7 +22525,7 @@
         <v>17.6149997711182</v>
       </c>
       <c r="G764" t="n">
-        <v>16.4630813598633</v>
+        <v>16.4630794525146</v>
       </c>
       <c r="H764" t="n">
         <v>388839</v>
@@ -22612,7 +22612,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>16.4957904815674</v>
+        <v>16.495792388916</v>
       </c>
       <c r="H767" t="n">
         <v>341314</v>
@@ -22670,7 +22670,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G769" t="n">
-        <v>16.8415985107422</v>
+        <v>16.8415966033936</v>
       </c>
       <c r="H769" t="n">
         <v>570466</v>
@@ -22728,7 +22728,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>16.5331764221191</v>
+        <v>16.5331783294678</v>
       </c>
       <c r="H771" t="n">
         <v>921657</v>
@@ -22757,7 +22757,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>16.4957904815674</v>
+        <v>16.495792388916</v>
       </c>
       <c r="H772" t="n">
         <v>357653</v>
@@ -22844,7 +22844,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G775" t="n">
-        <v>16.5985984802246</v>
+        <v>16.5986003875732</v>
       </c>
       <c r="H775" t="n">
         <v>272556</v>
@@ -22931,7 +22931,7 @@
         <v>17.2549991607666</v>
       </c>
       <c r="G778" t="n">
-        <v>16.1266212463379</v>
+        <v>16.1266231536865</v>
       </c>
       <c r="H778" t="n">
         <v>546458</v>
@@ -22989,7 +22989,7 @@
         <v>17.2549991607666</v>
       </c>
       <c r="G780" t="n">
-        <v>16.1266212463379</v>
+        <v>16.1266231536865</v>
       </c>
       <c r="H780" t="n">
         <v>354071</v>
@@ -23018,7 +23018,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>16.4490642547607</v>
+        <v>16.4490623474121</v>
       </c>
       <c r="H781" t="n">
         <v>395429</v>
@@ -23105,7 +23105,7 @@
         <v>17.6149997711182</v>
       </c>
       <c r="G784" t="n">
-        <v>16.4630813598633</v>
+        <v>16.4630794525146</v>
       </c>
       <c r="H784" t="n">
         <v>1652103</v>
@@ -23192,7 +23192,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G787" t="n">
-        <v>16.4957904815674</v>
+        <v>16.495792388916</v>
       </c>
       <c r="H787" t="n">
         <v>375724</v>
@@ -23221,7 +23221,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G788" t="n">
-        <v>16.5238304138184</v>
+        <v>16.5238285064697</v>
       </c>
       <c r="H788" t="n">
         <v>412006</v>
@@ -23424,7 +23424,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>17.1967449188232</v>
+        <v>17.1967468261719</v>
       </c>
       <c r="H795" t="n">
         <v>665839</v>
@@ -23511,7 +23511,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G798" t="n">
-        <v>17.5518970489502</v>
+        <v>17.5518989562988</v>
       </c>
       <c r="H798" t="n">
         <v>379392</v>
@@ -23540,7 +23540,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G799" t="n">
-        <v>17.4163780212402</v>
+        <v>17.4163799285889</v>
       </c>
       <c r="H799" t="n">
         <v>175003</v>
@@ -23569,7 +23569,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G800" t="n">
-        <v>17.1079616546631</v>
+        <v>17.1079597473145</v>
       </c>
       <c r="H800" t="n">
         <v>417559</v>
@@ -23598,7 +23598,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G801" t="n">
-        <v>17.1313228607178</v>
+        <v>17.1313247680664</v>
       </c>
       <c r="H801" t="n">
         <v>192081</v>
@@ -23656,7 +23656,7 @@
         <v>18.7150001525879</v>
       </c>
       <c r="G803" t="n">
-        <v>17.4911499023438</v>
+        <v>17.4911479949951</v>
       </c>
       <c r="H803" t="n">
         <v>440741</v>
@@ -23685,7 +23685,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G804" t="n">
-        <v>17.4397449493408</v>
+        <v>17.4397430419922</v>
       </c>
       <c r="H804" t="n">
         <v>202890</v>
@@ -23714,7 +23714,7 @@
         <v>18.6749992370605</v>
       </c>
       <c r="G805" t="n">
-        <v>17.4537620544434</v>
+        <v>17.453763961792</v>
       </c>
       <c r="H805" t="n">
         <v>268791</v>
@@ -23743,7 +23743,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G806" t="n">
-        <v>17.729471206665</v>
+        <v>17.7294731140137</v>
       </c>
       <c r="H806" t="n">
         <v>991047</v>
@@ -23772,7 +23772,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G807" t="n">
-        <v>17.6547050476074</v>
+        <v>17.6547031402588</v>
       </c>
       <c r="H807" t="n">
         <v>467189</v>
@@ -23830,7 +23830,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G809" t="n">
-        <v>17.4163780212402</v>
+        <v>17.4163799285889</v>
       </c>
       <c r="H809" t="n">
         <v>291517</v>
@@ -23888,7 +23888,7 @@
         <v>18.0249996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>16.8462696075439</v>
+        <v>16.8462677001953</v>
       </c>
       <c r="H811" t="n">
         <v>347878</v>
@@ -23946,7 +23946,7 @@
         <v>18</v>
       </c>
       <c r="G813" t="n">
-        <v>16.822904586792</v>
+        <v>16.8229064941406</v>
       </c>
       <c r="H813" t="n">
         <v>556290</v>
@@ -24004,7 +24004,7 @@
         <v>19.1650009155273</v>
       </c>
       <c r="G815" t="n">
-        <v>17.9117183685303</v>
+        <v>17.9117202758789</v>
       </c>
       <c r="H815" t="n">
         <v>871578</v>
@@ -24062,7 +24062,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G817" t="n">
-        <v>17.6593761444092</v>
+        <v>17.6593780517578</v>
       </c>
       <c r="H817" t="n">
         <v>1770207</v>
@@ -24207,7 +24207,7 @@
         <v>18.6149997711182</v>
       </c>
       <c r="G822" t="n">
-        <v>17.3976879119873</v>
+        <v>17.3976898193359</v>
       </c>
       <c r="H822" t="n">
         <v>242884</v>
@@ -24381,7 +24381,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G828" t="n">
-        <v>18.2154655456543</v>
+        <v>18.2154674530029</v>
       </c>
       <c r="H828" t="n">
         <v>396423</v>
@@ -24410,7 +24410,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G829" t="n">
-        <v>18.0565814971924</v>
+        <v>18.056583404541</v>
       </c>
       <c r="H829" t="n">
         <v>523051</v>
@@ -24613,7 +24613,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>18.5051918029785</v>
+        <v>18.5051937103271</v>
       </c>
       <c r="H836" t="n">
         <v>706748</v>
@@ -24642,7 +24642,7 @@
         <v>19.625</v>
       </c>
       <c r="G837" t="n">
-        <v>18.3416385650635</v>
+        <v>18.3416404724121</v>
       </c>
       <c r="H837" t="n">
         <v>166982</v>
@@ -24671,7 +24671,7 @@
         <v>19.5550003051758</v>
       </c>
       <c r="G838" t="n">
-        <v>18.276216506958</v>
+        <v>18.2762184143066</v>
       </c>
       <c r="H838" t="n">
         <v>188703</v>
@@ -24729,7 +24729,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G840" t="n">
-        <v>18.439769744873</v>
+        <v>18.4397716522217</v>
       </c>
       <c r="H840" t="n">
         <v>677306</v>
@@ -24758,7 +24758,7 @@
         <v>19.8250007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>18.5285606384277</v>
+        <v>18.5285625457764</v>
       </c>
       <c r="H841" t="n">
         <v>479730</v>
@@ -24816,7 +24816,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>18.5051918029785</v>
+        <v>18.5051937103271</v>
       </c>
       <c r="H843" t="n">
         <v>242255</v>
@@ -24990,7 +24990,7 @@
         <v>19.2849998474121</v>
       </c>
       <c r="G849" t="n">
-        <v>18.0238723754883</v>
+        <v>18.0238704681396</v>
       </c>
       <c r="H849" t="n">
         <v>481409</v>
@@ -25019,7 +25019,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G850" t="n">
-        <v>17.8603191375732</v>
+        <v>17.8603172302246</v>
       </c>
       <c r="H850" t="n">
         <v>346909</v>
@@ -25077,7 +25077,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G852" t="n">
-        <v>17.5986289978027</v>
+        <v>17.5986270904541</v>
       </c>
       <c r="H852" t="n">
         <v>400400</v>
@@ -25193,7 +25193,7 @@
         <v>21.25</v>
       </c>
       <c r="G856" t="n">
-        <v>19.8603744506836</v>
+        <v>19.860372543335</v>
       </c>
       <c r="H856" t="n">
         <v>4085499</v>
@@ -25251,7 +25251,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>19.9071025848389</v>
+        <v>19.9071044921875</v>
       </c>
       <c r="H858" t="n">
         <v>565898</v>
@@ -25425,7 +25425,7 @@
         <v>20.1299991607666</v>
       </c>
       <c r="G864" t="n">
-        <v>19.1187953948975</v>
+        <v>19.1187973022461</v>
       </c>
       <c r="H864" t="n">
         <v>286413</v>
@@ -25483,7 +25483,7 @@
         <v>19.9549999237061</v>
       </c>
       <c r="G866" t="n">
-        <v>18.9525890350342</v>
+        <v>18.9525871276855</v>
       </c>
       <c r="H866" t="n">
         <v>508519</v>
@@ -25541,7 +25541,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G868" t="n">
-        <v>17.7131443023682</v>
+        <v>17.7131423950195</v>
       </c>
       <c r="H868" t="n">
         <v>1061282</v>
@@ -25570,7 +25570,7 @@
         <v>18.6650009155273</v>
       </c>
       <c r="G869" t="n">
-        <v>17.7273902893066</v>
+        <v>17.7273921966553</v>
       </c>
       <c r="H869" t="n">
         <v>491859</v>
@@ -25599,7 +25599,7 @@
         <v>18.7749996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>17.8318634033203</v>
+        <v>17.8318614959717</v>
       </c>
       <c r="H870" t="n">
         <v>489772</v>
@@ -25657,7 +25657,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G872" t="n">
-        <v>18.6534118652344</v>
+        <v>18.6534099578857</v>
       </c>
       <c r="H872" t="n">
         <v>633892</v>
@@ -25773,7 +25773,7 @@
         <v>20.2299995422363</v>
       </c>
       <c r="G876" t="n">
-        <v>19.2137718200684</v>
+        <v>19.213773727417</v>
       </c>
       <c r="H876" t="n">
         <v>255924</v>
@@ -25802,7 +25802,7 @@
         <v>19.9850006103516</v>
       </c>
       <c r="G877" t="n">
-        <v>18.9810810089111</v>
+        <v>18.9810791015625</v>
       </c>
       <c r="H877" t="n">
         <v>573025</v>
@@ -25831,7 +25831,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G878" t="n">
-        <v>18.905101776123</v>
+        <v>18.9050998687744</v>
       </c>
       <c r="H878" t="n">
         <v>291697</v>
@@ -25860,7 +25860,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G879" t="n">
-        <v>19.0333194732666</v>
+        <v>19.033317565918</v>
       </c>
       <c r="H879" t="n">
         <v>294797</v>
@@ -25889,7 +25889,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G880" t="n">
-        <v>19.6601638793945</v>
+        <v>19.6601657867432</v>
       </c>
       <c r="H880" t="n">
         <v>602089</v>
@@ -26092,7 +26092,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G887" t="n">
-        <v>19.7456436157227</v>
+        <v>19.745641708374</v>
       </c>
       <c r="H887" t="n">
         <v>232823</v>
@@ -26208,7 +26208,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>20.4674644470215</v>
+        <v>20.4674663543701</v>
       </c>
       <c r="H891" t="n">
         <v>463182</v>
@@ -26237,7 +26237,7 @@
         <v>21.5699996948242</v>
       </c>
       <c r="G892" t="n">
-        <v>20.4864597320557</v>
+        <v>20.4864616394043</v>
       </c>
       <c r="H892" t="n">
         <v>439206</v>
@@ -26527,7 +26527,7 @@
         <v>21.0900001525879</v>
       </c>
       <c r="G902" t="n">
-        <v>20.0305728912354</v>
+        <v>20.030574798584</v>
       </c>
       <c r="H902" t="n">
         <v>771637</v>
@@ -26672,7 +26672,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G907" t="n">
-        <v>19.96409034729</v>
+        <v>19.9640884399414</v>
       </c>
       <c r="H907" t="n">
         <v>595451</v>
@@ -26701,7 +26701,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G908" t="n">
-        <v>20.0020790100098</v>
+        <v>20.0020809173584</v>
       </c>
       <c r="H908" t="n">
         <v>361424</v>
@@ -26904,7 +26904,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G915" t="n">
-        <v>17.2762508392334</v>
+        <v>17.2762489318848</v>
       </c>
       <c r="H915" t="n">
         <v>705843</v>
@@ -26933,7 +26933,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G916" t="n">
-        <v>17.2667541503906</v>
+        <v>17.266752243042</v>
       </c>
       <c r="H916" t="n">
         <v>428507</v>
@@ -27049,7 +27049,7 @@
         <v>17.9150009155273</v>
       </c>
       <c r="G920" t="n">
-        <v>17.0150661468506</v>
+        <v>17.0150680541992</v>
       </c>
       <c r="H920" t="n">
         <v>386059</v>
@@ -27078,7 +27078,7 @@
         <v>17.4750003814697</v>
       </c>
       <c r="G921" t="n">
-        <v>16.5971660614014</v>
+        <v>16.59716796875</v>
       </c>
       <c r="H921" t="n">
         <v>361687</v>
@@ -27107,7 +27107,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G922" t="n">
-        <v>16.2837467193604</v>
+        <v>16.2837448120117</v>
       </c>
       <c r="H922" t="n">
         <v>717691</v>
@@ -27223,7 +27223,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G926" t="n">
-        <v>16.9153385162354</v>
+        <v>16.915340423584</v>
       </c>
       <c r="H926" t="n">
         <v>202553</v>
@@ -27281,7 +27281,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G928" t="n">
-        <v>16.7348861694336</v>
+        <v>16.734884262085</v>
       </c>
       <c r="H928" t="n">
         <v>393838</v>
@@ -27310,7 +27310,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G929" t="n">
-        <v>16.9485816955566</v>
+        <v>16.948579788208</v>
       </c>
       <c r="H929" t="n">
         <v>294893</v>
@@ -27339,7 +27339,7 @@
         <v>17.6350002288818</v>
       </c>
       <c r="G930" t="n">
-        <v>16.7491321563721</v>
+        <v>16.7491302490234</v>
       </c>
       <c r="H930" t="n">
         <v>638773</v>
@@ -27426,7 +27426,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G933" t="n">
-        <v>16.6683979034424</v>
+        <v>16.668399810791</v>
       </c>
       <c r="H933" t="n">
         <v>336467</v>
@@ -27513,7 +27513,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G936" t="n">
-        <v>17.4329605102539</v>
+        <v>17.4329624176025</v>
       </c>
       <c r="H936" t="n">
         <v>832012</v>
@@ -27658,7 +27658,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>17.2857494354248</v>
+        <v>17.2857475280762</v>
       </c>
       <c r="H941" t="n">
         <v>1106208</v>
@@ -27948,7 +27948,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G951" t="n">
-        <v>16.34547996521</v>
+        <v>16.3454780578613</v>
       </c>
       <c r="H951" t="n">
         <v>647943</v>
@@ -28006,7 +28006,7 @@
         <v>16.9549999237061</v>
       </c>
       <c r="G953" t="n">
-        <v>16.1032886505127</v>
+        <v>16.1032905578613</v>
       </c>
       <c r="H953" t="n">
         <v>508993</v>
@@ -28035,7 +28035,7 @@
         <v>16.8649997711182</v>
       </c>
       <c r="G954" t="n">
-        <v>16.0178108215332</v>
+        <v>16.0178089141846</v>
       </c>
       <c r="H954" t="n">
         <v>543115</v>
@@ -28064,7 +28064,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>15.4811906814575</v>
+        <v>15.4811916351318</v>
       </c>
       <c r="H955" t="n">
         <v>881171</v>
@@ -28093,7 +28093,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G956" t="n">
-        <v>15.538179397583</v>
+        <v>15.5381784439087</v>
       </c>
       <c r="H956" t="n">
         <v>521455</v>
@@ -28122,7 +28122,7 @@
         <v>16.3850002288818</v>
       </c>
       <c r="G957" t="n">
-        <v>15.5619230270386</v>
+        <v>15.5619220733643</v>
       </c>
       <c r="H957" t="n">
         <v>387332</v>
@@ -28151,7 +28151,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>15.4811906814575</v>
+        <v>15.4811916351318</v>
       </c>
       <c r="H958" t="n">
         <v>462839</v>
@@ -28383,7 +28383,7 @@
         <v>16.1350002288818</v>
       </c>
       <c r="G966" t="n">
-        <v>15.324481010437</v>
+        <v>15.3244800567627</v>
       </c>
       <c r="H966" t="n">
         <v>556418</v>
@@ -28441,7 +28441,7 @@
         <v>16.0650005340576</v>
       </c>
       <c r="G968" t="n">
-        <v>15.2579965591431</v>
+        <v>15.2579975128174</v>
       </c>
       <c r="H968" t="n">
         <v>495274</v>
@@ -28528,7 +28528,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G971" t="n">
-        <v>15.0348014831543</v>
+        <v>15.0348024368286</v>
       </c>
       <c r="H971" t="n">
         <v>371138</v>
@@ -28557,7 +28557,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G972" t="n">
-        <v>15.3197317123413</v>
+        <v>15.319730758667</v>
       </c>
       <c r="H972" t="n">
         <v>1080701</v>
@@ -28586,7 +28586,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G973" t="n">
-        <v>15.960823059082</v>
+        <v>15.9608240127563</v>
       </c>
       <c r="H973" t="n">
         <v>1840392</v>
@@ -28644,7 +28644,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G975" t="n">
-        <v>15.8800916671753</v>
+        <v>15.8800926208496</v>
       </c>
       <c r="H975" t="n">
         <v>437079</v>
@@ -28731,7 +28731,7 @@
         <v>16.9950008392334</v>
       </c>
       <c r="G978" t="n">
-        <v>16.1412792205811</v>
+        <v>16.1412811279297</v>
       </c>
       <c r="H978" t="n">
         <v>604860</v>
@@ -28789,7 +28789,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G980" t="n">
-        <v>16.4024658203125</v>
+        <v>16.4024639129639</v>
       </c>
       <c r="H980" t="n">
         <v>649759</v>
@@ -28818,7 +28818,7 @@
         <v>17.4549999237061</v>
       </c>
       <c r="G981" t="n">
-        <v>16.5781707763672</v>
+        <v>16.5781726837158</v>
       </c>
       <c r="H981" t="n">
         <v>834030</v>
@@ -28934,7 +28934,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G985" t="n">
-        <v>17.2762508392334</v>
+        <v>17.2762489318848</v>
       </c>
       <c r="H985" t="n">
         <v>2378807</v>
@@ -29137,7 +29137,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G992" t="n">
-        <v>16.4024658203125</v>
+        <v>16.4024639129639</v>
       </c>
       <c r="H992" t="n">
         <v>280506</v>
@@ -29311,7 +29311,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G998" t="n">
-        <v>16.6873950958252</v>
+        <v>16.6873970031738</v>
       </c>
       <c r="H998" t="n">
         <v>609530</v>
@@ -29369,7 +29369,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1000" t="n">
-        <v>16.7348861694336</v>
+        <v>16.734884262085</v>
       </c>
       <c r="H1000" t="n">
         <v>290261</v>
@@ -29543,7 +29543,7 @@
         <v>18.2549991607666</v>
       </c>
       <c r="G1006" t="n">
-        <v>17.3379859924316</v>
+        <v>17.337984085083</v>
       </c>
       <c r="H1006" t="n">
         <v>449534</v>
@@ -29572,7 +29572,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G1007" t="n">
-        <v>17.409215927124</v>
+        <v>17.4092178344727</v>
       </c>
       <c r="H1007" t="n">
         <v>470462</v>
@@ -29630,7 +29630,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1009" t="n">
-        <v>17.5421829223633</v>
+        <v>17.5421848297119</v>
       </c>
       <c r="H1009" t="n">
         <v>335089</v>
@@ -29659,7 +29659,7 @@
         <v>18.4050006866455</v>
       </c>
       <c r="G1010" t="n">
-        <v>17.4804496765137</v>
+        <v>17.4804515838623</v>
       </c>
       <c r="H1010" t="n">
         <v>357823</v>
@@ -29717,7 +29717,7 @@
         <v>19.0750007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>18.1167945861816</v>
+        <v>18.1167964935303</v>
       </c>
       <c r="H1012" t="n">
         <v>838667</v>
@@ -29949,7 +29949,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1020" t="n">
-        <v>17.9885749816895</v>
+        <v>17.9885768890381</v>
       </c>
       <c r="H1020" t="n">
         <v>339183</v>
@@ -30123,7 +30123,7 @@
         <v>18.2549991607666</v>
       </c>
       <c r="G1026" t="n">
-        <v>17.3379859924316</v>
+        <v>17.337984085083</v>
       </c>
       <c r="H1026" t="n">
         <v>671311</v>
@@ -30181,7 +30181,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.2287616729736</v>
+        <v>17.228759765625</v>
       </c>
       <c r="H1028" t="n">
         <v>252655</v>
@@ -30210,7 +30210,7 @@
         <v>18</v>
       </c>
       <c r="G1029" t="n">
-        <v>17.0957946777344</v>
+        <v>17.095796585083</v>
       </c>
       <c r="H1029" t="n">
         <v>1142937</v>
@@ -30384,7 +30384,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1035" t="n">
-        <v>16.2979927062988</v>
+        <v>16.2979907989502</v>
       </c>
       <c r="H1035" t="n">
         <v>782661</v>
@@ -30442,7 +30442,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1037" t="n">
-        <v>15.8468503952026</v>
+        <v>15.8468494415283</v>
       </c>
       <c r="H1037" t="n">
         <v>727617</v>
@@ -30471,7 +30471,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1038" t="n">
-        <v>15.8800916671753</v>
+        <v>15.8800926208496</v>
       </c>
       <c r="H1038" t="n">
         <v>489487</v>
@@ -30616,7 +30616,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>15.7186326980591</v>
+        <v>15.7186317443848</v>
       </c>
       <c r="H1043" t="n">
         <v>350977</v>
@@ -30645,7 +30645,7 @@
         <v>16.1550006866455</v>
       </c>
       <c r="G1044" t="n">
-        <v>15.3434772491455</v>
+        <v>15.3434762954712</v>
       </c>
       <c r="H1044" t="n">
         <v>964969</v>
@@ -30674,7 +30674,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1045" t="n">
-        <v>15.9845676422119</v>
+        <v>15.9845685958862</v>
       </c>
       <c r="H1045" t="n">
         <v>961466</v>
@@ -30703,7 +30703,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.747127532959</v>
+        <v>15.7471265792847</v>
       </c>
       <c r="H1046" t="n">
         <v>537095</v>
@@ -30732,7 +30732,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1047" t="n">
-        <v>15.604660987854</v>
+        <v>15.6046619415283</v>
       </c>
       <c r="H1047" t="n">
         <v>418169</v>
@@ -30790,7 +30790,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1049" t="n">
-        <v>15.7043857574463</v>
+        <v>15.7043867111206</v>
       </c>
       <c r="H1049" t="n">
         <v>541345</v>
@@ -30819,7 +30819,7 @@
         <v>16.7250003814697</v>
       </c>
       <c r="G1050" t="n">
-        <v>15.8848428726196</v>
+        <v>15.8848438262939</v>
       </c>
       <c r="H1050" t="n">
         <v>924015</v>
@@ -30848,7 +30848,7 @@
         <v>16.3649997711182</v>
       </c>
       <c r="G1051" t="n">
-        <v>15.5429267883301</v>
+        <v>15.5429258346558</v>
       </c>
       <c r="H1051" t="n">
         <v>743062</v>
@@ -31022,7 +31022,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G1057" t="n">
-        <v>13.5721616744995</v>
+        <v>13.5721607208252</v>
       </c>
       <c r="H1057" t="n">
         <v>1192660</v>
@@ -31254,7 +31254,7 @@
         <v>11.3549995422363</v>
       </c>
       <c r="G1065" t="n">
-        <v>10.7845964431763</v>
+        <v>10.7845973968506</v>
       </c>
       <c r="H1065" t="n">
         <v>1903661</v>
@@ -31312,7 +31312,7 @@
         <v>10.164999961853</v>
       </c>
       <c r="G1067" t="n">
-        <v>9.65437507629395</v>
+        <v>9.65437412261963</v>
       </c>
       <c r="H1067" t="n">
         <v>1497885</v>
@@ -31515,7 +31515,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1074" t="n">
-        <v>13.0877799987793</v>
+        <v>13.0877809524536</v>
       </c>
       <c r="H1074" t="n">
         <v>1054229</v>
@@ -31573,7 +31573,7 @@
         <v>13.6549997329712</v>
       </c>
       <c r="G1076" t="n">
-        <v>12.9690599441528</v>
+        <v>12.9690589904785</v>
       </c>
       <c r="H1076" t="n">
         <v>932291</v>
@@ -31689,7 +31689,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1080" t="n">
-        <v>11.2072439193726</v>
+        <v>11.2072429656982</v>
       </c>
       <c r="H1080" t="n">
         <v>455495</v>
@@ -31747,7 +31747,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1082" t="n">
-        <v>11.1882476806641</v>
+        <v>11.1882467269897</v>
       </c>
       <c r="H1082" t="n">
         <v>446851</v>
@@ -31776,7 +31776,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1083" t="n">
-        <v>11.568154335022</v>
+        <v>11.5681552886963</v>
       </c>
       <c r="H1083" t="n">
         <v>348740</v>
@@ -31834,7 +31834,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1085" t="n">
-        <v>11.6251411437988</v>
+        <v>11.6251401901245</v>
       </c>
       <c r="H1085" t="n">
         <v>279217</v>
@@ -32269,7 +32269,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1100" t="n">
-        <v>10.3049659729004</v>
+        <v>10.3049650192261</v>
       </c>
       <c r="H1100" t="n">
         <v>318771</v>
@@ -32356,7 +32356,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G1103" t="n">
-        <v>10.3429565429688</v>
+        <v>10.3429574966431</v>
       </c>
       <c r="H1103" t="n">
         <v>387905</v>
@@ -32675,7 +32675,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G1114" t="n">
-        <v>9.64962673187256</v>
+        <v>9.64962577819824</v>
       </c>
       <c r="H1114" t="n">
         <v>646937</v>
@@ -32704,7 +32704,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1115" t="n">
-        <v>9.78259372711182</v>
+        <v>9.78259468078613</v>
       </c>
       <c r="H1115" t="n">
         <v>398851</v>
@@ -32791,7 +32791,7 @@
         <v>13</v>
       </c>
       <c r="G1118" t="n">
-        <v>12.346962928772</v>
+        <v>12.3469638824463</v>
       </c>
       <c r="H1118" t="n">
         <v>3283790</v>
@@ -33139,7 +33139,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1130" t="n">
-        <v>12.0620336532593</v>
+        <v>12.062032699585</v>
       </c>
       <c r="H1130" t="n">
         <v>882931</v>
@@ -33168,7 +33168,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1131" t="n">
-        <v>12.1190195083618</v>
+        <v>12.1190185546875</v>
       </c>
       <c r="H1131" t="n">
         <v>1075221</v>
@@ -33226,7 +33226,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1133" t="n">
-        <v>12.3089723587036</v>
+        <v>12.3089714050293</v>
       </c>
       <c r="H1133" t="n">
         <v>1027799</v>
@@ -33371,7 +33371,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1138" t="n">
-        <v>11.8055953979492</v>
+        <v>11.8055963516235</v>
       </c>
       <c r="H1138" t="n">
         <v>819399</v>
@@ -33487,7 +33487,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G1142" t="n">
-        <v>11.5206661224365</v>
+        <v>11.5206670761108</v>
       </c>
       <c r="H1142" t="n">
         <v>546985</v>
@@ -33574,7 +33574,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1145" t="n">
-        <v>11.5871486663818</v>
+        <v>11.5871496200562</v>
       </c>
       <c r="H1145" t="n">
         <v>444536</v>
@@ -33632,7 +33632,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1147" t="n">
-        <v>11.3402099609375</v>
+        <v>11.3402109146118</v>
       </c>
       <c r="H1147" t="n">
         <v>442064</v>
@@ -33690,7 +33690,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.9887971878052</v>
+        <v>10.9887962341309</v>
       </c>
       <c r="H1149" t="n">
         <v>424868</v>
@@ -33719,7 +33719,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G1150" t="n">
-        <v>11.1787519454956</v>
+        <v>11.1787509918213</v>
       </c>
       <c r="H1150" t="n">
         <v>464530</v>
@@ -33748,7 +33748,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1151" t="n">
-        <v>10.9887971878052</v>
+        <v>10.9887962341309</v>
       </c>
       <c r="H1151" t="n">
         <v>535403</v>
@@ -33777,7 +33777,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1152" t="n">
-        <v>11.1882476806641</v>
+        <v>11.1882467269897</v>
       </c>
       <c r="H1152" t="n">
         <v>476563</v>
@@ -34067,7 +34067,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G1162" t="n">
-        <v>11.0552806854248</v>
+        <v>11.0552816390991</v>
       </c>
       <c r="H1162" t="n">
         <v>584717</v>
@@ -34096,7 +34096,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1163" t="n">
-        <v>11.2167415618896</v>
+        <v>11.2167406082153</v>
       </c>
       <c r="H1163" t="n">
         <v>779097</v>
@@ -34357,7 +34357,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1172" t="n">
-        <v>11.6251411437988</v>
+        <v>11.6251401901245</v>
       </c>
       <c r="H1172" t="n">
         <v>966980</v>
@@ -34386,7 +34386,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1173" t="n">
-        <v>11.644136428833</v>
+        <v>11.6441354751587</v>
       </c>
       <c r="H1173" t="n">
         <v>606272</v>
@@ -34502,7 +34502,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1177" t="n">
-        <v>10.9603052139282</v>
+        <v>10.9603042602539</v>
       </c>
       <c r="H1177" t="n">
         <v>198677</v>
@@ -34589,7 +34589,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>10.7798490524292</v>
+        <v>10.7798480987549</v>
       </c>
       <c r="H1180" t="n">
         <v>321971</v>
@@ -34618,7 +34618,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1181" t="n">
-        <v>10.6753740310669</v>
+        <v>10.6753749847412</v>
       </c>
       <c r="H1181" t="n">
         <v>349616</v>
@@ -34676,7 +34676,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1183" t="n">
-        <v>11.6251411437988</v>
+        <v>11.6251401901245</v>
       </c>
       <c r="H1183" t="n">
         <v>469131</v>
@@ -34705,7 +34705,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1184" t="n">
-        <v>11.6251411437988</v>
+        <v>11.6251401901245</v>
       </c>
       <c r="H1184" t="n">
         <v>366008</v>
@@ -34821,7 +34821,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1188" t="n">
-        <v>11.7960987091064</v>
+        <v>11.7960996627808</v>
       </c>
       <c r="H1188" t="n">
         <v>437652</v>
@@ -34908,7 +34908,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G1191" t="n">
-        <v>11.4256896972656</v>
+        <v>11.4256887435913</v>
       </c>
       <c r="H1191" t="n">
         <v>405276</v>
@@ -35024,7 +35024,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G1195" t="n">
-        <v>11.4256896972656</v>
+        <v>11.4256887435913</v>
       </c>
       <c r="H1195" t="n">
         <v>331971</v>
@@ -35053,7 +35053,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>11.5871486663818</v>
+        <v>11.5871496200562</v>
       </c>
       <c r="H1196" t="n">
         <v>508547</v>
@@ -35198,7 +35198,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1201" t="n">
-        <v>11.568154335022</v>
+        <v>11.5681552886963</v>
       </c>
       <c r="H1201" t="n">
         <v>458047</v>
@@ -35314,7 +35314,7 @@
         <v>12.75</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.1095218658447</v>
+        <v>12.1095209121704</v>
       </c>
       <c r="H1205" t="n">
         <v>796074</v>
@@ -35343,7 +35343,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>12.0145444869995</v>
+        <v>12.0145454406738</v>
       </c>
       <c r="H1206" t="n">
         <v>316853</v>
@@ -35459,7 +35459,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.1285171508789</v>
+        <v>12.1285181045532</v>
       </c>
       <c r="H1210" t="n">
         <v>425924</v>
@@ -35517,7 +35517,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1212" t="n">
-        <v>12.2804803848267</v>
+        <v>12.2804794311523</v>
       </c>
       <c r="H1212" t="n">
         <v>495584</v>
@@ -35749,7 +35749,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>12.0145444869995</v>
+        <v>12.0145454406738</v>
       </c>
       <c r="H1220" t="n">
         <v>230560</v>
@@ -35807,7 +35807,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1222" t="n">
-        <v>12.8978281021118</v>
+        <v>12.8978271484375</v>
       </c>
       <c r="H1222" t="n">
         <v>2171962</v>
@@ -35865,7 +35865,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1224" t="n">
-        <v>11.8910760879517</v>
+        <v>11.8910751342773</v>
       </c>
       <c r="H1224" t="n">
         <v>529369</v>
@@ -35894,7 +35894,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G1225" t="n">
-        <v>11.6726293563843</v>
+        <v>11.67262840271</v>
       </c>
       <c r="H1225" t="n">
         <v>244312</v>
@@ -36068,7 +36068,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G1231" t="n">
-        <v>11.0552806854248</v>
+        <v>11.0552816390991</v>
       </c>
       <c r="H1231" t="n">
         <v>319792</v>
@@ -36155,7 +36155,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1234" t="n">
-        <v>11.3592052459717</v>
+        <v>11.359206199646</v>
       </c>
       <c r="H1234" t="n">
         <v>289953</v>
@@ -36213,7 +36213,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G1236" t="n">
-        <v>12.7933530807495</v>
+        <v>12.7933540344238</v>
       </c>
       <c r="H1236" t="n">
         <v>813432</v>
@@ -36271,7 +36271,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1238" t="n">
-        <v>12.8978281021118</v>
+        <v>12.8978271484375</v>
       </c>
       <c r="H1238" t="n">
         <v>905136</v>
@@ -36300,7 +36300,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1239" t="n">
-        <v>13.7811107635498</v>
+        <v>13.7811098098755</v>
       </c>
       <c r="H1239" t="n">
         <v>1165918</v>
@@ -36329,7 +36329,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1240" t="n">
-        <v>13.7146253585815</v>
+        <v>13.7146263122559</v>
       </c>
       <c r="H1240" t="n">
         <v>584415</v>
@@ -36387,7 +36387,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G1242" t="n">
-        <v>13.9330730438232</v>
+        <v>13.9330739974976</v>
       </c>
       <c r="H1242" t="n">
         <v>268344</v>
@@ -36445,7 +36445,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1244" t="n">
-        <v>14.3414726257324</v>
+        <v>14.3414716720581</v>
       </c>
       <c r="H1244" t="n">
         <v>573097</v>
@@ -36503,7 +36503,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1246" t="n">
-        <v>14.6264009475708</v>
+        <v>14.6264019012451</v>
       </c>
       <c r="H1246" t="n">
         <v>823200</v>
@@ -36532,7 +36532,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1247" t="n">
-        <v>14.6264009475708</v>
+        <v>14.6264019012451</v>
       </c>
       <c r="H1247" t="n">
         <v>353223</v>
@@ -36561,7 +36561,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G1248" t="n">
-        <v>14.3129796981812</v>
+        <v>14.3129787445068</v>
       </c>
       <c r="H1248" t="n">
         <v>692581</v>
@@ -36590,7 +36590,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1249" t="n">
-        <v>14.1515188217163</v>
+        <v>14.1515197753906</v>
       </c>
       <c r="H1249" t="n">
         <v>195884</v>
@@ -36677,7 +36677,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G1252" t="n">
-        <v>14.4649419784546</v>
+        <v>14.4649410247803</v>
       </c>
       <c r="H1252" t="n">
         <v>207534</v>
@@ -36706,7 +36706,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1253" t="n">
-        <v>14.9113321304321</v>
+        <v>14.9113311767578</v>
       </c>
       <c r="H1253" t="n">
         <v>539715</v>
@@ -36880,7 +36880,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G1259" t="n">
-        <v>14.5979089736938</v>
+        <v>14.5979099273682</v>
       </c>
       <c r="H1259" t="n">
         <v>255893</v>
@@ -36967,7 +36967,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1262" t="n">
-        <v>14.8828401565552</v>
+        <v>14.8828392028809</v>
       </c>
       <c r="H1262" t="n">
         <v>373492</v>
@@ -36996,7 +36996,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1263" t="n">
-        <v>14.8543472290039</v>
+        <v>14.8543462753296</v>
       </c>
       <c r="H1263" t="n">
         <v>350866</v>
@@ -37054,7 +37054,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1265" t="n">
-        <v>14.3794631958008</v>
+        <v>14.3794641494751</v>
       </c>
       <c r="H1265" t="n">
         <v>369816</v>
@@ -37373,7 +37373,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1276" t="n">
-        <v>14.5789136886597</v>
+        <v>14.578914642334</v>
       </c>
       <c r="H1276" t="n">
         <v>144339</v>
@@ -37402,7 +37402,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1277" t="n">
-        <v>14.4079551696777</v>
+        <v>14.4079561233521</v>
       </c>
       <c r="H1277" t="n">
         <v>195856</v>
@@ -37489,7 +37489,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1280" t="n">
-        <v>13.9615650177002</v>
+        <v>13.9615659713745</v>
       </c>
       <c r="H1280" t="n">
         <v>627502</v>
@@ -37547,7 +37547,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1282" t="n">
-        <v>14.3794631958008</v>
+        <v>14.3794641494751</v>
       </c>
       <c r="H1282" t="n">
         <v>310366</v>
@@ -37576,7 +37576,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G1283" t="n">
-        <v>14.4459466934204</v>
+        <v>14.4459457397461</v>
       </c>
       <c r="H1283" t="n">
         <v>253238</v>
@@ -37605,7 +37605,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G1284" t="n">
-        <v>15.3197317123413</v>
+        <v>15.319730758667</v>
       </c>
       <c r="H1284" t="n">
         <v>1360458</v>
@@ -37663,7 +37663,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1286" t="n">
-        <v>14.683388710022</v>
+        <v>14.6833877563477</v>
       </c>
       <c r="H1286" t="n">
         <v>261350</v>
@@ -37721,7 +37721,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1288" t="n">
-        <v>15.8041114807129</v>
+        <v>15.8041124343872</v>
       </c>
       <c r="H1288" t="n">
         <v>1007744</v>
@@ -37779,7 +37779,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1290" t="n">
-        <v>15.2627449035645</v>
+        <v>15.2627458572388</v>
       </c>
       <c r="H1290" t="n">
         <v>357033</v>
@@ -37837,7 +37837,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1292" t="n">
-        <v>15.0442991256714</v>
+        <v>15.0443000793457</v>
       </c>
       <c r="H1292" t="n">
         <v>236691</v>
@@ -37924,7 +37924,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1295" t="n">
-        <v>14.6359004974365</v>
+        <v>14.6358995437622</v>
       </c>
       <c r="H1295" t="n">
         <v>532047</v>
@@ -37953,7 +37953,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1296" t="n">
-        <v>14.6264009475708</v>
+        <v>14.6264019012451</v>
       </c>
       <c r="H1296" t="n">
         <v>395492</v>
@@ -37982,7 +37982,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1297" t="n">
-        <v>14.4364500045776</v>
+        <v>14.4364490509033</v>
       </c>
       <c r="H1297" t="n">
         <v>842933</v>
@@ -38011,7 +38011,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1298" t="n">
-        <v>14.5789136886597</v>
+        <v>14.578914642334</v>
       </c>
       <c r="H1298" t="n">
         <v>301305</v>
@@ -38214,7 +38214,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1305" t="n">
-        <v>14.7783651351929</v>
+        <v>14.7783641815186</v>
       </c>
       <c r="H1305" t="n">
         <v>340210</v>
@@ -38243,7 +38243,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G1306" t="n">
-        <v>14.825852394104</v>
+        <v>14.8258533477783</v>
       </c>
       <c r="H1306" t="n">
         <v>104373</v>
@@ -38359,7 +38359,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1310" t="n">
-        <v>15.1202812194824</v>
+        <v>15.1202802658081</v>
       </c>
       <c r="H1310" t="n">
         <v>191702</v>
@@ -38417,7 +38417,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1312" t="n">
-        <v>15.2627449035645</v>
+        <v>15.2627458572388</v>
       </c>
       <c r="H1312" t="n">
         <v>448450</v>
@@ -38475,7 +38475,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1314" t="n">
-        <v>15.1012859344482</v>
+        <v>15.1012849807739</v>
       </c>
       <c r="H1314" t="n">
         <v>135045</v>
@@ -38504,7 +38504,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G1315" t="n">
-        <v>14.8448476791382</v>
+        <v>14.8448486328125</v>
       </c>
       <c r="H1315" t="n">
         <v>523922</v>
@@ -38649,7 +38649,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1320" t="n">
-        <v>16.032054901123</v>
+        <v>16.0320568084717</v>
       </c>
       <c r="H1320" t="n">
         <v>326028</v>
@@ -38678,7 +38678,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1321" t="n">
-        <v>15.8231077194214</v>
+        <v>15.8231086730957</v>
       </c>
       <c r="H1321" t="n">
         <v>282425</v>
@@ -38736,7 +38736,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1323" t="n">
-        <v>15.8800916671753</v>
+        <v>15.8800926208496</v>
       </c>
       <c r="H1323" t="n">
         <v>189508</v>
@@ -38765,7 +38765,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>15.7376289367676</v>
+        <v>15.7376270294189</v>
       </c>
       <c r="H1324" t="n">
         <v>266463</v>
@@ -38852,7 +38852,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1327" t="n">
-        <v>15.7091369628906</v>
+        <v>15.7091360092163</v>
       </c>
       <c r="H1327" t="n">
         <v>255834</v>
@@ -38997,7 +38997,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1332" t="n">
-        <v>15.6996393203735</v>
+        <v>15.6996402740479</v>
       </c>
       <c r="H1332" t="n">
         <v>267931</v>
@@ -39026,7 +39026,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1333" t="n">
-        <v>15.538179397583</v>
+        <v>15.5381784439087</v>
       </c>
       <c r="H1333" t="n">
         <v>297213</v>
@@ -39084,7 +39084,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G1335" t="n">
-        <v>15.960823059082</v>
+        <v>15.9608240127563</v>
       </c>
       <c r="H1335" t="n">
         <v>327422</v>
@@ -39200,7 +39200,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1339" t="n">
-        <v>15.8468503952026</v>
+        <v>15.8468494415283</v>
       </c>
       <c r="H1339" t="n">
         <v>183071</v>
@@ -39229,7 +39229,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G1340" t="n">
-        <v>16.2837467193604</v>
+        <v>16.2837448120117</v>
       </c>
       <c r="H1340" t="n">
         <v>635746</v>
@@ -39374,7 +39374,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1345" t="n">
-        <v>16.4784469604492</v>
+        <v>16.4784488677979</v>
       </c>
       <c r="H1345" t="n">
         <v>458097</v>
@@ -39403,7 +39403,7 @@
         <v>17.9349994659424</v>
       </c>
       <c r="G1346" t="n">
-        <v>17.0340576171875</v>
+        <v>17.0340595245361</v>
       </c>
       <c r="H1346" t="n">
         <v>476173</v>
@@ -39461,7 +39461,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G1348" t="n">
-        <v>17.4567031860352</v>
+        <v>17.4567050933838</v>
       </c>
       <c r="H1348" t="n">
         <v>598052</v>
@@ -39577,7 +39577,7 @@
         <v>17.9850006103516</v>
       </c>
       <c r="G1352" t="n">
-        <v>17.0815467834473</v>
+        <v>17.0815486907959</v>
       </c>
       <c r="H1352" t="n">
         <v>171996</v>
@@ -39635,7 +39635,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1354" t="n">
-        <v>17.0245609283447</v>
+        <v>17.0245628356934</v>
       </c>
       <c r="H1354" t="n">
         <v>120508</v>
@@ -39693,7 +39693,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1356" t="n">
-        <v>17.5421829223633</v>
+        <v>17.5421848297119</v>
       </c>
       <c r="H1356" t="n">
         <v>453013</v>
@@ -39751,7 +39751,7 @@
         <v>18.3850002288818</v>
       </c>
       <c r="G1358" t="n">
-        <v>17.4614543914795</v>
+        <v>17.4614562988281</v>
       </c>
       <c r="H1358" t="n">
         <v>245410</v>
@@ -39896,7 +39896,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1363" t="n">
-        <v>18.1975250244141</v>
+        <v>18.1975231170654</v>
       </c>
       <c r="H1363" t="n">
         <v>262496</v>
@@ -39925,7 +39925,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G1364" t="n">
-        <v>18.1500377655029</v>
+        <v>18.1500358581543</v>
       </c>
       <c r="H1364" t="n">
         <v>98181</v>
@@ -40070,7 +40070,7 @@
         <v>18.9050006866455</v>
       </c>
       <c r="G1369" t="n">
-        <v>17.9553337097168</v>
+        <v>17.9553356170654</v>
       </c>
       <c r="H1369" t="n">
         <v>202418</v>
@@ -40157,7 +40157,7 @@
         <v>18.9950008392334</v>
       </c>
       <c r="G1372" t="n">
-        <v>18.0408134460449</v>
+        <v>18.0408115386963</v>
       </c>
       <c r="H1372" t="n">
         <v>393300</v>
@@ -40186,7 +40186,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1373" t="n">
-        <v>18.3304901123047</v>
+        <v>18.3304920196533</v>
       </c>
       <c r="H1373" t="n">
         <v>314066</v>
@@ -40215,7 +40215,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1374" t="n">
-        <v>18.3304901123047</v>
+        <v>18.3304920196533</v>
       </c>
       <c r="H1374" t="n">
         <v>368589</v>
@@ -40331,7 +40331,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G1378" t="n">
-        <v>18.3542346954346</v>
+        <v>18.3542366027832</v>
       </c>
       <c r="H1378" t="n">
         <v>205617</v>
@@ -40447,7 +40447,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G1382" t="n">
-        <v>18.3542346954346</v>
+        <v>18.3542366027832</v>
       </c>
       <c r="H1382" t="n">
         <v>357274</v>
@@ -40766,7 +40766,7 @@
         <v>19.3050003051758</v>
       </c>
       <c r="G1393" t="n">
-        <v>18.3352394104004</v>
+        <v>18.335241317749</v>
       </c>
       <c r="H1393" t="n">
         <v>153343</v>
@@ -40795,7 +40795,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G1394" t="n">
-        <v>17.8461093902588</v>
+        <v>17.8461112976074</v>
       </c>
       <c r="H1394" t="n">
         <v>862640</v>
@@ -40911,7 +40911,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1398" t="n">
-        <v>17.2287616729736</v>
+        <v>17.228759765625</v>
       </c>
       <c r="H1398" t="n">
         <v>182994</v>
@@ -40998,7 +40998,7 @@
         <v>18.0650005340576</v>
       </c>
       <c r="G1401" t="n">
-        <v>17.1575317382812</v>
+        <v>17.1575298309326</v>
       </c>
       <c r="H1401" t="n">
         <v>174374</v>
@@ -41114,7 +41114,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G1405" t="n">
-        <v>16.7253875732422</v>
+        <v>16.7253856658936</v>
       </c>
       <c r="H1405" t="n">
         <v>130393</v>
@@ -41259,7 +41259,7 @@
         <v>16.8250007629395</v>
       </c>
       <c r="G1410" t="n">
-        <v>15.9798202514648</v>
+        <v>15.9798192977905</v>
       </c>
       <c r="H1410" t="n">
         <v>226607</v>
@@ -41346,7 +41346,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G1413" t="n">
-        <v>16.2505035400391</v>
+        <v>16.2505054473877</v>
       </c>
       <c r="H1413" t="n">
         <v>208206</v>
@@ -41607,7 +41607,7 @@
         <v>16.9150009155273</v>
       </c>
       <c r="G1422" t="n">
-        <v>16.065299987793</v>
+        <v>16.0652980804443</v>
       </c>
       <c r="H1422" t="n">
         <v>166040</v>
@@ -41694,7 +41694,7 @@
         <v>18.3150005340576</v>
       </c>
       <c r="G1425" t="n">
-        <v>17.3949718475342</v>
+        <v>17.3949699401855</v>
       </c>
       <c r="H1425" t="n">
         <v>1075982</v>
@@ -41723,7 +41723,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G1426" t="n">
-        <v>18.4919528961182</v>
+        <v>18.4919509887695</v>
       </c>
       <c r="H1426" t="n">
         <v>1825372</v>
@@ -41897,7 +41897,7 @@
         <v>16.5650005340576</v>
       </c>
       <c r="G1432" t="n">
-        <v>15.7328805923462</v>
+        <v>15.7328796386719</v>
       </c>
       <c r="H1432" t="n">
         <v>1557331</v>
@@ -42013,7 +42013,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1436" t="n">
-        <v>15.8041114807129</v>
+        <v>15.8041124343872</v>
       </c>
       <c r="H1436" t="n">
         <v>400962</v>
@@ -42042,7 +42042,7 @@
         <v>16.8150005340576</v>
       </c>
       <c r="G1437" t="n">
-        <v>15.9703235626221</v>
+        <v>15.9703226089478</v>
       </c>
       <c r="H1437" t="n">
         <v>478682</v>
@@ -42187,7 +42187,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G1442" t="n">
-        <v>16.6873950958252</v>
+        <v>16.6873970031738</v>
       </c>
       <c r="H1442" t="n">
         <v>356835</v>
@@ -42274,7 +42274,7 @@
         <v>17.9349994659424</v>
       </c>
       <c r="G1445" t="n">
-        <v>17.0340576171875</v>
+        <v>17.0340595245361</v>
       </c>
       <c r="H1445" t="n">
         <v>595270</v>
@@ -42535,7 +42535,7 @@
         <v>17.6049995422363</v>
       </c>
       <c r="G1454" t="n">
-        <v>16.7206382751465</v>
+        <v>16.7206363677979</v>
       </c>
       <c r="H1454" t="n">
         <v>381572</v>
@@ -42593,7 +42593,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1456" t="n">
-        <v>16.9628276824951</v>
+        <v>16.9628295898438</v>
       </c>
       <c r="H1456" t="n">
         <v>490557</v>
@@ -42651,7 +42651,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1458" t="n">
-        <v>17.0245609283447</v>
+        <v>17.0245628356934</v>
       </c>
       <c r="H1458" t="n">
         <v>239347</v>
@@ -42709,7 +42709,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1460" t="n">
-        <v>16.8298606872559</v>
+        <v>16.8298587799072</v>
       </c>
       <c r="H1460" t="n">
         <v>299762</v>
@@ -42796,7 +42796,7 @@
         <v>17.9850006103516</v>
       </c>
       <c r="G1463" t="n">
-        <v>17.0815467834473</v>
+        <v>17.0815486907959</v>
       </c>
       <c r="H1463" t="n">
         <v>306425</v>
@@ -42854,7 +42854,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G1465" t="n">
-        <v>17.0245609283447</v>
+        <v>17.0245628356934</v>
       </c>
       <c r="H1465" t="n">
         <v>239316</v>
@@ -42970,7 +42970,7 @@
         <v>17.5949993133545</v>
       </c>
       <c r="G1469" t="n">
-        <v>16.7111396789551</v>
+        <v>16.7111377716064</v>
       </c>
       <c r="H1469" t="n">
         <v>239518</v>
@@ -43086,7 +43086,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1473" t="n">
-        <v>17.2287616729736</v>
+        <v>17.228759765625</v>
       </c>
       <c r="H1473" t="n">
         <v>227595</v>
@@ -43173,7 +43173,7 @@
         <v>18</v>
       </c>
       <c r="G1476" t="n">
-        <v>17.0957946777344</v>
+        <v>17.095796585083</v>
       </c>
       <c r="H1476" t="n">
         <v>256695</v>
@@ -43202,7 +43202,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G1477" t="n">
-        <v>17.4329605102539</v>
+        <v>17.4329624176025</v>
       </c>
       <c r="H1477" t="n">
         <v>394524</v>
@@ -43289,7 +43289,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1480" t="n">
-        <v>17.2857494354248</v>
+        <v>17.2857475280762</v>
       </c>
       <c r="H1480" t="n">
         <v>256636</v>
@@ -43347,7 +43347,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G1482" t="n">
-        <v>17.3427333831787</v>
+        <v>17.3427352905273</v>
       </c>
       <c r="H1482" t="n">
         <v>164225</v>
@@ -43550,7 +43550,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.7911262512207</v>
+        <v>18.7911281585693</v>
       </c>
       <c r="H1489" t="n">
         <v>580958</v>
@@ -43579,7 +43579,7 @@
         <v>19.9750003814697</v>
       </c>
       <c r="G1490" t="n">
-        <v>18.9715843200684</v>
+        <v>18.9715824127197</v>
       </c>
       <c r="H1490" t="n">
         <v>760653</v>
@@ -43637,7 +43637,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1492" t="n">
-        <v>17.9458351135254</v>
+        <v>17.945837020874</v>
       </c>
       <c r="H1492" t="n">
         <v>698032</v>
@@ -43666,7 +43666,7 @@
         <v>19.4050006866455</v>
       </c>
       <c r="G1493" t="n">
-        <v>18.4302177429199</v>
+        <v>18.4302158355713</v>
       </c>
       <c r="H1493" t="n">
         <v>677943</v>
@@ -43695,7 +43695,7 @@
         <v>19.5349998474121</v>
       </c>
       <c r="G1494" t="n">
-        <v>18.5536861419678</v>
+        <v>18.5536880493164</v>
       </c>
       <c r="H1494" t="n">
         <v>493405</v>
@@ -43724,7 +43724,7 @@
         <v>19.7549991607666</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.7626342773438</v>
+        <v>18.7626323699951</v>
       </c>
       <c r="H1495" t="n">
         <v>366254</v>
@@ -43753,7 +43753,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1496" t="n">
-        <v>19.0903053283691</v>
+        <v>19.0903034210205</v>
       </c>
       <c r="H1496" t="n">
         <v>655949</v>
@@ -43811,7 +43811,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>18.9240951538086</v>
+        <v>18.92409324646</v>
       </c>
       <c r="H1498" t="n">
         <v>727935</v>
@@ -43840,7 +43840,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1499" t="n">
-        <v>19.1662845611572</v>
+        <v>19.1662864685059</v>
       </c>
       <c r="H1499" t="n">
         <v>633946</v>
@@ -43869,7 +43869,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1500" t="n">
-        <v>19.1662845611572</v>
+        <v>19.1662864685059</v>
       </c>
       <c r="H1500" t="n">
         <v>447223</v>
@@ -44130,7 +44130,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G1509" t="n">
-        <v>19.7456436157227</v>
+        <v>19.745641708374</v>
       </c>
       <c r="H1509" t="n">
         <v>293466</v>
@@ -44217,7 +44217,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1512" t="n">
-        <v>21.0373268127441</v>
+        <v>21.0373249053955</v>
       </c>
       <c r="H1512" t="n">
         <v>923182</v>
@@ -44362,7 +44362,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G1517" t="n">
-        <v>20.1635417938232</v>
+        <v>20.1635398864746</v>
       </c>
       <c r="H1517" t="n">
         <v>373968</v>
@@ -44391,7 +44391,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G1518" t="n">
-        <v>20.0970554351807</v>
+        <v>20.0970573425293</v>
       </c>
       <c r="H1518" t="n">
         <v>537973</v>
@@ -44420,7 +44420,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G1519" t="n">
-        <v>20.7903861999512</v>
+        <v>20.7903842926025</v>
       </c>
       <c r="H1519" t="n">
         <v>591890</v>
@@ -44507,7 +44507,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1522" t="n">
-        <v>21.0373268127441</v>
+        <v>21.0373249053955</v>
       </c>
       <c r="H1522" t="n">
         <v>216817</v>
@@ -44536,7 +44536,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G1523" t="n">
-        <v>21.0183277130127</v>
+        <v>21.0183296203613</v>
       </c>
       <c r="H1523" t="n">
         <v>163933</v>
@@ -44565,7 +44565,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G1524" t="n">
-        <v>21.094310760498</v>
+        <v>21.0943088531494</v>
       </c>
       <c r="H1524" t="n">
         <v>261487</v>
@@ -44594,7 +44594,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1525" t="n">
-        <v>21.4172306060791</v>
+        <v>21.4172325134277</v>
       </c>
       <c r="H1525" t="n">
         <v>646406</v>
@@ -44623,7 +44623,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G1526" t="n">
-        <v>21.3982372283936</v>
+        <v>21.3982391357422</v>
       </c>
       <c r="H1526" t="n">
         <v>218266</v>
@@ -44681,7 +44681,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G1528" t="n">
-        <v>21.5691928863525</v>
+        <v>21.5691947937012</v>
       </c>
       <c r="H1528" t="n">
         <v>290973</v>
@@ -45058,7 +45058,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G1541" t="n">
-        <v>18.055061340332</v>
+        <v>18.0550594329834</v>
       </c>
       <c r="H1541" t="n">
         <v>598933</v>
@@ -45116,7 +45116,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1543" t="n">
-        <v>17.5421829223633</v>
+        <v>17.5421848297119</v>
       </c>
       <c r="H1543" t="n">
         <v>553477</v>
@@ -45290,7 +45290,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1549" t="n">
-        <v>18.5394420623779</v>
+        <v>18.5394401550293</v>
       </c>
       <c r="H1549" t="n">
         <v>396132</v>
@@ -45319,7 +45319,7 @@
         <v>19.0550003051758</v>
       </c>
       <c r="G1550" t="n">
-        <v>18.0977993011475</v>
+        <v>18.0977973937988</v>
       </c>
       <c r="H1550" t="n">
         <v>168469</v>
@@ -45348,7 +45348,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1551" t="n">
-        <v>17.9458351135254</v>
+        <v>17.945837020874</v>
       </c>
       <c r="H1551" t="n">
         <v>261232</v>
@@ -45377,7 +45377,7 @@
         <v>18.9950008392334</v>
       </c>
       <c r="G1552" t="n">
-        <v>18.0408134460449</v>
+        <v>18.0408115386963</v>
       </c>
       <c r="H1552" t="n">
         <v>178538</v>
@@ -45406,7 +45406,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G1553" t="n">
-        <v>18.0503101348877</v>
+        <v>18.0503082275391</v>
       </c>
       <c r="H1553" t="n">
         <v>183351</v>
@@ -45464,7 +45464,7 @@
         <v>19.25</v>
       </c>
       <c r="G1555" t="n">
-        <v>18.2830009460449</v>
+        <v>18.2830028533936</v>
       </c>
       <c r="H1555" t="n">
         <v>246876</v>
@@ -45580,7 +45580,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G1559" t="n">
-        <v>18.6819038391113</v>
+        <v>18.68190574646</v>
       </c>
       <c r="H1559" t="n">
         <v>326731</v>
@@ -45609,7 +45609,7 @@
         <v>19.7649993896484</v>
       </c>
       <c r="G1560" t="n">
-        <v>18.7721309661865</v>
+        <v>18.7721328735352</v>
       </c>
       <c r="H1560" t="n">
         <v>613272</v>
@@ -45638,7 +45638,7 @@
         <v>19.7950000762939</v>
       </c>
       <c r="G1561" t="n">
-        <v>18.8006248474121</v>
+        <v>18.8006267547607</v>
       </c>
       <c r="H1561" t="n">
         <v>277175</v>
@@ -45667,7 +45667,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1562" t="n">
-        <v>18.5964260101318</v>
+        <v>18.5964241027832</v>
       </c>
       <c r="H1562" t="n">
         <v>209980</v>
@@ -45696,7 +45696,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G1563" t="n">
-        <v>18.7768802642822</v>
+        <v>18.7768821716309</v>
       </c>
       <c r="H1563" t="n">
         <v>334413</v>
@@ -45783,7 +45783,7 @@
         <v>19.6450004577637</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.6581592559814</v>
+        <v>18.6581611633301</v>
       </c>
       <c r="H1566" t="n">
         <v>358435</v>
@@ -45841,7 +45841,7 @@
         <v>18.5650005340576</v>
       </c>
       <c r="G1568" t="n">
-        <v>17.6324157714844</v>
+        <v>17.6324138641357</v>
       </c>
       <c r="H1568" t="n">
         <v>299563</v>
@@ -45899,7 +45899,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G1570" t="n">
-        <v>17.12428855896</v>
+        <v>17.1242904663086</v>
       </c>
       <c r="H1570" t="n">
         <v>243617</v>
@@ -45986,7 +45986,7 @@
         <v>15.2749996185303</v>
       </c>
       <c r="G1573" t="n">
-        <v>14.5076808929443</v>
+        <v>14.5076818466187</v>
       </c>
       <c r="H1573" t="n">
         <v>715448</v>
@@ -46015,7 +46015,7 @@
         <v>16.7549991607666</v>
       </c>
       <c r="G1574" t="n">
-        <v>15.9133329391479</v>
+        <v>15.9133348464966</v>
       </c>
       <c r="H1574" t="n">
         <v>1254789</v>
@@ -46073,7 +46073,7 @@
         <v>16.1650009155273</v>
       </c>
       <c r="G1576" t="n">
-        <v>15.3529748916626</v>
+        <v>15.3529739379883</v>
       </c>
       <c r="H1576" t="n">
         <v>678377</v>
@@ -46160,7 +46160,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G1579" t="n">
-        <v>15.5856666564941</v>
+        <v>15.5856676101685</v>
       </c>
       <c r="H1579" t="n">
         <v>678989</v>
@@ -46189,7 +46189,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1580" t="n">
-        <v>15.7043857574463</v>
+        <v>15.7043867111206</v>
       </c>
       <c r="H1580" t="n">
         <v>591416</v>
@@ -46334,7 +46334,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1585" t="n">
-        <v>15.2532472610474</v>
+        <v>15.2532482147217</v>
       </c>
       <c r="H1585" t="n">
         <v>212871</v>
@@ -46363,7 +46363,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1586" t="n">
-        <v>15.5191831588745</v>
+        <v>15.5191822052002</v>
       </c>
       <c r="H1586" t="n">
         <v>176934</v>
@@ -46537,7 +46537,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1592" t="n">
-        <v>15.9750709533691</v>
+        <v>15.9750699996948</v>
       </c>
       <c r="H1592" t="n">
         <v>499755</v>
@@ -46566,7 +46566,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1593" t="n">
-        <v>15.2627449035645</v>
+        <v>15.2627458572388</v>
       </c>
       <c r="H1593" t="n">
         <v>528848</v>
@@ -46682,7 +46682,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1597" t="n">
-        <v>15.0442991256714</v>
+        <v>15.0443000793457</v>
       </c>
       <c r="H1597" t="n">
         <v>339465</v>
@@ -46740,7 +46740,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1599" t="n">
-        <v>15.4811906814575</v>
+        <v>15.4811916351318</v>
       </c>
       <c r="H1599" t="n">
         <v>368053</v>
@@ -46769,7 +46769,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1600" t="n">
-        <v>15.6331539154053</v>
+        <v>15.6331548690796</v>
       </c>
       <c r="H1600" t="n">
         <v>220814</v>
@@ -46827,7 +46827,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1602" t="n">
-        <v>15.6996393203735</v>
+        <v>15.6996402740479</v>
       </c>
       <c r="H1602" t="n">
         <v>249471</v>
@@ -46856,7 +46856,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1603" t="n">
-        <v>15.8895902633667</v>
+        <v>15.889591217041</v>
       </c>
       <c r="H1603" t="n">
         <v>184509</v>
@@ -47001,7 +47001,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1608" t="n">
-        <v>15.1392755508423</v>
+        <v>15.1392765045166</v>
       </c>
       <c r="H1608" t="n">
         <v>257315</v>
@@ -47088,7 +47088,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G1611" t="n">
-        <v>15.0348014831543</v>
+        <v>15.0348024368286</v>
       </c>
       <c r="H1611" t="n">
         <v>1097109</v>
@@ -47233,7 +47233,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1616" t="n">
-        <v>12.8123483657837</v>
+        <v>12.812349319458</v>
       </c>
       <c r="H1616" t="n">
         <v>1090137</v>
@@ -47291,7 +47291,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1618" t="n">
-        <v>14.1990079879761</v>
+        <v>14.1990070343018</v>
       </c>
       <c r="H1618" t="n">
         <v>610192</v>
@@ -47436,7 +47436,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1623" t="n">
-        <v>14.9113321304321</v>
+        <v>14.9113311767578</v>
       </c>
       <c r="H1623" t="n">
         <v>359301</v>
@@ -47494,7 +47494,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G1625" t="n">
-        <v>14.8327655792236</v>
+        <v>14.8327665328979</v>
       </c>
       <c r="H1625" t="n">
         <v>250206</v>
@@ -47552,7 +47552,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1627" t="n">
-        <v>14.6870603561401</v>
+        <v>14.6870594024658</v>
       </c>
       <c r="H1627" t="n">
         <v>521547</v>
@@ -47581,7 +47581,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1628" t="n">
-        <v>15.0756072998047</v>
+        <v>15.075608253479</v>
       </c>
       <c r="H1628" t="n">
         <v>290165</v>
@@ -47697,7 +47697,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1632" t="n">
-        <v>15.8915557861328</v>
+        <v>15.8915548324585</v>
       </c>
       <c r="H1632" t="n">
         <v>186049</v>
@@ -47726,7 +47726,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1633" t="n">
-        <v>15.9886903762817</v>
+        <v>15.9886913299561</v>
       </c>
       <c r="H1633" t="n">
         <v>198905</v>
@@ -47784,7 +47784,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1635" t="n">
-        <v>15.9692640304565</v>
+        <v>15.9692649841309</v>
       </c>
       <c r="H1635" t="n">
         <v>243201</v>
@@ -47929,7 +47929,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1640" t="n">
-        <v>13.7545480728149</v>
+        <v>13.7545490264893</v>
       </c>
       <c r="H1640" t="n">
         <v>584757</v>
@@ -48016,7 +48016,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1643" t="n">
-        <v>13.3660020828247</v>
+        <v>13.366003036499</v>
       </c>
       <c r="H1643" t="n">
         <v>326261</v>
@@ -48045,7 +48045,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1644" t="n">
-        <v>13.7254076004028</v>
+        <v>13.7254085540771</v>
       </c>
       <c r="H1644" t="n">
         <v>339680</v>
@@ -48074,7 +48074,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>13.9391088485718</v>
+        <v>13.9391078948975</v>
       </c>
       <c r="H1645" t="n">
         <v>191237</v>
@@ -48712,7 +48712,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1667" t="n">
-        <v>15.6972808837891</v>
+        <v>15.6972818374634</v>
       </c>
       <c r="H1667" t="n">
         <v>171031</v>
@@ -48770,7 +48770,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1669" t="n">
-        <v>16.2315311431885</v>
+        <v>16.2315330505371</v>
       </c>
       <c r="H1669" t="n">
         <v>146832</v>
@@ -48857,7 +48857,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1672" t="n">
-        <v>15.872127532959</v>
+        <v>15.8721265792847</v>
       </c>
       <c r="H1672" t="n">
         <v>91189</v>
@@ -48973,7 +48973,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1676" t="n">
-        <v>16.4646606445312</v>
+        <v>16.4646625518799</v>
       </c>
       <c r="H1676" t="n">
         <v>218918</v>
@@ -49234,7 +49234,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1685" t="n">
-        <v>17.0960502624512</v>
+        <v>17.0960483551025</v>
       </c>
       <c r="H1685" t="n">
         <v>53651</v>
@@ -49263,7 +49263,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1686" t="n">
-        <v>16.9503440856934</v>
+        <v>16.950345993042</v>
       </c>
       <c r="H1686" t="n">
         <v>96411</v>
@@ -49466,7 +49466,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1693" t="n">
-        <v>16.0664024353027</v>
+        <v>16.0664005279541</v>
       </c>
       <c r="H1693" t="n">
         <v>64523</v>
@@ -49524,7 +49524,7 @@
         <v>16.1100006103516</v>
       </c>
       <c r="G1695" t="n">
-        <v>15.6487140655518</v>
+        <v>15.6487131118774</v>
       </c>
       <c r="H1695" t="n">
         <v>138647</v>
@@ -49553,7 +49553,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1696" t="n">
-        <v>15.6001434326172</v>
+        <v>15.6001443862915</v>
       </c>
       <c r="H1696" t="n">
         <v>107360</v>
@@ -49785,7 +49785,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1704" t="n">
-        <v>15.1727437973022</v>
+        <v>15.1727428436279</v>
       </c>
       <c r="H1704" t="n">
         <v>117993</v>
@@ -49930,7 +49930,7 @@
         <v>14.75</v>
       </c>
       <c r="G1709" t="n">
-        <v>14.327654838562</v>
+        <v>14.3276538848877</v>
       </c>
       <c r="H1709" t="n">
         <v>175419</v>
@@ -50104,7 +50104,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1715" t="n">
-        <v>13.540846824646</v>
+        <v>13.5408477783203</v>
       </c>
       <c r="H1715" t="n">
         <v>135726</v>
@@ -50133,7 +50133,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1716" t="n">
-        <v>13.9391088485718</v>
+        <v>13.9391078948975</v>
       </c>
       <c r="H1716" t="n">
         <v>235008</v>
@@ -50945,7 +50945,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1744" t="n">
-        <v>14.8230514526367</v>
+        <v>14.823052406311</v>
       </c>
       <c r="H1744" t="n">
         <v>123488</v>
@@ -51090,7 +51090,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1749" t="n">
-        <v>16.2315311431885</v>
+        <v>16.2315330505371</v>
       </c>
       <c r="H1749" t="n">
         <v>179584</v>
@@ -51177,7 +51177,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1752" t="n">
-        <v>15.9304094314575</v>
+        <v>15.9304103851318</v>
       </c>
       <c r="H1752" t="n">
         <v>214610</v>
@@ -51235,7 +51235,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1754" t="n">
-        <v>15.9789781570435</v>
+        <v>15.9789791107178</v>
       </c>
       <c r="H1754" t="n">
         <v>133040</v>
@@ -51380,7 +51380,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G1759" t="n">
-        <v>15.7652769088745</v>
+        <v>15.7652759552002</v>
       </c>
       <c r="H1759" t="n">
         <v>90519</v>
@@ -51438,7 +51438,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1761" t="n">
-        <v>16.5229415893555</v>
+        <v>16.5229434967041</v>
       </c>
       <c r="H1761" t="n">
         <v>347709</v>
@@ -51525,7 +51525,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1764" t="n">
-        <v>16.8434944152832</v>
+        <v>16.8434925079346</v>
       </c>
       <c r="H1764" t="n">
         <v>142892</v>
@@ -51902,7 +51902,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1777" t="n">
-        <v>15.9789781570435</v>
+        <v>15.9789791107178</v>
       </c>
       <c r="H1777" t="n">
         <v>90096</v>
@@ -51989,7 +51989,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1780" t="n">
-        <v>15.9789781570435</v>
+        <v>15.9789791107178</v>
       </c>
       <c r="H1780" t="n">
         <v>112128</v>
@@ -52018,7 +52018,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1781" t="n">
-        <v>16.1635360717773</v>
+        <v>16.163537979126</v>
       </c>
       <c r="H1781" t="n">
         <v>112327</v>
@@ -52511,7 +52511,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1798" t="n">
-        <v>17.7954330444336</v>
+        <v>17.795431137085</v>
       </c>
       <c r="H1798" t="n">
         <v>64188</v>
@@ -52540,7 +52540,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1799" t="n">
-        <v>17.9119987487793</v>
+        <v>17.9119968414307</v>
       </c>
       <c r="H1799" t="n">
         <v>160816</v>
@@ -52569,7 +52569,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G1800" t="n">
-        <v>18.0382747650146</v>
+        <v>18.038272857666</v>
       </c>
       <c r="H1800" t="n">
         <v>151033</v>
@@ -53410,7 +53410,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G1829" t="n">
-        <v>18.0382747650146</v>
+        <v>18.038272857666</v>
       </c>
       <c r="H1829" t="n">
         <v>179876</v>
@@ -53526,7 +53526,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1833" t="n">
-        <v>16.5229415893555</v>
+        <v>16.5229434967041</v>
       </c>
       <c r="H1833" t="n">
         <v>268544</v>
@@ -53584,7 +53584,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1835" t="n">
-        <v>16.3189563751221</v>
+        <v>16.3189544677734</v>
       </c>
       <c r="H1835" t="n">
         <v>157907</v>
@@ -53613,7 +53613,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1836" t="n">
-        <v>16.581226348877</v>
+        <v>16.5812244415283</v>
       </c>
       <c r="H1836" t="n">
         <v>146650</v>
@@ -53874,7 +53874,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1845" t="n">
-        <v>16.076114654541</v>
+        <v>16.0761127471924</v>
       </c>
       <c r="H1845" t="n">
         <v>111434</v>
@@ -54048,7 +54048,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1851" t="n">
-        <v>16.0664024353027</v>
+        <v>16.0664005279541</v>
       </c>
       <c r="H1851" t="n">
         <v>106743</v>
@@ -54309,7 +54309,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1860" t="n">
-        <v>15.8818416595459</v>
+        <v>15.8818407058716</v>
       </c>
       <c r="H1860" t="n">
         <v>965592</v>
@@ -54338,7 +54338,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1861" t="n">
-        <v>15.7361364364624</v>
+        <v>15.7361373901367</v>
       </c>
       <c r="H1861" t="n">
         <v>192578</v>
@@ -54512,7 +54512,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1867" t="n">
-        <v>15.6778535842896</v>
+        <v>15.6778526306152</v>
       </c>
       <c r="H1867" t="n">
         <v>166702</v>
@@ -54657,7 +54657,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1872" t="n">
-        <v>15.0756072998047</v>
+        <v>15.075608253479</v>
       </c>
       <c r="H1872" t="n">
         <v>141839</v>
@@ -54686,7 +54686,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1873" t="n">
-        <v>15.085319519043</v>
+        <v>15.0853204727173</v>
       </c>
       <c r="H1873" t="n">
         <v>197921</v>
@@ -54860,7 +54860,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1879" t="n">
-        <v>14.7064876556396</v>
+        <v>14.706488609314</v>
       </c>
       <c r="H1879" t="n">
         <v>100521</v>
@@ -80125,6 +80125,35 @@
         <v>363116</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>6.32000017166138</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>6.375</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>6.32000017166138</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>6.32000017166138</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>330367</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SFER.MI.xlsx
+++ b/data/SFER.MI.xlsx
@@ -456,7 +456,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G3" t="n">
-        <v>18.0109672546387</v>
+        <v>18.0109634399414</v>
       </c>
       <c r="H3" t="n">
         <v>997627</v>
@@ -514,7 +514,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>17.9401931762695</v>
+        <v>17.9401950836182</v>
       </c>
       <c r="H5" t="n">
         <v>1381959</v>
@@ -543,7 +543,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>17.6836528778076</v>
+        <v>17.6836490631104</v>
       </c>
       <c r="H6" t="n">
         <v>951699</v>
@@ -572,7 +572,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G7" t="n">
-        <v>18.249813079834</v>
+        <v>18.2498111724854</v>
       </c>
       <c r="H7" t="n">
         <v>1189444</v>
@@ -630,7 +630,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G9" t="n">
-        <v>19.1344375610352</v>
+        <v>19.1344356536865</v>
       </c>
       <c r="H9" t="n">
         <v>1367537</v>
@@ -659,7 +659,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G10" t="n">
-        <v>18.8425102233887</v>
+        <v>18.84250831604</v>
       </c>
       <c r="H10" t="n">
         <v>1053164</v>
@@ -688,7 +688,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G11" t="n">
-        <v>18.4621257781982</v>
+        <v>18.462121963501</v>
       </c>
       <c r="H11" t="n">
         <v>802632</v>
@@ -717,7 +717,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G12" t="n">
-        <v>18.2852001190186</v>
+        <v>18.2851963043213</v>
       </c>
       <c r="H12" t="n">
         <v>939035</v>
@@ -775,7 +775,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G14" t="n">
-        <v>17.6394233703613</v>
+        <v>17.6394214630127</v>
       </c>
       <c r="H14" t="n">
         <v>943974</v>
@@ -804,7 +804,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G15" t="n">
-        <v>17.5686550140381</v>
+        <v>17.5686511993408</v>
       </c>
       <c r="H15" t="n">
         <v>1002361</v>
@@ -920,7 +920,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>18.2232723236084</v>
+        <v>18.223274230957</v>
       </c>
       <c r="H19" t="n">
         <v>550218</v>
@@ -1007,7 +1007,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G22" t="n">
-        <v>18.674430847168</v>
+        <v>18.6744346618652</v>
       </c>
       <c r="H22" t="n">
         <v>1011926</v>
@@ -1065,7 +1065,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G24" t="n">
-        <v>18.2055816650391</v>
+        <v>18.2055797576904</v>
       </c>
       <c r="H24" t="n">
         <v>1897967</v>
@@ -1094,7 +1094,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G25" t="n">
-        <v>18.2586555480957</v>
+        <v>18.258659362793</v>
       </c>
       <c r="H25" t="n">
         <v>716525</v>
@@ -1152,7 +1152,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G27" t="n">
-        <v>17.3563423156738</v>
+        <v>17.3563404083252</v>
       </c>
       <c r="H27" t="n">
         <v>875683</v>
@@ -1210,7 +1210,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>17.1617240905762</v>
+        <v>17.1617259979248</v>
       </c>
       <c r="H29" t="n">
         <v>741895</v>
@@ -1239,7 +1239,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G30" t="n">
-        <v>16.6486396789551</v>
+        <v>16.6486415863037</v>
       </c>
       <c r="H30" t="n">
         <v>1048393</v>
@@ -1268,7 +1268,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G31" t="n">
-        <v>17.0201835632324</v>
+        <v>17.0201873779297</v>
       </c>
       <c r="H31" t="n">
         <v>474221</v>
@@ -1297,7 +1297,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G32" t="n">
-        <v>17.4890365600586</v>
+        <v>17.48903465271</v>
       </c>
       <c r="H32" t="n">
         <v>658925</v>
@@ -1326,7 +1326,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G33" t="n">
-        <v>17.6305751800537</v>
+        <v>17.6305732727051</v>
       </c>
       <c r="H33" t="n">
         <v>742916</v>
@@ -1413,7 +1413,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G36" t="n">
-        <v>18.4532775878906</v>
+        <v>18.4532737731934</v>
       </c>
       <c r="H36" t="n">
         <v>500284</v>
@@ -1442,7 +1442,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>18.9752044677734</v>
+        <v>18.9752063751221</v>
       </c>
       <c r="H37" t="n">
         <v>534225</v>
@@ -1471,7 +1471,7 @@
         <v>20.5</v>
       </c>
       <c r="G38" t="n">
-        <v>18.1348133087158</v>
+        <v>18.1348094940186</v>
       </c>
       <c r="H38" t="n">
         <v>591716</v>
@@ -1500,7 +1500,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G39" t="n">
-        <v>17.3121089935303</v>
+        <v>17.3121070861816</v>
       </c>
       <c r="H39" t="n">
         <v>1119066</v>
@@ -1558,7 +1558,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G41" t="n">
-        <v>17.9048099517822</v>
+        <v>17.9048080444336</v>
       </c>
       <c r="H41" t="n">
         <v>422135</v>
@@ -1616,7 +1616,7 @@
         <v>21.5</v>
       </c>
       <c r="G43" t="n">
-        <v>19.0194339752197</v>
+        <v>19.019437789917</v>
       </c>
       <c r="H43" t="n">
         <v>1151116</v>
@@ -1645,7 +1645,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G44" t="n">
-        <v>19.001745223999</v>
+        <v>19.0017433166504</v>
       </c>
       <c r="H44" t="n">
         <v>479063</v>
@@ -1674,7 +1674,7 @@
         <v>21.3099994659424</v>
       </c>
       <c r="G45" t="n">
-        <v>18.8513584136963</v>
+        <v>18.851354598999</v>
       </c>
       <c r="H45" t="n">
         <v>368675</v>
@@ -1703,7 +1703,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G46" t="n">
-        <v>19.3113613128662</v>
+        <v>19.3113632202148</v>
       </c>
       <c r="H46" t="n">
         <v>602537</v>
@@ -1732,7 +1732,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G47" t="n">
-        <v>19.992525100708</v>
+        <v>19.9925231933594</v>
       </c>
       <c r="H47" t="n">
         <v>1033585</v>
@@ -1761,7 +1761,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>19.9482936859131</v>
+        <v>19.9482898712158</v>
       </c>
       <c r="H48" t="n">
         <v>1078018</v>
@@ -1790,7 +1790,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>19.7271347045898</v>
+        <v>19.7271366119385</v>
       </c>
       <c r="H49" t="n">
         <v>805952</v>
@@ -1819,7 +1819,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G50" t="n">
-        <v>19.3379039764404</v>
+        <v>19.3379020690918</v>
       </c>
       <c r="H50" t="n">
         <v>900267</v>
@@ -1906,7 +1906,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G53" t="n">
-        <v>19.1167469024658</v>
+        <v>19.1167449951172</v>
       </c>
       <c r="H53" t="n">
         <v>1070469</v>
@@ -1935,7 +1935,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G54" t="n">
-        <v>19.3379039764404</v>
+        <v>19.3379020690918</v>
       </c>
       <c r="H54" t="n">
         <v>460963</v>
@@ -1964,7 +1964,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G55" t="n">
-        <v>19.444055557251</v>
+        <v>19.4440574645996</v>
       </c>
       <c r="H55" t="n">
         <v>774964</v>
@@ -2051,7 +2051,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G58" t="n">
-        <v>19.4971351623535</v>
+        <v>19.4971332550049</v>
       </c>
       <c r="H58" t="n">
         <v>1161092</v>
@@ -2080,7 +2080,7 @@
         <v>22.0100002288818</v>
       </c>
       <c r="G59" t="n">
-        <v>19.4705944061279</v>
+        <v>19.4705963134766</v>
       </c>
       <c r="H59" t="n">
         <v>731623</v>
@@ -2138,7 +2138,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G61" t="n">
-        <v>19.4794445037842</v>
+        <v>19.4794425964355</v>
       </c>
       <c r="H61" t="n">
         <v>502164</v>
@@ -2196,7 +2196,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G63" t="n">
-        <v>19.8686752319336</v>
+        <v>19.868673324585</v>
       </c>
       <c r="H63" t="n">
         <v>732706</v>
@@ -2225,7 +2225,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G64" t="n">
-        <v>19.4971351623535</v>
+        <v>19.4971332550049</v>
       </c>
       <c r="H64" t="n">
         <v>538910</v>
@@ -2312,7 +2312,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G67" t="n">
-        <v>18.833667755127</v>
+        <v>18.8336658477783</v>
       </c>
       <c r="H67" t="n">
         <v>490898</v>
@@ -2341,7 +2341,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G68" t="n">
-        <v>18.5151996612549</v>
+        <v>18.5152034759521</v>
       </c>
       <c r="H68" t="n">
         <v>449428</v>
@@ -2370,7 +2370,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>18.9309730529785</v>
+        <v>18.9309711456299</v>
       </c>
       <c r="H69" t="n">
         <v>499244</v>
@@ -2428,7 +2428,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G71" t="n">
-        <v>18.5240440368652</v>
+        <v>18.5240459442139</v>
       </c>
       <c r="H71" t="n">
         <v>1288923</v>
@@ -2457,7 +2457,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G72" t="n">
-        <v>19.3113613128662</v>
+        <v>19.3113632202148</v>
       </c>
       <c r="H72" t="n">
         <v>724111</v>
@@ -2486,7 +2486,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>18.9486656188965</v>
+        <v>18.9486675262451</v>
       </c>
       <c r="H73" t="n">
         <v>659167</v>
@@ -2515,7 +2515,7 @@
         <v>21.25</v>
       </c>
       <c r="G74" t="n">
-        <v>18.7982788085938</v>
+        <v>18.7982807159424</v>
       </c>
       <c r="H74" t="n">
         <v>401285</v>
@@ -2602,7 +2602,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G77" t="n">
-        <v>18.8071250915527</v>
+        <v>18.8071269989014</v>
       </c>
       <c r="H77" t="n">
         <v>725644</v>
@@ -2689,7 +2689,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G80" t="n">
-        <v>17.8251914978027</v>
+        <v>17.8251934051514</v>
       </c>
       <c r="H80" t="n">
         <v>550622</v>
@@ -2776,7 +2776,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>18.3117370605469</v>
+        <v>18.3117389678955</v>
       </c>
       <c r="H83" t="n">
         <v>593433</v>
@@ -2834,7 +2834,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>18.0021190643311</v>
+        <v>18.0021171569824</v>
       </c>
       <c r="H85" t="n">
         <v>455661</v>
@@ -2863,7 +2863,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G86" t="n">
-        <v>17.7190418243408</v>
+        <v>17.7190399169922</v>
       </c>
       <c r="H86" t="n">
         <v>401376</v>
@@ -2892,7 +2892,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G87" t="n">
-        <v>17.9048099517822</v>
+        <v>17.9048080444336</v>
       </c>
       <c r="H87" t="n">
         <v>346687</v>
@@ -2950,7 +2950,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G89" t="n">
-        <v>17.1440296173096</v>
+        <v>17.1440334320068</v>
       </c>
       <c r="H89" t="n">
         <v>741696</v>
@@ -3037,7 +3037,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>17.6394233703613</v>
+        <v>17.6394214630127</v>
       </c>
       <c r="H92" t="n">
         <v>678917</v>
@@ -3095,7 +3095,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G94" t="n">
-        <v>18.833667755127</v>
+        <v>18.8336658477783</v>
       </c>
       <c r="H94" t="n">
         <v>1861606</v>
@@ -3124,7 +3124,7 @@
         <v>21.25</v>
       </c>
       <c r="G95" t="n">
-        <v>18.7982788085938</v>
+        <v>18.7982807159424</v>
       </c>
       <c r="H95" t="n">
         <v>742962</v>
@@ -3240,7 +3240,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G99" t="n">
-        <v>17.6482677459717</v>
+        <v>17.6482696533203</v>
       </c>
       <c r="H99" t="n">
         <v>692686</v>
@@ -3298,7 +3298,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G101" t="n">
-        <v>17.8112564086914</v>
+        <v>17.81125831604</v>
       </c>
       <c r="H101" t="n">
         <v>334331</v>
@@ -3356,7 +3356,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G103" t="n">
-        <v>17.6482677459717</v>
+        <v>17.6482696533203</v>
       </c>
       <c r="H103" t="n">
         <v>568202</v>
@@ -3472,7 +3472,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G107" t="n">
-        <v>17.3041763305664</v>
+        <v>17.3041744232178</v>
       </c>
       <c r="H107" t="n">
         <v>353691</v>
@@ -3617,7 +3617,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>17.7478713989258</v>
+        <v>17.7478733062744</v>
       </c>
       <c r="H112" t="n">
         <v>286254</v>
@@ -3646,7 +3646,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G113" t="n">
-        <v>17.6844863891602</v>
+        <v>17.6844882965088</v>
       </c>
       <c r="H113" t="n">
         <v>347407</v>
@@ -3675,7 +3675,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G114" t="n">
-        <v>17.1502418518066</v>
+        <v>17.150239944458</v>
       </c>
       <c r="H114" t="n">
         <v>471820</v>
@@ -3733,7 +3733,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G116" t="n">
-        <v>16.5435523986816</v>
+        <v>16.5435543060303</v>
       </c>
       <c r="H116" t="n">
         <v>483555</v>
@@ -3762,7 +3762,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G117" t="n">
-        <v>17.0415782928467</v>
+        <v>17.0415802001953</v>
       </c>
       <c r="H117" t="n">
         <v>604342</v>
@@ -3791,7 +3791,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G118" t="n">
-        <v>17.0777988433838</v>
+        <v>17.0778007507324</v>
       </c>
       <c r="H118" t="n">
         <v>634094</v>
@@ -3849,7 +3849,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G120" t="n">
-        <v>17.9380283355713</v>
+        <v>17.9380264282227</v>
       </c>
       <c r="H120" t="n">
         <v>766211</v>
@@ -3878,7 +3878,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G121" t="n">
-        <v>17.7297630310059</v>
+        <v>17.7297611236572</v>
       </c>
       <c r="H121" t="n">
         <v>523740</v>
@@ -3936,7 +3936,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G123" t="n">
-        <v>18.1825160980225</v>
+        <v>18.1825141906738</v>
       </c>
       <c r="H123" t="n">
         <v>467685</v>
@@ -3994,7 +3994,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>16.3896198272705</v>
+        <v>16.3896179199219</v>
       </c>
       <c r="H125" t="n">
         <v>973572</v>
@@ -4023,7 +4023,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G126" t="n">
-        <v>16.6793804168701</v>
+        <v>16.6793785095215</v>
       </c>
       <c r="H126" t="n">
         <v>635006</v>
@@ -4052,7 +4052,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G127" t="n">
-        <v>16.2628479003906</v>
+        <v>16.2628440856934</v>
       </c>
       <c r="H127" t="n">
         <v>670056</v>
@@ -4081,7 +4081,7 @@
         <v>18.25</v>
       </c>
       <c r="G128" t="n">
-        <v>16.5254421234131</v>
+        <v>16.5254440307617</v>
       </c>
       <c r="H128" t="n">
         <v>558415</v>
@@ -4139,7 +4139,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G130" t="n">
-        <v>16.8061466217041</v>
+        <v>16.8061485290527</v>
       </c>
       <c r="H130" t="n">
         <v>255804</v>
@@ -4226,7 +4226,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G133" t="n">
-        <v>15.8734788894653</v>
+        <v>15.8734798431396</v>
       </c>
       <c r="H133" t="n">
         <v>652419</v>
@@ -4255,7 +4255,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G134" t="n">
-        <v>16.3624534606934</v>
+        <v>16.3624496459961</v>
       </c>
       <c r="H134" t="n">
         <v>562960</v>
@@ -4284,7 +4284,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G135" t="n">
-        <v>16.4439468383789</v>
+        <v>16.4439487457275</v>
       </c>
       <c r="H135" t="n">
         <v>444582</v>
@@ -4342,7 +4342,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G137" t="n">
-        <v>17.0959091186523</v>
+        <v>17.095911026001</v>
       </c>
       <c r="H137" t="n">
         <v>684185</v>
@@ -4429,7 +4429,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G140" t="n">
-        <v>17.1502418518066</v>
+        <v>17.150239944458</v>
       </c>
       <c r="H140" t="n">
         <v>545374</v>
@@ -4574,7 +4574,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G145" t="n">
-        <v>18.1372394561768</v>
+        <v>18.1372413635254</v>
       </c>
       <c r="H145" t="n">
         <v>615453</v>
@@ -4603,7 +4603,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>17.9289722442627</v>
+        <v>17.9289741516113</v>
       </c>
       <c r="H146" t="n">
         <v>894618</v>
@@ -4632,7 +4632,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G147" t="n">
-        <v>18.7710933685303</v>
+        <v>18.771089553833</v>
       </c>
       <c r="H147" t="n">
         <v>1164581</v>
@@ -4661,7 +4661,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>18.6352634429932</v>
+        <v>18.6352672576904</v>
       </c>
       <c r="H148" t="n">
         <v>873688</v>
@@ -4719,7 +4719,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G150" t="n">
-        <v>19.214786529541</v>
+        <v>19.2147903442383</v>
       </c>
       <c r="H150" t="n">
         <v>859181</v>
@@ -4748,7 +4748,7 @@
         <v>20.5699996948242</v>
       </c>
       <c r="G151" t="n">
-        <v>18.6262092590332</v>
+        <v>18.6262111663818</v>
       </c>
       <c r="H151" t="n">
         <v>1004411</v>
@@ -4777,7 +4777,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G152" t="n">
-        <v>18.4994430541992</v>
+        <v>18.4994411468506</v>
       </c>
       <c r="H152" t="n">
         <v>1504019</v>
@@ -4806,7 +4806,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G153" t="n">
-        <v>18.2187366485596</v>
+        <v>18.2187328338623</v>
       </c>
       <c r="H153" t="n">
         <v>1091340</v>
@@ -4835,7 +4835,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G154" t="n">
-        <v>18.716760635376</v>
+        <v>18.7167625427246</v>
       </c>
       <c r="H154" t="n">
         <v>930993</v>
@@ -4893,7 +4893,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G156" t="n">
-        <v>18.762035369873</v>
+        <v>18.7620372772217</v>
       </c>
       <c r="H156" t="n">
         <v>454171</v>
@@ -4922,7 +4922,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G157" t="n">
-        <v>18.4994430541992</v>
+        <v>18.4994411468506</v>
       </c>
       <c r="H157" t="n">
         <v>593471</v>
@@ -4951,7 +4951,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G158" t="n">
-        <v>18.8073120117188</v>
+        <v>18.8073139190674</v>
       </c>
       <c r="H158" t="n">
         <v>652271</v>
@@ -5009,7 +5009,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G160" t="n">
-        <v>19.0427417755127</v>
+        <v>19.04274559021</v>
       </c>
       <c r="H160" t="n">
         <v>612736</v>
@@ -5038,7 +5038,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G161" t="n">
-        <v>18.6624317169189</v>
+        <v>18.6624298095703</v>
       </c>
       <c r="H161" t="n">
         <v>488367</v>
@@ -5067,7 +5067,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G162" t="n">
-        <v>18.6624317169189</v>
+        <v>18.6624298095703</v>
       </c>
       <c r="H162" t="n">
         <v>278516</v>
@@ -5096,7 +5096,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>18.4722785949707</v>
+        <v>18.4722766876221</v>
       </c>
       <c r="H163" t="n">
         <v>404764</v>
@@ -5125,7 +5125,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G164" t="n">
-        <v>18.6171569824219</v>
+        <v>18.6171550750732</v>
       </c>
       <c r="H164" t="n">
         <v>346826</v>
@@ -5183,7 +5183,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>18.9703044891357</v>
+        <v>18.9703063964844</v>
       </c>
       <c r="H166" t="n">
         <v>796139</v>
@@ -5212,7 +5212,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G167" t="n">
-        <v>18.6805419921875</v>
+        <v>18.6805400848389</v>
       </c>
       <c r="H167" t="n">
         <v>579799</v>
@@ -5241,7 +5241,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G168" t="n">
-        <v>18.6080989837646</v>
+        <v>18.6081008911133</v>
       </c>
       <c r="H168" t="n">
         <v>405254</v>
@@ -5299,7 +5299,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G170" t="n">
-        <v>18.716760635376</v>
+        <v>18.7167625427246</v>
       </c>
       <c r="H170" t="n">
         <v>499477</v>
@@ -5357,7 +5357,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>18.6080989837646</v>
+        <v>18.6081008911133</v>
       </c>
       <c r="H172" t="n">
         <v>495370</v>
@@ -5386,7 +5386,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G173" t="n">
-        <v>18.870698928833</v>
+        <v>18.8706970214844</v>
       </c>
       <c r="H173" t="n">
         <v>440037</v>
@@ -5415,7 +5415,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>18.6986503601074</v>
+        <v>18.6986522674561</v>
       </c>
       <c r="H174" t="n">
         <v>355898</v>
@@ -5444,7 +5444,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G175" t="n">
-        <v>18.762035369873</v>
+        <v>18.7620372772217</v>
       </c>
       <c r="H175" t="n">
         <v>290570</v>
@@ -5473,7 +5473,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>19.1061305999756</v>
+        <v>19.1061267852783</v>
       </c>
       <c r="H176" t="n">
         <v>842459</v>
@@ -5502,7 +5502,7 @@
         <v>22</v>
       </c>
       <c r="G177" t="n">
-        <v>19.9210815429688</v>
+        <v>19.9210834503174</v>
       </c>
       <c r="H177" t="n">
         <v>1987857</v>
@@ -5531,7 +5531,7 @@
         <v>21.75</v>
       </c>
       <c r="G178" t="n">
-        <v>19.6947059631348</v>
+        <v>19.6947078704834</v>
       </c>
       <c r="H178" t="n">
         <v>1164964</v>
@@ -5560,7 +5560,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>19.5588798522949</v>
+        <v>19.5588779449463</v>
       </c>
       <c r="H179" t="n">
         <v>770378</v>
@@ -5589,7 +5589,7 @@
         <v>21.4899997711182</v>
       </c>
       <c r="G180" t="n">
-        <v>19.4592742919922</v>
+        <v>19.4592761993408</v>
       </c>
       <c r="H180" t="n">
         <v>700088</v>
@@ -5618,7 +5618,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G181" t="n">
-        <v>19.314395904541</v>
+        <v>19.3143939971924</v>
       </c>
       <c r="H181" t="n">
         <v>672599</v>
@@ -5647,7 +5647,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G182" t="n">
-        <v>18.8888092041016</v>
+        <v>18.8888072967529</v>
       </c>
       <c r="H182" t="n">
         <v>1048604</v>
@@ -5676,7 +5676,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G183" t="n">
-        <v>18.6805419921875</v>
+        <v>18.6805400848389</v>
       </c>
       <c r="H183" t="n">
         <v>1124488</v>
@@ -5705,7 +5705,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G184" t="n">
-        <v>19.1332931518555</v>
+        <v>19.1332912445068</v>
       </c>
       <c r="H184" t="n">
         <v>666175</v>
@@ -5734,7 +5734,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G185" t="n">
-        <v>18.7710933685303</v>
+        <v>18.771089553833</v>
       </c>
       <c r="H185" t="n">
         <v>702087</v>
@@ -5821,7 +5821,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G188" t="n">
-        <v>20.4553279876709</v>
+        <v>20.4553298950195</v>
       </c>
       <c r="H188" t="n">
         <v>1218252</v>
@@ -5879,7 +5879,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G190" t="n">
-        <v>20.4553279876709</v>
+        <v>20.4553298950195</v>
       </c>
       <c r="H190" t="n">
         <v>521478</v>
@@ -5966,7 +5966,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>20.4643859863281</v>
+        <v>20.4643840789795</v>
       </c>
       <c r="H193" t="n">
         <v>742714</v>
@@ -6024,7 +6024,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>20.6907615661621</v>
+        <v>20.6907596588135</v>
       </c>
       <c r="H195" t="n">
         <v>495248</v>
@@ -6053,7 +6053,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>20.8446960449219</v>
+        <v>20.8446941375732</v>
       </c>
       <c r="H196" t="n">
         <v>733993</v>
@@ -6111,7 +6111,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G198" t="n">
-        <v>20.4010009765625</v>
+        <v>20.4009990692139</v>
       </c>
       <c r="H198" t="n">
         <v>504761</v>
@@ -6140,7 +6140,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G199" t="n">
-        <v>20.1021842956543</v>
+        <v>20.1021862030029</v>
       </c>
       <c r="H199" t="n">
         <v>693101</v>
@@ -6169,7 +6169,7 @@
         <v>22.6700000762939</v>
       </c>
       <c r="G200" t="n">
-        <v>20.5277690887451</v>
+        <v>20.5277709960938</v>
       </c>
       <c r="H200" t="n">
         <v>729967</v>
@@ -6198,7 +6198,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>20.3647804260254</v>
+        <v>20.3647766113281</v>
       </c>
       <c r="H201" t="n">
         <v>435292</v>
@@ -6227,7 +6227,7 @@
         <v>22.6900005340576</v>
       </c>
       <c r="G202" t="n">
-        <v>20.545877456665</v>
+        <v>20.5458812713623</v>
       </c>
       <c r="H202" t="n">
         <v>571600</v>
@@ -6256,7 +6256,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G203" t="n">
-        <v>20.7541465759277</v>
+        <v>20.7541484832764</v>
       </c>
       <c r="H203" t="n">
         <v>761654</v>
@@ -6285,7 +6285,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>20.4191074371338</v>
+        <v>20.4191093444824</v>
       </c>
       <c r="H204" t="n">
         <v>692871</v>
@@ -6314,7 +6314,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>20.0116310119629</v>
+        <v>20.0116329193115</v>
       </c>
       <c r="H205" t="n">
         <v>933957</v>
@@ -6372,7 +6372,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>20.3285579681396</v>
+        <v>20.3285617828369</v>
       </c>
       <c r="H207" t="n">
         <v>362070</v>
@@ -6430,7 +6430,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G209" t="n">
-        <v>20.03879737854</v>
+        <v>20.0387954711914</v>
       </c>
       <c r="H209" t="n">
         <v>380492</v>
@@ -6459,7 +6459,7 @@
         <v>22.25</v>
       </c>
       <c r="G210" t="n">
-        <v>20.1474571228027</v>
+        <v>20.1474590301514</v>
       </c>
       <c r="H210" t="n">
         <v>323432</v>
@@ -6488,7 +6488,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G211" t="n">
-        <v>20.2289543151855</v>
+        <v>20.2289524078369</v>
       </c>
       <c r="H211" t="n">
         <v>476244</v>
@@ -6517,7 +6517,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G212" t="n">
-        <v>20.5006046295166</v>
+        <v>20.5006065368652</v>
       </c>
       <c r="H212" t="n">
         <v>513406</v>
@@ -6546,7 +6546,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G213" t="n">
-        <v>20.5639877319336</v>
+        <v>20.5639896392822</v>
       </c>
       <c r="H213" t="n">
         <v>450892</v>
@@ -6604,7 +6604,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G215" t="n">
-        <v>20.03879737854</v>
+        <v>20.0387954711914</v>
       </c>
       <c r="H215" t="n">
         <v>225022</v>
@@ -6720,7 +6720,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G219" t="n">
-        <v>19.7218723297119</v>
+        <v>19.7218704223633</v>
       </c>
       <c r="H219" t="n">
         <v>366831</v>
@@ -6749,7 +6749,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G220" t="n">
-        <v>19.7943134307861</v>
+        <v>19.7943115234375</v>
       </c>
       <c r="H220" t="n">
         <v>211848</v>
@@ -6778,7 +6778,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G221" t="n">
-        <v>19.5226593017578</v>
+        <v>19.5226612091064</v>
       </c>
       <c r="H221" t="n">
         <v>845010</v>
@@ -6807,7 +6807,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>19.830530166626</v>
+        <v>19.8305282592773</v>
       </c>
       <c r="H222" t="n">
         <v>720123</v>
@@ -6865,7 +6865,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G224" t="n">
-        <v>19.7490367889404</v>
+        <v>19.7490348815918</v>
       </c>
       <c r="H224" t="n">
         <v>454641</v>
@@ -6894,7 +6894,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.4722785949707</v>
+        <v>18.4722766876221</v>
       </c>
       <c r="H225" t="n">
         <v>3206760</v>
@@ -6981,7 +6981,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G228" t="n">
-        <v>18.3273963928223</v>
+        <v>18.3273944854736</v>
       </c>
       <c r="H228" t="n">
         <v>773547</v>
@@ -7010,7 +7010,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>18.2458992004395</v>
+        <v>18.2459011077881</v>
       </c>
       <c r="H229" t="n">
         <v>502752</v>
@@ -7039,7 +7039,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G230" t="n">
-        <v>18.0104675292969</v>
+        <v>18.0104713439941</v>
       </c>
       <c r="H230" t="n">
         <v>460171</v>
@@ -7097,7 +7097,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G232" t="n">
-        <v>17.8565330505371</v>
+        <v>17.8565311431885</v>
       </c>
       <c r="H232" t="n">
         <v>279823</v>
@@ -7126,7 +7126,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>17.8203125</v>
+        <v>17.8203144073486</v>
       </c>
       <c r="H233" t="n">
         <v>203127</v>
@@ -7184,7 +7184,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G235" t="n">
-        <v>18.3455066680908</v>
+        <v>18.3455028533936</v>
       </c>
       <c r="H235" t="n">
         <v>701529</v>
@@ -7213,7 +7213,7 @@
         <v>20.3099994659424</v>
       </c>
       <c r="G236" t="n">
-        <v>18.3907794952393</v>
+        <v>18.3907775878906</v>
       </c>
       <c r="H236" t="n">
         <v>402506</v>
@@ -7242,7 +7242,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G237" t="n">
-        <v>18.8073120117188</v>
+        <v>18.8073139190674</v>
       </c>
       <c r="H237" t="n">
         <v>711240</v>
@@ -7271,7 +7271,7 @@
         <v>20.6700000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>18.716760635376</v>
+        <v>18.7167625427246</v>
       </c>
       <c r="H238" t="n">
         <v>591668</v>
@@ -7300,7 +7300,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G239" t="n">
-        <v>18.870698928833</v>
+        <v>18.8706970214844</v>
       </c>
       <c r="H239" t="n">
         <v>825902</v>
@@ -7329,7 +7329,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>19.1514053344727</v>
+        <v>19.151403427124</v>
       </c>
       <c r="H240" t="n">
         <v>521430</v>
@@ -7358,7 +7358,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>19.2872276306152</v>
+        <v>19.2872295379639</v>
       </c>
       <c r="H241" t="n">
         <v>673068</v>
@@ -7503,7 +7503,7 @@
         <v>21.2700004577637</v>
       </c>
       <c r="G246" t="n">
-        <v>19.260066986084</v>
+        <v>19.2600631713867</v>
       </c>
       <c r="H246" t="n">
         <v>348399</v>
@@ -7532,7 +7532,7 @@
         <v>21.75</v>
       </c>
       <c r="G247" t="n">
-        <v>19.6947059631348</v>
+        <v>19.6947078704834</v>
       </c>
       <c r="H247" t="n">
         <v>551071</v>
@@ -7648,7 +7648,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G251" t="n">
-        <v>20.3466663360596</v>
+        <v>20.3466682434082</v>
       </c>
       <c r="H251" t="n">
         <v>359013</v>
@@ -7677,7 +7677,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>20.2380084991455</v>
+        <v>20.2380065917969</v>
       </c>
       <c r="H252" t="n">
         <v>230612</v>
@@ -7706,7 +7706,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G253" t="n">
-        <v>20.1293487548828</v>
+        <v>20.1293468475342</v>
       </c>
       <c r="H253" t="n">
         <v>311609</v>
@@ -7764,7 +7764,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>20.2289543151855</v>
+        <v>20.2289524078369</v>
       </c>
       <c r="H255" t="n">
         <v>284063</v>
@@ -7793,7 +7793,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>20.1565132141113</v>
+        <v>20.15651512146</v>
       </c>
       <c r="H256" t="n">
         <v>178380</v>
@@ -7880,7 +7880,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G259" t="n">
-        <v>20.6183204650879</v>
+        <v>20.6183185577393</v>
       </c>
       <c r="H259" t="n">
         <v>666000</v>
@@ -7909,7 +7909,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G260" t="n">
-        <v>21.4785461425781</v>
+        <v>21.4785499572754</v>
       </c>
       <c r="H260" t="n">
         <v>1705785</v>
@@ -7967,7 +7967,7 @@
         <v>24.3700008392334</v>
       </c>
       <c r="G262" t="n">
-        <v>22.0671272277832</v>
+        <v>22.0671253204346</v>
       </c>
       <c r="H262" t="n">
         <v>1062423</v>
@@ -7996,7 +7996,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G263" t="n">
-        <v>22.0580730438232</v>
+        <v>22.0580711364746</v>
       </c>
       <c r="H263" t="n">
         <v>1362031</v>
@@ -8054,7 +8054,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G265" t="n">
-        <v>22.2935028076172</v>
+        <v>22.2934989929199</v>
       </c>
       <c r="H265" t="n">
         <v>1130923</v>
@@ -8083,7 +8083,7 @@
         <v>24.6299991607666</v>
       </c>
       <c r="G266" t="n">
-        <v>22.3025569915771</v>
+        <v>22.3025550842285</v>
       </c>
       <c r="H266" t="n">
         <v>604896</v>
@@ -8112,7 +8112,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>22.3206672668457</v>
+        <v>22.3206634521484</v>
       </c>
       <c r="H267" t="n">
         <v>414459</v>
@@ -8199,7 +8199,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G270" t="n">
-        <v>22.8186950683594</v>
+        <v>22.8186931610107</v>
       </c>
       <c r="H270" t="n">
         <v>1130838</v>
@@ -8228,7 +8228,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G271" t="n">
-        <v>23.0722332000732</v>
+        <v>23.0722370147705</v>
       </c>
       <c r="H271" t="n">
         <v>906513</v>
@@ -8257,7 +8257,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G272" t="n">
-        <v>22.8911361694336</v>
+        <v>22.891134262085</v>
       </c>
       <c r="H272" t="n">
         <v>650968</v>
@@ -8286,7 +8286,7 @@
         <v>25.5699996948242</v>
       </c>
       <c r="G273" t="n">
-        <v>23.1537284851074</v>
+        <v>23.1537303924561</v>
       </c>
       <c r="H273" t="n">
         <v>1005467</v>
@@ -8373,7 +8373,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G276" t="n">
-        <v>22.3568840026855</v>
+        <v>22.3568859100342</v>
       </c>
       <c r="H276" t="n">
         <v>736861</v>
@@ -8402,7 +8402,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>22.9092445373535</v>
+        <v>22.9092426300049</v>
       </c>
       <c r="H277" t="n">
         <v>1129609</v>
@@ -8431,7 +8431,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G278" t="n">
-        <v>22.1757869720459</v>
+        <v>22.1757888793945</v>
       </c>
       <c r="H278" t="n">
         <v>1066573</v>
@@ -8460,7 +8460,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G279" t="n">
-        <v>22.1395645141602</v>
+        <v>22.1395664215088</v>
       </c>
       <c r="H279" t="n">
         <v>498087</v>
@@ -8489,7 +8489,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G280" t="n">
-        <v>23.6064834594727</v>
+        <v>23.606481552124</v>
       </c>
       <c r="H280" t="n">
         <v>2579913</v>
@@ -8547,7 +8547,7 @@
         <v>26.6399993896484</v>
       </c>
       <c r="G282" t="n">
-        <v>24.1226177215576</v>
+        <v>24.1226196289062</v>
       </c>
       <c r="H282" t="n">
         <v>1541926</v>
@@ -8605,7 +8605,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G284" t="n">
-        <v>23.6879768371582</v>
+        <v>23.6879787445068</v>
       </c>
       <c r="H284" t="n">
         <v>648062</v>
@@ -8721,7 +8721,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>23.7241992950439</v>
+        <v>23.7241973876953</v>
       </c>
       <c r="H288" t="n">
         <v>395279</v>
@@ -8779,7 +8779,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G290" t="n">
-        <v>23.6879768371582</v>
+        <v>23.6879787445068</v>
       </c>
       <c r="H290" t="n">
         <v>721884</v>
@@ -8808,7 +8808,7 @@
         <v>26.3099994659424</v>
       </c>
       <c r="G291" t="n">
-        <v>23.823802947998</v>
+        <v>23.8238010406494</v>
       </c>
       <c r="H291" t="n">
         <v>504205</v>
@@ -8837,7 +8837,7 @@
         <v>26.1700000762939</v>
       </c>
       <c r="G292" t="n">
-        <v>23.6970329284668</v>
+        <v>23.6970310211182</v>
       </c>
       <c r="H292" t="n">
         <v>236982</v>
@@ -8866,7 +8866,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G293" t="n">
-        <v>23.7241992950439</v>
+        <v>23.7241973876953</v>
       </c>
       <c r="H293" t="n">
         <v>138589</v>
@@ -8895,7 +8895,7 @@
         <v>26.5200004577637</v>
       </c>
       <c r="G294" t="n">
-        <v>24.0139579772949</v>
+        <v>24.0139598846436</v>
       </c>
       <c r="H294" t="n">
         <v>741091</v>
@@ -8953,7 +8953,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>24.068286895752</v>
+        <v>24.0682907104492</v>
       </c>
       <c r="H296" t="n">
         <v>653226</v>
@@ -8982,7 +8982,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>23.9777355194092</v>
+        <v>23.9777393341064</v>
       </c>
       <c r="H297" t="n">
         <v>812325</v>
@@ -9011,7 +9011,7 @@
         <v>26.8299999237061</v>
       </c>
       <c r="G298" t="n">
-        <v>24.2946643829346</v>
+        <v>24.2946662902832</v>
       </c>
       <c r="H298" t="n">
         <v>540551</v>
@@ -9040,7 +9040,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G299" t="n">
-        <v>24.4304885864258</v>
+        <v>24.4304904937744</v>
       </c>
       <c r="H299" t="n">
         <v>1219756</v>
@@ -9069,7 +9069,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G300" t="n">
-        <v>24.61159324646</v>
+        <v>24.6115913391113</v>
       </c>
       <c r="H300" t="n">
         <v>640558</v>
@@ -9098,7 +9098,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>24.7655277252197</v>
+        <v>24.7655258178711</v>
       </c>
       <c r="H301" t="n">
         <v>889832</v>
@@ -9156,7 +9156,7 @@
         <v>28.0400009155273</v>
       </c>
       <c r="G303" t="n">
-        <v>25.390323638916</v>
+        <v>25.3903255462646</v>
       </c>
       <c r="H303" t="n">
         <v>911254</v>
@@ -9185,7 +9185,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G304" t="n">
-        <v>25.4265460968018</v>
+        <v>25.4265441894531</v>
       </c>
       <c r="H304" t="n">
         <v>549504</v>
@@ -9243,7 +9243,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>25.671028137207</v>
+        <v>25.6710319519043</v>
       </c>
       <c r="H306" t="n">
         <v>500694</v>
@@ -9272,7 +9272,7 @@
         <v>28.3299999237061</v>
       </c>
       <c r="G307" t="n">
-        <v>25.6529216766357</v>
+        <v>25.6529197692871</v>
       </c>
       <c r="H307" t="n">
         <v>363150</v>
@@ -9330,7 +9330,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>25.5352058410645</v>
+        <v>25.5352077484131</v>
       </c>
       <c r="H309" t="n">
         <v>734883</v>
@@ -9388,7 +9388,7 @@
         <v>27.5</v>
       </c>
       <c r="G311" t="n">
-        <v>24.9013519287109</v>
+        <v>24.9013538360596</v>
       </c>
       <c r="H311" t="n">
         <v>1035739</v>
@@ -9417,7 +9417,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>25.0643424987793</v>
+        <v>25.0643444061279</v>
       </c>
       <c r="H312" t="n">
         <v>650689</v>
@@ -9446,7 +9446,7 @@
         <v>27.3899993896484</v>
       </c>
       <c r="G313" t="n">
-        <v>24.8017482757568</v>
+        <v>24.8017463684082</v>
       </c>
       <c r="H313" t="n">
         <v>332263</v>
@@ -9475,7 +9475,7 @@
         <v>27.1900005340576</v>
       </c>
       <c r="G314" t="n">
-        <v>24.6206455230713</v>
+        <v>24.6206474304199</v>
       </c>
       <c r="H314" t="n">
         <v>412801</v>
@@ -9504,7 +9504,7 @@
         <v>27.5400009155273</v>
       </c>
       <c r="G315" t="n">
-        <v>24.937572479248</v>
+        <v>24.9375743865967</v>
       </c>
       <c r="H315" t="n">
         <v>486126</v>
@@ -9533,7 +9533,7 @@
         <v>28.0200004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>25.3722152709961</v>
+        <v>25.3722133636475</v>
       </c>
       <c r="H316" t="n">
         <v>452765</v>
@@ -9591,7 +9591,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G318" t="n">
-        <v>25.2273349761963</v>
+        <v>25.2273330688477</v>
       </c>
       <c r="H318" t="n">
         <v>385409</v>
@@ -9620,7 +9620,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>25.173002243042</v>
+        <v>25.1730041503906</v>
       </c>
       <c r="H319" t="n">
         <v>545914</v>
@@ -9678,7 +9678,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>25.3993797302246</v>
+        <v>25.399377822876</v>
       </c>
       <c r="H321" t="n">
         <v>203615</v>
@@ -9707,7 +9707,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G322" t="n">
-        <v>25.4265460968018</v>
+        <v>25.4265441894531</v>
       </c>
       <c r="H322" t="n">
         <v>230403</v>
@@ -9736,7 +9736,7 @@
         <v>28.4099998474121</v>
       </c>
       <c r="G323" t="n">
-        <v>25.72536277771</v>
+        <v>25.7253608703613</v>
       </c>
       <c r="H323" t="n">
         <v>704929</v>
@@ -9794,7 +9794,7 @@
         <v>27.75</v>
       </c>
       <c r="G325" t="n">
-        <v>25.1277275085449</v>
+        <v>25.1277294158936</v>
       </c>
       <c r="H325" t="n">
         <v>265673</v>
@@ -9852,7 +9852,7 @@
         <v>28.2099990844727</v>
       </c>
       <c r="G327" t="n">
-        <v>25.5442600250244</v>
+        <v>25.5442581176758</v>
       </c>
       <c r="H327" t="n">
         <v>365212</v>
@@ -9881,7 +9881,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G328" t="n">
-        <v>25.4808750152588</v>
+        <v>25.4808731079102</v>
       </c>
       <c r="H328" t="n">
         <v>240731</v>
@@ -9939,7 +9939,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>25.2635517120361</v>
+        <v>25.2635536193848</v>
       </c>
       <c r="H330" t="n">
         <v>387257</v>
@@ -9997,7 +9997,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G332" t="n">
-        <v>24.7836418151855</v>
+        <v>24.7836380004883</v>
       </c>
       <c r="H332" t="n">
         <v>660230</v>
@@ -10055,7 +10055,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>24.7655277252197</v>
+        <v>24.7655258178711</v>
       </c>
       <c r="H334" t="n">
         <v>653524</v>
@@ -10142,7 +10142,7 @@
         <v>28.1900005340576</v>
       </c>
       <c r="G337" t="n">
-        <v>25.5261516571045</v>
+        <v>25.5261497497559</v>
       </c>
       <c r="H337" t="n">
         <v>379396</v>
@@ -10200,7 +10200,7 @@
         <v>28.9200000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>26.1871681213379</v>
+        <v>26.1871662139893</v>
       </c>
       <c r="H339" t="n">
         <v>548992</v>
@@ -10258,7 +10258,7 @@
         <v>29.25</v>
       </c>
       <c r="G341" t="n">
-        <v>26.4859867095947</v>
+        <v>26.4859828948975</v>
       </c>
       <c r="H341" t="n">
         <v>324279</v>
@@ -10345,7 +10345,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>26.893461227417</v>
+        <v>26.8934593200684</v>
       </c>
       <c r="H344" t="n">
         <v>349802</v>
@@ -10374,7 +10374,7 @@
         <v>29</v>
       </c>
       <c r="G345" t="n">
-        <v>26.2596073150635</v>
+        <v>26.2596092224121</v>
       </c>
       <c r="H345" t="n">
         <v>806664</v>
@@ -10403,7 +10403,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>26.6670875549316</v>
+        <v>26.6670837402344</v>
       </c>
       <c r="H346" t="n">
         <v>297569</v>
@@ -10490,7 +10490,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G349" t="n">
-        <v>26.6037006378174</v>
+        <v>26.6036987304688</v>
       </c>
       <c r="H349" t="n">
         <v>284270</v>
@@ -10548,7 +10548,7 @@
         <v>29</v>
       </c>
       <c r="G351" t="n">
-        <v>26.2596073150635</v>
+        <v>26.2596092224121</v>
       </c>
       <c r="H351" t="n">
         <v>536086</v>
@@ -10606,7 +10606,7 @@
         <v>27.9699993133545</v>
       </c>
       <c r="G353" t="n">
-        <v>25.3269386291504</v>
+        <v>25.3269367218018</v>
       </c>
       <c r="H353" t="n">
         <v>304075</v>
@@ -10635,7 +10635,7 @@
         <v>28.5300006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>25.8340225219727</v>
+        <v>25.834020614624</v>
       </c>
       <c r="H354" t="n">
         <v>490864</v>
@@ -10664,7 +10664,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G355" t="n">
-        <v>25.8984451293945</v>
+        <v>25.8984413146973</v>
       </c>
       <c r="H355" t="n">
         <v>233836</v>
@@ -10809,7 +10809,7 @@
         <v>25.1299991607666</v>
       </c>
       <c r="G360" t="n">
-        <v>23.1282119750977</v>
+        <v>23.128210067749</v>
       </c>
       <c r="H360" t="n">
         <v>474720</v>
@@ -10838,7 +10838,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>22.9625492095947</v>
+        <v>22.962553024292</v>
       </c>
       <c r="H361" t="n">
         <v>858119</v>
@@ -10867,7 +10867,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>22.8705177307129</v>
+        <v>22.8705196380615</v>
       </c>
       <c r="H362" t="n">
         <v>814408</v>
@@ -10896,7 +10896,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G363" t="n">
-        <v>22.8613128662109</v>
+        <v>22.8613147735596</v>
       </c>
       <c r="H363" t="n">
         <v>526890</v>
@@ -10983,7 +10983,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G366" t="n">
-        <v>23.0453815460205</v>
+        <v>23.0453834533691</v>
       </c>
       <c r="H366" t="n">
         <v>445068</v>
@@ -11041,7 +11041,7 @@
         <v>24</v>
       </c>
       <c r="G368" t="n">
-        <v>22.088228225708</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H368" t="n">
         <v>1374366</v>
@@ -11099,7 +11099,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>22.2262763977051</v>
+        <v>22.2262744903564</v>
       </c>
       <c r="H370" t="n">
         <v>332429</v>
@@ -11157,7 +11157,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>22.3643283843994</v>
+        <v>22.364330291748</v>
       </c>
       <c r="H372" t="n">
         <v>603189</v>
@@ -11186,7 +11186,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G373" t="n">
-        <v>22.7416687011719</v>
+        <v>22.7416706085205</v>
       </c>
       <c r="H373" t="n">
         <v>827087</v>
@@ -11215,7 +11215,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G374" t="n">
-        <v>22.9533500671387</v>
+        <v>22.95334815979</v>
       </c>
       <c r="H374" t="n">
         <v>1434500</v>
@@ -11244,7 +11244,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G375" t="n">
-        <v>22.8797225952148</v>
+        <v>22.8797206878662</v>
       </c>
       <c r="H375" t="n">
         <v>368128</v>
@@ -11331,7 +11331,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G378" t="n">
-        <v>23.4319248199463</v>
+        <v>23.4319267272949</v>
       </c>
       <c r="H378" t="n">
         <v>355374</v>
@@ -11360,7 +11360,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G379" t="n">
-        <v>22.8060932159424</v>
+        <v>22.806095123291</v>
       </c>
       <c r="H379" t="n">
         <v>684365</v>
@@ -11389,7 +11389,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G380" t="n">
-        <v>23.0269737243652</v>
+        <v>23.0269775390625</v>
       </c>
       <c r="H380" t="n">
         <v>525690</v>
@@ -11418,7 +11418,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G381" t="n">
-        <v>22.6036167144775</v>
+        <v>22.6036148071289</v>
       </c>
       <c r="H381" t="n">
         <v>369901</v>
@@ -11447,7 +11447,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>22.253885269165</v>
+        <v>22.2538871765137</v>
       </c>
       <c r="H382" t="n">
         <v>540961</v>
@@ -11476,7 +11476,7 @@
         <v>23.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>21.5452213287354</v>
+        <v>21.545223236084</v>
       </c>
       <c r="H383" t="n">
         <v>915042</v>
@@ -11505,7 +11505,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>21.4900035858154</v>
+        <v>21.4900016784668</v>
       </c>
       <c r="H384" t="n">
         <v>361338</v>
@@ -11563,7 +11563,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G386" t="n">
-        <v>21.5544261932373</v>
+        <v>21.5544242858887</v>
       </c>
       <c r="H386" t="n">
         <v>216910</v>
@@ -11592,7 +11592,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>21.6740684509277</v>
+        <v>21.674072265625</v>
       </c>
       <c r="H387" t="n">
         <v>321536</v>
@@ -11621,7 +11621,7 @@
         <v>23.5</v>
       </c>
       <c r="G388" t="n">
-        <v>21.6280536651611</v>
+        <v>21.6280555725098</v>
       </c>
       <c r="H388" t="n">
         <v>357459</v>
@@ -11650,7 +11650,7 @@
         <v>23</v>
       </c>
       <c r="G389" t="n">
-        <v>21.1678829193115</v>
+        <v>21.1678848266602</v>
       </c>
       <c r="H389" t="n">
         <v>501698</v>
@@ -11679,7 +11679,7 @@
         <v>23</v>
       </c>
       <c r="G390" t="n">
-        <v>21.1678829193115</v>
+        <v>21.1678848266602</v>
       </c>
       <c r="H390" t="n">
         <v>281095</v>
@@ -11708,7 +11708,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G391" t="n">
-        <v>21.2046966552734</v>
+        <v>21.2046985626221</v>
       </c>
       <c r="H391" t="n">
         <v>426099</v>
@@ -11795,7 +11795,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G394" t="n">
-        <v>21.5084095001221</v>
+        <v>21.5084114074707</v>
       </c>
       <c r="H394" t="n">
         <v>401727</v>
@@ -11882,7 +11882,7 @@
         <v>23.8700008392334</v>
       </c>
       <c r="G397" t="n">
-        <v>21.9685840606689</v>
+        <v>21.9685821533203</v>
       </c>
       <c r="H397" t="n">
         <v>424576</v>
@@ -11940,7 +11940,7 @@
         <v>24.3099994659424</v>
       </c>
       <c r="G399" t="n">
-        <v>22.3735313415527</v>
+        <v>22.3735294342041</v>
       </c>
       <c r="H399" t="n">
         <v>712169</v>
@@ -11969,7 +11969,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G400" t="n">
-        <v>22.2170734405518</v>
+        <v>22.2170715332031</v>
       </c>
       <c r="H400" t="n">
         <v>358847</v>
@@ -11998,7 +11998,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G401" t="n">
-        <v>22.4103450775146</v>
+        <v>22.4103469848633</v>
       </c>
       <c r="H401" t="n">
         <v>372937</v>
@@ -12085,7 +12085,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G404" t="n">
-        <v>22.6404342651367</v>
+        <v>22.6404323577881</v>
       </c>
       <c r="H404" t="n">
         <v>432144</v>
@@ -12143,7 +12143,7 @@
         <v>24</v>
       </c>
       <c r="G406" t="n">
-        <v>22.088228225708</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H406" t="n">
         <v>1576783</v>
@@ -12230,7 +12230,7 @@
         <v>24</v>
       </c>
       <c r="G409" t="n">
-        <v>22.088228225708</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H409" t="n">
         <v>517420</v>
@@ -12288,7 +12288,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G411" t="n">
-        <v>22.539192199707</v>
+        <v>22.5391941070557</v>
       </c>
       <c r="H411" t="n">
         <v>497939</v>
@@ -12375,7 +12375,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G414" t="n">
-        <v>22.0514106750488</v>
+        <v>22.0514125823975</v>
       </c>
       <c r="H414" t="n">
         <v>315380</v>
@@ -12433,7 +12433,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G416" t="n">
-        <v>22.7876853942871</v>
+        <v>22.7876873016357</v>
       </c>
       <c r="H416" t="n">
         <v>366146</v>
@@ -12491,7 +12491,7 @@
         <v>24.0300006866455</v>
       </c>
       <c r="G418" t="n">
-        <v>22.1158351898193</v>
+        <v>22.1158390045166</v>
       </c>
       <c r="H418" t="n">
         <v>245071</v>
@@ -12520,7 +12520,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>21.7661056518555</v>
+        <v>21.7661037445068</v>
       </c>
       <c r="H419" t="n">
         <v>234785</v>
@@ -12549,7 +12549,7 @@
         <v>23.9699993133545</v>
       </c>
       <c r="G420" t="n">
-        <v>22.0606155395508</v>
+        <v>22.0606136322021</v>
       </c>
       <c r="H420" t="n">
         <v>197206</v>
@@ -12578,7 +12578,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G421" t="n">
-        <v>21.7569026947021</v>
+        <v>21.7569007873535</v>
       </c>
       <c r="H421" t="n">
         <v>283848</v>
@@ -12636,7 +12636,7 @@
         <v>24</v>
       </c>
       <c r="G423" t="n">
-        <v>22.088228225708</v>
+        <v>22.0882263183594</v>
       </c>
       <c r="H423" t="n">
         <v>206329</v>
@@ -12665,7 +12665,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>21.9961929321289</v>
+        <v>21.9961891174316</v>
       </c>
       <c r="H424" t="n">
         <v>138330</v>
@@ -12723,7 +12723,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G426" t="n">
-        <v>22.0053958892822</v>
+        <v>22.0053939819336</v>
       </c>
       <c r="H426" t="n">
         <v>237338</v>
@@ -12752,7 +12752,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G427" t="n">
-        <v>22.2170734405518</v>
+        <v>22.2170715332031</v>
       </c>
       <c r="H427" t="n">
         <v>537878</v>
@@ -12810,7 +12810,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G429" t="n">
-        <v>22.0053958892822</v>
+        <v>22.0053939819336</v>
       </c>
       <c r="H429" t="n">
         <v>233703</v>
@@ -12984,7 +12984,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G435" t="n">
-        <v>21.9961929321289</v>
+        <v>21.9961891174316</v>
       </c>
       <c r="H435" t="n">
         <v>619938</v>
@@ -13013,7 +13013,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>21.9041557312012</v>
+        <v>21.9041576385498</v>
       </c>
       <c r="H436" t="n">
         <v>1117273</v>
@@ -13071,7 +13071,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G438" t="n">
-        <v>20.8273544311523</v>
+        <v>20.827356338501</v>
       </c>
       <c r="H438" t="n">
         <v>1417619</v>
@@ -13100,7 +13100,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G439" t="n">
-        <v>21.0574417114258</v>
+        <v>21.0574398040771</v>
       </c>
       <c r="H439" t="n">
         <v>1031440</v>
@@ -13129,7 +13129,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G440" t="n">
-        <v>20.94700050354</v>
+        <v>20.9470024108887</v>
       </c>
       <c r="H440" t="n">
         <v>418634</v>
@@ -13158,7 +13158,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>20.799747467041</v>
+        <v>20.7997436523438</v>
       </c>
       <c r="H441" t="n">
         <v>1083075</v>
@@ -13187,7 +13187,7 @@
         <v>22.9300003051758</v>
       </c>
       <c r="G442" t="n">
-        <v>21.103458404541</v>
+        <v>21.1034603118896</v>
       </c>
       <c r="H442" t="n">
         <v>361840</v>
@@ -13274,7 +13274,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>21.950174331665</v>
+        <v>21.9501762390137</v>
       </c>
       <c r="H445" t="n">
         <v>1478816</v>
@@ -13332,7 +13332,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G447" t="n">
-        <v>22.0514106750488</v>
+        <v>22.0514125823975</v>
       </c>
       <c r="H447" t="n">
         <v>633441</v>
@@ -13361,7 +13361,7 @@
         <v>23.75</v>
       </c>
       <c r="G448" t="n">
-        <v>21.8581371307373</v>
+        <v>21.8581428527832</v>
       </c>
       <c r="H448" t="n">
         <v>541964</v>
@@ -13448,7 +13448,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G451" t="n">
-        <v>21.2967319488525</v>
+        <v>21.2967300415039</v>
       </c>
       <c r="H451" t="n">
         <v>599089</v>
@@ -13506,7 +13506,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>20.799747467041</v>
+        <v>20.7997436523438</v>
       </c>
       <c r="H453" t="n">
         <v>536977</v>
@@ -13593,7 +13593,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G456" t="n">
-        <v>21.0666427612305</v>
+        <v>21.0666446685791</v>
       </c>
       <c r="H456" t="n">
         <v>654865</v>
@@ -13622,7 +13622,7 @@
         <v>22.5</v>
       </c>
       <c r="G457" t="n">
-        <v>20.7077102661133</v>
+        <v>20.7077121734619</v>
       </c>
       <c r="H457" t="n">
         <v>475690</v>
@@ -13709,7 +13709,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G460" t="n">
-        <v>21.0206298828125</v>
+        <v>21.0206260681152</v>
       </c>
       <c r="H460" t="n">
         <v>386462</v>
@@ -13738,7 +13738,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G461" t="n">
-        <v>21.0022201538086</v>
+        <v>21.0022220611572</v>
       </c>
       <c r="H461" t="n">
         <v>547355</v>
@@ -13767,7 +13767,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G462" t="n">
-        <v>20.6340827941895</v>
+        <v>20.6340847015381</v>
       </c>
       <c r="H462" t="n">
         <v>547658</v>
@@ -13825,7 +13825,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>20.385591506958</v>
+        <v>20.3855895996094</v>
       </c>
       <c r="H464" t="n">
         <v>619987</v>
@@ -13854,7 +13854,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G465" t="n">
-        <v>20.3947925567627</v>
+        <v>20.3947944641113</v>
       </c>
       <c r="H465" t="n">
         <v>664948</v>
@@ -13912,7 +13912,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>19.9714374542236</v>
+        <v>19.9714393615723</v>
       </c>
       <c r="H467" t="n">
         <v>1435364</v>
@@ -13941,7 +13941,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>20.0634708404541</v>
+        <v>20.0634727478027</v>
       </c>
       <c r="H468" t="n">
         <v>1097685</v>
@@ -13970,7 +13970,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G469" t="n">
-        <v>20.4868278503418</v>
+        <v>20.4868297576904</v>
       </c>
       <c r="H469" t="n">
         <v>471696</v>
@@ -14057,7 +14057,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G472" t="n">
-        <v>21.0206298828125</v>
+        <v>21.0206260681152</v>
       </c>
       <c r="H472" t="n">
         <v>601843</v>
@@ -14086,7 +14086,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G473" t="n">
-        <v>21.0666427612305</v>
+        <v>21.0666446685791</v>
       </c>
       <c r="H473" t="n">
         <v>317345</v>
@@ -14115,7 +14115,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G474" t="n">
-        <v>21.2415103912354</v>
+        <v>21.2415084838867</v>
       </c>
       <c r="H474" t="n">
         <v>971079</v>
@@ -14144,7 +14144,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G475" t="n">
-        <v>20.9285907745361</v>
+        <v>20.9285926818848</v>
       </c>
       <c r="H475" t="n">
         <v>884159</v>
@@ -14173,7 +14173,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G476" t="n">
-        <v>20.94700050354</v>
+        <v>20.9470024108887</v>
       </c>
       <c r="H476" t="n">
         <v>584780</v>
@@ -14202,7 +14202,7 @@
         <v>22.5</v>
       </c>
       <c r="G477" t="n">
-        <v>20.7077102661133</v>
+        <v>20.7077121734619</v>
       </c>
       <c r="H477" t="n">
         <v>777593</v>
@@ -14260,7 +14260,7 @@
         <v>21.9099998474121</v>
       </c>
       <c r="G479" t="n">
-        <v>20.1647090911865</v>
+        <v>20.1647109985352</v>
       </c>
       <c r="H479" t="n">
         <v>1350938</v>
@@ -14318,7 +14318,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G481" t="n">
-        <v>19.2719764709473</v>
+        <v>19.2719783782959</v>
       </c>
       <c r="H481" t="n">
         <v>2609341</v>
@@ -14347,7 +14347,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>19.695333480835</v>
+        <v>19.6953353881836</v>
       </c>
       <c r="H482" t="n">
         <v>1022782</v>
@@ -14463,7 +14463,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G486" t="n">
-        <v>20.0450668334961</v>
+        <v>20.0450630187988</v>
       </c>
       <c r="H486" t="n">
         <v>455042</v>
@@ -14579,7 +14579,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>20.6616954803467</v>
+        <v>20.6616973876953</v>
       </c>
       <c r="H490" t="n">
         <v>354523</v>
@@ -14666,7 +14666,7 @@
         <v>22.5</v>
       </c>
       <c r="G493" t="n">
-        <v>20.7077102661133</v>
+        <v>20.7077121734619</v>
       </c>
       <c r="H493" t="n">
         <v>633331</v>
@@ -14695,7 +14695,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G494" t="n">
-        <v>21.0482406616211</v>
+        <v>21.0482387542725</v>
       </c>
       <c r="H494" t="n">
         <v>362134</v>
@@ -14724,7 +14724,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G495" t="n">
-        <v>21.0022201538086</v>
+        <v>21.0022220611572</v>
       </c>
       <c r="H495" t="n">
         <v>401957</v>
@@ -14753,7 +14753,7 @@
         <v>23.0300006866455</v>
       </c>
       <c r="G496" t="n">
-        <v>21.1954936981201</v>
+        <v>21.1954956054688</v>
       </c>
       <c r="H496" t="n">
         <v>542335</v>
@@ -14898,7 +14898,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G501" t="n">
-        <v>20.6708965301514</v>
+        <v>20.6708984375</v>
       </c>
       <c r="H501" t="n">
         <v>483213</v>
@@ -14927,7 +14927,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G502" t="n">
-        <v>20.7721347808838</v>
+        <v>20.7721366882324</v>
       </c>
       <c r="H502" t="n">
         <v>621541</v>
@@ -14956,7 +14956,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>19.4652481079102</v>
+        <v>19.4652500152588</v>
       </c>
       <c r="H503" t="n">
         <v>2465735</v>
@@ -14985,7 +14985,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G504" t="n">
-        <v>19.796573638916</v>
+        <v>19.7965717315674</v>
       </c>
       <c r="H504" t="n">
         <v>852016</v>
@@ -15043,7 +15043,7 @@
         <v>21.75</v>
       </c>
       <c r="G506" t="n">
-        <v>20.0174522399902</v>
+        <v>20.0174541473389</v>
       </c>
       <c r="H506" t="n">
         <v>379082</v>
@@ -15130,7 +15130,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>20.229133605957</v>
+        <v>20.2291355133057</v>
       </c>
       <c r="H509" t="n">
         <v>191733</v>
@@ -15188,7 +15188,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G511" t="n">
-        <v>20.385591506958</v>
+        <v>20.3855895996094</v>
       </c>
       <c r="H511" t="n">
         <v>231800</v>
@@ -15246,7 +15246,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>20.5236415863037</v>
+        <v>20.5236434936523</v>
       </c>
       <c r="H513" t="n">
         <v>314606</v>
@@ -15362,7 +15362,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G517" t="n">
-        <v>20.2659492492676</v>
+        <v>20.2659473419189</v>
       </c>
       <c r="H517" t="n">
         <v>876136</v>
@@ -15391,7 +15391,7 @@
         <v>22.2399997711182</v>
       </c>
       <c r="G518" t="n">
-        <v>20.4684238433838</v>
+        <v>20.4684219360352</v>
       </c>
       <c r="H518" t="n">
         <v>324669</v>
@@ -15449,7 +15449,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G520" t="n">
-        <v>20.4868278503418</v>
+        <v>20.4868297576904</v>
       </c>
       <c r="H520" t="n">
         <v>710973</v>
@@ -15565,7 +15565,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G524" t="n">
-        <v>20.1739139556885</v>
+        <v>20.1739120483398</v>
       </c>
       <c r="H524" t="n">
         <v>499386</v>
@@ -15594,7 +15594,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G525" t="n">
-        <v>20.94700050354</v>
+        <v>20.9470024108887</v>
       </c>
       <c r="H525" t="n">
         <v>908844</v>
@@ -15623,7 +15623,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G526" t="n">
-        <v>21.7569026947021</v>
+        <v>21.7569007873535</v>
       </c>
       <c r="H526" t="n">
         <v>1540488</v>
@@ -15652,7 +15652,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G527" t="n">
-        <v>21.2967319488525</v>
+        <v>21.2967300415039</v>
       </c>
       <c r="H527" t="n">
         <v>604201</v>
@@ -15681,7 +15681,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>21.2599182128906</v>
+        <v>21.259916305542</v>
       </c>
       <c r="H528" t="n">
         <v>954306</v>
@@ -15710,7 +15710,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>21.2599182128906</v>
+        <v>21.259916305542</v>
       </c>
       <c r="H529" t="n">
         <v>726158</v>
@@ -15739,7 +15739,7 @@
         <v>23.2199993133545</v>
       </c>
       <c r="G530" t="n">
-        <v>21.3703556060791</v>
+        <v>21.3703575134277</v>
       </c>
       <c r="H530" t="n">
         <v>398389</v>
@@ -15942,7 +15942,7 @@
         <v>22.1100006103516</v>
       </c>
       <c r="G537" t="n">
-        <v>20.3487796783447</v>
+        <v>20.3487777709961</v>
       </c>
       <c r="H537" t="n">
         <v>482372</v>
@@ -15971,7 +15971,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G538" t="n">
-        <v>20.6340827941895</v>
+        <v>20.6340847015381</v>
       </c>
       <c r="H538" t="n">
         <v>440448</v>
@@ -16029,7 +16029,7 @@
         <v>21.4300003051758</v>
       </c>
       <c r="G540" t="n">
-        <v>19.7229442596436</v>
+        <v>19.7229461669922</v>
       </c>
       <c r="H540" t="n">
         <v>544614</v>
@@ -16203,7 +16203,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G546" t="n">
-        <v>20.6340827941895</v>
+        <v>20.6340847015381</v>
       </c>
       <c r="H546" t="n">
         <v>184115</v>
@@ -16290,7 +16290,7 @@
         <v>23.0300006866455</v>
       </c>
       <c r="G549" t="n">
-        <v>21.1954936981201</v>
+        <v>21.1954956054688</v>
       </c>
       <c r="H549" t="n">
         <v>479582</v>
@@ -16319,7 +16319,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G550" t="n">
-        <v>20.9285907745361</v>
+        <v>20.9285926818848</v>
       </c>
       <c r="H550" t="n">
         <v>308603</v>
@@ -16377,7 +16377,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G552" t="n">
-        <v>20.8365573883057</v>
+        <v>20.8365592956543</v>
       </c>
       <c r="H552" t="n">
         <v>218015</v>
@@ -16406,7 +16406,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G553" t="n">
-        <v>21.2967319488525</v>
+        <v>21.2967300415039</v>
       </c>
       <c r="H553" t="n">
         <v>2496511</v>
@@ -16435,7 +16435,7 @@
         <v>23.4699993133545</v>
       </c>
       <c r="G554" t="n">
-        <v>21.6004447937012</v>
+        <v>21.6004428863525</v>
       </c>
       <c r="H554" t="n">
         <v>754894</v>
@@ -16551,7 +16551,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>20.109489440918</v>
+        <v>20.1094875335693</v>
       </c>
       <c r="H558" t="n">
         <v>598799</v>
@@ -16580,7 +16580,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>19.9714374542236</v>
+        <v>19.9714393615723</v>
       </c>
       <c r="H559" t="n">
         <v>860738</v>
@@ -16638,7 +16638,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G561" t="n">
-        <v>19.9990463256836</v>
+        <v>19.9990482330322</v>
       </c>
       <c r="H561" t="n">
         <v>740982</v>
@@ -16667,7 +16667,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>20.109489440918</v>
+        <v>20.1094875335693</v>
       </c>
       <c r="H562" t="n">
         <v>392838</v>
@@ -16812,7 +16812,7 @@
         <v>22.6800003051758</v>
       </c>
       <c r="G567" t="n">
-        <v>20.8733730316162</v>
+        <v>20.8733749389648</v>
       </c>
       <c r="H567" t="n">
         <v>588294</v>
@@ -16841,7 +16841,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G568" t="n">
-        <v>20.5236415863037</v>
+        <v>20.5236434936523</v>
       </c>
       <c r="H568" t="n">
         <v>305669</v>
@@ -16957,7 +16957,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G572" t="n">
-        <v>20.3027610778809</v>
+        <v>20.3027591705322</v>
       </c>
       <c r="H572" t="n">
         <v>439174</v>
@@ -16986,7 +16986,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>20.385591506958</v>
+        <v>20.3855895996094</v>
       </c>
       <c r="H573" t="n">
         <v>275874</v>
@@ -17015,7 +17015,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G574" t="n">
-        <v>20.6340827941895</v>
+        <v>20.6340847015381</v>
       </c>
       <c r="H574" t="n">
         <v>432527</v>
@@ -17044,7 +17044,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G575" t="n">
-        <v>20.64328956604</v>
+        <v>20.6432876586914</v>
       </c>
       <c r="H575" t="n">
         <v>199750</v>
@@ -17073,7 +17073,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>20.6156787872314</v>
+        <v>20.6156749725342</v>
       </c>
       <c r="H576" t="n">
         <v>263654</v>
@@ -17160,7 +17160,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>20.385591506958</v>
+        <v>20.3855895996094</v>
       </c>
       <c r="H579" t="n">
         <v>939126</v>
@@ -17189,7 +17189,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G580" t="n">
-        <v>20.3947925567627</v>
+        <v>20.3947944641113</v>
       </c>
       <c r="H580" t="n">
         <v>589931</v>
@@ -17276,7 +17276,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G583" t="n">
-        <v>21.2046966552734</v>
+        <v>21.2046985626221</v>
       </c>
       <c r="H583" t="n">
         <v>434729</v>
@@ -17305,7 +17305,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>21.2783241271973</v>
+        <v>21.2783260345459</v>
       </c>
       <c r="H584" t="n">
         <v>190641</v>
@@ -17392,7 +17392,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>21.5360202789307</v>
+        <v>21.536018371582</v>
       </c>
       <c r="H587" t="n">
         <v>858748</v>
@@ -17421,7 +17421,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>21.5360202789307</v>
+        <v>21.536018371582</v>
       </c>
       <c r="H588" t="n">
         <v>693444</v>
@@ -17450,7 +17450,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G589" t="n">
-        <v>21.7937145233154</v>
+        <v>21.7937164306641</v>
       </c>
       <c r="H589" t="n">
         <v>611824</v>
@@ -17508,7 +17508,7 @@
         <v>24.5</v>
       </c>
       <c r="G591" t="n">
-        <v>22.5483989715576</v>
+        <v>22.548397064209</v>
       </c>
       <c r="H591" t="n">
         <v>1072195</v>
@@ -17537,7 +17537,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G592" t="n">
-        <v>22.419548034668</v>
+        <v>22.4195499420166</v>
       </c>
       <c r="H592" t="n">
         <v>493451</v>
@@ -17566,7 +17566,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G593" t="n">
-        <v>22.2078704833984</v>
+        <v>22.2078685760498</v>
       </c>
       <c r="H593" t="n">
         <v>551639</v>
@@ -17595,7 +17595,7 @@
         <v>24.5200004577637</v>
       </c>
       <c r="G594" t="n">
-        <v>22.5668029785156</v>
+        <v>22.5668048858643</v>
       </c>
       <c r="H594" t="n">
         <v>527263</v>
@@ -17624,7 +17624,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G595" t="n">
-        <v>22.8797225952148</v>
+        <v>22.8797206878662</v>
       </c>
       <c r="H595" t="n">
         <v>677550</v>
@@ -17653,7 +17653,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G596" t="n">
-        <v>22.7416687011719</v>
+        <v>22.7416706085205</v>
       </c>
       <c r="H596" t="n">
         <v>747463</v>
@@ -17682,7 +17682,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>22.6404342651367</v>
+        <v>22.6404323577881</v>
       </c>
       <c r="H597" t="n">
         <v>903419</v>
@@ -17711,7 +17711,7 @@
         <v>24.5699996948242</v>
       </c>
       <c r="G598" t="n">
-        <v>22.6128196716309</v>
+        <v>22.6128215789795</v>
       </c>
       <c r="H598" t="n">
         <v>293934</v>
@@ -17769,7 +17769,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>22.9165344238281</v>
+        <v>22.9165325164795</v>
       </c>
       <c r="H600" t="n">
         <v>543073</v>
@@ -17798,7 +17798,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G601" t="n">
-        <v>22.6864471435547</v>
+        <v>22.6864452362061</v>
       </c>
       <c r="H601" t="n">
         <v>481261</v>
@@ -17856,7 +17856,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G603" t="n">
-        <v>22.833703994751</v>
+        <v>22.8337020874023</v>
       </c>
       <c r="H603" t="n">
         <v>232191</v>
@@ -17885,7 +17885,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G604" t="n">
-        <v>22.7692775726318</v>
+        <v>22.7692794799805</v>
       </c>
       <c r="H604" t="n">
         <v>300428</v>
@@ -17972,7 +17972,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>22.9165344238281</v>
+        <v>22.9165325164795</v>
       </c>
       <c r="H607" t="n">
         <v>378581</v>
@@ -18059,7 +18059,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>23.4118728637695</v>
+        <v>23.4118766784668</v>
       </c>
       <c r="H610" t="n">
         <v>373820</v>
@@ -18175,7 +18175,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G614" t="n">
-        <v>22.3557720184326</v>
+        <v>22.355770111084</v>
       </c>
       <c r="H614" t="n">
         <v>700947</v>
@@ -18204,7 +18204,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>22.6174602508545</v>
+        <v>22.6174621582031</v>
       </c>
       <c r="H615" t="n">
         <v>501155</v>
@@ -18291,7 +18291,7 @@
         <v>24.8199996948242</v>
       </c>
       <c r="G618" t="n">
-        <v>23.1969165802002</v>
+        <v>23.1969146728516</v>
       </c>
       <c r="H618" t="n">
         <v>302280</v>
@@ -18436,7 +18436,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G623" t="n">
-        <v>23.1595325469971</v>
+        <v>23.1595344543457</v>
       </c>
       <c r="H623" t="n">
         <v>393598</v>
@@ -18523,7 +18523,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G626" t="n">
-        <v>23.3838367462158</v>
+        <v>23.3838386535645</v>
       </c>
       <c r="H626" t="n">
         <v>354528</v>
@@ -18581,7 +18581,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G628" t="n">
-        <v>23.2623386383057</v>
+        <v>23.262336730957</v>
       </c>
       <c r="H628" t="n">
         <v>200051</v>
@@ -18610,7 +18610,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G629" t="n">
-        <v>22.9258804321289</v>
+        <v>22.9258823394775</v>
       </c>
       <c r="H629" t="n">
         <v>273653</v>
@@ -18639,7 +18639,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G630" t="n">
-        <v>20.9912452697754</v>
+        <v>20.991247177124</v>
       </c>
       <c r="H630" t="n">
         <v>3551454</v>
@@ -18755,7 +18755,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G634" t="n">
-        <v>19.7388763427734</v>
+        <v>19.7388744354248</v>
       </c>
       <c r="H634" t="n">
         <v>776810</v>
@@ -18813,7 +18813,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G636" t="n">
-        <v>19.3089561462402</v>
+        <v>19.3089580535889</v>
       </c>
       <c r="H636" t="n">
         <v>671130</v>
@@ -18842,7 +18842,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>19.533260345459</v>
+        <v>19.5332622528076</v>
       </c>
       <c r="H637" t="n">
         <v>512477</v>
@@ -18871,7 +18871,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G638" t="n">
-        <v>19.4958782196045</v>
+        <v>19.4958763122559</v>
       </c>
       <c r="H638" t="n">
         <v>703698</v>
@@ -18929,7 +18929,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G640" t="n">
-        <v>19.0285758972168</v>
+        <v>19.0285739898682</v>
       </c>
       <c r="H640" t="n">
         <v>403933</v>
@@ -18958,7 +18958,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G641" t="n">
-        <v>18.6266937255859</v>
+        <v>18.6266956329346</v>
       </c>
       <c r="H641" t="n">
         <v>874180</v>
@@ -19132,7 +19132,7 @@
         <v>19.9050006866455</v>
       </c>
       <c r="G647" t="n">
-        <v>18.603328704834</v>
+        <v>18.6033306121826</v>
       </c>
       <c r="H647" t="n">
         <v>410650</v>
@@ -19161,7 +19161,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G648" t="n">
-        <v>18.6360416412354</v>
+        <v>18.6360397338867</v>
       </c>
       <c r="H648" t="n">
         <v>360124</v>
@@ -19190,7 +19190,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G649" t="n">
-        <v>18.7949237823486</v>
+        <v>18.794921875</v>
       </c>
       <c r="H649" t="n">
         <v>502386</v>
@@ -19219,7 +19219,7 @@
         <v>20.0900001525879</v>
       </c>
       <c r="G650" t="n">
-        <v>18.7762298583984</v>
+        <v>18.7762317657471</v>
       </c>
       <c r="H650" t="n">
         <v>526322</v>
@@ -19248,7 +19248,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G651" t="n">
-        <v>18.7201538085938</v>
+        <v>18.7201557159424</v>
       </c>
       <c r="H651" t="n">
         <v>386178</v>
@@ -19306,7 +19306,7 @@
         <v>19.875</v>
       </c>
       <c r="G653" t="n">
-        <v>18.5752906799316</v>
+        <v>18.575288772583</v>
       </c>
       <c r="H653" t="n">
         <v>336549</v>
@@ -19335,7 +19335,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G654" t="n">
-        <v>18.3930416107178</v>
+        <v>18.3930435180664</v>
       </c>
       <c r="H654" t="n">
         <v>659845</v>
@@ -19364,7 +19364,7 @@
         <v>19.8250007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>18.5285625457764</v>
+        <v>18.5285606384277</v>
       </c>
       <c r="H655" t="n">
         <v>472136</v>
@@ -19393,7 +19393,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G656" t="n">
-        <v>18.495849609375</v>
+        <v>18.4958515167236</v>
       </c>
       <c r="H656" t="n">
         <v>454046</v>
@@ -19451,7 +19451,7 @@
         <v>19.6749992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>18.3883686065674</v>
+        <v>18.388370513916</v>
       </c>
       <c r="H658" t="n">
         <v>425030</v>
@@ -19480,7 +19480,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G659" t="n">
-        <v>18.4911766052246</v>
+        <v>18.491174697876</v>
       </c>
       <c r="H659" t="n">
         <v>448603</v>
@@ -19509,7 +19509,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G660" t="n">
-        <v>18.2435054779053</v>
+        <v>18.2435073852539</v>
       </c>
       <c r="H660" t="n">
         <v>1645512</v>
@@ -19596,7 +19596,7 @@
         <v>19.375</v>
       </c>
       <c r="G663" t="n">
-        <v>18.1079883575439</v>
+        <v>18.1079864501953</v>
       </c>
       <c r="H663" t="n">
         <v>697033</v>
@@ -19625,7 +19625,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G664" t="n">
-        <v>18.495849609375</v>
+        <v>18.4958515167236</v>
       </c>
       <c r="H664" t="n">
         <v>590871</v>
@@ -19683,7 +19683,7 @@
         <v>20.0699996948242</v>
       </c>
       <c r="G666" t="n">
-        <v>18.7575378417969</v>
+        <v>18.7575359344482</v>
       </c>
       <c r="H666" t="n">
         <v>247098</v>
@@ -19712,7 +19712,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G667" t="n">
-        <v>18.7294998168945</v>
+        <v>18.7295017242432</v>
       </c>
       <c r="H667" t="n">
         <v>363161</v>
@@ -19770,7 +19770,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G669" t="n">
-        <v>18.7201538085938</v>
+        <v>18.7201557159424</v>
       </c>
       <c r="H669" t="n">
         <v>247847</v>
@@ -19799,7 +19799,7 @@
         <v>19.7849998474121</v>
       </c>
       <c r="G670" t="n">
-        <v>18.4911766052246</v>
+        <v>18.491174697876</v>
       </c>
       <c r="H670" t="n">
         <v>378568</v>
@@ -19828,7 +19828,7 @@
         <v>19.5550003051758</v>
       </c>
       <c r="G671" t="n">
-        <v>18.2762184143066</v>
+        <v>18.276216506958</v>
       </c>
       <c r="H671" t="n">
         <v>210250</v>
@@ -19857,7 +19857,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G672" t="n">
-        <v>18.2528533935547</v>
+        <v>18.2528514862061</v>
       </c>
       <c r="H672" t="n">
         <v>202041</v>
@@ -19886,7 +19886,7 @@
         <v>19.4850006103516</v>
       </c>
       <c r="G673" t="n">
-        <v>18.2107944488525</v>
+        <v>18.2107963562012</v>
       </c>
       <c r="H673" t="n">
         <v>377383</v>
@@ -19915,7 +19915,7 @@
         <v>19.6650009155273</v>
       </c>
       <c r="G674" t="n">
-        <v>18.3790245056152</v>
+        <v>18.3790264129639</v>
       </c>
       <c r="H674" t="n">
         <v>356019</v>
@@ -19944,7 +19944,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G675" t="n">
-        <v>19.1407279968262</v>
+        <v>19.1407241821289</v>
       </c>
       <c r="H675" t="n">
         <v>1646978</v>
@@ -19973,7 +19973,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>19.4398002624512</v>
+        <v>19.4397983551025</v>
       </c>
       <c r="H676" t="n">
         <v>781937</v>
@@ -20118,7 +20118,7 @@
         <v>20.5</v>
       </c>
       <c r="G681" t="n">
-        <v>19.1594181060791</v>
+        <v>19.1594200134277</v>
       </c>
       <c r="H681" t="n">
         <v>262991</v>
@@ -20176,7 +20176,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>19.1126880645752</v>
+        <v>19.1126899719238</v>
       </c>
       <c r="H683" t="n">
         <v>405539</v>
@@ -20205,7 +20205,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G684" t="n">
-        <v>19.0939960479736</v>
+        <v>19.0939979553223</v>
       </c>
       <c r="H684" t="n">
         <v>440556</v>
@@ -20234,7 +20234,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G685" t="n">
-        <v>18.7388458251953</v>
+        <v>18.7388439178467</v>
       </c>
       <c r="H685" t="n">
         <v>362000</v>
@@ -20263,7 +20263,7 @@
         <v>20.5</v>
       </c>
       <c r="G686" t="n">
-        <v>19.1594181060791</v>
+        <v>19.1594200134277</v>
       </c>
       <c r="H686" t="n">
         <v>375929</v>
@@ -20321,7 +20321,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G688" t="n">
-        <v>18.8416519165039</v>
+        <v>18.8416538238525</v>
       </c>
       <c r="H688" t="n">
         <v>335800</v>
@@ -20379,7 +20379,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>19.2528820037842</v>
+        <v>19.2528800964355</v>
       </c>
       <c r="H690" t="n">
         <v>521428</v>
@@ -20408,7 +20408,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G691" t="n">
-        <v>19.5239162445068</v>
+        <v>19.5239124298096</v>
       </c>
       <c r="H691" t="n">
         <v>181397</v>
@@ -20437,7 +20437,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G692" t="n">
-        <v>19.4211082458496</v>
+        <v>19.4211101531982</v>
       </c>
       <c r="H692" t="n">
         <v>207950</v>
@@ -20466,7 +20466,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>19.8136425018311</v>
+        <v>19.8136444091797</v>
       </c>
       <c r="H693" t="n">
         <v>277253</v>
@@ -20495,7 +20495,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G694" t="n">
-        <v>20.0753307342529</v>
+        <v>20.0753326416016</v>
       </c>
       <c r="H694" t="n">
         <v>493504</v>
@@ -20524,7 +20524,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G695" t="n">
-        <v>19.7482204437256</v>
+        <v>19.748218536377</v>
       </c>
       <c r="H695" t="n">
         <v>450623</v>
@@ -20611,7 +20611,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>19.7669124603271</v>
+        <v>19.7669143676758</v>
       </c>
       <c r="H698" t="n">
         <v>331792</v>
@@ -20698,7 +20698,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G701" t="n">
-        <v>19.2809181213379</v>
+        <v>19.2809162139893</v>
       </c>
       <c r="H701" t="n">
         <v>334676</v>
@@ -20756,7 +20756,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G703" t="n">
-        <v>18.8977279663086</v>
+        <v>18.8977298736572</v>
       </c>
       <c r="H703" t="n">
         <v>336450</v>
@@ -20814,7 +20814,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G705" t="n">
-        <v>18.804271697998</v>
+        <v>18.8042678833008</v>
       </c>
       <c r="H705" t="n">
         <v>237961</v>
@@ -20843,7 +20843,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>18.8790378570557</v>
+        <v>18.8790397644043</v>
       </c>
       <c r="H706" t="n">
         <v>303793</v>
@@ -20930,7 +20930,7 @@
         <v>19.1049995422363</v>
       </c>
       <c r="G709" t="n">
-        <v>17.8556442260742</v>
+        <v>17.8556423187256</v>
       </c>
       <c r="H709" t="n">
         <v>1289181</v>
@@ -20988,7 +20988,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G711" t="n">
-        <v>17.1546897888184</v>
+        <v>17.1546878814697</v>
       </c>
       <c r="H711" t="n">
         <v>1871086</v>
@@ -21046,7 +21046,7 @@
         